--- a/artfynd/A 58548-2022 artfynd.xlsx
+++ b/artfynd/A 58548-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 58548-2022 artfynd.xlsx
+++ b/artfynd/A 58548-2022 artfynd.xlsx
@@ -15797,10 +15797,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>119874609</v>
+        <v>119874666</v>
       </c>
       <c r="B136" t="n">
-        <v>90954</v>
+        <v>74577</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -15809,20 +15809,25 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6040186</v>
+        <v>6426</v>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -15832,10 +15837,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>564083</v>
+        <v>563945</v>
       </c>
       <c r="R136" t="n">
-        <v>6705090</v>
+        <v>6704877</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15894,10 +15899,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>119874666</v>
+        <v>119874641</v>
       </c>
       <c r="B137" t="n">
-        <v>74577</v>
+        <v>97907</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -15906,38 +15911,47 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>6426</v>
+        <v>220787</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I137" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P137" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>563945</v>
+        <v>563808</v>
       </c>
       <c r="R137" t="n">
-        <v>6704877</v>
+        <v>6704697</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15996,10 +16010,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>119874641</v>
+        <v>119874609</v>
       </c>
       <c r="B138" t="n">
-        <v>97907</v>
+        <v>90954</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -16008,47 +16022,33 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I138" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J138" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>563808</v>
+        <v>564083</v>
       </c>
       <c r="R138" t="n">
-        <v>6704697</v>
+        <v>6705090</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -18672,10 +18672,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>119874678</v>
+        <v>119874622</v>
       </c>
       <c r="B163" t="n">
-        <v>5169</v>
+        <v>97907</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -18684,31 +18684,35 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I163" t="inlineStr"/>
-      <c r="M163" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P163" t="inlineStr">
@@ -18717,10 +18721,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>563957</v>
+        <v>563711</v>
       </c>
       <c r="R163" t="n">
-        <v>6704878</v>
+        <v>6704677</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -18779,7 +18783,7 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>119874622</v>
+        <v>119874632</v>
       </c>
       <c r="B164" t="n">
         <v>97907</v>
@@ -18814,7 +18818,7 @@
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
@@ -18828,10 +18832,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>563711</v>
+        <v>563770</v>
       </c>
       <c r="R164" t="n">
-        <v>6704677</v>
+        <v>6704729</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -18890,10 +18894,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>119874632</v>
+        <v>119874678</v>
       </c>
       <c r="B165" t="n">
-        <v>97907</v>
+        <v>5169</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -18902,35 +18906,31 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I165" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J165" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr"/>
+      <c r="M165" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P165" t="inlineStr">
@@ -18939,10 +18939,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>563770</v>
+        <v>563957</v>
       </c>
       <c r="R165" t="n">
-        <v>6704729</v>
+        <v>6704878</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -19547,10 +19547,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>119874596</v>
+        <v>119874571</v>
       </c>
       <c r="B171" t="n">
-        <v>57463</v>
+        <v>90562</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
@@ -19563,46 +19563,34 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I171" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K171" t="inlineStr"/>
-      <c r="L171" t="inlineStr"/>
-      <c r="M171" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N171" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr"/>
       <c r="P171" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>563633</v>
+        <v>563816</v>
       </c>
       <c r="R171" t="n">
-        <v>6704498</v>
+        <v>6704792</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -19661,10 +19649,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>119874571</v>
+        <v>119874597</v>
       </c>
       <c r="B172" t="n">
-        <v>90562</v>
+        <v>91494</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
@@ -19673,25 +19661,25 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>1202</v>
+        <v>4769</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -19701,10 +19689,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>563816</v>
+        <v>563943</v>
       </c>
       <c r="R172" t="n">
-        <v>6704792</v>
+        <v>6704878</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -19763,10 +19751,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>119874597</v>
+        <v>119874596</v>
       </c>
       <c r="B173" t="n">
-        <v>91494</v>
+        <v>57463</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
@@ -19775,38 +19763,50 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>4769</v>
+        <v>103021</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I173" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K173" t="inlineStr"/>
+      <c r="L173" t="inlineStr"/>
+      <c r="M173" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N173" t="inlineStr"/>
       <c r="P173" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>563943</v>
+        <v>563633</v>
       </c>
       <c r="R173" t="n">
-        <v>6704878</v>
+        <v>6704498</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -22657,10 +22657,10 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>119874682</v>
+        <v>119874612</v>
       </c>
       <c r="B200" t="n">
-        <v>5169</v>
+        <v>97907</v>
       </c>
       <c r="C200" t="inlineStr">
         <is>
@@ -22669,43 +22669,54 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I200" t="inlineStr"/>
-      <c r="M200" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J200" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L200" t="inlineStr"/>
+      <c r="N200" t="inlineStr"/>
       <c r="P200" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>564000</v>
+        <v>564201</v>
       </c>
       <c r="R200" t="n">
-        <v>6704958</v>
+        <v>6705191</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -22740,12 +22751,18 @@
           <t>2024-09-20</t>
         </is>
       </c>
+      <c r="AC200" t="inlineStr">
+        <is>
+          <t>1 blomstjälk</t>
+        </is>
+      </c>
       <c r="AD200" t="b">
         <v>0</v>
       </c>
       <c r="AE200" t="b">
         <v>0</v>
       </c>
+      <c r="AF200" t="inlineStr"/>
       <c r="AG200" t="b">
         <v>0</v>
       </c>
@@ -22764,7 +22781,7 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>119874612</v>
+        <v>119874627</v>
       </c>
       <c r="B201" t="n">
         <v>97907</v>
@@ -22799,7 +22816,7 @@
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">
@@ -22820,10 +22837,10 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>564201</v>
+        <v>563813</v>
       </c>
       <c r="R201" t="n">
-        <v>6705191</v>
+        <v>6704796</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -22860,7 +22877,7 @@
       </c>
       <c r="AC201" t="inlineStr">
         <is>
-          <t>1 blomstjälk</t>
+          <t>2 blomstjälkar</t>
         </is>
       </c>
       <c r="AD201" t="b">
@@ -22888,10 +22905,10 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>119874627</v>
+        <v>119874682</v>
       </c>
       <c r="B202" t="n">
-        <v>97907</v>
+        <v>5169</v>
       </c>
       <c r="C202" t="inlineStr">
         <is>
@@ -22900,54 +22917,43 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E202" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I202" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J202" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K202" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L202" t="inlineStr"/>
-      <c r="N202" t="inlineStr"/>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr"/>
+      <c r="M202" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P202" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>563813</v>
+        <v>564000</v>
       </c>
       <c r="R202" t="n">
-        <v>6704796</v>
+        <v>6704958</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -22982,18 +22988,12 @@
           <t>2024-09-20</t>
         </is>
       </c>
-      <c r="AC202" t="inlineStr">
-        <is>
-          <t>2 blomstjälkar</t>
-        </is>
-      </c>
       <c r="AD202" t="b">
         <v>0</v>
       </c>
       <c r="AE202" t="b">
         <v>0</v>
       </c>
-      <c r="AF202" t="inlineStr"/>
       <c r="AG202" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 58548-2022 artfynd.xlsx
+++ b/artfynd/A 58548-2022 artfynd.xlsx
@@ -19547,10 +19547,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>119874571</v>
+        <v>119874596</v>
       </c>
       <c r="B171" t="n">
-        <v>90562</v>
+        <v>57463</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
@@ -19563,34 +19563,46 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I171" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr"/>
+      <c r="L171" t="inlineStr"/>
+      <c r="M171" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N171" t="inlineStr"/>
       <c r="P171" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>563816</v>
+        <v>563633</v>
       </c>
       <c r="R171" t="n">
-        <v>6704792</v>
+        <v>6704498</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -19649,10 +19661,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>119874597</v>
+        <v>119874571</v>
       </c>
       <c r="B172" t="n">
-        <v>91494</v>
+        <v>90562</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
@@ -19661,25 +19673,25 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>4769</v>
+        <v>1202</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -19689,10 +19701,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>563943</v>
+        <v>563816</v>
       </c>
       <c r="R172" t="n">
-        <v>6704878</v>
+        <v>6704792</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -19751,10 +19763,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>119874596</v>
+        <v>119874597</v>
       </c>
       <c r="B173" t="n">
-        <v>57463</v>
+        <v>91494</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
@@ -19763,50 +19775,38 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>103021</v>
+        <v>4769</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I173" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K173" t="inlineStr"/>
-      <c r="L173" t="inlineStr"/>
-      <c r="M173" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N173" t="inlineStr"/>
+          <t>(Scop.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr"/>
       <c r="P173" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>563633</v>
+        <v>563943</v>
       </c>
       <c r="R173" t="n">
-        <v>6704498</v>
+        <v>6704878</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -19865,10 +19865,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>119874668</v>
+        <v>119874588</v>
       </c>
       <c r="B174" t="n">
-        <v>74577</v>
+        <v>90562</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
@@ -19877,25 +19877,25 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>6426</v>
+        <v>1202</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
@@ -19905,10 +19905,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>563937</v>
+        <v>564011</v>
       </c>
       <c r="R174" t="n">
-        <v>6704867</v>
+        <v>6705060</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -19967,10 +19967,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>119874588</v>
+        <v>119874668</v>
       </c>
       <c r="B175" t="n">
-        <v>90562</v>
+        <v>74577</v>
       </c>
       <c r="C175" t="inlineStr">
         <is>
@@ -19979,25 +19979,25 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>1202</v>
+        <v>6426</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
@@ -20007,10 +20007,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>564011</v>
+        <v>563937</v>
       </c>
       <c r="R175" t="n">
-        <v>6705060</v>
+        <v>6704867</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -20615,10 +20615,10 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>119874573</v>
+        <v>119874680</v>
       </c>
       <c r="B181" t="n">
-        <v>90562</v>
+        <v>5169</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
@@ -20627,38 +20627,43 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
+      <c r="M181" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P181" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>563794</v>
+        <v>563792</v>
       </c>
       <c r="R181" t="n">
-        <v>6704792</v>
+        <v>6704694</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -20717,10 +20722,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>119874569</v>
+        <v>119874649</v>
       </c>
       <c r="B182" t="n">
-        <v>90562</v>
+        <v>97907</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
@@ -20729,38 +20734,47 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I182" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J182" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P182" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>564137</v>
+        <v>563765</v>
       </c>
       <c r="R182" t="n">
-        <v>6705071</v>
+        <v>6704626</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -20819,10 +20833,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>119874680</v>
+        <v>119874613</v>
       </c>
       <c r="B183" t="n">
-        <v>5169</v>
+        <v>97907</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
@@ -20831,31 +20845,35 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I183" t="inlineStr"/>
-      <c r="M183" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P183" t="inlineStr">
@@ -20864,10 +20882,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>563792</v>
+        <v>563794</v>
       </c>
       <c r="R183" t="n">
-        <v>6704694</v>
+        <v>6704750</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -20926,10 +20944,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>119874649</v>
+        <v>119874573</v>
       </c>
       <c r="B184" t="n">
-        <v>97907</v>
+        <v>90562</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
@@ -20938,47 +20956,38 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I184" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J184" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr"/>
       <c r="P184" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>563765</v>
+        <v>563794</v>
       </c>
       <c r="R184" t="n">
-        <v>6704626</v>
+        <v>6704792</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -21037,10 +21046,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>119874613</v>
+        <v>119874569</v>
       </c>
       <c r="B185" t="n">
-        <v>97907</v>
+        <v>90562</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
@@ -21049,47 +21058,38 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I185" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J185" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr"/>
       <c r="P185" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>563794</v>
+        <v>564137</v>
       </c>
       <c r="R185" t="n">
-        <v>6704750</v>
+        <v>6705071</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -21796,10 +21796,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>119874572</v>
+        <v>119874625</v>
       </c>
       <c r="B192" t="n">
-        <v>90562</v>
+        <v>97907</v>
       </c>
       <c r="C192" t="inlineStr">
         <is>
@@ -21808,38 +21808,47 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E192" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I192" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J192" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P192" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>563815</v>
+        <v>564201</v>
       </c>
       <c r="R192" t="n">
-        <v>6704789</v>
+        <v>6705184</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -21898,10 +21907,10 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>119874583</v>
+        <v>119874647</v>
       </c>
       <c r="B193" t="n">
-        <v>90562</v>
+        <v>97907</v>
       </c>
       <c r="C193" t="inlineStr">
         <is>
@@ -21910,38 +21919,54 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I193" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J193" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L193" t="inlineStr"/>
+      <c r="N193" t="inlineStr"/>
       <c r="P193" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>563996</v>
+        <v>564036</v>
       </c>
       <c r="R193" t="n">
-        <v>6705007</v>
+        <v>6705043</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -21976,12 +22001,18 @@
           <t>2024-09-20</t>
         </is>
       </c>
+      <c r="AC193" t="inlineStr">
+        <is>
+          <t>1 blomstjälk</t>
+        </is>
+      </c>
       <c r="AD193" t="b">
         <v>0</v>
       </c>
       <c r="AE193" t="b">
         <v>0</v>
       </c>
+      <c r="AF193" t="inlineStr"/>
       <c r="AG193" t="b">
         <v>0</v>
       </c>
@@ -22000,10 +22031,10 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>119874575</v>
+        <v>119874618</v>
       </c>
       <c r="B194" t="n">
-        <v>90562</v>
+        <v>97907</v>
       </c>
       <c r="C194" t="inlineStr">
         <is>
@@ -22012,38 +22043,47 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I194" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J194" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P194" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>563720</v>
+        <v>564168</v>
       </c>
       <c r="R194" t="n">
-        <v>6704700</v>
+        <v>6705183</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -22102,10 +22142,10 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>119874625</v>
+        <v>119874572</v>
       </c>
       <c r="B195" t="n">
-        <v>97907</v>
+        <v>90562</v>
       </c>
       <c r="C195" t="inlineStr">
         <is>
@@ -22114,47 +22154,38 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I195" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J195" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr"/>
       <c r="P195" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>564201</v>
+        <v>563815</v>
       </c>
       <c r="R195" t="n">
-        <v>6705184</v>
+        <v>6704789</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -22213,10 +22244,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>119874647</v>
+        <v>119874583</v>
       </c>
       <c r="B196" t="n">
-        <v>97907</v>
+        <v>90562</v>
       </c>
       <c r="C196" t="inlineStr">
         <is>
@@ -22225,54 +22256,38 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E196" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I196" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J196" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K196" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L196" t="inlineStr"/>
-      <c r="N196" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr"/>
       <c r="P196" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>564036</v>
+        <v>563996</v>
       </c>
       <c r="R196" t="n">
-        <v>6705043</v>
+        <v>6705007</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -22307,18 +22322,12 @@
           <t>2024-09-20</t>
         </is>
       </c>
-      <c r="AC196" t="inlineStr">
-        <is>
-          <t>1 blomstjälk</t>
-        </is>
-      </c>
       <c r="AD196" t="b">
         <v>0</v>
       </c>
       <c r="AE196" t="b">
         <v>0</v>
       </c>
-      <c r="AF196" t="inlineStr"/>
       <c r="AG196" t="b">
         <v>0</v>
       </c>
@@ -22337,10 +22346,10 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>119874618</v>
+        <v>119874575</v>
       </c>
       <c r="B197" t="n">
-        <v>97907</v>
+        <v>90562</v>
       </c>
       <c r="C197" t="inlineStr">
         <is>
@@ -22349,47 +22358,38 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I197" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J197" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr"/>
       <c r="P197" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>564168</v>
+        <v>563720</v>
       </c>
       <c r="R197" t="n">
-        <v>6705183</v>
+        <v>6704700</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -22657,10 +22657,10 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>119874612</v>
+        <v>119874682</v>
       </c>
       <c r="B200" t="n">
-        <v>97907</v>
+        <v>5169</v>
       </c>
       <c r="C200" t="inlineStr">
         <is>
@@ -22669,54 +22669,43 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I200" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J200" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K200" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L200" t="inlineStr"/>
-      <c r="N200" t="inlineStr"/>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr"/>
+      <c r="M200" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P200" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>564201</v>
+        <v>564000</v>
       </c>
       <c r="R200" t="n">
-        <v>6705191</v>
+        <v>6704958</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -22751,18 +22740,12 @@
           <t>2024-09-20</t>
         </is>
       </c>
-      <c r="AC200" t="inlineStr">
-        <is>
-          <t>1 blomstjälk</t>
-        </is>
-      </c>
       <c r="AD200" t="b">
         <v>0</v>
       </c>
       <c r="AE200" t="b">
         <v>0</v>
       </c>
-      <c r="AF200" t="inlineStr"/>
       <c r="AG200" t="b">
         <v>0</v>
       </c>
@@ -22781,7 +22764,7 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>119874627</v>
+        <v>119874612</v>
       </c>
       <c r="B201" t="n">
         <v>97907</v>
@@ -22816,7 +22799,7 @@
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">
@@ -22837,10 +22820,10 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>563813</v>
+        <v>564201</v>
       </c>
       <c r="R201" t="n">
-        <v>6704796</v>
+        <v>6705191</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -22877,7 +22860,7 @@
       </c>
       <c r="AC201" t="inlineStr">
         <is>
-          <t>2 blomstjälkar</t>
+          <t>1 blomstjälk</t>
         </is>
       </c>
       <c r="AD201" t="b">
@@ -22905,10 +22888,10 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>119874682</v>
+        <v>119874627</v>
       </c>
       <c r="B202" t="n">
-        <v>5169</v>
+        <v>97907</v>
       </c>
       <c r="C202" t="inlineStr">
         <is>
@@ -22917,43 +22900,54 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E202" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I202" t="inlineStr"/>
-      <c r="M202" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J202" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L202" t="inlineStr"/>
+      <c r="N202" t="inlineStr"/>
       <c r="P202" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>564000</v>
+        <v>563813</v>
       </c>
       <c r="R202" t="n">
-        <v>6704958</v>
+        <v>6704796</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -22988,12 +22982,18 @@
           <t>2024-09-20</t>
         </is>
       </c>
+      <c r="AC202" t="inlineStr">
+        <is>
+          <t>2 blomstjälkar</t>
+        </is>
+      </c>
       <c r="AD202" t="b">
         <v>0</v>
       </c>
       <c r="AE202" t="b">
         <v>0</v>
       </c>
+      <c r="AF202" t="inlineStr"/>
       <c r="AG202" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 58548-2022 artfynd.xlsx
+++ b/artfynd/A 58548-2022 artfynd.xlsx
@@ -15695,10 +15695,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>119874582</v>
+        <v>119874617</v>
       </c>
       <c r="B135" t="n">
-        <v>90562</v>
+        <v>97907</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -15707,38 +15707,47 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I135" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P135" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>563958</v>
+        <v>563833</v>
       </c>
       <c r="R135" t="n">
-        <v>6704952</v>
+        <v>6704788</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -15797,10 +15806,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>119874666</v>
+        <v>119874663</v>
       </c>
       <c r="B136" t="n">
-        <v>74577</v>
+        <v>97907</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -15809,38 +15818,47 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6426</v>
+        <v>220787</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I136" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P136" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>563945</v>
+        <v>563835</v>
       </c>
       <c r="R136" t="n">
-        <v>6704877</v>
+        <v>6704743</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15899,7 +15917,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>119874641</v>
+        <v>119874634</v>
       </c>
       <c r="B137" t="n">
         <v>97907</v>
@@ -15948,10 +15966,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>563808</v>
+        <v>563712</v>
       </c>
       <c r="R137" t="n">
-        <v>6704697</v>
+        <v>6704670</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -16010,10 +16028,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>119874609</v>
+        <v>119874583</v>
       </c>
       <c r="B138" t="n">
-        <v>90954</v>
+        <v>90562</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -16026,16 +16044,21 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6040186</v>
+        <v>1202</v>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -16045,10 +16068,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>564083</v>
+        <v>563996</v>
       </c>
       <c r="R138" t="n">
-        <v>6705090</v>
+        <v>6705007</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -16107,10 +16130,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>119874567</v>
+        <v>119874576</v>
       </c>
       <c r="B139" t="n">
-        <v>90905</v>
+        <v>90562</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -16119,25 +16142,25 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>2062</v>
+        <v>1202</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -16147,10 +16170,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>564000</v>
+        <v>563718</v>
       </c>
       <c r="R139" t="n">
-        <v>6705011</v>
+        <v>6704695</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -16209,10 +16232,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>119874568</v>
+        <v>119874605</v>
       </c>
       <c r="B140" t="n">
-        <v>90905</v>
+        <v>90334</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -16221,25 +16244,25 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>2062</v>
+        <v>3215</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -16249,10 +16272,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>563986</v>
+        <v>563929</v>
       </c>
       <c r="R140" t="n">
-        <v>6705032</v>
+        <v>6704878</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -16311,10 +16334,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>119874605</v>
+        <v>119874580</v>
       </c>
       <c r="B141" t="n">
-        <v>90334</v>
+        <v>90562</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -16323,25 +16346,25 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>3215</v>
+        <v>1202</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -16351,10 +16374,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>563929</v>
+        <v>563702</v>
       </c>
       <c r="R141" t="n">
-        <v>6704878</v>
+        <v>6704652</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -16413,10 +16436,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>119874659</v>
+        <v>119874678</v>
       </c>
       <c r="B142" t="n">
-        <v>97907</v>
+        <v>5169</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -16425,35 +16448,31 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I142" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J142" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr"/>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P142" t="inlineStr">
@@ -16462,10 +16481,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>563746</v>
+        <v>563957</v>
       </c>
       <c r="R142" t="n">
-        <v>6704720</v>
+        <v>6704878</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -16759,10 +16778,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>119874566</v>
+        <v>119874569</v>
       </c>
       <c r="B145" t="n">
-        <v>90905</v>
+        <v>90562</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -16771,25 +16790,25 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>2062</v>
+        <v>1202</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -16802,7 +16821,7 @@
         <v>564137</v>
       </c>
       <c r="R145" t="n">
-        <v>6705070</v>
+        <v>6705071</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -16861,10 +16880,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>119874652</v>
+        <v>119874680</v>
       </c>
       <c r="B146" t="n">
-        <v>97907</v>
+        <v>5169</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -16873,35 +16892,31 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I146" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J146" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr"/>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P146" t="inlineStr">
@@ -16910,10 +16925,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>563976</v>
+        <v>563792</v>
       </c>
       <c r="R146" t="n">
-        <v>6704966</v>
+        <v>6704694</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16972,7 +16987,7 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>119874623</v>
+        <v>119874613</v>
       </c>
       <c r="B147" t="n">
         <v>97907</v>
@@ -17007,7 +17022,7 @@
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
@@ -17021,10 +17036,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>563637</v>
+        <v>563794</v>
       </c>
       <c r="R147" t="n">
-        <v>6704477</v>
+        <v>6704750</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -17083,10 +17098,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>119874576</v>
+        <v>119874625</v>
       </c>
       <c r="B148" t="n">
-        <v>90562</v>
+        <v>97907</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -17095,38 +17110,47 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I148" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P148" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>563718</v>
+        <v>564201</v>
       </c>
       <c r="R148" t="n">
-        <v>6704695</v>
+        <v>6705184</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -17185,10 +17209,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>119874577</v>
+        <v>119874661</v>
       </c>
       <c r="B149" t="n">
-        <v>90562</v>
+        <v>97907</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -17197,38 +17221,47 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I149" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P149" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>563703</v>
+        <v>563645</v>
       </c>
       <c r="R149" t="n">
-        <v>6704669</v>
+        <v>6704515</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -17287,10 +17320,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>119874590</v>
+        <v>119874597</v>
       </c>
       <c r="B150" t="n">
-        <v>90562</v>
+        <v>91494</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -17299,25 +17332,25 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>1202</v>
+        <v>4769</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -17327,10 +17360,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>564015</v>
+        <v>563943</v>
       </c>
       <c r="R150" t="n">
-        <v>6705047</v>
+        <v>6704878</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -17389,10 +17422,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>119874651</v>
+        <v>119874596</v>
       </c>
       <c r="B151" t="n">
-        <v>97907</v>
+        <v>57463</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -17401,47 +17434,50 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J151" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr"/>
+      <c r="L151" t="inlineStr"/>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>564256</v>
+        <v>563633</v>
       </c>
       <c r="R151" t="n">
-        <v>6705293</v>
+        <v>6704498</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -17500,7 +17536,7 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>119874630</v>
+        <v>119874615</v>
       </c>
       <c r="B152" t="n">
         <v>97907</v>
@@ -17535,7 +17571,7 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
@@ -17549,10 +17585,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>563815</v>
+        <v>563748</v>
       </c>
       <c r="R152" t="n">
-        <v>6704815</v>
+        <v>6704608</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -17611,10 +17647,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>119874604</v>
+        <v>119874632</v>
       </c>
       <c r="B153" t="n">
-        <v>90334</v>
+        <v>97907</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -17623,38 +17659,47 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>3215</v>
+        <v>220787</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I153" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P153" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>563936</v>
+        <v>563770</v>
       </c>
       <c r="R153" t="n">
-        <v>6704867</v>
+        <v>6704729</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -17713,7 +17758,7 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>119874581</v>
+        <v>119874573</v>
       </c>
       <c r="B154" t="n">
         <v>90562</v>
@@ -17753,10 +17798,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>563792</v>
+        <v>563794</v>
       </c>
       <c r="R154" t="n">
-        <v>6704700</v>
+        <v>6704792</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -17815,10 +17860,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>119874642</v>
+        <v>119874566</v>
       </c>
       <c r="B155" t="n">
-        <v>97907</v>
+        <v>90905</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -17831,43 +17876,34 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>220787</v>
+        <v>2062</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I155" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J155" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>563974</v>
+        <v>564137</v>
       </c>
       <c r="R155" t="n">
-        <v>6704953</v>
+        <v>6705070</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -17926,10 +17962,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>119874615</v>
+        <v>119874677</v>
       </c>
       <c r="B156" t="n">
-        <v>97907</v>
+        <v>93930</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -17938,47 +17974,38 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>220787</v>
+        <v>2383</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bågpraktmossa</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Plagiomnium medium</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I156" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J156" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Bruch &amp; Schimp.) T.J.Kop.</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>563748</v>
+        <v>563925</v>
       </c>
       <c r="R156" t="n">
-        <v>6704608</v>
+        <v>6704880</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -18037,10 +18064,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>119874684</v>
+        <v>119874658</v>
       </c>
       <c r="B157" t="n">
-        <v>100171</v>
+        <v>97907</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -18049,38 +18076,47 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I157" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P157" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>563956</v>
+        <v>563749</v>
       </c>
       <c r="R157" t="n">
-        <v>6704876</v>
+        <v>6704725</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -18139,10 +18175,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>119874607</v>
+        <v>119874641</v>
       </c>
       <c r="B158" t="n">
-        <v>90846</v>
+        <v>97907</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -18151,38 +18187,47 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I158" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P158" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>563821</v>
+        <v>563808</v>
       </c>
       <c r="R158" t="n">
-        <v>6704817</v>
+        <v>6704697</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -18241,10 +18286,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>119874677</v>
+        <v>119874582</v>
       </c>
       <c r="B159" t="n">
-        <v>93930</v>
+        <v>90562</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -18253,25 +18298,25 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>2383</v>
+        <v>1202</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Bågpraktmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Plagiomnium medium</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Bruch &amp; Schimp.) T.J.Kop.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -18281,10 +18326,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>563925</v>
+        <v>563958</v>
       </c>
       <c r="R159" t="n">
-        <v>6704880</v>
+        <v>6704952</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -18343,10 +18388,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>119874606</v>
+        <v>119874567</v>
       </c>
       <c r="B160" t="n">
-        <v>90846</v>
+        <v>90905</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -18355,25 +18400,25 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>658</v>
+        <v>2062</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -18383,10 +18428,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>563784</v>
+        <v>564000</v>
       </c>
       <c r="R160" t="n">
-        <v>6704721</v>
+        <v>6705011</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -18419,11 +18464,6 @@
       <c r="AA160" t="inlineStr">
         <is>
           <t>2024-09-20</t>
-        </is>
-      </c>
-      <c r="AC160" t="inlineStr">
-        <is>
-          <t>Äldre fruktkropp</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -18450,10 +18490,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>119874639</v>
+        <v>119874666</v>
       </c>
       <c r="B161" t="n">
-        <v>97907</v>
+        <v>74577</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -18462,47 +18502,38 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>220787</v>
+        <v>6426</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I161" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J161" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr"/>
       <c r="P161" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>563718</v>
+        <v>563945</v>
       </c>
       <c r="R161" t="n">
-        <v>6704563</v>
+        <v>6704877</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -18561,7 +18592,7 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>119874621</v>
+        <v>119874628</v>
       </c>
       <c r="B162" t="n">
         <v>97907</v>
@@ -18596,7 +18627,7 @@
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
@@ -18610,10 +18641,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>564283</v>
+        <v>564206</v>
       </c>
       <c r="R162" t="n">
-        <v>6705293</v>
+        <v>6705189</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -18672,10 +18703,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>119874622</v>
+        <v>119874585</v>
       </c>
       <c r="B163" t="n">
-        <v>97907</v>
+        <v>90562</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -18684,47 +18715,38 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I163" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J163" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr"/>
       <c r="P163" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>563711</v>
+        <v>563986</v>
       </c>
       <c r="R163" t="n">
-        <v>6704677</v>
+        <v>6705041</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -18783,7 +18805,7 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>119874632</v>
+        <v>119874642</v>
       </c>
       <c r="B164" t="n">
         <v>97907</v>
@@ -18832,10 +18854,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>563770</v>
+        <v>563974</v>
       </c>
       <c r="R164" t="n">
-        <v>6704729</v>
+        <v>6704953</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -18894,10 +18916,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>119874678</v>
+        <v>119874609</v>
       </c>
       <c r="B165" t="n">
-        <v>5169</v>
+        <v>90954</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -18906,43 +18928,33 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>100526</v>
-      </c>
-      <c r="F165" t="inlineStr">
-        <is>
-          <t>Bronshjon</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
-      <c r="M165" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P165" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>563957</v>
+        <v>564083</v>
       </c>
       <c r="R165" t="n">
-        <v>6704878</v>
+        <v>6705090</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -19001,10 +19013,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>119874628</v>
+        <v>119874684</v>
       </c>
       <c r="B166" t="n">
-        <v>97907</v>
+        <v>100171</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -19013,47 +19025,38 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I166" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J166" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr"/>
       <c r="P166" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>564206</v>
+        <v>563956</v>
       </c>
       <c r="R166" t="n">
-        <v>6705189</v>
+        <v>6704876</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -19112,7 +19115,7 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>119874644</v>
+        <v>119874622</v>
       </c>
       <c r="B167" t="n">
         <v>97907</v>
@@ -19147,7 +19150,7 @@
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
@@ -19161,10 +19164,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>563984</v>
+        <v>563711</v>
       </c>
       <c r="R167" t="n">
-        <v>6704957</v>
+        <v>6704677</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -19223,10 +19226,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>119874608</v>
+        <v>119874647</v>
       </c>
       <c r="B168" t="n">
-        <v>94311</v>
+        <v>97907</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
@@ -19235,38 +19238,54 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>2809</v>
+        <v>220787</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
-        </is>
-      </c>
-      <c r="I168" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L168" t="inlineStr"/>
+      <c r="N168" t="inlineStr"/>
       <c r="P168" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>563944</v>
+        <v>564036</v>
       </c>
       <c r="R168" t="n">
-        <v>6704880</v>
+        <v>6705043</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -19301,12 +19320,18 @@
           <t>2024-09-20</t>
         </is>
       </c>
+      <c r="AC168" t="inlineStr">
+        <is>
+          <t>1 blomstjälk</t>
+        </is>
+      </c>
       <c r="AD168" t="b">
         <v>0</v>
       </c>
       <c r="AE168" t="b">
         <v>0</v>
       </c>
+      <c r="AF168" t="inlineStr"/>
       <c r="AG168" t="b">
         <v>0</v>
       </c>
@@ -19325,7 +19350,7 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>119874624</v>
+        <v>119874630</v>
       </c>
       <c r="B169" t="n">
         <v>97907</v>
@@ -19360,7 +19385,7 @@
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
@@ -19374,10 +19399,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>563734</v>
+        <v>563815</v>
       </c>
       <c r="R169" t="n">
-        <v>6704595</v>
+        <v>6704815</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -19436,7 +19461,7 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>119874665</v>
+        <v>119874639</v>
       </c>
       <c r="B170" t="n">
         <v>97907</v>
@@ -19471,7 +19496,7 @@
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
@@ -19485,10 +19510,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>564008</v>
+        <v>563718</v>
       </c>
       <c r="R170" t="n">
-        <v>6704979</v>
+        <v>6704563</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -19547,10 +19572,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>119874596</v>
+        <v>119874616</v>
       </c>
       <c r="B171" t="n">
-        <v>57463</v>
+        <v>97907</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
@@ -19559,50 +19584,47 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K171" t="inlineStr"/>
-      <c r="L171" t="inlineStr"/>
-      <c r="M171" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N171" t="inlineStr"/>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P171" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>563633</v>
+        <v>563993</v>
       </c>
       <c r="R171" t="n">
-        <v>6704498</v>
+        <v>6705035</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -19661,7 +19683,7 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>119874571</v>
+        <v>119874588</v>
       </c>
       <c r="B172" t="n">
         <v>90562</v>
@@ -19701,10 +19723,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>563816</v>
+        <v>564011</v>
       </c>
       <c r="R172" t="n">
-        <v>6704792</v>
+        <v>6705060</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -19763,10 +19785,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>119874597</v>
+        <v>119874572</v>
       </c>
       <c r="B173" t="n">
-        <v>91494</v>
+        <v>90562</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
@@ -19775,25 +19797,25 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>4769</v>
+        <v>1202</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
@@ -19803,10 +19825,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>563943</v>
+        <v>563815</v>
       </c>
       <c r="R173" t="n">
-        <v>6704878</v>
+        <v>6704789</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -19865,7 +19887,7 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>119874588</v>
+        <v>119874575</v>
       </c>
       <c r="B174" t="n">
         <v>90562</v>
@@ -19905,10 +19927,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>564011</v>
+        <v>563720</v>
       </c>
       <c r="R174" t="n">
-        <v>6705060</v>
+        <v>6704700</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -19967,10 +19989,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>119874668</v>
+        <v>119874591</v>
       </c>
       <c r="B175" t="n">
-        <v>74577</v>
+        <v>90562</v>
       </c>
       <c r="C175" t="inlineStr">
         <is>
@@ -19979,25 +20001,25 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>6426</v>
+        <v>1202</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
@@ -20007,10 +20029,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>563937</v>
+        <v>564204</v>
       </c>
       <c r="R175" t="n">
-        <v>6704867</v>
+        <v>6705194</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -20069,7 +20091,7 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>119874658</v>
+        <v>119874655</v>
       </c>
       <c r="B176" t="n">
         <v>97907</v>
@@ -20118,10 +20140,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>563749</v>
+        <v>563757</v>
       </c>
       <c r="R176" t="n">
-        <v>6704725</v>
+        <v>6704730</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -20180,7 +20202,7 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>119874646</v>
+        <v>119874652</v>
       </c>
       <c r="B177" t="n">
         <v>97907</v>
@@ -20215,7 +20237,7 @@
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
@@ -20229,7 +20251,7 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>563995</v>
+        <v>563976</v>
       </c>
       <c r="R177" t="n">
         <v>6704966</v>
@@ -20291,7 +20313,7 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>119874663</v>
+        <v>119874637</v>
       </c>
       <c r="B178" t="n">
         <v>97907</v>
@@ -20326,7 +20348,7 @@
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
@@ -20340,10 +20362,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>563835</v>
+        <v>563648</v>
       </c>
       <c r="R178" t="n">
-        <v>6704743</v>
+        <v>6704505</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -20402,10 +20424,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>119874661</v>
+        <v>119874681</v>
       </c>
       <c r="B179" t="n">
-        <v>97907</v>
+        <v>5169</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
@@ -20414,35 +20436,31 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I179" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J179" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr"/>
+      <c r="M179" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P179" t="inlineStr">
@@ -20451,10 +20469,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>563645</v>
+        <v>563825</v>
       </c>
       <c r="R179" t="n">
-        <v>6704515</v>
+        <v>6704705</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -20513,10 +20531,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>119874586</v>
+        <v>119874633</v>
       </c>
       <c r="B180" t="n">
-        <v>90562</v>
+        <v>97907</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
@@ -20525,38 +20543,47 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I180" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J180" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P180" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>564005</v>
+        <v>563741</v>
       </c>
       <c r="R180" t="n">
-        <v>6705064</v>
+        <v>6704721</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -20615,10 +20642,10 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>119874680</v>
+        <v>119874623</v>
       </c>
       <c r="B181" t="n">
-        <v>5169</v>
+        <v>97907</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
@@ -20627,31 +20654,35 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I181" t="inlineStr"/>
-      <c r="M181" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J181" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P181" t="inlineStr">
@@ -20660,10 +20691,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>563792</v>
+        <v>563637</v>
       </c>
       <c r="R181" t="n">
-        <v>6704694</v>
+        <v>6704477</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -20722,10 +20753,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>119874649</v>
+        <v>119874586</v>
       </c>
       <c r="B182" t="n">
-        <v>97907</v>
+        <v>90562</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
@@ -20734,47 +20765,38 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I182" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J182" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr"/>
       <c r="P182" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>563765</v>
+        <v>564005</v>
       </c>
       <c r="R182" t="n">
-        <v>6704626</v>
+        <v>6705064</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -20833,10 +20855,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>119874613</v>
+        <v>119874571</v>
       </c>
       <c r="B183" t="n">
-        <v>97907</v>
+        <v>90562</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
@@ -20845,47 +20867,38 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I183" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J183" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr"/>
       <c r="P183" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>563794</v>
+        <v>563816</v>
       </c>
       <c r="R183" t="n">
-        <v>6704750</v>
+        <v>6704792</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -20944,7 +20957,7 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>119874573</v>
+        <v>119874574</v>
       </c>
       <c r="B184" t="n">
         <v>90562</v>
@@ -20984,10 +20997,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>563794</v>
+        <v>563796</v>
       </c>
       <c r="R184" t="n">
-        <v>6704792</v>
+        <v>6704785</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -21046,10 +21059,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>119874569</v>
+        <v>119874604</v>
       </c>
       <c r="B185" t="n">
-        <v>90562</v>
+        <v>90334</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
@@ -21058,25 +21071,25 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>1202</v>
+        <v>3215</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
@@ -21086,10 +21099,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>564137</v>
+        <v>563936</v>
       </c>
       <c r="R185" t="n">
-        <v>6705071</v>
+        <v>6704867</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -21148,10 +21161,10 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>119874580</v>
+        <v>119874606</v>
       </c>
       <c r="B186" t="n">
-        <v>90562</v>
+        <v>90846</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
@@ -21164,21 +21177,21 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
@@ -21188,10 +21201,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>563702</v>
+        <v>563784</v>
       </c>
       <c r="R186" t="n">
-        <v>6704652</v>
+        <v>6704721</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -21224,6 +21237,11 @@
       <c r="AA186" t="inlineStr">
         <is>
           <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AC186" t="inlineStr">
+        <is>
+          <t>Äldre fruktkropp</t>
         </is>
       </c>
       <c r="AD186" t="b">
@@ -21250,10 +21268,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>119874585</v>
+        <v>119874607</v>
       </c>
       <c r="B187" t="n">
-        <v>90562</v>
+        <v>90846</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
@@ -21266,21 +21284,21 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
@@ -21290,10 +21308,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>563986</v>
+        <v>563821</v>
       </c>
       <c r="R187" t="n">
-        <v>6705041</v>
+        <v>6704817</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -21352,10 +21370,10 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>119874619</v>
+        <v>119874685</v>
       </c>
       <c r="B188" t="n">
-        <v>97907</v>
+        <v>8421</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
@@ -21364,35 +21382,31 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>220787</v>
+        <v>106554</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I188" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J188" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr"/>
+      <c r="M188" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P188" t="inlineStr">
@@ -21401,10 +21415,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>564203</v>
+        <v>563845</v>
       </c>
       <c r="R188" t="n">
-        <v>6705186</v>
+        <v>6704771</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -21463,7 +21477,7 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>119874637</v>
+        <v>119874624</v>
       </c>
       <c r="B189" t="n">
         <v>97907</v>
@@ -21498,7 +21512,7 @@
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J189" t="inlineStr">
@@ -21512,10 +21526,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>563648</v>
+        <v>563734</v>
       </c>
       <c r="R189" t="n">
-        <v>6704505</v>
+        <v>6704595</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -21574,7 +21588,7 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>119874655</v>
+        <v>119874618</v>
       </c>
       <c r="B190" t="n">
         <v>97907</v>
@@ -21609,7 +21623,7 @@
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
@@ -21623,10 +21637,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>563757</v>
+        <v>564168</v>
       </c>
       <c r="R190" t="n">
-        <v>6704730</v>
+        <v>6705183</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -21685,10 +21699,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>119874633</v>
+        <v>119874581</v>
       </c>
       <c r="B191" t="n">
-        <v>97907</v>
+        <v>90562</v>
       </c>
       <c r="C191" t="inlineStr">
         <is>
@@ -21697,47 +21711,38 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E191" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I191" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J191" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr"/>
       <c r="P191" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>563741</v>
+        <v>563792</v>
       </c>
       <c r="R191" t="n">
-        <v>6704721</v>
+        <v>6704700</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -21796,7 +21801,7 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>119874625</v>
+        <v>119874665</v>
       </c>
       <c r="B192" t="n">
         <v>97907</v>
@@ -21831,7 +21836,7 @@
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
@@ -21845,10 +21850,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>564201</v>
+        <v>564008</v>
       </c>
       <c r="R192" t="n">
-        <v>6705184</v>
+        <v>6704979</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -21907,10 +21912,10 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>119874647</v>
+        <v>119874593</v>
       </c>
       <c r="B193" t="n">
-        <v>97907</v>
+        <v>90562</v>
       </c>
       <c r="C193" t="inlineStr">
         <is>
@@ -21919,54 +21924,38 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I193" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J193" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K193" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L193" t="inlineStr"/>
-      <c r="N193" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr"/>
       <c r="P193" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>564036</v>
+        <v>563710</v>
       </c>
       <c r="R193" t="n">
-        <v>6705043</v>
+        <v>6704663</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -22001,18 +21990,12 @@
           <t>2024-09-20</t>
         </is>
       </c>
-      <c r="AC193" t="inlineStr">
-        <is>
-          <t>1 blomstjälk</t>
-        </is>
-      </c>
       <c r="AD193" t="b">
         <v>0</v>
       </c>
       <c r="AE193" t="b">
         <v>0</v>
       </c>
-      <c r="AF193" t="inlineStr"/>
       <c r="AG193" t="b">
         <v>0</v>
       </c>
@@ -22031,7 +22014,7 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>119874618</v>
+        <v>119874621</v>
       </c>
       <c r="B194" t="n">
         <v>97907</v>
@@ -22066,7 +22049,7 @@
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
@@ -22080,10 +22063,10 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>564168</v>
+        <v>564283</v>
       </c>
       <c r="R194" t="n">
-        <v>6705183</v>
+        <v>6705293</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -22142,10 +22125,10 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>119874572</v>
+        <v>119874649</v>
       </c>
       <c r="B195" t="n">
-        <v>90562</v>
+        <v>97907</v>
       </c>
       <c r="C195" t="inlineStr">
         <is>
@@ -22154,38 +22137,47 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I195" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J195" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P195" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>563815</v>
+        <v>563765</v>
       </c>
       <c r="R195" t="n">
-        <v>6704789</v>
+        <v>6704626</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -22244,10 +22236,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>119874583</v>
+        <v>119874627</v>
       </c>
       <c r="B196" t="n">
-        <v>90562</v>
+        <v>97907</v>
       </c>
       <c r="C196" t="inlineStr">
         <is>
@@ -22256,38 +22248,54 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E196" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I196" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J196" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L196" t="inlineStr"/>
+      <c r="N196" t="inlineStr"/>
       <c r="P196" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>563996</v>
+        <v>563813</v>
       </c>
       <c r="R196" t="n">
-        <v>6705007</v>
+        <v>6704796</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -22322,12 +22330,18 @@
           <t>2024-09-20</t>
         </is>
       </c>
+      <c r="AC196" t="inlineStr">
+        <is>
+          <t>2 blomstjälkar</t>
+        </is>
+      </c>
       <c r="AD196" t="b">
         <v>0</v>
       </c>
       <c r="AE196" t="b">
         <v>0</v>
       </c>
+      <c r="AF196" t="inlineStr"/>
       <c r="AG196" t="b">
         <v>0</v>
       </c>
@@ -22346,10 +22360,10 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>119874575</v>
+        <v>119874644</v>
       </c>
       <c r="B197" t="n">
-        <v>90562</v>
+        <v>97907</v>
       </c>
       <c r="C197" t="inlineStr">
         <is>
@@ -22358,38 +22372,47 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I197" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J197" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P197" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>563720</v>
+        <v>563984</v>
       </c>
       <c r="R197" t="n">
-        <v>6704700</v>
+        <v>6704957</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -22448,10 +22471,10 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>119874685</v>
+        <v>119874568</v>
       </c>
       <c r="B198" t="n">
-        <v>8421</v>
+        <v>90905</v>
       </c>
       <c r="C198" t="inlineStr">
         <is>
@@ -22460,43 +22483,38 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E198" t="n">
-        <v>106554</v>
+        <v>2062</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I198" t="inlineStr"/>
-      <c r="M198" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P198" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>563845</v>
+        <v>563986</v>
       </c>
       <c r="R198" t="n">
-        <v>6704771</v>
+        <v>6705032</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -22555,10 +22573,10 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>119874593</v>
+        <v>119874608</v>
       </c>
       <c r="B199" t="n">
-        <v>90562</v>
+        <v>94311</v>
       </c>
       <c r="C199" t="inlineStr">
         <is>
@@ -22567,25 +22585,25 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E199" t="n">
-        <v>1202</v>
+        <v>2809</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I199" t="inlineStr"/>
@@ -22595,10 +22613,10 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>563710</v>
+        <v>563944</v>
       </c>
       <c r="R199" t="n">
-        <v>6704663</v>
+        <v>6704880</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -22764,10 +22782,10 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>119874612</v>
+        <v>119874577</v>
       </c>
       <c r="B201" t="n">
-        <v>97907</v>
+        <v>90562</v>
       </c>
       <c r="C201" t="inlineStr">
         <is>
@@ -22776,54 +22794,38 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E201" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I201" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J201" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K201" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L201" t="inlineStr"/>
-      <c r="N201" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr"/>
       <c r="P201" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>564201</v>
+        <v>563703</v>
       </c>
       <c r="R201" t="n">
-        <v>6705191</v>
+        <v>6704669</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -22858,18 +22860,12 @@
           <t>2024-09-20</t>
         </is>
       </c>
-      <c r="AC201" t="inlineStr">
-        <is>
-          <t>1 blomstjälk</t>
-        </is>
-      </c>
       <c r="AD201" t="b">
         <v>0</v>
       </c>
       <c r="AE201" t="b">
         <v>0</v>
       </c>
-      <c r="AF201" t="inlineStr"/>
       <c r="AG201" t="b">
         <v>0</v>
       </c>
@@ -22888,10 +22884,10 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>119874627</v>
+        <v>119874668</v>
       </c>
       <c r="B202" t="n">
-        <v>97907</v>
+        <v>74577</v>
       </c>
       <c r="C202" t="inlineStr">
         <is>
@@ -22900,54 +22896,38 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E202" t="n">
-        <v>220787</v>
+        <v>6426</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I202" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J202" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K202" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L202" t="inlineStr"/>
-      <c r="N202" t="inlineStr"/>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr"/>
       <c r="P202" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>563813</v>
+        <v>563937</v>
       </c>
       <c r="R202" t="n">
-        <v>6704796</v>
+        <v>6704867</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -22982,18 +22962,12 @@
           <t>2024-09-20</t>
         </is>
       </c>
-      <c r="AC202" t="inlineStr">
-        <is>
-          <t>2 blomstjälkar</t>
-        </is>
-      </c>
       <c r="AD202" t="b">
         <v>0</v>
       </c>
       <c r="AE202" t="b">
         <v>0</v>
       </c>
-      <c r="AF202" t="inlineStr"/>
       <c r="AG202" t="b">
         <v>0</v>
       </c>
@@ -23012,10 +22986,10 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>119874599</v>
+        <v>119874651</v>
       </c>
       <c r="B203" t="n">
-        <v>57326</v>
+        <v>97907</v>
       </c>
       <c r="C203" t="inlineStr">
         <is>
@@ -23024,31 +22998,35 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E203" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I203" t="inlineStr"/>
-      <c r="M203" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J203" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P203" t="inlineStr">
@@ -23057,10 +23035,10 @@
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>563944</v>
+        <v>564256</v>
       </c>
       <c r="R203" t="n">
-        <v>6704948</v>
+        <v>6705293</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -23119,7 +23097,7 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>119874634</v>
+        <v>119874646</v>
       </c>
       <c r="B204" t="n">
         <v>97907</v>
@@ -23154,7 +23132,7 @@
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J204" t="inlineStr">
@@ -23168,10 +23146,10 @@
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>563712</v>
+        <v>563995</v>
       </c>
       <c r="R204" t="n">
-        <v>6704670</v>
+        <v>6704966</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>
@@ -23230,7 +23208,7 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>119874591</v>
+        <v>119874590</v>
       </c>
       <c r="B205" t="n">
         <v>90562</v>
@@ -23270,10 +23248,10 @@
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>564204</v>
+        <v>564015</v>
       </c>
       <c r="R205" t="n">
-        <v>6705194</v>
+        <v>6705047</v>
       </c>
       <c r="S205" t="n">
         <v>10</v>
@@ -23332,10 +23310,10 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>119874574</v>
+        <v>119874599</v>
       </c>
       <c r="B206" t="n">
-        <v>90562</v>
+        <v>57326</v>
       </c>
       <c r="C206" t="inlineStr">
         <is>
@@ -23348,34 +23326,39 @@
         </is>
       </c>
       <c r="E206" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I206" t="inlineStr"/>
+      <c r="M206" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P206" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>563796</v>
+        <v>563944</v>
       </c>
       <c r="R206" t="n">
-        <v>6704785</v>
+        <v>6704948</v>
       </c>
       <c r="S206" t="n">
         <v>10</v>
@@ -23434,10 +23417,10 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>119874681</v>
+        <v>119874659</v>
       </c>
       <c r="B207" t="n">
-        <v>5169</v>
+        <v>97907</v>
       </c>
       <c r="C207" t="inlineStr">
         <is>
@@ -23446,31 +23429,35 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E207" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I207" t="inlineStr"/>
-      <c r="M207" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J207" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P207" t="inlineStr">
@@ -23479,10 +23466,10 @@
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>563825</v>
+        <v>563746</v>
       </c>
       <c r="R207" t="n">
-        <v>6704705</v>
+        <v>6704720</v>
       </c>
       <c r="S207" t="n">
         <v>10</v>
@@ -23541,7 +23528,7 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>119874616</v>
+        <v>119874612</v>
       </c>
       <c r="B208" t="n">
         <v>97907</v>
@@ -23584,16 +23571,23 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L208" t="inlineStr"/>
+      <c r="N208" t="inlineStr"/>
       <c r="P208" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>563993</v>
+        <v>564201</v>
       </c>
       <c r="R208" t="n">
-        <v>6705035</v>
+        <v>6705191</v>
       </c>
       <c r="S208" t="n">
         <v>10</v>
@@ -23628,12 +23622,18 @@
           <t>2024-09-20</t>
         </is>
       </c>
+      <c r="AC208" t="inlineStr">
+        <is>
+          <t>1 blomstjälk</t>
+        </is>
+      </c>
       <c r="AD208" t="b">
         <v>0</v>
       </c>
       <c r="AE208" t="b">
         <v>0</v>
       </c>
+      <c r="AF208" t="inlineStr"/>
       <c r="AG208" t="b">
         <v>0</v>
       </c>
@@ -23652,7 +23652,7 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>119874617</v>
+        <v>119874619</v>
       </c>
       <c r="B209" t="n">
         <v>97907</v>
@@ -23687,7 +23687,7 @@
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J209" t="inlineStr">
@@ -23701,10 +23701,10 @@
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>563833</v>
+        <v>564203</v>
       </c>
       <c r="R209" t="n">
-        <v>6704788</v>
+        <v>6705186</v>
       </c>
       <c r="S209" t="n">
         <v>10</v>

--- a/artfynd/A 58548-2022 artfynd.xlsx
+++ b/artfynd/A 58548-2022 artfynd.xlsx
@@ -15695,10 +15695,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>119874617</v>
+        <v>119874583</v>
       </c>
       <c r="B135" t="n">
-        <v>97907</v>
+        <v>90562</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -15707,47 +15707,38 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I135" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J135" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>563833</v>
+        <v>563996</v>
       </c>
       <c r="R135" t="n">
-        <v>6704788</v>
+        <v>6705007</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -15806,10 +15797,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>119874663</v>
+        <v>119874576</v>
       </c>
       <c r="B136" t="n">
-        <v>97907</v>
+        <v>90562</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -15818,47 +15809,38 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I136" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J136" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>563835</v>
+        <v>563718</v>
       </c>
       <c r="R136" t="n">
-        <v>6704743</v>
+        <v>6704695</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15917,10 +15899,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>119874634</v>
+        <v>119874605</v>
       </c>
       <c r="B137" t="n">
-        <v>97907</v>
+        <v>90334</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -15929,47 +15911,38 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>220787</v>
+        <v>3215</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I137" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J137" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>563712</v>
+        <v>563929</v>
       </c>
       <c r="R137" t="n">
-        <v>6704670</v>
+        <v>6704878</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -16028,10 +16001,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>119874583</v>
+        <v>119874617</v>
       </c>
       <c r="B138" t="n">
-        <v>90562</v>
+        <v>97907</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -16040,38 +16013,47 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I138" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P138" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>563996</v>
+        <v>563833</v>
       </c>
       <c r="R138" t="n">
-        <v>6705007</v>
+        <v>6704788</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -16130,10 +16112,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>119874576</v>
+        <v>119874663</v>
       </c>
       <c r="B139" t="n">
-        <v>90562</v>
+        <v>97907</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -16142,38 +16124,47 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I139" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P139" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>563718</v>
+        <v>563835</v>
       </c>
       <c r="R139" t="n">
-        <v>6704695</v>
+        <v>6704743</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -16232,10 +16223,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>119874605</v>
+        <v>119874634</v>
       </c>
       <c r="B140" t="n">
-        <v>90334</v>
+        <v>97907</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -16244,38 +16235,47 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>3215</v>
+        <v>220787</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I140" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P140" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>563929</v>
+        <v>563712</v>
       </c>
       <c r="R140" t="n">
-        <v>6704878</v>
+        <v>6704670</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -17098,10 +17098,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>119874625</v>
+        <v>119874596</v>
       </c>
       <c r="B148" t="n">
-        <v>97907</v>
+        <v>57463</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -17110,47 +17110,50 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J148" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr"/>
+      <c r="L148" t="inlineStr"/>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>564201</v>
+        <v>563633</v>
       </c>
       <c r="R148" t="n">
-        <v>6705184</v>
+        <v>6704498</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -17209,7 +17212,7 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>119874661</v>
+        <v>119874625</v>
       </c>
       <c r="B149" t="n">
         <v>97907</v>
@@ -17244,7 +17247,7 @@
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
@@ -17258,10 +17261,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>563645</v>
+        <v>564201</v>
       </c>
       <c r="R149" t="n">
-        <v>6704515</v>
+        <v>6705184</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -17320,10 +17323,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>119874597</v>
+        <v>119874661</v>
       </c>
       <c r="B150" t="n">
-        <v>91494</v>
+        <v>97907</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -17332,38 +17335,47 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>4769</v>
+        <v>220787</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I150" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P150" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>563943</v>
+        <v>563645</v>
       </c>
       <c r="R150" t="n">
-        <v>6704878</v>
+        <v>6704515</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -17422,10 +17434,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>119874596</v>
+        <v>119874597</v>
       </c>
       <c r="B151" t="n">
-        <v>57463</v>
+        <v>91494</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -17434,50 +17446,38 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>103021</v>
+        <v>4769</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I151" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K151" t="inlineStr"/>
-      <c r="L151" t="inlineStr"/>
-      <c r="M151" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N151" t="inlineStr"/>
+          <t>(Scop.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>563633</v>
+        <v>563943</v>
       </c>
       <c r="R151" t="n">
-        <v>6704498</v>
+        <v>6704878</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -20531,10 +20531,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>119874633</v>
+        <v>119874586</v>
       </c>
       <c r="B180" t="n">
-        <v>97907</v>
+        <v>90562</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
@@ -20543,47 +20543,38 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I180" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J180" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr"/>
       <c r="P180" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>563741</v>
+        <v>564005</v>
       </c>
       <c r="R180" t="n">
-        <v>6704721</v>
+        <v>6705064</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -20642,10 +20633,10 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>119874623</v>
+        <v>119874571</v>
       </c>
       <c r="B181" t="n">
-        <v>97907</v>
+        <v>90562</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
@@ -20654,47 +20645,38 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I181" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J181" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr"/>
       <c r="P181" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>563637</v>
+        <v>563816</v>
       </c>
       <c r="R181" t="n">
-        <v>6704477</v>
+        <v>6704792</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -20753,10 +20735,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>119874586</v>
+        <v>119874633</v>
       </c>
       <c r="B182" t="n">
-        <v>90562</v>
+        <v>97907</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
@@ -20765,38 +20747,47 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I182" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J182" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P182" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>564005</v>
+        <v>563741</v>
       </c>
       <c r="R182" t="n">
-        <v>6705064</v>
+        <v>6704721</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -20855,10 +20846,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>119874571</v>
+        <v>119874623</v>
       </c>
       <c r="B183" t="n">
-        <v>90562</v>
+        <v>97907</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
@@ -20867,38 +20858,47 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I183" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P183" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>563816</v>
+        <v>563637</v>
       </c>
       <c r="R183" t="n">
-        <v>6704792</v>
+        <v>6704477</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -22014,10 +22014,10 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>119874621</v>
+        <v>119874568</v>
       </c>
       <c r="B194" t="n">
-        <v>97907</v>
+        <v>90905</v>
       </c>
       <c r="C194" t="inlineStr">
         <is>
@@ -22030,43 +22030,34 @@
         </is>
       </c>
       <c r="E194" t="n">
-        <v>220787</v>
+        <v>2062</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I194" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J194" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr"/>
       <c r="P194" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>564283</v>
+        <v>563986</v>
       </c>
       <c r="R194" t="n">
-        <v>6705293</v>
+        <v>6705032</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -22125,10 +22116,10 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>119874649</v>
+        <v>119874682</v>
       </c>
       <c r="B195" t="n">
-        <v>97907</v>
+        <v>5169</v>
       </c>
       <c r="C195" t="inlineStr">
         <is>
@@ -22137,35 +22128,31 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I195" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J195" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr"/>
+      <c r="M195" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P195" t="inlineStr">
@@ -22174,10 +22161,10 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>563765</v>
+        <v>564000</v>
       </c>
       <c r="R195" t="n">
-        <v>6704626</v>
+        <v>6704958</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -22236,10 +22223,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>119874627</v>
+        <v>119874608</v>
       </c>
       <c r="B196" t="n">
-        <v>97907</v>
+        <v>94311</v>
       </c>
       <c r="C196" t="inlineStr">
         <is>
@@ -22248,54 +22235,38 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E196" t="n">
-        <v>220787</v>
+        <v>2809</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I196" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J196" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K196" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L196" t="inlineStr"/>
-      <c r="N196" t="inlineStr"/>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr"/>
       <c r="P196" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>563813</v>
+        <v>563944</v>
       </c>
       <c r="R196" t="n">
-        <v>6704796</v>
+        <v>6704880</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -22330,18 +22301,12 @@
           <t>2024-09-20</t>
         </is>
       </c>
-      <c r="AC196" t="inlineStr">
-        <is>
-          <t>2 blomstjälkar</t>
-        </is>
-      </c>
       <c r="AD196" t="b">
         <v>0</v>
       </c>
       <c r="AE196" t="b">
         <v>0</v>
       </c>
-      <c r="AF196" t="inlineStr"/>
       <c r="AG196" t="b">
         <v>0</v>
       </c>
@@ -22360,7 +22325,7 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>119874644</v>
+        <v>119874621</v>
       </c>
       <c r="B197" t="n">
         <v>97907</v>
@@ -22395,7 +22360,7 @@
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
@@ -22409,10 +22374,10 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>563984</v>
+        <v>564283</v>
       </c>
       <c r="R197" t="n">
-        <v>6704957</v>
+        <v>6705293</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -22471,10 +22436,10 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>119874568</v>
+        <v>119874649</v>
       </c>
       <c r="B198" t="n">
-        <v>90905</v>
+        <v>97907</v>
       </c>
       <c r="C198" t="inlineStr">
         <is>
@@ -22487,34 +22452,43 @@
         </is>
       </c>
       <c r="E198" t="n">
-        <v>2062</v>
+        <v>220787</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I198" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J198" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P198" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>563986</v>
+        <v>563765</v>
       </c>
       <c r="R198" t="n">
-        <v>6705032</v>
+        <v>6704626</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -22573,10 +22547,10 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>119874608</v>
+        <v>119874627</v>
       </c>
       <c r="B199" t="n">
-        <v>94311</v>
+        <v>97907</v>
       </c>
       <c r="C199" t="inlineStr">
         <is>
@@ -22585,38 +22559,54 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E199" t="n">
-        <v>2809</v>
+        <v>220787</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
-        </is>
-      </c>
-      <c r="I199" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J199" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L199" t="inlineStr"/>
+      <c r="N199" t="inlineStr"/>
       <c r="P199" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>563944</v>
+        <v>563813</v>
       </c>
       <c r="R199" t="n">
-        <v>6704880</v>
+        <v>6704796</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -22651,12 +22641,18 @@
           <t>2024-09-20</t>
         </is>
       </c>
+      <c r="AC199" t="inlineStr">
+        <is>
+          <t>2 blomstjälkar</t>
+        </is>
+      </c>
       <c r="AD199" t="b">
         <v>0</v>
       </c>
       <c r="AE199" t="b">
         <v>0</v>
       </c>
+      <c r="AF199" t="inlineStr"/>
       <c r="AG199" t="b">
         <v>0</v>
       </c>
@@ -22675,10 +22671,10 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>119874682</v>
+        <v>119874644</v>
       </c>
       <c r="B200" t="n">
-        <v>5169</v>
+        <v>97907</v>
       </c>
       <c r="C200" t="inlineStr">
         <is>
@@ -22687,31 +22683,35 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I200" t="inlineStr"/>
-      <c r="M200" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J200" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P200" t="inlineStr">
@@ -22720,10 +22720,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>564000</v>
+        <v>563984</v>
       </c>
       <c r="R200" t="n">
-        <v>6704958</v>
+        <v>6704957</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>

--- a/artfynd/A 58548-2022 artfynd.xlsx
+++ b/artfynd/A 58548-2022 artfynd.xlsx
@@ -15695,10 +15695,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>119874583</v>
+        <v>119874668</v>
       </c>
       <c r="B135" t="n">
-        <v>90562</v>
+        <v>74577</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -15707,25 +15707,25 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>1202</v>
+        <v>6426</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -15735,10 +15735,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>563996</v>
+        <v>563937</v>
       </c>
       <c r="R135" t="n">
-        <v>6705007</v>
+        <v>6704867</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -15797,7 +15797,7 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>119874576</v>
+        <v>119874574</v>
       </c>
       <c r="B136" t="n">
         <v>90562</v>
@@ -15837,10 +15837,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>563718</v>
+        <v>563796</v>
       </c>
       <c r="R136" t="n">
-        <v>6704695</v>
+        <v>6704785</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15899,10 +15899,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>119874605</v>
+        <v>119874597</v>
       </c>
       <c r="B137" t="n">
-        <v>90334</v>
+        <v>91494</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -15915,21 +15915,21 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>3215</v>
+        <v>4769</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -15939,7 +15939,7 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>563929</v>
+        <v>563943</v>
       </c>
       <c r="R137" t="n">
         <v>6704878</v>
@@ -16001,7 +16001,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>119874617</v>
+        <v>119874633</v>
       </c>
       <c r="B138" t="n">
         <v>97907</v>
@@ -16036,7 +16036,7 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -16050,10 +16050,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>563833</v>
+        <v>563741</v>
       </c>
       <c r="R138" t="n">
-        <v>6704788</v>
+        <v>6704721</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -16112,7 +16112,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>119874663</v>
+        <v>119874626</v>
       </c>
       <c r="B139" t="n">
         <v>97907</v>
@@ -16147,7 +16147,7 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -16155,16 +16155,23 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L139" t="inlineStr"/>
+      <c r="N139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>563835</v>
+        <v>564019</v>
       </c>
       <c r="R139" t="n">
-        <v>6704743</v>
+        <v>6704997</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -16199,12 +16206,18 @@
           <t>2024-09-20</t>
         </is>
       </c>
+      <c r="AC139" t="inlineStr">
+        <is>
+          <t>1 blomstjälk</t>
+        </is>
+      </c>
       <c r="AD139" t="b">
         <v>0</v>
       </c>
       <c r="AE139" t="b">
         <v>0</v>
       </c>
+      <c r="AF139" t="inlineStr"/>
       <c r="AG139" t="b">
         <v>0</v>
       </c>
@@ -16223,7 +16236,7 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>119874634</v>
+        <v>119874625</v>
       </c>
       <c r="B140" t="n">
         <v>97907</v>
@@ -16258,7 +16271,7 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
@@ -16272,10 +16285,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>563712</v>
+        <v>564201</v>
       </c>
       <c r="R140" t="n">
-        <v>6704670</v>
+        <v>6705184</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -16334,7 +16347,7 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>119874580</v>
+        <v>119874571</v>
       </c>
       <c r="B141" t="n">
         <v>90562</v>
@@ -16374,10 +16387,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>563702</v>
+        <v>563816</v>
       </c>
       <c r="R141" t="n">
-        <v>6704652</v>
+        <v>6704792</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -16436,10 +16449,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>119874678</v>
+        <v>119874581</v>
       </c>
       <c r="B142" t="n">
-        <v>5169</v>
+        <v>90562</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -16448,43 +16461,38 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
-      <c r="M142" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P142" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>563957</v>
+        <v>563792</v>
       </c>
       <c r="R142" t="n">
-        <v>6704878</v>
+        <v>6704700</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -16543,7 +16551,7 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>119874626</v>
+        <v>119874644</v>
       </c>
       <c r="B143" t="n">
         <v>97907</v>
@@ -16586,23 +16594,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K143" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L143" t="inlineStr"/>
-      <c r="N143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>564019</v>
+        <v>563984</v>
       </c>
       <c r="R143" t="n">
-        <v>6704997</v>
+        <v>6704957</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -16637,18 +16638,12 @@
           <t>2024-09-20</t>
         </is>
       </c>
-      <c r="AC143" t="inlineStr">
-        <is>
-          <t>1 blomstjälk</t>
-        </is>
-      </c>
       <c r="AD143" t="b">
         <v>0</v>
       </c>
       <c r="AE143" t="b">
         <v>0</v>
       </c>
-      <c r="AF143" t="inlineStr"/>
       <c r="AG143" t="b">
         <v>0</v>
       </c>
@@ -16667,10 +16662,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>119874635</v>
+        <v>119874609</v>
       </c>
       <c r="B144" t="n">
-        <v>97907</v>
+        <v>90954</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -16679,47 +16674,33 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F144" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I144" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J144" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>563705</v>
+        <v>564083</v>
       </c>
       <c r="R144" t="n">
-        <v>6704657</v>
+        <v>6705090</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -16778,10 +16759,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>119874569</v>
+        <v>119874652</v>
       </c>
       <c r="B145" t="n">
-        <v>90562</v>
+        <v>97907</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -16790,38 +16771,47 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I145" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P145" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>564137</v>
+        <v>563976</v>
       </c>
       <c r="R145" t="n">
-        <v>6705071</v>
+        <v>6704966</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -16880,10 +16870,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>119874680</v>
+        <v>119874651</v>
       </c>
       <c r="B146" t="n">
-        <v>5169</v>
+        <v>97907</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -16892,31 +16882,35 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I146" t="inlineStr"/>
-      <c r="M146" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P146" t="inlineStr">
@@ -16925,10 +16919,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>563792</v>
+        <v>564256</v>
       </c>
       <c r="R146" t="n">
-        <v>6704694</v>
+        <v>6705293</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16987,10 +16981,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>119874613</v>
+        <v>119874678</v>
       </c>
       <c r="B147" t="n">
-        <v>97907</v>
+        <v>5169</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -16999,35 +16993,31 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I147" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J147" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr"/>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P147" t="inlineStr">
@@ -17036,10 +17026,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>563794</v>
+        <v>563957</v>
       </c>
       <c r="R147" t="n">
-        <v>6704750</v>
+        <v>6704878</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -17098,10 +17088,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>119874596</v>
+        <v>119874591</v>
       </c>
       <c r="B148" t="n">
-        <v>57463</v>
+        <v>90562</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -17114,46 +17104,34 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I148" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K148" t="inlineStr"/>
-      <c r="L148" t="inlineStr"/>
-      <c r="M148" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N148" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>563633</v>
+        <v>564204</v>
       </c>
       <c r="R148" t="n">
-        <v>6704498</v>
+        <v>6705194</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -17212,10 +17190,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>119874625</v>
+        <v>119874680</v>
       </c>
       <c r="B149" t="n">
-        <v>97907</v>
+        <v>5169</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -17224,35 +17202,31 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I149" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J149" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr"/>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P149" t="inlineStr">
@@ -17261,10 +17235,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>564201</v>
+        <v>563792</v>
       </c>
       <c r="R149" t="n">
-        <v>6705184</v>
+        <v>6704694</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -17323,10 +17297,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>119874661</v>
+        <v>119874572</v>
       </c>
       <c r="B150" t="n">
-        <v>97907</v>
+        <v>90562</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -17335,47 +17309,38 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I150" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J150" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>563645</v>
+        <v>563815</v>
       </c>
       <c r="R150" t="n">
-        <v>6704515</v>
+        <v>6704789</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -17434,10 +17399,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>119874597</v>
+        <v>119874606</v>
       </c>
       <c r="B151" t="n">
-        <v>91494</v>
+        <v>90846</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -17446,25 +17411,25 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>4769</v>
+        <v>658</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -17474,10 +17439,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>563943</v>
+        <v>563784</v>
       </c>
       <c r="R151" t="n">
-        <v>6704878</v>
+        <v>6704721</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -17510,6 +17475,11 @@
       <c r="AA151" t="inlineStr">
         <is>
           <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AC151" t="inlineStr">
+        <is>
+          <t>Äldre fruktkropp</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -17536,10 +17506,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>119874615</v>
+        <v>119874685</v>
       </c>
       <c r="B152" t="n">
-        <v>97907</v>
+        <v>8421</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -17548,35 +17518,31 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>220787</v>
+        <v>106554</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I152" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J152" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr"/>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P152" t="inlineStr">
@@ -17585,10 +17551,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>563748</v>
+        <v>563845</v>
       </c>
       <c r="R152" t="n">
-        <v>6704608</v>
+        <v>6704771</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -17647,10 +17613,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>119874632</v>
+        <v>119874575</v>
       </c>
       <c r="B153" t="n">
-        <v>97907</v>
+        <v>90562</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -17659,47 +17625,38 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I153" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J153" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>563770</v>
+        <v>563720</v>
       </c>
       <c r="R153" t="n">
-        <v>6704729</v>
+        <v>6704700</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -17758,10 +17715,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>119874573</v>
+        <v>119874605</v>
       </c>
       <c r="B154" t="n">
-        <v>90562</v>
+        <v>90334</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -17770,25 +17727,25 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>1202</v>
+        <v>3215</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -17798,10 +17755,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>563794</v>
+        <v>563929</v>
       </c>
       <c r="R154" t="n">
-        <v>6704792</v>
+        <v>6704878</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -17860,10 +17817,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>119874566</v>
+        <v>119874684</v>
       </c>
       <c r="B155" t="n">
-        <v>90905</v>
+        <v>100171</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -17872,25 +17829,25 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>2062</v>
+        <v>222498</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -17900,10 +17857,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>564137</v>
+        <v>563956</v>
       </c>
       <c r="R155" t="n">
-        <v>6705070</v>
+        <v>6704876</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -17962,10 +17919,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>119874677</v>
+        <v>119874642</v>
       </c>
       <c r="B156" t="n">
-        <v>93930</v>
+        <v>97907</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -17974,38 +17931,47 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>2383</v>
+        <v>220787</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Bågpraktmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Plagiomnium medium</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Bruch &amp; Schimp.) T.J.Kop.</t>
-        </is>
-      </c>
-      <c r="I156" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P156" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>563925</v>
+        <v>563974</v>
       </c>
       <c r="R156" t="n">
-        <v>6704880</v>
+        <v>6704953</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -18064,10 +18030,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>119874658</v>
+        <v>119874682</v>
       </c>
       <c r="B157" t="n">
-        <v>97907</v>
+        <v>5169</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -18076,35 +18042,31 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I157" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J157" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr"/>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P157" t="inlineStr">
@@ -18113,10 +18075,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>563749</v>
+        <v>564000</v>
       </c>
       <c r="R157" t="n">
-        <v>6704725</v>
+        <v>6704958</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -18175,7 +18137,7 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>119874641</v>
+        <v>119874624</v>
       </c>
       <c r="B158" t="n">
         <v>97907</v>
@@ -18210,7 +18172,7 @@
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
@@ -18224,10 +18186,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>563808</v>
+        <v>563734</v>
       </c>
       <c r="R158" t="n">
-        <v>6704697</v>
+        <v>6704595</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -18286,10 +18248,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>119874582</v>
+        <v>119874566</v>
       </c>
       <c r="B159" t="n">
-        <v>90562</v>
+        <v>90905</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -18298,25 +18260,25 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>1202</v>
+        <v>2062</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -18326,10 +18288,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>563958</v>
+        <v>564137</v>
       </c>
       <c r="R159" t="n">
-        <v>6704952</v>
+        <v>6705070</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -18388,10 +18350,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>119874567</v>
+        <v>119874593</v>
       </c>
       <c r="B160" t="n">
-        <v>90905</v>
+        <v>90562</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -18400,25 +18362,25 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>2062</v>
+        <v>1202</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -18428,10 +18390,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>564000</v>
+        <v>563710</v>
       </c>
       <c r="R160" t="n">
-        <v>6705011</v>
+        <v>6704663</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -18490,10 +18452,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>119874666</v>
+        <v>119874582</v>
       </c>
       <c r="B161" t="n">
-        <v>74577</v>
+        <v>90562</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -18502,25 +18464,25 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>6426</v>
+        <v>1202</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
@@ -18530,10 +18492,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>563945</v>
+        <v>563958</v>
       </c>
       <c r="R161" t="n">
-        <v>6704877</v>
+        <v>6704952</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -18592,10 +18554,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>119874628</v>
+        <v>119874586</v>
       </c>
       <c r="B162" t="n">
-        <v>97907</v>
+        <v>90562</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
@@ -18604,47 +18566,38 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I162" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J162" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr"/>
       <c r="P162" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>564206</v>
+        <v>564005</v>
       </c>
       <c r="R162" t="n">
-        <v>6705189</v>
+        <v>6705064</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -18703,10 +18656,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>119874585</v>
+        <v>119874608</v>
       </c>
       <c r="B163" t="n">
-        <v>90562</v>
+        <v>94311</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -18715,25 +18668,25 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>1202</v>
+        <v>2809</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
@@ -18743,10 +18696,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>563986</v>
+        <v>563944</v>
       </c>
       <c r="R163" t="n">
-        <v>6705041</v>
+        <v>6704880</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -18805,7 +18758,7 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>119874642</v>
+        <v>119874637</v>
       </c>
       <c r="B164" t="n">
         <v>97907</v>
@@ -18854,10 +18807,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>563974</v>
+        <v>563648</v>
       </c>
       <c r="R164" t="n">
-        <v>6704953</v>
+        <v>6704505</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -18916,10 +18869,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>119874609</v>
+        <v>119874663</v>
       </c>
       <c r="B165" t="n">
-        <v>90954</v>
+        <v>97907</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -18928,33 +18881,47 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>6040186</v>
+        <v>220787</v>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
-        </is>
-      </c>
-      <c r="I165" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P165" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>564083</v>
+        <v>563835</v>
       </c>
       <c r="R165" t="n">
-        <v>6705090</v>
+        <v>6704743</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -19013,10 +18980,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>119874684</v>
+        <v>119874568</v>
       </c>
       <c r="B166" t="n">
-        <v>100171</v>
+        <v>90905</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -19025,25 +18992,25 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>222498</v>
+        <v>2062</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
@@ -19053,10 +19020,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>563956</v>
+        <v>563986</v>
       </c>
       <c r="R166" t="n">
-        <v>6704876</v>
+        <v>6705032</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -19115,10 +19082,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>119874622</v>
+        <v>119874585</v>
       </c>
       <c r="B167" t="n">
-        <v>97907</v>
+        <v>90562</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
@@ -19127,47 +19094,38 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I167" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J167" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr"/>
       <c r="P167" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>563711</v>
+        <v>563986</v>
       </c>
       <c r="R167" t="n">
-        <v>6704677</v>
+        <v>6705041</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -19226,7 +19184,7 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>119874647</v>
+        <v>119874628</v>
       </c>
       <c r="B168" t="n">
         <v>97907</v>
@@ -19261,7 +19219,7 @@
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
@@ -19269,23 +19227,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K168" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L168" t="inlineStr"/>
-      <c r="N168" t="inlineStr"/>
       <c r="P168" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>564036</v>
+        <v>564206</v>
       </c>
       <c r="R168" t="n">
-        <v>6705043</v>
+        <v>6705189</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -19320,18 +19271,12 @@
           <t>2024-09-20</t>
         </is>
       </c>
-      <c r="AC168" t="inlineStr">
-        <is>
-          <t>1 blomstjälk</t>
-        </is>
-      </c>
       <c r="AD168" t="b">
         <v>0</v>
       </c>
       <c r="AE168" t="b">
         <v>0</v>
       </c>
-      <c r="AF168" t="inlineStr"/>
       <c r="AG168" t="b">
         <v>0</v>
       </c>
@@ -19350,7 +19295,7 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>119874630</v>
+        <v>119874613</v>
       </c>
       <c r="B169" t="n">
         <v>97907</v>
@@ -19385,7 +19330,7 @@
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
@@ -19399,10 +19344,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>563815</v>
+        <v>563794</v>
       </c>
       <c r="R169" t="n">
-        <v>6704815</v>
+        <v>6704750</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -19461,10 +19406,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>119874639</v>
+        <v>119874576</v>
       </c>
       <c r="B170" t="n">
-        <v>97907</v>
+        <v>90562</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
@@ -19473,37 +19418,28 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I170" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J170" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr"/>
       <c r="P170" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
@@ -19513,7 +19449,7 @@
         <v>563718</v>
       </c>
       <c r="R170" t="n">
-        <v>6704563</v>
+        <v>6704695</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -19572,10 +19508,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>119874616</v>
+        <v>119874573</v>
       </c>
       <c r="B171" t="n">
-        <v>97907</v>
+        <v>90562</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
@@ -19584,47 +19520,38 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I171" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J171" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr"/>
       <c r="P171" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>563993</v>
+        <v>563794</v>
       </c>
       <c r="R171" t="n">
-        <v>6705035</v>
+        <v>6704792</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -19785,10 +19712,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>119874572</v>
+        <v>119874567</v>
       </c>
       <c r="B173" t="n">
-        <v>90562</v>
+        <v>90905</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
@@ -19797,25 +19724,25 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>1202</v>
+        <v>2062</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
@@ -19825,10 +19752,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>563815</v>
+        <v>564000</v>
       </c>
       <c r="R173" t="n">
-        <v>6704789</v>
+        <v>6705011</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -19887,10 +19814,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>119874575</v>
+        <v>119874681</v>
       </c>
       <c r="B174" t="n">
-        <v>90562</v>
+        <v>5169</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
@@ -19899,38 +19826,43 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
+      <c r="M174" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P174" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>563720</v>
+        <v>563825</v>
       </c>
       <c r="R174" t="n">
-        <v>6704700</v>
+        <v>6704705</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -19989,10 +19921,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>119874591</v>
+        <v>119874647</v>
       </c>
       <c r="B175" t="n">
-        <v>90562</v>
+        <v>97907</v>
       </c>
       <c r="C175" t="inlineStr">
         <is>
@@ -20001,38 +19933,54 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I175" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L175" t="inlineStr"/>
+      <c r="N175" t="inlineStr"/>
       <c r="P175" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>564204</v>
+        <v>564036</v>
       </c>
       <c r="R175" t="n">
-        <v>6705194</v>
+        <v>6705043</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -20067,12 +20015,18 @@
           <t>2024-09-20</t>
         </is>
       </c>
+      <c r="AC175" t="inlineStr">
+        <is>
+          <t>1 blomstjälk</t>
+        </is>
+      </c>
       <c r="AD175" t="b">
         <v>0</v>
       </c>
       <c r="AE175" t="b">
         <v>0</v>
       </c>
+      <c r="AF175" t="inlineStr"/>
       <c r="AG175" t="b">
         <v>0</v>
       </c>
@@ -20091,10 +20045,10 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>119874655</v>
+        <v>119874599</v>
       </c>
       <c r="B176" t="n">
-        <v>97907</v>
+        <v>57326</v>
       </c>
       <c r="C176" t="inlineStr">
         <is>
@@ -20103,35 +20057,31 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I176" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J176" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr"/>
+      <c r="M176" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P176" t="inlineStr">
@@ -20140,10 +20090,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>563757</v>
+        <v>563944</v>
       </c>
       <c r="R176" t="n">
-        <v>6704730</v>
+        <v>6704948</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -20202,7 +20152,7 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>119874652</v>
+        <v>119874612</v>
       </c>
       <c r="B177" t="n">
         <v>97907</v>
@@ -20237,7 +20187,7 @@
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
@@ -20245,16 +20195,23 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L177" t="inlineStr"/>
+      <c r="N177" t="inlineStr"/>
       <c r="P177" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>563976</v>
+        <v>564201</v>
       </c>
       <c r="R177" t="n">
-        <v>6704966</v>
+        <v>6705191</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -20289,12 +20246,18 @@
           <t>2024-09-20</t>
         </is>
       </c>
+      <c r="AC177" t="inlineStr">
+        <is>
+          <t>1 blomstjälk</t>
+        </is>
+      </c>
       <c r="AD177" t="b">
         <v>0</v>
       </c>
       <c r="AE177" t="b">
         <v>0</v>
       </c>
+      <c r="AF177" t="inlineStr"/>
       <c r="AG177" t="b">
         <v>0</v>
       </c>
@@ -20313,7 +20276,7 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>119874637</v>
+        <v>119874622</v>
       </c>
       <c r="B178" t="n">
         <v>97907</v>
@@ -20348,7 +20311,7 @@
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
@@ -20362,10 +20325,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>563648</v>
+        <v>563711</v>
       </c>
       <c r="R178" t="n">
-        <v>6704505</v>
+        <v>6704677</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -20424,10 +20387,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>119874681</v>
+        <v>119874618</v>
       </c>
       <c r="B179" t="n">
-        <v>5169</v>
+        <v>97907</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
@@ -20436,31 +20399,35 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I179" t="inlineStr"/>
-      <c r="M179" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J179" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P179" t="inlineStr">
@@ -20469,10 +20436,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>563825</v>
+        <v>564168</v>
       </c>
       <c r="R179" t="n">
-        <v>6704705</v>
+        <v>6705183</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -20531,10 +20498,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>119874586</v>
+        <v>119874617</v>
       </c>
       <c r="B180" t="n">
-        <v>90562</v>
+        <v>97907</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
@@ -20543,38 +20510,47 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I180" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J180" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P180" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>564005</v>
+        <v>563833</v>
       </c>
       <c r="R180" t="n">
-        <v>6705064</v>
+        <v>6704788</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -20633,10 +20609,10 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>119874571</v>
+        <v>119874641</v>
       </c>
       <c r="B181" t="n">
-        <v>90562</v>
+        <v>97907</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
@@ -20645,38 +20621,47 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I181" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J181" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P181" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>563816</v>
+        <v>563808</v>
       </c>
       <c r="R181" t="n">
-        <v>6704792</v>
+        <v>6704697</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -20735,10 +20720,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>119874633</v>
+        <v>119874607</v>
       </c>
       <c r="B182" t="n">
-        <v>97907</v>
+        <v>90846</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
@@ -20747,47 +20732,38 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I182" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J182" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr"/>
       <c r="P182" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>563741</v>
+        <v>563821</v>
       </c>
       <c r="R182" t="n">
-        <v>6704721</v>
+        <v>6704817</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -20846,10 +20822,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>119874623</v>
+        <v>119874569</v>
       </c>
       <c r="B183" t="n">
-        <v>97907</v>
+        <v>90562</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
@@ -20858,47 +20834,38 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I183" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J183" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr"/>
       <c r="P183" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>563637</v>
+        <v>564137</v>
       </c>
       <c r="R183" t="n">
-        <v>6704477</v>
+        <v>6705071</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -20957,10 +20924,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>119874574</v>
+        <v>119874634</v>
       </c>
       <c r="B184" t="n">
-        <v>90562</v>
+        <v>97907</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
@@ -20969,38 +20936,47 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I184" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J184" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P184" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>563796</v>
+        <v>563712</v>
       </c>
       <c r="R184" t="n">
-        <v>6704785</v>
+        <v>6704670</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -21059,10 +21035,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>119874604</v>
+        <v>119874658</v>
       </c>
       <c r="B185" t="n">
-        <v>90334</v>
+        <v>97907</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
@@ -21071,38 +21047,47 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>3215</v>
+        <v>220787</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I185" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J185" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P185" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>563936</v>
+        <v>563749</v>
       </c>
       <c r="R185" t="n">
-        <v>6704867</v>
+        <v>6704725</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -21161,10 +21146,10 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>119874606</v>
+        <v>119874616</v>
       </c>
       <c r="B186" t="n">
-        <v>90846</v>
+        <v>97907</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
@@ -21173,38 +21158,47 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I186" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J186" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P186" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>563784</v>
+        <v>563993</v>
       </c>
       <c r="R186" t="n">
-        <v>6704721</v>
+        <v>6705035</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -21237,11 +21231,6 @@
       <c r="AA186" t="inlineStr">
         <is>
           <t>2024-09-20</t>
-        </is>
-      </c>
-      <c r="AC186" t="inlineStr">
-        <is>
-          <t>Äldre fruktkropp</t>
         </is>
       </c>
       <c r="AD186" t="b">
@@ -21268,10 +21257,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>119874607</v>
+        <v>119874596</v>
       </c>
       <c r="B187" t="n">
-        <v>90846</v>
+        <v>57463</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
@@ -21284,34 +21273,46 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>658</v>
+        <v>103021</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I187" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K187" t="inlineStr"/>
+      <c r="L187" t="inlineStr"/>
+      <c r="M187" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N187" t="inlineStr"/>
       <c r="P187" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>563821</v>
+        <v>563633</v>
       </c>
       <c r="R187" t="n">
-        <v>6704817</v>
+        <v>6704498</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -21370,10 +21371,10 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>119874685</v>
+        <v>119874583</v>
       </c>
       <c r="B188" t="n">
-        <v>8421</v>
+        <v>90562</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
@@ -21382,43 +21383,38 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>106554</v>
+        <v>1202</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
-      <c r="M188" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P188" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>563845</v>
+        <v>563996</v>
       </c>
       <c r="R188" t="n">
-        <v>6704771</v>
+        <v>6705007</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -21477,10 +21473,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>119874624</v>
+        <v>119874577</v>
       </c>
       <c r="B189" t="n">
-        <v>97907</v>
+        <v>90562</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
@@ -21489,47 +21485,38 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E189" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I189" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J189" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr"/>
       <c r="P189" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>563734</v>
+        <v>563703</v>
       </c>
       <c r="R189" t="n">
-        <v>6704595</v>
+        <v>6704669</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -21588,7 +21575,7 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>119874618</v>
+        <v>119874646</v>
       </c>
       <c r="B190" t="n">
         <v>97907</v>
@@ -21623,7 +21610,7 @@
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
@@ -21637,10 +21624,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>564168</v>
+        <v>563995</v>
       </c>
       <c r="R190" t="n">
-        <v>6705183</v>
+        <v>6704966</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -21699,10 +21686,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>119874581</v>
+        <v>119874604</v>
       </c>
       <c r="B191" t="n">
-        <v>90562</v>
+        <v>90334</v>
       </c>
       <c r="C191" t="inlineStr">
         <is>
@@ -21711,25 +21698,25 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E191" t="n">
-        <v>1202</v>
+        <v>3215</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
@@ -21739,10 +21726,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>563792</v>
+        <v>563936</v>
       </c>
       <c r="R191" t="n">
-        <v>6704700</v>
+        <v>6704867</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -21801,10 +21788,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>119874665</v>
+        <v>119874677</v>
       </c>
       <c r="B192" t="n">
-        <v>97907</v>
+        <v>93930</v>
       </c>
       <c r="C192" t="inlineStr">
         <is>
@@ -21813,47 +21800,38 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E192" t="n">
-        <v>220787</v>
+        <v>2383</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bågpraktmossa</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Plagiomnium medium</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I192" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J192" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Bruch &amp; Schimp.) T.J.Kop.</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr"/>
       <c r="P192" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>564008</v>
+        <v>563925</v>
       </c>
       <c r="R192" t="n">
-        <v>6704979</v>
+        <v>6704880</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -21912,10 +21890,10 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>119874593</v>
+        <v>119874630</v>
       </c>
       <c r="B193" t="n">
-        <v>90562</v>
+        <v>97907</v>
       </c>
       <c r="C193" t="inlineStr">
         <is>
@@ -21924,38 +21902,47 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I193" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J193" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P193" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>563710</v>
+        <v>563815</v>
       </c>
       <c r="R193" t="n">
-        <v>6704663</v>
+        <v>6704815</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -22014,10 +22001,10 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>119874568</v>
+        <v>119874619</v>
       </c>
       <c r="B194" t="n">
-        <v>90905</v>
+        <v>97907</v>
       </c>
       <c r="C194" t="inlineStr">
         <is>
@@ -22030,34 +22017,43 @@
         </is>
       </c>
       <c r="E194" t="n">
-        <v>2062</v>
+        <v>220787</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I194" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J194" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P194" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>563986</v>
+        <v>564203</v>
       </c>
       <c r="R194" t="n">
-        <v>6705032</v>
+        <v>6705186</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -22116,10 +22112,10 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>119874682</v>
+        <v>119874627</v>
       </c>
       <c r="B195" t="n">
-        <v>5169</v>
+        <v>97907</v>
       </c>
       <c r="C195" t="inlineStr">
         <is>
@@ -22128,43 +22124,54 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I195" t="inlineStr"/>
-      <c r="M195" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J195" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L195" t="inlineStr"/>
+      <c r="N195" t="inlineStr"/>
       <c r="P195" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>564000</v>
+        <v>563813</v>
       </c>
       <c r="R195" t="n">
-        <v>6704958</v>
+        <v>6704796</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -22199,12 +22206,18 @@
           <t>2024-09-20</t>
         </is>
       </c>
+      <c r="AC195" t="inlineStr">
+        <is>
+          <t>2 blomstjälkar</t>
+        </is>
+      </c>
       <c r="AD195" t="b">
         <v>0</v>
       </c>
       <c r="AE195" t="b">
         <v>0</v>
       </c>
+      <c r="AF195" t="inlineStr"/>
       <c r="AG195" t="b">
         <v>0</v>
       </c>
@@ -22223,10 +22236,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>119874608</v>
+        <v>119874655</v>
       </c>
       <c r="B196" t="n">
-        <v>94311</v>
+        <v>97907</v>
       </c>
       <c r="C196" t="inlineStr">
         <is>
@@ -22235,38 +22248,47 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E196" t="n">
-        <v>2809</v>
+        <v>220787</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
-        </is>
-      </c>
-      <c r="I196" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J196" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P196" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>563944</v>
+        <v>563757</v>
       </c>
       <c r="R196" t="n">
-        <v>6704880</v>
+        <v>6704730</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -22325,7 +22347,7 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>119874621</v>
+        <v>119874661</v>
       </c>
       <c r="B197" t="n">
         <v>97907</v>
@@ -22360,7 +22382,7 @@
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
@@ -22374,10 +22396,10 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>564283</v>
+        <v>563645</v>
       </c>
       <c r="R197" t="n">
-        <v>6705293</v>
+        <v>6704515</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -22436,7 +22458,7 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>119874649</v>
+        <v>119874621</v>
       </c>
       <c r="B198" t="n">
         <v>97907</v>
@@ -22471,7 +22493,7 @@
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J198" t="inlineStr">
@@ -22485,10 +22507,10 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>563765</v>
+        <v>564283</v>
       </c>
       <c r="R198" t="n">
-        <v>6704626</v>
+        <v>6705293</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -22547,7 +22569,7 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>119874627</v>
+        <v>119874623</v>
       </c>
       <c r="B199" t="n">
         <v>97907</v>
@@ -22582,7 +22604,7 @@
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
@@ -22590,23 +22612,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K199" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L199" t="inlineStr"/>
-      <c r="N199" t="inlineStr"/>
       <c r="P199" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>563813</v>
+        <v>563637</v>
       </c>
       <c r="R199" t="n">
-        <v>6704796</v>
+        <v>6704477</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -22641,18 +22656,12 @@
           <t>2024-09-20</t>
         </is>
       </c>
-      <c r="AC199" t="inlineStr">
-        <is>
-          <t>2 blomstjälkar</t>
-        </is>
-      </c>
       <c r="AD199" t="b">
         <v>0</v>
       </c>
       <c r="AE199" t="b">
         <v>0</v>
       </c>
-      <c r="AF199" t="inlineStr"/>
       <c r="AG199" t="b">
         <v>0</v>
       </c>
@@ -22671,10 +22680,10 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>119874644</v>
+        <v>119874666</v>
       </c>
       <c r="B200" t="n">
-        <v>97907</v>
+        <v>74577</v>
       </c>
       <c r="C200" t="inlineStr">
         <is>
@@ -22683,47 +22692,38 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>220787</v>
+        <v>6426</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I200" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J200" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr"/>
       <c r="P200" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>563984</v>
+        <v>563945</v>
       </c>
       <c r="R200" t="n">
-        <v>6704957</v>
+        <v>6704877</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -22782,7 +22782,7 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>119874577</v>
+        <v>119874580</v>
       </c>
       <c r="B201" t="n">
         <v>90562</v>
@@ -22822,10 +22822,10 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>563703</v>
+        <v>563702</v>
       </c>
       <c r="R201" t="n">
-        <v>6704669</v>
+        <v>6704652</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -22884,10 +22884,10 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>119874668</v>
+        <v>119874632</v>
       </c>
       <c r="B202" t="n">
-        <v>74577</v>
+        <v>97907</v>
       </c>
       <c r="C202" t="inlineStr">
         <is>
@@ -22896,38 +22896,47 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E202" t="n">
-        <v>6426</v>
+        <v>220787</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I202" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J202" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P202" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>563937</v>
+        <v>563770</v>
       </c>
       <c r="R202" t="n">
-        <v>6704867</v>
+        <v>6704729</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -22986,7 +22995,7 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>119874651</v>
+        <v>119874659</v>
       </c>
       <c r="B203" t="n">
         <v>97907</v>
@@ -23035,10 +23044,10 @@
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>564256</v>
+        <v>563746</v>
       </c>
       <c r="R203" t="n">
-        <v>6705293</v>
+        <v>6704720</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -23097,10 +23106,10 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>119874646</v>
+        <v>119874590</v>
       </c>
       <c r="B204" t="n">
-        <v>97907</v>
+        <v>90562</v>
       </c>
       <c r="C204" t="inlineStr">
         <is>
@@ -23109,47 +23118,38 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E204" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I204" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J204" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr"/>
       <c r="P204" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>563995</v>
+        <v>564015</v>
       </c>
       <c r="R204" t="n">
-        <v>6704966</v>
+        <v>6705047</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>
@@ -23208,10 +23208,10 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>119874590</v>
+        <v>119874665</v>
       </c>
       <c r="B205" t="n">
-        <v>90562</v>
+        <v>97907</v>
       </c>
       <c r="C205" t="inlineStr">
         <is>
@@ -23220,38 +23220,47 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E205" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I205" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J205" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P205" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>564015</v>
+        <v>564008</v>
       </c>
       <c r="R205" t="n">
-        <v>6705047</v>
+        <v>6704979</v>
       </c>
       <c r="S205" t="n">
         <v>10</v>
@@ -23310,10 +23319,10 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>119874599</v>
+        <v>119874615</v>
       </c>
       <c r="B206" t="n">
-        <v>57326</v>
+        <v>97907</v>
       </c>
       <c r="C206" t="inlineStr">
         <is>
@@ -23322,31 +23331,35 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E206" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I206" t="inlineStr"/>
-      <c r="M206" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J206" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P206" t="inlineStr">
@@ -23355,10 +23368,10 @@
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>563944</v>
+        <v>563748</v>
       </c>
       <c r="R206" t="n">
-        <v>6704948</v>
+        <v>6704608</v>
       </c>
       <c r="S206" t="n">
         <v>10</v>
@@ -23417,7 +23430,7 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>119874659</v>
+        <v>119874639</v>
       </c>
       <c r="B207" t="n">
         <v>97907</v>
@@ -23452,7 +23465,7 @@
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J207" t="inlineStr">
@@ -23466,10 +23479,10 @@
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>563746</v>
+        <v>563718</v>
       </c>
       <c r="R207" t="n">
-        <v>6704720</v>
+        <v>6704563</v>
       </c>
       <c r="S207" t="n">
         <v>10</v>
@@ -23528,7 +23541,7 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>119874612</v>
+        <v>119874635</v>
       </c>
       <c r="B208" t="n">
         <v>97907</v>
@@ -23563,7 +23576,7 @@
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J208" t="inlineStr">
@@ -23571,23 +23584,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K208" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L208" t="inlineStr"/>
-      <c r="N208" t="inlineStr"/>
       <c r="P208" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>564201</v>
+        <v>563705</v>
       </c>
       <c r="R208" t="n">
-        <v>6705191</v>
+        <v>6704657</v>
       </c>
       <c r="S208" t="n">
         <v>10</v>
@@ -23622,18 +23628,12 @@
           <t>2024-09-20</t>
         </is>
       </c>
-      <c r="AC208" t="inlineStr">
-        <is>
-          <t>1 blomstjälk</t>
-        </is>
-      </c>
       <c r="AD208" t="b">
         <v>0</v>
       </c>
       <c r="AE208" t="b">
         <v>0</v>
       </c>
-      <c r="AF208" t="inlineStr"/>
       <c r="AG208" t="b">
         <v>0</v>
       </c>
@@ -23652,7 +23652,7 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>119874619</v>
+        <v>119874649</v>
       </c>
       <c r="B209" t="n">
         <v>97907</v>
@@ -23687,7 +23687,7 @@
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J209" t="inlineStr">
@@ -23701,10 +23701,10 @@
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>564203</v>
+        <v>563765</v>
       </c>
       <c r="R209" t="n">
-        <v>6705186</v>
+        <v>6704626</v>
       </c>
       <c r="S209" t="n">
         <v>10</v>

--- a/artfynd/A 58548-2022 artfynd.xlsx
+++ b/artfynd/A 58548-2022 artfynd.xlsx
@@ -15797,10 +15797,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>119874574</v>
+        <v>119874633</v>
       </c>
       <c r="B136" t="n">
-        <v>90562</v>
+        <v>97907</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -15809,38 +15809,47 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I136" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P136" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>563796</v>
+        <v>563741</v>
       </c>
       <c r="R136" t="n">
-        <v>6704785</v>
+        <v>6704721</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15899,10 +15908,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>119874597</v>
+        <v>119874625</v>
       </c>
       <c r="B137" t="n">
-        <v>91494</v>
+        <v>97907</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -15911,38 +15920,47 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>4769</v>
+        <v>220787</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I137" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P137" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>563943</v>
+        <v>564201</v>
       </c>
       <c r="R137" t="n">
-        <v>6704878</v>
+        <v>6705184</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -16001,7 +16019,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>119874633</v>
+        <v>119874626</v>
       </c>
       <c r="B138" t="n">
         <v>97907</v>
@@ -16044,16 +16062,23 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L138" t="inlineStr"/>
+      <c r="N138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>563741</v>
+        <v>564019</v>
       </c>
       <c r="R138" t="n">
-        <v>6704721</v>
+        <v>6704997</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -16088,12 +16113,18 @@
           <t>2024-09-20</t>
         </is>
       </c>
+      <c r="AC138" t="inlineStr">
+        <is>
+          <t>1 blomstjälk</t>
+        </is>
+      </c>
       <c r="AD138" t="b">
         <v>0</v>
       </c>
       <c r="AE138" t="b">
         <v>0</v>
       </c>
+      <c r="AF138" t="inlineStr"/>
       <c r="AG138" t="b">
         <v>0</v>
       </c>
@@ -16112,10 +16143,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>119874626</v>
+        <v>119874574</v>
       </c>
       <c r="B139" t="n">
-        <v>97907</v>
+        <v>90562</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -16124,54 +16155,38 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I139" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J139" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K139" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L139" t="inlineStr"/>
-      <c r="N139" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>564019</v>
+        <v>563796</v>
       </c>
       <c r="R139" t="n">
-        <v>6704997</v>
+        <v>6704785</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -16206,18 +16221,12 @@
           <t>2024-09-20</t>
         </is>
       </c>
-      <c r="AC139" t="inlineStr">
-        <is>
-          <t>1 blomstjälk</t>
-        </is>
-      </c>
       <c r="AD139" t="b">
         <v>0</v>
       </c>
       <c r="AE139" t="b">
         <v>0</v>
       </c>
-      <c r="AF139" t="inlineStr"/>
       <c r="AG139" t="b">
         <v>0</v>
       </c>
@@ -16236,10 +16245,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>119874625</v>
+        <v>119874597</v>
       </c>
       <c r="B140" t="n">
-        <v>97907</v>
+        <v>91494</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -16248,47 +16257,38 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>220787</v>
+        <v>4769</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I140" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J140" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Scop.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>564201</v>
+        <v>563943</v>
       </c>
       <c r="R140" t="n">
-        <v>6705184</v>
+        <v>6704878</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -17399,10 +17399,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>119874606</v>
+        <v>119874575</v>
       </c>
       <c r="B151" t="n">
-        <v>90846</v>
+        <v>90562</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -17415,21 +17415,21 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -17439,10 +17439,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>563784</v>
+        <v>563720</v>
       </c>
       <c r="R151" t="n">
-        <v>6704721</v>
+        <v>6704700</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -17475,11 +17475,6 @@
       <c r="AA151" t="inlineStr">
         <is>
           <t>2024-09-20</t>
-        </is>
-      </c>
-      <c r="AC151" t="inlineStr">
-        <is>
-          <t>Äldre fruktkropp</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -17506,10 +17501,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>119874685</v>
+        <v>119874606</v>
       </c>
       <c r="B152" t="n">
-        <v>8421</v>
+        <v>90846</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -17518,43 +17513,38 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>106554</v>
+        <v>658</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
-      <c r="M152" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P152" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>563845</v>
+        <v>563784</v>
       </c>
       <c r="R152" t="n">
-        <v>6704771</v>
+        <v>6704721</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -17587,6 +17577,11 @@
       <c r="AA152" t="inlineStr">
         <is>
           <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AC152" t="inlineStr">
+        <is>
+          <t>Äldre fruktkropp</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -17613,10 +17608,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>119874575</v>
+        <v>119874685</v>
       </c>
       <c r="B153" t="n">
-        <v>90562</v>
+        <v>8421</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -17625,38 +17620,43 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>1202</v>
+        <v>106554</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P153" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>563720</v>
+        <v>563845</v>
       </c>
       <c r="R153" t="n">
-        <v>6704700</v>
+        <v>6704771</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -17715,10 +17715,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>119874605</v>
+        <v>119874642</v>
       </c>
       <c r="B154" t="n">
-        <v>90334</v>
+        <v>97907</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -17727,38 +17727,47 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>3215</v>
+        <v>220787</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I154" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P154" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>563929</v>
+        <v>563974</v>
       </c>
       <c r="R154" t="n">
-        <v>6704878</v>
+        <v>6704953</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -17817,10 +17826,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>119874684</v>
+        <v>119874605</v>
       </c>
       <c r="B155" t="n">
-        <v>100171</v>
+        <v>90334</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -17833,21 +17842,21 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>222498</v>
+        <v>3215</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -17857,10 +17866,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>563956</v>
+        <v>563929</v>
       </c>
       <c r="R155" t="n">
-        <v>6704876</v>
+        <v>6704878</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -17919,10 +17928,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>119874642</v>
+        <v>119874684</v>
       </c>
       <c r="B156" t="n">
-        <v>97907</v>
+        <v>100171</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -17931,47 +17940,38 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I156" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J156" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>563974</v>
+        <v>563956</v>
       </c>
       <c r="R156" t="n">
-        <v>6704953</v>
+        <v>6704876</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -20924,7 +20924,7 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>119874634</v>
+        <v>119874658</v>
       </c>
       <c r="B184" t="n">
         <v>97907</v>
@@ -20959,7 +20959,7 @@
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
@@ -20973,10 +20973,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>563712</v>
+        <v>563749</v>
       </c>
       <c r="R184" t="n">
-        <v>6704670</v>
+        <v>6704725</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -21035,7 +21035,7 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>119874658</v>
+        <v>119874634</v>
       </c>
       <c r="B185" t="n">
         <v>97907</v>
@@ -21070,7 +21070,7 @@
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J185" t="inlineStr">
@@ -21084,10 +21084,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>563749</v>
+        <v>563712</v>
       </c>
       <c r="R185" t="n">
-        <v>6704725</v>
+        <v>6704670</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -22680,10 +22680,10 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>119874666</v>
+        <v>119874580</v>
       </c>
       <c r="B200" t="n">
-        <v>74577</v>
+        <v>90562</v>
       </c>
       <c r="C200" t="inlineStr">
         <is>
@@ -22692,25 +22692,25 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>6426</v>
+        <v>1202</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
@@ -22720,10 +22720,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>563945</v>
+        <v>563702</v>
       </c>
       <c r="R200" t="n">
-        <v>6704877</v>
+        <v>6704652</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -22782,10 +22782,10 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>119874580</v>
+        <v>119874632</v>
       </c>
       <c r="B201" t="n">
-        <v>90562</v>
+        <v>97907</v>
       </c>
       <c r="C201" t="inlineStr">
         <is>
@@ -22794,38 +22794,47 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E201" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I201" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P201" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>563702</v>
+        <v>563770</v>
       </c>
       <c r="R201" t="n">
-        <v>6704652</v>
+        <v>6704729</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -22884,7 +22893,7 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>119874632</v>
+        <v>119874659</v>
       </c>
       <c r="B202" t="n">
         <v>97907</v>
@@ -22919,7 +22928,7 @@
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J202" t="inlineStr">
@@ -22933,10 +22942,10 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>563770</v>
+        <v>563746</v>
       </c>
       <c r="R202" t="n">
-        <v>6704729</v>
+        <v>6704720</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -22995,10 +23004,10 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>119874659</v>
+        <v>119874666</v>
       </c>
       <c r="B203" t="n">
-        <v>97907</v>
+        <v>74577</v>
       </c>
       <c r="C203" t="inlineStr">
         <is>
@@ -23007,47 +23016,38 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E203" t="n">
-        <v>220787</v>
+        <v>6426</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I203" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J203" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr"/>
       <c r="P203" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>563746</v>
+        <v>563945</v>
       </c>
       <c r="R203" t="n">
-        <v>6704720</v>
+        <v>6704877</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>

--- a/artfynd/A 58548-2022 artfynd.xlsx
+++ b/artfynd/A 58548-2022 artfynd.xlsx
@@ -15695,10 +15695,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>119874668</v>
+        <v>119874658</v>
       </c>
       <c r="B135" t="n">
-        <v>74577</v>
+        <v>97907</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -15707,38 +15707,47 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6426</v>
+        <v>220787</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I135" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P135" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>563937</v>
+        <v>563749</v>
       </c>
       <c r="R135" t="n">
-        <v>6704867</v>
+        <v>6704725</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -15797,7 +15806,7 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>119874633</v>
+        <v>119874661</v>
       </c>
       <c r="B136" t="n">
         <v>97907</v>
@@ -15832,7 +15841,7 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
@@ -15846,10 +15855,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>563741</v>
+        <v>563645</v>
       </c>
       <c r="R136" t="n">
-        <v>6704721</v>
+        <v>6704515</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15908,7 +15917,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>119874625</v>
+        <v>119874649</v>
       </c>
       <c r="B137" t="n">
         <v>97907</v>
@@ -15943,7 +15952,7 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
@@ -15957,10 +15966,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>564201</v>
+        <v>563765</v>
       </c>
       <c r="R137" t="n">
-        <v>6705184</v>
+        <v>6704626</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -16019,10 +16028,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>119874626</v>
+        <v>119874685</v>
       </c>
       <c r="B138" t="n">
-        <v>97907</v>
+        <v>8421</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -16031,54 +16040,43 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>220787</v>
+        <v>106554</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I138" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J138" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K138" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L138" t="inlineStr"/>
-      <c r="N138" t="inlineStr"/>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr"/>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P138" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>564019</v>
+        <v>563845</v>
       </c>
       <c r="R138" t="n">
-        <v>6704997</v>
+        <v>6704771</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -16113,18 +16111,12 @@
           <t>2024-09-20</t>
         </is>
       </c>
-      <c r="AC138" t="inlineStr">
-        <is>
-          <t>1 blomstjälk</t>
-        </is>
-      </c>
       <c r="AD138" t="b">
         <v>0</v>
       </c>
       <c r="AE138" t="b">
         <v>0</v>
       </c>
-      <c r="AF138" t="inlineStr"/>
       <c r="AG138" t="b">
         <v>0</v>
       </c>
@@ -16143,10 +16135,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>119874574</v>
+        <v>119874665</v>
       </c>
       <c r="B139" t="n">
-        <v>90562</v>
+        <v>97907</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -16155,38 +16147,47 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I139" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P139" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>563796</v>
+        <v>564008</v>
       </c>
       <c r="R139" t="n">
-        <v>6704785</v>
+        <v>6704979</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -16245,10 +16246,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>119874597</v>
+        <v>119874618</v>
       </c>
       <c r="B140" t="n">
-        <v>91494</v>
+        <v>97907</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -16257,38 +16258,47 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>4769</v>
+        <v>220787</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I140" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P140" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>563943</v>
+        <v>564168</v>
       </c>
       <c r="R140" t="n">
-        <v>6704878</v>
+        <v>6705183</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -16347,10 +16357,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>119874571</v>
+        <v>119874613</v>
       </c>
       <c r="B141" t="n">
-        <v>90562</v>
+        <v>97907</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -16359,38 +16369,47 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I141" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P141" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>563816</v>
+        <v>563794</v>
       </c>
       <c r="R141" t="n">
-        <v>6704792</v>
+        <v>6704750</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -16449,10 +16468,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>119874581</v>
+        <v>119874651</v>
       </c>
       <c r="B142" t="n">
-        <v>90562</v>
+        <v>97907</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -16461,38 +16480,47 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I142" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P142" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>563792</v>
+        <v>564256</v>
       </c>
       <c r="R142" t="n">
-        <v>6704700</v>
+        <v>6705293</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -16551,10 +16579,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>119874644</v>
+        <v>119874567</v>
       </c>
       <c r="B143" t="n">
-        <v>97907</v>
+        <v>90905</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -16567,43 +16595,34 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>220787</v>
+        <v>2062</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I143" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J143" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>563984</v>
+        <v>564000</v>
       </c>
       <c r="R143" t="n">
-        <v>6704957</v>
+        <v>6705011</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -16662,10 +16681,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>119874609</v>
+        <v>119874590</v>
       </c>
       <c r="B144" t="n">
-        <v>90954</v>
+        <v>90562</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -16678,16 +16697,21 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>6040186</v>
+        <v>1202</v>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -16697,10 +16721,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>564083</v>
+        <v>564015</v>
       </c>
       <c r="R144" t="n">
-        <v>6705090</v>
+        <v>6705047</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -16759,10 +16783,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>119874652</v>
+        <v>119874581</v>
       </c>
       <c r="B145" t="n">
-        <v>97907</v>
+        <v>90562</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -16771,47 +16795,38 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I145" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J145" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>563976</v>
+        <v>563792</v>
       </c>
       <c r="R145" t="n">
-        <v>6704966</v>
+        <v>6704700</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -16870,10 +16885,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>119874651</v>
+        <v>119874682</v>
       </c>
       <c r="B146" t="n">
-        <v>97907</v>
+        <v>5169</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -16882,35 +16897,31 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I146" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J146" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr"/>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P146" t="inlineStr">
@@ -16919,10 +16930,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>564256</v>
+        <v>564000</v>
       </c>
       <c r="R146" t="n">
-        <v>6705293</v>
+        <v>6704958</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16981,10 +16992,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>119874678</v>
+        <v>119874605</v>
       </c>
       <c r="B147" t="n">
-        <v>5169</v>
+        <v>90334</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -16997,36 +17008,31 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>100526</v>
+        <v>3215</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
-      <c r="M147" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P147" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>563957</v>
+        <v>563929</v>
       </c>
       <c r="R147" t="n">
         <v>6704878</v>
@@ -17088,10 +17094,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>119874591</v>
+        <v>119874647</v>
       </c>
       <c r="B148" t="n">
-        <v>90562</v>
+        <v>97907</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -17100,38 +17106,54 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I148" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L148" t="inlineStr"/>
+      <c r="N148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>564204</v>
+        <v>564036</v>
       </c>
       <c r="R148" t="n">
-        <v>6705194</v>
+        <v>6705043</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -17166,12 +17188,18 @@
           <t>2024-09-20</t>
         </is>
       </c>
+      <c r="AC148" t="inlineStr">
+        <is>
+          <t>1 blomstjälk</t>
+        </is>
+      </c>
       <c r="AD148" t="b">
         <v>0</v>
       </c>
       <c r="AE148" t="b">
         <v>0</v>
       </c>
+      <c r="AF148" t="inlineStr"/>
       <c r="AG148" t="b">
         <v>0</v>
       </c>
@@ -17190,10 +17218,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>119874680</v>
+        <v>119874646</v>
       </c>
       <c r="B149" t="n">
-        <v>5169</v>
+        <v>97907</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -17202,31 +17230,35 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I149" t="inlineStr"/>
-      <c r="M149" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P149" t="inlineStr">
@@ -17235,10 +17267,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>563792</v>
+        <v>563995</v>
       </c>
       <c r="R149" t="n">
-        <v>6704694</v>
+        <v>6704966</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -17297,10 +17329,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>119874572</v>
+        <v>119874617</v>
       </c>
       <c r="B150" t="n">
-        <v>90562</v>
+        <v>97907</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -17309,38 +17341,47 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I150" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P150" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>563815</v>
+        <v>563833</v>
       </c>
       <c r="R150" t="n">
-        <v>6704789</v>
+        <v>6704788</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -17399,10 +17440,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>119874575</v>
+        <v>119874644</v>
       </c>
       <c r="B151" t="n">
-        <v>90562</v>
+        <v>97907</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -17411,38 +17452,47 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I151" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P151" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>563720</v>
+        <v>563984</v>
       </c>
       <c r="R151" t="n">
-        <v>6704700</v>
+        <v>6704957</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -17501,10 +17551,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>119874606</v>
+        <v>119874574</v>
       </c>
       <c r="B152" t="n">
-        <v>90846</v>
+        <v>90562</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -17517,21 +17567,21 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -17541,10 +17591,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>563784</v>
+        <v>563796</v>
       </c>
       <c r="R152" t="n">
-        <v>6704721</v>
+        <v>6704785</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -17577,11 +17627,6 @@
       <c r="AA152" t="inlineStr">
         <is>
           <t>2024-09-20</t>
-        </is>
-      </c>
-      <c r="AC152" t="inlineStr">
-        <is>
-          <t>Äldre fruktkropp</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -17608,10 +17653,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>119874685</v>
+        <v>119874684</v>
       </c>
       <c r="B153" t="n">
-        <v>8421</v>
+        <v>100171</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -17624,39 +17669,34 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>106554</v>
+        <v>222498</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
-      <c r="M153" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P153" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>563845</v>
+        <v>563956</v>
       </c>
       <c r="R153" t="n">
-        <v>6704771</v>
+        <v>6704876</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -17826,10 +17866,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>119874605</v>
+        <v>119874571</v>
       </c>
       <c r="B155" t="n">
-        <v>90334</v>
+        <v>90562</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -17838,25 +17878,25 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>3215</v>
+        <v>1202</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -17866,10 +17906,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>563929</v>
+        <v>563816</v>
       </c>
       <c r="R155" t="n">
-        <v>6704878</v>
+        <v>6704792</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -17928,10 +17968,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>119874684</v>
+        <v>119874582</v>
       </c>
       <c r="B156" t="n">
-        <v>100171</v>
+        <v>90562</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -17940,25 +17980,25 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -17968,10 +18008,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>563956</v>
+        <v>563958</v>
       </c>
       <c r="R156" t="n">
-        <v>6704876</v>
+        <v>6704952</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -18030,10 +18070,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>119874682</v>
+        <v>119874666</v>
       </c>
       <c r="B157" t="n">
-        <v>5169</v>
+        <v>74577</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -18046,39 +18086,34 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>100526</v>
+        <v>6426</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
-      <c r="M157" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P157" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>564000</v>
+        <v>563945</v>
       </c>
       <c r="R157" t="n">
-        <v>6704958</v>
+        <v>6704877</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -18137,10 +18172,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>119874624</v>
+        <v>119874596</v>
       </c>
       <c r="B158" t="n">
-        <v>97907</v>
+        <v>57463</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -18149,47 +18184,50 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J158" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr"/>
+      <c r="L158" t="inlineStr"/>
+      <c r="M158" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>563734</v>
+        <v>563633</v>
       </c>
       <c r="R158" t="n">
-        <v>6704595</v>
+        <v>6704498</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -18248,10 +18286,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>119874566</v>
+        <v>119874597</v>
       </c>
       <c r="B159" t="n">
-        <v>90905</v>
+        <v>91494</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -18260,25 +18298,25 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>2062</v>
+        <v>4769</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -18288,10 +18326,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>564137</v>
+        <v>563943</v>
       </c>
       <c r="R159" t="n">
-        <v>6705070</v>
+        <v>6704878</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -18350,7 +18388,7 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>119874593</v>
+        <v>119874588</v>
       </c>
       <c r="B160" t="n">
         <v>90562</v>
@@ -18390,10 +18428,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>563710</v>
+        <v>564011</v>
       </c>
       <c r="R160" t="n">
-        <v>6704663</v>
+        <v>6705060</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -18452,7 +18490,7 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>119874582</v>
+        <v>119874575</v>
       </c>
       <c r="B161" t="n">
         <v>90562</v>
@@ -18492,10 +18530,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>563958</v>
+        <v>563720</v>
       </c>
       <c r="R161" t="n">
-        <v>6704952</v>
+        <v>6704700</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -18554,10 +18592,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>119874586</v>
+        <v>119874681</v>
       </c>
       <c r="B162" t="n">
-        <v>90562</v>
+        <v>5169</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
@@ -18566,38 +18604,43 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
+      <c r="M162" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P162" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>564005</v>
+        <v>563825</v>
       </c>
       <c r="R162" t="n">
-        <v>6705064</v>
+        <v>6704705</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -18656,10 +18699,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>119874608</v>
+        <v>119874668</v>
       </c>
       <c r="B163" t="n">
-        <v>94311</v>
+        <v>74577</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -18672,21 +18715,21 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>2809</v>
+        <v>6426</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
@@ -18696,10 +18739,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>563944</v>
+        <v>563937</v>
       </c>
       <c r="R163" t="n">
-        <v>6704880</v>
+        <v>6704867</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -18758,10 +18801,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>119874637</v>
+        <v>119874593</v>
       </c>
       <c r="B164" t="n">
-        <v>97907</v>
+        <v>90562</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -18770,47 +18813,38 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I164" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J164" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>563648</v>
+        <v>563710</v>
       </c>
       <c r="R164" t="n">
-        <v>6704505</v>
+        <v>6704663</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -18869,10 +18903,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>119874663</v>
+        <v>119874607</v>
       </c>
       <c r="B165" t="n">
-        <v>97907</v>
+        <v>90846</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -18881,47 +18915,38 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I165" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J165" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>563835</v>
+        <v>563821</v>
       </c>
       <c r="R165" t="n">
-        <v>6704743</v>
+        <v>6704817</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -18980,7 +19005,7 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>119874568</v>
+        <v>119874566</v>
       </c>
       <c r="B166" t="n">
         <v>90905</v>
@@ -19020,10 +19045,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>563986</v>
+        <v>564137</v>
       </c>
       <c r="R166" t="n">
-        <v>6705032</v>
+        <v>6705070</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -19082,10 +19107,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>119874585</v>
+        <v>119874633</v>
       </c>
       <c r="B167" t="n">
-        <v>90562</v>
+        <v>97907</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
@@ -19094,38 +19119,47 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I167" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P167" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>563986</v>
+        <v>563741</v>
       </c>
       <c r="R167" t="n">
-        <v>6705041</v>
+        <v>6704721</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -19184,7 +19218,7 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>119874628</v>
+        <v>119874663</v>
       </c>
       <c r="B168" t="n">
         <v>97907</v>
@@ -19219,7 +19253,7 @@
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
@@ -19233,10 +19267,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>564206</v>
+        <v>563835</v>
       </c>
       <c r="R168" t="n">
-        <v>6705189</v>
+        <v>6704743</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -19295,7 +19329,7 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>119874613</v>
+        <v>119874655</v>
       </c>
       <c r="B169" t="n">
         <v>97907</v>
@@ -19330,7 +19364,7 @@
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
@@ -19344,10 +19378,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>563794</v>
+        <v>563757</v>
       </c>
       <c r="R169" t="n">
-        <v>6704750</v>
+        <v>6704730</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -19406,10 +19440,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>119874576</v>
+        <v>119874628</v>
       </c>
       <c r="B170" t="n">
-        <v>90562</v>
+        <v>97907</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
@@ -19418,38 +19452,47 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I170" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P170" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>563718</v>
+        <v>564206</v>
       </c>
       <c r="R170" t="n">
-        <v>6704695</v>
+        <v>6705189</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -19508,10 +19551,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>119874573</v>
+        <v>119874630</v>
       </c>
       <c r="B171" t="n">
-        <v>90562</v>
+        <v>97907</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
@@ -19520,38 +19563,47 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I171" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P171" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>563794</v>
+        <v>563815</v>
       </c>
       <c r="R171" t="n">
-        <v>6704792</v>
+        <v>6704815</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -19610,7 +19662,7 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>119874588</v>
+        <v>119874580</v>
       </c>
       <c r="B172" t="n">
         <v>90562</v>
@@ -19650,10 +19702,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>564011</v>
+        <v>563702</v>
       </c>
       <c r="R172" t="n">
-        <v>6705060</v>
+        <v>6704652</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -19712,10 +19764,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>119874567</v>
+        <v>119874678</v>
       </c>
       <c r="B173" t="n">
-        <v>90905</v>
+        <v>5169</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
@@ -19724,38 +19776,43 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>2062</v>
+        <v>100526</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
+      <c r="M173" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P173" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>564000</v>
+        <v>563957</v>
       </c>
       <c r="R173" t="n">
-        <v>6705011</v>
+        <v>6704878</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -19814,10 +19871,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>119874681</v>
+        <v>119874606</v>
       </c>
       <c r="B174" t="n">
-        <v>5169</v>
+        <v>90846</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
@@ -19826,43 +19883,38 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>100526</v>
+        <v>658</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
-      <c r="M174" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P174" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>563825</v>
+        <v>563784</v>
       </c>
       <c r="R174" t="n">
-        <v>6704705</v>
+        <v>6704721</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -19895,6 +19947,11 @@
       <c r="AA174" t="inlineStr">
         <is>
           <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AC174" t="inlineStr">
+        <is>
+          <t>Äldre fruktkropp</t>
         </is>
       </c>
       <c r="AD174" t="b">
@@ -19921,7 +19978,7 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>119874647</v>
+        <v>119874624</v>
       </c>
       <c r="B175" t="n">
         <v>97907</v>
@@ -19956,7 +20013,7 @@
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
@@ -19964,23 +20021,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K175" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L175" t="inlineStr"/>
-      <c r="N175" t="inlineStr"/>
       <c r="P175" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>564036</v>
+        <v>563734</v>
       </c>
       <c r="R175" t="n">
-        <v>6705043</v>
+        <v>6704595</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -20015,18 +20065,12 @@
           <t>2024-09-20</t>
         </is>
       </c>
-      <c r="AC175" t="inlineStr">
-        <is>
-          <t>1 blomstjälk</t>
-        </is>
-      </c>
       <c r="AD175" t="b">
         <v>0</v>
       </c>
       <c r="AE175" t="b">
         <v>0</v>
       </c>
-      <c r="AF175" t="inlineStr"/>
       <c r="AG175" t="b">
         <v>0</v>
       </c>
@@ -20045,10 +20089,10 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>119874599</v>
+        <v>119874627</v>
       </c>
       <c r="B176" t="n">
-        <v>57326</v>
+        <v>97907</v>
       </c>
       <c r="C176" t="inlineStr">
         <is>
@@ -20057,43 +20101,54 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I176" t="inlineStr"/>
-      <c r="M176" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L176" t="inlineStr"/>
+      <c r="N176" t="inlineStr"/>
       <c r="P176" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>563944</v>
+        <v>563813</v>
       </c>
       <c r="R176" t="n">
-        <v>6704948</v>
+        <v>6704796</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -20128,12 +20183,18 @@
           <t>2024-09-20</t>
         </is>
       </c>
+      <c r="AC176" t="inlineStr">
+        <is>
+          <t>2 blomstjälkar</t>
+        </is>
+      </c>
       <c r="AD176" t="b">
         <v>0</v>
       </c>
       <c r="AE176" t="b">
         <v>0</v>
       </c>
+      <c r="AF176" t="inlineStr"/>
       <c r="AG176" t="b">
         <v>0</v>
       </c>
@@ -20152,7 +20213,7 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>119874612</v>
+        <v>119874619</v>
       </c>
       <c r="B177" t="n">
         <v>97907</v>
@@ -20187,7 +20248,7 @@
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
@@ -20195,23 +20256,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K177" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L177" t="inlineStr"/>
-      <c r="N177" t="inlineStr"/>
       <c r="P177" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>564201</v>
+        <v>564203</v>
       </c>
       <c r="R177" t="n">
-        <v>6705191</v>
+        <v>6705186</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -20246,18 +20300,12 @@
           <t>2024-09-20</t>
         </is>
       </c>
-      <c r="AC177" t="inlineStr">
-        <is>
-          <t>1 blomstjälk</t>
-        </is>
-      </c>
       <c r="AD177" t="b">
         <v>0</v>
       </c>
       <c r="AE177" t="b">
         <v>0</v>
       </c>
-      <c r="AF177" t="inlineStr"/>
       <c r="AG177" t="b">
         <v>0</v>
       </c>
@@ -20276,7 +20324,7 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>119874622</v>
+        <v>119874626</v>
       </c>
       <c r="B178" t="n">
         <v>97907</v>
@@ -20311,7 +20359,7 @@
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
@@ -20319,16 +20367,23 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L178" t="inlineStr"/>
+      <c r="N178" t="inlineStr"/>
       <c r="P178" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>563711</v>
+        <v>564019</v>
       </c>
       <c r="R178" t="n">
-        <v>6704677</v>
+        <v>6704997</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -20363,12 +20418,18 @@
           <t>2024-09-20</t>
         </is>
       </c>
+      <c r="AC178" t="inlineStr">
+        <is>
+          <t>1 blomstjälk</t>
+        </is>
+      </c>
       <c r="AD178" t="b">
         <v>0</v>
       </c>
       <c r="AE178" t="b">
         <v>0</v>
       </c>
+      <c r="AF178" t="inlineStr"/>
       <c r="AG178" t="b">
         <v>0</v>
       </c>
@@ -20387,7 +20448,7 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>119874618</v>
+        <v>119874639</v>
       </c>
       <c r="B179" t="n">
         <v>97907</v>
@@ -20422,7 +20483,7 @@
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
@@ -20436,10 +20497,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>564168</v>
+        <v>563718</v>
       </c>
       <c r="R179" t="n">
-        <v>6705183</v>
+        <v>6704563</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -20498,7 +20559,7 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>119874617</v>
+        <v>119874659</v>
       </c>
       <c r="B180" t="n">
         <v>97907</v>
@@ -20533,7 +20594,7 @@
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
@@ -20547,10 +20608,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>563833</v>
+        <v>563746</v>
       </c>
       <c r="R180" t="n">
-        <v>6704788</v>
+        <v>6704720</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -20609,7 +20670,7 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>119874641</v>
+        <v>119874623</v>
       </c>
       <c r="B181" t="n">
         <v>97907</v>
@@ -20644,7 +20705,7 @@
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
@@ -20658,10 +20719,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>563808</v>
+        <v>563637</v>
       </c>
       <c r="R181" t="n">
-        <v>6704697</v>
+        <v>6704477</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -20720,10 +20781,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>119874607</v>
+        <v>119874608</v>
       </c>
       <c r="B182" t="n">
-        <v>90846</v>
+        <v>94311</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
@@ -20732,25 +20793,25 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>658</v>
+        <v>2809</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
@@ -20760,10 +20821,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>563821</v>
+        <v>563944</v>
       </c>
       <c r="R182" t="n">
-        <v>6704817</v>
+        <v>6704880</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -20924,7 +20985,7 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>119874658</v>
+        <v>119874621</v>
       </c>
       <c r="B184" t="n">
         <v>97907</v>
@@ -20959,7 +21020,7 @@
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
@@ -20973,10 +21034,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>563749</v>
+        <v>564283</v>
       </c>
       <c r="R184" t="n">
-        <v>6704725</v>
+        <v>6705293</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -21035,7 +21096,7 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>119874634</v>
+        <v>119874616</v>
       </c>
       <c r="B185" t="n">
         <v>97907</v>
@@ -21070,7 +21131,7 @@
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J185" t="inlineStr">
@@ -21084,10 +21145,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>563712</v>
+        <v>563993</v>
       </c>
       <c r="R185" t="n">
-        <v>6704670</v>
+        <v>6705035</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -21146,10 +21207,10 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>119874616</v>
+        <v>119874568</v>
       </c>
       <c r="B186" t="n">
-        <v>97907</v>
+        <v>90905</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
@@ -21162,43 +21223,34 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>220787</v>
+        <v>2062</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I186" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J186" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr"/>
       <c r="P186" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>563993</v>
+        <v>563986</v>
       </c>
       <c r="R186" t="n">
-        <v>6705035</v>
+        <v>6705032</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -21257,10 +21309,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>119874596</v>
+        <v>119874583</v>
       </c>
       <c r="B187" t="n">
-        <v>57463</v>
+        <v>90562</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
@@ -21273,46 +21325,34 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I187" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K187" t="inlineStr"/>
-      <c r="L187" t="inlineStr"/>
-      <c r="M187" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N187" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr"/>
       <c r="P187" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>563633</v>
+        <v>563996</v>
       </c>
       <c r="R187" t="n">
-        <v>6704498</v>
+        <v>6705007</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -21371,10 +21411,10 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>119874583</v>
+        <v>119874599</v>
       </c>
       <c r="B188" t="n">
-        <v>90562</v>
+        <v>57326</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
@@ -21387,34 +21427,39 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
+      <c r="M188" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P188" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>563996</v>
+        <v>563944</v>
       </c>
       <c r="R188" t="n">
-        <v>6705007</v>
+        <v>6704948</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -21473,10 +21518,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>119874577</v>
+        <v>119874680</v>
       </c>
       <c r="B189" t="n">
-        <v>90562</v>
+        <v>5169</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
@@ -21485,38 +21530,43 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E189" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
+      <c r="M189" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P189" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>563703</v>
+        <v>563792</v>
       </c>
       <c r="R189" t="n">
-        <v>6704669</v>
+        <v>6704694</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -21575,10 +21625,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>119874646</v>
+        <v>119874609</v>
       </c>
       <c r="B190" t="n">
-        <v>97907</v>
+        <v>90954</v>
       </c>
       <c r="C190" t="inlineStr">
         <is>
@@ -21587,47 +21637,33 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E190" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F190" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I190" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J190" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr"/>
       <c r="P190" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>563995</v>
+        <v>564083</v>
       </c>
       <c r="R190" t="n">
-        <v>6704966</v>
+        <v>6705090</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -21686,10 +21722,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>119874604</v>
+        <v>119874652</v>
       </c>
       <c r="B191" t="n">
-        <v>90334</v>
+        <v>97907</v>
       </c>
       <c r="C191" t="inlineStr">
         <is>
@@ -21698,38 +21734,47 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E191" t="n">
-        <v>3215</v>
+        <v>220787</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I191" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J191" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P191" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>563936</v>
+        <v>563976</v>
       </c>
       <c r="R191" t="n">
-        <v>6704867</v>
+        <v>6704966</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -21788,10 +21833,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>119874677</v>
+        <v>119874641</v>
       </c>
       <c r="B192" t="n">
-        <v>93930</v>
+        <v>97907</v>
       </c>
       <c r="C192" t="inlineStr">
         <is>
@@ -21800,38 +21845,47 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E192" t="n">
-        <v>2383</v>
+        <v>220787</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Bågpraktmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Plagiomnium medium</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(Bruch &amp; Schimp.) T.J.Kop.</t>
-        </is>
-      </c>
-      <c r="I192" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J192" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P192" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>563925</v>
+        <v>563808</v>
       </c>
       <c r="R192" t="n">
-        <v>6704880</v>
+        <v>6704697</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -21890,7 +21944,7 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>119874630</v>
+        <v>119874637</v>
       </c>
       <c r="B193" t="n">
         <v>97907</v>
@@ -21939,10 +21993,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>563815</v>
+        <v>563648</v>
       </c>
       <c r="R193" t="n">
-        <v>6704815</v>
+        <v>6704505</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -22001,10 +22055,10 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>119874619</v>
+        <v>119874604</v>
       </c>
       <c r="B194" t="n">
-        <v>97907</v>
+        <v>90334</v>
       </c>
       <c r="C194" t="inlineStr">
         <is>
@@ -22013,47 +22067,38 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>220787</v>
+        <v>3215</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I194" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J194" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr"/>
       <c r="P194" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>564203</v>
+        <v>563936</v>
       </c>
       <c r="R194" t="n">
-        <v>6705186</v>
+        <v>6704867</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -22112,10 +22157,10 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>119874627</v>
+        <v>119874591</v>
       </c>
       <c r="B195" t="n">
-        <v>97907</v>
+        <v>90562</v>
       </c>
       <c r="C195" t="inlineStr">
         <is>
@@ -22124,54 +22169,38 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I195" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J195" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K195" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L195" t="inlineStr"/>
-      <c r="N195" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr"/>
       <c r="P195" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>563813</v>
+        <v>564204</v>
       </c>
       <c r="R195" t="n">
-        <v>6704796</v>
+        <v>6705194</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -22206,18 +22235,12 @@
           <t>2024-09-20</t>
         </is>
       </c>
-      <c r="AC195" t="inlineStr">
-        <is>
-          <t>2 blomstjälkar</t>
-        </is>
-      </c>
       <c r="AD195" t="b">
         <v>0</v>
       </c>
       <c r="AE195" t="b">
         <v>0</v>
       </c>
-      <c r="AF195" t="inlineStr"/>
       <c r="AG195" t="b">
         <v>0</v>
       </c>
@@ -22236,10 +22259,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>119874655</v>
+        <v>119874585</v>
       </c>
       <c r="B196" t="n">
-        <v>97907</v>
+        <v>90562</v>
       </c>
       <c r="C196" t="inlineStr">
         <is>
@@ -22248,47 +22271,38 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E196" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I196" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J196" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr"/>
       <c r="P196" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>563757</v>
+        <v>563986</v>
       </c>
       <c r="R196" t="n">
-        <v>6704730</v>
+        <v>6705041</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -22347,10 +22361,10 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>119874661</v>
+        <v>119874577</v>
       </c>
       <c r="B197" t="n">
-        <v>97907</v>
+        <v>90562</v>
       </c>
       <c r="C197" t="inlineStr">
         <is>
@@ -22359,47 +22373,38 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I197" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J197" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr"/>
       <c r="P197" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>563645</v>
+        <v>563703</v>
       </c>
       <c r="R197" t="n">
-        <v>6704515</v>
+        <v>6704669</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -22458,10 +22463,10 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>119874621</v>
+        <v>119874677</v>
       </c>
       <c r="B198" t="n">
-        <v>97907</v>
+        <v>93930</v>
       </c>
       <c r="C198" t="inlineStr">
         <is>
@@ -22470,47 +22475,38 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E198" t="n">
-        <v>220787</v>
+        <v>2383</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bågpraktmossa</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Plagiomnium medium</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I198" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J198" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Bruch &amp; Schimp.) T.J.Kop.</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr"/>
       <c r="P198" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>564283</v>
+        <v>563925</v>
       </c>
       <c r="R198" t="n">
-        <v>6705293</v>
+        <v>6704880</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -22569,7 +22565,7 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>119874623</v>
+        <v>119874612</v>
       </c>
       <c r="B199" t="n">
         <v>97907</v>
@@ -22604,7 +22600,7 @@
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
@@ -22612,16 +22608,23 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L199" t="inlineStr"/>
+      <c r="N199" t="inlineStr"/>
       <c r="P199" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>563637</v>
+        <v>564201</v>
       </c>
       <c r="R199" t="n">
-        <v>6704477</v>
+        <v>6705191</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -22656,12 +22659,18 @@
           <t>2024-09-20</t>
         </is>
       </c>
+      <c r="AC199" t="inlineStr">
+        <is>
+          <t>1 blomstjälk</t>
+        </is>
+      </c>
       <c r="AD199" t="b">
         <v>0</v>
       </c>
       <c r="AE199" t="b">
         <v>0</v>
       </c>
+      <c r="AF199" t="inlineStr"/>
       <c r="AG199" t="b">
         <v>0</v>
       </c>
@@ -22680,7 +22689,7 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>119874580</v>
+        <v>119874576</v>
       </c>
       <c r="B200" t="n">
         <v>90562</v>
@@ -22720,10 +22729,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>563702</v>
+        <v>563718</v>
       </c>
       <c r="R200" t="n">
-        <v>6704652</v>
+        <v>6704695</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -22782,7 +22791,7 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>119874632</v>
+        <v>119874625</v>
       </c>
       <c r="B201" t="n">
         <v>97907</v>
@@ -22817,7 +22826,7 @@
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">
@@ -22831,10 +22840,10 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>563770</v>
+        <v>564201</v>
       </c>
       <c r="R201" t="n">
-        <v>6704729</v>
+        <v>6705184</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -22893,7 +22902,7 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>119874659</v>
+        <v>119874635</v>
       </c>
       <c r="B202" t="n">
         <v>97907</v>
@@ -22928,7 +22937,7 @@
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J202" t="inlineStr">
@@ -22942,10 +22951,10 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>563746</v>
+        <v>563705</v>
       </c>
       <c r="R202" t="n">
-        <v>6704720</v>
+        <v>6704657</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -23004,10 +23013,10 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>119874666</v>
+        <v>119874573</v>
       </c>
       <c r="B203" t="n">
-        <v>74577</v>
+        <v>90562</v>
       </c>
       <c r="C203" t="inlineStr">
         <is>
@@ -23016,25 +23025,25 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E203" t="n">
-        <v>6426</v>
+        <v>1202</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I203" t="inlineStr"/>
@@ -23044,10 +23053,10 @@
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>563945</v>
+        <v>563794</v>
       </c>
       <c r="R203" t="n">
-        <v>6704877</v>
+        <v>6704792</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -23106,7 +23115,7 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>119874590</v>
+        <v>119874586</v>
       </c>
       <c r="B204" t="n">
         <v>90562</v>
@@ -23146,10 +23155,10 @@
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>564015</v>
+        <v>564005</v>
       </c>
       <c r="R204" t="n">
-        <v>6705047</v>
+        <v>6705064</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>
@@ -23208,7 +23217,7 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>119874665</v>
+        <v>119874634</v>
       </c>
       <c r="B205" t="n">
         <v>97907</v>
@@ -23243,7 +23252,7 @@
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J205" t="inlineStr">
@@ -23257,10 +23266,10 @@
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>564008</v>
+        <v>563712</v>
       </c>
       <c r="R205" t="n">
-        <v>6704979</v>
+        <v>6704670</v>
       </c>
       <c r="S205" t="n">
         <v>10</v>
@@ -23319,10 +23328,10 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>119874615</v>
+        <v>119874572</v>
       </c>
       <c r="B206" t="n">
-        <v>97907</v>
+        <v>90562</v>
       </c>
       <c r="C206" t="inlineStr">
         <is>
@@ -23331,47 +23340,38 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E206" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I206" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J206" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr"/>
       <c r="P206" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>563748</v>
+        <v>563815</v>
       </c>
       <c r="R206" t="n">
-        <v>6704608</v>
+        <v>6704789</v>
       </c>
       <c r="S206" t="n">
         <v>10</v>
@@ -23430,7 +23430,7 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>119874639</v>
+        <v>119874622</v>
       </c>
       <c r="B207" t="n">
         <v>97907</v>
@@ -23465,7 +23465,7 @@
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J207" t="inlineStr">
@@ -23479,10 +23479,10 @@
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>563718</v>
+        <v>563711</v>
       </c>
       <c r="R207" t="n">
-        <v>6704563</v>
+        <v>6704677</v>
       </c>
       <c r="S207" t="n">
         <v>10</v>
@@ -23541,7 +23541,7 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>119874635</v>
+        <v>119874615</v>
       </c>
       <c r="B208" t="n">
         <v>97907</v>
@@ -23576,7 +23576,7 @@
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J208" t="inlineStr">
@@ -23590,10 +23590,10 @@
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>563705</v>
+        <v>563748</v>
       </c>
       <c r="R208" t="n">
-        <v>6704657</v>
+        <v>6704608</v>
       </c>
       <c r="S208" t="n">
         <v>10</v>
@@ -23652,7 +23652,7 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>119874649</v>
+        <v>119874632</v>
       </c>
       <c r="B209" t="n">
         <v>97907</v>
@@ -23687,7 +23687,7 @@
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J209" t="inlineStr">
@@ -23701,10 +23701,10 @@
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>563765</v>
+        <v>563770</v>
       </c>
       <c r="R209" t="n">
-        <v>6704626</v>
+        <v>6704729</v>
       </c>
       <c r="S209" t="n">
         <v>10</v>

--- a/artfynd/A 58548-2022 artfynd.xlsx
+++ b/artfynd/A 58548-2022 artfynd.xlsx
@@ -16028,10 +16028,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>119874685</v>
+        <v>119874590</v>
       </c>
       <c r="B138" t="n">
-        <v>8421</v>
+        <v>90562</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -16040,43 +16040,38 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>106554</v>
+        <v>1202</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
-      <c r="M138" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P138" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>563845</v>
+        <v>564015</v>
       </c>
       <c r="R138" t="n">
-        <v>6704771</v>
+        <v>6705047</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -16135,10 +16130,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>119874665</v>
+        <v>119874581</v>
       </c>
       <c r="B139" t="n">
-        <v>97907</v>
+        <v>90562</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -16147,47 +16142,38 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I139" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J139" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>564008</v>
+        <v>563792</v>
       </c>
       <c r="R139" t="n">
-        <v>6704979</v>
+        <v>6704700</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -16246,10 +16232,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>119874618</v>
+        <v>119874682</v>
       </c>
       <c r="B140" t="n">
-        <v>97907</v>
+        <v>5169</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -16258,35 +16244,31 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I140" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J140" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr"/>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P140" t="inlineStr">
@@ -16295,10 +16277,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>564168</v>
+        <v>564000</v>
       </c>
       <c r="R140" t="n">
-        <v>6705183</v>
+        <v>6704958</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -16357,10 +16339,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>119874613</v>
+        <v>119874685</v>
       </c>
       <c r="B141" t="n">
-        <v>97907</v>
+        <v>8421</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -16369,35 +16351,31 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>220787</v>
+        <v>106554</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I141" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J141" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr"/>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P141" t="inlineStr">
@@ -16406,10 +16384,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>563794</v>
+        <v>563845</v>
       </c>
       <c r="R141" t="n">
-        <v>6704750</v>
+        <v>6704771</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -16468,7 +16446,7 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>119874651</v>
+        <v>119874665</v>
       </c>
       <c r="B142" t="n">
         <v>97907</v>
@@ -16503,7 +16481,7 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
@@ -16517,10 +16495,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>564256</v>
+        <v>564008</v>
       </c>
       <c r="R142" t="n">
-        <v>6705293</v>
+        <v>6704979</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -16579,10 +16557,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>119874567</v>
+        <v>119874618</v>
       </c>
       <c r="B143" t="n">
-        <v>90905</v>
+        <v>97907</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -16595,34 +16573,43 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>2062</v>
+        <v>220787</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I143" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P143" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>564000</v>
+        <v>564168</v>
       </c>
       <c r="R143" t="n">
-        <v>6705011</v>
+        <v>6705183</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -16681,10 +16668,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>119874590</v>
+        <v>119874613</v>
       </c>
       <c r="B144" t="n">
-        <v>90562</v>
+        <v>97907</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -16693,38 +16680,47 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I144" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P144" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>564015</v>
+        <v>563794</v>
       </c>
       <c r="R144" t="n">
-        <v>6705047</v>
+        <v>6704750</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -16783,10 +16779,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>119874581</v>
+        <v>119874651</v>
       </c>
       <c r="B145" t="n">
-        <v>90562</v>
+        <v>97907</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -16795,38 +16791,47 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I145" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P145" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>563792</v>
+        <v>564256</v>
       </c>
       <c r="R145" t="n">
-        <v>6704700</v>
+        <v>6705293</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -16885,10 +16890,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>119874682</v>
+        <v>119874567</v>
       </c>
       <c r="B146" t="n">
-        <v>5169</v>
+        <v>90905</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -16897,33 +16902,28 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>100526</v>
+        <v>2062</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
-      <c r="M146" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P146" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
@@ -16933,7 +16933,7 @@
         <v>564000</v>
       </c>
       <c r="R146" t="n">
-        <v>6704958</v>
+        <v>6705011</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16992,10 +16992,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>119874605</v>
+        <v>119874647</v>
       </c>
       <c r="B147" t="n">
-        <v>90334</v>
+        <v>97907</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -17004,38 +17004,54 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>3215</v>
+        <v>220787</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I147" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L147" t="inlineStr"/>
+      <c r="N147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>563929</v>
+        <v>564036</v>
       </c>
       <c r="R147" t="n">
-        <v>6704878</v>
+        <v>6705043</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -17070,12 +17086,18 @@
           <t>2024-09-20</t>
         </is>
       </c>
+      <c r="AC147" t="inlineStr">
+        <is>
+          <t>1 blomstjälk</t>
+        </is>
+      </c>
       <c r="AD147" t="b">
         <v>0</v>
       </c>
       <c r="AE147" t="b">
         <v>0</v>
       </c>
+      <c r="AF147" t="inlineStr"/>
       <c r="AG147" t="b">
         <v>0</v>
       </c>
@@ -17094,7 +17116,7 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>119874647</v>
+        <v>119874646</v>
       </c>
       <c r="B148" t="n">
         <v>97907</v>
@@ -17129,7 +17151,7 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
@@ -17137,23 +17159,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K148" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L148" t="inlineStr"/>
-      <c r="N148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>564036</v>
+        <v>563995</v>
       </c>
       <c r="R148" t="n">
-        <v>6705043</v>
+        <v>6704966</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -17188,18 +17203,12 @@
           <t>2024-09-20</t>
         </is>
       </c>
-      <c r="AC148" t="inlineStr">
-        <is>
-          <t>1 blomstjälk</t>
-        </is>
-      </c>
       <c r="AD148" t="b">
         <v>0</v>
       </c>
       <c r="AE148" t="b">
         <v>0</v>
       </c>
-      <c r="AF148" t="inlineStr"/>
       <c r="AG148" t="b">
         <v>0</v>
       </c>
@@ -17218,7 +17227,7 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>119874646</v>
+        <v>119874617</v>
       </c>
       <c r="B149" t="n">
         <v>97907</v>
@@ -17253,7 +17262,7 @@
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
@@ -17267,10 +17276,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>563995</v>
+        <v>563833</v>
       </c>
       <c r="R149" t="n">
-        <v>6704966</v>
+        <v>6704788</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -17329,7 +17338,7 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>119874617</v>
+        <v>119874644</v>
       </c>
       <c r="B150" t="n">
         <v>97907</v>
@@ -17364,7 +17373,7 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
@@ -17378,10 +17387,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>563833</v>
+        <v>563984</v>
       </c>
       <c r="R150" t="n">
-        <v>6704788</v>
+        <v>6704957</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -17440,10 +17449,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>119874644</v>
+        <v>119874605</v>
       </c>
       <c r="B151" t="n">
-        <v>97907</v>
+        <v>90334</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -17452,47 +17461,38 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>220787</v>
+        <v>3215</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I151" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J151" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>563984</v>
+        <v>563929</v>
       </c>
       <c r="R151" t="n">
-        <v>6704957</v>
+        <v>6704878</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -17755,10 +17755,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>119874642</v>
+        <v>119874571</v>
       </c>
       <c r="B154" t="n">
-        <v>97907</v>
+        <v>90562</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -17767,47 +17767,38 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I154" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J154" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr"/>
       <c r="P154" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>563974</v>
+        <v>563816</v>
       </c>
       <c r="R154" t="n">
-        <v>6704953</v>
+        <v>6704792</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -17866,10 +17857,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>119874571</v>
+        <v>119874642</v>
       </c>
       <c r="B155" t="n">
-        <v>90562</v>
+        <v>97907</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -17878,38 +17869,47 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I155" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P155" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>563816</v>
+        <v>563974</v>
       </c>
       <c r="R155" t="n">
-        <v>6704792</v>
+        <v>6704953</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -17968,10 +17968,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>119874582</v>
+        <v>119874666</v>
       </c>
       <c r="B156" t="n">
-        <v>90562</v>
+        <v>74577</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -17980,25 +17980,25 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>1202</v>
+        <v>6426</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -18008,10 +18008,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>563958</v>
+        <v>563945</v>
       </c>
       <c r="R156" t="n">
-        <v>6704952</v>
+        <v>6704877</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -18070,10 +18070,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>119874666</v>
+        <v>119874582</v>
       </c>
       <c r="B157" t="n">
-        <v>74577</v>
+        <v>90562</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -18082,25 +18082,25 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>6426</v>
+        <v>1202</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -18110,10 +18110,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>563945</v>
+        <v>563958</v>
       </c>
       <c r="R157" t="n">
-        <v>6704877</v>
+        <v>6704952</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -18172,10 +18172,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>119874596</v>
+        <v>119874588</v>
       </c>
       <c r="B158" t="n">
-        <v>57463</v>
+        <v>90562</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -18188,46 +18188,34 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I158" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K158" t="inlineStr"/>
-      <c r="L158" t="inlineStr"/>
-      <c r="M158" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N158" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>563633</v>
+        <v>564011</v>
       </c>
       <c r="R158" t="n">
-        <v>6704498</v>
+        <v>6705060</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -18286,10 +18274,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>119874597</v>
+        <v>119874575</v>
       </c>
       <c r="B159" t="n">
-        <v>91494</v>
+        <v>90562</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -18298,25 +18286,25 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>4769</v>
+        <v>1202</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -18326,10 +18314,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>563943</v>
+        <v>563720</v>
       </c>
       <c r="R159" t="n">
-        <v>6704878</v>
+        <v>6704700</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -18388,10 +18376,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>119874588</v>
+        <v>119874596</v>
       </c>
       <c r="B160" t="n">
-        <v>90562</v>
+        <v>57463</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -18404,34 +18392,46 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I160" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr"/>
+      <c r="L160" t="inlineStr"/>
+      <c r="M160" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N160" t="inlineStr"/>
       <c r="P160" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>564011</v>
+        <v>563633</v>
       </c>
       <c r="R160" t="n">
-        <v>6705060</v>
+        <v>6704498</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -18490,10 +18490,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>119874575</v>
+        <v>119874597</v>
       </c>
       <c r="B161" t="n">
-        <v>90562</v>
+        <v>91494</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -18502,25 +18502,25 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>1202</v>
+        <v>4769</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
@@ -18530,10 +18530,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>563720</v>
+        <v>563943</v>
       </c>
       <c r="R161" t="n">
-        <v>6704700</v>
+        <v>6704878</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -19440,10 +19440,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>119874628</v>
+        <v>119874580</v>
       </c>
       <c r="B170" t="n">
-        <v>97907</v>
+        <v>90562</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
@@ -19452,47 +19452,38 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I170" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J170" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr"/>
       <c r="P170" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>564206</v>
+        <v>563702</v>
       </c>
       <c r="R170" t="n">
-        <v>6705189</v>
+        <v>6704652</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -19551,7 +19542,7 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>119874630</v>
+        <v>119874628</v>
       </c>
       <c r="B171" t="n">
         <v>97907</v>
@@ -19600,10 +19591,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>563815</v>
+        <v>564206</v>
       </c>
       <c r="R171" t="n">
-        <v>6704815</v>
+        <v>6705189</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -19662,10 +19653,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>119874580</v>
+        <v>119874630</v>
       </c>
       <c r="B172" t="n">
-        <v>90562</v>
+        <v>97907</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
@@ -19674,38 +19665,47 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I172" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P172" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>563702</v>
+        <v>563815</v>
       </c>
       <c r="R172" t="n">
-        <v>6704652</v>
+        <v>6704815</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -20781,10 +20781,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>119874608</v>
+        <v>119874569</v>
       </c>
       <c r="B182" t="n">
-        <v>94311</v>
+        <v>90562</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
@@ -20793,25 +20793,25 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>2809</v>
+        <v>1202</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
@@ -20821,10 +20821,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>563944</v>
+        <v>564137</v>
       </c>
       <c r="R182" t="n">
-        <v>6704880</v>
+        <v>6705071</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -20883,10 +20883,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>119874569</v>
+        <v>119874608</v>
       </c>
       <c r="B183" t="n">
-        <v>90562</v>
+        <v>94311</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
@@ -20895,25 +20895,25 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>1202</v>
+        <v>2809</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
@@ -20923,10 +20923,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>564137</v>
+        <v>563944</v>
       </c>
       <c r="R183" t="n">
-        <v>6705071</v>
+        <v>6704880</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -21207,10 +21207,10 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>119874568</v>
+        <v>119874609</v>
       </c>
       <c r="B186" t="n">
-        <v>90905</v>
+        <v>90954</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
@@ -21219,25 +21219,20 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>2062</v>
-      </c>
-      <c r="F186" t="inlineStr">
-        <is>
-          <t>Ulltickeporing</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
@@ -21247,10 +21242,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>563986</v>
+        <v>564083</v>
       </c>
       <c r="R186" t="n">
-        <v>6705032</v>
+        <v>6705090</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -21411,10 +21406,10 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>119874599</v>
+        <v>119874568</v>
       </c>
       <c r="B188" t="n">
-        <v>57326</v>
+        <v>90905</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
@@ -21423,43 +21418,38 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>100049</v>
+        <v>2062</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
-      <c r="M188" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P188" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>563944</v>
+        <v>563986</v>
       </c>
       <c r="R188" t="n">
-        <v>6704948</v>
+        <v>6705032</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -21518,10 +21508,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>119874680</v>
+        <v>119874599</v>
       </c>
       <c r="B189" t="n">
-        <v>5169</v>
+        <v>57326</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
@@ -21530,31 +21520,31 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E189" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
       <c r="M189" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P189" t="inlineStr">
@@ -21563,10 +21553,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>563792</v>
+        <v>563944</v>
       </c>
       <c r="R189" t="n">
-        <v>6704694</v>
+        <v>6704948</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -21625,10 +21615,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>119874609</v>
+        <v>119874680</v>
       </c>
       <c r="B190" t="n">
-        <v>90954</v>
+        <v>5169</v>
       </c>
       <c r="C190" t="inlineStr">
         <is>
@@ -21637,33 +21627,43 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E190" t="n">
-        <v>6040186</v>
+        <v>100526</v>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
+      <c r="M190" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P190" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>564083</v>
+        <v>563792</v>
       </c>
       <c r="R190" t="n">
-        <v>6705090</v>
+        <v>6704694</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -21944,10 +21944,10 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>119874637</v>
+        <v>119874604</v>
       </c>
       <c r="B193" t="n">
-        <v>97907</v>
+        <v>90334</v>
       </c>
       <c r="C193" t="inlineStr">
         <is>
@@ -21956,47 +21956,38 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>220787</v>
+        <v>3215</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I193" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J193" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr"/>
       <c r="P193" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>563648</v>
+        <v>563936</v>
       </c>
       <c r="R193" t="n">
-        <v>6704505</v>
+        <v>6704867</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -22055,10 +22046,10 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>119874604</v>
+        <v>119874637</v>
       </c>
       <c r="B194" t="n">
-        <v>90334</v>
+        <v>97907</v>
       </c>
       <c r="C194" t="inlineStr">
         <is>
@@ -22067,38 +22058,47 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>3215</v>
+        <v>220787</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I194" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J194" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P194" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>563936</v>
+        <v>563648</v>
       </c>
       <c r="R194" t="n">
-        <v>6704867</v>
+        <v>6704505</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -22463,10 +22463,10 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>119874677</v>
+        <v>119874612</v>
       </c>
       <c r="B198" t="n">
-        <v>93930</v>
+        <v>97907</v>
       </c>
       <c r="C198" t="inlineStr">
         <is>
@@ -22475,38 +22475,54 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E198" t="n">
-        <v>2383</v>
+        <v>220787</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Bågpraktmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Plagiomnium medium</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(Bruch &amp; Schimp.) T.J.Kop.</t>
-        </is>
-      </c>
-      <c r="I198" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J198" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L198" t="inlineStr"/>
+      <c r="N198" t="inlineStr"/>
       <c r="P198" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>563925</v>
+        <v>564201</v>
       </c>
       <c r="R198" t="n">
-        <v>6704880</v>
+        <v>6705191</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -22541,12 +22557,18 @@
           <t>2024-09-20</t>
         </is>
       </c>
+      <c r="AC198" t="inlineStr">
+        <is>
+          <t>1 blomstjälk</t>
+        </is>
+      </c>
       <c r="AD198" t="b">
         <v>0</v>
       </c>
       <c r="AE198" t="b">
         <v>0</v>
       </c>
+      <c r="AF198" t="inlineStr"/>
       <c r="AG198" t="b">
         <v>0</v>
       </c>
@@ -22565,10 +22587,10 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>119874612</v>
+        <v>119874677</v>
       </c>
       <c r="B199" t="n">
-        <v>97907</v>
+        <v>93930</v>
       </c>
       <c r="C199" t="inlineStr">
         <is>
@@ -22577,54 +22599,38 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E199" t="n">
-        <v>220787</v>
+        <v>2383</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bågpraktmossa</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Plagiomnium medium</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I199" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J199" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K199" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L199" t="inlineStr"/>
-      <c r="N199" t="inlineStr"/>
+          <t>(Bruch &amp; Schimp.) T.J.Kop.</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr"/>
       <c r="P199" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>564201</v>
+        <v>563925</v>
       </c>
       <c r="R199" t="n">
-        <v>6705191</v>
+        <v>6704880</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -22659,18 +22665,12 @@
           <t>2024-09-20</t>
         </is>
       </c>
-      <c r="AC199" t="inlineStr">
-        <is>
-          <t>1 blomstjälk</t>
-        </is>
-      </c>
       <c r="AD199" t="b">
         <v>0</v>
       </c>
       <c r="AE199" t="b">
         <v>0</v>
       </c>
-      <c r="AF199" t="inlineStr"/>
       <c r="AG199" t="b">
         <v>0</v>
       </c>
@@ -23115,10 +23115,10 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>119874586</v>
+        <v>119874634</v>
       </c>
       <c r="B204" t="n">
-        <v>90562</v>
+        <v>97907</v>
       </c>
       <c r="C204" t="inlineStr">
         <is>
@@ -23127,38 +23127,47 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E204" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I204" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J204" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P204" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>564005</v>
+        <v>563712</v>
       </c>
       <c r="R204" t="n">
-        <v>6705064</v>
+        <v>6704670</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>
@@ -23217,10 +23226,10 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>119874634</v>
+        <v>119874586</v>
       </c>
       <c r="B205" t="n">
-        <v>97907</v>
+        <v>90562</v>
       </c>
       <c r="C205" t="inlineStr">
         <is>
@@ -23229,47 +23238,38 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E205" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I205" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J205" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr"/>
       <c r="P205" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>563712</v>
+        <v>564005</v>
       </c>
       <c r="R205" t="n">
-        <v>6704670</v>
+        <v>6705064</v>
       </c>
       <c r="S205" t="n">
         <v>10</v>

--- a/artfynd/A 58548-2022 artfynd.xlsx
+++ b/artfynd/A 58548-2022 artfynd.xlsx
@@ -16992,10 +16992,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>119874647</v>
+        <v>119874605</v>
       </c>
       <c r="B147" t="n">
-        <v>97907</v>
+        <v>90334</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -17004,54 +17004,38 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>220787</v>
+        <v>3215</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I147" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J147" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K147" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L147" t="inlineStr"/>
-      <c r="N147" t="inlineStr"/>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>564036</v>
+        <v>563929</v>
       </c>
       <c r="R147" t="n">
-        <v>6705043</v>
+        <v>6704878</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -17086,18 +17070,12 @@
           <t>2024-09-20</t>
         </is>
       </c>
-      <c r="AC147" t="inlineStr">
-        <is>
-          <t>1 blomstjälk</t>
-        </is>
-      </c>
       <c r="AD147" t="b">
         <v>0</v>
       </c>
       <c r="AE147" t="b">
         <v>0</v>
       </c>
-      <c r="AF147" t="inlineStr"/>
       <c r="AG147" t="b">
         <v>0</v>
       </c>
@@ -17116,7 +17094,7 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>119874646</v>
+        <v>119874647</v>
       </c>
       <c r="B148" t="n">
         <v>97907</v>
@@ -17151,7 +17129,7 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
@@ -17159,16 +17137,23 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L148" t="inlineStr"/>
+      <c r="N148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>563995</v>
+        <v>564036</v>
       </c>
       <c r="R148" t="n">
-        <v>6704966</v>
+        <v>6705043</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -17203,12 +17188,18 @@
           <t>2024-09-20</t>
         </is>
       </c>
+      <c r="AC148" t="inlineStr">
+        <is>
+          <t>1 blomstjälk</t>
+        </is>
+      </c>
       <c r="AD148" t="b">
         <v>0</v>
       </c>
       <c r="AE148" t="b">
         <v>0</v>
       </c>
+      <c r="AF148" t="inlineStr"/>
       <c r="AG148" t="b">
         <v>0</v>
       </c>
@@ -17227,7 +17218,7 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>119874617</v>
+        <v>119874646</v>
       </c>
       <c r="B149" t="n">
         <v>97907</v>
@@ -17262,7 +17253,7 @@
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
@@ -17276,10 +17267,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>563833</v>
+        <v>563995</v>
       </c>
       <c r="R149" t="n">
-        <v>6704788</v>
+        <v>6704966</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -17338,7 +17329,7 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>119874644</v>
+        <v>119874617</v>
       </c>
       <c r="B150" t="n">
         <v>97907</v>
@@ -17373,7 +17364,7 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
@@ -17387,10 +17378,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>563984</v>
+        <v>563833</v>
       </c>
       <c r="R150" t="n">
-        <v>6704957</v>
+        <v>6704788</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -17449,10 +17440,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>119874605</v>
+        <v>119874644</v>
       </c>
       <c r="B151" t="n">
-        <v>90334</v>
+        <v>97907</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -17461,38 +17452,47 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>3215</v>
+        <v>220787</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I151" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P151" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>563929</v>
+        <v>563984</v>
       </c>
       <c r="R151" t="n">
-        <v>6704878</v>
+        <v>6704957</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -17755,10 +17755,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>119874571</v>
+        <v>119874642</v>
       </c>
       <c r="B154" t="n">
-        <v>90562</v>
+        <v>97907</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -17767,38 +17767,47 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I154" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P154" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>563816</v>
+        <v>563974</v>
       </c>
       <c r="R154" t="n">
-        <v>6704792</v>
+        <v>6704953</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -17857,10 +17866,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>119874642</v>
+        <v>119874571</v>
       </c>
       <c r="B155" t="n">
-        <v>97907</v>
+        <v>90562</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -17869,47 +17878,38 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I155" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J155" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>563974</v>
+        <v>563816</v>
       </c>
       <c r="R155" t="n">
-        <v>6704953</v>
+        <v>6704792</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -18172,10 +18172,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>119874588</v>
+        <v>119874596</v>
       </c>
       <c r="B158" t="n">
-        <v>90562</v>
+        <v>57463</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -18188,34 +18188,46 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I158" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr"/>
+      <c r="L158" t="inlineStr"/>
+      <c r="M158" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>564011</v>
+        <v>563633</v>
       </c>
       <c r="R158" t="n">
-        <v>6705060</v>
+        <v>6704498</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -18274,10 +18286,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>119874575</v>
+        <v>119874597</v>
       </c>
       <c r="B159" t="n">
-        <v>90562</v>
+        <v>91494</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -18286,25 +18298,25 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>1202</v>
+        <v>4769</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -18314,10 +18326,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>563720</v>
+        <v>563943</v>
       </c>
       <c r="R159" t="n">
-        <v>6704700</v>
+        <v>6704878</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -18376,10 +18388,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>119874596</v>
+        <v>119874588</v>
       </c>
       <c r="B160" t="n">
-        <v>57463</v>
+        <v>90562</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -18392,46 +18404,34 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I160" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K160" t="inlineStr"/>
-      <c r="L160" t="inlineStr"/>
-      <c r="M160" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N160" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr"/>
       <c r="P160" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>563633</v>
+        <v>564011</v>
       </c>
       <c r="R160" t="n">
-        <v>6704498</v>
+        <v>6705060</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -18490,10 +18490,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>119874597</v>
+        <v>119874575</v>
       </c>
       <c r="B161" t="n">
-        <v>91494</v>
+        <v>90562</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -18502,25 +18502,25 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>4769</v>
+        <v>1202</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
@@ -18530,10 +18530,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>563943</v>
+        <v>563720</v>
       </c>
       <c r="R161" t="n">
-        <v>6704878</v>
+        <v>6704700</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -18801,10 +18801,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>119874593</v>
+        <v>119874566</v>
       </c>
       <c r="B164" t="n">
-        <v>90562</v>
+        <v>90905</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -18813,25 +18813,25 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>1202</v>
+        <v>2062</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -18841,10 +18841,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>563710</v>
+        <v>564137</v>
       </c>
       <c r="R164" t="n">
-        <v>6704663</v>
+        <v>6705070</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -18903,10 +18903,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>119874607</v>
+        <v>119874633</v>
       </c>
       <c r="B165" t="n">
-        <v>90846</v>
+        <v>97907</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -18915,38 +18915,47 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I165" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P165" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>563821</v>
+        <v>563741</v>
       </c>
       <c r="R165" t="n">
-        <v>6704817</v>
+        <v>6704721</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -19005,10 +19014,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>119874566</v>
+        <v>119874663</v>
       </c>
       <c r="B166" t="n">
-        <v>90905</v>
+        <v>97907</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -19021,34 +19030,43 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>2062</v>
+        <v>220787</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I166" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P166" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>564137</v>
+        <v>563835</v>
       </c>
       <c r="R166" t="n">
-        <v>6705070</v>
+        <v>6704743</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -19107,7 +19125,7 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>119874633</v>
+        <v>119874655</v>
       </c>
       <c r="B167" t="n">
         <v>97907</v>
@@ -19142,7 +19160,7 @@
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
@@ -19156,10 +19174,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>563741</v>
+        <v>563757</v>
       </c>
       <c r="R167" t="n">
-        <v>6704721</v>
+        <v>6704730</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -19218,10 +19236,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>119874663</v>
+        <v>119874593</v>
       </c>
       <c r="B168" t="n">
-        <v>97907</v>
+        <v>90562</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
@@ -19230,47 +19248,38 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I168" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J168" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr"/>
       <c r="P168" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>563835</v>
+        <v>563710</v>
       </c>
       <c r="R168" t="n">
-        <v>6704743</v>
+        <v>6704663</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -19329,10 +19338,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>119874655</v>
+        <v>119874607</v>
       </c>
       <c r="B169" t="n">
-        <v>97907</v>
+        <v>90846</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
@@ -19341,47 +19350,38 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I169" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J169" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr"/>
       <c r="P169" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>563757</v>
+        <v>563821</v>
       </c>
       <c r="R169" t="n">
-        <v>6704730</v>
+        <v>6704817</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -19440,10 +19440,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>119874580</v>
+        <v>119874628</v>
       </c>
       <c r="B170" t="n">
-        <v>90562</v>
+        <v>97907</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
@@ -19452,38 +19452,47 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I170" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P170" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>563702</v>
+        <v>564206</v>
       </c>
       <c r="R170" t="n">
-        <v>6704652</v>
+        <v>6705189</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -19542,7 +19551,7 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>119874628</v>
+        <v>119874630</v>
       </c>
       <c r="B171" t="n">
         <v>97907</v>
@@ -19591,10 +19600,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>564206</v>
+        <v>563815</v>
       </c>
       <c r="R171" t="n">
-        <v>6705189</v>
+        <v>6704815</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -19653,10 +19662,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>119874630</v>
+        <v>119874580</v>
       </c>
       <c r="B172" t="n">
-        <v>97907</v>
+        <v>90562</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
@@ -19665,47 +19674,38 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I172" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J172" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr"/>
       <c r="P172" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>563815</v>
+        <v>563702</v>
       </c>
       <c r="R172" t="n">
-        <v>6704815</v>
+        <v>6704652</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -21207,10 +21207,10 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>119874609</v>
+        <v>119874568</v>
       </c>
       <c r="B186" t="n">
-        <v>90954</v>
+        <v>90905</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
@@ -21219,20 +21219,25 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>6040186</v>
+        <v>2062</v>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>Ulltickeporing</t>
+        </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
@@ -21242,10 +21247,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>564083</v>
+        <v>563986</v>
       </c>
       <c r="R186" t="n">
-        <v>6705090</v>
+        <v>6705032</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -21406,10 +21411,10 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>119874568</v>
+        <v>119874599</v>
       </c>
       <c r="B188" t="n">
-        <v>90905</v>
+        <v>57326</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
@@ -21418,38 +21423,43 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>2062</v>
+        <v>100049</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
+      <c r="M188" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P188" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>563986</v>
+        <v>563944</v>
       </c>
       <c r="R188" t="n">
-        <v>6705032</v>
+        <v>6704948</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -21508,10 +21518,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>119874599</v>
+        <v>119874680</v>
       </c>
       <c r="B189" t="n">
-        <v>57326</v>
+        <v>5169</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
@@ -21520,31 +21530,31 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E189" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
       <c r="M189" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P189" t="inlineStr">
@@ -21553,10 +21563,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>563944</v>
+        <v>563792</v>
       </c>
       <c r="R189" t="n">
-        <v>6704948</v>
+        <v>6704694</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -21615,10 +21625,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>119874680</v>
+        <v>119874609</v>
       </c>
       <c r="B190" t="n">
-        <v>5169</v>
+        <v>90954</v>
       </c>
       <c r="C190" t="inlineStr">
         <is>
@@ -21627,43 +21637,33 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E190" t="n">
-        <v>100526</v>
-      </c>
-      <c r="F190" t="inlineStr">
-        <is>
-          <t>Bronshjon</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
-      <c r="M190" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P190" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>563792</v>
+        <v>564083</v>
       </c>
       <c r="R190" t="n">
-        <v>6704694</v>
+        <v>6705090</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -21944,10 +21944,10 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>119874604</v>
+        <v>119874637</v>
       </c>
       <c r="B193" t="n">
-        <v>90334</v>
+        <v>97907</v>
       </c>
       <c r="C193" t="inlineStr">
         <is>
@@ -21956,38 +21956,47 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>3215</v>
+        <v>220787</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I193" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J193" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P193" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>563936</v>
+        <v>563648</v>
       </c>
       <c r="R193" t="n">
-        <v>6704867</v>
+        <v>6704505</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -22046,10 +22055,10 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>119874637</v>
+        <v>119874604</v>
       </c>
       <c r="B194" t="n">
-        <v>97907</v>
+        <v>90334</v>
       </c>
       <c r="C194" t="inlineStr">
         <is>
@@ -22058,47 +22067,38 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>220787</v>
+        <v>3215</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I194" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J194" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr"/>
       <c r="P194" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>563648</v>
+        <v>563936</v>
       </c>
       <c r="R194" t="n">
-        <v>6704505</v>
+        <v>6704867</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -23115,10 +23115,10 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>119874634</v>
+        <v>119874586</v>
       </c>
       <c r="B204" t="n">
-        <v>97907</v>
+        <v>90562</v>
       </c>
       <c r="C204" t="inlineStr">
         <is>
@@ -23127,47 +23127,38 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E204" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I204" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J204" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr"/>
       <c r="P204" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>563712</v>
+        <v>564005</v>
       </c>
       <c r="R204" t="n">
-        <v>6704670</v>
+        <v>6705064</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>
@@ -23226,10 +23217,10 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>119874586</v>
+        <v>119874634</v>
       </c>
       <c r="B205" t="n">
-        <v>90562</v>
+        <v>97907</v>
       </c>
       <c r="C205" t="inlineStr">
         <is>
@@ -23238,38 +23229,47 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E205" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I205" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J205" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P205" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>564005</v>
+        <v>563712</v>
       </c>
       <c r="R205" t="n">
-        <v>6705064</v>
+        <v>6704670</v>
       </c>
       <c r="S205" t="n">
         <v>10</v>

--- a/artfynd/A 58548-2022 artfynd.xlsx
+++ b/artfynd/A 58548-2022 artfynd.xlsx
@@ -16028,10 +16028,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>119874590</v>
+        <v>119874685</v>
       </c>
       <c r="B138" t="n">
-        <v>90562</v>
+        <v>8421</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -16040,38 +16040,43 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>1202</v>
+        <v>106554</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P138" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>564015</v>
+        <v>563845</v>
       </c>
       <c r="R138" t="n">
-        <v>6705047</v>
+        <v>6704771</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -16130,10 +16135,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>119874581</v>
+        <v>119874665</v>
       </c>
       <c r="B139" t="n">
-        <v>90562</v>
+        <v>97907</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -16142,38 +16147,47 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I139" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P139" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>563792</v>
+        <v>564008</v>
       </c>
       <c r="R139" t="n">
-        <v>6704700</v>
+        <v>6704979</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -16232,10 +16246,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>119874682</v>
+        <v>119874618</v>
       </c>
       <c r="B140" t="n">
-        <v>5169</v>
+        <v>97907</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -16244,31 +16258,35 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I140" t="inlineStr"/>
-      <c r="M140" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P140" t="inlineStr">
@@ -16277,10 +16295,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>564000</v>
+        <v>564168</v>
       </c>
       <c r="R140" t="n">
-        <v>6704958</v>
+        <v>6705183</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -16339,10 +16357,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>119874685</v>
+        <v>119874613</v>
       </c>
       <c r="B141" t="n">
-        <v>8421</v>
+        <v>97907</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -16351,31 +16369,35 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>106554</v>
+        <v>220787</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I141" t="inlineStr"/>
-      <c r="M141" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P141" t="inlineStr">
@@ -16384,10 +16406,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>563845</v>
+        <v>563794</v>
       </c>
       <c r="R141" t="n">
-        <v>6704771</v>
+        <v>6704750</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -16446,7 +16468,7 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>119874665</v>
+        <v>119874651</v>
       </c>
       <c r="B142" t="n">
         <v>97907</v>
@@ -16481,7 +16503,7 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
@@ -16495,10 +16517,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>564008</v>
+        <v>564256</v>
       </c>
       <c r="R142" t="n">
-        <v>6704979</v>
+        <v>6705293</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -16557,10 +16579,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>119874618</v>
+        <v>119874567</v>
       </c>
       <c r="B143" t="n">
-        <v>97907</v>
+        <v>90905</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -16573,43 +16595,34 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>220787</v>
+        <v>2062</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I143" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J143" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>564168</v>
+        <v>564000</v>
       </c>
       <c r="R143" t="n">
-        <v>6705183</v>
+        <v>6705011</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -16668,10 +16681,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>119874613</v>
+        <v>119874590</v>
       </c>
       <c r="B144" t="n">
-        <v>97907</v>
+        <v>90562</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -16680,47 +16693,38 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I144" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J144" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>563794</v>
+        <v>564015</v>
       </c>
       <c r="R144" t="n">
-        <v>6704750</v>
+        <v>6705047</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -16779,10 +16783,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>119874651</v>
+        <v>119874581</v>
       </c>
       <c r="B145" t="n">
-        <v>97907</v>
+        <v>90562</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -16791,47 +16795,38 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I145" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J145" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>564256</v>
+        <v>563792</v>
       </c>
       <c r="R145" t="n">
-        <v>6705293</v>
+        <v>6704700</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -16890,10 +16885,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>119874567</v>
+        <v>119874682</v>
       </c>
       <c r="B146" t="n">
-        <v>90905</v>
+        <v>5169</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -16902,28 +16897,33 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>2062</v>
+        <v>100526</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P146" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
@@ -16933,7 +16933,7 @@
         <v>564000</v>
       </c>
       <c r="R146" t="n">
-        <v>6705011</v>
+        <v>6704958</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -17755,10 +17755,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>119874642</v>
+        <v>119874571</v>
       </c>
       <c r="B154" t="n">
-        <v>97907</v>
+        <v>90562</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -17767,47 +17767,38 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I154" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J154" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr"/>
       <c r="P154" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>563974</v>
+        <v>563816</v>
       </c>
       <c r="R154" t="n">
-        <v>6704953</v>
+        <v>6704792</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -17866,10 +17857,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>119874571</v>
+        <v>119874642</v>
       </c>
       <c r="B155" t="n">
-        <v>90562</v>
+        <v>97907</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -17878,38 +17869,47 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I155" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P155" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>563816</v>
+        <v>563974</v>
       </c>
       <c r="R155" t="n">
-        <v>6704792</v>
+        <v>6704953</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -18801,10 +18801,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>119874566</v>
+        <v>119874593</v>
       </c>
       <c r="B164" t="n">
-        <v>90905</v>
+        <v>90562</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -18813,25 +18813,25 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>2062</v>
+        <v>1202</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -18841,10 +18841,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>564137</v>
+        <v>563710</v>
       </c>
       <c r="R164" t="n">
-        <v>6705070</v>
+        <v>6704663</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -18903,10 +18903,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>119874633</v>
+        <v>119874607</v>
       </c>
       <c r="B165" t="n">
-        <v>97907</v>
+        <v>90846</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -18915,47 +18915,38 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I165" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J165" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>563741</v>
+        <v>563821</v>
       </c>
       <c r="R165" t="n">
-        <v>6704721</v>
+        <v>6704817</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -19014,10 +19005,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>119874663</v>
+        <v>119874566</v>
       </c>
       <c r="B166" t="n">
-        <v>97907</v>
+        <v>90905</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -19030,43 +19021,34 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>220787</v>
+        <v>2062</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I166" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J166" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr"/>
       <c r="P166" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>563835</v>
+        <v>564137</v>
       </c>
       <c r="R166" t="n">
-        <v>6704743</v>
+        <v>6705070</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -19125,7 +19107,7 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>119874655</v>
+        <v>119874633</v>
       </c>
       <c r="B167" t="n">
         <v>97907</v>
@@ -19160,7 +19142,7 @@
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
@@ -19174,10 +19156,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>563757</v>
+        <v>563741</v>
       </c>
       <c r="R167" t="n">
-        <v>6704730</v>
+        <v>6704721</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -19236,10 +19218,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>119874593</v>
+        <v>119874663</v>
       </c>
       <c r="B168" t="n">
-        <v>90562</v>
+        <v>97907</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
@@ -19248,38 +19230,47 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I168" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P168" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>563710</v>
+        <v>563835</v>
       </c>
       <c r="R168" t="n">
-        <v>6704663</v>
+        <v>6704743</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -19338,10 +19329,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>119874607</v>
+        <v>119874655</v>
       </c>
       <c r="B169" t="n">
-        <v>90846</v>
+        <v>97907</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
@@ -19350,38 +19341,47 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I169" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P169" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>563821</v>
+        <v>563757</v>
       </c>
       <c r="R169" t="n">
-        <v>6704817</v>
+        <v>6704730</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -20781,10 +20781,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>119874569</v>
+        <v>119874608</v>
       </c>
       <c r="B182" t="n">
-        <v>90562</v>
+        <v>94311</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
@@ -20793,25 +20793,25 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>1202</v>
+        <v>2809</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
@@ -20821,10 +20821,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>564137</v>
+        <v>563944</v>
       </c>
       <c r="R182" t="n">
-        <v>6705071</v>
+        <v>6704880</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -20883,10 +20883,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>119874608</v>
+        <v>119874569</v>
       </c>
       <c r="B183" t="n">
-        <v>94311</v>
+        <v>90562</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
@@ -20895,25 +20895,25 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>2809</v>
+        <v>1202</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
@@ -20923,10 +20923,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>563944</v>
+        <v>564137</v>
       </c>
       <c r="R183" t="n">
-        <v>6704880</v>
+        <v>6705071</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>

--- a/artfynd/A 58548-2022 artfynd.xlsx
+++ b/artfynd/A 58548-2022 artfynd.xlsx
@@ -16028,10 +16028,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>119874685</v>
+        <v>119874590</v>
       </c>
       <c r="B138" t="n">
-        <v>8421</v>
+        <v>90562</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -16040,43 +16040,38 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>106554</v>
+        <v>1202</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
-      <c r="M138" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P138" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>563845</v>
+        <v>564015</v>
       </c>
       <c r="R138" t="n">
-        <v>6704771</v>
+        <v>6705047</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -16135,10 +16130,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>119874665</v>
+        <v>119874581</v>
       </c>
       <c r="B139" t="n">
-        <v>97907</v>
+        <v>90562</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -16147,47 +16142,38 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I139" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J139" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>564008</v>
+        <v>563792</v>
       </c>
       <c r="R139" t="n">
-        <v>6704979</v>
+        <v>6704700</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -16246,10 +16232,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>119874618</v>
+        <v>119874682</v>
       </c>
       <c r="B140" t="n">
-        <v>97907</v>
+        <v>5169</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -16258,35 +16244,31 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I140" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J140" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr"/>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P140" t="inlineStr">
@@ -16295,10 +16277,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>564168</v>
+        <v>564000</v>
       </c>
       <c r="R140" t="n">
-        <v>6705183</v>
+        <v>6704958</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -16357,10 +16339,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>119874613</v>
+        <v>119874685</v>
       </c>
       <c r="B141" t="n">
-        <v>97907</v>
+        <v>8421</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -16369,35 +16351,31 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>220787</v>
+        <v>106554</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I141" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J141" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr"/>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P141" t="inlineStr">
@@ -16406,10 +16384,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>563794</v>
+        <v>563845</v>
       </c>
       <c r="R141" t="n">
-        <v>6704750</v>
+        <v>6704771</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -16468,7 +16446,7 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>119874651</v>
+        <v>119874665</v>
       </c>
       <c r="B142" t="n">
         <v>97907</v>
@@ -16503,7 +16481,7 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
@@ -16517,10 +16495,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>564256</v>
+        <v>564008</v>
       </c>
       <c r="R142" t="n">
-        <v>6705293</v>
+        <v>6704979</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -16579,10 +16557,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>119874567</v>
+        <v>119874618</v>
       </c>
       <c r="B143" t="n">
-        <v>90905</v>
+        <v>97907</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -16595,34 +16573,43 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>2062</v>
+        <v>220787</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I143" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P143" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>564000</v>
+        <v>564168</v>
       </c>
       <c r="R143" t="n">
-        <v>6705011</v>
+        <v>6705183</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -16681,10 +16668,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>119874590</v>
+        <v>119874613</v>
       </c>
       <c r="B144" t="n">
-        <v>90562</v>
+        <v>97907</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -16693,38 +16680,47 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I144" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P144" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>564015</v>
+        <v>563794</v>
       </c>
       <c r="R144" t="n">
-        <v>6705047</v>
+        <v>6704750</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -16783,10 +16779,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>119874581</v>
+        <v>119874651</v>
       </c>
       <c r="B145" t="n">
-        <v>90562</v>
+        <v>97907</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -16795,38 +16791,47 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I145" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P145" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>563792</v>
+        <v>564256</v>
       </c>
       <c r="R145" t="n">
-        <v>6704700</v>
+        <v>6705293</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -16885,10 +16890,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>119874682</v>
+        <v>119874567</v>
       </c>
       <c r="B146" t="n">
-        <v>5169</v>
+        <v>90905</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -16897,33 +16902,28 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>100526</v>
+        <v>2062</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
-      <c r="M146" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P146" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
@@ -16933,7 +16933,7 @@
         <v>564000</v>
       </c>
       <c r="R146" t="n">
-        <v>6704958</v>
+        <v>6705011</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16992,10 +16992,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>119874605</v>
+        <v>119874647</v>
       </c>
       <c r="B147" t="n">
-        <v>90334</v>
+        <v>97907</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -17004,38 +17004,54 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>3215</v>
+        <v>220787</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I147" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L147" t="inlineStr"/>
+      <c r="N147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>563929</v>
+        <v>564036</v>
       </c>
       <c r="R147" t="n">
-        <v>6704878</v>
+        <v>6705043</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -17070,12 +17086,18 @@
           <t>2024-09-20</t>
         </is>
       </c>
+      <c r="AC147" t="inlineStr">
+        <is>
+          <t>1 blomstjälk</t>
+        </is>
+      </c>
       <c r="AD147" t="b">
         <v>0</v>
       </c>
       <c r="AE147" t="b">
         <v>0</v>
       </c>
+      <c r="AF147" t="inlineStr"/>
       <c r="AG147" t="b">
         <v>0</v>
       </c>
@@ -17094,7 +17116,7 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>119874647</v>
+        <v>119874646</v>
       </c>
       <c r="B148" t="n">
         <v>97907</v>
@@ -17129,7 +17151,7 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
@@ -17137,23 +17159,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K148" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L148" t="inlineStr"/>
-      <c r="N148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>564036</v>
+        <v>563995</v>
       </c>
       <c r="R148" t="n">
-        <v>6705043</v>
+        <v>6704966</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -17188,18 +17203,12 @@
           <t>2024-09-20</t>
         </is>
       </c>
-      <c r="AC148" t="inlineStr">
-        <is>
-          <t>1 blomstjälk</t>
-        </is>
-      </c>
       <c r="AD148" t="b">
         <v>0</v>
       </c>
       <c r="AE148" t="b">
         <v>0</v>
       </c>
-      <c r="AF148" t="inlineStr"/>
       <c r="AG148" t="b">
         <v>0</v>
       </c>
@@ -17218,7 +17227,7 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>119874646</v>
+        <v>119874617</v>
       </c>
       <c r="B149" t="n">
         <v>97907</v>
@@ -17253,7 +17262,7 @@
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
@@ -17267,10 +17276,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>563995</v>
+        <v>563833</v>
       </c>
       <c r="R149" t="n">
-        <v>6704966</v>
+        <v>6704788</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -17329,7 +17338,7 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>119874617</v>
+        <v>119874644</v>
       </c>
       <c r="B150" t="n">
         <v>97907</v>
@@ -17364,7 +17373,7 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
@@ -17378,10 +17387,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>563833</v>
+        <v>563984</v>
       </c>
       <c r="R150" t="n">
-        <v>6704788</v>
+        <v>6704957</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -17440,10 +17449,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>119874644</v>
+        <v>119874605</v>
       </c>
       <c r="B151" t="n">
-        <v>97907</v>
+        <v>90334</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -17452,47 +17461,38 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>220787</v>
+        <v>3215</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I151" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J151" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>563984</v>
+        <v>563929</v>
       </c>
       <c r="R151" t="n">
-        <v>6704957</v>
+        <v>6704878</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -17968,10 +17968,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>119874666</v>
+        <v>119874582</v>
       </c>
       <c r="B156" t="n">
-        <v>74577</v>
+        <v>90562</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -17980,25 +17980,25 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>6426</v>
+        <v>1202</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -18008,10 +18008,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>563945</v>
+        <v>563958</v>
       </c>
       <c r="R156" t="n">
-        <v>6704877</v>
+        <v>6704952</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -18070,10 +18070,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>119874582</v>
+        <v>119874666</v>
       </c>
       <c r="B157" t="n">
-        <v>90562</v>
+        <v>74577</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -18082,25 +18082,25 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>1202</v>
+        <v>6426</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -18110,10 +18110,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>563958</v>
+        <v>563945</v>
       </c>
       <c r="R157" t="n">
-        <v>6704952</v>
+        <v>6704877</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -18172,10 +18172,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>119874596</v>
+        <v>119874588</v>
       </c>
       <c r="B158" t="n">
-        <v>57463</v>
+        <v>90562</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -18188,46 +18188,34 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I158" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K158" t="inlineStr"/>
-      <c r="L158" t="inlineStr"/>
-      <c r="M158" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N158" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>563633</v>
+        <v>564011</v>
       </c>
       <c r="R158" t="n">
-        <v>6704498</v>
+        <v>6705060</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -18286,10 +18274,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>119874597</v>
+        <v>119874575</v>
       </c>
       <c r="B159" t="n">
-        <v>91494</v>
+        <v>90562</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -18298,25 +18286,25 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>4769</v>
+        <v>1202</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -18326,10 +18314,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>563943</v>
+        <v>563720</v>
       </c>
       <c r="R159" t="n">
-        <v>6704878</v>
+        <v>6704700</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -18388,10 +18376,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>119874588</v>
+        <v>119874596</v>
       </c>
       <c r="B160" t="n">
-        <v>90562</v>
+        <v>57463</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -18404,34 +18392,46 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I160" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr"/>
+      <c r="L160" t="inlineStr"/>
+      <c r="M160" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N160" t="inlineStr"/>
       <c r="P160" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>564011</v>
+        <v>563633</v>
       </c>
       <c r="R160" t="n">
-        <v>6705060</v>
+        <v>6704498</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -18490,10 +18490,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>119874575</v>
+        <v>119874597</v>
       </c>
       <c r="B161" t="n">
-        <v>90562</v>
+        <v>91494</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -18502,25 +18502,25 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>1202</v>
+        <v>4769</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
@@ -18530,10 +18530,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>563720</v>
+        <v>563943</v>
       </c>
       <c r="R161" t="n">
-        <v>6704700</v>
+        <v>6704878</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -18801,10 +18801,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>119874593</v>
+        <v>119874566</v>
       </c>
       <c r="B164" t="n">
-        <v>90562</v>
+        <v>90905</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -18813,25 +18813,25 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>1202</v>
+        <v>2062</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -18841,10 +18841,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>563710</v>
+        <v>564137</v>
       </c>
       <c r="R164" t="n">
-        <v>6704663</v>
+        <v>6705070</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -18903,10 +18903,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>119874607</v>
+        <v>119874633</v>
       </c>
       <c r="B165" t="n">
-        <v>90846</v>
+        <v>97907</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -18915,38 +18915,47 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I165" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P165" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>563821</v>
+        <v>563741</v>
       </c>
       <c r="R165" t="n">
-        <v>6704817</v>
+        <v>6704721</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -19005,10 +19014,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>119874566</v>
+        <v>119874663</v>
       </c>
       <c r="B166" t="n">
-        <v>90905</v>
+        <v>97907</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -19021,34 +19030,43 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>2062</v>
+        <v>220787</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I166" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P166" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>564137</v>
+        <v>563835</v>
       </c>
       <c r="R166" t="n">
-        <v>6705070</v>
+        <v>6704743</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -19107,7 +19125,7 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>119874633</v>
+        <v>119874655</v>
       </c>
       <c r="B167" t="n">
         <v>97907</v>
@@ -19142,7 +19160,7 @@
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
@@ -19156,10 +19174,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>563741</v>
+        <v>563757</v>
       </c>
       <c r="R167" t="n">
-        <v>6704721</v>
+        <v>6704730</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -19218,10 +19236,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>119874663</v>
+        <v>119874593</v>
       </c>
       <c r="B168" t="n">
-        <v>97907</v>
+        <v>90562</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
@@ -19230,47 +19248,38 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I168" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J168" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr"/>
       <c r="P168" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>563835</v>
+        <v>563710</v>
       </c>
       <c r="R168" t="n">
-        <v>6704743</v>
+        <v>6704663</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -19329,10 +19338,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>119874655</v>
+        <v>119874607</v>
       </c>
       <c r="B169" t="n">
-        <v>97907</v>
+        <v>90846</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
@@ -19341,47 +19350,38 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I169" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J169" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr"/>
       <c r="P169" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>563757</v>
+        <v>563821</v>
       </c>
       <c r="R169" t="n">
-        <v>6704730</v>
+        <v>6704817</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -22463,10 +22463,10 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>119874612</v>
+        <v>119874677</v>
       </c>
       <c r="B198" t="n">
-        <v>97907</v>
+        <v>93930</v>
       </c>
       <c r="C198" t="inlineStr">
         <is>
@@ -22475,54 +22475,38 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E198" t="n">
-        <v>220787</v>
+        <v>2383</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bågpraktmossa</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Plagiomnium medium</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I198" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J198" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K198" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L198" t="inlineStr"/>
-      <c r="N198" t="inlineStr"/>
+          <t>(Bruch &amp; Schimp.) T.J.Kop.</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr"/>
       <c r="P198" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>564201</v>
+        <v>563925</v>
       </c>
       <c r="R198" t="n">
-        <v>6705191</v>
+        <v>6704880</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -22557,18 +22541,12 @@
           <t>2024-09-20</t>
         </is>
       </c>
-      <c r="AC198" t="inlineStr">
-        <is>
-          <t>1 blomstjälk</t>
-        </is>
-      </c>
       <c r="AD198" t="b">
         <v>0</v>
       </c>
       <c r="AE198" t="b">
         <v>0</v>
       </c>
-      <c r="AF198" t="inlineStr"/>
       <c r="AG198" t="b">
         <v>0</v>
       </c>
@@ -22587,10 +22565,10 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>119874677</v>
+        <v>119874612</v>
       </c>
       <c r="B199" t="n">
-        <v>93930</v>
+        <v>97907</v>
       </c>
       <c r="C199" t="inlineStr">
         <is>
@@ -22599,38 +22577,54 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E199" t="n">
-        <v>2383</v>
+        <v>220787</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Bågpraktmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Plagiomnium medium</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(Bruch &amp; Schimp.) T.J.Kop.</t>
-        </is>
-      </c>
-      <c r="I199" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J199" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L199" t="inlineStr"/>
+      <c r="N199" t="inlineStr"/>
       <c r="P199" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>563925</v>
+        <v>564201</v>
       </c>
       <c r="R199" t="n">
-        <v>6704880</v>
+        <v>6705191</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -22665,12 +22659,18 @@
           <t>2024-09-20</t>
         </is>
       </c>
+      <c r="AC199" t="inlineStr">
+        <is>
+          <t>1 blomstjälk</t>
+        </is>
+      </c>
       <c r="AD199" t="b">
         <v>0</v>
       </c>
       <c r="AE199" t="b">
         <v>0</v>
       </c>
+      <c r="AF199" t="inlineStr"/>
       <c r="AG199" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 58548-2022 artfynd.xlsx
+++ b/artfynd/A 58548-2022 artfynd.xlsx
@@ -17968,10 +17968,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>119874582</v>
+        <v>119874666</v>
       </c>
       <c r="B156" t="n">
-        <v>90562</v>
+        <v>74577</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -17980,25 +17980,25 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>1202</v>
+        <v>6426</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -18008,10 +18008,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>563958</v>
+        <v>563945</v>
       </c>
       <c r="R156" t="n">
-        <v>6704952</v>
+        <v>6704877</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -18070,10 +18070,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>119874666</v>
+        <v>119874582</v>
       </c>
       <c r="B157" t="n">
-        <v>74577</v>
+        <v>90562</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -18082,25 +18082,25 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>6426</v>
+        <v>1202</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -18110,10 +18110,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>563945</v>
+        <v>563958</v>
       </c>
       <c r="R157" t="n">
-        <v>6704877</v>
+        <v>6704952</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -18801,10 +18801,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>119874566</v>
+        <v>119874593</v>
       </c>
       <c r="B164" t="n">
-        <v>90905</v>
+        <v>90562</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -18813,25 +18813,25 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>2062</v>
+        <v>1202</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -18841,10 +18841,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>564137</v>
+        <v>563710</v>
       </c>
       <c r="R164" t="n">
-        <v>6705070</v>
+        <v>6704663</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -18903,10 +18903,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>119874633</v>
+        <v>119874607</v>
       </c>
       <c r="B165" t="n">
-        <v>97907</v>
+        <v>90846</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -18915,47 +18915,38 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I165" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J165" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>563741</v>
+        <v>563821</v>
       </c>
       <c r="R165" t="n">
-        <v>6704721</v>
+        <v>6704817</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -19014,10 +19005,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>119874663</v>
+        <v>119874566</v>
       </c>
       <c r="B166" t="n">
-        <v>97907</v>
+        <v>90905</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -19030,43 +19021,34 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>220787</v>
+        <v>2062</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I166" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J166" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr"/>
       <c r="P166" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>563835</v>
+        <v>564137</v>
       </c>
       <c r="R166" t="n">
-        <v>6704743</v>
+        <v>6705070</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -19125,7 +19107,7 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>119874655</v>
+        <v>119874633</v>
       </c>
       <c r="B167" t="n">
         <v>97907</v>
@@ -19160,7 +19142,7 @@
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
@@ -19174,10 +19156,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>563757</v>
+        <v>563741</v>
       </c>
       <c r="R167" t="n">
-        <v>6704730</v>
+        <v>6704721</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -19236,10 +19218,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>119874593</v>
+        <v>119874663</v>
       </c>
       <c r="B168" t="n">
-        <v>90562</v>
+        <v>97907</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
@@ -19248,38 +19230,47 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I168" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P168" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>563710</v>
+        <v>563835</v>
       </c>
       <c r="R168" t="n">
-        <v>6704663</v>
+        <v>6704743</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -19338,10 +19329,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>119874607</v>
+        <v>119874655</v>
       </c>
       <c r="B169" t="n">
-        <v>90846</v>
+        <v>97907</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
@@ -19350,38 +19341,47 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I169" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P169" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>563821</v>
+        <v>563757</v>
       </c>
       <c r="R169" t="n">
-        <v>6704817</v>
+        <v>6704730</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -20781,10 +20781,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>119874608</v>
+        <v>119874569</v>
       </c>
       <c r="B182" t="n">
-        <v>94311</v>
+        <v>90562</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
@@ -20793,25 +20793,25 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>2809</v>
+        <v>1202</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
@@ -20821,10 +20821,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>563944</v>
+        <v>564137</v>
       </c>
       <c r="R182" t="n">
-        <v>6704880</v>
+        <v>6705071</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -20883,10 +20883,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>119874569</v>
+        <v>119874608</v>
       </c>
       <c r="B183" t="n">
-        <v>90562</v>
+        <v>94311</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
@@ -20895,25 +20895,25 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>1202</v>
+        <v>2809</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
@@ -20923,10 +20923,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>564137</v>
+        <v>563944</v>
       </c>
       <c r="R183" t="n">
-        <v>6705071</v>
+        <v>6704880</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>

--- a/artfynd/A 58548-2022 artfynd.xlsx
+++ b/artfynd/A 58548-2022 artfynd.xlsx
@@ -17755,10 +17755,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>119874571</v>
+        <v>119874642</v>
       </c>
       <c r="B154" t="n">
-        <v>90562</v>
+        <v>97907</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -17767,38 +17767,47 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I154" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P154" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>563816</v>
+        <v>563974</v>
       </c>
       <c r="R154" t="n">
-        <v>6704792</v>
+        <v>6704953</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -17857,10 +17866,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>119874642</v>
+        <v>119874571</v>
       </c>
       <c r="B155" t="n">
-        <v>97907</v>
+        <v>90562</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -17869,47 +17878,38 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I155" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J155" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>563974</v>
+        <v>563816</v>
       </c>
       <c r="R155" t="n">
-        <v>6704953</v>
+        <v>6704792</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -17968,10 +17968,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>119874666</v>
+        <v>119874582</v>
       </c>
       <c r="B156" t="n">
-        <v>74577</v>
+        <v>90562</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -17980,25 +17980,25 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>6426</v>
+        <v>1202</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -18008,10 +18008,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>563945</v>
+        <v>563958</v>
       </c>
       <c r="R156" t="n">
-        <v>6704877</v>
+        <v>6704952</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -18070,10 +18070,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>119874582</v>
+        <v>119874666</v>
       </c>
       <c r="B157" t="n">
-        <v>90562</v>
+        <v>74577</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -18082,25 +18082,25 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>1202</v>
+        <v>6426</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -18110,10 +18110,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>563958</v>
+        <v>563945</v>
       </c>
       <c r="R157" t="n">
-        <v>6704952</v>
+        <v>6704877</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -18801,10 +18801,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>119874593</v>
+        <v>119874566</v>
       </c>
       <c r="B164" t="n">
-        <v>90562</v>
+        <v>90905</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -18813,25 +18813,25 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>1202</v>
+        <v>2062</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -18841,10 +18841,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>563710</v>
+        <v>564137</v>
       </c>
       <c r="R164" t="n">
-        <v>6704663</v>
+        <v>6705070</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -18903,10 +18903,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>119874607</v>
+        <v>119874633</v>
       </c>
       <c r="B165" t="n">
-        <v>90846</v>
+        <v>97907</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -18915,38 +18915,47 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I165" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P165" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>563821</v>
+        <v>563741</v>
       </c>
       <c r="R165" t="n">
-        <v>6704817</v>
+        <v>6704721</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -19005,10 +19014,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>119874566</v>
+        <v>119874663</v>
       </c>
       <c r="B166" t="n">
-        <v>90905</v>
+        <v>97907</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -19021,34 +19030,43 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>2062</v>
+        <v>220787</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I166" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P166" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>564137</v>
+        <v>563835</v>
       </c>
       <c r="R166" t="n">
-        <v>6705070</v>
+        <v>6704743</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -19107,7 +19125,7 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>119874633</v>
+        <v>119874655</v>
       </c>
       <c r="B167" t="n">
         <v>97907</v>
@@ -19142,7 +19160,7 @@
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
@@ -19156,10 +19174,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>563741</v>
+        <v>563757</v>
       </c>
       <c r="R167" t="n">
-        <v>6704721</v>
+        <v>6704730</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -19218,10 +19236,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>119874663</v>
+        <v>119874593</v>
       </c>
       <c r="B168" t="n">
-        <v>97907</v>
+        <v>90562</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
@@ -19230,47 +19248,38 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I168" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J168" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr"/>
       <c r="P168" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>563835</v>
+        <v>563710</v>
       </c>
       <c r="R168" t="n">
-        <v>6704743</v>
+        <v>6704663</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -19329,10 +19338,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>119874655</v>
+        <v>119874607</v>
       </c>
       <c r="B169" t="n">
-        <v>97907</v>
+        <v>90846</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
@@ -19341,47 +19350,38 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I169" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J169" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr"/>
       <c r="P169" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>563757</v>
+        <v>563821</v>
       </c>
       <c r="R169" t="n">
-        <v>6704730</v>
+        <v>6704817</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>

--- a/artfynd/A 58548-2022 artfynd.xlsx
+++ b/artfynd/A 58548-2022 artfynd.xlsx
@@ -15695,10 +15695,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>119874658</v>
+        <v>119874608</v>
       </c>
       <c r="B135" t="n">
-        <v>97907</v>
+        <v>94334</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -15707,47 +15707,38 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>220787</v>
+        <v>2809</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I135" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J135" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>563749</v>
+        <v>563944</v>
       </c>
       <c r="R135" t="n">
-        <v>6704725</v>
+        <v>6704880</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -15806,10 +15797,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>119874661</v>
+        <v>119874583</v>
       </c>
       <c r="B136" t="n">
-        <v>97907</v>
+        <v>90580</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -15818,47 +15809,38 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I136" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J136" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>563645</v>
+        <v>563996</v>
       </c>
       <c r="R136" t="n">
-        <v>6704515</v>
+        <v>6705007</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15917,10 +15899,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>119874649</v>
+        <v>119874678</v>
       </c>
       <c r="B137" t="n">
-        <v>97907</v>
+        <v>5169</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -15929,35 +15911,31 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I137" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J137" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr"/>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P137" t="inlineStr">
@@ -15966,10 +15944,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>563765</v>
+        <v>563957</v>
       </c>
       <c r="R137" t="n">
-        <v>6704626</v>
+        <v>6704878</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -16028,10 +16006,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>119874590</v>
+        <v>119874651</v>
       </c>
       <c r="B138" t="n">
-        <v>90562</v>
+        <v>97930</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -16040,38 +16018,47 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I138" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P138" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>564015</v>
+        <v>564256</v>
       </c>
       <c r="R138" t="n">
-        <v>6705047</v>
+        <v>6705293</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -16130,10 +16117,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>119874581</v>
+        <v>119874609</v>
       </c>
       <c r="B139" t="n">
-        <v>90562</v>
+        <v>90972</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -16146,21 +16133,16 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>1202</v>
-      </c>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>Ullticka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -16170,10 +16152,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>563792</v>
+        <v>564083</v>
       </c>
       <c r="R139" t="n">
-        <v>6704700</v>
+        <v>6705090</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -16232,10 +16214,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>119874682</v>
+        <v>119874612</v>
       </c>
       <c r="B140" t="n">
-        <v>5169</v>
+        <v>97930</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -16244,43 +16226,54 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I140" t="inlineStr"/>
-      <c r="M140" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L140" t="inlineStr"/>
+      <c r="N140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>564000</v>
+        <v>564201</v>
       </c>
       <c r="R140" t="n">
-        <v>6704958</v>
+        <v>6705191</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -16315,12 +16308,18 @@
           <t>2024-09-20</t>
         </is>
       </c>
+      <c r="AC140" t="inlineStr">
+        <is>
+          <t>1 blomstjälk</t>
+        </is>
+      </c>
       <c r="AD140" t="b">
         <v>0</v>
       </c>
       <c r="AE140" t="b">
         <v>0</v>
       </c>
+      <c r="AF140" t="inlineStr"/>
       <c r="AG140" t="b">
         <v>0</v>
       </c>
@@ -16339,10 +16338,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>119874685</v>
+        <v>119874572</v>
       </c>
       <c r="B141" t="n">
-        <v>8421</v>
+        <v>90580</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -16351,43 +16350,38 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>106554</v>
+        <v>1202</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
-      <c r="M141" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P141" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>563845</v>
+        <v>563815</v>
       </c>
       <c r="R141" t="n">
-        <v>6704771</v>
+        <v>6704789</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -16446,10 +16440,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>119874665</v>
+        <v>119874596</v>
       </c>
       <c r="B142" t="n">
-        <v>97907</v>
+        <v>57473</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -16458,25 +16452,25 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -16484,21 +16478,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J142" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="K142" t="inlineStr"/>
+      <c r="L142" t="inlineStr"/>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>564008</v>
+        <v>563633</v>
       </c>
       <c r="R142" t="n">
-        <v>6704979</v>
+        <v>6704498</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -16557,10 +16554,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>119874618</v>
+        <v>119874593</v>
       </c>
       <c r="B143" t="n">
-        <v>97907</v>
+        <v>90580</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -16569,47 +16566,38 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I143" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J143" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>564168</v>
+        <v>563710</v>
       </c>
       <c r="R143" t="n">
-        <v>6705183</v>
+        <v>6704663</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -16668,10 +16656,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>119874613</v>
+        <v>119874658</v>
       </c>
       <c r="B144" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -16703,7 +16691,7 @@
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
@@ -16717,10 +16705,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>563794</v>
+        <v>563749</v>
       </c>
       <c r="R144" t="n">
-        <v>6704750</v>
+        <v>6704725</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -16779,10 +16767,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>119874651</v>
+        <v>119874615</v>
       </c>
       <c r="B145" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -16814,7 +16802,7 @@
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
@@ -16828,10 +16816,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>564256</v>
+        <v>563748</v>
       </c>
       <c r="R145" t="n">
-        <v>6705293</v>
+        <v>6704608</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -16890,10 +16878,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>119874567</v>
+        <v>119874568</v>
       </c>
       <c r="B146" t="n">
-        <v>90905</v>
+        <v>90923</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -16930,10 +16918,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>564000</v>
+        <v>563986</v>
       </c>
       <c r="R146" t="n">
-        <v>6705011</v>
+        <v>6705032</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16992,10 +16980,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>119874647</v>
+        <v>119874580</v>
       </c>
       <c r="B147" t="n">
-        <v>97907</v>
+        <v>90580</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -17004,54 +16992,38 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I147" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J147" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K147" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L147" t="inlineStr"/>
-      <c r="N147" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>564036</v>
+        <v>563702</v>
       </c>
       <c r="R147" t="n">
-        <v>6705043</v>
+        <v>6704652</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -17086,18 +17058,12 @@
           <t>2024-09-20</t>
         </is>
       </c>
-      <c r="AC147" t="inlineStr">
-        <is>
-          <t>1 blomstjälk</t>
-        </is>
-      </c>
       <c r="AD147" t="b">
         <v>0</v>
       </c>
       <c r="AE147" t="b">
         <v>0</v>
       </c>
-      <c r="AF147" t="inlineStr"/>
       <c r="AG147" t="b">
         <v>0</v>
       </c>
@@ -17116,10 +17082,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>119874646</v>
+        <v>119874622</v>
       </c>
       <c r="B148" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -17151,7 +17117,7 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
@@ -17165,10 +17131,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>563995</v>
+        <v>563711</v>
       </c>
       <c r="R148" t="n">
-        <v>6704966</v>
+        <v>6704677</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -17227,10 +17193,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>119874617</v>
+        <v>119874685</v>
       </c>
       <c r="B149" t="n">
-        <v>97907</v>
+        <v>8421</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -17239,35 +17205,31 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>220787</v>
+        <v>106554</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I149" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J149" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr"/>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P149" t="inlineStr">
@@ -17276,10 +17238,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>563833</v>
+        <v>563845</v>
       </c>
       <c r="R149" t="n">
-        <v>6704788</v>
+        <v>6704771</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -17338,10 +17300,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>119874644</v>
+        <v>119874625</v>
       </c>
       <c r="B150" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -17373,7 +17335,7 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
@@ -17387,10 +17349,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>563984</v>
+        <v>564201</v>
       </c>
       <c r="R150" t="n">
-        <v>6704957</v>
+        <v>6705184</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -17449,10 +17411,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>119874605</v>
+        <v>119874613</v>
       </c>
       <c r="B151" t="n">
-        <v>90334</v>
+        <v>97930</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -17461,38 +17423,47 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>3215</v>
+        <v>220787</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I151" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P151" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>563929</v>
+        <v>563794</v>
       </c>
       <c r="R151" t="n">
-        <v>6704878</v>
+        <v>6704750</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -17551,10 +17522,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>119874574</v>
+        <v>119874627</v>
       </c>
       <c r="B152" t="n">
-        <v>90562</v>
+        <v>97930</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -17563,38 +17534,54 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I152" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L152" t="inlineStr"/>
+      <c r="N152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>563796</v>
+        <v>563813</v>
       </c>
       <c r="R152" t="n">
-        <v>6704785</v>
+        <v>6704796</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -17629,12 +17616,18 @@
           <t>2024-09-20</t>
         </is>
       </c>
+      <c r="AC152" t="inlineStr">
+        <is>
+          <t>2 blomstjälkar</t>
+        </is>
+      </c>
       <c r="AD152" t="b">
         <v>0</v>
       </c>
       <c r="AE152" t="b">
         <v>0</v>
       </c>
+      <c r="AF152" t="inlineStr"/>
       <c r="AG152" t="b">
         <v>0</v>
       </c>
@@ -17653,10 +17646,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>119874684</v>
+        <v>119874586</v>
       </c>
       <c r="B153" t="n">
-        <v>100171</v>
+        <v>90580</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -17665,25 +17658,25 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -17693,10 +17686,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>563956</v>
+        <v>564005</v>
       </c>
       <c r="R153" t="n">
-        <v>6704876</v>
+        <v>6705064</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -17755,10 +17748,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>119874642</v>
+        <v>119874628</v>
       </c>
       <c r="B154" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -17804,10 +17797,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>563974</v>
+        <v>564206</v>
       </c>
       <c r="R154" t="n">
-        <v>6704953</v>
+        <v>6705189</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -17866,10 +17859,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>119874571</v>
+        <v>119874617</v>
       </c>
       <c r="B155" t="n">
-        <v>90562</v>
+        <v>97930</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -17878,38 +17871,47 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I155" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P155" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>563816</v>
+        <v>563833</v>
       </c>
       <c r="R155" t="n">
-        <v>6704792</v>
+        <v>6704788</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -17968,10 +17970,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>119874582</v>
+        <v>119874623</v>
       </c>
       <c r="B156" t="n">
-        <v>90562</v>
+        <v>97930</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -17980,38 +17982,47 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I156" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P156" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>563958</v>
+        <v>563637</v>
       </c>
       <c r="R156" t="n">
-        <v>6704952</v>
+        <v>6704477</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -18070,10 +18081,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>119874666</v>
+        <v>119874588</v>
       </c>
       <c r="B157" t="n">
-        <v>74577</v>
+        <v>90580</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -18082,25 +18093,25 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>6426</v>
+        <v>1202</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -18110,10 +18121,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>563945</v>
+        <v>564011</v>
       </c>
       <c r="R157" t="n">
-        <v>6704877</v>
+        <v>6705060</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -18172,10 +18183,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>119874588</v>
+        <v>119874646</v>
       </c>
       <c r="B158" t="n">
-        <v>90562</v>
+        <v>97930</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -18184,38 +18195,47 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I158" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P158" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>564011</v>
+        <v>563995</v>
       </c>
       <c r="R158" t="n">
-        <v>6705060</v>
+        <v>6704966</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -18274,10 +18294,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>119874575</v>
+        <v>119874663</v>
       </c>
       <c r="B159" t="n">
-        <v>90562</v>
+        <v>97930</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -18286,38 +18306,47 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I159" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P159" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>563720</v>
+        <v>563835</v>
       </c>
       <c r="R159" t="n">
-        <v>6704700</v>
+        <v>6704743</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -18376,10 +18405,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>119874596</v>
+        <v>119874604</v>
       </c>
       <c r="B160" t="n">
-        <v>57463</v>
+        <v>90351</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -18388,50 +18417,38 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>103021</v>
+        <v>3215</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I160" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K160" t="inlineStr"/>
-      <c r="L160" t="inlineStr"/>
-      <c r="M160" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N160" t="inlineStr"/>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr"/>
       <c r="P160" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>563633</v>
+        <v>563936</v>
       </c>
       <c r="R160" t="n">
-        <v>6704498</v>
+        <v>6704867</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -18490,10 +18507,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>119874597</v>
+        <v>119874574</v>
       </c>
       <c r="B161" t="n">
-        <v>91494</v>
+        <v>90580</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -18502,25 +18519,25 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>4769</v>
+        <v>1202</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
@@ -18530,10 +18547,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>563943</v>
+        <v>563796</v>
       </c>
       <c r="R161" t="n">
-        <v>6704878</v>
+        <v>6704785</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -18592,10 +18609,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>119874681</v>
+        <v>119874577</v>
       </c>
       <c r="B162" t="n">
-        <v>5169</v>
+        <v>90580</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
@@ -18604,43 +18621,38 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
-      <c r="M162" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P162" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>563825</v>
+        <v>563703</v>
       </c>
       <c r="R162" t="n">
-        <v>6704705</v>
+        <v>6704669</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -18699,10 +18711,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>119874668</v>
+        <v>119874607</v>
       </c>
       <c r="B163" t="n">
-        <v>74577</v>
+        <v>90864</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -18711,25 +18723,25 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>6426</v>
+        <v>658</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
@@ -18739,10 +18751,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>563937</v>
+        <v>563821</v>
       </c>
       <c r="R163" t="n">
-        <v>6704867</v>
+        <v>6704817</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -18801,10 +18813,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>119874566</v>
+        <v>119874606</v>
       </c>
       <c r="B164" t="n">
-        <v>90905</v>
+        <v>90864</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -18813,25 +18825,25 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>2062</v>
+        <v>658</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -18841,10 +18853,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>564137</v>
+        <v>563784</v>
       </c>
       <c r="R164" t="n">
-        <v>6705070</v>
+        <v>6704721</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -18877,6 +18889,11 @@
       <c r="AA164" t="inlineStr">
         <is>
           <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AC164" t="inlineStr">
+        <is>
+          <t>Äldre fruktkropp</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -18903,10 +18920,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>119874633</v>
+        <v>119874644</v>
       </c>
       <c r="B165" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -18952,10 +18969,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>563741</v>
+        <v>563984</v>
       </c>
       <c r="R165" t="n">
-        <v>6704721</v>
+        <v>6704957</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -19014,10 +19031,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>119874663</v>
+        <v>119874618</v>
       </c>
       <c r="B166" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -19049,7 +19066,7 @@
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
@@ -19063,10 +19080,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>563835</v>
+        <v>564168</v>
       </c>
       <c r="R166" t="n">
-        <v>6704743</v>
+        <v>6705183</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -19125,10 +19142,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>119874655</v>
+        <v>119874635</v>
       </c>
       <c r="B167" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
@@ -19160,7 +19177,7 @@
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
@@ -19174,10 +19191,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>563757</v>
+        <v>563705</v>
       </c>
       <c r="R167" t="n">
-        <v>6704730</v>
+        <v>6704657</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -19236,10 +19253,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>119874593</v>
+        <v>119874582</v>
       </c>
       <c r="B168" t="n">
-        <v>90562</v>
+        <v>90580</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
@@ -19276,10 +19293,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>563710</v>
+        <v>563958</v>
       </c>
       <c r="R168" t="n">
-        <v>6704663</v>
+        <v>6704952</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -19338,10 +19355,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>119874607</v>
+        <v>119874677</v>
       </c>
       <c r="B169" t="n">
-        <v>90846</v>
+        <v>93953</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
@@ -19350,25 +19367,25 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>658</v>
+        <v>2383</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Bågpraktmossa</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Plagiomnium medium</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Bruch &amp; Schimp.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
@@ -19378,10 +19395,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>563821</v>
+        <v>563925</v>
       </c>
       <c r="R169" t="n">
-        <v>6704817</v>
+        <v>6704880</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -19440,10 +19457,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>119874628</v>
+        <v>119874585</v>
       </c>
       <c r="B170" t="n">
-        <v>97907</v>
+        <v>90580</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
@@ -19452,47 +19469,38 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I170" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J170" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr"/>
       <c r="P170" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>564206</v>
+        <v>563986</v>
       </c>
       <c r="R170" t="n">
-        <v>6705189</v>
+        <v>6705041</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -19551,10 +19559,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>119874630</v>
+        <v>119874571</v>
       </c>
       <c r="B171" t="n">
-        <v>97907</v>
+        <v>90580</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
@@ -19563,47 +19571,38 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I171" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J171" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr"/>
       <c r="P171" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>563815</v>
+        <v>563816</v>
       </c>
       <c r="R171" t="n">
-        <v>6704815</v>
+        <v>6704792</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -19662,10 +19661,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>119874580</v>
+        <v>119874684</v>
       </c>
       <c r="B172" t="n">
-        <v>90562</v>
+        <v>100194</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
@@ -19674,25 +19673,25 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -19702,10 +19701,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>563702</v>
+        <v>563956</v>
       </c>
       <c r="R172" t="n">
-        <v>6704652</v>
+        <v>6704876</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -19764,10 +19763,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>119874678</v>
+        <v>119874576</v>
       </c>
       <c r="B173" t="n">
-        <v>5169</v>
+        <v>90580</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
@@ -19776,43 +19775,38 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
-      <c r="M173" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P173" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>563957</v>
+        <v>563718</v>
       </c>
       <c r="R173" t="n">
-        <v>6704878</v>
+        <v>6704695</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -19871,10 +19865,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>119874606</v>
+        <v>119874569</v>
       </c>
       <c r="B174" t="n">
-        <v>90846</v>
+        <v>90580</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
@@ -19887,21 +19881,21 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
@@ -19911,10 +19905,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>563784</v>
+        <v>564137</v>
       </c>
       <c r="R174" t="n">
-        <v>6704721</v>
+        <v>6705071</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -19947,11 +19941,6 @@
       <c r="AA174" t="inlineStr">
         <is>
           <t>2024-09-20</t>
-        </is>
-      </c>
-      <c r="AC174" t="inlineStr">
-        <is>
-          <t>Äldre fruktkropp</t>
         </is>
       </c>
       <c r="AD174" t="b">
@@ -19978,10 +19967,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>119874624</v>
+        <v>119874655</v>
       </c>
       <c r="B175" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C175" t="inlineStr">
         <is>
@@ -20013,7 +20002,7 @@
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
@@ -20027,10 +20016,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>563734</v>
+        <v>563757</v>
       </c>
       <c r="R175" t="n">
-        <v>6704595</v>
+        <v>6704730</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -20089,10 +20078,10 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>119874627</v>
+        <v>119874624</v>
       </c>
       <c r="B176" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C176" t="inlineStr">
         <is>
@@ -20124,7 +20113,7 @@
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
@@ -20132,23 +20121,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K176" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L176" t="inlineStr"/>
-      <c r="N176" t="inlineStr"/>
       <c r="P176" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>563813</v>
+        <v>563734</v>
       </c>
       <c r="R176" t="n">
-        <v>6704796</v>
+        <v>6704595</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -20183,18 +20165,12 @@
           <t>2024-09-20</t>
         </is>
       </c>
-      <c r="AC176" t="inlineStr">
-        <is>
-          <t>2 blomstjälkar</t>
-        </is>
-      </c>
       <c r="AD176" t="b">
         <v>0</v>
       </c>
       <c r="AE176" t="b">
         <v>0</v>
       </c>
-      <c r="AF176" t="inlineStr"/>
       <c r="AG176" t="b">
         <v>0</v>
       </c>
@@ -20213,10 +20189,10 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>119874619</v>
+        <v>119874659</v>
       </c>
       <c r="B177" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C177" t="inlineStr">
         <is>
@@ -20248,7 +20224,7 @@
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
@@ -20262,10 +20238,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>564203</v>
+        <v>563746</v>
       </c>
       <c r="R177" t="n">
-        <v>6705186</v>
+        <v>6704720</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -20324,10 +20300,10 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>119874626</v>
+        <v>119874630</v>
       </c>
       <c r="B178" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>
@@ -20367,23 +20343,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K178" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L178" t="inlineStr"/>
-      <c r="N178" t="inlineStr"/>
       <c r="P178" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>564019</v>
+        <v>563815</v>
       </c>
       <c r="R178" t="n">
-        <v>6704997</v>
+        <v>6704815</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -20418,18 +20387,12 @@
           <t>2024-09-20</t>
         </is>
       </c>
-      <c r="AC178" t="inlineStr">
-        <is>
-          <t>1 blomstjälk</t>
-        </is>
-      </c>
       <c r="AD178" t="b">
         <v>0</v>
       </c>
       <c r="AE178" t="b">
         <v>0</v>
       </c>
-      <c r="AF178" t="inlineStr"/>
       <c r="AG178" t="b">
         <v>0</v>
       </c>
@@ -20448,10 +20411,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>119874639</v>
+        <v>119874632</v>
       </c>
       <c r="B179" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
@@ -20497,10 +20460,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>563718</v>
+        <v>563770</v>
       </c>
       <c r="R179" t="n">
-        <v>6704563</v>
+        <v>6704729</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -20559,10 +20522,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>119874659</v>
+        <v>119874590</v>
       </c>
       <c r="B180" t="n">
-        <v>97907</v>
+        <v>90580</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
@@ -20571,47 +20534,38 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I180" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J180" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr"/>
       <c r="P180" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>563746</v>
+        <v>564015</v>
       </c>
       <c r="R180" t="n">
-        <v>6704720</v>
+        <v>6705047</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -20670,10 +20624,10 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>119874623</v>
+        <v>119874573</v>
       </c>
       <c r="B181" t="n">
-        <v>97907</v>
+        <v>90580</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
@@ -20682,47 +20636,38 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I181" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J181" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr"/>
       <c r="P181" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>563637</v>
+        <v>563794</v>
       </c>
       <c r="R181" t="n">
-        <v>6704477</v>
+        <v>6704792</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -20781,10 +20726,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>119874569</v>
+        <v>119874581</v>
       </c>
       <c r="B182" t="n">
-        <v>90562</v>
+        <v>90580</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
@@ -20821,10 +20766,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>564137</v>
+        <v>563792</v>
       </c>
       <c r="R182" t="n">
-        <v>6705071</v>
+        <v>6704700</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -20883,10 +20828,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>119874608</v>
+        <v>119874621</v>
       </c>
       <c r="B183" t="n">
-        <v>94311</v>
+        <v>97930</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
@@ -20895,38 +20840,47 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>2809</v>
+        <v>220787</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
-        </is>
-      </c>
-      <c r="I183" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P183" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>563944</v>
+        <v>564283</v>
       </c>
       <c r="R183" t="n">
-        <v>6704880</v>
+        <v>6705293</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -20985,10 +20939,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>119874621</v>
+        <v>119874616</v>
       </c>
       <c r="B184" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
@@ -21020,7 +20974,7 @@
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
@@ -21034,10 +20988,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>564283</v>
+        <v>563993</v>
       </c>
       <c r="R184" t="n">
-        <v>6705293</v>
+        <v>6705035</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -21096,10 +21050,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>119874616</v>
+        <v>119874637</v>
       </c>
       <c r="B185" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
@@ -21131,7 +21085,7 @@
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J185" t="inlineStr">
@@ -21145,10 +21099,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>563993</v>
+        <v>563648</v>
       </c>
       <c r="R185" t="n">
-        <v>6705035</v>
+        <v>6704505</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -21207,10 +21161,10 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>119874568</v>
+        <v>119874639</v>
       </c>
       <c r="B186" t="n">
-        <v>90905</v>
+        <v>97930</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
@@ -21223,34 +21177,43 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>2062</v>
+        <v>220787</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I186" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J186" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P186" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>563986</v>
+        <v>563718</v>
       </c>
       <c r="R186" t="n">
-        <v>6705032</v>
+        <v>6704563</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -21309,10 +21272,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>119874583</v>
+        <v>119874682</v>
       </c>
       <c r="B187" t="n">
-        <v>90562</v>
+        <v>5169</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
@@ -21321,38 +21284,43 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
+      <c r="M187" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P187" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>563996</v>
+        <v>564000</v>
       </c>
       <c r="R187" t="n">
-        <v>6705007</v>
+        <v>6704958</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -21411,10 +21379,10 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>119874599</v>
+        <v>119874626</v>
       </c>
       <c r="B188" t="n">
-        <v>57326</v>
+        <v>97930</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
@@ -21423,43 +21391,54 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I188" t="inlineStr"/>
-      <c r="M188" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J188" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L188" t="inlineStr"/>
+      <c r="N188" t="inlineStr"/>
       <c r="P188" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>563944</v>
+        <v>564019</v>
       </c>
       <c r="R188" t="n">
-        <v>6704948</v>
+        <v>6704997</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -21494,12 +21473,18 @@
           <t>2024-09-20</t>
         </is>
       </c>
+      <c r="AC188" t="inlineStr">
+        <is>
+          <t>1 blomstjälk</t>
+        </is>
+      </c>
       <c r="AD188" t="b">
         <v>0</v>
       </c>
       <c r="AE188" t="b">
         <v>0</v>
       </c>
+      <c r="AF188" t="inlineStr"/>
       <c r="AG188" t="b">
         <v>0</v>
       </c>
@@ -21518,10 +21503,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>119874680</v>
+        <v>119874634</v>
       </c>
       <c r="B189" t="n">
-        <v>5169</v>
+        <v>97930</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
@@ -21530,31 +21515,35 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E189" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I189" t="inlineStr"/>
-      <c r="M189" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J189" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P189" t="inlineStr">
@@ -21563,10 +21552,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>563792</v>
+        <v>563712</v>
       </c>
       <c r="R189" t="n">
-        <v>6704694</v>
+        <v>6704670</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -21625,10 +21614,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>119874609</v>
+        <v>119874605</v>
       </c>
       <c r="B190" t="n">
-        <v>90954</v>
+        <v>90351</v>
       </c>
       <c r="C190" t="inlineStr">
         <is>
@@ -21637,20 +21626,25 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E190" t="n">
-        <v>6040186</v>
+        <v>3215</v>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>Rödgul trumpetsvamp</t>
+        </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
@@ -21660,10 +21654,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>564083</v>
+        <v>563929</v>
       </c>
       <c r="R190" t="n">
-        <v>6705090</v>
+        <v>6704878</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -21722,10 +21716,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>119874652</v>
+        <v>119874633</v>
       </c>
       <c r="B191" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C191" t="inlineStr">
         <is>
@@ -21757,7 +21751,7 @@
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
@@ -21771,10 +21765,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>563976</v>
+        <v>563741</v>
       </c>
       <c r="R191" t="n">
-        <v>6704966</v>
+        <v>6704721</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -21833,10 +21827,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>119874641</v>
+        <v>119874661</v>
       </c>
       <c r="B192" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C192" t="inlineStr">
         <is>
@@ -21868,7 +21862,7 @@
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
@@ -21882,10 +21876,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>563808</v>
+        <v>563645</v>
       </c>
       <c r="R192" t="n">
-        <v>6704697</v>
+        <v>6704515</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -21944,10 +21938,10 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>119874637</v>
+        <v>119874567</v>
       </c>
       <c r="B193" t="n">
-        <v>97907</v>
+        <v>90923</v>
       </c>
       <c r="C193" t="inlineStr">
         <is>
@@ -21960,43 +21954,34 @@
         </is>
       </c>
       <c r="E193" t="n">
-        <v>220787</v>
+        <v>2062</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I193" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J193" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr"/>
       <c r="P193" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>563648</v>
+        <v>564000</v>
       </c>
       <c r="R193" t="n">
-        <v>6704505</v>
+        <v>6705011</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -22055,10 +22040,10 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>119874604</v>
+        <v>119874665</v>
       </c>
       <c r="B194" t="n">
-        <v>90334</v>
+        <v>97930</v>
       </c>
       <c r="C194" t="inlineStr">
         <is>
@@ -22067,38 +22052,47 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>3215</v>
+        <v>220787</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I194" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J194" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P194" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>563936</v>
+        <v>564008</v>
       </c>
       <c r="R194" t="n">
-        <v>6704867</v>
+        <v>6704979</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -22157,10 +22151,10 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>119874591</v>
+        <v>119874597</v>
       </c>
       <c r="B195" t="n">
-        <v>90562</v>
+        <v>91512</v>
       </c>
       <c r="C195" t="inlineStr">
         <is>
@@ -22169,25 +22163,25 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>1202</v>
+        <v>4769</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
@@ -22197,10 +22191,10 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>564204</v>
+        <v>563943</v>
       </c>
       <c r="R195" t="n">
-        <v>6705194</v>
+        <v>6704878</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -22259,10 +22253,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>119874585</v>
+        <v>119874642</v>
       </c>
       <c r="B196" t="n">
-        <v>90562</v>
+        <v>97930</v>
       </c>
       <c r="C196" t="inlineStr">
         <is>
@@ -22271,38 +22265,47 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E196" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I196" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J196" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P196" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>563986</v>
+        <v>563974</v>
       </c>
       <c r="R196" t="n">
-        <v>6705041</v>
+        <v>6704953</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -22361,10 +22364,10 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>119874577</v>
+        <v>119874599</v>
       </c>
       <c r="B197" t="n">
-        <v>90562</v>
+        <v>57336</v>
       </c>
       <c r="C197" t="inlineStr">
         <is>
@@ -22377,34 +22380,39 @@
         </is>
       </c>
       <c r="E197" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
+      <c r="M197" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P197" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>563703</v>
+        <v>563944</v>
       </c>
       <c r="R197" t="n">
-        <v>6704669</v>
+        <v>6704948</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -22463,10 +22471,10 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>119874677</v>
+        <v>119874619</v>
       </c>
       <c r="B198" t="n">
-        <v>93930</v>
+        <v>97930</v>
       </c>
       <c r="C198" t="inlineStr">
         <is>
@@ -22475,38 +22483,47 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E198" t="n">
-        <v>2383</v>
+        <v>220787</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Bågpraktmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Plagiomnium medium</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(Bruch &amp; Schimp.) T.J.Kop.</t>
-        </is>
-      </c>
-      <c r="I198" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J198" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P198" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>563925</v>
+        <v>564203</v>
       </c>
       <c r="R198" t="n">
-        <v>6704880</v>
+        <v>6705186</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -22565,10 +22582,10 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>119874612</v>
+        <v>119874591</v>
       </c>
       <c r="B199" t="n">
-        <v>97907</v>
+        <v>90580</v>
       </c>
       <c r="C199" t="inlineStr">
         <is>
@@ -22577,54 +22594,38 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E199" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I199" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J199" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K199" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L199" t="inlineStr"/>
-      <c r="N199" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr"/>
       <c r="P199" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>564201</v>
+        <v>564204</v>
       </c>
       <c r="R199" t="n">
-        <v>6705191</v>
+        <v>6705194</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -22659,18 +22660,12 @@
           <t>2024-09-20</t>
         </is>
       </c>
-      <c r="AC199" t="inlineStr">
-        <is>
-          <t>1 blomstjälk</t>
-        </is>
-      </c>
       <c r="AD199" t="b">
         <v>0</v>
       </c>
       <c r="AE199" t="b">
         <v>0</v>
       </c>
-      <c r="AF199" t="inlineStr"/>
       <c r="AG199" t="b">
         <v>0</v>
       </c>
@@ -22689,10 +22684,10 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>119874576</v>
+        <v>119874666</v>
       </c>
       <c r="B200" t="n">
-        <v>90562</v>
+        <v>74593</v>
       </c>
       <c r="C200" t="inlineStr">
         <is>
@@ -22701,25 +22696,25 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>1202</v>
+        <v>6426</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
@@ -22729,10 +22724,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>563718</v>
+        <v>563945</v>
       </c>
       <c r="R200" t="n">
-        <v>6704695</v>
+        <v>6704877</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -22791,10 +22786,10 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>119874625</v>
+        <v>119874575</v>
       </c>
       <c r="B201" t="n">
-        <v>97907</v>
+        <v>90580</v>
       </c>
       <c r="C201" t="inlineStr">
         <is>
@@ -22803,47 +22798,38 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E201" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I201" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J201" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr"/>
       <c r="P201" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>564201</v>
+        <v>563720</v>
       </c>
       <c r="R201" t="n">
-        <v>6705184</v>
+        <v>6704700</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -22902,10 +22888,10 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>119874635</v>
+        <v>119874681</v>
       </c>
       <c r="B202" t="n">
-        <v>97907</v>
+        <v>5169</v>
       </c>
       <c r="C202" t="inlineStr">
         <is>
@@ -22914,35 +22900,31 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E202" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I202" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J202" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr"/>
+      <c r="M202" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P202" t="inlineStr">
@@ -22951,10 +22933,10 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>563705</v>
+        <v>563825</v>
       </c>
       <c r="R202" t="n">
-        <v>6704657</v>
+        <v>6704705</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -23013,10 +22995,10 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>119874573</v>
+        <v>119874680</v>
       </c>
       <c r="B203" t="n">
-        <v>90562</v>
+        <v>5169</v>
       </c>
       <c r="C203" t="inlineStr">
         <is>
@@ -23025,38 +23007,43 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E203" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I203" t="inlineStr"/>
+      <c r="M203" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P203" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>563794</v>
+        <v>563792</v>
       </c>
       <c r="R203" t="n">
-        <v>6704792</v>
+        <v>6704694</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -23115,10 +23102,10 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>119874586</v>
+        <v>119874652</v>
       </c>
       <c r="B204" t="n">
-        <v>90562</v>
+        <v>97930</v>
       </c>
       <c r="C204" t="inlineStr">
         <is>
@@ -23127,38 +23114,47 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E204" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I204" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J204" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P204" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>564005</v>
+        <v>563976</v>
       </c>
       <c r="R204" t="n">
-        <v>6705064</v>
+        <v>6704966</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>
@@ -23217,10 +23213,10 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>119874634</v>
+        <v>119874649</v>
       </c>
       <c r="B205" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C205" t="inlineStr">
         <is>
@@ -23252,7 +23248,7 @@
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J205" t="inlineStr">
@@ -23266,10 +23262,10 @@
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>563712</v>
+        <v>563765</v>
       </c>
       <c r="R205" t="n">
-        <v>6704670</v>
+        <v>6704626</v>
       </c>
       <c r="S205" t="n">
         <v>10</v>
@@ -23328,10 +23324,10 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>119874572</v>
+        <v>119874641</v>
       </c>
       <c r="B206" t="n">
-        <v>90562</v>
+        <v>97930</v>
       </c>
       <c r="C206" t="inlineStr">
         <is>
@@ -23340,38 +23336,47 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E206" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I206" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J206" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P206" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>563815</v>
+        <v>563808</v>
       </c>
       <c r="R206" t="n">
-        <v>6704789</v>
+        <v>6704697</v>
       </c>
       <c r="S206" t="n">
         <v>10</v>
@@ -23430,10 +23435,10 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>119874622</v>
+        <v>119874566</v>
       </c>
       <c r="B207" t="n">
-        <v>97907</v>
+        <v>90923</v>
       </c>
       <c r="C207" t="inlineStr">
         <is>
@@ -23446,43 +23451,34 @@
         </is>
       </c>
       <c r="E207" t="n">
-        <v>220787</v>
+        <v>2062</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I207" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J207" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr"/>
       <c r="P207" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>563711</v>
+        <v>564137</v>
       </c>
       <c r="R207" t="n">
-        <v>6704677</v>
+        <v>6705070</v>
       </c>
       <c r="S207" t="n">
         <v>10</v>
@@ -23541,10 +23537,10 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>119874615</v>
+        <v>119874668</v>
       </c>
       <c r="B208" t="n">
-        <v>97907</v>
+        <v>74593</v>
       </c>
       <c r="C208" t="inlineStr">
         <is>
@@ -23553,47 +23549,38 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E208" t="n">
-        <v>220787</v>
+        <v>6426</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I208" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J208" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr"/>
       <c r="P208" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>563748</v>
+        <v>563937</v>
       </c>
       <c r="R208" t="n">
-        <v>6704608</v>
+        <v>6704867</v>
       </c>
       <c r="S208" t="n">
         <v>10</v>
@@ -23652,10 +23639,10 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>119874632</v>
+        <v>119874647</v>
       </c>
       <c r="B209" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C209" t="inlineStr">
         <is>
@@ -23687,7 +23674,7 @@
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J209" t="inlineStr">
@@ -23695,16 +23682,23 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L209" t="inlineStr"/>
+      <c r="N209" t="inlineStr"/>
       <c r="P209" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>563770</v>
+        <v>564036</v>
       </c>
       <c r="R209" t="n">
-        <v>6704729</v>
+        <v>6705043</v>
       </c>
       <c r="S209" t="n">
         <v>10</v>
@@ -23739,12 +23733,18 @@
           <t>2024-09-20</t>
         </is>
       </c>
+      <c r="AC209" t="inlineStr">
+        <is>
+          <t>1 blomstjälk</t>
+        </is>
+      </c>
       <c r="AD209" t="b">
         <v>0</v>
       </c>
       <c r="AE209" t="b">
         <v>0</v>
       </c>
+      <c r="AF209" t="inlineStr"/>
       <c r="AG209" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 58548-2022 artfynd.xlsx
+++ b/artfynd/A 58548-2022 artfynd.xlsx
@@ -16214,10 +16214,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>119874612</v>
+        <v>119874572</v>
       </c>
       <c r="B140" t="n">
-        <v>97930</v>
+        <v>90580</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -16226,54 +16226,38 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I140" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J140" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K140" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L140" t="inlineStr"/>
-      <c r="N140" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>564201</v>
+        <v>563815</v>
       </c>
       <c r="R140" t="n">
-        <v>6705191</v>
+        <v>6704789</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -16308,18 +16292,12 @@
           <t>2024-09-20</t>
         </is>
       </c>
-      <c r="AC140" t="inlineStr">
-        <is>
-          <t>1 blomstjälk</t>
-        </is>
-      </c>
       <c r="AD140" t="b">
         <v>0</v>
       </c>
       <c r="AE140" t="b">
         <v>0</v>
       </c>
-      <c r="AF140" t="inlineStr"/>
       <c r="AG140" t="b">
         <v>0</v>
       </c>
@@ -16338,10 +16316,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>119874572</v>
+        <v>119874596</v>
       </c>
       <c r="B141" t="n">
-        <v>90580</v>
+        <v>57473</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -16354,34 +16332,46 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I141" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr"/>
+      <c r="L141" t="inlineStr"/>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>563815</v>
+        <v>563633</v>
       </c>
       <c r="R141" t="n">
-        <v>6704789</v>
+        <v>6704498</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -16440,10 +16430,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>119874596</v>
+        <v>119874612</v>
       </c>
       <c r="B142" t="n">
-        <v>57473</v>
+        <v>97930</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -16452,39 +16442,43 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K142" t="inlineStr"/>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="L142" t="inlineStr"/>
-      <c r="M142" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
@@ -16492,10 +16486,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>563633</v>
+        <v>564201</v>
       </c>
       <c r="R142" t="n">
-        <v>6704498</v>
+        <v>6705191</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -16530,12 +16524,18 @@
           <t>2024-09-20</t>
         </is>
       </c>
+      <c r="AC142" t="inlineStr">
+        <is>
+          <t>1 blomstjälk</t>
+        </is>
+      </c>
       <c r="AD142" t="b">
         <v>0</v>
       </c>
       <c r="AE142" t="b">
         <v>0</v>
       </c>
+      <c r="AF142" t="inlineStr"/>
       <c r="AG142" t="b">
         <v>0</v>
       </c>
@@ -16878,10 +16878,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>119874568</v>
+        <v>119874622</v>
       </c>
       <c r="B146" t="n">
-        <v>90923</v>
+        <v>97930</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -16894,34 +16894,43 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>2062</v>
+        <v>220787</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I146" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P146" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>563986</v>
+        <v>563711</v>
       </c>
       <c r="R146" t="n">
-        <v>6705032</v>
+        <v>6704677</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16980,10 +16989,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>119874580</v>
+        <v>119874568</v>
       </c>
       <c r="B147" t="n">
-        <v>90580</v>
+        <v>90923</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -16992,25 +17001,25 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>1202</v>
+        <v>2062</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -17020,10 +17029,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>563702</v>
+        <v>563986</v>
       </c>
       <c r="R147" t="n">
-        <v>6704652</v>
+        <v>6705032</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -17082,10 +17091,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>119874622</v>
+        <v>119874580</v>
       </c>
       <c r="B148" t="n">
-        <v>97930</v>
+        <v>90580</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -17094,47 +17103,38 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I148" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J148" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>563711</v>
+        <v>563702</v>
       </c>
       <c r="R148" t="n">
-        <v>6704677</v>
+        <v>6704652</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -18405,10 +18405,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>119874604</v>
+        <v>119874644</v>
       </c>
       <c r="B160" t="n">
-        <v>90351</v>
+        <v>97930</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -18417,38 +18417,47 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>3215</v>
+        <v>220787</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I160" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P160" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>563936</v>
+        <v>563984</v>
       </c>
       <c r="R160" t="n">
-        <v>6704867</v>
+        <v>6704957</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -18507,10 +18516,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>119874574</v>
+        <v>119874618</v>
       </c>
       <c r="B161" t="n">
-        <v>90580</v>
+        <v>97930</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -18519,38 +18528,47 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I161" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P161" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>563796</v>
+        <v>564168</v>
       </c>
       <c r="R161" t="n">
-        <v>6704785</v>
+        <v>6705183</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -18609,10 +18627,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>119874577</v>
+        <v>119874604</v>
       </c>
       <c r="B162" t="n">
-        <v>90580</v>
+        <v>90351</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
@@ -18621,25 +18639,25 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>1202</v>
+        <v>3215</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -18649,10 +18667,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>563703</v>
+        <v>563936</v>
       </c>
       <c r="R162" t="n">
-        <v>6704669</v>
+        <v>6704867</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -18711,10 +18729,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>119874607</v>
+        <v>119874574</v>
       </c>
       <c r="B163" t="n">
-        <v>90864</v>
+        <v>90580</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -18727,21 +18745,21 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
@@ -18751,10 +18769,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>563821</v>
+        <v>563796</v>
       </c>
       <c r="R163" t="n">
-        <v>6704817</v>
+        <v>6704785</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -18813,10 +18831,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>119874606</v>
+        <v>119874577</v>
       </c>
       <c r="B164" t="n">
-        <v>90864</v>
+        <v>90580</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -18829,21 +18847,21 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -18853,10 +18871,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>563784</v>
+        <v>563703</v>
       </c>
       <c r="R164" t="n">
-        <v>6704721</v>
+        <v>6704669</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -18889,11 +18907,6 @@
       <c r="AA164" t="inlineStr">
         <is>
           <t>2024-09-20</t>
-        </is>
-      </c>
-      <c r="AC164" t="inlineStr">
-        <is>
-          <t>Äldre fruktkropp</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -18920,10 +18933,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>119874644</v>
+        <v>119874607</v>
       </c>
       <c r="B165" t="n">
-        <v>97930</v>
+        <v>90864</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -18932,47 +18945,38 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I165" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J165" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>563984</v>
+        <v>563821</v>
       </c>
       <c r="R165" t="n">
-        <v>6704957</v>
+        <v>6704817</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -19031,10 +19035,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>119874618</v>
+        <v>119874606</v>
       </c>
       <c r="B166" t="n">
-        <v>97930</v>
+        <v>90864</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -19043,47 +19047,38 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I166" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J166" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr"/>
       <c r="P166" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>564168</v>
+        <v>563784</v>
       </c>
       <c r="R166" t="n">
-        <v>6705183</v>
+        <v>6704721</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -19116,6 +19111,11 @@
       <c r="AA166" t="inlineStr">
         <is>
           <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AC166" t="inlineStr">
+        <is>
+          <t>Äldre fruktkropp</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -21614,10 +21614,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>119874605</v>
+        <v>119874633</v>
       </c>
       <c r="B190" t="n">
-        <v>90351</v>
+        <v>97930</v>
       </c>
       <c r="C190" t="inlineStr">
         <is>
@@ -21626,38 +21626,47 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E190" t="n">
-        <v>3215</v>
+        <v>220787</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I190" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J190" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P190" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>563929</v>
+        <v>563741</v>
       </c>
       <c r="R190" t="n">
-        <v>6704878</v>
+        <v>6704721</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -21716,7 +21725,7 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>119874633</v>
+        <v>119874661</v>
       </c>
       <c r="B191" t="n">
         <v>97930</v>
@@ -21751,7 +21760,7 @@
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
@@ -21765,10 +21774,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>563741</v>
+        <v>563645</v>
       </c>
       <c r="R191" t="n">
-        <v>6704721</v>
+        <v>6704515</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -21827,10 +21836,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>119874661</v>
+        <v>119874605</v>
       </c>
       <c r="B192" t="n">
-        <v>97930</v>
+        <v>90351</v>
       </c>
       <c r="C192" t="inlineStr">
         <is>
@@ -21839,47 +21848,38 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E192" t="n">
-        <v>220787</v>
+        <v>3215</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I192" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J192" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr"/>
       <c r="P192" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>563645</v>
+        <v>563929</v>
       </c>
       <c r="R192" t="n">
-        <v>6704515</v>
+        <v>6704878</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -22253,10 +22253,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>119874642</v>
+        <v>119874599</v>
       </c>
       <c r="B196" t="n">
-        <v>97930</v>
+        <v>57336</v>
       </c>
       <c r="C196" t="inlineStr">
         <is>
@@ -22265,35 +22265,31 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E196" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I196" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J196" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr"/>
+      <c r="M196" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P196" t="inlineStr">
@@ -22302,10 +22298,10 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>563974</v>
+        <v>563944</v>
       </c>
       <c r="R196" t="n">
-        <v>6704953</v>
+        <v>6704948</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -22364,10 +22360,10 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>119874599</v>
+        <v>119874642</v>
       </c>
       <c r="B197" t="n">
-        <v>57336</v>
+        <v>97930</v>
       </c>
       <c r="C197" t="inlineStr">
         <is>
@@ -22376,31 +22372,35 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I197" t="inlineStr"/>
-      <c r="M197" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J197" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P197" t="inlineStr">
@@ -22409,10 +22409,10 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>563944</v>
+        <v>563974</v>
       </c>
       <c r="R197" t="n">
-        <v>6704948</v>
+        <v>6704953</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -22471,10 +22471,10 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>119874619</v>
+        <v>119874591</v>
       </c>
       <c r="B198" t="n">
-        <v>97930</v>
+        <v>90580</v>
       </c>
       <c r="C198" t="inlineStr">
         <is>
@@ -22483,47 +22483,38 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E198" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I198" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J198" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr"/>
       <c r="P198" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>564203</v>
+        <v>564204</v>
       </c>
       <c r="R198" t="n">
-        <v>6705186</v>
+        <v>6705194</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -22582,7 +22573,7 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>119874591</v>
+        <v>119874575</v>
       </c>
       <c r="B199" t="n">
         <v>90580</v>
@@ -22622,10 +22613,10 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>564204</v>
+        <v>563720</v>
       </c>
       <c r="R199" t="n">
-        <v>6705194</v>
+        <v>6704700</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -22684,10 +22675,10 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>119874666</v>
+        <v>119874680</v>
       </c>
       <c r="B200" t="n">
-        <v>74593</v>
+        <v>5169</v>
       </c>
       <c r="C200" t="inlineStr">
         <is>
@@ -22700,34 +22691,39 @@
         </is>
       </c>
       <c r="E200" t="n">
-        <v>6426</v>
+        <v>100526</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
+      <c r="M200" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P200" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>563945</v>
+        <v>563792</v>
       </c>
       <c r="R200" t="n">
-        <v>6704877</v>
+        <v>6704694</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -22786,10 +22782,10 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>119874575</v>
+        <v>119874666</v>
       </c>
       <c r="B201" t="n">
-        <v>90580</v>
+        <v>74593</v>
       </c>
       <c r="C201" t="inlineStr">
         <is>
@@ -22798,25 +22794,25 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E201" t="n">
-        <v>1202</v>
+        <v>6426</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I201" t="inlineStr"/>
@@ -22826,10 +22822,10 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>563720</v>
+        <v>563945</v>
       </c>
       <c r="R201" t="n">
-        <v>6704700</v>
+        <v>6704877</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -22888,10 +22884,10 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>119874681</v>
+        <v>119874619</v>
       </c>
       <c r="B202" t="n">
-        <v>5169</v>
+        <v>97930</v>
       </c>
       <c r="C202" t="inlineStr">
         <is>
@@ -22900,31 +22896,35 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E202" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I202" t="inlineStr"/>
-      <c r="M202" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J202" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P202" t="inlineStr">
@@ -22933,10 +22933,10 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>563825</v>
+        <v>564203</v>
       </c>
       <c r="R202" t="n">
-        <v>6704705</v>
+        <v>6705186</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -22995,7 +22995,7 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>119874680</v>
+        <v>119874681</v>
       </c>
       <c r="B203" t="n">
         <v>5169</v>
@@ -23040,10 +23040,10 @@
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>563792</v>
+        <v>563825</v>
       </c>
       <c r="R203" t="n">
-        <v>6704694</v>
+        <v>6704705</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>

--- a/artfynd/A 58548-2022 artfynd.xlsx
+++ b/artfynd/A 58548-2022 artfynd.xlsx
@@ -15695,10 +15695,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>119874608</v>
+        <v>119874655</v>
       </c>
       <c r="B135" t="n">
-        <v>94334</v>
+        <v>97930</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -15707,38 +15707,47 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>2809</v>
+        <v>220787</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
-        </is>
-      </c>
-      <c r="I135" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P135" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>563944</v>
+        <v>563757</v>
       </c>
       <c r="R135" t="n">
-        <v>6704880</v>
+        <v>6704730</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -15797,10 +15806,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>119874583</v>
+        <v>119874628</v>
       </c>
       <c r="B136" t="n">
-        <v>90580</v>
+        <v>97930</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -15809,38 +15818,47 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I136" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P136" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>563996</v>
+        <v>564206</v>
       </c>
       <c r="R136" t="n">
-        <v>6705007</v>
+        <v>6705189</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15899,10 +15917,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>119874678</v>
+        <v>119874651</v>
       </c>
       <c r="B137" t="n">
-        <v>5169</v>
+        <v>97930</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -15911,31 +15929,35 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I137" t="inlineStr"/>
-      <c r="M137" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P137" t="inlineStr">
@@ -15944,10 +15966,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>563957</v>
+        <v>564256</v>
       </c>
       <c r="R137" t="n">
-        <v>6704878</v>
+        <v>6705293</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -16006,10 +16028,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>119874651</v>
+        <v>119874583</v>
       </c>
       <c r="B138" t="n">
-        <v>97930</v>
+        <v>90580</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -16018,47 +16040,38 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I138" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J138" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>564256</v>
+        <v>563996</v>
       </c>
       <c r="R138" t="n">
-        <v>6705293</v>
+        <v>6705007</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -16117,10 +16130,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>119874609</v>
+        <v>119874585</v>
       </c>
       <c r="B139" t="n">
-        <v>90972</v>
+        <v>90580</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -16133,16 +16146,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6040186</v>
+        <v>1202</v>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -16152,10 +16170,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>564083</v>
+        <v>563986</v>
       </c>
       <c r="R139" t="n">
-        <v>6705090</v>
+        <v>6705041</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -16214,10 +16232,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>119874572</v>
+        <v>119874685</v>
       </c>
       <c r="B140" t="n">
-        <v>90580</v>
+        <v>8421</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -16226,38 +16244,43 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>1202</v>
+        <v>106554</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P140" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>563815</v>
+        <v>563845</v>
       </c>
       <c r="R140" t="n">
-        <v>6704789</v>
+        <v>6704771</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -16316,10 +16339,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>119874596</v>
+        <v>119874590</v>
       </c>
       <c r="B141" t="n">
-        <v>57473</v>
+        <v>90580</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -16332,46 +16355,34 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I141" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K141" t="inlineStr"/>
-      <c r="L141" t="inlineStr"/>
-      <c r="M141" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N141" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>563633</v>
+        <v>564015</v>
       </c>
       <c r="R141" t="n">
-        <v>6704498</v>
+        <v>6705047</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -16430,10 +16441,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>119874612</v>
+        <v>119874668</v>
       </c>
       <c r="B142" t="n">
-        <v>97930</v>
+        <v>74593</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -16442,54 +16453,38 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>220787</v>
+        <v>6426</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I142" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J142" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K142" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L142" t="inlineStr"/>
-      <c r="N142" t="inlineStr"/>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>564201</v>
+        <v>563937</v>
       </c>
       <c r="R142" t="n">
-        <v>6705191</v>
+        <v>6704867</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -16524,18 +16519,12 @@
           <t>2024-09-20</t>
         </is>
       </c>
-      <c r="AC142" t="inlineStr">
-        <is>
-          <t>1 blomstjälk</t>
-        </is>
-      </c>
       <c r="AD142" t="b">
         <v>0</v>
       </c>
       <c r="AE142" t="b">
         <v>0</v>
       </c>
-      <c r="AF142" t="inlineStr"/>
       <c r="AG142" t="b">
         <v>0</v>
       </c>
@@ -16554,10 +16543,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>119874593</v>
+        <v>119874663</v>
       </c>
       <c r="B143" t="n">
-        <v>90580</v>
+        <v>97930</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -16566,38 +16555,47 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I143" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P143" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>563710</v>
+        <v>563835</v>
       </c>
       <c r="R143" t="n">
-        <v>6704663</v>
+        <v>6704743</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -16656,7 +16654,7 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>119874658</v>
+        <v>119874624</v>
       </c>
       <c r="B144" t="n">
         <v>97930</v>
@@ -16691,7 +16689,7 @@
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
@@ -16705,10 +16703,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>563749</v>
+        <v>563734</v>
       </c>
       <c r="R144" t="n">
-        <v>6704725</v>
+        <v>6704595</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -16767,10 +16765,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>119874615</v>
+        <v>119874606</v>
       </c>
       <c r="B145" t="n">
-        <v>97930</v>
+        <v>90864</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -16779,47 +16777,38 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I145" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J145" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>563748</v>
+        <v>563784</v>
       </c>
       <c r="R145" t="n">
-        <v>6704608</v>
+        <v>6704721</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -16852,6 +16841,11 @@
       <c r="AA145" t="inlineStr">
         <is>
           <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AC145" t="inlineStr">
+        <is>
+          <t>Äldre fruktkropp</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -16878,10 +16872,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>119874622</v>
+        <v>119874607</v>
       </c>
       <c r="B146" t="n">
-        <v>97930</v>
+        <v>90864</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -16890,47 +16884,38 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I146" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J146" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>563711</v>
+        <v>563821</v>
       </c>
       <c r="R146" t="n">
-        <v>6704677</v>
+        <v>6704817</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16989,10 +16974,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>119874568</v>
+        <v>119874569</v>
       </c>
       <c r="B147" t="n">
-        <v>90923</v>
+        <v>90580</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -17001,25 +16986,25 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>2062</v>
+        <v>1202</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -17029,10 +17014,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>563986</v>
+        <v>564137</v>
       </c>
       <c r="R147" t="n">
-        <v>6705032</v>
+        <v>6705071</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -17091,10 +17076,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>119874580</v>
+        <v>119874639</v>
       </c>
       <c r="B148" t="n">
-        <v>90580</v>
+        <v>97930</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -17103,38 +17088,47 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I148" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P148" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>563702</v>
+        <v>563718</v>
       </c>
       <c r="R148" t="n">
-        <v>6704652</v>
+        <v>6704563</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -17193,10 +17187,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>119874685</v>
+        <v>119874613</v>
       </c>
       <c r="B149" t="n">
-        <v>8421</v>
+        <v>97930</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -17205,31 +17199,35 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>106554</v>
+        <v>220787</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I149" t="inlineStr"/>
-      <c r="M149" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P149" t="inlineStr">
@@ -17238,10 +17236,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>563845</v>
+        <v>563794</v>
       </c>
       <c r="R149" t="n">
-        <v>6704771</v>
+        <v>6704750</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -17300,7 +17298,7 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>119874625</v>
+        <v>119874623</v>
       </c>
       <c r="B150" t="n">
         <v>97930</v>
@@ -17349,10 +17347,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>564201</v>
+        <v>563637</v>
       </c>
       <c r="R150" t="n">
-        <v>6705184</v>
+        <v>6704477</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -17411,7 +17409,7 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>119874613</v>
+        <v>119874641</v>
       </c>
       <c r="B151" t="n">
         <v>97930</v>
@@ -17446,7 +17444,7 @@
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
@@ -17460,10 +17458,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>563794</v>
+        <v>563808</v>
       </c>
       <c r="R151" t="n">
-        <v>6704750</v>
+        <v>6704697</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -17522,10 +17520,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>119874627</v>
+        <v>119874576</v>
       </c>
       <c r="B152" t="n">
-        <v>97930</v>
+        <v>90580</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -17534,54 +17532,38 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I152" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J152" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K152" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L152" t="inlineStr"/>
-      <c r="N152" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>563813</v>
+        <v>563718</v>
       </c>
       <c r="R152" t="n">
-        <v>6704796</v>
+        <v>6704695</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -17616,18 +17598,12 @@
           <t>2024-09-20</t>
         </is>
       </c>
-      <c r="AC152" t="inlineStr">
-        <is>
-          <t>2 blomstjälkar</t>
-        </is>
-      </c>
       <c r="AD152" t="b">
         <v>0</v>
       </c>
       <c r="AE152" t="b">
         <v>0</v>
       </c>
-      <c r="AF152" t="inlineStr"/>
       <c r="AG152" t="b">
         <v>0</v>
       </c>
@@ -17646,7 +17622,7 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>119874586</v>
+        <v>119874581</v>
       </c>
       <c r="B153" t="n">
         <v>90580</v>
@@ -17686,10 +17662,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>564005</v>
+        <v>563792</v>
       </c>
       <c r="R153" t="n">
-        <v>6705064</v>
+        <v>6704700</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -17748,10 +17724,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>119874628</v>
+        <v>119874677</v>
       </c>
       <c r="B154" t="n">
-        <v>97930</v>
+        <v>93953</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -17760,47 +17736,38 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>220787</v>
+        <v>2383</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bågpraktmossa</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Plagiomnium medium</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I154" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J154" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Bruch &amp; Schimp.) T.J.Kop.</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr"/>
       <c r="P154" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>564206</v>
+        <v>563925</v>
       </c>
       <c r="R154" t="n">
-        <v>6705189</v>
+        <v>6704880</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -17859,10 +17826,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>119874617</v>
+        <v>119874678</v>
       </c>
       <c r="B155" t="n">
-        <v>97930</v>
+        <v>5169</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -17871,35 +17838,31 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I155" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J155" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr"/>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P155" t="inlineStr">
@@ -17908,10 +17871,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>563833</v>
+        <v>563957</v>
       </c>
       <c r="R155" t="n">
-        <v>6704788</v>
+        <v>6704878</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -17970,7 +17933,7 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>119874623</v>
+        <v>119874658</v>
       </c>
       <c r="B156" t="n">
         <v>97930</v>
@@ -18005,7 +17968,7 @@
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
@@ -18019,10 +17982,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>563637</v>
+        <v>563749</v>
       </c>
       <c r="R156" t="n">
-        <v>6704477</v>
+        <v>6704725</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -18081,10 +18044,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>119874588</v>
+        <v>119874626</v>
       </c>
       <c r="B157" t="n">
-        <v>90580</v>
+        <v>97930</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -18093,38 +18056,54 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I157" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L157" t="inlineStr"/>
+      <c r="N157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>564011</v>
+        <v>564019</v>
       </c>
       <c r="R157" t="n">
-        <v>6705060</v>
+        <v>6704997</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -18159,12 +18138,18 @@
           <t>2024-09-20</t>
         </is>
       </c>
+      <c r="AC157" t="inlineStr">
+        <is>
+          <t>1 blomstjälk</t>
+        </is>
+      </c>
       <c r="AD157" t="b">
         <v>0</v>
       </c>
       <c r="AE157" t="b">
         <v>0</v>
       </c>
+      <c r="AF157" t="inlineStr"/>
       <c r="AG157" t="b">
         <v>0</v>
       </c>
@@ -18183,7 +18168,7 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>119874646</v>
+        <v>119874642</v>
       </c>
       <c r="B158" t="n">
         <v>97930</v>
@@ -18218,7 +18203,7 @@
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
@@ -18232,10 +18217,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>563995</v>
+        <v>563974</v>
       </c>
       <c r="R158" t="n">
-        <v>6704966</v>
+        <v>6704953</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -18294,7 +18279,7 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>119874663</v>
+        <v>119874647</v>
       </c>
       <c r="B159" t="n">
         <v>97930</v>
@@ -18329,7 +18314,7 @@
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
@@ -18337,16 +18322,23 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L159" t="inlineStr"/>
+      <c r="N159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>563835</v>
+        <v>564036</v>
       </c>
       <c r="R159" t="n">
-        <v>6704743</v>
+        <v>6705043</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -18381,12 +18373,18 @@
           <t>2024-09-20</t>
         </is>
       </c>
+      <c r="AC159" t="inlineStr">
+        <is>
+          <t>1 blomstjälk</t>
+        </is>
+      </c>
       <c r="AD159" t="b">
         <v>0</v>
       </c>
       <c r="AE159" t="b">
         <v>0</v>
       </c>
+      <c r="AF159" t="inlineStr"/>
       <c r="AG159" t="b">
         <v>0</v>
       </c>
@@ -18405,7 +18403,7 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>119874644</v>
+        <v>119874634</v>
       </c>
       <c r="B160" t="n">
         <v>97930</v>
@@ -18454,10 +18452,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>563984</v>
+        <v>563712</v>
       </c>
       <c r="R160" t="n">
-        <v>6704957</v>
+        <v>6704670</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -18516,10 +18514,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>119874618</v>
+        <v>119874582</v>
       </c>
       <c r="B161" t="n">
-        <v>97930</v>
+        <v>90580</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -18528,47 +18526,38 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I161" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J161" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr"/>
       <c r="P161" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>564168</v>
+        <v>563958</v>
       </c>
       <c r="R161" t="n">
-        <v>6705183</v>
+        <v>6704952</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -18627,10 +18616,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>119874604</v>
+        <v>119874572</v>
       </c>
       <c r="B162" t="n">
-        <v>90351</v>
+        <v>90580</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
@@ -18639,25 +18628,25 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>3215</v>
+        <v>1202</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -18667,10 +18656,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>563936</v>
+        <v>563815</v>
       </c>
       <c r="R162" t="n">
-        <v>6704867</v>
+        <v>6704789</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -18729,10 +18718,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>119874574</v>
+        <v>119874630</v>
       </c>
       <c r="B163" t="n">
-        <v>90580</v>
+        <v>97930</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -18741,38 +18730,47 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I163" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P163" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>563796</v>
+        <v>563815</v>
       </c>
       <c r="R163" t="n">
-        <v>6704785</v>
+        <v>6704815</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -18831,10 +18829,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>119874577</v>
+        <v>119874665</v>
       </c>
       <c r="B164" t="n">
-        <v>90580</v>
+        <v>97930</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -18843,38 +18841,47 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I164" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P164" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>563703</v>
+        <v>564008</v>
       </c>
       <c r="R164" t="n">
-        <v>6704669</v>
+        <v>6704979</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -18933,10 +18940,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>119874607</v>
+        <v>119874574</v>
       </c>
       <c r="B165" t="n">
-        <v>90864</v>
+        <v>90580</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -18949,21 +18956,21 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -18973,10 +18980,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>563821</v>
+        <v>563796</v>
       </c>
       <c r="R165" t="n">
-        <v>6704817</v>
+        <v>6704785</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -19035,10 +19042,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>119874606</v>
+        <v>119874684</v>
       </c>
       <c r="B166" t="n">
-        <v>90864</v>
+        <v>100194</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -19047,25 +19054,25 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>658</v>
+        <v>222498</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
@@ -19075,10 +19082,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>563784</v>
+        <v>563956</v>
       </c>
       <c r="R166" t="n">
-        <v>6704721</v>
+        <v>6704876</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -19111,11 +19118,6 @@
       <c r="AA166" t="inlineStr">
         <is>
           <t>2024-09-20</t>
-        </is>
-      </c>
-      <c r="AC166" t="inlineStr">
-        <is>
-          <t>Äldre fruktkropp</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -19142,7 +19144,7 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>119874635</v>
+        <v>119874612</v>
       </c>
       <c r="B167" t="n">
         <v>97930</v>
@@ -19177,7 +19179,7 @@
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
@@ -19185,16 +19187,23 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L167" t="inlineStr"/>
+      <c r="N167" t="inlineStr"/>
       <c r="P167" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>563705</v>
+        <v>564201</v>
       </c>
       <c r="R167" t="n">
-        <v>6704657</v>
+        <v>6705191</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -19229,12 +19238,18 @@
           <t>2024-09-20</t>
         </is>
       </c>
+      <c r="AC167" t="inlineStr">
+        <is>
+          <t>1 blomstjälk</t>
+        </is>
+      </c>
       <c r="AD167" t="b">
         <v>0</v>
       </c>
       <c r="AE167" t="b">
         <v>0</v>
       </c>
+      <c r="AF167" t="inlineStr"/>
       <c r="AG167" t="b">
         <v>0</v>
       </c>
@@ -19253,10 +19268,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>119874582</v>
+        <v>119874616</v>
       </c>
       <c r="B168" t="n">
-        <v>90580</v>
+        <v>97930</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
@@ -19265,38 +19280,47 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I168" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P168" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>563958</v>
+        <v>563993</v>
       </c>
       <c r="R168" t="n">
-        <v>6704952</v>
+        <v>6705035</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -19355,10 +19379,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>119874677</v>
+        <v>119874632</v>
       </c>
       <c r="B169" t="n">
-        <v>93953</v>
+        <v>97930</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
@@ -19367,38 +19391,47 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>2383</v>
+        <v>220787</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Bågpraktmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Plagiomnium medium</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Bruch &amp; Schimp.) T.J.Kop.</t>
-        </is>
-      </c>
-      <c r="I169" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P169" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>563925</v>
+        <v>563770</v>
       </c>
       <c r="R169" t="n">
-        <v>6704880</v>
+        <v>6704729</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -19457,10 +19490,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>119874585</v>
+        <v>119874644</v>
       </c>
       <c r="B170" t="n">
-        <v>90580</v>
+        <v>97930</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
@@ -19469,38 +19502,47 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I170" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P170" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>563986</v>
+        <v>563984</v>
       </c>
       <c r="R170" t="n">
-        <v>6705041</v>
+        <v>6704957</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -19559,10 +19601,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>119874571</v>
+        <v>119874680</v>
       </c>
       <c r="B171" t="n">
-        <v>90580</v>
+        <v>5169</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
@@ -19571,38 +19613,43 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
+      <c r="M171" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P171" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>563816</v>
+        <v>563792</v>
       </c>
       <c r="R171" t="n">
-        <v>6704792</v>
+        <v>6704694</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -19661,10 +19708,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>119874684</v>
+        <v>119874575</v>
       </c>
       <c r="B172" t="n">
-        <v>100194</v>
+        <v>90580</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
@@ -19673,25 +19720,25 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -19701,10 +19748,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>563956</v>
+        <v>563720</v>
       </c>
       <c r="R172" t="n">
-        <v>6704876</v>
+        <v>6704700</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -19763,10 +19810,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>119874576</v>
+        <v>119874605</v>
       </c>
       <c r="B173" t="n">
-        <v>90580</v>
+        <v>90351</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
@@ -19775,25 +19822,25 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>1202</v>
+        <v>3215</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
@@ -19803,10 +19850,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>563718</v>
+        <v>563929</v>
       </c>
       <c r="R173" t="n">
-        <v>6704695</v>
+        <v>6704878</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -19865,10 +19912,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>119874569</v>
+        <v>119874625</v>
       </c>
       <c r="B174" t="n">
-        <v>90580</v>
+        <v>97930</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
@@ -19877,38 +19924,47 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I174" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P174" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>564137</v>
+        <v>564201</v>
       </c>
       <c r="R174" t="n">
-        <v>6705071</v>
+        <v>6705184</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -19967,10 +20023,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>119874655</v>
+        <v>119874573</v>
       </c>
       <c r="B175" t="n">
-        <v>97930</v>
+        <v>90580</v>
       </c>
       <c r="C175" t="inlineStr">
         <is>
@@ -19979,47 +20035,38 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I175" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J175" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr"/>
       <c r="P175" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>563757</v>
+        <v>563794</v>
       </c>
       <c r="R175" t="n">
-        <v>6704730</v>
+        <v>6704792</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -20078,7 +20125,7 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>119874624</v>
+        <v>119874622</v>
       </c>
       <c r="B176" t="n">
         <v>97930</v>
@@ -20127,10 +20174,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>563734</v>
+        <v>563711</v>
       </c>
       <c r="R176" t="n">
-        <v>6704595</v>
+        <v>6704677</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -20189,10 +20236,10 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>119874659</v>
+        <v>119874609</v>
       </c>
       <c r="B177" t="n">
-        <v>97930</v>
+        <v>90972</v>
       </c>
       <c r="C177" t="inlineStr">
         <is>
@@ -20201,47 +20248,33 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F177" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I177" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J177" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr"/>
       <c r="P177" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>563746</v>
+        <v>564083</v>
       </c>
       <c r="R177" t="n">
-        <v>6704720</v>
+        <v>6705090</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -20300,10 +20333,10 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>119874630</v>
+        <v>119874593</v>
       </c>
       <c r="B178" t="n">
-        <v>97930</v>
+        <v>90580</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>
@@ -20312,47 +20345,38 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I178" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J178" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr"/>
       <c r="P178" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>563815</v>
+        <v>563710</v>
       </c>
       <c r="R178" t="n">
-        <v>6704815</v>
+        <v>6704663</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -20411,10 +20435,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>119874632</v>
+        <v>119874597</v>
       </c>
       <c r="B179" t="n">
-        <v>97930</v>
+        <v>91512</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
@@ -20423,47 +20447,38 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>220787</v>
+        <v>4769</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I179" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J179" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Scop.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr"/>
       <c r="P179" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>563770</v>
+        <v>563943</v>
       </c>
       <c r="R179" t="n">
-        <v>6704729</v>
+        <v>6704878</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -20522,10 +20537,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>119874590</v>
+        <v>119874646</v>
       </c>
       <c r="B180" t="n">
-        <v>90580</v>
+        <v>97930</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
@@ -20534,38 +20549,47 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I180" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J180" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P180" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>564015</v>
+        <v>563995</v>
       </c>
       <c r="R180" t="n">
-        <v>6705047</v>
+        <v>6704966</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -20624,10 +20648,10 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>119874573</v>
+        <v>119874619</v>
       </c>
       <c r="B181" t="n">
-        <v>90580</v>
+        <v>97930</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
@@ -20636,38 +20660,47 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I181" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J181" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P181" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>563794</v>
+        <v>564203</v>
       </c>
       <c r="R181" t="n">
-        <v>6704792</v>
+        <v>6705186</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -20726,10 +20759,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>119874581</v>
+        <v>119874649</v>
       </c>
       <c r="B182" t="n">
-        <v>90580</v>
+        <v>97930</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
@@ -20738,38 +20771,47 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I182" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J182" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P182" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>563792</v>
+        <v>563765</v>
       </c>
       <c r="R182" t="n">
-        <v>6704700</v>
+        <v>6704626</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -20828,7 +20870,7 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>119874621</v>
+        <v>119874633</v>
       </c>
       <c r="B183" t="n">
         <v>97930</v>
@@ -20863,7 +20905,7 @@
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
@@ -20877,10 +20919,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>564283</v>
+        <v>563741</v>
       </c>
       <c r="R183" t="n">
-        <v>6705293</v>
+        <v>6704721</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -20939,7 +20981,7 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>119874616</v>
+        <v>119874635</v>
       </c>
       <c r="B184" t="n">
         <v>97930</v>
@@ -20974,7 +21016,7 @@
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
@@ -20988,10 +21030,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>563993</v>
+        <v>563705</v>
       </c>
       <c r="R184" t="n">
-        <v>6705035</v>
+        <v>6704657</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -21050,10 +21092,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>119874637</v>
+        <v>119874567</v>
       </c>
       <c r="B185" t="n">
-        <v>97930</v>
+        <v>90923</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
@@ -21066,43 +21108,34 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>220787</v>
+        <v>2062</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I185" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J185" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr"/>
       <c r="P185" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>563648</v>
+        <v>564000</v>
       </c>
       <c r="R185" t="n">
-        <v>6704505</v>
+        <v>6705011</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -21161,10 +21194,10 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>119874639</v>
+        <v>119874580</v>
       </c>
       <c r="B186" t="n">
-        <v>97930</v>
+        <v>90580</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
@@ -21173,47 +21206,38 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I186" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J186" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr"/>
       <c r="P186" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>563718</v>
+        <v>563702</v>
       </c>
       <c r="R186" t="n">
-        <v>6704563</v>
+        <v>6704652</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -21272,10 +21296,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>119874682</v>
+        <v>119874615</v>
       </c>
       <c r="B187" t="n">
-        <v>5169</v>
+        <v>97930</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
@@ -21284,31 +21308,35 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I187" t="inlineStr"/>
-      <c r="M187" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J187" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P187" t="inlineStr">
@@ -21317,10 +21345,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>564000</v>
+        <v>563748</v>
       </c>
       <c r="R187" t="n">
-        <v>6704958</v>
+        <v>6704608</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -21379,10 +21407,10 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>119874626</v>
+        <v>119874596</v>
       </c>
       <c r="B188" t="n">
-        <v>97930</v>
+        <v>57473</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
@@ -21391,43 +21419,39 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J188" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K188" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K188" t="inlineStr"/>
       <c r="L188" t="inlineStr"/>
+      <c r="M188" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N188" t="inlineStr"/>
       <c r="P188" t="inlineStr">
         <is>
@@ -21435,10 +21459,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>564019</v>
+        <v>563633</v>
       </c>
       <c r="R188" t="n">
-        <v>6704997</v>
+        <v>6704498</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -21473,18 +21497,12 @@
           <t>2024-09-20</t>
         </is>
       </c>
-      <c r="AC188" t="inlineStr">
-        <is>
-          <t>1 blomstjälk</t>
-        </is>
-      </c>
       <c r="AD188" t="b">
         <v>0</v>
       </c>
       <c r="AE188" t="b">
         <v>0</v>
       </c>
-      <c r="AF188" t="inlineStr"/>
       <c r="AG188" t="b">
         <v>0</v>
       </c>
@@ -21503,10 +21521,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>119874634</v>
+        <v>119874591</v>
       </c>
       <c r="B189" t="n">
-        <v>97930</v>
+        <v>90580</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
@@ -21515,47 +21533,38 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E189" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I189" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J189" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr"/>
       <c r="P189" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>563712</v>
+        <v>564204</v>
       </c>
       <c r="R189" t="n">
-        <v>6704670</v>
+        <v>6705194</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -21614,10 +21623,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>119874633</v>
+        <v>119874682</v>
       </c>
       <c r="B190" t="n">
-        <v>97930</v>
+        <v>5169</v>
       </c>
       <c r="C190" t="inlineStr">
         <is>
@@ -21626,35 +21635,31 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E190" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I190" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J190" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr"/>
+      <c r="M190" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P190" t="inlineStr">
@@ -21663,10 +21668,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>563741</v>
+        <v>564000</v>
       </c>
       <c r="R190" t="n">
-        <v>6704721</v>
+        <v>6704958</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -21725,7 +21730,7 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>119874661</v>
+        <v>119874659</v>
       </c>
       <c r="B191" t="n">
         <v>97930</v>
@@ -21774,10 +21779,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>563645</v>
+        <v>563746</v>
       </c>
       <c r="R191" t="n">
-        <v>6704515</v>
+        <v>6704720</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -21836,10 +21841,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>119874605</v>
+        <v>119874627</v>
       </c>
       <c r="B192" t="n">
-        <v>90351</v>
+        <v>97930</v>
       </c>
       <c r="C192" t="inlineStr">
         <is>
@@ -21848,38 +21853,54 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E192" t="n">
-        <v>3215</v>
+        <v>220787</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I192" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J192" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L192" t="inlineStr"/>
+      <c r="N192" t="inlineStr"/>
       <c r="P192" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>563929</v>
+        <v>563813</v>
       </c>
       <c r="R192" t="n">
-        <v>6704878</v>
+        <v>6704796</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -21914,12 +21935,18 @@
           <t>2024-09-20</t>
         </is>
       </c>
+      <c r="AC192" t="inlineStr">
+        <is>
+          <t>2 blomstjälkar</t>
+        </is>
+      </c>
       <c r="AD192" t="b">
         <v>0</v>
       </c>
       <c r="AE192" t="b">
         <v>0</v>
       </c>
+      <c r="AF192" t="inlineStr"/>
       <c r="AG192" t="b">
         <v>0</v>
       </c>
@@ -21938,10 +21965,10 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>119874567</v>
+        <v>119874608</v>
       </c>
       <c r="B193" t="n">
-        <v>90923</v>
+        <v>94334</v>
       </c>
       <c r="C193" t="inlineStr">
         <is>
@@ -21950,25 +21977,25 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>2062</v>
+        <v>2809</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
@@ -21978,10 +22005,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>564000</v>
+        <v>563944</v>
       </c>
       <c r="R193" t="n">
-        <v>6705011</v>
+        <v>6704880</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -22040,10 +22067,10 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>119874665</v>
+        <v>119874588</v>
       </c>
       <c r="B194" t="n">
-        <v>97930</v>
+        <v>90580</v>
       </c>
       <c r="C194" t="inlineStr">
         <is>
@@ -22052,47 +22079,38 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I194" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J194" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr"/>
       <c r="P194" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>564008</v>
+        <v>564011</v>
       </c>
       <c r="R194" t="n">
-        <v>6704979</v>
+        <v>6705060</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -22151,10 +22169,10 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>119874597</v>
+        <v>119874586</v>
       </c>
       <c r="B195" t="n">
-        <v>91512</v>
+        <v>90580</v>
       </c>
       <c r="C195" t="inlineStr">
         <is>
@@ -22163,25 +22181,25 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>4769</v>
+        <v>1202</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
@@ -22191,10 +22209,10 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>563943</v>
+        <v>564005</v>
       </c>
       <c r="R195" t="n">
-        <v>6704878</v>
+        <v>6705064</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -22360,10 +22378,10 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>119874642</v>
+        <v>119874568</v>
       </c>
       <c r="B197" t="n">
-        <v>97930</v>
+        <v>90923</v>
       </c>
       <c r="C197" t="inlineStr">
         <is>
@@ -22376,43 +22394,34 @@
         </is>
       </c>
       <c r="E197" t="n">
-        <v>220787</v>
+        <v>2062</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I197" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J197" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr"/>
       <c r="P197" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>563974</v>
+        <v>563986</v>
       </c>
       <c r="R197" t="n">
-        <v>6704953</v>
+        <v>6705032</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -22471,10 +22480,10 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>119874591</v>
+        <v>119874566</v>
       </c>
       <c r="B198" t="n">
-        <v>90580</v>
+        <v>90923</v>
       </c>
       <c r="C198" t="inlineStr">
         <is>
@@ -22483,25 +22492,25 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E198" t="n">
-        <v>1202</v>
+        <v>2062</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I198" t="inlineStr"/>
@@ -22511,10 +22520,10 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>564204</v>
+        <v>564137</v>
       </c>
       <c r="R198" t="n">
-        <v>6705194</v>
+        <v>6705070</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -22573,10 +22582,10 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>119874575</v>
+        <v>119874621</v>
       </c>
       <c r="B199" t="n">
-        <v>90580</v>
+        <v>97930</v>
       </c>
       <c r="C199" t="inlineStr">
         <is>
@@ -22585,38 +22594,47 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E199" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I199" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J199" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P199" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>563720</v>
+        <v>564283</v>
       </c>
       <c r="R199" t="n">
-        <v>6704700</v>
+        <v>6705293</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -22675,7 +22693,7 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>119874680</v>
+        <v>119874681</v>
       </c>
       <c r="B200" t="n">
         <v>5169</v>
@@ -22720,10 +22738,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>563792</v>
+        <v>563825</v>
       </c>
       <c r="R200" t="n">
-        <v>6704694</v>
+        <v>6704705</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -22782,10 +22800,10 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>119874666</v>
+        <v>119874604</v>
       </c>
       <c r="B201" t="n">
-        <v>74593</v>
+        <v>90351</v>
       </c>
       <c r="C201" t="inlineStr">
         <is>
@@ -22798,21 +22816,21 @@
         </is>
       </c>
       <c r="E201" t="n">
-        <v>6426</v>
+        <v>3215</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I201" t="inlineStr"/>
@@ -22822,10 +22840,10 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>563945</v>
+        <v>563936</v>
       </c>
       <c r="R201" t="n">
-        <v>6704877</v>
+        <v>6704867</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -22884,7 +22902,7 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>119874619</v>
+        <v>119874618</v>
       </c>
       <c r="B202" t="n">
         <v>97930</v>
@@ -22919,7 +22937,7 @@
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J202" t="inlineStr">
@@ -22933,10 +22951,10 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>564203</v>
+        <v>564168</v>
       </c>
       <c r="R202" t="n">
-        <v>6705186</v>
+        <v>6705183</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -22995,10 +23013,10 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>119874681</v>
+        <v>119874571</v>
       </c>
       <c r="B203" t="n">
-        <v>5169</v>
+        <v>90580</v>
       </c>
       <c r="C203" t="inlineStr">
         <is>
@@ -23007,43 +23025,38 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E203" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I203" t="inlineStr"/>
-      <c r="M203" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P203" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>563825</v>
+        <v>563816</v>
       </c>
       <c r="R203" t="n">
-        <v>6704705</v>
+        <v>6704792</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -23102,10 +23115,10 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>119874652</v>
+        <v>119874577</v>
       </c>
       <c r="B204" t="n">
-        <v>97930</v>
+        <v>90580</v>
       </c>
       <c r="C204" t="inlineStr">
         <is>
@@ -23114,47 +23127,38 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E204" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I204" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J204" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr"/>
       <c r="P204" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>563976</v>
+        <v>563703</v>
       </c>
       <c r="R204" t="n">
-        <v>6704966</v>
+        <v>6704669</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>
@@ -23213,10 +23217,10 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>119874649</v>
+        <v>119874666</v>
       </c>
       <c r="B205" t="n">
-        <v>97930</v>
+        <v>74593</v>
       </c>
       <c r="C205" t="inlineStr">
         <is>
@@ -23225,47 +23229,38 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E205" t="n">
-        <v>220787</v>
+        <v>6426</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I205" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J205" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr"/>
       <c r="P205" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>563765</v>
+        <v>563945</v>
       </c>
       <c r="R205" t="n">
-        <v>6704626</v>
+        <v>6704877</v>
       </c>
       <c r="S205" t="n">
         <v>10</v>
@@ -23324,7 +23319,7 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>119874641</v>
+        <v>119874617</v>
       </c>
       <c r="B206" t="n">
         <v>97930</v>
@@ -23359,7 +23354,7 @@
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J206" t="inlineStr">
@@ -23373,10 +23368,10 @@
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>563808</v>
+        <v>563833</v>
       </c>
       <c r="R206" t="n">
-        <v>6704697</v>
+        <v>6704788</v>
       </c>
       <c r="S206" t="n">
         <v>10</v>
@@ -23435,10 +23430,10 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>119874566</v>
+        <v>119874637</v>
       </c>
       <c r="B207" t="n">
-        <v>90923</v>
+        <v>97930</v>
       </c>
       <c r="C207" t="inlineStr">
         <is>
@@ -23451,34 +23446,43 @@
         </is>
       </c>
       <c r="E207" t="n">
-        <v>2062</v>
+        <v>220787</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I207" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J207" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P207" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>564137</v>
+        <v>563648</v>
       </c>
       <c r="R207" t="n">
-        <v>6705070</v>
+        <v>6704505</v>
       </c>
       <c r="S207" t="n">
         <v>10</v>
@@ -23537,10 +23541,10 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>119874668</v>
+        <v>119874661</v>
       </c>
       <c r="B208" t="n">
-        <v>74593</v>
+        <v>97930</v>
       </c>
       <c r="C208" t="inlineStr">
         <is>
@@ -23549,38 +23553,47 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E208" t="n">
-        <v>6426</v>
+        <v>220787</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I208" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J208" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P208" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>563937</v>
+        <v>563645</v>
       </c>
       <c r="R208" t="n">
-        <v>6704867</v>
+        <v>6704515</v>
       </c>
       <c r="S208" t="n">
         <v>10</v>
@@ -23639,7 +23652,7 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>119874647</v>
+        <v>119874652</v>
       </c>
       <c r="B209" t="n">
         <v>97930</v>
@@ -23674,7 +23687,7 @@
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J209" t="inlineStr">
@@ -23682,23 +23695,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K209" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L209" t="inlineStr"/>
-      <c r="N209" t="inlineStr"/>
       <c r="P209" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>564036</v>
+        <v>563976</v>
       </c>
       <c r="R209" t="n">
-        <v>6705043</v>
+        <v>6704966</v>
       </c>
       <c r="S209" t="n">
         <v>10</v>
@@ -23733,18 +23739,12 @@
           <t>2024-09-20</t>
         </is>
       </c>
-      <c r="AC209" t="inlineStr">
-        <is>
-          <t>1 blomstjälk</t>
-        </is>
-      </c>
       <c r="AD209" t="b">
         <v>0</v>
       </c>
       <c r="AE209" t="b">
         <v>0</v>
       </c>
-      <c r="AF209" t="inlineStr"/>
       <c r="AG209" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 58548-2022 artfynd.xlsx
+++ b/artfynd/A 58548-2022 artfynd.xlsx
@@ -16232,10 +16232,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>119874685</v>
+        <v>119874590</v>
       </c>
       <c r="B140" t="n">
-        <v>8421</v>
+        <v>90580</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -16244,43 +16244,38 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>106554</v>
+        <v>1202</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
-      <c r="M140" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P140" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>563845</v>
+        <v>564015</v>
       </c>
       <c r="R140" t="n">
-        <v>6704771</v>
+        <v>6705047</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -16339,10 +16334,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>119874590</v>
+        <v>119874668</v>
       </c>
       <c r="B141" t="n">
-        <v>90580</v>
+        <v>74593</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -16351,25 +16346,25 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>1202</v>
+        <v>6426</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -16379,10 +16374,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>564015</v>
+        <v>563937</v>
       </c>
       <c r="R141" t="n">
-        <v>6705047</v>
+        <v>6704867</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -16441,10 +16436,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>119874668</v>
+        <v>119874663</v>
       </c>
       <c r="B142" t="n">
-        <v>74593</v>
+        <v>97930</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -16453,38 +16448,47 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>6426</v>
+        <v>220787</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I142" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P142" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>563937</v>
+        <v>563835</v>
       </c>
       <c r="R142" t="n">
-        <v>6704867</v>
+        <v>6704743</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -16543,7 +16547,7 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>119874663</v>
+        <v>119874624</v>
       </c>
       <c r="B143" t="n">
         <v>97930</v>
@@ -16578,7 +16582,7 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
@@ -16592,10 +16596,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>563835</v>
+        <v>563734</v>
       </c>
       <c r="R143" t="n">
-        <v>6704743</v>
+        <v>6704595</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -16654,10 +16658,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>119874624</v>
+        <v>119874685</v>
       </c>
       <c r="B144" t="n">
-        <v>97930</v>
+        <v>8421</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -16666,35 +16670,31 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>220787</v>
+        <v>106554</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I144" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J144" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr"/>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P144" t="inlineStr">
@@ -16703,10 +16703,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>563734</v>
+        <v>563845</v>
       </c>
       <c r="R144" t="n">
-        <v>6704595</v>
+        <v>6704771</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -17933,10 +17933,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>119874658</v>
+        <v>119874582</v>
       </c>
       <c r="B156" t="n">
-        <v>97930</v>
+        <v>90580</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -17945,47 +17945,38 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I156" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J156" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>563749</v>
+        <v>563958</v>
       </c>
       <c r="R156" t="n">
-        <v>6704725</v>
+        <v>6704952</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -18044,10 +18035,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>119874626</v>
+        <v>119874572</v>
       </c>
       <c r="B157" t="n">
-        <v>97930</v>
+        <v>90580</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -18056,54 +18047,38 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I157" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J157" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K157" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L157" t="inlineStr"/>
-      <c r="N157" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>564019</v>
+        <v>563815</v>
       </c>
       <c r="R157" t="n">
-        <v>6704997</v>
+        <v>6704789</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -18138,18 +18113,12 @@
           <t>2024-09-20</t>
         </is>
       </c>
-      <c r="AC157" t="inlineStr">
-        <is>
-          <t>1 blomstjälk</t>
-        </is>
-      </c>
       <c r="AD157" t="b">
         <v>0</v>
       </c>
       <c r="AE157" t="b">
         <v>0</v>
       </c>
-      <c r="AF157" t="inlineStr"/>
       <c r="AG157" t="b">
         <v>0</v>
       </c>
@@ -18168,7 +18137,7 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>119874642</v>
+        <v>119874658</v>
       </c>
       <c r="B158" t="n">
         <v>97930</v>
@@ -18203,7 +18172,7 @@
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
@@ -18217,10 +18186,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>563974</v>
+        <v>563749</v>
       </c>
       <c r="R158" t="n">
-        <v>6704953</v>
+        <v>6704725</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -18279,7 +18248,7 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>119874647</v>
+        <v>119874626</v>
       </c>
       <c r="B159" t="n">
         <v>97930</v>
@@ -18314,7 +18283,7 @@
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
@@ -18335,10 +18304,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>564036</v>
+        <v>564019</v>
       </c>
       <c r="R159" t="n">
-        <v>6705043</v>
+        <v>6704997</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -18403,7 +18372,7 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>119874634</v>
+        <v>119874642</v>
       </c>
       <c r="B160" t="n">
         <v>97930</v>
@@ -18452,10 +18421,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>563712</v>
+        <v>563974</v>
       </c>
       <c r="R160" t="n">
-        <v>6704670</v>
+        <v>6704953</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -18514,10 +18483,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>119874582</v>
+        <v>119874647</v>
       </c>
       <c r="B161" t="n">
-        <v>90580</v>
+        <v>97930</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -18526,38 +18495,54 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I161" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L161" t="inlineStr"/>
+      <c r="N161" t="inlineStr"/>
       <c r="P161" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>563958</v>
+        <v>564036</v>
       </c>
       <c r="R161" t="n">
-        <v>6704952</v>
+        <v>6705043</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -18592,12 +18577,18 @@
           <t>2024-09-20</t>
         </is>
       </c>
+      <c r="AC161" t="inlineStr">
+        <is>
+          <t>1 blomstjälk</t>
+        </is>
+      </c>
       <c r="AD161" t="b">
         <v>0</v>
       </c>
       <c r="AE161" t="b">
         <v>0</v>
       </c>
+      <c r="AF161" t="inlineStr"/>
       <c r="AG161" t="b">
         <v>0</v>
       </c>
@@ -18616,10 +18607,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>119874572</v>
+        <v>119874634</v>
       </c>
       <c r="B162" t="n">
-        <v>90580</v>
+        <v>97930</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
@@ -18628,38 +18619,47 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I162" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P162" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>563815</v>
+        <v>563712</v>
       </c>
       <c r="R162" t="n">
-        <v>6704789</v>
+        <v>6704670</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -21730,10 +21730,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>119874659</v>
+        <v>119874588</v>
       </c>
       <c r="B191" t="n">
-        <v>97930</v>
+        <v>90580</v>
       </c>
       <c r="C191" t="inlineStr">
         <is>
@@ -21742,47 +21742,38 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E191" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I191" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J191" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr"/>
       <c r="P191" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>563746</v>
+        <v>564011</v>
       </c>
       <c r="R191" t="n">
-        <v>6704720</v>
+        <v>6705060</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -21841,10 +21832,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>119874627</v>
+        <v>119874586</v>
       </c>
       <c r="B192" t="n">
-        <v>97930</v>
+        <v>90580</v>
       </c>
       <c r="C192" t="inlineStr">
         <is>
@@ -21853,54 +21844,38 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E192" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I192" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J192" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K192" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L192" t="inlineStr"/>
-      <c r="N192" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr"/>
       <c r="P192" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>563813</v>
+        <v>564005</v>
       </c>
       <c r="R192" t="n">
-        <v>6704796</v>
+        <v>6705064</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -21935,18 +21910,12 @@
           <t>2024-09-20</t>
         </is>
       </c>
-      <c r="AC192" t="inlineStr">
-        <is>
-          <t>2 blomstjälkar</t>
-        </is>
-      </c>
       <c r="AD192" t="b">
         <v>0</v>
       </c>
       <c r="AE192" t="b">
         <v>0</v>
       </c>
-      <c r="AF192" t="inlineStr"/>
       <c r="AG192" t="b">
         <v>0</v>
       </c>
@@ -21965,10 +21934,10 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>119874608</v>
+        <v>119874599</v>
       </c>
       <c r="B193" t="n">
-        <v>94334</v>
+        <v>57336</v>
       </c>
       <c r="C193" t="inlineStr">
         <is>
@@ -21977,28 +21946,33 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>2809</v>
+        <v>100049</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
+      <c r="M193" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P193" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
@@ -22008,7 +21982,7 @@
         <v>563944</v>
       </c>
       <c r="R193" t="n">
-        <v>6704880</v>
+        <v>6704948</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -22067,10 +22041,10 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>119874588</v>
+        <v>119874659</v>
       </c>
       <c r="B194" t="n">
-        <v>90580</v>
+        <v>97930</v>
       </c>
       <c r="C194" t="inlineStr">
         <is>
@@ -22079,38 +22053,47 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I194" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J194" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P194" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>564011</v>
+        <v>563746</v>
       </c>
       <c r="R194" t="n">
-        <v>6705060</v>
+        <v>6704720</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -22169,10 +22152,10 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>119874586</v>
+        <v>119874627</v>
       </c>
       <c r="B195" t="n">
-        <v>90580</v>
+        <v>97930</v>
       </c>
       <c r="C195" t="inlineStr">
         <is>
@@ -22181,38 +22164,54 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I195" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J195" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L195" t="inlineStr"/>
+      <c r="N195" t="inlineStr"/>
       <c r="P195" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>564005</v>
+        <v>563813</v>
       </c>
       <c r="R195" t="n">
-        <v>6705064</v>
+        <v>6704796</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -22247,12 +22246,18 @@
           <t>2024-09-20</t>
         </is>
       </c>
+      <c r="AC195" t="inlineStr">
+        <is>
+          <t>2 blomstjälkar</t>
+        </is>
+      </c>
       <c r="AD195" t="b">
         <v>0</v>
       </c>
       <c r="AE195" t="b">
         <v>0</v>
       </c>
+      <c r="AF195" t="inlineStr"/>
       <c r="AG195" t="b">
         <v>0</v>
       </c>
@@ -22271,10 +22276,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>119874599</v>
+        <v>119874608</v>
       </c>
       <c r="B196" t="n">
-        <v>57336</v>
+        <v>94334</v>
       </c>
       <c r="C196" t="inlineStr">
         <is>
@@ -22283,33 +22288,28 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E196" t="n">
-        <v>100049</v>
+        <v>2809</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
-      <c r="M196" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P196" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
@@ -22319,7 +22319,7 @@
         <v>563944</v>
       </c>
       <c r="R196" t="n">
-        <v>6704948</v>
+        <v>6704880</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -23319,7 +23319,7 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>119874617</v>
+        <v>119874652</v>
       </c>
       <c r="B206" t="n">
         <v>97930</v>
@@ -23354,7 +23354,7 @@
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J206" t="inlineStr">
@@ -23368,10 +23368,10 @@
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>563833</v>
+        <v>563976</v>
       </c>
       <c r="R206" t="n">
-        <v>6704788</v>
+        <v>6704966</v>
       </c>
       <c r="S206" t="n">
         <v>10</v>
@@ -23430,7 +23430,7 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>119874637</v>
+        <v>119874617</v>
       </c>
       <c r="B207" t="n">
         <v>97930</v>
@@ -23465,7 +23465,7 @@
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J207" t="inlineStr">
@@ -23479,10 +23479,10 @@
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>563648</v>
+        <v>563833</v>
       </c>
       <c r="R207" t="n">
-        <v>6704505</v>
+        <v>6704788</v>
       </c>
       <c r="S207" t="n">
         <v>10</v>
@@ -23541,7 +23541,7 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>119874661</v>
+        <v>119874637</v>
       </c>
       <c r="B208" t="n">
         <v>97930</v>
@@ -23576,7 +23576,7 @@
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J208" t="inlineStr">
@@ -23590,10 +23590,10 @@
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>563645</v>
+        <v>563648</v>
       </c>
       <c r="R208" t="n">
-        <v>6704515</v>
+        <v>6704505</v>
       </c>
       <c r="S208" t="n">
         <v>10</v>
@@ -23652,7 +23652,7 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>119874652</v>
+        <v>119874661</v>
       </c>
       <c r="B209" t="n">
         <v>97930</v>
@@ -23701,10 +23701,10 @@
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>563976</v>
+        <v>563645</v>
       </c>
       <c r="R209" t="n">
-        <v>6704966</v>
+        <v>6704515</v>
       </c>
       <c r="S209" t="n">
         <v>10</v>

--- a/artfynd/A 58548-2022 artfynd.xlsx
+++ b/artfynd/A 58548-2022 artfynd.xlsx
@@ -15695,10 +15695,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>119874655</v>
+        <v>119874678</v>
       </c>
       <c r="B135" t="n">
-        <v>97930</v>
+        <v>5169</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -15707,35 +15707,31 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I135" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J135" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr"/>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P135" t="inlineStr">
@@ -15744,10 +15740,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>563757</v>
+        <v>563957</v>
       </c>
       <c r="R135" t="n">
-        <v>6704730</v>
+        <v>6704878</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -15806,7 +15802,7 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>119874628</v>
+        <v>119874661</v>
       </c>
       <c r="B136" t="n">
         <v>97930</v>
@@ -15841,7 +15837,7 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
@@ -15855,10 +15851,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>564206</v>
+        <v>563645</v>
       </c>
       <c r="R136" t="n">
-        <v>6705189</v>
+        <v>6704515</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15917,10 +15913,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>119874651</v>
+        <v>119874566</v>
       </c>
       <c r="B137" t="n">
-        <v>97930</v>
+        <v>90923</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -15933,43 +15929,34 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>220787</v>
+        <v>2062</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I137" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J137" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>564256</v>
+        <v>564137</v>
       </c>
       <c r="R137" t="n">
-        <v>6705293</v>
+        <v>6705070</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -16028,7 +16015,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>119874583</v>
+        <v>119874572</v>
       </c>
       <c r="B138" t="n">
         <v>90580</v>
@@ -16068,10 +16055,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>563996</v>
+        <v>563815</v>
       </c>
       <c r="R138" t="n">
-        <v>6705007</v>
+        <v>6704789</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -16130,7 +16117,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>119874585</v>
+        <v>119874569</v>
       </c>
       <c r="B139" t="n">
         <v>90580</v>
@@ -16170,10 +16157,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>563986</v>
+        <v>564137</v>
       </c>
       <c r="R139" t="n">
-        <v>6705041</v>
+        <v>6705071</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -16232,7 +16219,7 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>119874590</v>
+        <v>119874580</v>
       </c>
       <c r="B140" t="n">
         <v>90580</v>
@@ -16272,10 +16259,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>564015</v>
+        <v>563702</v>
       </c>
       <c r="R140" t="n">
-        <v>6705047</v>
+        <v>6704652</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -16334,10 +16321,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>119874668</v>
+        <v>119874588</v>
       </c>
       <c r="B141" t="n">
-        <v>74593</v>
+        <v>90580</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -16346,25 +16333,25 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6426</v>
+        <v>1202</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -16374,10 +16361,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>563937</v>
+        <v>564011</v>
       </c>
       <c r="R141" t="n">
-        <v>6704867</v>
+        <v>6705060</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -16436,7 +16423,7 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>119874663</v>
+        <v>119874619</v>
       </c>
       <c r="B142" t="n">
         <v>97930</v>
@@ -16471,7 +16458,7 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
@@ -16485,10 +16472,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>563835</v>
+        <v>564203</v>
       </c>
       <c r="R142" t="n">
-        <v>6704743</v>
+        <v>6705186</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -16547,7 +16534,7 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>119874624</v>
+        <v>119874616</v>
       </c>
       <c r="B143" t="n">
         <v>97930</v>
@@ -16582,7 +16569,7 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
@@ -16596,10 +16583,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>563734</v>
+        <v>563993</v>
       </c>
       <c r="R143" t="n">
-        <v>6704595</v>
+        <v>6705035</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -16658,10 +16645,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>119874685</v>
+        <v>119874680</v>
       </c>
       <c r="B144" t="n">
-        <v>8421</v>
+        <v>5169</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -16674,21 +16661,21 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>106554</v>
+        <v>100526</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -16703,10 +16690,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>563845</v>
+        <v>563792</v>
       </c>
       <c r="R144" t="n">
-        <v>6704771</v>
+        <v>6704694</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -16765,10 +16752,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>119874606</v>
+        <v>119874627</v>
       </c>
       <c r="B145" t="n">
-        <v>90864</v>
+        <v>97930</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -16777,38 +16764,54 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I145" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L145" t="inlineStr"/>
+      <c r="N145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>563784</v>
+        <v>563813</v>
       </c>
       <c r="R145" t="n">
-        <v>6704721</v>
+        <v>6704796</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -16845,7 +16848,7 @@
       </c>
       <c r="AC145" t="inlineStr">
         <is>
-          <t>Äldre fruktkropp</t>
+          <t>2 blomstjälkar</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -16854,6 +16857,7 @@
       <c r="AE145" t="b">
         <v>0</v>
       </c>
+      <c r="AF145" t="inlineStr"/>
       <c r="AG145" t="b">
         <v>0</v>
       </c>
@@ -16872,10 +16876,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>119874607</v>
+        <v>119874581</v>
       </c>
       <c r="B146" t="n">
-        <v>90864</v>
+        <v>90580</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -16888,21 +16892,21 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -16912,10 +16916,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>563821</v>
+        <v>563792</v>
       </c>
       <c r="R146" t="n">
-        <v>6704817</v>
+        <v>6704700</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16974,10 +16978,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>119874569</v>
+        <v>119874596</v>
       </c>
       <c r="B147" t="n">
-        <v>90580</v>
+        <v>57473</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -16990,34 +16994,46 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I147" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr"/>
+      <c r="L147" t="inlineStr"/>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>564137</v>
+        <v>563633</v>
       </c>
       <c r="R147" t="n">
-        <v>6705071</v>
+        <v>6704498</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -17076,7 +17092,7 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>119874639</v>
+        <v>119874628</v>
       </c>
       <c r="B148" t="n">
         <v>97930</v>
@@ -17125,10 +17141,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>563718</v>
+        <v>564206</v>
       </c>
       <c r="R148" t="n">
-        <v>6704563</v>
+        <v>6705189</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -17187,7 +17203,7 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>119874613</v>
+        <v>119874659</v>
       </c>
       <c r="B149" t="n">
         <v>97930</v>
@@ -17222,7 +17238,7 @@
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
@@ -17236,10 +17252,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>563794</v>
+        <v>563746</v>
       </c>
       <c r="R149" t="n">
-        <v>6704750</v>
+        <v>6704720</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -17298,10 +17314,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>119874623</v>
+        <v>119874606</v>
       </c>
       <c r="B150" t="n">
-        <v>97930</v>
+        <v>90864</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -17310,47 +17326,38 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I150" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J150" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>563637</v>
+        <v>563784</v>
       </c>
       <c r="R150" t="n">
-        <v>6704477</v>
+        <v>6704721</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -17383,6 +17390,11 @@
       <c r="AA150" t="inlineStr">
         <is>
           <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AC150" t="inlineStr">
+        <is>
+          <t>Äldre fruktkropp</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -17409,10 +17421,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>119874641</v>
+        <v>119874666</v>
       </c>
       <c r="B151" t="n">
-        <v>97930</v>
+        <v>74593</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -17421,47 +17433,38 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>220787</v>
+        <v>6426</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I151" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J151" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>563808</v>
+        <v>563945</v>
       </c>
       <c r="R151" t="n">
-        <v>6704697</v>
+        <v>6704877</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -17520,7 +17523,7 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>119874576</v>
+        <v>119874591</v>
       </c>
       <c r="B152" t="n">
         <v>90580</v>
@@ -17560,10 +17563,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>563718</v>
+        <v>564204</v>
       </c>
       <c r="R152" t="n">
-        <v>6704695</v>
+        <v>6705194</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -17622,7 +17625,7 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>119874581</v>
+        <v>119874590</v>
       </c>
       <c r="B153" t="n">
         <v>90580</v>
@@ -17662,10 +17665,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>563792</v>
+        <v>564015</v>
       </c>
       <c r="R153" t="n">
-        <v>6704700</v>
+        <v>6705047</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -17724,10 +17727,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>119874677</v>
+        <v>119874685</v>
       </c>
       <c r="B154" t="n">
-        <v>93953</v>
+        <v>8421</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -17740,34 +17743,39 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>2383</v>
+        <v>106554</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Bågpraktmossa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Plagiomnium medium</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Bruch &amp; Schimp.) T.J.Kop.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
+      <c r="M154" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P154" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>563925</v>
+        <v>563845</v>
       </c>
       <c r="R154" t="n">
-        <v>6704880</v>
+        <v>6704771</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -17826,10 +17834,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>119874678</v>
+        <v>119874646</v>
       </c>
       <c r="B155" t="n">
-        <v>5169</v>
+        <v>97930</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -17838,31 +17846,35 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I155" t="inlineStr"/>
-      <c r="M155" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P155" t="inlineStr">
@@ -17871,10 +17883,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>563957</v>
+        <v>563995</v>
       </c>
       <c r="R155" t="n">
-        <v>6704878</v>
+        <v>6704966</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -17933,10 +17945,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>119874582</v>
+        <v>119874651</v>
       </c>
       <c r="B156" t="n">
-        <v>90580</v>
+        <v>97930</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -17945,38 +17957,47 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I156" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P156" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>563958</v>
+        <v>564256</v>
       </c>
       <c r="R156" t="n">
-        <v>6704952</v>
+        <v>6705293</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -18035,10 +18056,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>119874572</v>
+        <v>119874658</v>
       </c>
       <c r="B157" t="n">
-        <v>90580</v>
+        <v>97930</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -18047,38 +18068,47 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I157" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P157" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>563815</v>
+        <v>563749</v>
       </c>
       <c r="R157" t="n">
-        <v>6704789</v>
+        <v>6704725</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -18137,7 +18167,7 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>119874658</v>
+        <v>119874632</v>
       </c>
       <c r="B158" t="n">
         <v>97930</v>
@@ -18172,7 +18202,7 @@
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
@@ -18186,10 +18216,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>563749</v>
+        <v>563770</v>
       </c>
       <c r="R158" t="n">
-        <v>6704725</v>
+        <v>6704729</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -18248,7 +18278,7 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>119874626</v>
+        <v>119874634</v>
       </c>
       <c r="B159" t="n">
         <v>97930</v>
@@ -18291,23 +18321,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K159" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L159" t="inlineStr"/>
-      <c r="N159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>564019</v>
+        <v>563712</v>
       </c>
       <c r="R159" t="n">
-        <v>6704997</v>
+        <v>6704670</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -18342,18 +18365,12 @@
           <t>2024-09-20</t>
         </is>
       </c>
-      <c r="AC159" t="inlineStr">
-        <is>
-          <t>1 blomstjälk</t>
-        </is>
-      </c>
       <c r="AD159" t="b">
         <v>0</v>
       </c>
       <c r="AE159" t="b">
         <v>0</v>
       </c>
-      <c r="AF159" t="inlineStr"/>
       <c r="AG159" t="b">
         <v>0</v>
       </c>
@@ -18372,10 +18389,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>119874642</v>
+        <v>119874609</v>
       </c>
       <c r="B160" t="n">
-        <v>97930</v>
+        <v>90972</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -18384,47 +18401,33 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F160" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I160" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J160" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr"/>
       <c r="P160" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>563974</v>
+        <v>564083</v>
       </c>
       <c r="R160" t="n">
-        <v>6704953</v>
+        <v>6705090</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -18483,10 +18486,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>119874647</v>
+        <v>119874567</v>
       </c>
       <c r="B161" t="n">
-        <v>97930</v>
+        <v>90923</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -18499,50 +18502,34 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>220787</v>
+        <v>2062</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I161" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J161" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K161" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L161" t="inlineStr"/>
-      <c r="N161" t="inlineStr"/>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr"/>
       <c r="P161" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>564036</v>
+        <v>564000</v>
       </c>
       <c r="R161" t="n">
-        <v>6705043</v>
+        <v>6705011</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -18577,18 +18564,12 @@
           <t>2024-09-20</t>
         </is>
       </c>
-      <c r="AC161" t="inlineStr">
-        <is>
-          <t>1 blomstjälk</t>
-        </is>
-      </c>
       <c r="AD161" t="b">
         <v>0</v>
       </c>
       <c r="AE161" t="b">
         <v>0</v>
       </c>
-      <c r="AF161" t="inlineStr"/>
       <c r="AG161" t="b">
         <v>0</v>
       </c>
@@ -18607,10 +18588,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>119874634</v>
+        <v>119874586</v>
       </c>
       <c r="B162" t="n">
-        <v>97930</v>
+        <v>90580</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
@@ -18619,47 +18600,38 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I162" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J162" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr"/>
       <c r="P162" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>563712</v>
+        <v>564005</v>
       </c>
       <c r="R162" t="n">
-        <v>6704670</v>
+        <v>6705064</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -18718,7 +18690,7 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>119874630</v>
+        <v>119874635</v>
       </c>
       <c r="B163" t="n">
         <v>97930</v>
@@ -18767,10 +18739,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>563815</v>
+        <v>563705</v>
       </c>
       <c r="R163" t="n">
-        <v>6704815</v>
+        <v>6704657</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -18829,7 +18801,7 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>119874665</v>
+        <v>119874637</v>
       </c>
       <c r="B164" t="n">
         <v>97930</v>
@@ -18864,7 +18836,7 @@
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
@@ -18878,10 +18850,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>564008</v>
+        <v>563648</v>
       </c>
       <c r="R164" t="n">
-        <v>6704979</v>
+        <v>6704505</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -18940,10 +18912,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>119874574</v>
+        <v>119874663</v>
       </c>
       <c r="B165" t="n">
-        <v>90580</v>
+        <v>97930</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -18952,38 +18924,47 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I165" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P165" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>563796</v>
+        <v>563835</v>
       </c>
       <c r="R165" t="n">
-        <v>6704785</v>
+        <v>6704743</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -19042,10 +19023,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>119874684</v>
+        <v>119874624</v>
       </c>
       <c r="B166" t="n">
-        <v>100194</v>
+        <v>97930</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -19054,38 +19035,47 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I166" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P166" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>563956</v>
+        <v>563734</v>
       </c>
       <c r="R166" t="n">
-        <v>6704876</v>
+        <v>6704595</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -19144,7 +19134,7 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>119874612</v>
+        <v>119874623</v>
       </c>
       <c r="B167" t="n">
         <v>97930</v>
@@ -19179,7 +19169,7 @@
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
@@ -19187,23 +19177,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K167" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L167" t="inlineStr"/>
-      <c r="N167" t="inlineStr"/>
       <c r="P167" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>564201</v>
+        <v>563637</v>
       </c>
       <c r="R167" t="n">
-        <v>6705191</v>
+        <v>6704477</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -19238,18 +19221,12 @@
           <t>2024-09-20</t>
         </is>
       </c>
-      <c r="AC167" t="inlineStr">
-        <is>
-          <t>1 blomstjälk</t>
-        </is>
-      </c>
       <c r="AD167" t="b">
         <v>0</v>
       </c>
       <c r="AE167" t="b">
         <v>0</v>
       </c>
-      <c r="AF167" t="inlineStr"/>
       <c r="AG167" t="b">
         <v>0</v>
       </c>
@@ -19268,10 +19245,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>119874616</v>
+        <v>119874568</v>
       </c>
       <c r="B168" t="n">
-        <v>97930</v>
+        <v>90923</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
@@ -19284,43 +19261,34 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>220787</v>
+        <v>2062</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I168" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J168" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr"/>
       <c r="P168" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>563993</v>
+        <v>563986</v>
       </c>
       <c r="R168" t="n">
-        <v>6705035</v>
+        <v>6705032</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -19379,10 +19347,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>119874632</v>
+        <v>119874577</v>
       </c>
       <c r="B169" t="n">
-        <v>97930</v>
+        <v>90580</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
@@ -19391,47 +19359,38 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I169" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J169" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr"/>
       <c r="P169" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>563770</v>
+        <v>563703</v>
       </c>
       <c r="R169" t="n">
-        <v>6704729</v>
+        <v>6704669</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -19490,10 +19449,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>119874644</v>
+        <v>119874605</v>
       </c>
       <c r="B170" t="n">
-        <v>97930</v>
+        <v>90351</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
@@ -19502,47 +19461,38 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>220787</v>
+        <v>3215</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I170" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J170" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr"/>
       <c r="P170" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>563984</v>
+        <v>563929</v>
       </c>
       <c r="R170" t="n">
-        <v>6704957</v>
+        <v>6704878</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -19601,10 +19551,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>119874680</v>
+        <v>119874575</v>
       </c>
       <c r="B171" t="n">
-        <v>5169</v>
+        <v>90580</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
@@ -19613,43 +19563,38 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
-      <c r="M171" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P171" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>563792</v>
+        <v>563720</v>
       </c>
       <c r="R171" t="n">
-        <v>6704694</v>
+        <v>6704700</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -19708,7 +19653,7 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>119874575</v>
+        <v>119874571</v>
       </c>
       <c r="B172" t="n">
         <v>90580</v>
@@ -19748,10 +19693,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>563720</v>
+        <v>563816</v>
       </c>
       <c r="R172" t="n">
-        <v>6704700</v>
+        <v>6704792</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -19810,10 +19755,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>119874605</v>
+        <v>119874599</v>
       </c>
       <c r="B173" t="n">
-        <v>90351</v>
+        <v>57336</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
@@ -19822,38 +19767,43 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>3215</v>
+        <v>100049</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
+      <c r="M173" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P173" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>563929</v>
+        <v>563944</v>
       </c>
       <c r="R173" t="n">
-        <v>6704878</v>
+        <v>6704948</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -19912,10 +19862,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>119874625</v>
+        <v>119874593</v>
       </c>
       <c r="B174" t="n">
-        <v>97930</v>
+        <v>90580</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
@@ -19924,47 +19874,38 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I174" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J174" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr"/>
       <c r="P174" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>564201</v>
+        <v>563710</v>
       </c>
       <c r="R174" t="n">
-        <v>6705184</v>
+        <v>6704663</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -20023,10 +19964,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>119874573</v>
+        <v>119874647</v>
       </c>
       <c r="B175" t="n">
-        <v>90580</v>
+        <v>97930</v>
       </c>
       <c r="C175" t="inlineStr">
         <is>
@@ -20035,38 +19976,54 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I175" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L175" t="inlineStr"/>
+      <c r="N175" t="inlineStr"/>
       <c r="P175" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>563794</v>
+        <v>564036</v>
       </c>
       <c r="R175" t="n">
-        <v>6704792</v>
+        <v>6705043</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -20101,12 +20058,18 @@
           <t>2024-09-20</t>
         </is>
       </c>
+      <c r="AC175" t="inlineStr">
+        <is>
+          <t>1 blomstjälk</t>
+        </is>
+      </c>
       <c r="AD175" t="b">
         <v>0</v>
       </c>
       <c r="AE175" t="b">
         <v>0</v>
       </c>
+      <c r="AF175" t="inlineStr"/>
       <c r="AG175" t="b">
         <v>0</v>
       </c>
@@ -20125,7 +20088,7 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>119874622</v>
+        <v>119874618</v>
       </c>
       <c r="B176" t="n">
         <v>97930</v>
@@ -20160,7 +20123,7 @@
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
@@ -20174,10 +20137,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>563711</v>
+        <v>564168</v>
       </c>
       <c r="R176" t="n">
-        <v>6704677</v>
+        <v>6705183</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -20236,10 +20199,10 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>119874609</v>
+        <v>119874655</v>
       </c>
       <c r="B177" t="n">
-        <v>90972</v>
+        <v>97930</v>
       </c>
       <c r="C177" t="inlineStr">
         <is>
@@ -20248,33 +20211,47 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>6040186</v>
+        <v>220787</v>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
-        </is>
-      </c>
-      <c r="I177" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P177" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>564083</v>
+        <v>563757</v>
       </c>
       <c r="R177" t="n">
-        <v>6705090</v>
+        <v>6704730</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -20333,10 +20310,10 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>119874593</v>
+        <v>119874682</v>
       </c>
       <c r="B178" t="n">
-        <v>90580</v>
+        <v>5169</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>
@@ -20345,38 +20322,43 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
+      <c r="M178" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P178" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>563710</v>
+        <v>564000</v>
       </c>
       <c r="R178" t="n">
-        <v>6704663</v>
+        <v>6704958</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -20435,10 +20417,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>119874597</v>
+        <v>119874612</v>
       </c>
       <c r="B179" t="n">
-        <v>91512</v>
+        <v>97930</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
@@ -20447,38 +20429,54 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>4769</v>
+        <v>220787</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I179" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J179" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L179" t="inlineStr"/>
+      <c r="N179" t="inlineStr"/>
       <c r="P179" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>563943</v>
+        <v>564201</v>
       </c>
       <c r="R179" t="n">
-        <v>6704878</v>
+        <v>6705191</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -20513,12 +20511,18 @@
           <t>2024-09-20</t>
         </is>
       </c>
+      <c r="AC179" t="inlineStr">
+        <is>
+          <t>1 blomstjälk</t>
+        </is>
+      </c>
       <c r="AD179" t="b">
         <v>0</v>
       </c>
       <c r="AE179" t="b">
         <v>0</v>
       </c>
+      <c r="AF179" t="inlineStr"/>
       <c r="AG179" t="b">
         <v>0</v>
       </c>
@@ -20537,7 +20541,7 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>119874646</v>
+        <v>119874625</v>
       </c>
       <c r="B180" t="n">
         <v>97930</v>
@@ -20572,7 +20576,7 @@
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
@@ -20586,10 +20590,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>563995</v>
+        <v>564201</v>
       </c>
       <c r="R180" t="n">
-        <v>6704966</v>
+        <v>6705184</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -20648,7 +20652,7 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>119874619</v>
+        <v>119874641</v>
       </c>
       <c r="B181" t="n">
         <v>97930</v>
@@ -20683,7 +20687,7 @@
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
@@ -20697,10 +20701,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>564203</v>
+        <v>563808</v>
       </c>
       <c r="R181" t="n">
-        <v>6705186</v>
+        <v>6704697</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -20759,10 +20763,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>119874649</v>
+        <v>119874576</v>
       </c>
       <c r="B182" t="n">
-        <v>97930</v>
+        <v>90580</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
@@ -20771,47 +20775,38 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I182" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J182" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr"/>
       <c r="P182" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>563765</v>
+        <v>563718</v>
       </c>
       <c r="R182" t="n">
-        <v>6704626</v>
+        <v>6704695</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -20870,10 +20865,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>119874633</v>
+        <v>119874585</v>
       </c>
       <c r="B183" t="n">
-        <v>97930</v>
+        <v>90580</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
@@ -20882,47 +20877,38 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I183" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J183" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr"/>
       <c r="P183" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>563741</v>
+        <v>563986</v>
       </c>
       <c r="R183" t="n">
-        <v>6704721</v>
+        <v>6705041</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -20981,7 +20967,7 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>119874635</v>
+        <v>119874615</v>
       </c>
       <c r="B184" t="n">
         <v>97930</v>
@@ -21016,7 +21002,7 @@
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
@@ -21030,10 +21016,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>563705</v>
+        <v>563748</v>
       </c>
       <c r="R184" t="n">
-        <v>6704657</v>
+        <v>6704608</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -21092,10 +21078,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>119874567</v>
+        <v>119874608</v>
       </c>
       <c r="B185" t="n">
-        <v>90923</v>
+        <v>94334</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
@@ -21104,25 +21090,25 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>2062</v>
+        <v>2809</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
@@ -21132,10 +21118,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>564000</v>
+        <v>563944</v>
       </c>
       <c r="R185" t="n">
-        <v>6705011</v>
+        <v>6704880</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -21194,10 +21180,10 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>119874580</v>
+        <v>119874681</v>
       </c>
       <c r="B186" t="n">
-        <v>90580</v>
+        <v>5169</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
@@ -21206,38 +21192,43 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
+      <c r="M186" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P186" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>563702</v>
+        <v>563825</v>
       </c>
       <c r="R186" t="n">
-        <v>6704652</v>
+        <v>6704705</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -21296,10 +21287,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>119874615</v>
+        <v>119874573</v>
       </c>
       <c r="B187" t="n">
-        <v>97930</v>
+        <v>90580</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
@@ -21308,47 +21299,38 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I187" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J187" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr"/>
       <c r="P187" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>563748</v>
+        <v>563794</v>
       </c>
       <c r="R187" t="n">
-        <v>6704608</v>
+        <v>6704792</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -21407,10 +21389,10 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>119874596</v>
+        <v>119874604</v>
       </c>
       <c r="B188" t="n">
-        <v>57473</v>
+        <v>90351</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
@@ -21419,50 +21401,38 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>103021</v>
+        <v>3215</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I188" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K188" t="inlineStr"/>
-      <c r="L188" t="inlineStr"/>
-      <c r="M188" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N188" t="inlineStr"/>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr"/>
       <c r="P188" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>563633</v>
+        <v>563936</v>
       </c>
       <c r="R188" t="n">
-        <v>6704498</v>
+        <v>6704867</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -21521,10 +21491,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>119874591</v>
+        <v>119874633</v>
       </c>
       <c r="B189" t="n">
-        <v>90580</v>
+        <v>97930</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
@@ -21533,38 +21503,47 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E189" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I189" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J189" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P189" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>564204</v>
+        <v>563741</v>
       </c>
       <c r="R189" t="n">
-        <v>6705194</v>
+        <v>6704721</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -21623,10 +21602,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>119874682</v>
+        <v>119874649</v>
       </c>
       <c r="B190" t="n">
-        <v>5169</v>
+        <v>97930</v>
       </c>
       <c r="C190" t="inlineStr">
         <is>
@@ -21635,31 +21614,35 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E190" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I190" t="inlineStr"/>
-      <c r="M190" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J190" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P190" t="inlineStr">
@@ -21668,10 +21651,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>564000</v>
+        <v>563765</v>
       </c>
       <c r="R190" t="n">
-        <v>6704958</v>
+        <v>6704626</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -21730,10 +21713,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>119874588</v>
+        <v>119874630</v>
       </c>
       <c r="B191" t="n">
-        <v>90580</v>
+        <v>97930</v>
       </c>
       <c r="C191" t="inlineStr">
         <is>
@@ -21742,38 +21725,47 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E191" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I191" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J191" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P191" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>564011</v>
+        <v>563815</v>
       </c>
       <c r="R191" t="n">
-        <v>6705060</v>
+        <v>6704815</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -21832,10 +21824,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>119874586</v>
+        <v>119874644</v>
       </c>
       <c r="B192" t="n">
-        <v>90580</v>
+        <v>97930</v>
       </c>
       <c r="C192" t="inlineStr">
         <is>
@@ -21844,38 +21836,47 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E192" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I192" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J192" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P192" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>564005</v>
+        <v>563984</v>
       </c>
       <c r="R192" t="n">
-        <v>6705064</v>
+        <v>6704957</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -21934,10 +21935,10 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>119874599</v>
+        <v>119874684</v>
       </c>
       <c r="B193" t="n">
-        <v>57336</v>
+        <v>100194</v>
       </c>
       <c r="C193" t="inlineStr">
         <is>
@@ -21946,43 +21947,38 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
-      <c r="M193" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P193" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>563944</v>
+        <v>563956</v>
       </c>
       <c r="R193" t="n">
-        <v>6704948</v>
+        <v>6704876</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -22041,7 +22037,7 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>119874659</v>
+        <v>119874626</v>
       </c>
       <c r="B194" t="n">
         <v>97930</v>
@@ -22076,7 +22072,7 @@
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
@@ -22084,16 +22080,23 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L194" t="inlineStr"/>
+      <c r="N194" t="inlineStr"/>
       <c r="P194" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>563746</v>
+        <v>564019</v>
       </c>
       <c r="R194" t="n">
-        <v>6704720</v>
+        <v>6704997</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -22128,12 +22131,18 @@
           <t>2024-09-20</t>
         </is>
       </c>
+      <c r="AC194" t="inlineStr">
+        <is>
+          <t>1 blomstjälk</t>
+        </is>
+      </c>
       <c r="AD194" t="b">
         <v>0</v>
       </c>
       <c r="AE194" t="b">
         <v>0</v>
       </c>
+      <c r="AF194" t="inlineStr"/>
       <c r="AG194" t="b">
         <v>0</v>
       </c>
@@ -22152,7 +22161,7 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>119874627</v>
+        <v>119874621</v>
       </c>
       <c r="B195" t="n">
         <v>97930</v>
@@ -22187,7 +22196,7 @@
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J195" t="inlineStr">
@@ -22195,23 +22204,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K195" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L195" t="inlineStr"/>
-      <c r="N195" t="inlineStr"/>
       <c r="P195" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>563813</v>
+        <v>564283</v>
       </c>
       <c r="R195" t="n">
-        <v>6704796</v>
+        <v>6705293</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -22246,18 +22248,12 @@
           <t>2024-09-20</t>
         </is>
       </c>
-      <c r="AC195" t="inlineStr">
-        <is>
-          <t>2 blomstjälkar</t>
-        </is>
-      </c>
       <c r="AD195" t="b">
         <v>0</v>
       </c>
       <c r="AE195" t="b">
         <v>0</v>
       </c>
-      <c r="AF195" t="inlineStr"/>
       <c r="AG195" t="b">
         <v>0</v>
       </c>
@@ -22276,10 +22272,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>119874608</v>
+        <v>119874639</v>
       </c>
       <c r="B196" t="n">
-        <v>94334</v>
+        <v>97930</v>
       </c>
       <c r="C196" t="inlineStr">
         <is>
@@ -22288,38 +22284,47 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E196" t="n">
-        <v>2809</v>
+        <v>220787</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
-        </is>
-      </c>
-      <c r="I196" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J196" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P196" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>563944</v>
+        <v>563718</v>
       </c>
       <c r="R196" t="n">
-        <v>6704880</v>
+        <v>6704563</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -22378,10 +22383,10 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>119874568</v>
+        <v>119874668</v>
       </c>
       <c r="B197" t="n">
-        <v>90923</v>
+        <v>74593</v>
       </c>
       <c r="C197" t="inlineStr">
         <is>
@@ -22390,25 +22395,25 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>2062</v>
+        <v>6426</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
@@ -22418,10 +22423,10 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>563986</v>
+        <v>563937</v>
       </c>
       <c r="R197" t="n">
-        <v>6705032</v>
+        <v>6704867</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -22480,10 +22485,10 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>119874566</v>
+        <v>119874607</v>
       </c>
       <c r="B198" t="n">
-        <v>90923</v>
+        <v>90864</v>
       </c>
       <c r="C198" t="inlineStr">
         <is>
@@ -22492,25 +22497,25 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E198" t="n">
-        <v>2062</v>
+        <v>658</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I198" t="inlineStr"/>
@@ -22520,10 +22525,10 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>564137</v>
+        <v>563821</v>
       </c>
       <c r="R198" t="n">
-        <v>6705070</v>
+        <v>6704817</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -22582,7 +22587,7 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>119874621</v>
+        <v>119874665</v>
       </c>
       <c r="B199" t="n">
         <v>97930</v>
@@ -22617,7 +22622,7 @@
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
@@ -22631,10 +22636,10 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>564283</v>
+        <v>564008</v>
       </c>
       <c r="R199" t="n">
-        <v>6705293</v>
+        <v>6704979</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -22693,10 +22698,10 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>119874681</v>
+        <v>119874642</v>
       </c>
       <c r="B200" t="n">
-        <v>5169</v>
+        <v>97930</v>
       </c>
       <c r="C200" t="inlineStr">
         <is>
@@ -22705,31 +22710,35 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I200" t="inlineStr"/>
-      <c r="M200" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J200" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P200" t="inlineStr">
@@ -22738,10 +22747,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>563825</v>
+        <v>563974</v>
       </c>
       <c r="R200" t="n">
-        <v>6704705</v>
+        <v>6704953</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -22800,10 +22809,10 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>119874604</v>
+        <v>119874652</v>
       </c>
       <c r="B201" t="n">
-        <v>90351</v>
+        <v>97930</v>
       </c>
       <c r="C201" t="inlineStr">
         <is>
@@ -22812,38 +22821,47 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E201" t="n">
-        <v>3215</v>
+        <v>220787</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I201" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P201" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>563936</v>
+        <v>563976</v>
       </c>
       <c r="R201" t="n">
-        <v>6704867</v>
+        <v>6704966</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -22902,7 +22920,7 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>119874618</v>
+        <v>119874622</v>
       </c>
       <c r="B202" t="n">
         <v>97930</v>
@@ -22937,7 +22955,7 @@
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J202" t="inlineStr">
@@ -22951,10 +22969,10 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>564168</v>
+        <v>563711</v>
       </c>
       <c r="R202" t="n">
-        <v>6705183</v>
+        <v>6704677</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -23013,10 +23031,10 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>119874571</v>
+        <v>119874617</v>
       </c>
       <c r="B203" t="n">
-        <v>90580</v>
+        <v>97930</v>
       </c>
       <c r="C203" t="inlineStr">
         <is>
@@ -23025,38 +23043,47 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E203" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I203" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J203" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P203" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>563816</v>
+        <v>563833</v>
       </c>
       <c r="R203" t="n">
-        <v>6704792</v>
+        <v>6704788</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -23115,10 +23142,10 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>119874577</v>
+        <v>119874613</v>
       </c>
       <c r="B204" t="n">
-        <v>90580</v>
+        <v>97930</v>
       </c>
       <c r="C204" t="inlineStr">
         <is>
@@ -23127,38 +23154,47 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E204" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I204" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J204" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P204" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>563703</v>
+        <v>563794</v>
       </c>
       <c r="R204" t="n">
-        <v>6704669</v>
+        <v>6704750</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>
@@ -23217,10 +23253,10 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>119874666</v>
+        <v>119874677</v>
       </c>
       <c r="B205" t="n">
-        <v>74593</v>
+        <v>93953</v>
       </c>
       <c r="C205" t="inlineStr">
         <is>
@@ -23233,21 +23269,21 @@
         </is>
       </c>
       <c r="E205" t="n">
-        <v>6426</v>
+        <v>2383</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Bågpraktmossa</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Plagiomnium medium</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Bruch &amp; Schimp.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I205" t="inlineStr"/>
@@ -23257,10 +23293,10 @@
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>563945</v>
+        <v>563925</v>
       </c>
       <c r="R205" t="n">
-        <v>6704877</v>
+        <v>6704880</v>
       </c>
       <c r="S205" t="n">
         <v>10</v>
@@ -23319,10 +23355,10 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>119874652</v>
+        <v>119874583</v>
       </c>
       <c r="B206" t="n">
-        <v>97930</v>
+        <v>90580</v>
       </c>
       <c r="C206" t="inlineStr">
         <is>
@@ -23331,47 +23367,38 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E206" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I206" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J206" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr"/>
       <c r="P206" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>563976</v>
+        <v>563996</v>
       </c>
       <c r="R206" t="n">
-        <v>6704966</v>
+        <v>6705007</v>
       </c>
       <c r="S206" t="n">
         <v>10</v>
@@ -23430,10 +23457,10 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>119874617</v>
+        <v>119874582</v>
       </c>
       <c r="B207" t="n">
-        <v>97930</v>
+        <v>90580</v>
       </c>
       <c r="C207" t="inlineStr">
         <is>
@@ -23442,47 +23469,38 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E207" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I207" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J207" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr"/>
       <c r="P207" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>563833</v>
+        <v>563958</v>
       </c>
       <c r="R207" t="n">
-        <v>6704788</v>
+        <v>6704952</v>
       </c>
       <c r="S207" t="n">
         <v>10</v>
@@ -23541,10 +23559,10 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>119874637</v>
+        <v>119874574</v>
       </c>
       <c r="B208" t="n">
-        <v>97930</v>
+        <v>90580</v>
       </c>
       <c r="C208" t="inlineStr">
         <is>
@@ -23553,47 +23571,38 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E208" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I208" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J208" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr"/>
       <c r="P208" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>563648</v>
+        <v>563796</v>
       </c>
       <c r="R208" t="n">
-        <v>6704505</v>
+        <v>6704785</v>
       </c>
       <c r="S208" t="n">
         <v>10</v>
@@ -23652,10 +23661,10 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>119874661</v>
+        <v>119874597</v>
       </c>
       <c r="B209" t="n">
-        <v>97930</v>
+        <v>91512</v>
       </c>
       <c r="C209" t="inlineStr">
         <is>
@@ -23664,47 +23673,38 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E209" t="n">
-        <v>220787</v>
+        <v>4769</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I209" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J209" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Scop.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr"/>
       <c r="P209" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>563645</v>
+        <v>563943</v>
       </c>
       <c r="R209" t="n">
-        <v>6704515</v>
+        <v>6704878</v>
       </c>
       <c r="S209" t="n">
         <v>10</v>

--- a/artfynd/A 58548-2022 artfynd.xlsx
+++ b/artfynd/A 58548-2022 artfynd.xlsx
@@ -17625,10 +17625,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>119874590</v>
+        <v>119874646</v>
       </c>
       <c r="B153" t="n">
-        <v>90580</v>
+        <v>97930</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -17637,38 +17637,47 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I153" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P153" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>564015</v>
+        <v>563995</v>
       </c>
       <c r="R153" t="n">
-        <v>6705047</v>
+        <v>6704966</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -17727,10 +17736,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>119874685</v>
+        <v>119874651</v>
       </c>
       <c r="B154" t="n">
-        <v>8421</v>
+        <v>97930</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -17739,31 +17748,35 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>106554</v>
+        <v>220787</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I154" t="inlineStr"/>
-      <c r="M154" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P154" t="inlineStr">
@@ -17772,10 +17785,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>563845</v>
+        <v>564256</v>
       </c>
       <c r="R154" t="n">
-        <v>6704771</v>
+        <v>6705293</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -17834,10 +17847,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>119874646</v>
+        <v>119874590</v>
       </c>
       <c r="B155" t="n">
-        <v>97930</v>
+        <v>90580</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -17846,47 +17859,38 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I155" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J155" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>563995</v>
+        <v>564015</v>
       </c>
       <c r="R155" t="n">
-        <v>6704966</v>
+        <v>6705047</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -17945,10 +17949,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>119874651</v>
+        <v>119874685</v>
       </c>
       <c r="B156" t="n">
-        <v>97930</v>
+        <v>8421</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -17957,35 +17961,31 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>220787</v>
+        <v>106554</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I156" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J156" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr"/>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P156" t="inlineStr">
@@ -17994,10 +17994,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>564256</v>
+        <v>563845</v>
       </c>
       <c r="R156" t="n">
-        <v>6705293</v>
+        <v>6704771</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -18801,10 +18801,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>119874637</v>
+        <v>119874568</v>
       </c>
       <c r="B164" t="n">
-        <v>97930</v>
+        <v>90923</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -18817,43 +18817,34 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>220787</v>
+        <v>2062</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I164" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J164" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>563648</v>
+        <v>563986</v>
       </c>
       <c r="R164" t="n">
-        <v>6704505</v>
+        <v>6705032</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -18912,10 +18903,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>119874663</v>
+        <v>119874577</v>
       </c>
       <c r="B165" t="n">
-        <v>97930</v>
+        <v>90580</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -18924,47 +18915,38 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I165" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J165" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>563835</v>
+        <v>563703</v>
       </c>
       <c r="R165" t="n">
-        <v>6704743</v>
+        <v>6704669</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -19023,10 +19005,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>119874624</v>
+        <v>119874605</v>
       </c>
       <c r="B166" t="n">
-        <v>97930</v>
+        <v>90351</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -19035,47 +19017,38 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>220787</v>
+        <v>3215</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I166" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J166" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr"/>
       <c r="P166" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>563734</v>
+        <v>563929</v>
       </c>
       <c r="R166" t="n">
-        <v>6704595</v>
+        <v>6704878</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -19134,7 +19107,7 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>119874623</v>
+        <v>119874637</v>
       </c>
       <c r="B167" t="n">
         <v>97930</v>
@@ -19169,7 +19142,7 @@
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
@@ -19183,10 +19156,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>563637</v>
+        <v>563648</v>
       </c>
       <c r="R167" t="n">
-        <v>6704477</v>
+        <v>6704505</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -19245,10 +19218,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>119874568</v>
+        <v>119874663</v>
       </c>
       <c r="B168" t="n">
-        <v>90923</v>
+        <v>97930</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
@@ -19261,34 +19234,43 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>2062</v>
+        <v>220787</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I168" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P168" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>563986</v>
+        <v>563835</v>
       </c>
       <c r="R168" t="n">
-        <v>6705032</v>
+        <v>6704743</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -19347,10 +19329,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>119874577</v>
+        <v>119874624</v>
       </c>
       <c r="B169" t="n">
-        <v>90580</v>
+        <v>97930</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
@@ -19359,38 +19341,47 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I169" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P169" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>563703</v>
+        <v>563734</v>
       </c>
       <c r="R169" t="n">
-        <v>6704669</v>
+        <v>6704595</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -19449,10 +19440,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>119874605</v>
+        <v>119874623</v>
       </c>
       <c r="B170" t="n">
-        <v>90351</v>
+        <v>97930</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
@@ -19461,38 +19452,47 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>3215</v>
+        <v>220787</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I170" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P170" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>563929</v>
+        <v>563637</v>
       </c>
       <c r="R170" t="n">
-        <v>6704878</v>
+        <v>6704477</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -21287,10 +21287,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>119874573</v>
+        <v>119874633</v>
       </c>
       <c r="B187" t="n">
-        <v>90580</v>
+        <v>97930</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
@@ -21299,38 +21299,47 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I187" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J187" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P187" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>563794</v>
+        <v>563741</v>
       </c>
       <c r="R187" t="n">
-        <v>6704792</v>
+        <v>6704721</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -21389,10 +21398,10 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>119874604</v>
+        <v>119874649</v>
       </c>
       <c r="B188" t="n">
-        <v>90351</v>
+        <v>97930</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
@@ -21401,38 +21410,47 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>3215</v>
+        <v>220787</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I188" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J188" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P188" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>563936</v>
+        <v>563765</v>
       </c>
       <c r="R188" t="n">
-        <v>6704867</v>
+        <v>6704626</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -21491,7 +21509,7 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>119874633</v>
+        <v>119874630</v>
       </c>
       <c r="B189" t="n">
         <v>97930</v>
@@ -21540,10 +21558,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>563741</v>
+        <v>563815</v>
       </c>
       <c r="R189" t="n">
-        <v>6704721</v>
+        <v>6704815</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -21602,7 +21620,7 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>119874649</v>
+        <v>119874644</v>
       </c>
       <c r="B190" t="n">
         <v>97930</v>
@@ -21637,7 +21655,7 @@
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
@@ -21651,10 +21669,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>563765</v>
+        <v>563984</v>
       </c>
       <c r="R190" t="n">
-        <v>6704626</v>
+        <v>6704957</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -21713,10 +21731,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>119874630</v>
+        <v>119874604</v>
       </c>
       <c r="B191" t="n">
-        <v>97930</v>
+        <v>90351</v>
       </c>
       <c r="C191" t="inlineStr">
         <is>
@@ -21725,47 +21743,38 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E191" t="n">
-        <v>220787</v>
+        <v>3215</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I191" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J191" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr"/>
       <c r="P191" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>563815</v>
+        <v>563936</v>
       </c>
       <c r="R191" t="n">
-        <v>6704815</v>
+        <v>6704867</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -21824,10 +21833,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>119874644</v>
+        <v>119874573</v>
       </c>
       <c r="B192" t="n">
-        <v>97930</v>
+        <v>90580</v>
       </c>
       <c r="C192" t="inlineStr">
         <is>
@@ -21836,47 +21845,38 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E192" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I192" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J192" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr"/>
       <c r="P192" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>563984</v>
+        <v>563794</v>
       </c>
       <c r="R192" t="n">
-        <v>6704957</v>
+        <v>6704792</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -23355,10 +23355,10 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>119874583</v>
+        <v>119874597</v>
       </c>
       <c r="B206" t="n">
-        <v>90580</v>
+        <v>91512</v>
       </c>
       <c r="C206" t="inlineStr">
         <is>
@@ -23367,25 +23367,25 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E206" t="n">
-        <v>1202</v>
+        <v>4769</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I206" t="inlineStr"/>
@@ -23395,10 +23395,10 @@
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>563996</v>
+        <v>563943</v>
       </c>
       <c r="R206" t="n">
-        <v>6705007</v>
+        <v>6704878</v>
       </c>
       <c r="S206" t="n">
         <v>10</v>
@@ -23457,7 +23457,7 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>119874582</v>
+        <v>119874583</v>
       </c>
       <c r="B207" t="n">
         <v>90580</v>
@@ -23497,10 +23497,10 @@
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>563958</v>
+        <v>563996</v>
       </c>
       <c r="R207" t="n">
-        <v>6704952</v>
+        <v>6705007</v>
       </c>
       <c r="S207" t="n">
         <v>10</v>
@@ -23559,7 +23559,7 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>119874574</v>
+        <v>119874582</v>
       </c>
       <c r="B208" t="n">
         <v>90580</v>
@@ -23599,10 +23599,10 @@
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>563796</v>
+        <v>563958</v>
       </c>
       <c r="R208" t="n">
-        <v>6704785</v>
+        <v>6704952</v>
       </c>
       <c r="S208" t="n">
         <v>10</v>
@@ -23661,10 +23661,10 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>119874597</v>
+        <v>119874574</v>
       </c>
       <c r="B209" t="n">
-        <v>91512</v>
+        <v>90580</v>
       </c>
       <c r="C209" t="inlineStr">
         <is>
@@ -23673,25 +23673,25 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E209" t="n">
-        <v>4769</v>
+        <v>1202</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I209" t="inlineStr"/>
@@ -23701,10 +23701,10 @@
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>563943</v>
+        <v>563796</v>
       </c>
       <c r="R209" t="n">
-        <v>6704878</v>
+        <v>6704785</v>
       </c>
       <c r="S209" t="n">
         <v>10</v>

--- a/artfynd/A 58548-2022 artfynd.xlsx
+++ b/artfynd/A 58548-2022 artfynd.xlsx
@@ -15695,10 +15695,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>119874678</v>
+        <v>119874607</v>
       </c>
       <c r="B135" t="n">
-        <v>5169</v>
+        <v>90864</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -15707,43 +15707,38 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>100526</v>
+        <v>658</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
-      <c r="M135" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P135" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>563957</v>
+        <v>563821</v>
       </c>
       <c r="R135" t="n">
-        <v>6704878</v>
+        <v>6704817</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -15802,10 +15797,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>119874661</v>
+        <v>119874582</v>
       </c>
       <c r="B136" t="n">
-        <v>97930</v>
+        <v>90580</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -15814,47 +15809,38 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I136" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J136" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>563645</v>
+        <v>563958</v>
       </c>
       <c r="R136" t="n">
-        <v>6704515</v>
+        <v>6704952</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15913,10 +15899,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>119874566</v>
+        <v>119874571</v>
       </c>
       <c r="B137" t="n">
-        <v>90923</v>
+        <v>90580</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -15925,25 +15911,25 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>2062</v>
+        <v>1202</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -15953,10 +15939,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>564137</v>
+        <v>563816</v>
       </c>
       <c r="R137" t="n">
-        <v>6705070</v>
+        <v>6704792</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -16015,10 +16001,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>119874572</v>
+        <v>119874599</v>
       </c>
       <c r="B138" t="n">
-        <v>90580</v>
+        <v>57336</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -16031,34 +16017,39 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P138" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>563815</v>
+        <v>563944</v>
       </c>
       <c r="R138" t="n">
-        <v>6704789</v>
+        <v>6704948</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -16117,7 +16108,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>119874569</v>
+        <v>119874577</v>
       </c>
       <c r="B139" t="n">
         <v>90580</v>
@@ -16157,10 +16148,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>564137</v>
+        <v>563703</v>
       </c>
       <c r="R139" t="n">
-        <v>6705071</v>
+        <v>6704669</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -16219,10 +16210,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>119874580</v>
+        <v>119874678</v>
       </c>
       <c r="B140" t="n">
-        <v>90580</v>
+        <v>5169</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -16231,38 +16222,43 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P140" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>563702</v>
+        <v>563957</v>
       </c>
       <c r="R140" t="n">
-        <v>6704652</v>
+        <v>6704878</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -16321,7 +16317,7 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>119874588</v>
+        <v>119874576</v>
       </c>
       <c r="B141" t="n">
         <v>90580</v>
@@ -16361,10 +16357,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>564011</v>
+        <v>563718</v>
       </c>
       <c r="R141" t="n">
-        <v>6705060</v>
+        <v>6704695</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -16423,10 +16419,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>119874619</v>
+        <v>119874574</v>
       </c>
       <c r="B142" t="n">
-        <v>97930</v>
+        <v>90580</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -16435,47 +16431,38 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I142" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J142" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>564203</v>
+        <v>563796</v>
       </c>
       <c r="R142" t="n">
-        <v>6705186</v>
+        <v>6704785</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -16534,10 +16521,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>119874616</v>
+        <v>119874604</v>
       </c>
       <c r="B143" t="n">
-        <v>97930</v>
+        <v>90351</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -16546,47 +16533,38 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>220787</v>
+        <v>3215</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I143" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J143" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>563993</v>
+        <v>563936</v>
       </c>
       <c r="R143" t="n">
-        <v>6705035</v>
+        <v>6704867</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -16645,10 +16623,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>119874680</v>
+        <v>119874633</v>
       </c>
       <c r="B144" t="n">
-        <v>5169</v>
+        <v>97930</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -16657,31 +16635,35 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I144" t="inlineStr"/>
-      <c r="M144" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P144" t="inlineStr">
@@ -16690,10 +16672,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>563792</v>
+        <v>563741</v>
       </c>
       <c r="R144" t="n">
-        <v>6704694</v>
+        <v>6704721</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -16752,10 +16734,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>119874627</v>
+        <v>119874606</v>
       </c>
       <c r="B145" t="n">
-        <v>97930</v>
+        <v>90864</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -16764,54 +16746,38 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I145" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J145" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K145" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L145" t="inlineStr"/>
-      <c r="N145" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>563813</v>
+        <v>563784</v>
       </c>
       <c r="R145" t="n">
-        <v>6704796</v>
+        <v>6704721</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -16848,7 +16814,7 @@
       </c>
       <c r="AC145" t="inlineStr">
         <is>
-          <t>2 blomstjälkar</t>
+          <t>Äldre fruktkropp</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -16857,7 +16823,6 @@
       <c r="AE145" t="b">
         <v>0</v>
       </c>
-      <c r="AF145" t="inlineStr"/>
       <c r="AG145" t="b">
         <v>0</v>
       </c>
@@ -16876,10 +16841,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>119874581</v>
+        <v>119874677</v>
       </c>
       <c r="B146" t="n">
-        <v>90580</v>
+        <v>93953</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -16888,25 +16853,25 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>1202</v>
+        <v>2383</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bågpraktmossa</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Plagiomnium medium</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Bruch &amp; Schimp.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -16916,10 +16881,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>563792</v>
+        <v>563925</v>
       </c>
       <c r="R146" t="n">
-        <v>6704700</v>
+        <v>6704880</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16978,10 +16943,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>119874596</v>
+        <v>119874666</v>
       </c>
       <c r="B147" t="n">
-        <v>57473</v>
+        <v>74593</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -16990,50 +16955,38 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>103021</v>
+        <v>6426</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I147" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K147" t="inlineStr"/>
-      <c r="L147" t="inlineStr"/>
-      <c r="M147" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N147" t="inlineStr"/>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>563633</v>
+        <v>563945</v>
       </c>
       <c r="R147" t="n">
-        <v>6704498</v>
+        <v>6704877</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -17092,7 +17045,7 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>119874628</v>
+        <v>119874622</v>
       </c>
       <c r="B148" t="n">
         <v>97930</v>
@@ -17127,7 +17080,7 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
@@ -17141,10 +17094,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>564206</v>
+        <v>563711</v>
       </c>
       <c r="R148" t="n">
-        <v>6705189</v>
+        <v>6704677</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -17203,7 +17156,7 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>119874659</v>
+        <v>119874625</v>
       </c>
       <c r="B149" t="n">
         <v>97930</v>
@@ -17238,7 +17191,7 @@
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
@@ -17252,10 +17205,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>563746</v>
+        <v>564201</v>
       </c>
       <c r="R149" t="n">
-        <v>6704720</v>
+        <v>6705184</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -17314,10 +17267,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>119874606</v>
+        <v>119874647</v>
       </c>
       <c r="B150" t="n">
-        <v>90864</v>
+        <v>97930</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -17326,38 +17279,54 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I150" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L150" t="inlineStr"/>
+      <c r="N150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>563784</v>
+        <v>564036</v>
       </c>
       <c r="R150" t="n">
-        <v>6704721</v>
+        <v>6705043</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -17394,7 +17363,7 @@
       </c>
       <c r="AC150" t="inlineStr">
         <is>
-          <t>Äldre fruktkropp</t>
+          <t>1 blomstjälk</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -17403,6 +17372,7 @@
       <c r="AE150" t="b">
         <v>0</v>
       </c>
+      <c r="AF150" t="inlineStr"/>
       <c r="AG150" t="b">
         <v>0</v>
       </c>
@@ -17421,10 +17391,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>119874666</v>
+        <v>119874618</v>
       </c>
       <c r="B151" t="n">
-        <v>74593</v>
+        <v>97930</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -17433,38 +17403,47 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>6426</v>
+        <v>220787</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I151" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P151" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>563945</v>
+        <v>564168</v>
       </c>
       <c r="R151" t="n">
-        <v>6704877</v>
+        <v>6705183</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -17523,10 +17502,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>119874591</v>
+        <v>119874637</v>
       </c>
       <c r="B152" t="n">
-        <v>90580</v>
+        <v>97930</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -17535,38 +17514,47 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I152" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P152" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>564204</v>
+        <v>563648</v>
       </c>
       <c r="R152" t="n">
-        <v>6705194</v>
+        <v>6704505</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -17625,10 +17613,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>119874646</v>
+        <v>119874680</v>
       </c>
       <c r="B153" t="n">
-        <v>97930</v>
+        <v>5169</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -17637,35 +17625,31 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I153" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J153" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr"/>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P153" t="inlineStr">
@@ -17674,10 +17658,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>563995</v>
+        <v>563792</v>
       </c>
       <c r="R153" t="n">
-        <v>6704966</v>
+        <v>6704694</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -17736,10 +17720,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>119874651</v>
+        <v>119874567</v>
       </c>
       <c r="B154" t="n">
-        <v>97930</v>
+        <v>90923</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -17752,43 +17736,34 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>220787</v>
+        <v>2062</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I154" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J154" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr"/>
       <c r="P154" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>564256</v>
+        <v>564000</v>
       </c>
       <c r="R154" t="n">
-        <v>6705293</v>
+        <v>6705011</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -17847,7 +17822,7 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>119874590</v>
+        <v>119874573</v>
       </c>
       <c r="B155" t="n">
         <v>90580</v>
@@ -17887,10 +17862,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>564015</v>
+        <v>563794</v>
       </c>
       <c r="R155" t="n">
-        <v>6705047</v>
+        <v>6704792</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -17949,10 +17924,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>119874685</v>
+        <v>119874588</v>
       </c>
       <c r="B156" t="n">
-        <v>8421</v>
+        <v>90580</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -17961,43 +17936,38 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>106554</v>
+        <v>1202</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
-      <c r="M156" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P156" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>563845</v>
+        <v>564011</v>
       </c>
       <c r="R156" t="n">
-        <v>6704771</v>
+        <v>6705060</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -18056,10 +18026,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>119874658</v>
+        <v>119874585</v>
       </c>
       <c r="B157" t="n">
-        <v>97930</v>
+        <v>90580</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -18068,47 +18038,38 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I157" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J157" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>563749</v>
+        <v>563986</v>
       </c>
       <c r="R157" t="n">
-        <v>6704725</v>
+        <v>6705041</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -18167,7 +18128,7 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>119874632</v>
+        <v>119874635</v>
       </c>
       <c r="B158" t="n">
         <v>97930</v>
@@ -18216,10 +18177,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>563770</v>
+        <v>563705</v>
       </c>
       <c r="R158" t="n">
-        <v>6704729</v>
+        <v>6704657</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -18278,7 +18239,7 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>119874634</v>
+        <v>119874663</v>
       </c>
       <c r="B159" t="n">
         <v>97930</v>
@@ -18313,7 +18274,7 @@
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
@@ -18327,10 +18288,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>563712</v>
+        <v>563835</v>
       </c>
       <c r="R159" t="n">
-        <v>6704670</v>
+        <v>6704743</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -18389,10 +18350,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>119874609</v>
+        <v>119874644</v>
       </c>
       <c r="B160" t="n">
-        <v>90972</v>
+        <v>97930</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -18401,33 +18362,47 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>6040186</v>
+        <v>220787</v>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
-        </is>
-      </c>
-      <c r="I160" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P160" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>564083</v>
+        <v>563984</v>
       </c>
       <c r="R160" t="n">
-        <v>6705090</v>
+        <v>6704957</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -18486,10 +18461,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>119874567</v>
+        <v>119874616</v>
       </c>
       <c r="B161" t="n">
-        <v>90923</v>
+        <v>97930</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -18502,34 +18477,43 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>2062</v>
+        <v>220787</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I161" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P161" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>564000</v>
+        <v>563993</v>
       </c>
       <c r="R161" t="n">
-        <v>6705011</v>
+        <v>6705035</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -18588,7 +18572,7 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>119874586</v>
+        <v>119874593</v>
       </c>
       <c r="B162" t="n">
         <v>90580</v>
@@ -18628,10 +18612,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>564005</v>
+        <v>563710</v>
       </c>
       <c r="R162" t="n">
-        <v>6705064</v>
+        <v>6704663</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -18690,10 +18674,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>119874635</v>
+        <v>119874575</v>
       </c>
       <c r="B163" t="n">
-        <v>97930</v>
+        <v>90580</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -18702,47 +18686,38 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I163" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J163" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr"/>
       <c r="P163" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>563705</v>
+        <v>563720</v>
       </c>
       <c r="R163" t="n">
-        <v>6704657</v>
+        <v>6704700</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -18801,10 +18776,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>119874568</v>
+        <v>119874581</v>
       </c>
       <c r="B164" t="n">
-        <v>90923</v>
+        <v>90580</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -18813,25 +18788,25 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>2062</v>
+        <v>1202</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -18841,10 +18816,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>563986</v>
+        <v>563792</v>
       </c>
       <c r="R164" t="n">
-        <v>6705032</v>
+        <v>6704700</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -18903,10 +18878,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>119874577</v>
+        <v>119874624</v>
       </c>
       <c r="B165" t="n">
-        <v>90580</v>
+        <v>97930</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -18915,38 +18890,47 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I165" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P165" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>563703</v>
+        <v>563734</v>
       </c>
       <c r="R165" t="n">
-        <v>6704669</v>
+        <v>6704595</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -19005,10 +18989,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>119874605</v>
+        <v>119874630</v>
       </c>
       <c r="B166" t="n">
-        <v>90351</v>
+        <v>97930</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -19017,38 +19001,47 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>3215</v>
+        <v>220787</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I166" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P166" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>563929</v>
+        <v>563815</v>
       </c>
       <c r="R166" t="n">
-        <v>6704878</v>
+        <v>6704815</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -19107,7 +19100,7 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>119874637</v>
+        <v>119874651</v>
       </c>
       <c r="B167" t="n">
         <v>97930</v>
@@ -19142,7 +19135,7 @@
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
@@ -19156,10 +19149,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>563648</v>
+        <v>564256</v>
       </c>
       <c r="R167" t="n">
-        <v>6704505</v>
+        <v>6705293</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -19218,10 +19211,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>119874663</v>
+        <v>119874568</v>
       </c>
       <c r="B168" t="n">
-        <v>97930</v>
+        <v>90923</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
@@ -19234,43 +19227,34 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>220787</v>
+        <v>2062</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I168" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J168" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr"/>
       <c r="P168" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>563835</v>
+        <v>563986</v>
       </c>
       <c r="R168" t="n">
-        <v>6704743</v>
+        <v>6705032</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -19329,7 +19313,7 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>119874624</v>
+        <v>119874639</v>
       </c>
       <c r="B169" t="n">
         <v>97930</v>
@@ -19364,7 +19348,7 @@
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
@@ -19378,10 +19362,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>563734</v>
+        <v>563718</v>
       </c>
       <c r="R169" t="n">
-        <v>6704595</v>
+        <v>6704563</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -19440,10 +19424,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>119874623</v>
+        <v>119874572</v>
       </c>
       <c r="B170" t="n">
-        <v>97930</v>
+        <v>90580</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
@@ -19452,47 +19436,38 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I170" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J170" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr"/>
       <c r="P170" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>563637</v>
+        <v>563815</v>
       </c>
       <c r="R170" t="n">
-        <v>6704477</v>
+        <v>6704789</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -19551,10 +19526,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>119874575</v>
+        <v>119874596</v>
       </c>
       <c r="B171" t="n">
-        <v>90580</v>
+        <v>57473</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
@@ -19567,34 +19542,46 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I171" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr"/>
+      <c r="L171" t="inlineStr"/>
+      <c r="M171" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N171" t="inlineStr"/>
       <c r="P171" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>563720</v>
+        <v>563633</v>
       </c>
       <c r="R171" t="n">
-        <v>6704700</v>
+        <v>6704498</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -19653,10 +19640,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>119874571</v>
+        <v>119874658</v>
       </c>
       <c r="B172" t="n">
-        <v>90580</v>
+        <v>97930</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
@@ -19665,38 +19652,47 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I172" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P172" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>563816</v>
+        <v>563749</v>
       </c>
       <c r="R172" t="n">
-        <v>6704792</v>
+        <v>6704725</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -19755,10 +19751,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>119874599</v>
+        <v>119874642</v>
       </c>
       <c r="B173" t="n">
-        <v>57336</v>
+        <v>97930</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
@@ -19767,31 +19763,35 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I173" t="inlineStr"/>
-      <c r="M173" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P173" t="inlineStr">
@@ -19800,10 +19800,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>563944</v>
+        <v>563974</v>
       </c>
       <c r="R173" t="n">
-        <v>6704948</v>
+        <v>6704953</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -19862,10 +19862,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>119874593</v>
+        <v>119874655</v>
       </c>
       <c r="B174" t="n">
-        <v>90580</v>
+        <v>97930</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
@@ -19874,38 +19874,47 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I174" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P174" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>563710</v>
+        <v>563757</v>
       </c>
       <c r="R174" t="n">
-        <v>6704663</v>
+        <v>6704730</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -19964,7 +19973,7 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>119874647</v>
+        <v>119874627</v>
       </c>
       <c r="B175" t="n">
         <v>97930</v>
@@ -19999,7 +20008,7 @@
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
@@ -20020,10 +20029,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>564036</v>
+        <v>563813</v>
       </c>
       <c r="R175" t="n">
-        <v>6705043</v>
+        <v>6704796</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -20060,7 +20069,7 @@
       </c>
       <c r="AC175" t="inlineStr">
         <is>
-          <t>1 blomstjälk</t>
+          <t>2 blomstjälkar</t>
         </is>
       </c>
       <c r="AD175" t="b">
@@ -20088,7 +20097,7 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>119874618</v>
+        <v>119874612</v>
       </c>
       <c r="B176" t="n">
         <v>97930</v>
@@ -20123,7 +20132,7 @@
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
@@ -20131,16 +20140,23 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L176" t="inlineStr"/>
+      <c r="N176" t="inlineStr"/>
       <c r="P176" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>564168</v>
+        <v>564201</v>
       </c>
       <c r="R176" t="n">
-        <v>6705183</v>
+        <v>6705191</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -20175,12 +20191,18 @@
           <t>2024-09-20</t>
         </is>
       </c>
+      <c r="AC176" t="inlineStr">
+        <is>
+          <t>1 blomstjälk</t>
+        </is>
+      </c>
       <c r="AD176" t="b">
         <v>0</v>
       </c>
       <c r="AE176" t="b">
         <v>0</v>
       </c>
+      <c r="AF176" t="inlineStr"/>
       <c r="AG176" t="b">
         <v>0</v>
       </c>
@@ -20199,7 +20221,7 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>119874655</v>
+        <v>119874619</v>
       </c>
       <c r="B177" t="n">
         <v>97930</v>
@@ -20234,7 +20256,7 @@
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
@@ -20248,10 +20270,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>563757</v>
+        <v>564203</v>
       </c>
       <c r="R177" t="n">
-        <v>6704730</v>
+        <v>6705186</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -20310,10 +20332,10 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>119874682</v>
+        <v>119874659</v>
       </c>
       <c r="B178" t="n">
-        <v>5169</v>
+        <v>97930</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>
@@ -20322,31 +20344,35 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I178" t="inlineStr"/>
-      <c r="M178" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P178" t="inlineStr">
@@ -20355,10 +20381,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>564000</v>
+        <v>563746</v>
       </c>
       <c r="R178" t="n">
-        <v>6704958</v>
+        <v>6704720</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -20417,10 +20443,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>119874612</v>
+        <v>119874685</v>
       </c>
       <c r="B179" t="n">
-        <v>97930</v>
+        <v>8421</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
@@ -20429,54 +20455,43 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>220787</v>
+        <v>106554</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I179" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J179" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K179" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L179" t="inlineStr"/>
-      <c r="N179" t="inlineStr"/>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr"/>
+      <c r="M179" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P179" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>564201</v>
+        <v>563845</v>
       </c>
       <c r="R179" t="n">
-        <v>6705191</v>
+        <v>6704771</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -20511,18 +20526,12 @@
           <t>2024-09-20</t>
         </is>
       </c>
-      <c r="AC179" t="inlineStr">
-        <is>
-          <t>1 blomstjälk</t>
-        </is>
-      </c>
       <c r="AD179" t="b">
         <v>0</v>
       </c>
       <c r="AE179" t="b">
         <v>0</v>
       </c>
-      <c r="AF179" t="inlineStr"/>
       <c r="AG179" t="b">
         <v>0</v>
       </c>
@@ -20541,10 +20550,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>119874625</v>
+        <v>119874684</v>
       </c>
       <c r="B180" t="n">
-        <v>97930</v>
+        <v>100194</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
@@ -20553,47 +20562,38 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I180" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J180" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr"/>
       <c r="P180" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>564201</v>
+        <v>563956</v>
       </c>
       <c r="R180" t="n">
-        <v>6705184</v>
+        <v>6704876</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -20652,10 +20652,10 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>119874641</v>
+        <v>119874609</v>
       </c>
       <c r="B181" t="n">
-        <v>97930</v>
+        <v>90972</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
@@ -20664,47 +20664,33 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F181" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I181" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J181" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr"/>
       <c r="P181" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>563808</v>
+        <v>564083</v>
       </c>
       <c r="R181" t="n">
-        <v>6704697</v>
+        <v>6705090</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -20763,7 +20749,7 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>119874576</v>
+        <v>119874569</v>
       </c>
       <c r="B182" t="n">
         <v>90580</v>
@@ -20803,10 +20789,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>563718</v>
+        <v>564137</v>
       </c>
       <c r="R182" t="n">
-        <v>6704695</v>
+        <v>6705071</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -20865,10 +20851,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>119874585</v>
+        <v>119874608</v>
       </c>
       <c r="B183" t="n">
-        <v>90580</v>
+        <v>94334</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
@@ -20877,25 +20863,25 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>1202</v>
+        <v>2809</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
@@ -20905,10 +20891,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>563986</v>
+        <v>563944</v>
       </c>
       <c r="R183" t="n">
-        <v>6705041</v>
+        <v>6704880</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -21078,10 +21064,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>119874608</v>
+        <v>119874623</v>
       </c>
       <c r="B185" t="n">
-        <v>94334</v>
+        <v>97930</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
@@ -21090,38 +21076,47 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>2809</v>
+        <v>220787</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
-        </is>
-      </c>
-      <c r="I185" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J185" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P185" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>563944</v>
+        <v>563637</v>
       </c>
       <c r="R185" t="n">
-        <v>6704880</v>
+        <v>6704477</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -21180,10 +21175,10 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>119874681</v>
+        <v>119874668</v>
       </c>
       <c r="B186" t="n">
-        <v>5169</v>
+        <v>74593</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
@@ -21196,39 +21191,34 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>100526</v>
+        <v>6426</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
-      <c r="M186" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P186" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>563825</v>
+        <v>563937</v>
       </c>
       <c r="R186" t="n">
-        <v>6704705</v>
+        <v>6704867</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -21287,7 +21277,7 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>119874633</v>
+        <v>119874621</v>
       </c>
       <c r="B187" t="n">
         <v>97930</v>
@@ -21322,7 +21312,7 @@
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
@@ -21336,10 +21326,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>563741</v>
+        <v>564283</v>
       </c>
       <c r="R187" t="n">
-        <v>6704721</v>
+        <v>6705293</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -21398,7 +21388,7 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>119874649</v>
+        <v>119874634</v>
       </c>
       <c r="B188" t="n">
         <v>97930</v>
@@ -21433,7 +21423,7 @@
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
@@ -21447,10 +21437,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>563765</v>
+        <v>563712</v>
       </c>
       <c r="R188" t="n">
-        <v>6704626</v>
+        <v>6704670</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -21509,10 +21499,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>119874630</v>
+        <v>119874583</v>
       </c>
       <c r="B189" t="n">
-        <v>97930</v>
+        <v>90580</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
@@ -21521,47 +21511,38 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E189" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I189" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J189" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr"/>
       <c r="P189" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>563815</v>
+        <v>563996</v>
       </c>
       <c r="R189" t="n">
-        <v>6704815</v>
+        <v>6705007</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -21620,10 +21601,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>119874644</v>
+        <v>119874580</v>
       </c>
       <c r="B190" t="n">
-        <v>97930</v>
+        <v>90580</v>
       </c>
       <c r="C190" t="inlineStr">
         <is>
@@ -21632,47 +21613,38 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E190" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I190" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J190" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr"/>
       <c r="P190" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>563984</v>
+        <v>563702</v>
       </c>
       <c r="R190" t="n">
-        <v>6704957</v>
+        <v>6704652</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -21731,10 +21703,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>119874604</v>
+        <v>119874617</v>
       </c>
       <c r="B191" t="n">
-        <v>90351</v>
+        <v>97930</v>
       </c>
       <c r="C191" t="inlineStr">
         <is>
@@ -21743,38 +21715,47 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E191" t="n">
-        <v>3215</v>
+        <v>220787</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I191" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J191" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P191" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>563936</v>
+        <v>563833</v>
       </c>
       <c r="R191" t="n">
-        <v>6704867</v>
+        <v>6704788</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -21833,10 +21814,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>119874573</v>
+        <v>119874641</v>
       </c>
       <c r="B192" t="n">
-        <v>90580</v>
+        <v>97930</v>
       </c>
       <c r="C192" t="inlineStr">
         <is>
@@ -21845,38 +21826,47 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E192" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I192" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J192" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P192" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>563794</v>
+        <v>563808</v>
       </c>
       <c r="R192" t="n">
-        <v>6704792</v>
+        <v>6704697</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -21935,10 +21925,10 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>119874684</v>
+        <v>119874586</v>
       </c>
       <c r="B193" t="n">
-        <v>100194</v>
+        <v>90580</v>
       </c>
       <c r="C193" t="inlineStr">
         <is>
@@ -21947,25 +21937,25 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
@@ -21975,10 +21965,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>563956</v>
+        <v>564005</v>
       </c>
       <c r="R193" t="n">
-        <v>6704876</v>
+        <v>6705064</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -22037,7 +22027,7 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>119874626</v>
+        <v>119874628</v>
       </c>
       <c r="B194" t="n">
         <v>97930</v>
@@ -22080,23 +22070,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K194" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L194" t="inlineStr"/>
-      <c r="N194" t="inlineStr"/>
       <c r="P194" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>564019</v>
+        <v>564206</v>
       </c>
       <c r="R194" t="n">
-        <v>6704997</v>
+        <v>6705189</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -22131,18 +22114,12 @@
           <t>2024-09-20</t>
         </is>
       </c>
-      <c r="AC194" t="inlineStr">
-        <is>
-          <t>1 blomstjälk</t>
-        </is>
-      </c>
       <c r="AD194" t="b">
         <v>0</v>
       </c>
       <c r="AE194" t="b">
         <v>0</v>
       </c>
-      <c r="AF194" t="inlineStr"/>
       <c r="AG194" t="b">
         <v>0</v>
       </c>
@@ -22161,7 +22138,7 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>119874621</v>
+        <v>119874652</v>
       </c>
       <c r="B195" t="n">
         <v>97930</v>
@@ -22196,7 +22173,7 @@
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J195" t="inlineStr">
@@ -22210,10 +22187,10 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>564283</v>
+        <v>563976</v>
       </c>
       <c r="R195" t="n">
-        <v>6705293</v>
+        <v>6704966</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -22272,10 +22249,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>119874639</v>
+        <v>119874590</v>
       </c>
       <c r="B196" t="n">
-        <v>97930</v>
+        <v>90580</v>
       </c>
       <c r="C196" t="inlineStr">
         <is>
@@ -22284,47 +22261,38 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E196" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I196" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J196" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr"/>
       <c r="P196" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>563718</v>
+        <v>564015</v>
       </c>
       <c r="R196" t="n">
-        <v>6704563</v>
+        <v>6705047</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -22383,10 +22351,10 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>119874668</v>
+        <v>119874605</v>
       </c>
       <c r="B197" t="n">
-        <v>74593</v>
+        <v>90351</v>
       </c>
       <c r="C197" t="inlineStr">
         <is>
@@ -22399,21 +22367,21 @@
         </is>
       </c>
       <c r="E197" t="n">
-        <v>6426</v>
+        <v>3215</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
@@ -22423,10 +22391,10 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>563937</v>
+        <v>563929</v>
       </c>
       <c r="R197" t="n">
-        <v>6704867</v>
+        <v>6704878</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -22485,10 +22453,10 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>119874607</v>
+        <v>119874632</v>
       </c>
       <c r="B198" t="n">
-        <v>90864</v>
+        <v>97930</v>
       </c>
       <c r="C198" t="inlineStr">
         <is>
@@ -22497,38 +22465,47 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E198" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I198" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J198" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P198" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>563821</v>
+        <v>563770</v>
       </c>
       <c r="R198" t="n">
-        <v>6704817</v>
+        <v>6704729</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -22587,10 +22564,10 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>119874665</v>
+        <v>119874566</v>
       </c>
       <c r="B199" t="n">
-        <v>97930</v>
+        <v>90923</v>
       </c>
       <c r="C199" t="inlineStr">
         <is>
@@ -22603,43 +22580,34 @@
         </is>
       </c>
       <c r="E199" t="n">
-        <v>220787</v>
+        <v>2062</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I199" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J199" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr"/>
       <c r="P199" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>564008</v>
+        <v>564137</v>
       </c>
       <c r="R199" t="n">
-        <v>6704979</v>
+        <v>6705070</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -22698,7 +22666,7 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>119874642</v>
+        <v>119874665</v>
       </c>
       <c r="B200" t="n">
         <v>97930</v>
@@ -22733,7 +22701,7 @@
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J200" t="inlineStr">
@@ -22747,10 +22715,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>563974</v>
+        <v>564008</v>
       </c>
       <c r="R200" t="n">
-        <v>6704953</v>
+        <v>6704979</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -22809,7 +22777,7 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>119874652</v>
+        <v>119874661</v>
       </c>
       <c r="B201" t="n">
         <v>97930</v>
@@ -22858,10 +22826,10 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>563976</v>
+        <v>563645</v>
       </c>
       <c r="R201" t="n">
-        <v>6704966</v>
+        <v>6704515</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -22920,7 +22888,7 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>119874622</v>
+        <v>119874646</v>
       </c>
       <c r="B202" t="n">
         <v>97930</v>
@@ -22955,7 +22923,7 @@
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J202" t="inlineStr">
@@ -22969,10 +22937,10 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>563711</v>
+        <v>563995</v>
       </c>
       <c r="R202" t="n">
-        <v>6704677</v>
+        <v>6704966</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -23031,10 +22999,10 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>119874617</v>
+        <v>119874682</v>
       </c>
       <c r="B203" t="n">
-        <v>97930</v>
+        <v>5169</v>
       </c>
       <c r="C203" t="inlineStr">
         <is>
@@ -23043,35 +23011,31 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E203" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I203" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J203" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr"/>
+      <c r="M203" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P203" t="inlineStr">
@@ -23080,10 +23044,10 @@
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>563833</v>
+        <v>564000</v>
       </c>
       <c r="R203" t="n">
-        <v>6704788</v>
+        <v>6704958</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -23142,10 +23106,10 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>119874613</v>
+        <v>119874597</v>
       </c>
       <c r="B204" t="n">
-        <v>97930</v>
+        <v>91512</v>
       </c>
       <c r="C204" t="inlineStr">
         <is>
@@ -23154,47 +23118,38 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E204" t="n">
-        <v>220787</v>
+        <v>4769</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I204" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J204" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Scop.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr"/>
       <c r="P204" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>563794</v>
+        <v>563943</v>
       </c>
       <c r="R204" t="n">
-        <v>6704750</v>
+        <v>6704878</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>
@@ -23253,10 +23208,10 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>119874677</v>
+        <v>119874626</v>
       </c>
       <c r="B205" t="n">
-        <v>93953</v>
+        <v>97930</v>
       </c>
       <c r="C205" t="inlineStr">
         <is>
@@ -23265,38 +23220,54 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E205" t="n">
-        <v>2383</v>
+        <v>220787</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Bågpraktmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Plagiomnium medium</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>(Bruch &amp; Schimp.) T.J.Kop.</t>
-        </is>
-      </c>
-      <c r="I205" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J205" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L205" t="inlineStr"/>
+      <c r="N205" t="inlineStr"/>
       <c r="P205" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>563925</v>
+        <v>564019</v>
       </c>
       <c r="R205" t="n">
-        <v>6704880</v>
+        <v>6704997</v>
       </c>
       <c r="S205" t="n">
         <v>10</v>
@@ -23331,12 +23302,18 @@
           <t>2024-09-20</t>
         </is>
       </c>
+      <c r="AC205" t="inlineStr">
+        <is>
+          <t>1 blomstjälk</t>
+        </is>
+      </c>
       <c r="AD205" t="b">
         <v>0</v>
       </c>
       <c r="AE205" t="b">
         <v>0</v>
       </c>
+      <c r="AF205" t="inlineStr"/>
       <c r="AG205" t="b">
         <v>0</v>
       </c>
@@ -23355,10 +23332,10 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>119874597</v>
+        <v>119874591</v>
       </c>
       <c r="B206" t="n">
-        <v>91512</v>
+        <v>90580</v>
       </c>
       <c r="C206" t="inlineStr">
         <is>
@@ -23367,25 +23344,25 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E206" t="n">
-        <v>4769</v>
+        <v>1202</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I206" t="inlineStr"/>
@@ -23395,10 +23372,10 @@
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>563943</v>
+        <v>564204</v>
       </c>
       <c r="R206" t="n">
-        <v>6704878</v>
+        <v>6705194</v>
       </c>
       <c r="S206" t="n">
         <v>10</v>
@@ -23457,10 +23434,10 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>119874583</v>
+        <v>119874681</v>
       </c>
       <c r="B207" t="n">
-        <v>90580</v>
+        <v>5169</v>
       </c>
       <c r="C207" t="inlineStr">
         <is>
@@ -23469,38 +23446,43 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E207" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I207" t="inlineStr"/>
+      <c r="M207" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P207" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>563996</v>
+        <v>563825</v>
       </c>
       <c r="R207" t="n">
-        <v>6705007</v>
+        <v>6704705</v>
       </c>
       <c r="S207" t="n">
         <v>10</v>
@@ -23559,10 +23541,10 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>119874582</v>
+        <v>119874649</v>
       </c>
       <c r="B208" t="n">
-        <v>90580</v>
+        <v>97930</v>
       </c>
       <c r="C208" t="inlineStr">
         <is>
@@ -23571,38 +23553,47 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E208" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I208" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J208" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P208" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>563958</v>
+        <v>563765</v>
       </c>
       <c r="R208" t="n">
-        <v>6704952</v>
+        <v>6704626</v>
       </c>
       <c r="S208" t="n">
         <v>10</v>
@@ -23661,10 +23652,10 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>119874574</v>
+        <v>119874613</v>
       </c>
       <c r="B209" t="n">
-        <v>90580</v>
+        <v>97930</v>
       </c>
       <c r="C209" t="inlineStr">
         <is>
@@ -23673,38 +23664,47 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E209" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I209" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J209" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P209" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>563796</v>
+        <v>563794</v>
       </c>
       <c r="R209" t="n">
-        <v>6704785</v>
+        <v>6704750</v>
       </c>
       <c r="S209" t="n">
         <v>10</v>

--- a/artfynd/A 58548-2022 artfynd.xlsx
+++ b/artfynd/A 58548-2022 artfynd.xlsx
@@ -15695,10 +15695,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>119874607</v>
+        <v>119874605</v>
       </c>
       <c r="B135" t="n">
-        <v>90864</v>
+        <v>90351</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -15707,25 +15707,25 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>658</v>
+        <v>3215</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -15735,10 +15735,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>563821</v>
+        <v>563929</v>
       </c>
       <c r="R135" t="n">
-        <v>6704817</v>
+        <v>6704878</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -15797,10 +15797,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>119874582</v>
+        <v>119874626</v>
       </c>
       <c r="B136" t="n">
-        <v>90580</v>
+        <v>97930</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -15809,38 +15809,54 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I136" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L136" t="inlineStr"/>
+      <c r="N136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>563958</v>
+        <v>564019</v>
       </c>
       <c r="R136" t="n">
-        <v>6704952</v>
+        <v>6704997</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15875,12 +15891,18 @@
           <t>2024-09-20</t>
         </is>
       </c>
+      <c r="AC136" t="inlineStr">
+        <is>
+          <t>1 blomstjälk</t>
+        </is>
+      </c>
       <c r="AD136" t="b">
         <v>0</v>
       </c>
       <c r="AE136" t="b">
         <v>0</v>
       </c>
+      <c r="AF136" t="inlineStr"/>
       <c r="AG136" t="b">
         <v>0</v>
       </c>
@@ -15899,10 +15921,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>119874571</v>
+        <v>119874613</v>
       </c>
       <c r="B137" t="n">
-        <v>90580</v>
+        <v>97930</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -15911,38 +15933,47 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I137" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P137" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>563816</v>
+        <v>563794</v>
       </c>
       <c r="R137" t="n">
-        <v>6704792</v>
+        <v>6704750</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -16001,10 +16032,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>119874599</v>
+        <v>119874617</v>
       </c>
       <c r="B138" t="n">
-        <v>57336</v>
+        <v>97930</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -16013,31 +16044,35 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I138" t="inlineStr"/>
-      <c r="M138" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P138" t="inlineStr">
@@ -16046,10 +16081,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>563944</v>
+        <v>563833</v>
       </c>
       <c r="R138" t="n">
-        <v>6704948</v>
+        <v>6704788</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -16108,10 +16143,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>119874577</v>
+        <v>119874622</v>
       </c>
       <c r="B139" t="n">
-        <v>90580</v>
+        <v>97930</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -16120,38 +16155,47 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I139" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P139" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>563703</v>
+        <v>563711</v>
       </c>
       <c r="R139" t="n">
-        <v>6704669</v>
+        <v>6704677</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -16210,10 +16254,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>119874678</v>
+        <v>119874604</v>
       </c>
       <c r="B140" t="n">
-        <v>5169</v>
+        <v>90351</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -16226,39 +16270,34 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>100526</v>
+        <v>3215</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
-      <c r="M140" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P140" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>563957</v>
+        <v>563936</v>
       </c>
       <c r="R140" t="n">
-        <v>6704878</v>
+        <v>6704867</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -16317,10 +16356,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>119874576</v>
+        <v>119874651</v>
       </c>
       <c r="B141" t="n">
-        <v>90580</v>
+        <v>97930</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -16329,38 +16368,47 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I141" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P141" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>563718</v>
+        <v>564256</v>
       </c>
       <c r="R141" t="n">
-        <v>6704695</v>
+        <v>6705293</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -16419,10 +16467,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>119874574</v>
+        <v>119874623</v>
       </c>
       <c r="B142" t="n">
-        <v>90580</v>
+        <v>97930</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -16431,38 +16479,47 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I142" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P142" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>563796</v>
+        <v>563637</v>
       </c>
       <c r="R142" t="n">
-        <v>6704785</v>
+        <v>6704477</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -16521,10 +16578,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>119874604</v>
+        <v>119874635</v>
       </c>
       <c r="B143" t="n">
-        <v>90351</v>
+        <v>97930</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -16533,38 +16590,47 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>3215</v>
+        <v>220787</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I143" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P143" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>563936</v>
+        <v>563705</v>
       </c>
       <c r="R143" t="n">
-        <v>6704867</v>
+        <v>6704657</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -16623,7 +16689,7 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>119874633</v>
+        <v>119874665</v>
       </c>
       <c r="B144" t="n">
         <v>97930</v>
@@ -16658,7 +16724,7 @@
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
@@ -16672,10 +16738,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>563741</v>
+        <v>564008</v>
       </c>
       <c r="R144" t="n">
-        <v>6704721</v>
+        <v>6704979</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -16734,10 +16800,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>119874606</v>
+        <v>119874641</v>
       </c>
       <c r="B145" t="n">
-        <v>90864</v>
+        <v>97930</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -16746,38 +16812,47 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I145" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P145" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>563784</v>
+        <v>563808</v>
       </c>
       <c r="R145" t="n">
-        <v>6704721</v>
+        <v>6704697</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -16810,11 +16885,6 @@
       <c r="AA145" t="inlineStr">
         <is>
           <t>2024-09-20</t>
-        </is>
-      </c>
-      <c r="AC145" t="inlineStr">
-        <is>
-          <t>Äldre fruktkropp</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -16841,10 +16911,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>119874677</v>
+        <v>119874666</v>
       </c>
       <c r="B146" t="n">
-        <v>93953</v>
+        <v>74593</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -16857,21 +16927,21 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>2383</v>
+        <v>6426</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Bågpraktmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Plagiomnium medium</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Bruch &amp; Schimp.) T.J.Kop.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -16881,10 +16951,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>563925</v>
+        <v>563945</v>
       </c>
       <c r="R146" t="n">
-        <v>6704880</v>
+        <v>6704877</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16943,10 +17013,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>119874666</v>
+        <v>119874609</v>
       </c>
       <c r="B147" t="n">
-        <v>74593</v>
+        <v>90972</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -16955,25 +17025,20 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>6426</v>
-      </c>
-      <c r="F147" t="inlineStr">
-        <is>
-          <t>Kattfotslav</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -16983,10 +17048,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>563945</v>
+        <v>564083</v>
       </c>
       <c r="R147" t="n">
-        <v>6704877</v>
+        <v>6705090</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -17045,7 +17110,7 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>119874622</v>
+        <v>119874628</v>
       </c>
       <c r="B148" t="n">
         <v>97930</v>
@@ -17080,7 +17145,7 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
@@ -17094,10 +17159,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>563711</v>
+        <v>564206</v>
       </c>
       <c r="R148" t="n">
-        <v>6704677</v>
+        <v>6705189</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -17156,7 +17221,7 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>119874625</v>
+        <v>119874637</v>
       </c>
       <c r="B149" t="n">
         <v>97930</v>
@@ -17191,7 +17256,7 @@
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
@@ -17205,10 +17270,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>564201</v>
+        <v>563648</v>
       </c>
       <c r="R149" t="n">
-        <v>6705184</v>
+        <v>6704505</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -17267,10 +17332,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>119874647</v>
+        <v>119874680</v>
       </c>
       <c r="B150" t="n">
-        <v>97930</v>
+        <v>5169</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -17279,54 +17344,43 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I150" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J150" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K150" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L150" t="inlineStr"/>
-      <c r="N150" t="inlineStr"/>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr"/>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P150" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>564036</v>
+        <v>563792</v>
       </c>
       <c r="R150" t="n">
-        <v>6705043</v>
+        <v>6704694</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -17361,18 +17415,12 @@
           <t>2024-09-20</t>
         </is>
       </c>
-      <c r="AC150" t="inlineStr">
-        <is>
-          <t>1 blomstjälk</t>
-        </is>
-      </c>
       <c r="AD150" t="b">
         <v>0</v>
       </c>
       <c r="AE150" t="b">
         <v>0</v>
       </c>
-      <c r="AF150" t="inlineStr"/>
       <c r="AG150" t="b">
         <v>0</v>
       </c>
@@ -17391,10 +17439,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>119874618</v>
+        <v>119874575</v>
       </c>
       <c r="B151" t="n">
-        <v>97930</v>
+        <v>90580</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -17403,47 +17451,38 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I151" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J151" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>564168</v>
+        <v>563720</v>
       </c>
       <c r="R151" t="n">
-        <v>6705183</v>
+        <v>6704700</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -17502,10 +17541,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>119874637</v>
+        <v>119874668</v>
       </c>
       <c r="B152" t="n">
-        <v>97930</v>
+        <v>74593</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -17514,47 +17553,38 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>220787</v>
+        <v>6426</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I152" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J152" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>563648</v>
+        <v>563937</v>
       </c>
       <c r="R152" t="n">
-        <v>6704505</v>
+        <v>6704867</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -17613,10 +17643,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>119874680</v>
+        <v>119874634</v>
       </c>
       <c r="B153" t="n">
-        <v>5169</v>
+        <v>97930</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -17625,31 +17655,35 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I153" t="inlineStr"/>
-      <c r="M153" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P153" t="inlineStr">
@@ -17658,10 +17692,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>563792</v>
+        <v>563712</v>
       </c>
       <c r="R153" t="n">
-        <v>6704694</v>
+        <v>6704670</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -17720,10 +17754,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>119874567</v>
+        <v>119874569</v>
       </c>
       <c r="B154" t="n">
-        <v>90923</v>
+        <v>90580</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -17732,25 +17766,25 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>2062</v>
+        <v>1202</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -17760,10 +17794,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>564000</v>
+        <v>564137</v>
       </c>
       <c r="R154" t="n">
-        <v>6705011</v>
+        <v>6705071</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -17822,7 +17856,7 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>119874573</v>
+        <v>119874577</v>
       </c>
       <c r="B155" t="n">
         <v>90580</v>
@@ -17862,10 +17896,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>563794</v>
+        <v>563703</v>
       </c>
       <c r="R155" t="n">
-        <v>6704792</v>
+        <v>6704669</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -17924,10 +17958,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>119874588</v>
+        <v>119874568</v>
       </c>
       <c r="B156" t="n">
-        <v>90580</v>
+        <v>90923</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -17936,25 +17970,25 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>1202</v>
+        <v>2062</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -17964,10 +17998,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>564011</v>
+        <v>563986</v>
       </c>
       <c r="R156" t="n">
-        <v>6705060</v>
+        <v>6705032</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -18026,10 +18060,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>119874585</v>
+        <v>119874618</v>
       </c>
       <c r="B157" t="n">
-        <v>90580</v>
+        <v>97930</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -18038,38 +18072,47 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I157" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P157" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>563986</v>
+        <v>564168</v>
       </c>
       <c r="R157" t="n">
-        <v>6705041</v>
+        <v>6705183</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -18128,7 +18171,7 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>119874635</v>
+        <v>119874661</v>
       </c>
       <c r="B158" t="n">
         <v>97930</v>
@@ -18163,7 +18206,7 @@
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
@@ -18177,10 +18220,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>563705</v>
+        <v>563645</v>
       </c>
       <c r="R158" t="n">
-        <v>6704657</v>
+        <v>6704515</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -18239,7 +18282,7 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>119874663</v>
+        <v>119874649</v>
       </c>
       <c r="B159" t="n">
         <v>97930</v>
@@ -18274,7 +18317,7 @@
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
@@ -18288,10 +18331,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>563835</v>
+        <v>563765</v>
       </c>
       <c r="R159" t="n">
-        <v>6704743</v>
+        <v>6704626</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -18350,7 +18393,7 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>119874644</v>
+        <v>119874633</v>
       </c>
       <c r="B160" t="n">
         <v>97930</v>
@@ -18399,10 +18442,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>563984</v>
+        <v>563741</v>
       </c>
       <c r="R160" t="n">
-        <v>6704957</v>
+        <v>6704721</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -18461,10 +18504,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>119874616</v>
+        <v>119874576</v>
       </c>
       <c r="B161" t="n">
-        <v>97930</v>
+        <v>90580</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -18473,47 +18516,38 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I161" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J161" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr"/>
       <c r="P161" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>563993</v>
+        <v>563718</v>
       </c>
       <c r="R161" t="n">
-        <v>6705035</v>
+        <v>6704695</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -18572,10 +18606,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>119874593</v>
+        <v>119874566</v>
       </c>
       <c r="B162" t="n">
-        <v>90580</v>
+        <v>90923</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
@@ -18584,25 +18618,25 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>1202</v>
+        <v>2062</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -18612,10 +18646,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>563710</v>
+        <v>564137</v>
       </c>
       <c r="R162" t="n">
-        <v>6704663</v>
+        <v>6705070</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -18674,7 +18708,7 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>119874575</v>
+        <v>119874591</v>
       </c>
       <c r="B163" t="n">
         <v>90580</v>
@@ -18714,10 +18748,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>563720</v>
+        <v>564204</v>
       </c>
       <c r="R163" t="n">
-        <v>6704700</v>
+        <v>6705194</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -18776,10 +18810,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>119874581</v>
+        <v>119874625</v>
       </c>
       <c r="B164" t="n">
-        <v>90580</v>
+        <v>97930</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -18788,38 +18822,47 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I164" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P164" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>563792</v>
+        <v>564201</v>
       </c>
       <c r="R164" t="n">
-        <v>6704700</v>
+        <v>6705184</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -18878,7 +18921,7 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>119874624</v>
+        <v>119874630</v>
       </c>
       <c r="B165" t="n">
         <v>97930</v>
@@ -18913,7 +18956,7 @@
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
@@ -18927,10 +18970,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>563734</v>
+        <v>563815</v>
       </c>
       <c r="R165" t="n">
-        <v>6704595</v>
+        <v>6704815</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -18989,7 +19032,7 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>119874630</v>
+        <v>119874659</v>
       </c>
       <c r="B166" t="n">
         <v>97930</v>
@@ -19024,7 +19067,7 @@
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
@@ -19038,10 +19081,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>563815</v>
+        <v>563746</v>
       </c>
       <c r="R166" t="n">
-        <v>6704815</v>
+        <v>6704720</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -19100,7 +19143,7 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>119874651</v>
+        <v>119874639</v>
       </c>
       <c r="B167" t="n">
         <v>97930</v>
@@ -19135,7 +19178,7 @@
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
@@ -19149,10 +19192,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>564256</v>
+        <v>563718</v>
       </c>
       <c r="R167" t="n">
-        <v>6705293</v>
+        <v>6704563</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -19211,10 +19254,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>119874568</v>
+        <v>119874684</v>
       </c>
       <c r="B168" t="n">
-        <v>90923</v>
+        <v>100194</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
@@ -19223,25 +19266,25 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>2062</v>
+        <v>222498</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -19251,10 +19294,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>563986</v>
+        <v>563956</v>
       </c>
       <c r="R168" t="n">
-        <v>6705032</v>
+        <v>6704876</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -19313,7 +19356,7 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>119874639</v>
+        <v>119874616</v>
       </c>
       <c r="B169" t="n">
         <v>97930</v>
@@ -19348,7 +19391,7 @@
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
@@ -19362,10 +19405,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>563718</v>
+        <v>563993</v>
       </c>
       <c r="R169" t="n">
-        <v>6704563</v>
+        <v>6705035</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -19424,10 +19467,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>119874572</v>
+        <v>119874627</v>
       </c>
       <c r="B170" t="n">
-        <v>90580</v>
+        <v>97930</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
@@ -19436,38 +19479,54 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I170" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L170" t="inlineStr"/>
+      <c r="N170" t="inlineStr"/>
       <c r="P170" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>563815</v>
+        <v>563813</v>
       </c>
       <c r="R170" t="n">
-        <v>6704789</v>
+        <v>6704796</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -19502,12 +19561,18 @@
           <t>2024-09-20</t>
         </is>
       </c>
+      <c r="AC170" t="inlineStr">
+        <is>
+          <t>2 blomstjälkar</t>
+        </is>
+      </c>
       <c r="AD170" t="b">
         <v>0</v>
       </c>
       <c r="AE170" t="b">
         <v>0</v>
       </c>
+      <c r="AF170" t="inlineStr"/>
       <c r="AG170" t="b">
         <v>0</v>
       </c>
@@ -19526,10 +19591,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>119874596</v>
+        <v>119874606</v>
       </c>
       <c r="B171" t="n">
-        <v>57473</v>
+        <v>90864</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
@@ -19542,46 +19607,34 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>103021</v>
+        <v>658</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I171" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K171" t="inlineStr"/>
-      <c r="L171" t="inlineStr"/>
-      <c r="M171" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N171" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr"/>
       <c r="P171" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>563633</v>
+        <v>563784</v>
       </c>
       <c r="R171" t="n">
-        <v>6704498</v>
+        <v>6704721</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -19614,6 +19667,11 @@
       <c r="AA171" t="inlineStr">
         <is>
           <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AC171" t="inlineStr">
+        <is>
+          <t>Äldre fruktkropp</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -19640,10 +19698,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>119874658</v>
+        <v>119874582</v>
       </c>
       <c r="B172" t="n">
-        <v>97930</v>
+        <v>90580</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
@@ -19652,47 +19710,38 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I172" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J172" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr"/>
       <c r="P172" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>563749</v>
+        <v>563958</v>
       </c>
       <c r="R172" t="n">
-        <v>6704725</v>
+        <v>6704952</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -19751,7 +19800,7 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>119874642</v>
+        <v>119874612</v>
       </c>
       <c r="B173" t="n">
         <v>97930</v>
@@ -19786,7 +19835,7 @@
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
@@ -19794,16 +19843,23 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L173" t="inlineStr"/>
+      <c r="N173" t="inlineStr"/>
       <c r="P173" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>563974</v>
+        <v>564201</v>
       </c>
       <c r="R173" t="n">
-        <v>6704953</v>
+        <v>6705191</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -19838,12 +19894,18 @@
           <t>2024-09-20</t>
         </is>
       </c>
+      <c r="AC173" t="inlineStr">
+        <is>
+          <t>1 blomstjälk</t>
+        </is>
+      </c>
       <c r="AD173" t="b">
         <v>0</v>
       </c>
       <c r="AE173" t="b">
         <v>0</v>
       </c>
+      <c r="AF173" t="inlineStr"/>
       <c r="AG173" t="b">
         <v>0</v>
       </c>
@@ -19862,7 +19924,7 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>119874655</v>
+        <v>119874624</v>
       </c>
       <c r="B174" t="n">
         <v>97930</v>
@@ -19897,7 +19959,7 @@
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
@@ -19911,10 +19973,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>563757</v>
+        <v>563734</v>
       </c>
       <c r="R174" t="n">
-        <v>6704730</v>
+        <v>6704595</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -19973,7 +20035,7 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>119874627</v>
+        <v>119874632</v>
       </c>
       <c r="B175" t="n">
         <v>97930</v>
@@ -20008,7 +20070,7 @@
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
@@ -20016,23 +20078,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K175" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L175" t="inlineStr"/>
-      <c r="N175" t="inlineStr"/>
       <c r="P175" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>563813</v>
+        <v>563770</v>
       </c>
       <c r="R175" t="n">
-        <v>6704796</v>
+        <v>6704729</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -20067,18 +20122,12 @@
           <t>2024-09-20</t>
         </is>
       </c>
-      <c r="AC175" t="inlineStr">
-        <is>
-          <t>2 blomstjälkar</t>
-        </is>
-      </c>
       <c r="AD175" t="b">
         <v>0</v>
       </c>
       <c r="AE175" t="b">
         <v>0</v>
       </c>
-      <c r="AF175" t="inlineStr"/>
       <c r="AG175" t="b">
         <v>0</v>
       </c>
@@ -20097,10 +20146,10 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>119874612</v>
+        <v>119874593</v>
       </c>
       <c r="B176" t="n">
-        <v>97930</v>
+        <v>90580</v>
       </c>
       <c r="C176" t="inlineStr">
         <is>
@@ -20109,54 +20158,38 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I176" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J176" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K176" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L176" t="inlineStr"/>
-      <c r="N176" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr"/>
       <c r="P176" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>564201</v>
+        <v>563710</v>
       </c>
       <c r="R176" t="n">
-        <v>6705191</v>
+        <v>6704663</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -20191,18 +20224,12 @@
           <t>2024-09-20</t>
         </is>
       </c>
-      <c r="AC176" t="inlineStr">
-        <is>
-          <t>1 blomstjälk</t>
-        </is>
-      </c>
       <c r="AD176" t="b">
         <v>0</v>
       </c>
       <c r="AE176" t="b">
         <v>0</v>
       </c>
-      <c r="AF176" t="inlineStr"/>
       <c r="AG176" t="b">
         <v>0</v>
       </c>
@@ -20221,10 +20248,10 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>119874619</v>
+        <v>119874571</v>
       </c>
       <c r="B177" t="n">
-        <v>97930</v>
+        <v>90580</v>
       </c>
       <c r="C177" t="inlineStr">
         <is>
@@ -20233,47 +20260,38 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I177" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J177" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr"/>
       <c r="P177" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>564203</v>
+        <v>563816</v>
       </c>
       <c r="R177" t="n">
-        <v>6705186</v>
+        <v>6704792</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -20332,10 +20350,10 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>119874659</v>
+        <v>119874677</v>
       </c>
       <c r="B178" t="n">
-        <v>97930</v>
+        <v>93953</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>
@@ -20344,47 +20362,38 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>220787</v>
+        <v>2383</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bågpraktmossa</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Plagiomnium medium</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I178" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J178" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Bruch &amp; Schimp.) T.J.Kop.</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr"/>
       <c r="P178" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>563746</v>
+        <v>563925</v>
       </c>
       <c r="R178" t="n">
-        <v>6704720</v>
+        <v>6704880</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -20443,10 +20452,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>119874685</v>
+        <v>119874647</v>
       </c>
       <c r="B179" t="n">
-        <v>8421</v>
+        <v>97930</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
@@ -20455,43 +20464,54 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>106554</v>
+        <v>220787</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I179" t="inlineStr"/>
-      <c r="M179" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J179" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L179" t="inlineStr"/>
+      <c r="N179" t="inlineStr"/>
       <c r="P179" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>563845</v>
+        <v>564036</v>
       </c>
       <c r="R179" t="n">
-        <v>6704771</v>
+        <v>6705043</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -20526,12 +20546,18 @@
           <t>2024-09-20</t>
         </is>
       </c>
+      <c r="AC179" t="inlineStr">
+        <is>
+          <t>1 blomstjälk</t>
+        </is>
+      </c>
       <c r="AD179" t="b">
         <v>0</v>
       </c>
       <c r="AE179" t="b">
         <v>0</v>
       </c>
+      <c r="AF179" t="inlineStr"/>
       <c r="AG179" t="b">
         <v>0</v>
       </c>
@@ -20550,10 +20576,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>119874684</v>
+        <v>119874597</v>
       </c>
       <c r="B180" t="n">
-        <v>100194</v>
+        <v>91512</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
@@ -20566,21 +20592,21 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>222498</v>
+        <v>4769</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
@@ -20590,10 +20616,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>563956</v>
+        <v>563943</v>
       </c>
       <c r="R180" t="n">
-        <v>6704876</v>
+        <v>6704878</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -20652,10 +20678,10 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>119874609</v>
+        <v>119874678</v>
       </c>
       <c r="B181" t="n">
-        <v>90972</v>
+        <v>5169</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
@@ -20664,33 +20690,43 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>6040186</v>
+        <v>100526</v>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
+      <c r="M181" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P181" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>564083</v>
+        <v>563957</v>
       </c>
       <c r="R181" t="n">
-        <v>6705090</v>
+        <v>6704878</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -20749,10 +20785,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>119874569</v>
+        <v>119874608</v>
       </c>
       <c r="B182" t="n">
-        <v>90580</v>
+        <v>94334</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
@@ -20761,25 +20797,25 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>1202</v>
+        <v>2809</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
@@ -20789,10 +20825,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>564137</v>
+        <v>563944</v>
       </c>
       <c r="R182" t="n">
-        <v>6705071</v>
+        <v>6704880</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -20851,10 +20887,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>119874608</v>
+        <v>119874572</v>
       </c>
       <c r="B183" t="n">
-        <v>94334</v>
+        <v>90580</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
@@ -20863,25 +20899,25 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>2809</v>
+        <v>1202</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
@@ -20891,10 +20927,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>563944</v>
+        <v>563815</v>
       </c>
       <c r="R183" t="n">
-        <v>6704880</v>
+        <v>6704789</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -20953,10 +20989,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>119874615</v>
+        <v>119874580</v>
       </c>
       <c r="B184" t="n">
-        <v>97930</v>
+        <v>90580</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
@@ -20965,47 +21001,38 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I184" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J184" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr"/>
       <c r="P184" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>563748</v>
+        <v>563702</v>
       </c>
       <c r="R184" t="n">
-        <v>6704608</v>
+        <v>6704652</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -21064,10 +21091,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>119874623</v>
+        <v>119874567</v>
       </c>
       <c r="B185" t="n">
-        <v>97930</v>
+        <v>90923</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
@@ -21080,43 +21107,34 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>220787</v>
+        <v>2062</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I185" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J185" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr"/>
       <c r="P185" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>563637</v>
+        <v>564000</v>
       </c>
       <c r="R185" t="n">
-        <v>6704477</v>
+        <v>6705011</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -21175,10 +21193,10 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>119874668</v>
+        <v>119874619</v>
       </c>
       <c r="B186" t="n">
-        <v>74593</v>
+        <v>97930</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
@@ -21187,38 +21205,47 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>6426</v>
+        <v>220787</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I186" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J186" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P186" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>563937</v>
+        <v>564203</v>
       </c>
       <c r="R186" t="n">
-        <v>6704867</v>
+        <v>6705186</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -21277,10 +21304,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>119874621</v>
+        <v>119874685</v>
       </c>
       <c r="B187" t="n">
-        <v>97930</v>
+        <v>8421</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
@@ -21289,35 +21316,31 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>220787</v>
+        <v>106554</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I187" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J187" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr"/>
+      <c r="M187" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P187" t="inlineStr">
@@ -21326,10 +21349,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>564283</v>
+        <v>563845</v>
       </c>
       <c r="R187" t="n">
-        <v>6705293</v>
+        <v>6704771</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -21388,7 +21411,7 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>119874634</v>
+        <v>119874646</v>
       </c>
       <c r="B188" t="n">
         <v>97930</v>
@@ -21423,7 +21446,7 @@
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
@@ -21437,10 +21460,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>563712</v>
+        <v>563995</v>
       </c>
       <c r="R188" t="n">
-        <v>6704670</v>
+        <v>6704966</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -21499,10 +21522,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>119874583</v>
+        <v>119874663</v>
       </c>
       <c r="B189" t="n">
-        <v>90580</v>
+        <v>97930</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
@@ -21511,38 +21534,47 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E189" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I189" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J189" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P189" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>563996</v>
+        <v>563835</v>
       </c>
       <c r="R189" t="n">
-        <v>6705007</v>
+        <v>6704743</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -21601,10 +21633,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>119874580</v>
+        <v>119874615</v>
       </c>
       <c r="B190" t="n">
-        <v>90580</v>
+        <v>97930</v>
       </c>
       <c r="C190" t="inlineStr">
         <is>
@@ -21613,38 +21645,47 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E190" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I190" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J190" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P190" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>563702</v>
+        <v>563748</v>
       </c>
       <c r="R190" t="n">
-        <v>6704652</v>
+        <v>6704608</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -21703,10 +21744,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>119874617</v>
+        <v>119874573</v>
       </c>
       <c r="B191" t="n">
-        <v>97930</v>
+        <v>90580</v>
       </c>
       <c r="C191" t="inlineStr">
         <is>
@@ -21715,47 +21756,38 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E191" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I191" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J191" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr"/>
       <c r="P191" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>563833</v>
+        <v>563794</v>
       </c>
       <c r="R191" t="n">
-        <v>6704788</v>
+        <v>6704792</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -21814,10 +21846,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>119874641</v>
+        <v>119874583</v>
       </c>
       <c r="B192" t="n">
-        <v>97930</v>
+        <v>90580</v>
       </c>
       <c r="C192" t="inlineStr">
         <is>
@@ -21826,47 +21858,38 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E192" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I192" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J192" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr"/>
       <c r="P192" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>563808</v>
+        <v>563996</v>
       </c>
       <c r="R192" t="n">
-        <v>6704697</v>
+        <v>6705007</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -22027,10 +22050,10 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>119874628</v>
+        <v>119874574</v>
       </c>
       <c r="B194" t="n">
-        <v>97930</v>
+        <v>90580</v>
       </c>
       <c r="C194" t="inlineStr">
         <is>
@@ -22039,47 +22062,38 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I194" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J194" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr"/>
       <c r="P194" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>564206</v>
+        <v>563796</v>
       </c>
       <c r="R194" t="n">
-        <v>6705189</v>
+        <v>6704785</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -22138,10 +22152,10 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>119874652</v>
+        <v>119874596</v>
       </c>
       <c r="B195" t="n">
-        <v>97930</v>
+        <v>57473</v>
       </c>
       <c r="C195" t="inlineStr">
         <is>
@@ -22150,47 +22164,50 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J195" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K195" t="inlineStr"/>
+      <c r="L195" t="inlineStr"/>
+      <c r="M195" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N195" t="inlineStr"/>
       <c r="P195" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>563976</v>
+        <v>563633</v>
       </c>
       <c r="R195" t="n">
-        <v>6704966</v>
+        <v>6704498</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -22249,10 +22266,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>119874590</v>
+        <v>119874655</v>
       </c>
       <c r="B196" t="n">
-        <v>90580</v>
+        <v>97930</v>
       </c>
       <c r="C196" t="inlineStr">
         <is>
@@ -22261,38 +22278,47 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E196" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I196" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J196" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P196" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>564015</v>
+        <v>563757</v>
       </c>
       <c r="R196" t="n">
-        <v>6705047</v>
+        <v>6704730</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -22351,10 +22377,10 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>119874605</v>
+        <v>119874642</v>
       </c>
       <c r="B197" t="n">
-        <v>90351</v>
+        <v>97930</v>
       </c>
       <c r="C197" t="inlineStr">
         <is>
@@ -22363,38 +22389,47 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>3215</v>
+        <v>220787</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I197" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J197" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P197" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>563929</v>
+        <v>563974</v>
       </c>
       <c r="R197" t="n">
-        <v>6704878</v>
+        <v>6704953</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -22453,10 +22488,10 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>119874632</v>
+        <v>119874590</v>
       </c>
       <c r="B198" t="n">
-        <v>97930</v>
+        <v>90580</v>
       </c>
       <c r="C198" t="inlineStr">
         <is>
@@ -22465,47 +22500,38 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E198" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I198" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J198" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr"/>
       <c r="P198" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>563770</v>
+        <v>564015</v>
       </c>
       <c r="R198" t="n">
-        <v>6704729</v>
+        <v>6705047</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -22564,10 +22590,10 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>119874566</v>
+        <v>119874588</v>
       </c>
       <c r="B199" t="n">
-        <v>90923</v>
+        <v>90580</v>
       </c>
       <c r="C199" t="inlineStr">
         <is>
@@ -22576,25 +22602,25 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E199" t="n">
-        <v>2062</v>
+        <v>1202</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I199" t="inlineStr"/>
@@ -22604,10 +22630,10 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>564137</v>
+        <v>564011</v>
       </c>
       <c r="R199" t="n">
-        <v>6705070</v>
+        <v>6705060</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -22666,10 +22692,10 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>119874665</v>
+        <v>119874607</v>
       </c>
       <c r="B200" t="n">
-        <v>97930</v>
+        <v>90864</v>
       </c>
       <c r="C200" t="inlineStr">
         <is>
@@ -22678,47 +22704,38 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I200" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J200" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr"/>
       <c r="P200" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>564008</v>
+        <v>563821</v>
       </c>
       <c r="R200" t="n">
-        <v>6704979</v>
+        <v>6704817</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -22777,10 +22794,10 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>119874661</v>
+        <v>119874581</v>
       </c>
       <c r="B201" t="n">
-        <v>97930</v>
+        <v>90580</v>
       </c>
       <c r="C201" t="inlineStr">
         <is>
@@ -22789,47 +22806,38 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E201" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I201" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J201" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr"/>
       <c r="P201" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>563645</v>
+        <v>563792</v>
       </c>
       <c r="R201" t="n">
-        <v>6704515</v>
+        <v>6704700</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -22888,10 +22896,10 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>119874646</v>
+        <v>119874681</v>
       </c>
       <c r="B202" t="n">
-        <v>97930</v>
+        <v>5169</v>
       </c>
       <c r="C202" t="inlineStr">
         <is>
@@ -22900,35 +22908,31 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E202" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I202" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J202" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr"/>
+      <c r="M202" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P202" t="inlineStr">
@@ -22937,10 +22941,10 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>563995</v>
+        <v>563825</v>
       </c>
       <c r="R202" t="n">
-        <v>6704966</v>
+        <v>6704705</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -22999,10 +23003,10 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>119874682</v>
+        <v>119874644</v>
       </c>
       <c r="B203" t="n">
-        <v>5169</v>
+        <v>97930</v>
       </c>
       <c r="C203" t="inlineStr">
         <is>
@@ -23011,31 +23015,35 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E203" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I203" t="inlineStr"/>
-      <c r="M203" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J203" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P203" t="inlineStr">
@@ -23044,10 +23052,10 @@
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>564000</v>
+        <v>563984</v>
       </c>
       <c r="R203" t="n">
-        <v>6704958</v>
+        <v>6704957</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -23106,10 +23114,10 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>119874597</v>
+        <v>119874658</v>
       </c>
       <c r="B204" t="n">
-        <v>91512</v>
+        <v>97930</v>
       </c>
       <c r="C204" t="inlineStr">
         <is>
@@ -23118,38 +23126,47 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E204" t="n">
-        <v>4769</v>
+        <v>220787</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I204" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J204" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P204" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>563943</v>
+        <v>563749</v>
       </c>
       <c r="R204" t="n">
-        <v>6704878</v>
+        <v>6704725</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>
@@ -23208,10 +23225,10 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>119874626</v>
+        <v>119874585</v>
       </c>
       <c r="B205" t="n">
-        <v>97930</v>
+        <v>90580</v>
       </c>
       <c r="C205" t="inlineStr">
         <is>
@@ -23220,54 +23237,38 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E205" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I205" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J205" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K205" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L205" t="inlineStr"/>
-      <c r="N205" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr"/>
       <c r="P205" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>564019</v>
+        <v>563986</v>
       </c>
       <c r="R205" t="n">
-        <v>6704997</v>
+        <v>6705041</v>
       </c>
       <c r="S205" t="n">
         <v>10</v>
@@ -23302,18 +23303,12 @@
           <t>2024-09-20</t>
         </is>
       </c>
-      <c r="AC205" t="inlineStr">
-        <is>
-          <t>1 blomstjälk</t>
-        </is>
-      </c>
       <c r="AD205" t="b">
         <v>0</v>
       </c>
       <c r="AE205" t="b">
         <v>0</v>
       </c>
-      <c r="AF205" t="inlineStr"/>
       <c r="AG205" t="b">
         <v>0</v>
       </c>
@@ -23332,10 +23327,10 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>119874591</v>
+        <v>119874599</v>
       </c>
       <c r="B206" t="n">
-        <v>90580</v>
+        <v>57336</v>
       </c>
       <c r="C206" t="inlineStr">
         <is>
@@ -23348,34 +23343,39 @@
         </is>
       </c>
       <c r="E206" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I206" t="inlineStr"/>
+      <c r="M206" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P206" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>564204</v>
+        <v>563944</v>
       </c>
       <c r="R206" t="n">
-        <v>6705194</v>
+        <v>6704948</v>
       </c>
       <c r="S206" t="n">
         <v>10</v>
@@ -23434,7 +23434,7 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>119874681</v>
+        <v>119874682</v>
       </c>
       <c r="B207" t="n">
         <v>5169</v>
@@ -23479,10 +23479,10 @@
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>563825</v>
+        <v>564000</v>
       </c>
       <c r="R207" t="n">
-        <v>6704705</v>
+        <v>6704958</v>
       </c>
       <c r="S207" t="n">
         <v>10</v>
@@ -23541,7 +23541,7 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>119874649</v>
+        <v>119874621</v>
       </c>
       <c r="B208" t="n">
         <v>97930</v>
@@ -23576,7 +23576,7 @@
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J208" t="inlineStr">
@@ -23590,10 +23590,10 @@
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>563765</v>
+        <v>564283</v>
       </c>
       <c r="R208" t="n">
-        <v>6704626</v>
+        <v>6705293</v>
       </c>
       <c r="S208" t="n">
         <v>10</v>
@@ -23652,7 +23652,7 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>119874613</v>
+        <v>119874652</v>
       </c>
       <c r="B209" t="n">
         <v>97930</v>
@@ -23687,7 +23687,7 @@
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J209" t="inlineStr">
@@ -23701,10 +23701,10 @@
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>563794</v>
+        <v>563976</v>
       </c>
       <c r="R209" t="n">
-        <v>6704750</v>
+        <v>6704966</v>
       </c>
       <c r="S209" t="n">
         <v>10</v>

--- a/artfynd/A 58548-2022 artfynd.xlsx
+++ b/artfynd/A 58548-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY209"/>
+  <dimension ref="A1:AY221"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23761,6 +23761,1282 @@
       </c>
       <c r="AY209" t="inlineStr"/>
     </row>
+    <row r="210">
+      <c r="A210" t="n">
+        <v>122010893</v>
+      </c>
+      <c r="B210" t="n">
+        <v>90707</v>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E210" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I210" t="inlineStr"/>
+      <c r="P210" t="inlineStr">
+        <is>
+          <t>Pellkärret, Dlr</t>
+        </is>
+      </c>
+      <c r="Q210" t="n">
+        <v>563600</v>
+      </c>
+      <c r="R210" t="n">
+        <v>6704463</v>
+      </c>
+      <c r="S210" t="n">
+        <v>10</v>
+      </c>
+      <c r="T210" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U210" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V210" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W210" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y210" t="inlineStr">
+        <is>
+          <t>2025-01-09</t>
+        </is>
+      </c>
+      <c r="AA210" t="inlineStr">
+        <is>
+          <t>2025-01-09</t>
+        </is>
+      </c>
+      <c r="AD210" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE210" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG210" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT210" t="inlineStr"/>
+      <c r="AW210" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX210" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY210" t="inlineStr"/>
+    </row>
+    <row r="211">
+      <c r="A211" t="n">
+        <v>122010908</v>
+      </c>
+      <c r="B211" t="n">
+        <v>5173</v>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E211" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr"/>
+      <c r="M211" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P211" t="inlineStr">
+        <is>
+          <t>Pellkärret, Dlr</t>
+        </is>
+      </c>
+      <c r="Q211" t="n">
+        <v>563625</v>
+      </c>
+      <c r="R211" t="n">
+        <v>6704469</v>
+      </c>
+      <c r="S211" t="n">
+        <v>10</v>
+      </c>
+      <c r="T211" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U211" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V211" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W211" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y211" t="inlineStr">
+        <is>
+          <t>2025-01-09</t>
+        </is>
+      </c>
+      <c r="AA211" t="inlineStr">
+        <is>
+          <t>2025-01-09</t>
+        </is>
+      </c>
+      <c r="AD211" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE211" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG211" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT211" t="inlineStr"/>
+      <c r="AW211" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX211" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY211" t="inlineStr"/>
+    </row>
+    <row r="212">
+      <c r="A212" t="n">
+        <v>122010907</v>
+      </c>
+      <c r="B212" t="n">
+        <v>5173</v>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E212" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr"/>
+      <c r="M212" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P212" t="inlineStr">
+        <is>
+          <t>Pellkärret, Dlr</t>
+        </is>
+      </c>
+      <c r="Q212" t="n">
+        <v>563819</v>
+      </c>
+      <c r="R212" t="n">
+        <v>6704826</v>
+      </c>
+      <c r="S212" t="n">
+        <v>10</v>
+      </c>
+      <c r="T212" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U212" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V212" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W212" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y212" t="inlineStr">
+        <is>
+          <t>2025-01-09</t>
+        </is>
+      </c>
+      <c r="AA212" t="inlineStr">
+        <is>
+          <t>2025-01-09</t>
+        </is>
+      </c>
+      <c r="AD212" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE212" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG212" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT212" t="inlineStr"/>
+      <c r="AW212" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX212" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY212" t="inlineStr"/>
+    </row>
+    <row r="213">
+      <c r="A213" t="n">
+        <v>122010894</v>
+      </c>
+      <c r="B213" t="n">
+        <v>90742</v>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E213" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I213" t="inlineStr"/>
+      <c r="P213" t="inlineStr">
+        <is>
+          <t>Pellkärret, Dlr</t>
+        </is>
+      </c>
+      <c r="Q213" t="n">
+        <v>564343</v>
+      </c>
+      <c r="R213" t="n">
+        <v>6705432</v>
+      </c>
+      <c r="S213" t="n">
+        <v>10</v>
+      </c>
+      <c r="T213" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U213" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V213" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W213" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y213" t="inlineStr">
+        <is>
+          <t>2025-01-09</t>
+        </is>
+      </c>
+      <c r="AA213" t="inlineStr">
+        <is>
+          <t>2025-01-09</t>
+        </is>
+      </c>
+      <c r="AD213" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE213" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG213" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT213" t="inlineStr"/>
+      <c r="AW213" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX213" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY213" t="inlineStr"/>
+    </row>
+    <row r="214">
+      <c r="A214" t="n">
+        <v>122010895</v>
+      </c>
+      <c r="B214" t="n">
+        <v>90742</v>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E214" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I214" t="inlineStr"/>
+      <c r="P214" t="inlineStr">
+        <is>
+          <t>Pellkärret, Dlr</t>
+        </is>
+      </c>
+      <c r="Q214" t="n">
+        <v>563619</v>
+      </c>
+      <c r="R214" t="n">
+        <v>6704484</v>
+      </c>
+      <c r="S214" t="n">
+        <v>10</v>
+      </c>
+      <c r="T214" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U214" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V214" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W214" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y214" t="inlineStr">
+        <is>
+          <t>2025-01-09</t>
+        </is>
+      </c>
+      <c r="AA214" t="inlineStr">
+        <is>
+          <t>2025-01-09</t>
+        </is>
+      </c>
+      <c r="AD214" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE214" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG214" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT214" t="inlineStr"/>
+      <c r="AW214" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX214" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY214" t="inlineStr"/>
+    </row>
+    <row r="215">
+      <c r="A215" t="n">
+        <v>122010906</v>
+      </c>
+      <c r="B215" t="n">
+        <v>5173</v>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E215" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I215" t="inlineStr"/>
+      <c r="M215" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P215" t="inlineStr">
+        <is>
+          <t>Pellkärret, Dlr</t>
+        </is>
+      </c>
+      <c r="Q215" t="n">
+        <v>563921</v>
+      </c>
+      <c r="R215" t="n">
+        <v>6704919</v>
+      </c>
+      <c r="S215" t="n">
+        <v>10</v>
+      </c>
+      <c r="T215" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U215" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V215" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W215" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y215" t="inlineStr">
+        <is>
+          <t>2025-01-09</t>
+        </is>
+      </c>
+      <c r="AA215" t="inlineStr">
+        <is>
+          <t>2025-01-09</t>
+        </is>
+      </c>
+      <c r="AD215" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE215" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG215" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT215" t="inlineStr"/>
+      <c r="AW215" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX215" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY215" t="inlineStr"/>
+    </row>
+    <row r="216">
+      <c r="A216" t="n">
+        <v>122010902</v>
+      </c>
+      <c r="B216" t="n">
+        <v>57381</v>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E216" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I216" t="inlineStr"/>
+      <c r="M216" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P216" t="inlineStr">
+        <is>
+          <t>Pellkärret, Dlr</t>
+        </is>
+      </c>
+      <c r="Q216" t="n">
+        <v>563803</v>
+      </c>
+      <c r="R216" t="n">
+        <v>6704669</v>
+      </c>
+      <c r="S216" t="n">
+        <v>10</v>
+      </c>
+      <c r="T216" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U216" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V216" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W216" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y216" t="inlineStr">
+        <is>
+          <t>2025-01-09</t>
+        </is>
+      </c>
+      <c r="AA216" t="inlineStr">
+        <is>
+          <t>2025-01-09</t>
+        </is>
+      </c>
+      <c r="AD216" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE216" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG216" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT216" t="inlineStr"/>
+      <c r="AW216" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX216" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY216" t="inlineStr"/>
+    </row>
+    <row r="217">
+      <c r="A217" t="n">
+        <v>122010909</v>
+      </c>
+      <c r="B217" t="n">
+        <v>5173</v>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E217" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I217" t="inlineStr"/>
+      <c r="M217" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P217" t="inlineStr">
+        <is>
+          <t>Pellkärret, Dlr</t>
+        </is>
+      </c>
+      <c r="Q217" t="n">
+        <v>563850</v>
+      </c>
+      <c r="R217" t="n">
+        <v>6704731</v>
+      </c>
+      <c r="S217" t="n">
+        <v>10</v>
+      </c>
+      <c r="T217" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U217" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V217" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W217" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y217" t="inlineStr">
+        <is>
+          <t>2025-01-09</t>
+        </is>
+      </c>
+      <c r="AA217" t="inlineStr">
+        <is>
+          <t>2025-01-09</t>
+        </is>
+      </c>
+      <c r="AD217" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE217" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG217" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT217" t="inlineStr"/>
+      <c r="AW217" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX217" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY217" t="inlineStr"/>
+    </row>
+    <row r="218">
+      <c r="A218" t="n">
+        <v>122010904</v>
+      </c>
+      <c r="B218" t="n">
+        <v>98131</v>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E218" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I218" t="inlineStr"/>
+      <c r="J218" t="inlineStr"/>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L218" t="inlineStr"/>
+      <c r="N218" t="inlineStr"/>
+      <c r="P218" t="inlineStr">
+        <is>
+          <t>Pellkärret, Dlr</t>
+        </is>
+      </c>
+      <c r="Q218" t="n">
+        <v>563814</v>
+      </c>
+      <c r="R218" t="n">
+        <v>6704820</v>
+      </c>
+      <c r="S218" t="n">
+        <v>10</v>
+      </c>
+      <c r="T218" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U218" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V218" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W218" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y218" t="inlineStr">
+        <is>
+          <t>2025-01-09</t>
+        </is>
+      </c>
+      <c r="AA218" t="inlineStr">
+        <is>
+          <t>2025-01-09</t>
+        </is>
+      </c>
+      <c r="AD218" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE218" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF218" t="inlineStr"/>
+      <c r="AG218" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT218" t="inlineStr"/>
+      <c r="AW218" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX218" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY218" t="inlineStr"/>
+    </row>
+    <row r="219">
+      <c r="A219" t="n">
+        <v>122010898</v>
+      </c>
+      <c r="B219" t="n">
+        <v>57518</v>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E219" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I219" t="inlineStr"/>
+      <c r="P219" t="inlineStr">
+        <is>
+          <t>Pellkärret, Dlr</t>
+        </is>
+      </c>
+      <c r="Q219" t="n">
+        <v>563884</v>
+      </c>
+      <c r="R219" t="n">
+        <v>6704911</v>
+      </c>
+      <c r="S219" t="n">
+        <v>10</v>
+      </c>
+      <c r="T219" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U219" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V219" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W219" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y219" t="inlineStr">
+        <is>
+          <t>2025-01-09</t>
+        </is>
+      </c>
+      <c r="AA219" t="inlineStr">
+        <is>
+          <t>2025-01-09</t>
+        </is>
+      </c>
+      <c r="AD219" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE219" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG219" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT219" t="inlineStr"/>
+      <c r="AW219" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX219" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY219" t="inlineStr"/>
+    </row>
+    <row r="220">
+      <c r="A220" t="n">
+        <v>122010905</v>
+      </c>
+      <c r="B220" t="n">
+        <v>98131</v>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E220" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I220" t="inlineStr"/>
+      <c r="J220" t="inlineStr"/>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L220" t="inlineStr"/>
+      <c r="N220" t="inlineStr"/>
+      <c r="P220" t="inlineStr">
+        <is>
+          <t>Pellkärret, Dlr</t>
+        </is>
+      </c>
+      <c r="Q220" t="n">
+        <v>563702</v>
+      </c>
+      <c r="R220" t="n">
+        <v>6704641</v>
+      </c>
+      <c r="S220" t="n">
+        <v>10</v>
+      </c>
+      <c r="T220" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U220" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V220" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W220" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y220" t="inlineStr">
+        <is>
+          <t>2025-01-09</t>
+        </is>
+      </c>
+      <c r="AA220" t="inlineStr">
+        <is>
+          <t>2025-01-09</t>
+        </is>
+      </c>
+      <c r="AD220" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE220" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF220" t="inlineStr"/>
+      <c r="AG220" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT220" t="inlineStr"/>
+      <c r="AW220" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX220" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY220" t="inlineStr"/>
+    </row>
+    <row r="221">
+      <c r="A221" t="n">
+        <v>122010903</v>
+      </c>
+      <c r="B221" t="n">
+        <v>98131</v>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E221" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr"/>
+      <c r="J221" t="inlineStr"/>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L221" t="inlineStr"/>
+      <c r="N221" t="inlineStr"/>
+      <c r="P221" t="inlineStr">
+        <is>
+          <t>Pellkärret, Dlr</t>
+        </is>
+      </c>
+      <c r="Q221" t="n">
+        <v>564274</v>
+      </c>
+      <c r="R221" t="n">
+        <v>6705386</v>
+      </c>
+      <c r="S221" t="n">
+        <v>10</v>
+      </c>
+      <c r="T221" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U221" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V221" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W221" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y221" t="inlineStr">
+        <is>
+          <t>2025-01-09</t>
+        </is>
+      </c>
+      <c r="AA221" t="inlineStr">
+        <is>
+          <t>2025-01-09</t>
+        </is>
+      </c>
+      <c r="AD221" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE221" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF221" t="inlineStr"/>
+      <c r="AG221" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT221" t="inlineStr"/>
+      <c r="AW221" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX221" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY221" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 58548-2022 artfynd.xlsx
+++ b/artfynd/A 58548-2022 artfynd.xlsx
@@ -23763,10 +23763,10 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>122010893</v>
+        <v>122010902</v>
       </c>
       <c r="B210" t="n">
-        <v>90707</v>
+        <v>57381</v>
       </c>
       <c r="C210" t="inlineStr">
         <is>
@@ -23775,38 +23775,43 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E210" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I210" t="inlineStr"/>
+      <c r="M210" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P210" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>563600</v>
+        <v>563803</v>
       </c>
       <c r="R210" t="n">
-        <v>6704463</v>
+        <v>6704669</v>
       </c>
       <c r="S210" t="n">
         <v>10</v>
@@ -23865,10 +23870,10 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>122010908</v>
+        <v>122010903</v>
       </c>
       <c r="B211" t="n">
-        <v>5173</v>
+        <v>98131</v>
       </c>
       <c r="C211" t="inlineStr">
         <is>
@@ -23877,43 +23882,46 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E211" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I211" t="inlineStr"/>
-      <c r="M211" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
+      <c r="J211" t="inlineStr"/>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L211" t="inlineStr"/>
+      <c r="N211" t="inlineStr"/>
       <c r="P211" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>563625</v>
+        <v>564274</v>
       </c>
       <c r="R211" t="n">
-        <v>6704469</v>
+        <v>6705386</v>
       </c>
       <c r="S211" t="n">
         <v>10</v>
@@ -23954,6 +23962,7 @@
       <c r="AE211" t="b">
         <v>0</v>
       </c>
+      <c r="AF211" t="inlineStr"/>
       <c r="AG211" t="b">
         <v>0</v>
       </c>
@@ -23972,10 +23981,10 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>122010907</v>
+        <v>122010893</v>
       </c>
       <c r="B212" t="n">
-        <v>5173</v>
+        <v>90707</v>
       </c>
       <c r="C212" t="inlineStr">
         <is>
@@ -23988,39 +23997,34 @@
         </is>
       </c>
       <c r="E212" t="n">
-        <v>100526</v>
+        <v>5447</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I212" t="inlineStr"/>
-      <c r="M212" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P212" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>563819</v>
+        <v>563600</v>
       </c>
       <c r="R212" t="n">
-        <v>6704826</v>
+        <v>6704463</v>
       </c>
       <c r="S212" t="n">
         <v>10</v>
@@ -24079,10 +24083,10 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>122010894</v>
+        <v>122010909</v>
       </c>
       <c r="B213" t="n">
-        <v>90742</v>
+        <v>5173</v>
       </c>
       <c r="C213" t="inlineStr">
         <is>
@@ -24091,38 +24095,43 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E213" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I213" t="inlineStr"/>
+      <c r="M213" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P213" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>564343</v>
+        <v>563850</v>
       </c>
       <c r="R213" t="n">
-        <v>6705432</v>
+        <v>6704731</v>
       </c>
       <c r="S213" t="n">
         <v>10</v>
@@ -24181,10 +24190,10 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>122010895</v>
+        <v>122010907</v>
       </c>
       <c r="B214" t="n">
-        <v>90742</v>
+        <v>5173</v>
       </c>
       <c r="C214" t="inlineStr">
         <is>
@@ -24193,38 +24202,43 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E214" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I214" t="inlineStr"/>
+      <c r="M214" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P214" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>563619</v>
+        <v>563819</v>
       </c>
       <c r="R214" t="n">
-        <v>6704484</v>
+        <v>6704826</v>
       </c>
       <c r="S214" t="n">
         <v>10</v>
@@ -24283,7 +24297,7 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>122010906</v>
+        <v>122010908</v>
       </c>
       <c r="B215" t="n">
         <v>5173</v>
@@ -24328,10 +24342,10 @@
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>563921</v>
+        <v>563625</v>
       </c>
       <c r="R215" t="n">
-        <v>6704919</v>
+        <v>6704469</v>
       </c>
       <c r="S215" t="n">
         <v>10</v>
@@ -24390,10 +24404,10 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>122010902</v>
+        <v>122010906</v>
       </c>
       <c r="B216" t="n">
-        <v>57381</v>
+        <v>5173</v>
       </c>
       <c r="C216" t="inlineStr">
         <is>
@@ -24402,31 +24416,31 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E216" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I216" t="inlineStr"/>
       <c r="M216" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P216" t="inlineStr">
@@ -24435,10 +24449,10 @@
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>563803</v>
+        <v>563921</v>
       </c>
       <c r="R216" t="n">
-        <v>6704669</v>
+        <v>6704919</v>
       </c>
       <c r="S216" t="n">
         <v>10</v>
@@ -24497,10 +24511,10 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>122010909</v>
+        <v>122010894</v>
       </c>
       <c r="B217" t="n">
-        <v>5173</v>
+        <v>90742</v>
       </c>
       <c r="C217" t="inlineStr">
         <is>
@@ -24509,43 +24523,38 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E217" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I217" t="inlineStr"/>
-      <c r="M217" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P217" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>563850</v>
+        <v>564343</v>
       </c>
       <c r="R217" t="n">
-        <v>6704731</v>
+        <v>6705432</v>
       </c>
       <c r="S217" t="n">
         <v>10</v>
@@ -24604,10 +24613,10 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>122010904</v>
+        <v>122010898</v>
       </c>
       <c r="B218" t="n">
-        <v>98131</v>
+        <v>57518</v>
       </c>
       <c r="C218" t="inlineStr">
         <is>
@@ -24616,46 +24625,38 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E218" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I218" t="inlineStr"/>
-      <c r="J218" t="inlineStr"/>
-      <c r="K218" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L218" t="inlineStr"/>
-      <c r="N218" t="inlineStr"/>
       <c r="P218" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>563814</v>
+        <v>563884</v>
       </c>
       <c r="R218" t="n">
-        <v>6704820</v>
+        <v>6704911</v>
       </c>
       <c r="S218" t="n">
         <v>10</v>
@@ -24696,7 +24697,6 @@
       <c r="AE218" t="b">
         <v>0</v>
       </c>
-      <c r="AF218" t="inlineStr"/>
       <c r="AG218" t="b">
         <v>0</v>
       </c>
@@ -24715,10 +24715,10 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>122010898</v>
+        <v>122010905</v>
       </c>
       <c r="B219" t="n">
-        <v>57518</v>
+        <v>98131</v>
       </c>
       <c r="C219" t="inlineStr">
         <is>
@@ -24727,38 +24727,46 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E219" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I219" t="inlineStr"/>
+      <c r="J219" t="inlineStr"/>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L219" t="inlineStr"/>
+      <c r="N219" t="inlineStr"/>
       <c r="P219" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>563884</v>
+        <v>563702</v>
       </c>
       <c r="R219" t="n">
-        <v>6704911</v>
+        <v>6704641</v>
       </c>
       <c r="S219" t="n">
         <v>10</v>
@@ -24799,6 +24807,7 @@
       <c r="AE219" t="b">
         <v>0</v>
       </c>
+      <c r="AF219" t="inlineStr"/>
       <c r="AG219" t="b">
         <v>0</v>
       </c>
@@ -24817,7 +24826,7 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>122010905</v>
+        <v>122010904</v>
       </c>
       <c r="B220" t="n">
         <v>98131</v>
@@ -24865,10 +24874,10 @@
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>563702</v>
+        <v>563814</v>
       </c>
       <c r="R220" t="n">
-        <v>6704641</v>
+        <v>6704820</v>
       </c>
       <c r="S220" t="n">
         <v>10</v>
@@ -24928,10 +24937,10 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>122010903</v>
+        <v>122010895</v>
       </c>
       <c r="B221" t="n">
-        <v>98131</v>
+        <v>90742</v>
       </c>
       <c r="C221" t="inlineStr">
         <is>
@@ -24940,46 +24949,38 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E221" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I221" t="inlineStr"/>
-      <c r="J221" t="inlineStr"/>
-      <c r="K221" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L221" t="inlineStr"/>
-      <c r="N221" t="inlineStr"/>
       <c r="P221" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>564274</v>
+        <v>563619</v>
       </c>
       <c r="R221" t="n">
-        <v>6705386</v>
+        <v>6704484</v>
       </c>
       <c r="S221" t="n">
         <v>10</v>
@@ -25020,7 +25021,6 @@
       <c r="AE221" t="b">
         <v>0</v>
       </c>
-      <c r="AF221" t="inlineStr"/>
       <c r="AG221" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 58548-2022 artfynd.xlsx
+++ b/artfynd/A 58548-2022 artfynd.xlsx
@@ -23763,10 +23763,10 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>122010902</v>
+        <v>122010904</v>
       </c>
       <c r="B210" t="n">
-        <v>57381</v>
+        <v>98133</v>
       </c>
       <c r="C210" t="inlineStr">
         <is>
@@ -23775,43 +23775,46 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E210" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I210" t="inlineStr"/>
-      <c r="M210" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J210" t="inlineStr"/>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L210" t="inlineStr"/>
+      <c r="N210" t="inlineStr"/>
       <c r="P210" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>563803</v>
+        <v>563814</v>
       </c>
       <c r="R210" t="n">
-        <v>6704669</v>
+        <v>6704820</v>
       </c>
       <c r="S210" t="n">
         <v>10</v>
@@ -23852,6 +23855,7 @@
       <c r="AE210" t="b">
         <v>0</v>
       </c>
+      <c r="AF210" t="inlineStr"/>
       <c r="AG210" t="b">
         <v>0</v>
       </c>
@@ -23870,10 +23874,10 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>122010903</v>
+        <v>122010909</v>
       </c>
       <c r="B211" t="n">
-        <v>98131</v>
+        <v>5173</v>
       </c>
       <c r="C211" t="inlineStr">
         <is>
@@ -23882,46 +23886,43 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E211" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I211" t="inlineStr"/>
-      <c r="J211" t="inlineStr"/>
-      <c r="K211" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L211" t="inlineStr"/>
-      <c r="N211" t="inlineStr"/>
+      <c r="M211" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P211" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>564274</v>
+        <v>563850</v>
       </c>
       <c r="R211" t="n">
-        <v>6705386</v>
+        <v>6704731</v>
       </c>
       <c r="S211" t="n">
         <v>10</v>
@@ -23962,7 +23963,6 @@
       <c r="AE211" t="b">
         <v>0</v>
       </c>
-      <c r="AF211" t="inlineStr"/>
       <c r="AG211" t="b">
         <v>0</v>
       </c>
@@ -23981,10 +23981,10 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>122010893</v>
+        <v>122010894</v>
       </c>
       <c r="B212" t="n">
-        <v>90707</v>
+        <v>90744</v>
       </c>
       <c r="C212" t="inlineStr">
         <is>
@@ -23993,25 +23993,25 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E212" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I212" t="inlineStr"/>
@@ -24021,10 +24021,10 @@
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>563600</v>
+        <v>564343</v>
       </c>
       <c r="R212" t="n">
-        <v>6704463</v>
+        <v>6705432</v>
       </c>
       <c r="S212" t="n">
         <v>10</v>
@@ -24083,10 +24083,10 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>122010909</v>
+        <v>122010902</v>
       </c>
       <c r="B213" t="n">
-        <v>5173</v>
+        <v>57381</v>
       </c>
       <c r="C213" t="inlineStr">
         <is>
@@ -24095,31 +24095,31 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E213" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I213" t="inlineStr"/>
       <c r="M213" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P213" t="inlineStr">
@@ -24128,10 +24128,10 @@
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>563850</v>
+        <v>563803</v>
       </c>
       <c r="R213" t="n">
-        <v>6704731</v>
+        <v>6704669</v>
       </c>
       <c r="S213" t="n">
         <v>10</v>
@@ -24190,7 +24190,7 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>122010907</v>
+        <v>122010908</v>
       </c>
       <c r="B214" t="n">
         <v>5173</v>
@@ -24235,10 +24235,10 @@
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>563819</v>
+        <v>563625</v>
       </c>
       <c r="R214" t="n">
-        <v>6704826</v>
+        <v>6704469</v>
       </c>
       <c r="S214" t="n">
         <v>10</v>
@@ -24297,10 +24297,10 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>122010908</v>
+        <v>122010905</v>
       </c>
       <c r="B215" t="n">
-        <v>5173</v>
+        <v>98133</v>
       </c>
       <c r="C215" t="inlineStr">
         <is>
@@ -24309,43 +24309,46 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E215" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I215" t="inlineStr"/>
-      <c r="M215" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
+      <c r="J215" t="inlineStr"/>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L215" t="inlineStr"/>
+      <c r="N215" t="inlineStr"/>
       <c r="P215" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>563625</v>
+        <v>563702</v>
       </c>
       <c r="R215" t="n">
-        <v>6704469</v>
+        <v>6704641</v>
       </c>
       <c r="S215" t="n">
         <v>10</v>
@@ -24386,6 +24389,7 @@
       <c r="AE215" t="b">
         <v>0</v>
       </c>
+      <c r="AF215" t="inlineStr"/>
       <c r="AG215" t="b">
         <v>0</v>
       </c>
@@ -24404,10 +24408,10 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>122010906</v>
+        <v>122010898</v>
       </c>
       <c r="B216" t="n">
-        <v>5173</v>
+        <v>57518</v>
       </c>
       <c r="C216" t="inlineStr">
         <is>
@@ -24416,43 +24420,38 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E216" t="n">
-        <v>100526</v>
+        <v>103021</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I216" t="inlineStr"/>
-      <c r="M216" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P216" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>563921</v>
+        <v>563884</v>
       </c>
       <c r="R216" t="n">
-        <v>6704919</v>
+        <v>6704911</v>
       </c>
       <c r="S216" t="n">
         <v>10</v>
@@ -24511,10 +24510,10 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>122010894</v>
+        <v>122010903</v>
       </c>
       <c r="B217" t="n">
-        <v>90742</v>
+        <v>98133</v>
       </c>
       <c r="C217" t="inlineStr">
         <is>
@@ -24523,38 +24522,46 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E217" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I217" t="inlineStr"/>
+      <c r="J217" t="inlineStr"/>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L217" t="inlineStr"/>
+      <c r="N217" t="inlineStr"/>
       <c r="P217" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>564343</v>
+        <v>564274</v>
       </c>
       <c r="R217" t="n">
-        <v>6705432</v>
+        <v>6705386</v>
       </c>
       <c r="S217" t="n">
         <v>10</v>
@@ -24595,6 +24602,7 @@
       <c r="AE217" t="b">
         <v>0</v>
       </c>
+      <c r="AF217" t="inlineStr"/>
       <c r="AG217" t="b">
         <v>0</v>
       </c>
@@ -24613,10 +24621,10 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>122010898</v>
+        <v>122010895</v>
       </c>
       <c r="B218" t="n">
-        <v>57518</v>
+        <v>90744</v>
       </c>
       <c r="C218" t="inlineStr">
         <is>
@@ -24629,21 +24637,21 @@
         </is>
       </c>
       <c r="E218" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I218" t="inlineStr"/>
@@ -24653,10 +24661,10 @@
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>563884</v>
+        <v>563619</v>
       </c>
       <c r="R218" t="n">
-        <v>6704911</v>
+        <v>6704484</v>
       </c>
       <c r="S218" t="n">
         <v>10</v>
@@ -24715,10 +24723,10 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>122010905</v>
+        <v>122010893</v>
       </c>
       <c r="B219" t="n">
-        <v>98131</v>
+        <v>90709</v>
       </c>
       <c r="C219" t="inlineStr">
         <is>
@@ -24727,46 +24735,38 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E219" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I219" t="inlineStr"/>
-      <c r="J219" t="inlineStr"/>
-      <c r="K219" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L219" t="inlineStr"/>
-      <c r="N219" t="inlineStr"/>
       <c r="P219" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>563702</v>
+        <v>563600</v>
       </c>
       <c r="R219" t="n">
-        <v>6704641</v>
+        <v>6704463</v>
       </c>
       <c r="S219" t="n">
         <v>10</v>
@@ -24807,7 +24807,6 @@
       <c r="AE219" t="b">
         <v>0</v>
       </c>
-      <c r="AF219" t="inlineStr"/>
       <c r="AG219" t="b">
         <v>0</v>
       </c>
@@ -24826,10 +24825,10 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>122010904</v>
+        <v>122010906</v>
       </c>
       <c r="B220" t="n">
-        <v>98131</v>
+        <v>5173</v>
       </c>
       <c r="C220" t="inlineStr">
         <is>
@@ -24838,46 +24837,43 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E220" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I220" t="inlineStr"/>
-      <c r="J220" t="inlineStr"/>
-      <c r="K220" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L220" t="inlineStr"/>
-      <c r="N220" t="inlineStr"/>
+      <c r="M220" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P220" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>563814</v>
+        <v>563921</v>
       </c>
       <c r="R220" t="n">
-        <v>6704820</v>
+        <v>6704919</v>
       </c>
       <c r="S220" t="n">
         <v>10</v>
@@ -24918,7 +24914,6 @@
       <c r="AE220" t="b">
         <v>0</v>
       </c>
-      <c r="AF220" t="inlineStr"/>
       <c r="AG220" t="b">
         <v>0</v>
       </c>
@@ -24937,10 +24932,10 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>122010895</v>
+        <v>122010907</v>
       </c>
       <c r="B221" t="n">
-        <v>90742</v>
+        <v>5173</v>
       </c>
       <c r="C221" t="inlineStr">
         <is>
@@ -24949,38 +24944,43 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E221" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I221" t="inlineStr"/>
+      <c r="M221" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P221" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>563619</v>
+        <v>563819</v>
       </c>
       <c r="R221" t="n">
-        <v>6704484</v>
+        <v>6704826</v>
       </c>
       <c r="S221" t="n">
         <v>10</v>

--- a/artfynd/A 58548-2022 artfynd.xlsx
+++ b/artfynd/A 58548-2022 artfynd.xlsx
@@ -23763,10 +23763,10 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>122010904</v>
+        <v>122010893</v>
       </c>
       <c r="B210" t="n">
-        <v>98133</v>
+        <v>90710</v>
       </c>
       <c r="C210" t="inlineStr">
         <is>
@@ -23775,46 +23775,38 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E210" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I210" t="inlineStr"/>
-      <c r="J210" t="inlineStr"/>
-      <c r="K210" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L210" t="inlineStr"/>
-      <c r="N210" t="inlineStr"/>
       <c r="P210" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>563814</v>
+        <v>563600</v>
       </c>
       <c r="R210" t="n">
-        <v>6704820</v>
+        <v>6704463</v>
       </c>
       <c r="S210" t="n">
         <v>10</v>
@@ -23855,7 +23847,6 @@
       <c r="AE210" t="b">
         <v>0</v>
       </c>
-      <c r="AF210" t="inlineStr"/>
       <c r="AG210" t="b">
         <v>0</v>
       </c>
@@ -23874,10 +23865,10 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>122010909</v>
+        <v>122010903</v>
       </c>
       <c r="B211" t="n">
-        <v>5173</v>
+        <v>98140</v>
       </c>
       <c r="C211" t="inlineStr">
         <is>
@@ -23886,43 +23877,46 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E211" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I211" t="inlineStr"/>
-      <c r="M211" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
+      <c r="J211" t="inlineStr"/>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L211" t="inlineStr"/>
+      <c r="N211" t="inlineStr"/>
       <c r="P211" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>563850</v>
+        <v>564274</v>
       </c>
       <c r="R211" t="n">
-        <v>6704731</v>
+        <v>6705386</v>
       </c>
       <c r="S211" t="n">
         <v>10</v>
@@ -23963,6 +23957,7 @@
       <c r="AE211" t="b">
         <v>0</v>
       </c>
+      <c r="AF211" t="inlineStr"/>
       <c r="AG211" t="b">
         <v>0</v>
       </c>
@@ -23981,10 +23976,10 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>122010894</v>
+        <v>122010908</v>
       </c>
       <c r="B212" t="n">
-        <v>90744</v>
+        <v>5173</v>
       </c>
       <c r="C212" t="inlineStr">
         <is>
@@ -23993,38 +23988,43 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E212" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I212" t="inlineStr"/>
+      <c r="M212" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P212" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>564343</v>
+        <v>563625</v>
       </c>
       <c r="R212" t="n">
-        <v>6705432</v>
+        <v>6704469</v>
       </c>
       <c r="S212" t="n">
         <v>10</v>
@@ -24083,10 +24083,10 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>122010902</v>
+        <v>122010904</v>
       </c>
       <c r="B213" t="n">
-        <v>57381</v>
+        <v>98140</v>
       </c>
       <c r="C213" t="inlineStr">
         <is>
@@ -24095,43 +24095,46 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E213" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I213" t="inlineStr"/>
-      <c r="M213" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J213" t="inlineStr"/>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L213" t="inlineStr"/>
+      <c r="N213" t="inlineStr"/>
       <c r="P213" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>563803</v>
+        <v>563814</v>
       </c>
       <c r="R213" t="n">
-        <v>6704669</v>
+        <v>6704820</v>
       </c>
       <c r="S213" t="n">
         <v>10</v>
@@ -24172,6 +24175,7 @@
       <c r="AE213" t="b">
         <v>0</v>
       </c>
+      <c r="AF213" t="inlineStr"/>
       <c r="AG213" t="b">
         <v>0</v>
       </c>
@@ -24190,10 +24194,10 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>122010908</v>
+        <v>122010905</v>
       </c>
       <c r="B214" t="n">
-        <v>5173</v>
+        <v>98140</v>
       </c>
       <c r="C214" t="inlineStr">
         <is>
@@ -24202,43 +24206,46 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E214" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I214" t="inlineStr"/>
-      <c r="M214" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
+      <c r="J214" t="inlineStr"/>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L214" t="inlineStr"/>
+      <c r="N214" t="inlineStr"/>
       <c r="P214" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>563625</v>
+        <v>563702</v>
       </c>
       <c r="R214" t="n">
-        <v>6704469</v>
+        <v>6704641</v>
       </c>
       <c r="S214" t="n">
         <v>10</v>
@@ -24279,6 +24286,7 @@
       <c r="AE214" t="b">
         <v>0</v>
       </c>
+      <c r="AF214" t="inlineStr"/>
       <c r="AG214" t="b">
         <v>0</v>
       </c>
@@ -24297,10 +24305,10 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>122010905</v>
+        <v>122010898</v>
       </c>
       <c r="B215" t="n">
-        <v>98133</v>
+        <v>57518</v>
       </c>
       <c r="C215" t="inlineStr">
         <is>
@@ -24309,46 +24317,38 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E215" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I215" t="inlineStr"/>
-      <c r="J215" t="inlineStr"/>
-      <c r="K215" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L215" t="inlineStr"/>
-      <c r="N215" t="inlineStr"/>
       <c r="P215" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>563702</v>
+        <v>563884</v>
       </c>
       <c r="R215" t="n">
-        <v>6704641</v>
+        <v>6704911</v>
       </c>
       <c r="S215" t="n">
         <v>10</v>
@@ -24389,7 +24389,6 @@
       <c r="AE215" t="b">
         <v>0</v>
       </c>
-      <c r="AF215" t="inlineStr"/>
       <c r="AG215" t="b">
         <v>0</v>
       </c>
@@ -24408,10 +24407,10 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>122010898</v>
+        <v>122010907</v>
       </c>
       <c r="B216" t="n">
-        <v>57518</v>
+        <v>5173</v>
       </c>
       <c r="C216" t="inlineStr">
         <is>
@@ -24420,38 +24419,43 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E216" t="n">
-        <v>103021</v>
+        <v>100526</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I216" t="inlineStr"/>
+      <c r="M216" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P216" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>563884</v>
+        <v>563819</v>
       </c>
       <c r="R216" t="n">
-        <v>6704911</v>
+        <v>6704826</v>
       </c>
       <c r="S216" t="n">
         <v>10</v>
@@ -24510,10 +24514,10 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>122010903</v>
+        <v>122010909</v>
       </c>
       <c r="B217" t="n">
-        <v>98133</v>
+        <v>5173</v>
       </c>
       <c r="C217" t="inlineStr">
         <is>
@@ -24522,46 +24526,43 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E217" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I217" t="inlineStr"/>
-      <c r="J217" t="inlineStr"/>
-      <c r="K217" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L217" t="inlineStr"/>
-      <c r="N217" t="inlineStr"/>
+      <c r="M217" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P217" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>564274</v>
+        <v>563850</v>
       </c>
       <c r="R217" t="n">
-        <v>6705386</v>
+        <v>6704731</v>
       </c>
       <c r="S217" t="n">
         <v>10</v>
@@ -24602,7 +24603,6 @@
       <c r="AE217" t="b">
         <v>0</v>
       </c>
-      <c r="AF217" t="inlineStr"/>
       <c r="AG217" t="b">
         <v>0</v>
       </c>
@@ -24621,10 +24621,10 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>122010895</v>
+        <v>122010906</v>
       </c>
       <c r="B218" t="n">
-        <v>90744</v>
+        <v>5173</v>
       </c>
       <c r="C218" t="inlineStr">
         <is>
@@ -24633,38 +24633,43 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E218" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I218" t="inlineStr"/>
+      <c r="M218" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P218" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>563619</v>
+        <v>563921</v>
       </c>
       <c r="R218" t="n">
-        <v>6704484</v>
+        <v>6704919</v>
       </c>
       <c r="S218" t="n">
         <v>10</v>
@@ -24723,10 +24728,10 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>122010893</v>
+        <v>122010895</v>
       </c>
       <c r="B219" t="n">
-        <v>90709</v>
+        <v>90745</v>
       </c>
       <c r="C219" t="inlineStr">
         <is>
@@ -24735,25 +24740,25 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E219" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I219" t="inlineStr"/>
@@ -24763,10 +24768,10 @@
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>563600</v>
+        <v>563619</v>
       </c>
       <c r="R219" t="n">
-        <v>6704463</v>
+        <v>6704484</v>
       </c>
       <c r="S219" t="n">
         <v>10</v>
@@ -24825,10 +24830,10 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>122010906</v>
+        <v>122010902</v>
       </c>
       <c r="B220" t="n">
-        <v>5173</v>
+        <v>57381</v>
       </c>
       <c r="C220" t="inlineStr">
         <is>
@@ -24837,31 +24842,31 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E220" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I220" t="inlineStr"/>
       <c r="M220" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P220" t="inlineStr">
@@ -24870,10 +24875,10 @@
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>563921</v>
+        <v>563803</v>
       </c>
       <c r="R220" t="n">
-        <v>6704919</v>
+        <v>6704669</v>
       </c>
       <c r="S220" t="n">
         <v>10</v>
@@ -24932,10 +24937,10 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>122010907</v>
+        <v>122010894</v>
       </c>
       <c r="B221" t="n">
-        <v>5173</v>
+        <v>90745</v>
       </c>
       <c r="C221" t="inlineStr">
         <is>
@@ -24944,43 +24949,38 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E221" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I221" t="inlineStr"/>
-      <c r="M221" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P221" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>563819</v>
+        <v>564343</v>
       </c>
       <c r="R221" t="n">
-        <v>6704826</v>
+        <v>6705432</v>
       </c>
       <c r="S221" t="n">
         <v>10</v>

--- a/artfynd/A 58548-2022 artfynd.xlsx
+++ b/artfynd/A 58548-2022 artfynd.xlsx
@@ -23763,10 +23763,10 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>122010893</v>
+        <v>122010898</v>
       </c>
       <c r="B210" t="n">
-        <v>90710</v>
+        <v>57522</v>
       </c>
       <c r="C210" t="inlineStr">
         <is>
@@ -23775,25 +23775,25 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E210" t="n">
-        <v>5447</v>
+        <v>103021</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I210" t="inlineStr"/>
@@ -23803,10 +23803,10 @@
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>563600</v>
+        <v>563884</v>
       </c>
       <c r="R210" t="n">
-        <v>6704463</v>
+        <v>6704911</v>
       </c>
       <c r="S210" t="n">
         <v>10</v>
@@ -23865,10 +23865,10 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>122010903</v>
+        <v>122010905</v>
       </c>
       <c r="B211" t="n">
-        <v>98140</v>
+        <v>98149</v>
       </c>
       <c r="C211" t="inlineStr">
         <is>
@@ -23913,10 +23913,10 @@
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>564274</v>
+        <v>563702</v>
       </c>
       <c r="R211" t="n">
-        <v>6705386</v>
+        <v>6704641</v>
       </c>
       <c r="S211" t="n">
         <v>10</v>
@@ -23976,7 +23976,7 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>122010908</v>
+        <v>122010906</v>
       </c>
       <c r="B212" t="n">
         <v>5173</v>
@@ -24021,10 +24021,10 @@
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>563625</v>
+        <v>563921</v>
       </c>
       <c r="R212" t="n">
-        <v>6704469</v>
+        <v>6704919</v>
       </c>
       <c r="S212" t="n">
         <v>10</v>
@@ -24086,7 +24086,7 @@
         <v>122010904</v>
       </c>
       <c r="B213" t="n">
-        <v>98140</v>
+        <v>98149</v>
       </c>
       <c r="C213" t="inlineStr">
         <is>
@@ -24194,10 +24194,10 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>122010905</v>
+        <v>122010908</v>
       </c>
       <c r="B214" t="n">
-        <v>98140</v>
+        <v>5173</v>
       </c>
       <c r="C214" t="inlineStr">
         <is>
@@ -24206,46 +24206,43 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E214" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I214" t="inlineStr"/>
-      <c r="J214" t="inlineStr"/>
-      <c r="K214" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L214" t="inlineStr"/>
-      <c r="N214" t="inlineStr"/>
+      <c r="M214" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P214" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>563702</v>
+        <v>563625</v>
       </c>
       <c r="R214" t="n">
-        <v>6704641</v>
+        <v>6704469</v>
       </c>
       <c r="S214" t="n">
         <v>10</v>
@@ -24286,7 +24283,6 @@
       <c r="AE214" t="b">
         <v>0</v>
       </c>
-      <c r="AF214" t="inlineStr"/>
       <c r="AG214" t="b">
         <v>0</v>
       </c>
@@ -24305,10 +24301,10 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>122010898</v>
+        <v>122010909</v>
       </c>
       <c r="B215" t="n">
-        <v>57518</v>
+        <v>5173</v>
       </c>
       <c r="C215" t="inlineStr">
         <is>
@@ -24317,38 +24313,43 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E215" t="n">
-        <v>103021</v>
+        <v>100526</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I215" t="inlineStr"/>
+      <c r="M215" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P215" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>563884</v>
+        <v>563850</v>
       </c>
       <c r="R215" t="n">
-        <v>6704911</v>
+        <v>6704731</v>
       </c>
       <c r="S215" t="n">
         <v>10</v>
@@ -24514,10 +24515,10 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>122010909</v>
+        <v>122010895</v>
       </c>
       <c r="B217" t="n">
-        <v>5173</v>
+        <v>90754</v>
       </c>
       <c r="C217" t="inlineStr">
         <is>
@@ -24526,43 +24527,38 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E217" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I217" t="inlineStr"/>
-      <c r="M217" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P217" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>563850</v>
+        <v>563619</v>
       </c>
       <c r="R217" t="n">
-        <v>6704731</v>
+        <v>6704484</v>
       </c>
       <c r="S217" t="n">
         <v>10</v>
@@ -24621,10 +24617,10 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>122010906</v>
+        <v>122010893</v>
       </c>
       <c r="B218" t="n">
-        <v>5173</v>
+        <v>90719</v>
       </c>
       <c r="C218" t="inlineStr">
         <is>
@@ -24637,39 +24633,34 @@
         </is>
       </c>
       <c r="E218" t="n">
-        <v>100526</v>
+        <v>5447</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I218" t="inlineStr"/>
-      <c r="M218" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P218" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>563921</v>
+        <v>563600</v>
       </c>
       <c r="R218" t="n">
-        <v>6704919</v>
+        <v>6704463</v>
       </c>
       <c r="S218" t="n">
         <v>10</v>
@@ -24728,10 +24719,10 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>122010895</v>
+        <v>122010902</v>
       </c>
       <c r="B219" t="n">
-        <v>90745</v>
+        <v>57385</v>
       </c>
       <c r="C219" t="inlineStr">
         <is>
@@ -24744,34 +24735,39 @@
         </is>
       </c>
       <c r="E219" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I219" t="inlineStr"/>
+      <c r="M219" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P219" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>563619</v>
+        <v>563803</v>
       </c>
       <c r="R219" t="n">
-        <v>6704484</v>
+        <v>6704669</v>
       </c>
       <c r="S219" t="n">
         <v>10</v>
@@ -24830,10 +24826,10 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>122010902</v>
+        <v>122010894</v>
       </c>
       <c r="B220" t="n">
-        <v>57381</v>
+        <v>90754</v>
       </c>
       <c r="C220" t="inlineStr">
         <is>
@@ -24846,39 +24842,34 @@
         </is>
       </c>
       <c r="E220" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I220" t="inlineStr"/>
-      <c r="M220" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P220" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>563803</v>
+        <v>564343</v>
       </c>
       <c r="R220" t="n">
-        <v>6704669</v>
+        <v>6705432</v>
       </c>
       <c r="S220" t="n">
         <v>10</v>
@@ -24937,10 +24928,10 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>122010894</v>
+        <v>122010903</v>
       </c>
       <c r="B221" t="n">
-        <v>90745</v>
+        <v>98149</v>
       </c>
       <c r="C221" t="inlineStr">
         <is>
@@ -24949,38 +24940,46 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E221" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I221" t="inlineStr"/>
+      <c r="J221" t="inlineStr"/>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L221" t="inlineStr"/>
+      <c r="N221" t="inlineStr"/>
       <c r="P221" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>564343</v>
+        <v>564274</v>
       </c>
       <c r="R221" t="n">
-        <v>6705432</v>
+        <v>6705386</v>
       </c>
       <c r="S221" t="n">
         <v>10</v>
@@ -25021,6 +25020,7 @@
       <c r="AE221" t="b">
         <v>0</v>
       </c>
+      <c r="AF221" t="inlineStr"/>
       <c r="AG221" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 58548-2022 artfynd.xlsx
+++ b/artfynd/A 58548-2022 artfynd.xlsx
@@ -24408,10 +24408,10 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>122010907</v>
+        <v>122010895</v>
       </c>
       <c r="B216" t="n">
-        <v>5173</v>
+        <v>90754</v>
       </c>
       <c r="C216" t="inlineStr">
         <is>
@@ -24420,43 +24420,38 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E216" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I216" t="inlineStr"/>
-      <c r="M216" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P216" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>563819</v>
+        <v>563619</v>
       </c>
       <c r="R216" t="n">
-        <v>6704826</v>
+        <v>6704484</v>
       </c>
       <c r="S216" t="n">
         <v>10</v>
@@ -24515,10 +24510,10 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>122010895</v>
+        <v>122010907</v>
       </c>
       <c r="B217" t="n">
-        <v>90754</v>
+        <v>5173</v>
       </c>
       <c r="C217" t="inlineStr">
         <is>
@@ -24527,38 +24522,43 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E217" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I217" t="inlineStr"/>
+      <c r="M217" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P217" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>563619</v>
+        <v>563819</v>
       </c>
       <c r="R217" t="n">
-        <v>6704484</v>
+        <v>6704826</v>
       </c>
       <c r="S217" t="n">
         <v>10</v>

--- a/artfynd/A 58548-2022 artfynd.xlsx
+++ b/artfynd/A 58548-2022 artfynd.xlsx
@@ -24408,10 +24408,10 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>122010895</v>
+        <v>122010907</v>
       </c>
       <c r="B216" t="n">
-        <v>90754</v>
+        <v>5173</v>
       </c>
       <c r="C216" t="inlineStr">
         <is>
@@ -24420,38 +24420,43 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E216" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I216" t="inlineStr"/>
+      <c r="M216" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P216" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>563619</v>
+        <v>563819</v>
       </c>
       <c r="R216" t="n">
-        <v>6704484</v>
+        <v>6704826</v>
       </c>
       <c r="S216" t="n">
         <v>10</v>
@@ -24510,10 +24515,10 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>122010907</v>
+        <v>122010895</v>
       </c>
       <c r="B217" t="n">
-        <v>5173</v>
+        <v>90754</v>
       </c>
       <c r="C217" t="inlineStr">
         <is>
@@ -24522,43 +24527,38 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E217" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I217" t="inlineStr"/>
-      <c r="M217" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P217" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>563819</v>
+        <v>563619</v>
       </c>
       <c r="R217" t="n">
-        <v>6704826</v>
+        <v>6704484</v>
       </c>
       <c r="S217" t="n">
         <v>10</v>

--- a/artfynd/A 58548-2022 artfynd.xlsx
+++ b/artfynd/A 58548-2022 artfynd.xlsx
@@ -23763,10 +23763,10 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>122010898</v>
+        <v>122010902</v>
       </c>
       <c r="B210" t="n">
-        <v>57522</v>
+        <v>57388</v>
       </c>
       <c r="C210" t="inlineStr">
         <is>
@@ -23779,34 +23779,39 @@
         </is>
       </c>
       <c r="E210" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I210" t="inlineStr"/>
+      <c r="M210" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P210" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>563884</v>
+        <v>563803</v>
       </c>
       <c r="R210" t="n">
-        <v>6704911</v>
+        <v>6704669</v>
       </c>
       <c r="S210" t="n">
         <v>10</v>
@@ -23865,10 +23870,10 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>122010905</v>
+        <v>122010909</v>
       </c>
       <c r="B211" t="n">
-        <v>98149</v>
+        <v>5173</v>
       </c>
       <c r="C211" t="inlineStr">
         <is>
@@ -23877,46 +23882,43 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E211" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I211" t="inlineStr"/>
-      <c r="J211" t="inlineStr"/>
-      <c r="K211" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L211" t="inlineStr"/>
-      <c r="N211" t="inlineStr"/>
+      <c r="M211" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P211" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>563702</v>
+        <v>563850</v>
       </c>
       <c r="R211" t="n">
-        <v>6704641</v>
+        <v>6704731</v>
       </c>
       <c r="S211" t="n">
         <v>10</v>
@@ -23957,7 +23959,6 @@
       <c r="AE211" t="b">
         <v>0</v>
       </c>
-      <c r="AF211" t="inlineStr"/>
       <c r="AG211" t="b">
         <v>0</v>
       </c>
@@ -23976,7 +23977,7 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>122010906</v>
+        <v>122010908</v>
       </c>
       <c r="B212" t="n">
         <v>5173</v>
@@ -24021,10 +24022,10 @@
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>563921</v>
+        <v>563625</v>
       </c>
       <c r="R212" t="n">
-        <v>6704919</v>
+        <v>6704469</v>
       </c>
       <c r="S212" t="n">
         <v>10</v>
@@ -24083,10 +24084,10 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>122010904</v>
+        <v>122010905</v>
       </c>
       <c r="B213" t="n">
-        <v>98149</v>
+        <v>98157</v>
       </c>
       <c r="C213" t="inlineStr">
         <is>
@@ -24131,10 +24132,10 @@
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>563814</v>
+        <v>563702</v>
       </c>
       <c r="R213" t="n">
-        <v>6704820</v>
+        <v>6704641</v>
       </c>
       <c r="S213" t="n">
         <v>10</v>
@@ -24194,10 +24195,10 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>122010908</v>
+        <v>122010904</v>
       </c>
       <c r="B214" t="n">
-        <v>5173</v>
+        <v>98157</v>
       </c>
       <c r="C214" t="inlineStr">
         <is>
@@ -24206,43 +24207,46 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E214" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I214" t="inlineStr"/>
-      <c r="M214" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
+      <c r="J214" t="inlineStr"/>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L214" t="inlineStr"/>
+      <c r="N214" t="inlineStr"/>
       <c r="P214" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>563625</v>
+        <v>563814</v>
       </c>
       <c r="R214" t="n">
-        <v>6704469</v>
+        <v>6704820</v>
       </c>
       <c r="S214" t="n">
         <v>10</v>
@@ -24283,6 +24287,7 @@
       <c r="AE214" t="b">
         <v>0</v>
       </c>
+      <c r="AF214" t="inlineStr"/>
       <c r="AG214" t="b">
         <v>0</v>
       </c>
@@ -24301,10 +24306,10 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>122010909</v>
+        <v>122010898</v>
       </c>
       <c r="B215" t="n">
-        <v>5173</v>
+        <v>57525</v>
       </c>
       <c r="C215" t="inlineStr">
         <is>
@@ -24313,43 +24318,38 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E215" t="n">
-        <v>100526</v>
+        <v>103021</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I215" t="inlineStr"/>
-      <c r="M215" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P215" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>563850</v>
+        <v>563884</v>
       </c>
       <c r="R215" t="n">
-        <v>6704731</v>
+        <v>6704911</v>
       </c>
       <c r="S215" t="n">
         <v>10</v>
@@ -24408,7 +24408,7 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>122010907</v>
+        <v>122010906</v>
       </c>
       <c r="B216" t="n">
         <v>5173</v>
@@ -24453,10 +24453,10 @@
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>563819</v>
+        <v>563921</v>
       </c>
       <c r="R216" t="n">
-        <v>6704826</v>
+        <v>6704919</v>
       </c>
       <c r="S216" t="n">
         <v>10</v>
@@ -24518,7 +24518,7 @@
         <v>122010895</v>
       </c>
       <c r="B217" t="n">
-        <v>90754</v>
+        <v>90761</v>
       </c>
       <c r="C217" t="inlineStr">
         <is>
@@ -24617,10 +24617,10 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>122010893</v>
+        <v>122010903</v>
       </c>
       <c r="B218" t="n">
-        <v>90719</v>
+        <v>98157</v>
       </c>
       <c r="C218" t="inlineStr">
         <is>
@@ -24629,38 +24629,46 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E218" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I218" t="inlineStr"/>
+      <c r="J218" t="inlineStr"/>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L218" t="inlineStr"/>
+      <c r="N218" t="inlineStr"/>
       <c r="P218" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>563600</v>
+        <v>564274</v>
       </c>
       <c r="R218" t="n">
-        <v>6704463</v>
+        <v>6705386</v>
       </c>
       <c r="S218" t="n">
         <v>10</v>
@@ -24701,6 +24709,7 @@
       <c r="AE218" t="b">
         <v>0</v>
       </c>
+      <c r="AF218" t="inlineStr"/>
       <c r="AG218" t="b">
         <v>0</v>
       </c>
@@ -24719,10 +24728,10 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>122010902</v>
+        <v>122010894</v>
       </c>
       <c r="B219" t="n">
-        <v>57385</v>
+        <v>90761</v>
       </c>
       <c r="C219" t="inlineStr">
         <is>
@@ -24735,39 +24744,34 @@
         </is>
       </c>
       <c r="E219" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I219" t="inlineStr"/>
-      <c r="M219" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P219" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>563803</v>
+        <v>564343</v>
       </c>
       <c r="R219" t="n">
-        <v>6704669</v>
+        <v>6705432</v>
       </c>
       <c r="S219" t="n">
         <v>10</v>
@@ -24826,10 +24830,10 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>122010894</v>
+        <v>122010893</v>
       </c>
       <c r="B220" t="n">
-        <v>90754</v>
+        <v>90726</v>
       </c>
       <c r="C220" t="inlineStr">
         <is>
@@ -24838,25 +24842,25 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E220" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I220" t="inlineStr"/>
@@ -24866,10 +24870,10 @@
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>564343</v>
+        <v>563600</v>
       </c>
       <c r="R220" t="n">
-        <v>6705432</v>
+        <v>6704463</v>
       </c>
       <c r="S220" t="n">
         <v>10</v>
@@ -24928,10 +24932,10 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>122010903</v>
+        <v>122010907</v>
       </c>
       <c r="B221" t="n">
-        <v>98149</v>
+        <v>5173</v>
       </c>
       <c r="C221" t="inlineStr">
         <is>
@@ -24940,46 +24944,43 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E221" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I221" t="inlineStr"/>
-      <c r="J221" t="inlineStr"/>
-      <c r="K221" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L221" t="inlineStr"/>
-      <c r="N221" t="inlineStr"/>
+      <c r="M221" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P221" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>564274</v>
+        <v>563819</v>
       </c>
       <c r="R221" t="n">
-        <v>6705386</v>
+        <v>6704826</v>
       </c>
       <c r="S221" t="n">
         <v>10</v>
@@ -25020,7 +25021,6 @@
       <c r="AE221" t="b">
         <v>0</v>
       </c>
-      <c r="AF221" t="inlineStr"/>
       <c r="AG221" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 58548-2022 artfynd.xlsx
+++ b/artfynd/A 58548-2022 artfynd.xlsx
@@ -23763,10 +23763,10 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>122010902</v>
+        <v>122010894</v>
       </c>
       <c r="B210" t="n">
-        <v>57388</v>
+        <v>90763</v>
       </c>
       <c r="C210" t="inlineStr">
         <is>
@@ -23779,39 +23779,34 @@
         </is>
       </c>
       <c r="E210" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I210" t="inlineStr"/>
-      <c r="M210" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P210" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>563803</v>
+        <v>564343</v>
       </c>
       <c r="R210" t="n">
-        <v>6704669</v>
+        <v>6705432</v>
       </c>
       <c r="S210" t="n">
         <v>10</v>
@@ -23870,10 +23865,10 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>122010909</v>
+        <v>122010905</v>
       </c>
       <c r="B211" t="n">
-        <v>5173</v>
+        <v>98159</v>
       </c>
       <c r="C211" t="inlineStr">
         <is>
@@ -23882,43 +23877,46 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E211" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I211" t="inlineStr"/>
-      <c r="M211" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
+      <c r="J211" t="inlineStr"/>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L211" t="inlineStr"/>
+      <c r="N211" t="inlineStr"/>
       <c r="P211" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>563850</v>
+        <v>563702</v>
       </c>
       <c r="R211" t="n">
-        <v>6704731</v>
+        <v>6704641</v>
       </c>
       <c r="S211" t="n">
         <v>10</v>
@@ -23959,6 +23957,7 @@
       <c r="AE211" t="b">
         <v>0</v>
       </c>
+      <c r="AF211" t="inlineStr"/>
       <c r="AG211" t="b">
         <v>0</v>
       </c>
@@ -23977,7 +23976,7 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>122010908</v>
+        <v>122010906</v>
       </c>
       <c r="B212" t="n">
         <v>5173</v>
@@ -24022,10 +24021,10 @@
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>563625</v>
+        <v>563921</v>
       </c>
       <c r="R212" t="n">
-        <v>6704469</v>
+        <v>6704919</v>
       </c>
       <c r="S212" t="n">
         <v>10</v>
@@ -24084,10 +24083,10 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>122010905</v>
+        <v>122010902</v>
       </c>
       <c r="B213" t="n">
-        <v>98157</v>
+        <v>57390</v>
       </c>
       <c r="C213" t="inlineStr">
         <is>
@@ -24096,46 +24095,43 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E213" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I213" t="inlineStr"/>
-      <c r="J213" t="inlineStr"/>
-      <c r="K213" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L213" t="inlineStr"/>
-      <c r="N213" t="inlineStr"/>
+      <c r="M213" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P213" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>563702</v>
+        <v>563803</v>
       </c>
       <c r="R213" t="n">
-        <v>6704641</v>
+        <v>6704669</v>
       </c>
       <c r="S213" t="n">
         <v>10</v>
@@ -24176,7 +24172,6 @@
       <c r="AE213" t="b">
         <v>0</v>
       </c>
-      <c r="AF213" t="inlineStr"/>
       <c r="AG213" t="b">
         <v>0</v>
       </c>
@@ -24195,10 +24190,10 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>122010904</v>
+        <v>122010907</v>
       </c>
       <c r="B214" t="n">
-        <v>98157</v>
+        <v>5173</v>
       </c>
       <c r="C214" t="inlineStr">
         <is>
@@ -24207,46 +24202,43 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E214" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I214" t="inlineStr"/>
-      <c r="J214" t="inlineStr"/>
-      <c r="K214" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L214" t="inlineStr"/>
-      <c r="N214" t="inlineStr"/>
+      <c r="M214" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P214" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>563814</v>
+        <v>563819</v>
       </c>
       <c r="R214" t="n">
-        <v>6704820</v>
+        <v>6704826</v>
       </c>
       <c r="S214" t="n">
         <v>10</v>
@@ -24287,7 +24279,6 @@
       <c r="AE214" t="b">
         <v>0</v>
       </c>
-      <c r="AF214" t="inlineStr"/>
       <c r="AG214" t="b">
         <v>0</v>
       </c>
@@ -24306,10 +24297,10 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>122010898</v>
+        <v>122010909</v>
       </c>
       <c r="B215" t="n">
-        <v>57525</v>
+        <v>5173</v>
       </c>
       <c r="C215" t="inlineStr">
         <is>
@@ -24318,38 +24309,43 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E215" t="n">
-        <v>103021</v>
+        <v>100526</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I215" t="inlineStr"/>
+      <c r="M215" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P215" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>563884</v>
+        <v>563850</v>
       </c>
       <c r="R215" t="n">
-        <v>6704911</v>
+        <v>6704731</v>
       </c>
       <c r="S215" t="n">
         <v>10</v>
@@ -24408,7 +24404,7 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>122010906</v>
+        <v>122010908</v>
       </c>
       <c r="B216" t="n">
         <v>5173</v>
@@ -24453,10 +24449,10 @@
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>563921</v>
+        <v>563625</v>
       </c>
       <c r="R216" t="n">
-        <v>6704919</v>
+        <v>6704469</v>
       </c>
       <c r="S216" t="n">
         <v>10</v>
@@ -24515,10 +24511,10 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>122010895</v>
+        <v>122010893</v>
       </c>
       <c r="B217" t="n">
-        <v>90761</v>
+        <v>90728</v>
       </c>
       <c r="C217" t="inlineStr">
         <is>
@@ -24527,25 +24523,25 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E217" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I217" t="inlineStr"/>
@@ -24555,10 +24551,10 @@
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>563619</v>
+        <v>563600</v>
       </c>
       <c r="R217" t="n">
-        <v>6704484</v>
+        <v>6704463</v>
       </c>
       <c r="S217" t="n">
         <v>10</v>
@@ -24617,10 +24613,10 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>122010903</v>
+        <v>122010904</v>
       </c>
       <c r="B218" t="n">
-        <v>98157</v>
+        <v>98159</v>
       </c>
       <c r="C218" t="inlineStr">
         <is>
@@ -24665,10 +24661,10 @@
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>564274</v>
+        <v>563814</v>
       </c>
       <c r="R218" t="n">
-        <v>6705386</v>
+        <v>6704820</v>
       </c>
       <c r="S218" t="n">
         <v>10</v>
@@ -24728,10 +24724,10 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>122010894</v>
+        <v>122010903</v>
       </c>
       <c r="B219" t="n">
-        <v>90761</v>
+        <v>98159</v>
       </c>
       <c r="C219" t="inlineStr">
         <is>
@@ -24740,38 +24736,46 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E219" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I219" t="inlineStr"/>
+      <c r="J219" t="inlineStr"/>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L219" t="inlineStr"/>
+      <c r="N219" t="inlineStr"/>
       <c r="P219" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>564343</v>
+        <v>564274</v>
       </c>
       <c r="R219" t="n">
-        <v>6705432</v>
+        <v>6705386</v>
       </c>
       <c r="S219" t="n">
         <v>10</v>
@@ -24812,6 +24816,7 @@
       <c r="AE219" t="b">
         <v>0</v>
       </c>
+      <c r="AF219" t="inlineStr"/>
       <c r="AG219" t="b">
         <v>0</v>
       </c>
@@ -24830,10 +24835,10 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>122010893</v>
+        <v>122010898</v>
       </c>
       <c r="B220" t="n">
-        <v>90726</v>
+        <v>57527</v>
       </c>
       <c r="C220" t="inlineStr">
         <is>
@@ -24842,25 +24847,25 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E220" t="n">
-        <v>5447</v>
+        <v>103021</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I220" t="inlineStr"/>
@@ -24870,10 +24875,10 @@
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>563600</v>
+        <v>563884</v>
       </c>
       <c r="R220" t="n">
-        <v>6704463</v>
+        <v>6704911</v>
       </c>
       <c r="S220" t="n">
         <v>10</v>
@@ -24932,10 +24937,10 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>122010907</v>
+        <v>122010895</v>
       </c>
       <c r="B221" t="n">
-        <v>5173</v>
+        <v>90763</v>
       </c>
       <c r="C221" t="inlineStr">
         <is>
@@ -24944,43 +24949,38 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E221" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I221" t="inlineStr"/>
-      <c r="M221" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P221" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>563819</v>
+        <v>563619</v>
       </c>
       <c r="R221" t="n">
-        <v>6704826</v>
+        <v>6704484</v>
       </c>
       <c r="S221" t="n">
         <v>10</v>

--- a/artfynd/A 58548-2022 artfynd.xlsx
+++ b/artfynd/A 58548-2022 artfynd.xlsx
@@ -23763,10 +23763,10 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>122010894</v>
+        <v>122010905</v>
       </c>
       <c r="B210" t="n">
-        <v>90763</v>
+        <v>98159</v>
       </c>
       <c r="C210" t="inlineStr">
         <is>
@@ -23775,38 +23775,46 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E210" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I210" t="inlineStr"/>
+      <c r="J210" t="inlineStr"/>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L210" t="inlineStr"/>
+      <c r="N210" t="inlineStr"/>
       <c r="P210" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>564343</v>
+        <v>563702</v>
       </c>
       <c r="R210" t="n">
-        <v>6705432</v>
+        <v>6704641</v>
       </c>
       <c r="S210" t="n">
         <v>10</v>
@@ -23847,6 +23855,7 @@
       <c r="AE210" t="b">
         <v>0</v>
       </c>
+      <c r="AF210" t="inlineStr"/>
       <c r="AG210" t="b">
         <v>0</v>
       </c>
@@ -23865,7 +23874,7 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>122010905</v>
+        <v>122010903</v>
       </c>
       <c r="B211" t="n">
         <v>98159</v>
@@ -23913,10 +23922,10 @@
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>563702</v>
+        <v>564274</v>
       </c>
       <c r="R211" t="n">
-        <v>6704641</v>
+        <v>6705386</v>
       </c>
       <c r="S211" t="n">
         <v>10</v>
@@ -23976,10 +23985,10 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>122010906</v>
+        <v>122010893</v>
       </c>
       <c r="B212" t="n">
-        <v>5173</v>
+        <v>90728</v>
       </c>
       <c r="C212" t="inlineStr">
         <is>
@@ -23992,39 +24001,34 @@
         </is>
       </c>
       <c r="E212" t="n">
-        <v>100526</v>
+        <v>5447</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I212" t="inlineStr"/>
-      <c r="M212" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P212" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>563921</v>
+        <v>563600</v>
       </c>
       <c r="R212" t="n">
-        <v>6704919</v>
+        <v>6704463</v>
       </c>
       <c r="S212" t="n">
         <v>10</v>
@@ -24083,10 +24087,10 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>122010902</v>
+        <v>122010909</v>
       </c>
       <c r="B213" t="n">
-        <v>57390</v>
+        <v>5173</v>
       </c>
       <c r="C213" t="inlineStr">
         <is>
@@ -24095,31 +24099,31 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E213" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I213" t="inlineStr"/>
       <c r="M213" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P213" t="inlineStr">
@@ -24128,10 +24132,10 @@
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>563803</v>
+        <v>563850</v>
       </c>
       <c r="R213" t="n">
-        <v>6704669</v>
+        <v>6704731</v>
       </c>
       <c r="S213" t="n">
         <v>10</v>
@@ -24190,10 +24194,10 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>122010907</v>
+        <v>122010898</v>
       </c>
       <c r="B214" t="n">
-        <v>5173</v>
+        <v>57527</v>
       </c>
       <c r="C214" t="inlineStr">
         <is>
@@ -24202,43 +24206,38 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E214" t="n">
-        <v>100526</v>
+        <v>103021</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I214" t="inlineStr"/>
-      <c r="M214" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P214" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>563819</v>
+        <v>563884</v>
       </c>
       <c r="R214" t="n">
-        <v>6704826</v>
+        <v>6704911</v>
       </c>
       <c r="S214" t="n">
         <v>10</v>
@@ -24297,10 +24296,10 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>122010909</v>
+        <v>122010902</v>
       </c>
       <c r="B215" t="n">
-        <v>5173</v>
+        <v>57390</v>
       </c>
       <c r="C215" t="inlineStr">
         <is>
@@ -24309,31 +24308,31 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E215" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I215" t="inlineStr"/>
       <c r="M215" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P215" t="inlineStr">
@@ -24342,10 +24341,10 @@
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>563850</v>
+        <v>563803</v>
       </c>
       <c r="R215" t="n">
-        <v>6704731</v>
+        <v>6704669</v>
       </c>
       <c r="S215" t="n">
         <v>10</v>
@@ -24511,10 +24510,10 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>122010893</v>
+        <v>122010904</v>
       </c>
       <c r="B217" t="n">
-        <v>90728</v>
+        <v>98159</v>
       </c>
       <c r="C217" t="inlineStr">
         <is>
@@ -24523,38 +24522,46 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E217" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I217" t="inlineStr"/>
+      <c r="J217" t="inlineStr"/>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L217" t="inlineStr"/>
+      <c r="N217" t="inlineStr"/>
       <c r="P217" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>563600</v>
+        <v>563814</v>
       </c>
       <c r="R217" t="n">
-        <v>6704463</v>
+        <v>6704820</v>
       </c>
       <c r="S217" t="n">
         <v>10</v>
@@ -24595,6 +24602,7 @@
       <c r="AE217" t="b">
         <v>0</v>
       </c>
+      <c r="AF217" t="inlineStr"/>
       <c r="AG217" t="b">
         <v>0</v>
       </c>
@@ -24613,10 +24621,10 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>122010904</v>
+        <v>122010895</v>
       </c>
       <c r="B218" t="n">
-        <v>98159</v>
+        <v>90763</v>
       </c>
       <c r="C218" t="inlineStr">
         <is>
@@ -24625,46 +24633,38 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E218" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I218" t="inlineStr"/>
-      <c r="J218" t="inlineStr"/>
-      <c r="K218" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L218" t="inlineStr"/>
-      <c r="N218" t="inlineStr"/>
       <c r="P218" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>563814</v>
+        <v>563619</v>
       </c>
       <c r="R218" t="n">
-        <v>6704820</v>
+        <v>6704484</v>
       </c>
       <c r="S218" t="n">
         <v>10</v>
@@ -24705,7 +24705,6 @@
       <c r="AE218" t="b">
         <v>0</v>
       </c>
-      <c r="AF218" t="inlineStr"/>
       <c r="AG218" t="b">
         <v>0</v>
       </c>
@@ -24724,10 +24723,10 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>122010903</v>
+        <v>122010907</v>
       </c>
       <c r="B219" t="n">
-        <v>98159</v>
+        <v>5173</v>
       </c>
       <c r="C219" t="inlineStr">
         <is>
@@ -24736,46 +24735,43 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E219" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I219" t="inlineStr"/>
-      <c r="J219" t="inlineStr"/>
-      <c r="K219" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L219" t="inlineStr"/>
-      <c r="N219" t="inlineStr"/>
+      <c r="M219" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P219" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>564274</v>
+        <v>563819</v>
       </c>
       <c r="R219" t="n">
-        <v>6705386</v>
+        <v>6704826</v>
       </c>
       <c r="S219" t="n">
         <v>10</v>
@@ -24816,7 +24812,6 @@
       <c r="AE219" t="b">
         <v>0</v>
       </c>
-      <c r="AF219" t="inlineStr"/>
       <c r="AG219" t="b">
         <v>0</v>
       </c>
@@ -24835,10 +24830,10 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>122010898</v>
+        <v>122010894</v>
       </c>
       <c r="B220" t="n">
-        <v>57527</v>
+        <v>90763</v>
       </c>
       <c r="C220" t="inlineStr">
         <is>
@@ -24851,21 +24846,21 @@
         </is>
       </c>
       <c r="E220" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I220" t="inlineStr"/>
@@ -24875,10 +24870,10 @@
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>563884</v>
+        <v>564343</v>
       </c>
       <c r="R220" t="n">
-        <v>6704911</v>
+        <v>6705432</v>
       </c>
       <c r="S220" t="n">
         <v>10</v>
@@ -24937,10 +24932,10 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>122010895</v>
+        <v>122010906</v>
       </c>
       <c r="B221" t="n">
-        <v>90763</v>
+        <v>5173</v>
       </c>
       <c r="C221" t="inlineStr">
         <is>
@@ -24949,38 +24944,43 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E221" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I221" t="inlineStr"/>
+      <c r="M221" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P221" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>563619</v>
+        <v>563921</v>
       </c>
       <c r="R221" t="n">
-        <v>6704484</v>
+        <v>6704919</v>
       </c>
       <c r="S221" t="n">
         <v>10</v>

--- a/artfynd/A 58548-2022 artfynd.xlsx
+++ b/artfynd/A 58548-2022 artfynd.xlsx
@@ -23763,10 +23763,10 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>122010906</v>
+        <v>122010902</v>
       </c>
       <c r="B210" t="n">
-        <v>5173</v>
+        <v>57390</v>
       </c>
       <c r="C210" t="inlineStr">
         <is>
@@ -23775,31 +23775,31 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E210" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I210" t="inlineStr"/>
       <c r="M210" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P210" t="inlineStr">
@@ -23808,10 +23808,10 @@
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>563921</v>
+        <v>563803</v>
       </c>
       <c r="R210" t="n">
-        <v>6704919</v>
+        <v>6704669</v>
       </c>
       <c r="S210" t="n">
         <v>10</v>
@@ -23870,10 +23870,10 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>122010898</v>
+        <v>122010894</v>
       </c>
       <c r="B211" t="n">
-        <v>57527</v>
+        <v>90779</v>
       </c>
       <c r="C211" t="inlineStr">
         <is>
@@ -23886,21 +23886,21 @@
         </is>
       </c>
       <c r="E211" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I211" t="inlineStr"/>
@@ -23910,10 +23910,10 @@
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>563884</v>
+        <v>564343</v>
       </c>
       <c r="R211" t="n">
-        <v>6704911</v>
+        <v>6705432</v>
       </c>
       <c r="S211" t="n">
         <v>10</v>
@@ -23972,10 +23972,10 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>122010903</v>
+        <v>122010907</v>
       </c>
       <c r="B212" t="n">
-        <v>98175</v>
+        <v>5173</v>
       </c>
       <c r="C212" t="inlineStr">
         <is>
@@ -23984,46 +23984,43 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E212" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I212" t="inlineStr"/>
-      <c r="J212" t="inlineStr"/>
-      <c r="K212" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L212" t="inlineStr"/>
-      <c r="N212" t="inlineStr"/>
+      <c r="M212" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P212" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>564274</v>
+        <v>563819</v>
       </c>
       <c r="R212" t="n">
-        <v>6705386</v>
+        <v>6704826</v>
       </c>
       <c r="S212" t="n">
         <v>10</v>
@@ -24064,7 +24061,6 @@
       <c r="AE212" t="b">
         <v>0</v>
       </c>
-      <c r="AF212" t="inlineStr"/>
       <c r="AG212" t="b">
         <v>0</v>
       </c>
@@ -24083,7 +24079,7 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>122010894</v>
+        <v>122010895</v>
       </c>
       <c r="B213" t="n">
         <v>90779</v>
@@ -24123,10 +24119,10 @@
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>564343</v>
+        <v>563619</v>
       </c>
       <c r="R213" t="n">
-        <v>6705432</v>
+        <v>6704484</v>
       </c>
       <c r="S213" t="n">
         <v>10</v>
@@ -24185,10 +24181,10 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>122010893</v>
+        <v>122010905</v>
       </c>
       <c r="B214" t="n">
-        <v>90744</v>
+        <v>98175</v>
       </c>
       <c r="C214" t="inlineStr">
         <is>
@@ -24197,38 +24193,46 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E214" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I214" t="inlineStr"/>
+      <c r="J214" t="inlineStr"/>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L214" t="inlineStr"/>
+      <c r="N214" t="inlineStr"/>
       <c r="P214" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>563600</v>
+        <v>563702</v>
       </c>
       <c r="R214" t="n">
-        <v>6704463</v>
+        <v>6704641</v>
       </c>
       <c r="S214" t="n">
         <v>10</v>
@@ -24269,6 +24273,7 @@
       <c r="AE214" t="b">
         <v>0</v>
       </c>
+      <c r="AF214" t="inlineStr"/>
       <c r="AG214" t="b">
         <v>0</v>
       </c>
@@ -24287,10 +24292,10 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>122010908</v>
+        <v>122010903</v>
       </c>
       <c r="B215" t="n">
-        <v>5173</v>
+        <v>98175</v>
       </c>
       <c r="C215" t="inlineStr">
         <is>
@@ -24299,43 +24304,46 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E215" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I215" t="inlineStr"/>
-      <c r="M215" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
+      <c r="J215" t="inlineStr"/>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L215" t="inlineStr"/>
+      <c r="N215" t="inlineStr"/>
       <c r="P215" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>563625</v>
+        <v>564274</v>
       </c>
       <c r="R215" t="n">
-        <v>6704469</v>
+        <v>6705386</v>
       </c>
       <c r="S215" t="n">
         <v>10</v>
@@ -24376,6 +24384,7 @@
       <c r="AE215" t="b">
         <v>0</v>
       </c>
+      <c r="AF215" t="inlineStr"/>
       <c r="AG215" t="b">
         <v>0</v>
       </c>
@@ -24394,7 +24403,7 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>122010907</v>
+        <v>122010909</v>
       </c>
       <c r="B216" t="n">
         <v>5173</v>
@@ -24439,10 +24448,10 @@
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>563819</v>
+        <v>563850</v>
       </c>
       <c r="R216" t="n">
-        <v>6704826</v>
+        <v>6704731</v>
       </c>
       <c r="S216" t="n">
         <v>10</v>
@@ -24501,7 +24510,7 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>122010909</v>
+        <v>122010908</v>
       </c>
       <c r="B217" t="n">
         <v>5173</v>
@@ -24546,10 +24555,10 @@
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>563850</v>
+        <v>563625</v>
       </c>
       <c r="R217" t="n">
-        <v>6704731</v>
+        <v>6704469</v>
       </c>
       <c r="S217" t="n">
         <v>10</v>
@@ -24608,10 +24617,10 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>122010904</v>
+        <v>122010906</v>
       </c>
       <c r="B218" t="n">
-        <v>98175</v>
+        <v>5173</v>
       </c>
       <c r="C218" t="inlineStr">
         <is>
@@ -24620,46 +24629,43 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E218" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I218" t="inlineStr"/>
-      <c r="J218" t="inlineStr"/>
-      <c r="K218" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L218" t="inlineStr"/>
-      <c r="N218" t="inlineStr"/>
+      <c r="M218" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P218" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>563814</v>
+        <v>563921</v>
       </c>
       <c r="R218" t="n">
-        <v>6704820</v>
+        <v>6704919</v>
       </c>
       <c r="S218" t="n">
         <v>10</v>
@@ -24700,7 +24706,6 @@
       <c r="AE218" t="b">
         <v>0</v>
       </c>
-      <c r="AF218" t="inlineStr"/>
       <c r="AG218" t="b">
         <v>0</v>
       </c>
@@ -24719,7 +24724,7 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>122010905</v>
+        <v>122010904</v>
       </c>
       <c r="B219" t="n">
         <v>98175</v>
@@ -24767,10 +24772,10 @@
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>563702</v>
+        <v>563814</v>
       </c>
       <c r="R219" t="n">
-        <v>6704641</v>
+        <v>6704820</v>
       </c>
       <c r="S219" t="n">
         <v>10</v>
@@ -24830,10 +24835,10 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>122010895</v>
+        <v>122010893</v>
       </c>
       <c r="B220" t="n">
-        <v>90779</v>
+        <v>90744</v>
       </c>
       <c r="C220" t="inlineStr">
         <is>
@@ -24842,25 +24847,25 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E220" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I220" t="inlineStr"/>
@@ -24870,10 +24875,10 @@
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>563619</v>
+        <v>563600</v>
       </c>
       <c r="R220" t="n">
-        <v>6704484</v>
+        <v>6704463</v>
       </c>
       <c r="S220" t="n">
         <v>10</v>
@@ -24932,10 +24937,10 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>122010902</v>
+        <v>122010898</v>
       </c>
       <c r="B221" t="n">
-        <v>57390</v>
+        <v>57527</v>
       </c>
       <c r="C221" t="inlineStr">
         <is>
@@ -24948,39 +24953,34 @@
         </is>
       </c>
       <c r="E221" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I221" t="inlineStr"/>
-      <c r="M221" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P221" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>563803</v>
+        <v>563884</v>
       </c>
       <c r="R221" t="n">
-        <v>6704669</v>
+        <v>6704911</v>
       </c>
       <c r="S221" t="n">
         <v>10</v>

--- a/artfynd/A 58548-2022 artfynd.xlsx
+++ b/artfynd/A 58548-2022 artfynd.xlsx
@@ -23870,10 +23870,10 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>122010894</v>
+        <v>122010907</v>
       </c>
       <c r="B211" t="n">
-        <v>90779</v>
+        <v>5173</v>
       </c>
       <c r="C211" t="inlineStr">
         <is>
@@ -23882,38 +23882,43 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E211" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I211" t="inlineStr"/>
+      <c r="M211" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P211" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>564343</v>
+        <v>563819</v>
       </c>
       <c r="R211" t="n">
-        <v>6705432</v>
+        <v>6704826</v>
       </c>
       <c r="S211" t="n">
         <v>10</v>
@@ -23972,10 +23977,10 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>122010907</v>
+        <v>122010894</v>
       </c>
       <c r="B212" t="n">
-        <v>5173</v>
+        <v>90779</v>
       </c>
       <c r="C212" t="inlineStr">
         <is>
@@ -23984,43 +23989,38 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E212" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I212" t="inlineStr"/>
-      <c r="M212" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P212" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>563819</v>
+        <v>564343</v>
       </c>
       <c r="R212" t="n">
-        <v>6704826</v>
+        <v>6705432</v>
       </c>
       <c r="S212" t="n">
         <v>10</v>

--- a/artfynd/A 58548-2022 artfynd.xlsx
+++ b/artfynd/A 58548-2022 artfynd.xlsx
@@ -23870,7 +23870,7 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>122010907</v>
+        <v>122010909</v>
       </c>
       <c r="B211" t="n">
         <v>5173</v>
@@ -23915,10 +23915,10 @@
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>563819</v>
+        <v>563850</v>
       </c>
       <c r="R211" t="n">
-        <v>6704826</v>
+        <v>6704731</v>
       </c>
       <c r="S211" t="n">
         <v>10</v>
@@ -23977,10 +23977,10 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>122010894</v>
+        <v>122010906</v>
       </c>
       <c r="B212" t="n">
-        <v>90779</v>
+        <v>5173</v>
       </c>
       <c r="C212" t="inlineStr">
         <is>
@@ -23989,38 +23989,43 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E212" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I212" t="inlineStr"/>
+      <c r="M212" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P212" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>564343</v>
+        <v>563921</v>
       </c>
       <c r="R212" t="n">
-        <v>6705432</v>
+        <v>6704919</v>
       </c>
       <c r="S212" t="n">
         <v>10</v>
@@ -24079,10 +24084,10 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>122010895</v>
+        <v>122010894</v>
       </c>
       <c r="B213" t="n">
-        <v>90779</v>
+        <v>90789</v>
       </c>
       <c r="C213" t="inlineStr">
         <is>
@@ -24119,10 +24124,10 @@
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>563619</v>
+        <v>564343</v>
       </c>
       <c r="R213" t="n">
-        <v>6704484</v>
+        <v>6705432</v>
       </c>
       <c r="S213" t="n">
         <v>10</v>
@@ -24181,10 +24186,10 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>122010905</v>
+        <v>122010907</v>
       </c>
       <c r="B214" t="n">
-        <v>98175</v>
+        <v>5173</v>
       </c>
       <c r="C214" t="inlineStr">
         <is>
@@ -24193,46 +24198,43 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E214" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I214" t="inlineStr"/>
-      <c r="J214" t="inlineStr"/>
-      <c r="K214" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L214" t="inlineStr"/>
-      <c r="N214" t="inlineStr"/>
+      <c r="M214" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P214" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>563702</v>
+        <v>563819</v>
       </c>
       <c r="R214" t="n">
-        <v>6704641</v>
+        <v>6704826</v>
       </c>
       <c r="S214" t="n">
         <v>10</v>
@@ -24273,7 +24275,6 @@
       <c r="AE214" t="b">
         <v>0</v>
       </c>
-      <c r="AF214" t="inlineStr"/>
       <c r="AG214" t="b">
         <v>0</v>
       </c>
@@ -24292,10 +24293,10 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>122010903</v>
+        <v>122010905</v>
       </c>
       <c r="B215" t="n">
-        <v>98175</v>
+        <v>98185</v>
       </c>
       <c r="C215" t="inlineStr">
         <is>
@@ -24340,10 +24341,10 @@
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>564274</v>
+        <v>563702</v>
       </c>
       <c r="R215" t="n">
-        <v>6705386</v>
+        <v>6704641</v>
       </c>
       <c r="S215" t="n">
         <v>10</v>
@@ -24403,10 +24404,10 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>122010909</v>
+        <v>122010895</v>
       </c>
       <c r="B216" t="n">
-        <v>5173</v>
+        <v>90789</v>
       </c>
       <c r="C216" t="inlineStr">
         <is>
@@ -24415,43 +24416,38 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E216" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I216" t="inlineStr"/>
-      <c r="M216" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P216" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>563850</v>
+        <v>563619</v>
       </c>
       <c r="R216" t="n">
-        <v>6704731</v>
+        <v>6704484</v>
       </c>
       <c r="S216" t="n">
         <v>10</v>
@@ -24510,10 +24506,10 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>122010908</v>
+        <v>122010903</v>
       </c>
       <c r="B217" t="n">
-        <v>5173</v>
+        <v>98185</v>
       </c>
       <c r="C217" t="inlineStr">
         <is>
@@ -24522,43 +24518,46 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E217" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I217" t="inlineStr"/>
-      <c r="M217" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
+      <c r="J217" t="inlineStr"/>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L217" t="inlineStr"/>
+      <c r="N217" t="inlineStr"/>
       <c r="P217" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>563625</v>
+        <v>564274</v>
       </c>
       <c r="R217" t="n">
-        <v>6704469</v>
+        <v>6705386</v>
       </c>
       <c r="S217" t="n">
         <v>10</v>
@@ -24599,6 +24598,7 @@
       <c r="AE217" t="b">
         <v>0</v>
       </c>
+      <c r="AF217" t="inlineStr"/>
       <c r="AG217" t="b">
         <v>0</v>
       </c>
@@ -24617,7 +24617,7 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>122010906</v>
+        <v>122010908</v>
       </c>
       <c r="B218" t="n">
         <v>5173</v>
@@ -24662,10 +24662,10 @@
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>563921</v>
+        <v>563625</v>
       </c>
       <c r="R218" t="n">
-        <v>6704919</v>
+        <v>6704469</v>
       </c>
       <c r="S218" t="n">
         <v>10</v>
@@ -24724,10 +24724,10 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>122010904</v>
+        <v>122010898</v>
       </c>
       <c r="B219" t="n">
-        <v>98175</v>
+        <v>57527</v>
       </c>
       <c r="C219" t="inlineStr">
         <is>
@@ -24736,46 +24736,38 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E219" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I219" t="inlineStr"/>
-      <c r="J219" t="inlineStr"/>
-      <c r="K219" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L219" t="inlineStr"/>
-      <c r="N219" t="inlineStr"/>
       <c r="P219" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>563814</v>
+        <v>563884</v>
       </c>
       <c r="R219" t="n">
-        <v>6704820</v>
+        <v>6704911</v>
       </c>
       <c r="S219" t="n">
         <v>10</v>
@@ -24816,7 +24808,6 @@
       <c r="AE219" t="b">
         <v>0</v>
       </c>
-      <c r="AF219" t="inlineStr"/>
       <c r="AG219" t="b">
         <v>0</v>
       </c>
@@ -24835,10 +24826,10 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>122010893</v>
+        <v>122010904</v>
       </c>
       <c r="B220" t="n">
-        <v>90744</v>
+        <v>98185</v>
       </c>
       <c r="C220" t="inlineStr">
         <is>
@@ -24847,38 +24838,46 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E220" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I220" t="inlineStr"/>
+      <c r="J220" t="inlineStr"/>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L220" t="inlineStr"/>
+      <c r="N220" t="inlineStr"/>
       <c r="P220" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>563600</v>
+        <v>563814</v>
       </c>
       <c r="R220" t="n">
-        <v>6704463</v>
+        <v>6704820</v>
       </c>
       <c r="S220" t="n">
         <v>10</v>
@@ -24919,6 +24918,7 @@
       <c r="AE220" t="b">
         <v>0</v>
       </c>
+      <c r="AF220" t="inlineStr"/>
       <c r="AG220" t="b">
         <v>0</v>
       </c>
@@ -24937,10 +24937,10 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>122010898</v>
+        <v>122010893</v>
       </c>
       <c r="B221" t="n">
-        <v>57527</v>
+        <v>90754</v>
       </c>
       <c r="C221" t="inlineStr">
         <is>
@@ -24949,25 +24949,25 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E221" t="n">
-        <v>103021</v>
+        <v>5447</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I221" t="inlineStr"/>
@@ -24977,10 +24977,10 @@
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>563884</v>
+        <v>563600</v>
       </c>
       <c r="R221" t="n">
-        <v>6704911</v>
+        <v>6704463</v>
       </c>
       <c r="S221" t="n">
         <v>10</v>

--- a/artfynd/A 58548-2022 artfynd.xlsx
+++ b/artfynd/A 58548-2022 artfynd.xlsx
@@ -23763,10 +23763,10 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>122010902</v>
+        <v>122010906</v>
       </c>
       <c r="B210" t="n">
-        <v>57390</v>
+        <v>5173</v>
       </c>
       <c r="C210" t="inlineStr">
         <is>
@@ -23775,31 +23775,31 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E210" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I210" t="inlineStr"/>
       <c r="M210" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P210" t="inlineStr">
@@ -23808,10 +23808,10 @@
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>563803</v>
+        <v>563921</v>
       </c>
       <c r="R210" t="n">
-        <v>6704669</v>
+        <v>6704919</v>
       </c>
       <c r="S210" t="n">
         <v>10</v>
@@ -23870,7 +23870,7 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>122010909</v>
+        <v>122010907</v>
       </c>
       <c r="B211" t="n">
         <v>5173</v>
@@ -23915,10 +23915,10 @@
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>563850</v>
+        <v>563819</v>
       </c>
       <c r="R211" t="n">
-        <v>6704731</v>
+        <v>6704826</v>
       </c>
       <c r="S211" t="n">
         <v>10</v>
@@ -23977,7 +23977,7 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>122010906</v>
+        <v>122010908</v>
       </c>
       <c r="B212" t="n">
         <v>5173</v>
@@ -24022,10 +24022,10 @@
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>563921</v>
+        <v>563625</v>
       </c>
       <c r="R212" t="n">
-        <v>6704919</v>
+        <v>6704469</v>
       </c>
       <c r="S212" t="n">
         <v>10</v>
@@ -24084,10 +24084,10 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>122010894</v>
+        <v>122010903</v>
       </c>
       <c r="B213" t="n">
-        <v>90789</v>
+        <v>98185</v>
       </c>
       <c r="C213" t="inlineStr">
         <is>
@@ -24096,38 +24096,46 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E213" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I213" t="inlineStr"/>
+      <c r="J213" t="inlineStr"/>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L213" t="inlineStr"/>
+      <c r="N213" t="inlineStr"/>
       <c r="P213" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>564343</v>
+        <v>564274</v>
       </c>
       <c r="R213" t="n">
-        <v>6705432</v>
+        <v>6705386</v>
       </c>
       <c r="S213" t="n">
         <v>10</v>
@@ -24168,6 +24176,7 @@
       <c r="AE213" t="b">
         <v>0</v>
       </c>
+      <c r="AF213" t="inlineStr"/>
       <c r="AG213" t="b">
         <v>0</v>
       </c>
@@ -24186,10 +24195,10 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>122010907</v>
+        <v>122010895</v>
       </c>
       <c r="B214" t="n">
-        <v>5173</v>
+        <v>90789</v>
       </c>
       <c r="C214" t="inlineStr">
         <is>
@@ -24198,43 +24207,38 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E214" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I214" t="inlineStr"/>
-      <c r="M214" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P214" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>563819</v>
+        <v>563619</v>
       </c>
       <c r="R214" t="n">
-        <v>6704826</v>
+        <v>6704484</v>
       </c>
       <c r="S214" t="n">
         <v>10</v>
@@ -24293,10 +24297,10 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>122010905</v>
+        <v>122010898</v>
       </c>
       <c r="B215" t="n">
-        <v>98185</v>
+        <v>57527</v>
       </c>
       <c r="C215" t="inlineStr">
         <is>
@@ -24305,46 +24309,38 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E215" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I215" t="inlineStr"/>
-      <c r="J215" t="inlineStr"/>
-      <c r="K215" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L215" t="inlineStr"/>
-      <c r="N215" t="inlineStr"/>
       <c r="P215" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>563702</v>
+        <v>563884</v>
       </c>
       <c r="R215" t="n">
-        <v>6704641</v>
+        <v>6704911</v>
       </c>
       <c r="S215" t="n">
         <v>10</v>
@@ -24385,7 +24381,6 @@
       <c r="AE215" t="b">
         <v>0</v>
       </c>
-      <c r="AF215" t="inlineStr"/>
       <c r="AG215" t="b">
         <v>0</v>
       </c>
@@ -24404,10 +24399,10 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>122010895</v>
+        <v>122010905</v>
       </c>
       <c r="B216" t="n">
-        <v>90789</v>
+        <v>98185</v>
       </c>
       <c r="C216" t="inlineStr">
         <is>
@@ -24416,38 +24411,46 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E216" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I216" t="inlineStr"/>
+      <c r="J216" t="inlineStr"/>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L216" t="inlineStr"/>
+      <c r="N216" t="inlineStr"/>
       <c r="P216" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>563619</v>
+        <v>563702</v>
       </c>
       <c r="R216" t="n">
-        <v>6704484</v>
+        <v>6704641</v>
       </c>
       <c r="S216" t="n">
         <v>10</v>
@@ -24488,6 +24491,7 @@
       <c r="AE216" t="b">
         <v>0</v>
       </c>
+      <c r="AF216" t="inlineStr"/>
       <c r="AG216" t="b">
         <v>0</v>
       </c>
@@ -24506,10 +24510,10 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>122010903</v>
+        <v>122010909</v>
       </c>
       <c r="B217" t="n">
-        <v>98185</v>
+        <v>5173</v>
       </c>
       <c r="C217" t="inlineStr">
         <is>
@@ -24518,46 +24522,43 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E217" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I217" t="inlineStr"/>
-      <c r="J217" t="inlineStr"/>
-      <c r="K217" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L217" t="inlineStr"/>
-      <c r="N217" t="inlineStr"/>
+      <c r="M217" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P217" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>564274</v>
+        <v>563850</v>
       </c>
       <c r="R217" t="n">
-        <v>6705386</v>
+        <v>6704731</v>
       </c>
       <c r="S217" t="n">
         <v>10</v>
@@ -24598,7 +24599,6 @@
       <c r="AE217" t="b">
         <v>0</v>
       </c>
-      <c r="AF217" t="inlineStr"/>
       <c r="AG217" t="b">
         <v>0</v>
       </c>
@@ -24617,10 +24617,10 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>122010908</v>
+        <v>122010904</v>
       </c>
       <c r="B218" t="n">
-        <v>5173</v>
+        <v>98185</v>
       </c>
       <c r="C218" t="inlineStr">
         <is>
@@ -24629,43 +24629,46 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E218" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I218" t="inlineStr"/>
-      <c r="M218" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
+      <c r="J218" t="inlineStr"/>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L218" t="inlineStr"/>
+      <c r="N218" t="inlineStr"/>
       <c r="P218" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>563625</v>
+        <v>563814</v>
       </c>
       <c r="R218" t="n">
-        <v>6704469</v>
+        <v>6704820</v>
       </c>
       <c r="S218" t="n">
         <v>10</v>
@@ -24706,6 +24709,7 @@
       <c r="AE218" t="b">
         <v>0</v>
       </c>
+      <c r="AF218" t="inlineStr"/>
       <c r="AG218" t="b">
         <v>0</v>
       </c>
@@ -24724,10 +24728,10 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>122010898</v>
+        <v>122010894</v>
       </c>
       <c r="B219" t="n">
-        <v>57527</v>
+        <v>90789</v>
       </c>
       <c r="C219" t="inlineStr">
         <is>
@@ -24740,21 +24744,21 @@
         </is>
       </c>
       <c r="E219" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I219" t="inlineStr"/>
@@ -24764,10 +24768,10 @@
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>563884</v>
+        <v>564343</v>
       </c>
       <c r="R219" t="n">
-        <v>6704911</v>
+        <v>6705432</v>
       </c>
       <c r="S219" t="n">
         <v>10</v>
@@ -24826,10 +24830,10 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>122010904</v>
+        <v>122010893</v>
       </c>
       <c r="B220" t="n">
-        <v>98185</v>
+        <v>90754</v>
       </c>
       <c r="C220" t="inlineStr">
         <is>
@@ -24838,46 +24842,38 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E220" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I220" t="inlineStr"/>
-      <c r="J220" t="inlineStr"/>
-      <c r="K220" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L220" t="inlineStr"/>
-      <c r="N220" t="inlineStr"/>
       <c r="P220" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>563814</v>
+        <v>563600</v>
       </c>
       <c r="R220" t="n">
-        <v>6704820</v>
+        <v>6704463</v>
       </c>
       <c r="S220" t="n">
         <v>10</v>
@@ -24918,7 +24914,6 @@
       <c r="AE220" t="b">
         <v>0</v>
       </c>
-      <c r="AF220" t="inlineStr"/>
       <c r="AG220" t="b">
         <v>0</v>
       </c>
@@ -24937,10 +24932,10 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>122010893</v>
+        <v>122010902</v>
       </c>
       <c r="B221" t="n">
-        <v>90754</v>
+        <v>57390</v>
       </c>
       <c r="C221" t="inlineStr">
         <is>
@@ -24949,38 +24944,43 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E221" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I221" t="inlineStr"/>
+      <c r="M221" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P221" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>563600</v>
+        <v>563803</v>
       </c>
       <c r="R221" t="n">
-        <v>6704463</v>
+        <v>6704669</v>
       </c>
       <c r="S221" t="n">
         <v>10</v>

--- a/artfynd/A 58548-2022 artfynd.xlsx
+++ b/artfynd/A 58548-2022 artfynd.xlsx
@@ -24297,10 +24297,10 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>122010898</v>
+        <v>122010905</v>
       </c>
       <c r="B215" t="n">
-        <v>57527</v>
+        <v>98185</v>
       </c>
       <c r="C215" t="inlineStr">
         <is>
@@ -24309,38 +24309,46 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E215" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I215" t="inlineStr"/>
+      <c r="J215" t="inlineStr"/>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L215" t="inlineStr"/>
+      <c r="N215" t="inlineStr"/>
       <c r="P215" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>563884</v>
+        <v>563702</v>
       </c>
       <c r="R215" t="n">
-        <v>6704911</v>
+        <v>6704641</v>
       </c>
       <c r="S215" t="n">
         <v>10</v>
@@ -24381,6 +24389,7 @@
       <c r="AE215" t="b">
         <v>0</v>
       </c>
+      <c r="AF215" t="inlineStr"/>
       <c r="AG215" t="b">
         <v>0</v>
       </c>
@@ -24399,10 +24408,10 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>122010905</v>
+        <v>122010898</v>
       </c>
       <c r="B216" t="n">
-        <v>98185</v>
+        <v>57527</v>
       </c>
       <c r="C216" t="inlineStr">
         <is>
@@ -24411,46 +24420,38 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E216" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I216" t="inlineStr"/>
-      <c r="J216" t="inlineStr"/>
-      <c r="K216" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L216" t="inlineStr"/>
-      <c r="N216" t="inlineStr"/>
       <c r="P216" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>563702</v>
+        <v>563884</v>
       </c>
       <c r="R216" t="n">
-        <v>6704641</v>
+        <v>6704911</v>
       </c>
       <c r="S216" t="n">
         <v>10</v>
@@ -24491,7 +24492,6 @@
       <c r="AE216" t="b">
         <v>0</v>
       </c>
-      <c r="AF216" t="inlineStr"/>
       <c r="AG216" t="b">
         <v>0</v>
       </c>
@@ -24830,10 +24830,10 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>122010893</v>
+        <v>122010902</v>
       </c>
       <c r="B220" t="n">
-        <v>90754</v>
+        <v>57390</v>
       </c>
       <c r="C220" t="inlineStr">
         <is>
@@ -24842,38 +24842,43 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E220" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I220" t="inlineStr"/>
+      <c r="M220" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P220" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>563600</v>
+        <v>563803</v>
       </c>
       <c r="R220" t="n">
-        <v>6704463</v>
+        <v>6704669</v>
       </c>
       <c r="S220" t="n">
         <v>10</v>
@@ -24932,10 +24937,10 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>122010902</v>
+        <v>122010893</v>
       </c>
       <c r="B221" t="n">
-        <v>57390</v>
+        <v>90754</v>
       </c>
       <c r="C221" t="inlineStr">
         <is>
@@ -24944,43 +24949,38 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E221" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I221" t="inlineStr"/>
-      <c r="M221" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P221" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>563803</v>
+        <v>563600</v>
       </c>
       <c r="R221" t="n">
-        <v>6704669</v>
+        <v>6704463</v>
       </c>
       <c r="S221" t="n">
         <v>10</v>

--- a/artfynd/A 58548-2022 artfynd.xlsx
+++ b/artfynd/A 58548-2022 artfynd.xlsx
@@ -23870,7 +23870,7 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>122010907</v>
+        <v>122010909</v>
       </c>
       <c r="B211" t="n">
         <v>5173</v>
@@ -23915,10 +23915,10 @@
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>563819</v>
+        <v>563850</v>
       </c>
       <c r="R211" t="n">
-        <v>6704826</v>
+        <v>6704731</v>
       </c>
       <c r="S211" t="n">
         <v>10</v>
@@ -23977,10 +23977,10 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>122010908</v>
+        <v>122010902</v>
       </c>
       <c r="B212" t="n">
-        <v>5173</v>
+        <v>57395</v>
       </c>
       <c r="C212" t="inlineStr">
         <is>
@@ -23989,31 +23989,31 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E212" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I212" t="inlineStr"/>
       <c r="M212" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P212" t="inlineStr">
@@ -24022,10 +24022,10 @@
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>563625</v>
+        <v>563803</v>
       </c>
       <c r="R212" t="n">
-        <v>6704469</v>
+        <v>6704669</v>
       </c>
       <c r="S212" t="n">
         <v>10</v>
@@ -24087,7 +24087,7 @@
         <v>122010903</v>
       </c>
       <c r="B213" t="n">
-        <v>98185</v>
+        <v>98197</v>
       </c>
       <c r="C213" t="inlineStr">
         <is>
@@ -24195,10 +24195,10 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>122010895</v>
+        <v>122010893</v>
       </c>
       <c r="B214" t="n">
-        <v>90789</v>
+        <v>90766</v>
       </c>
       <c r="C214" t="inlineStr">
         <is>
@@ -24207,25 +24207,25 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E214" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I214" t="inlineStr"/>
@@ -24235,10 +24235,10 @@
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>563619</v>
+        <v>563600</v>
       </c>
       <c r="R214" t="n">
-        <v>6704484</v>
+        <v>6704463</v>
       </c>
       <c r="S214" t="n">
         <v>10</v>
@@ -24297,10 +24297,10 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>122010905</v>
+        <v>122010904</v>
       </c>
       <c r="B215" t="n">
-        <v>98185</v>
+        <v>98197</v>
       </c>
       <c r="C215" t="inlineStr">
         <is>
@@ -24345,10 +24345,10 @@
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>563702</v>
+        <v>563814</v>
       </c>
       <c r="R215" t="n">
-        <v>6704641</v>
+        <v>6704820</v>
       </c>
       <c r="S215" t="n">
         <v>10</v>
@@ -24408,10 +24408,10 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>122010898</v>
+        <v>122010908</v>
       </c>
       <c r="B216" t="n">
-        <v>57527</v>
+        <v>5173</v>
       </c>
       <c r="C216" t="inlineStr">
         <is>
@@ -24420,38 +24420,43 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E216" t="n">
-        <v>103021</v>
+        <v>100526</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I216" t="inlineStr"/>
+      <c r="M216" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P216" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>563884</v>
+        <v>563625</v>
       </c>
       <c r="R216" t="n">
-        <v>6704911</v>
+        <v>6704469</v>
       </c>
       <c r="S216" t="n">
         <v>10</v>
@@ -24510,10 +24515,10 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>122010909</v>
+        <v>122010905</v>
       </c>
       <c r="B217" t="n">
-        <v>5173</v>
+        <v>98197</v>
       </c>
       <c r="C217" t="inlineStr">
         <is>
@@ -24522,43 +24527,46 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E217" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I217" t="inlineStr"/>
-      <c r="M217" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
+      <c r="J217" t="inlineStr"/>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L217" t="inlineStr"/>
+      <c r="N217" t="inlineStr"/>
       <c r="P217" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>563850</v>
+        <v>563702</v>
       </c>
       <c r="R217" t="n">
-        <v>6704731</v>
+        <v>6704641</v>
       </c>
       <c r="S217" t="n">
         <v>10</v>
@@ -24599,6 +24607,7 @@
       <c r="AE217" t="b">
         <v>0</v>
       </c>
+      <c r="AF217" t="inlineStr"/>
       <c r="AG217" t="b">
         <v>0</v>
       </c>
@@ -24617,10 +24626,10 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>122010904</v>
+        <v>122010898</v>
       </c>
       <c r="B218" t="n">
-        <v>98185</v>
+        <v>57532</v>
       </c>
       <c r="C218" t="inlineStr">
         <is>
@@ -24629,46 +24638,38 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E218" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I218" t="inlineStr"/>
-      <c r="J218" t="inlineStr"/>
-      <c r="K218" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L218" t="inlineStr"/>
-      <c r="N218" t="inlineStr"/>
       <c r="P218" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>563814</v>
+        <v>563884</v>
       </c>
       <c r="R218" t="n">
-        <v>6704820</v>
+        <v>6704911</v>
       </c>
       <c r="S218" t="n">
         <v>10</v>
@@ -24709,7 +24710,6 @@
       <c r="AE218" t="b">
         <v>0</v>
       </c>
-      <c r="AF218" t="inlineStr"/>
       <c r="AG218" t="b">
         <v>0</v>
       </c>
@@ -24731,7 +24731,7 @@
         <v>122010894</v>
       </c>
       <c r="B219" t="n">
-        <v>90789</v>
+        <v>90801</v>
       </c>
       <c r="C219" t="inlineStr">
         <is>
@@ -24830,10 +24830,10 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>122010902</v>
+        <v>122010895</v>
       </c>
       <c r="B220" t="n">
-        <v>57390</v>
+        <v>90801</v>
       </c>
       <c r="C220" t="inlineStr">
         <is>
@@ -24846,39 +24846,34 @@
         </is>
       </c>
       <c r="E220" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I220" t="inlineStr"/>
-      <c r="M220" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P220" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>563803</v>
+        <v>563619</v>
       </c>
       <c r="R220" t="n">
-        <v>6704669</v>
+        <v>6704484</v>
       </c>
       <c r="S220" t="n">
         <v>10</v>
@@ -24937,10 +24932,10 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>122010893</v>
+        <v>122010907</v>
       </c>
       <c r="B221" t="n">
-        <v>90754</v>
+        <v>5173</v>
       </c>
       <c r="C221" t="inlineStr">
         <is>
@@ -24953,34 +24948,39 @@
         </is>
       </c>
       <c r="E221" t="n">
-        <v>5447</v>
+        <v>100526</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I221" t="inlineStr"/>
+      <c r="M221" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P221" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>563600</v>
+        <v>563819</v>
       </c>
       <c r="R221" t="n">
-        <v>6704463</v>
+        <v>6704826</v>
       </c>
       <c r="S221" t="n">
         <v>10</v>

--- a/artfynd/A 58548-2022 artfynd.xlsx
+++ b/artfynd/A 58548-2022 artfynd.xlsx
@@ -23763,10 +23763,10 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>122010906</v>
+        <v>122010894</v>
       </c>
       <c r="B210" t="n">
-        <v>5173</v>
+        <v>90808</v>
       </c>
       <c r="C210" t="inlineStr">
         <is>
@@ -23775,43 +23775,38 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E210" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I210" t="inlineStr"/>
-      <c r="M210" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P210" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>563921</v>
+        <v>564343</v>
       </c>
       <c r="R210" t="n">
-        <v>6704919</v>
+        <v>6705432</v>
       </c>
       <c r="S210" t="n">
         <v>10</v>
@@ -23870,10 +23865,10 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>122010909</v>
+        <v>122010903</v>
       </c>
       <c r="B211" t="n">
-        <v>5173</v>
+        <v>98202</v>
       </c>
       <c r="C211" t="inlineStr">
         <is>
@@ -23882,43 +23877,46 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E211" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I211" t="inlineStr"/>
-      <c r="M211" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
+      <c r="J211" t="inlineStr"/>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L211" t="inlineStr"/>
+      <c r="N211" t="inlineStr"/>
       <c r="P211" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>563850</v>
+        <v>564274</v>
       </c>
       <c r="R211" t="n">
-        <v>6704731</v>
+        <v>6705386</v>
       </c>
       <c r="S211" t="n">
         <v>10</v>
@@ -23959,6 +23957,7 @@
       <c r="AE211" t="b">
         <v>0</v>
       </c>
+      <c r="AF211" t="inlineStr"/>
       <c r="AG211" t="b">
         <v>0</v>
       </c>
@@ -23977,10 +23976,10 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>122010902</v>
+        <v>122010909</v>
       </c>
       <c r="B212" t="n">
-        <v>57395</v>
+        <v>5173</v>
       </c>
       <c r="C212" t="inlineStr">
         <is>
@@ -23989,31 +23988,31 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E212" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I212" t="inlineStr"/>
       <c r="M212" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P212" t="inlineStr">
@@ -24022,10 +24021,10 @@
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>563803</v>
+        <v>563850</v>
       </c>
       <c r="R212" t="n">
-        <v>6704669</v>
+        <v>6704731</v>
       </c>
       <c r="S212" t="n">
         <v>10</v>
@@ -24084,10 +24083,10 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>122010903</v>
+        <v>122010895</v>
       </c>
       <c r="B213" t="n">
-        <v>98197</v>
+        <v>90808</v>
       </c>
       <c r="C213" t="inlineStr">
         <is>
@@ -24096,46 +24095,38 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E213" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I213" t="inlineStr"/>
-      <c r="J213" t="inlineStr"/>
-      <c r="K213" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L213" t="inlineStr"/>
-      <c r="N213" t="inlineStr"/>
       <c r="P213" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>564274</v>
+        <v>563619</v>
       </c>
       <c r="R213" t="n">
-        <v>6705386</v>
+        <v>6704484</v>
       </c>
       <c r="S213" t="n">
         <v>10</v>
@@ -24176,7 +24167,6 @@
       <c r="AE213" t="b">
         <v>0</v>
       </c>
-      <c r="AF213" t="inlineStr"/>
       <c r="AG213" t="b">
         <v>0</v>
       </c>
@@ -24195,10 +24185,10 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>122010893</v>
+        <v>122010908</v>
       </c>
       <c r="B214" t="n">
-        <v>90766</v>
+        <v>5173</v>
       </c>
       <c r="C214" t="inlineStr">
         <is>
@@ -24211,34 +24201,39 @@
         </is>
       </c>
       <c r="E214" t="n">
-        <v>5447</v>
+        <v>100526</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I214" t="inlineStr"/>
+      <c r="M214" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P214" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>563600</v>
+        <v>563625</v>
       </c>
       <c r="R214" t="n">
-        <v>6704463</v>
+        <v>6704469</v>
       </c>
       <c r="S214" t="n">
         <v>10</v>
@@ -24297,10 +24292,10 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>122010904</v>
+        <v>122010902</v>
       </c>
       <c r="B215" t="n">
-        <v>98197</v>
+        <v>57395</v>
       </c>
       <c r="C215" t="inlineStr">
         <is>
@@ -24309,46 +24304,43 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E215" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I215" t="inlineStr"/>
-      <c r="J215" t="inlineStr"/>
-      <c r="K215" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L215" t="inlineStr"/>
-      <c r="N215" t="inlineStr"/>
+      <c r="M215" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P215" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>563814</v>
+        <v>563803</v>
       </c>
       <c r="R215" t="n">
-        <v>6704820</v>
+        <v>6704669</v>
       </c>
       <c r="S215" t="n">
         <v>10</v>
@@ -24389,7 +24381,6 @@
       <c r="AE215" t="b">
         <v>0</v>
       </c>
-      <c r="AF215" t="inlineStr"/>
       <c r="AG215" t="b">
         <v>0</v>
       </c>
@@ -24408,10 +24399,10 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>122010908</v>
+        <v>122010904</v>
       </c>
       <c r="B216" t="n">
-        <v>5173</v>
+        <v>98202</v>
       </c>
       <c r="C216" t="inlineStr">
         <is>
@@ -24420,43 +24411,46 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E216" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I216" t="inlineStr"/>
-      <c r="M216" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
+      <c r="J216" t="inlineStr"/>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L216" t="inlineStr"/>
+      <c r="N216" t="inlineStr"/>
       <c r="P216" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>563625</v>
+        <v>563814</v>
       </c>
       <c r="R216" t="n">
-        <v>6704469</v>
+        <v>6704820</v>
       </c>
       <c r="S216" t="n">
         <v>10</v>
@@ -24497,6 +24491,7 @@
       <c r="AE216" t="b">
         <v>0</v>
       </c>
+      <c r="AF216" t="inlineStr"/>
       <c r="AG216" t="b">
         <v>0</v>
       </c>
@@ -24518,7 +24513,7 @@
         <v>122010905</v>
       </c>
       <c r="B217" t="n">
-        <v>98197</v>
+        <v>98202</v>
       </c>
       <c r="C217" t="inlineStr">
         <is>
@@ -24626,10 +24621,10 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>122010898</v>
+        <v>122010907</v>
       </c>
       <c r="B218" t="n">
-        <v>57532</v>
+        <v>5173</v>
       </c>
       <c r="C218" t="inlineStr">
         <is>
@@ -24638,38 +24633,43 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E218" t="n">
-        <v>103021</v>
+        <v>100526</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I218" t="inlineStr"/>
+      <c r="M218" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P218" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>563884</v>
+        <v>563819</v>
       </c>
       <c r="R218" t="n">
-        <v>6704911</v>
+        <v>6704826</v>
       </c>
       <c r="S218" t="n">
         <v>10</v>
@@ -24728,10 +24728,10 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>122010894</v>
+        <v>122010906</v>
       </c>
       <c r="B219" t="n">
-        <v>90801</v>
+        <v>5173</v>
       </c>
       <c r="C219" t="inlineStr">
         <is>
@@ -24740,38 +24740,43 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E219" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I219" t="inlineStr"/>
+      <c r="M219" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P219" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>564343</v>
+        <v>563921</v>
       </c>
       <c r="R219" t="n">
-        <v>6705432</v>
+        <v>6704919</v>
       </c>
       <c r="S219" t="n">
         <v>10</v>
@@ -24830,10 +24835,10 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>122010895</v>
+        <v>122010898</v>
       </c>
       <c r="B220" t="n">
-        <v>90801</v>
+        <v>57532</v>
       </c>
       <c r="C220" t="inlineStr">
         <is>
@@ -24846,21 +24851,21 @@
         </is>
       </c>
       <c r="E220" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I220" t="inlineStr"/>
@@ -24870,10 +24875,10 @@
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>563619</v>
+        <v>563884</v>
       </c>
       <c r="R220" t="n">
-        <v>6704484</v>
+        <v>6704911</v>
       </c>
       <c r="S220" t="n">
         <v>10</v>
@@ -24932,10 +24937,10 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>122010907</v>
+        <v>122010893</v>
       </c>
       <c r="B221" t="n">
-        <v>5173</v>
+        <v>90773</v>
       </c>
       <c r="C221" t="inlineStr">
         <is>
@@ -24948,39 +24953,34 @@
         </is>
       </c>
       <c r="E221" t="n">
-        <v>100526</v>
+        <v>5447</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I221" t="inlineStr"/>
-      <c r="M221" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P221" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>563819</v>
+        <v>563600</v>
       </c>
       <c r="R221" t="n">
-        <v>6704826</v>
+        <v>6704463</v>
       </c>
       <c r="S221" t="n">
         <v>10</v>

--- a/artfynd/A 58548-2022 artfynd.xlsx
+++ b/artfynd/A 58548-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY221"/>
+  <dimension ref="A1:AY223"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25037,6 +25037,219 @@
       </c>
       <c r="AY221" t="inlineStr"/>
     </row>
+    <row r="222">
+      <c r="A222" t="n">
+        <v>123380239</v>
+      </c>
+      <c r="B222" t="n">
+        <v>90952</v>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E222" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I222" t="inlineStr"/>
+      <c r="P222" t="inlineStr">
+        <is>
+          <t>Pellkärret, Dlr</t>
+        </is>
+      </c>
+      <c r="Q222" t="n">
+        <v>564078</v>
+      </c>
+      <c r="R222" t="n">
+        <v>6705115</v>
+      </c>
+      <c r="S222" t="n">
+        <v>10</v>
+      </c>
+      <c r="T222" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U222" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V222" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W222" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y222" t="inlineStr">
+        <is>
+          <t>2025-03-22</t>
+        </is>
+      </c>
+      <c r="AA222" t="inlineStr">
+        <is>
+          <t>2025-03-22</t>
+        </is>
+      </c>
+      <c r="AD222" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE222" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG222" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT222" t="inlineStr"/>
+      <c r="AW222" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX222" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY222" t="inlineStr"/>
+    </row>
+    <row r="223">
+      <c r="A223" t="n">
+        <v>123380241</v>
+      </c>
+      <c r="B223" t="n">
+        <v>98365</v>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E223" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J223" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P223" t="inlineStr">
+        <is>
+          <t>Pellkärret, Dlr</t>
+        </is>
+      </c>
+      <c r="Q223" t="n">
+        <v>564111</v>
+      </c>
+      <c r="R223" t="n">
+        <v>6705156</v>
+      </c>
+      <c r="S223" t="n">
+        <v>10</v>
+      </c>
+      <c r="T223" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U223" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V223" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W223" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y223" t="inlineStr">
+        <is>
+          <t>2025-03-22</t>
+        </is>
+      </c>
+      <c r="AA223" t="inlineStr">
+        <is>
+          <t>2025-03-22</t>
+        </is>
+      </c>
+      <c r="AD223" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE223" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG223" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT223" t="inlineStr"/>
+      <c r="AW223" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX223" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY223" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 58548-2022 artfynd.xlsx
+++ b/artfynd/A 58548-2022 artfynd.xlsx
@@ -25039,10 +25039,10 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>123380239</v>
+        <v>123380241</v>
       </c>
       <c r="B222" t="n">
-        <v>90952</v>
+        <v>98368</v>
       </c>
       <c r="C222" t="inlineStr">
         <is>
@@ -25051,38 +25051,47 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E222" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I222" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J222" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P222" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>564078</v>
+        <v>564111</v>
       </c>
       <c r="R222" t="n">
-        <v>6705115</v>
+        <v>6705156</v>
       </c>
       <c r="S222" t="n">
         <v>10</v>
@@ -25141,10 +25150,10 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>123380241</v>
+        <v>123380239</v>
       </c>
       <c r="B223" t="n">
-        <v>98365</v>
+        <v>90955</v>
       </c>
       <c r="C223" t="inlineStr">
         <is>
@@ -25153,47 +25162,38 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E223" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I223" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J223" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I223" t="inlineStr"/>
       <c r="P223" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>564111</v>
+        <v>564078</v>
       </c>
       <c r="R223" t="n">
-        <v>6705156</v>
+        <v>6705115</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>

--- a/artfynd/A 58548-2022 artfynd.xlsx
+++ b/artfynd/A 58548-2022 artfynd.xlsx
@@ -25039,10 +25039,10 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>123380241</v>
+        <v>123380239</v>
       </c>
       <c r="B222" t="n">
-        <v>98368</v>
+        <v>90957</v>
       </c>
       <c r="C222" t="inlineStr">
         <is>
@@ -25051,47 +25051,38 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E222" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I222" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J222" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I222" t="inlineStr"/>
       <c r="P222" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>564111</v>
+        <v>564078</v>
       </c>
       <c r="R222" t="n">
-        <v>6705156</v>
+        <v>6705115</v>
       </c>
       <c r="S222" t="n">
         <v>10</v>
@@ -25150,10 +25141,10 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>123380239</v>
+        <v>123380241</v>
       </c>
       <c r="B223" t="n">
-        <v>90955</v>
+        <v>98370</v>
       </c>
       <c r="C223" t="inlineStr">
         <is>
@@ -25162,38 +25153,47 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E223" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I223" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J223" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P223" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>564078</v>
+        <v>564111</v>
       </c>
       <c r="R223" t="n">
-        <v>6705115</v>
+        <v>6705156</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>

--- a/artfynd/A 58548-2022 artfynd.xlsx
+++ b/artfynd/A 58548-2022 artfynd.xlsx
@@ -25042,7 +25042,7 @@
         <v>123380239</v>
       </c>
       <c r="B222" t="n">
-        <v>90957</v>
+        <v>90963</v>
       </c>
       <c r="C222" t="inlineStr">
         <is>
@@ -25144,7 +25144,7 @@
         <v>123380241</v>
       </c>
       <c r="B223" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C223" t="inlineStr">
         <is>

--- a/artfynd/A 58548-2022 artfynd.xlsx
+++ b/artfynd/A 58548-2022 artfynd.xlsx
@@ -25039,10 +25039,10 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>123380241</v>
+        <v>123380239</v>
       </c>
       <c r="B222" t="n">
-        <v>98379</v>
+        <v>90983</v>
       </c>
       <c r="C222" t="inlineStr">
         <is>
@@ -25051,47 +25051,38 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E222" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I222" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J222" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I222" t="inlineStr"/>
       <c r="P222" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>564111</v>
+        <v>564078</v>
       </c>
       <c r="R222" t="n">
-        <v>6705156</v>
+        <v>6705115</v>
       </c>
       <c r="S222" t="n">
         <v>10</v>
@@ -25150,10 +25141,10 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>123380239</v>
+        <v>123380241</v>
       </c>
       <c r="B223" t="n">
-        <v>90966</v>
+        <v>98396</v>
       </c>
       <c r="C223" t="inlineStr">
         <is>
@@ -25162,38 +25153,47 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E223" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I223" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J223" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P223" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>564078</v>
+        <v>564111</v>
       </c>
       <c r="R223" t="n">
-        <v>6705115</v>
+        <v>6705156</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>

--- a/artfynd/A 58548-2022 artfynd.xlsx
+++ b/artfynd/A 58548-2022 artfynd.xlsx
@@ -25039,10 +25039,10 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>123380239</v>
+        <v>123380241</v>
       </c>
       <c r="B222" t="n">
-        <v>90983</v>
+        <v>98502</v>
       </c>
       <c r="C222" t="inlineStr">
         <is>
@@ -25051,38 +25051,47 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E222" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I222" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J222" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P222" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>564078</v>
+        <v>564111</v>
       </c>
       <c r="R222" t="n">
-        <v>6705115</v>
+        <v>6705156</v>
       </c>
       <c r="S222" t="n">
         <v>10</v>
@@ -25141,10 +25150,10 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>123380241</v>
+        <v>123380239</v>
       </c>
       <c r="B223" t="n">
-        <v>98396</v>
+        <v>90988</v>
       </c>
       <c r="C223" t="inlineStr">
         <is>
@@ -25153,47 +25162,38 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E223" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I223" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J223" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I223" t="inlineStr"/>
       <c r="P223" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>564111</v>
+        <v>564078</v>
       </c>
       <c r="R223" t="n">
-        <v>6705156</v>
+        <v>6705115</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>

--- a/artfynd/A 58548-2022 artfynd.xlsx
+++ b/artfynd/A 58548-2022 artfynd.xlsx
@@ -24926,10 +24926,10 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>123380239</v>
+        <v>123380241</v>
       </c>
       <c r="B221" t="n">
-        <v>90990</v>
+        <v>98079</v>
       </c>
       <c r="C221" t="inlineStr">
         <is>
@@ -24938,38 +24938,47 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E221" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I221" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J221" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P221" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>564078</v>
+        <v>564111</v>
       </c>
       <c r="R221" t="n">
-        <v>6705115</v>
+        <v>6705156</v>
       </c>
       <c r="S221" t="n">
         <v>10</v>
@@ -25028,10 +25037,10 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>123380241</v>
+        <v>123380239</v>
       </c>
       <c r="B222" t="n">
-        <v>98504</v>
+        <v>90990</v>
       </c>
       <c r="C222" t="inlineStr">
         <is>
@@ -25040,47 +25049,38 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E222" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I222" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J222" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I222" t="inlineStr"/>
       <c r="P222" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>564111</v>
+        <v>564078</v>
       </c>
       <c r="R222" t="n">
-        <v>6705156</v>
+        <v>6705115</v>
       </c>
       <c r="S222" t="n">
         <v>10</v>

--- a/artfynd/A 58548-2022 artfynd.xlsx
+++ b/artfynd/A 58548-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY222"/>
+  <dimension ref="A1:AY265"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25137,6 +25137,4363 @@
       </c>
       <c r="AY222" t="inlineStr"/>
     </row>
+    <row r="223">
+      <c r="A223" t="n">
+        <v>127683156</v>
+      </c>
+      <c r="B223" t="n">
+        <v>57658</v>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E223" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I223" t="inlineStr"/>
+      <c r="M223" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P223" t="inlineStr">
+        <is>
+          <t>Pellkärret, Dlr</t>
+        </is>
+      </c>
+      <c r="Q223" t="n">
+        <v>564124</v>
+      </c>
+      <c r="R223" t="n">
+        <v>6705171</v>
+      </c>
+      <c r="S223" t="n">
+        <v>10</v>
+      </c>
+      <c r="T223" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U223" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V223" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W223" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y223" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AA223" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AD223" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE223" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG223" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT223" t="inlineStr"/>
+      <c r="AW223" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX223" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY223" t="inlineStr"/>
+    </row>
+    <row r="224">
+      <c r="A224" t="n">
+        <v>127683140</v>
+      </c>
+      <c r="B224" t="n">
+        <v>91330</v>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E224" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I224" t="inlineStr"/>
+      <c r="P224" t="inlineStr">
+        <is>
+          <t>Pellkärret, Dlr</t>
+        </is>
+      </c>
+      <c r="Q224" t="n">
+        <v>564253</v>
+      </c>
+      <c r="R224" t="n">
+        <v>6705225</v>
+      </c>
+      <c r="S224" t="n">
+        <v>10</v>
+      </c>
+      <c r="T224" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U224" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V224" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W224" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y224" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AA224" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AD224" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE224" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG224" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT224" t="inlineStr"/>
+      <c r="AW224" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX224" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY224" t="inlineStr"/>
+    </row>
+    <row r="225">
+      <c r="A225" t="n">
+        <v>127683181</v>
+      </c>
+      <c r="B225" t="n">
+        <v>91696</v>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E225" t="n">
+        <v>2064</v>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>Kilporing</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>Skeletocutis kuehneri</t>
+        </is>
+      </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>A.David</t>
+        </is>
+      </c>
+      <c r="I225" t="inlineStr"/>
+      <c r="P225" t="inlineStr">
+        <is>
+          <t>Pellkärret, Dlr</t>
+        </is>
+      </c>
+      <c r="Q225" t="n">
+        <v>564128</v>
+      </c>
+      <c r="R225" t="n">
+        <v>6705055</v>
+      </c>
+      <c r="S225" t="n">
+        <v>10</v>
+      </c>
+      <c r="T225" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U225" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V225" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W225" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y225" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AA225" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AC225" t="inlineStr">
+        <is>
+          <t>Kommer att mikroskoperas</t>
+        </is>
+      </c>
+      <c r="AD225" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE225" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG225" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT225" t="inlineStr"/>
+      <c r="AW225" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX225" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY225" t="inlineStr"/>
+    </row>
+    <row r="226">
+      <c r="A226" t="n">
+        <v>127683183</v>
+      </c>
+      <c r="B226" t="n">
+        <v>98448</v>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E226" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J226" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="P226" t="inlineStr">
+        <is>
+          <t>Pellkärret, Dlr</t>
+        </is>
+      </c>
+      <c r="Q226" t="n">
+        <v>564023</v>
+      </c>
+      <c r="R226" t="n">
+        <v>6705072</v>
+      </c>
+      <c r="S226" t="n">
+        <v>10</v>
+      </c>
+      <c r="T226" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U226" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V226" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W226" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y226" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AA226" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AC226" t="inlineStr">
+        <is>
+          <t>2 blomstjälkar</t>
+        </is>
+      </c>
+      <c r="AD226" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE226" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG226" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT226" t="inlineStr"/>
+      <c r="AW226" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX226" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY226" t="inlineStr"/>
+    </row>
+    <row r="227">
+      <c r="A227" t="n">
+        <v>127683166</v>
+      </c>
+      <c r="B227" t="n">
+        <v>97325</v>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E227" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I227" t="inlineStr"/>
+      <c r="P227" t="inlineStr">
+        <is>
+          <t>Pellkärret, Dlr</t>
+        </is>
+      </c>
+      <c r="Q227" t="n">
+        <v>563939</v>
+      </c>
+      <c r="R227" t="n">
+        <v>6704940</v>
+      </c>
+      <c r="S227" t="n">
+        <v>10</v>
+      </c>
+      <c r="T227" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U227" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V227" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W227" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y227" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AA227" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AD227" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE227" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG227" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT227" t="inlineStr"/>
+      <c r="AW227" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX227" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY227" t="inlineStr"/>
+    </row>
+    <row r="228">
+      <c r="A228" t="n">
+        <v>127683193</v>
+      </c>
+      <c r="B228" t="n">
+        <v>92654</v>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E228" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I228" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J228" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P228" t="inlineStr">
+        <is>
+          <t>Pellkärret, Dlr</t>
+        </is>
+      </c>
+      <c r="Q228" t="n">
+        <v>563883</v>
+      </c>
+      <c r="R228" t="n">
+        <v>6704908</v>
+      </c>
+      <c r="S228" t="n">
+        <v>10</v>
+      </c>
+      <c r="T228" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U228" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V228" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W228" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y228" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AA228" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AD228" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE228" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG228" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT228" t="inlineStr"/>
+      <c r="AW228" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX228" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY228" t="inlineStr"/>
+    </row>
+    <row r="229">
+      <c r="A229" t="n">
+        <v>127683144</v>
+      </c>
+      <c r="B229" t="n">
+        <v>91330</v>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E229" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I229" t="inlineStr"/>
+      <c r="P229" t="inlineStr">
+        <is>
+          <t>Pellkärret, Dlr</t>
+        </is>
+      </c>
+      <c r="Q229" t="n">
+        <v>563970</v>
+      </c>
+      <c r="R229" t="n">
+        <v>6704986</v>
+      </c>
+      <c r="S229" t="n">
+        <v>10</v>
+      </c>
+      <c r="T229" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U229" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V229" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W229" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y229" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AA229" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AD229" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE229" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG229" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT229" t="inlineStr"/>
+      <c r="AW229" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX229" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY229" t="inlineStr"/>
+    </row>
+    <row r="230">
+      <c r="A230" t="n">
+        <v>127683154</v>
+      </c>
+      <c r="B230" t="n">
+        <v>57658</v>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E230" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I230" t="inlineStr"/>
+      <c r="M230" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P230" t="inlineStr">
+        <is>
+          <t>Pellkärret, Dlr</t>
+        </is>
+      </c>
+      <c r="Q230" t="n">
+        <v>564140</v>
+      </c>
+      <c r="R230" t="n">
+        <v>6705076</v>
+      </c>
+      <c r="S230" t="n">
+        <v>10</v>
+      </c>
+      <c r="T230" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U230" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V230" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W230" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y230" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AA230" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AD230" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE230" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG230" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT230" t="inlineStr"/>
+      <c r="AW230" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX230" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY230" t="inlineStr"/>
+    </row>
+    <row r="231">
+      <c r="A231" t="n">
+        <v>127683147</v>
+      </c>
+      <c r="B231" t="n">
+        <v>57821</v>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E231" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I231" t="inlineStr"/>
+      <c r="M231" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="P231" t="inlineStr">
+        <is>
+          <t>Pellkärret, Dlr</t>
+        </is>
+      </c>
+      <c r="Q231" t="n">
+        <v>564237</v>
+      </c>
+      <c r="R231" t="n">
+        <v>6705225</v>
+      </c>
+      <c r="S231" t="n">
+        <v>10</v>
+      </c>
+      <c r="T231" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U231" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V231" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W231" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y231" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AA231" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AD231" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE231" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG231" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT231" t="inlineStr"/>
+      <c r="AW231" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX231" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY231" t="inlineStr"/>
+    </row>
+    <row r="232">
+      <c r="A232" t="n">
+        <v>127683203</v>
+      </c>
+      <c r="B232" t="n">
+        <v>91731</v>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E232" t="n">
+        <v>715</v>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>Finporing</t>
+        </is>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>Gloeoporus pannocinctus</t>
+        </is>
+      </c>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>(Romell) J.Erikss.</t>
+        </is>
+      </c>
+      <c r="I232" t="inlineStr"/>
+      <c r="P232" t="inlineStr">
+        <is>
+          <t>Pellkärret, Dlr</t>
+        </is>
+      </c>
+      <c r="Q232" t="n">
+        <v>563955</v>
+      </c>
+      <c r="R232" t="n">
+        <v>6704996</v>
+      </c>
+      <c r="S232" t="n">
+        <v>10</v>
+      </c>
+      <c r="T232" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U232" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V232" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W232" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y232" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AA232" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AD232" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE232" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG232" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT232" t="inlineStr"/>
+      <c r="AW232" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX232" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY232" t="inlineStr"/>
+    </row>
+    <row r="233">
+      <c r="A233" t="n">
+        <v>127683173</v>
+      </c>
+      <c r="B233" t="n">
+        <v>95304</v>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E233" t="n">
+        <v>2387</v>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>Källpraktmossa</t>
+        </is>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>Pseudobryum cinclidioides</t>
+        </is>
+      </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>(Huebener) T.J.Kop.</t>
+        </is>
+      </c>
+      <c r="I233" t="inlineStr"/>
+      <c r="P233" t="inlineStr">
+        <is>
+          <t>Pellkärret, Dlr</t>
+        </is>
+      </c>
+      <c r="Q233" t="n">
+        <v>563865</v>
+      </c>
+      <c r="R233" t="n">
+        <v>6704888</v>
+      </c>
+      <c r="S233" t="n">
+        <v>10</v>
+      </c>
+      <c r="T233" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U233" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V233" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W233" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y233" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AA233" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AC233" t="inlineStr">
+        <is>
+          <t>I källdråg utan planerad hänsyn</t>
+        </is>
+      </c>
+      <c r="AD233" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE233" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG233" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT233" t="inlineStr"/>
+      <c r="AW233" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX233" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY233" t="inlineStr"/>
+    </row>
+    <row r="234">
+      <c r="A234" t="n">
+        <v>127683159</v>
+      </c>
+      <c r="B234" t="n">
+        <v>92232</v>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E234" t="n">
+        <v>4740</v>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>Sotriska</t>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>Lactarius lignyotus</t>
+        </is>
+      </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I234" t="inlineStr"/>
+      <c r="P234" t="inlineStr">
+        <is>
+          <t>Pellkärret, Dlr</t>
+        </is>
+      </c>
+      <c r="Q234" t="n">
+        <v>564226</v>
+      </c>
+      <c r="R234" t="n">
+        <v>6705244</v>
+      </c>
+      <c r="S234" t="n">
+        <v>10</v>
+      </c>
+      <c r="T234" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U234" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V234" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W234" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y234" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AA234" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AD234" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE234" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG234" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT234" t="inlineStr"/>
+      <c r="AW234" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX234" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY234" t="inlineStr"/>
+    </row>
+    <row r="235">
+      <c r="A235" t="n">
+        <v>127683165</v>
+      </c>
+      <c r="B235" t="n">
+        <v>91952</v>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E235" t="n">
+        <v>483</v>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>Rostskinn</t>
+        </is>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>Crustoderma dryinum</t>
+        </is>
+      </c>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
+        </is>
+      </c>
+      <c r="I235" t="inlineStr"/>
+      <c r="P235" t="inlineStr">
+        <is>
+          <t>Pellkärret, Dlr</t>
+        </is>
+      </c>
+      <c r="Q235" t="n">
+        <v>564089</v>
+      </c>
+      <c r="R235" t="n">
+        <v>6705072</v>
+      </c>
+      <c r="S235" t="n">
+        <v>10</v>
+      </c>
+      <c r="T235" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U235" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V235" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W235" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y235" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AA235" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AD235" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE235" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG235" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT235" t="inlineStr"/>
+      <c r="AW235" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX235" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY235" t="inlineStr"/>
+    </row>
+    <row r="236">
+      <c r="A236" t="n">
+        <v>127683146</v>
+      </c>
+      <c r="B236" t="n">
+        <v>4773</v>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E236" t="n">
+        <v>100299</v>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>Thomsons trägnagare</t>
+        </is>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>Cacotemnus thomsoni</t>
+        </is>
+      </c>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I236" t="inlineStr"/>
+      <c r="M236" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P236" t="inlineStr">
+        <is>
+          <t>Pellkärret, Dlr</t>
+        </is>
+      </c>
+      <c r="Q236" t="n">
+        <v>564057</v>
+      </c>
+      <c r="R236" t="n">
+        <v>6705124</v>
+      </c>
+      <c r="S236" t="n">
+        <v>10</v>
+      </c>
+      <c r="T236" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U236" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V236" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W236" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y236" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AA236" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AD236" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE236" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG236" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT236" t="inlineStr"/>
+      <c r="AW236" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX236" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY236" t="inlineStr"/>
+    </row>
+    <row r="237">
+      <c r="A237" t="n">
+        <v>127683188</v>
+      </c>
+      <c r="B237" t="n">
+        <v>98448</v>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E237" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I237" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J237" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K237" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="P237" t="inlineStr">
+        <is>
+          <t>Pellkärret, Dlr</t>
+        </is>
+      </c>
+      <c r="Q237" t="n">
+        <v>563940</v>
+      </c>
+      <c r="R237" t="n">
+        <v>6704945</v>
+      </c>
+      <c r="S237" t="n">
+        <v>10</v>
+      </c>
+      <c r="T237" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U237" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V237" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W237" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y237" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AA237" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AD237" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE237" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG237" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT237" t="inlineStr"/>
+      <c r="AW237" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX237" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY237" t="inlineStr"/>
+    </row>
+    <row r="238">
+      <c r="A238" t="n">
+        <v>127683152</v>
+      </c>
+      <c r="B238" t="n">
+        <v>92265</v>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E238" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I238" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J238" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P238" t="inlineStr">
+        <is>
+          <t>Pellkärret, Dlr</t>
+        </is>
+      </c>
+      <c r="Q238" t="n">
+        <v>563895</v>
+      </c>
+      <c r="R238" t="n">
+        <v>6704903</v>
+      </c>
+      <c r="S238" t="n">
+        <v>10</v>
+      </c>
+      <c r="T238" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U238" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V238" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W238" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y238" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AA238" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AD238" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE238" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG238" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT238" t="inlineStr"/>
+      <c r="AW238" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX238" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY238" t="inlineStr"/>
+    </row>
+    <row r="239">
+      <c r="A239" t="n">
+        <v>127683163</v>
+      </c>
+      <c r="B239" t="n">
+        <v>91102</v>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E239" t="n">
+        <v>3215</v>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>Rödgul trumpetsvamp</t>
+        </is>
+      </c>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>Craterellus lutescens</t>
+        </is>
+      </c>
+      <c r="H239" t="inlineStr">
+        <is>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I239" t="inlineStr"/>
+      <c r="P239" t="inlineStr">
+        <is>
+          <t>Pellkärret, Dlr</t>
+        </is>
+      </c>
+      <c r="Q239" t="n">
+        <v>564121</v>
+      </c>
+      <c r="R239" t="n">
+        <v>6705165</v>
+      </c>
+      <c r="S239" t="n">
+        <v>10</v>
+      </c>
+      <c r="T239" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U239" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V239" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W239" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y239" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AA239" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AC239" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
+      <c r="AD239" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE239" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG239" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT239" t="inlineStr"/>
+      <c r="AW239" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX239" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY239" t="inlineStr"/>
+    </row>
+    <row r="240">
+      <c r="A240" t="n">
+        <v>127683196</v>
+      </c>
+      <c r="B240" t="n">
+        <v>92654</v>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E240" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H240" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I240" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J240" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P240" t="inlineStr">
+        <is>
+          <t>Pellkärret, Dlr</t>
+        </is>
+      </c>
+      <c r="Q240" t="n">
+        <v>564163</v>
+      </c>
+      <c r="R240" t="n">
+        <v>6705180</v>
+      </c>
+      <c r="S240" t="n">
+        <v>10</v>
+      </c>
+      <c r="T240" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U240" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V240" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W240" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y240" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AA240" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AD240" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE240" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG240" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT240" t="inlineStr"/>
+      <c r="AW240" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX240" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY240" t="inlineStr"/>
+    </row>
+    <row r="241">
+      <c r="A241" t="n">
+        <v>127683138</v>
+      </c>
+      <c r="B241" t="n">
+        <v>91688</v>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E241" t="n">
+        <v>2062</v>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>Ulltickeporing</t>
+        </is>
+      </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>Skeletocutis brevispora</t>
+        </is>
+      </c>
+      <c r="H241" t="inlineStr">
+        <is>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I241" t="inlineStr"/>
+      <c r="P241" t="inlineStr">
+        <is>
+          <t>Pellkärret, Dlr</t>
+        </is>
+      </c>
+      <c r="Q241" t="n">
+        <v>564145</v>
+      </c>
+      <c r="R241" t="n">
+        <v>6705081</v>
+      </c>
+      <c r="S241" t="n">
+        <v>10</v>
+      </c>
+      <c r="T241" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U241" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V241" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W241" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y241" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AA241" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AD241" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE241" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG241" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT241" t="inlineStr"/>
+      <c r="AW241" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX241" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY241" t="inlineStr"/>
+    </row>
+    <row r="242">
+      <c r="A242" t="n">
+        <v>127683185</v>
+      </c>
+      <c r="B242" t="n">
+        <v>98448</v>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E242" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H242" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I242" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J242" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K242" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="P242" t="inlineStr">
+        <is>
+          <t>Pellkärret, Dlr</t>
+        </is>
+      </c>
+      <c r="Q242" t="n">
+        <v>564009</v>
+      </c>
+      <c r="R242" t="n">
+        <v>6705051</v>
+      </c>
+      <c r="S242" t="n">
+        <v>10</v>
+      </c>
+      <c r="T242" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U242" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V242" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W242" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y242" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AA242" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AD242" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE242" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG242" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT242" t="inlineStr"/>
+      <c r="AW242" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX242" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY242" t="inlineStr"/>
+    </row>
+    <row r="243">
+      <c r="A243" t="n">
+        <v>127683182</v>
+      </c>
+      <c r="B243" t="n">
+        <v>75080</v>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E243" t="n">
+        <v>6426</v>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
+      </c>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H243" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I243" t="inlineStr"/>
+      <c r="P243" t="inlineStr">
+        <is>
+          <t>Pellkärret, Dlr</t>
+        </is>
+      </c>
+      <c r="Q243" t="n">
+        <v>563929</v>
+      </c>
+      <c r="R243" t="n">
+        <v>6704888</v>
+      </c>
+      <c r="S243" t="n">
+        <v>10</v>
+      </c>
+      <c r="T243" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U243" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V243" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W243" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y243" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AA243" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AD243" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE243" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG243" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT243" t="inlineStr"/>
+      <c r="AW243" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX243" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY243" t="inlineStr"/>
+    </row>
+    <row r="244">
+      <c r="A244" t="n">
+        <v>127683149</v>
+      </c>
+      <c r="B244" t="n">
+        <v>57821</v>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E244" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H244" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I244" t="inlineStr"/>
+      <c r="M244" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="P244" t="inlineStr">
+        <is>
+          <t>Pellkärret, Dlr</t>
+        </is>
+      </c>
+      <c r="Q244" t="n">
+        <v>564082</v>
+      </c>
+      <c r="R244" t="n">
+        <v>6705145</v>
+      </c>
+      <c r="S244" t="n">
+        <v>10</v>
+      </c>
+      <c r="T244" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U244" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V244" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W244" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y244" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AA244" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AD244" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE244" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG244" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT244" t="inlineStr"/>
+      <c r="AW244" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX244" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY244" t="inlineStr"/>
+    </row>
+    <row r="245">
+      <c r="A245" t="n">
+        <v>127683162</v>
+      </c>
+      <c r="B245" t="n">
+        <v>95692</v>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E245" t="n">
+        <v>2813</v>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>Skogshakmossa</t>
+        </is>
+      </c>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>Rhytidiadelphus subpinnatus</t>
+        </is>
+      </c>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t>(Lindb.) T.J.Kop.</t>
+        </is>
+      </c>
+      <c r="I245" t="inlineStr"/>
+      <c r="P245" t="inlineStr">
+        <is>
+          <t>Pellkärret, Dlr</t>
+        </is>
+      </c>
+      <c r="Q245" t="n">
+        <v>563934</v>
+      </c>
+      <c r="R245" t="n">
+        <v>6704860</v>
+      </c>
+      <c r="S245" t="n">
+        <v>10</v>
+      </c>
+      <c r="T245" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U245" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V245" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W245" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y245" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AA245" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AD245" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE245" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG245" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT245" t="inlineStr"/>
+      <c r="AW245" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX245" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY245" t="inlineStr"/>
+    </row>
+    <row r="246">
+      <c r="A246" t="n">
+        <v>127683195</v>
+      </c>
+      <c r="B246" t="n">
+        <v>92654</v>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E246" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H246" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I246" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J246" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P246" t="inlineStr">
+        <is>
+          <t>Pellkärret, Dlr</t>
+        </is>
+      </c>
+      <c r="Q246" t="n">
+        <v>563882</v>
+      </c>
+      <c r="R246" t="n">
+        <v>6704905</v>
+      </c>
+      <c r="S246" t="n">
+        <v>10</v>
+      </c>
+      <c r="T246" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U246" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V246" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W246" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y246" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AA246" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AD246" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE246" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG246" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT246" t="inlineStr"/>
+      <c r="AW246" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX246" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY246" t="inlineStr"/>
+    </row>
+    <row r="247">
+      <c r="A247" t="n">
+        <v>127683135</v>
+      </c>
+      <c r="B247" t="n">
+        <v>91295</v>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E247" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H247" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I247" t="inlineStr"/>
+      <c r="P247" t="inlineStr">
+        <is>
+          <t>Pellkärret, Dlr</t>
+        </is>
+      </c>
+      <c r="Q247" t="n">
+        <v>564226</v>
+      </c>
+      <c r="R247" t="n">
+        <v>6705244</v>
+      </c>
+      <c r="S247" t="n">
+        <v>10</v>
+      </c>
+      <c r="T247" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U247" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V247" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W247" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y247" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AA247" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AD247" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE247" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG247" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT247" t="inlineStr"/>
+      <c r="AW247" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX247" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY247" t="inlineStr"/>
+    </row>
+    <row r="248">
+      <c r="A248" t="n">
+        <v>127683184</v>
+      </c>
+      <c r="B248" t="n">
+        <v>98448</v>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E248" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H248" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I248" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J248" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K248" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="P248" t="inlineStr">
+        <is>
+          <t>Pellkärret, Dlr</t>
+        </is>
+      </c>
+      <c r="Q248" t="n">
+        <v>563880</v>
+      </c>
+      <c r="R248" t="n">
+        <v>6704891</v>
+      </c>
+      <c r="S248" t="n">
+        <v>10</v>
+      </c>
+      <c r="T248" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U248" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V248" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W248" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y248" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AA248" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AC248" t="inlineStr">
+        <is>
+          <t>3 blomstjälkar</t>
+        </is>
+      </c>
+      <c r="AD248" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE248" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG248" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT248" t="inlineStr"/>
+      <c r="AW248" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX248" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY248" t="inlineStr"/>
+    </row>
+    <row r="249">
+      <c r="A249" t="n">
+        <v>127683137</v>
+      </c>
+      <c r="B249" t="n">
+        <v>91688</v>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E249" t="n">
+        <v>2062</v>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>Ulltickeporing</t>
+        </is>
+      </c>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>Skeletocutis brevispora</t>
+        </is>
+      </c>
+      <c r="H249" t="inlineStr">
+        <is>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I249" t="inlineStr"/>
+      <c r="P249" t="inlineStr">
+        <is>
+          <t>Pellkärret, Dlr</t>
+        </is>
+      </c>
+      <c r="Q249" t="n">
+        <v>564130</v>
+      </c>
+      <c r="R249" t="n">
+        <v>6705091</v>
+      </c>
+      <c r="S249" t="n">
+        <v>10</v>
+      </c>
+      <c r="T249" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U249" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V249" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W249" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y249" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AA249" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AD249" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE249" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG249" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT249" t="inlineStr"/>
+      <c r="AW249" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX249" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY249" t="inlineStr"/>
+    </row>
+    <row r="250">
+      <c r="A250" t="n">
+        <v>127683151</v>
+      </c>
+      <c r="B250" t="n">
+        <v>92265</v>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E250" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H250" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I250" t="inlineStr"/>
+      <c r="P250" t="inlineStr">
+        <is>
+          <t>Pellkärret, Dlr</t>
+        </is>
+      </c>
+      <c r="Q250" t="n">
+        <v>563873</v>
+      </c>
+      <c r="R250" t="n">
+        <v>6704890</v>
+      </c>
+      <c r="S250" t="n">
+        <v>10</v>
+      </c>
+      <c r="T250" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U250" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V250" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W250" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y250" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AA250" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AC250" t="inlineStr">
+        <is>
+          <t>Intill källdråg utan planerad hänsyn</t>
+        </is>
+      </c>
+      <c r="AD250" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE250" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG250" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT250" t="inlineStr"/>
+      <c r="AW250" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX250" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY250" t="inlineStr"/>
+    </row>
+    <row r="251">
+      <c r="A251" t="n">
+        <v>127683141</v>
+      </c>
+      <c r="B251" t="n">
+        <v>91330</v>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E251" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H251" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I251" t="inlineStr"/>
+      <c r="P251" t="inlineStr">
+        <is>
+          <t>Pellkärret, Dlr</t>
+        </is>
+      </c>
+      <c r="Q251" t="n">
+        <v>564130</v>
+      </c>
+      <c r="R251" t="n">
+        <v>6705091</v>
+      </c>
+      <c r="S251" t="n">
+        <v>10</v>
+      </c>
+      <c r="T251" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U251" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V251" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W251" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y251" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AA251" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AD251" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE251" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG251" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT251" t="inlineStr"/>
+      <c r="AW251" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX251" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY251" t="inlineStr"/>
+    </row>
+    <row r="252">
+      <c r="A252" t="n">
+        <v>127683199</v>
+      </c>
+      <c r="B252" t="n">
+        <v>95299</v>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E252" t="n">
+        <v>2383</v>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>Bågpraktmossa</t>
+        </is>
+      </c>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>Plagiomnium medium</t>
+        </is>
+      </c>
+      <c r="H252" t="inlineStr">
+        <is>
+          <t>(Bruch &amp; Schimp.) T.J.Kop.</t>
+        </is>
+      </c>
+      <c r="I252" t="inlineStr"/>
+      <c r="P252" t="inlineStr">
+        <is>
+          <t>Pellkärret, Dlr</t>
+        </is>
+      </c>
+      <c r="Q252" t="n">
+        <v>564058</v>
+      </c>
+      <c r="R252" t="n">
+        <v>6705124</v>
+      </c>
+      <c r="S252" t="n">
+        <v>10</v>
+      </c>
+      <c r="T252" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U252" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V252" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W252" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y252" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AA252" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AC252" t="inlineStr">
+        <is>
+          <t>i översinlningsområde utanför hänsyn</t>
+        </is>
+      </c>
+      <c r="AD252" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE252" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG252" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT252" t="inlineStr"/>
+      <c r="AW252" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX252" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY252" t="inlineStr"/>
+    </row>
+    <row r="253">
+      <c r="A253" t="n">
+        <v>127683139</v>
+      </c>
+      <c r="B253" t="n">
+        <v>91688</v>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E253" t="n">
+        <v>2062</v>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>Ulltickeporing</t>
+        </is>
+      </c>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>Skeletocutis brevispora</t>
+        </is>
+      </c>
+      <c r="H253" t="inlineStr">
+        <is>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I253" t="inlineStr"/>
+      <c r="P253" t="inlineStr">
+        <is>
+          <t>Pellkärret, Dlr</t>
+        </is>
+      </c>
+      <c r="Q253" t="n">
+        <v>563999</v>
+      </c>
+      <c r="R253" t="n">
+        <v>6705007</v>
+      </c>
+      <c r="S253" t="n">
+        <v>10</v>
+      </c>
+      <c r="T253" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U253" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V253" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W253" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y253" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AA253" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AD253" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE253" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG253" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT253" t="inlineStr"/>
+      <c r="AW253" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX253" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY253" t="inlineStr"/>
+    </row>
+    <row r="254">
+      <c r="A254" t="n">
+        <v>127683200</v>
+      </c>
+      <c r="B254" t="n">
+        <v>100630</v>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E254" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H254" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I254" t="inlineStr"/>
+      <c r="P254" t="inlineStr">
+        <is>
+          <t>Pellkärret, Dlr</t>
+        </is>
+      </c>
+      <c r="Q254" t="n">
+        <v>563890</v>
+      </c>
+      <c r="R254" t="n">
+        <v>6704897</v>
+      </c>
+      <c r="S254" t="n">
+        <v>10</v>
+      </c>
+      <c r="T254" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U254" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V254" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W254" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y254" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AA254" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AD254" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE254" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG254" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT254" t="inlineStr"/>
+      <c r="AW254" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX254" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY254" t="inlineStr"/>
+    </row>
+    <row r="255">
+      <c r="A255" t="n">
+        <v>127683145</v>
+      </c>
+      <c r="B255" t="n">
+        <v>91330</v>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E255" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H255" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I255" t="inlineStr"/>
+      <c r="P255" t="inlineStr">
+        <is>
+          <t>Pellkärret, Dlr</t>
+        </is>
+      </c>
+      <c r="Q255" t="n">
+        <v>563995</v>
+      </c>
+      <c r="R255" t="n">
+        <v>6705021</v>
+      </c>
+      <c r="S255" t="n">
+        <v>10</v>
+      </c>
+      <c r="T255" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U255" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V255" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W255" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y255" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AA255" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AD255" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE255" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG255" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT255" t="inlineStr"/>
+      <c r="AW255" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX255" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY255" t="inlineStr"/>
+    </row>
+    <row r="256">
+      <c r="A256" t="n">
+        <v>127683155</v>
+      </c>
+      <c r="B256" t="n">
+        <v>57658</v>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E256" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H256" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I256" t="inlineStr"/>
+      <c r="M256" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="P256" t="inlineStr">
+        <is>
+          <t>Pellkärret, Dlr</t>
+        </is>
+      </c>
+      <c r="Q256" t="n">
+        <v>564144</v>
+      </c>
+      <c r="R256" t="n">
+        <v>6705112</v>
+      </c>
+      <c r="S256" t="n">
+        <v>10</v>
+      </c>
+      <c r="T256" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U256" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V256" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W256" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y256" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AA256" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AD256" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE256" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG256" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT256" t="inlineStr"/>
+      <c r="AW256" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX256" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY256" t="inlineStr"/>
+    </row>
+    <row r="257">
+      <c r="A257" t="n">
+        <v>127683201</v>
+      </c>
+      <c r="B257" t="n">
+        <v>100630</v>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E257" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H257" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I257" t="inlineStr"/>
+      <c r="P257" t="inlineStr">
+        <is>
+          <t>Pellkärret, Dlr</t>
+        </is>
+      </c>
+      <c r="Q257" t="n">
+        <v>563881</v>
+      </c>
+      <c r="R257" t="n">
+        <v>6704905</v>
+      </c>
+      <c r="S257" t="n">
+        <v>10</v>
+      </c>
+      <c r="T257" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U257" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V257" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W257" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y257" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AA257" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AD257" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE257" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG257" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT257" t="inlineStr"/>
+      <c r="AW257" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX257" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY257" t="inlineStr"/>
+    </row>
+    <row r="258">
+      <c r="A258" t="n">
+        <v>127683142</v>
+      </c>
+      <c r="B258" t="n">
+        <v>91330</v>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E258" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H258" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I258" t="inlineStr"/>
+      <c r="P258" t="inlineStr">
+        <is>
+          <t>Pellkärret, Dlr</t>
+        </is>
+      </c>
+      <c r="Q258" t="n">
+        <v>564128</v>
+      </c>
+      <c r="R258" t="n">
+        <v>6705064</v>
+      </c>
+      <c r="S258" t="n">
+        <v>10</v>
+      </c>
+      <c r="T258" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U258" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V258" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W258" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y258" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AA258" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AD258" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE258" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG258" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT258" t="inlineStr"/>
+      <c r="AW258" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX258" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY258" t="inlineStr"/>
+    </row>
+    <row r="259">
+      <c r="A259" t="n">
+        <v>127683158</v>
+      </c>
+      <c r="B259" t="n">
+        <v>57658</v>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E259" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H259" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I259" t="inlineStr"/>
+      <c r="M259" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P259" t="inlineStr">
+        <is>
+          <t>Pellkärret, Dlr</t>
+        </is>
+      </c>
+      <c r="Q259" t="n">
+        <v>563970</v>
+      </c>
+      <c r="R259" t="n">
+        <v>6704954</v>
+      </c>
+      <c r="S259" t="n">
+        <v>10</v>
+      </c>
+      <c r="T259" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U259" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V259" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W259" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y259" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AA259" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AD259" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE259" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG259" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT259" t="inlineStr"/>
+      <c r="AW259" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX259" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY259" t="inlineStr"/>
+    </row>
+    <row r="260">
+      <c r="A260" t="n">
+        <v>127683157</v>
+      </c>
+      <c r="B260" t="n">
+        <v>57658</v>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E260" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H260" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I260" t="inlineStr"/>
+      <c r="M260" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P260" t="inlineStr">
+        <is>
+          <t>Pellkärret, Dlr</t>
+        </is>
+      </c>
+      <c r="Q260" t="n">
+        <v>564052</v>
+      </c>
+      <c r="R260" t="n">
+        <v>6705031</v>
+      </c>
+      <c r="S260" t="n">
+        <v>10</v>
+      </c>
+      <c r="T260" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U260" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V260" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W260" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y260" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AA260" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AD260" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE260" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG260" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT260" t="inlineStr"/>
+      <c r="AW260" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX260" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY260" t="inlineStr"/>
+    </row>
+    <row r="261">
+      <c r="A261" t="n">
+        <v>127683164</v>
+      </c>
+      <c r="B261" t="n">
+        <v>91102</v>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E261" t="n">
+        <v>3215</v>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>Rödgul trumpetsvamp</t>
+        </is>
+      </c>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>Craterellus lutescens</t>
+        </is>
+      </c>
+      <c r="H261" t="inlineStr">
+        <is>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I261" t="inlineStr"/>
+      <c r="P261" t="inlineStr">
+        <is>
+          <t>Pellkärret, Dlr</t>
+        </is>
+      </c>
+      <c r="Q261" t="n">
+        <v>564133</v>
+      </c>
+      <c r="R261" t="n">
+        <v>6705173</v>
+      </c>
+      <c r="S261" t="n">
+        <v>10</v>
+      </c>
+      <c r="T261" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U261" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V261" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W261" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y261" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AA261" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AD261" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE261" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG261" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT261" t="inlineStr"/>
+      <c r="AW261" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX261" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY261" t="inlineStr"/>
+    </row>
+    <row r="262">
+      <c r="A262" t="n">
+        <v>127683133</v>
+      </c>
+      <c r="B262" t="n">
+        <v>91295</v>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E262" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H262" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I262" t="inlineStr"/>
+      <c r="P262" t="inlineStr">
+        <is>
+          <t>Pellkärret, Dlr</t>
+        </is>
+      </c>
+      <c r="Q262" t="n">
+        <v>564052</v>
+      </c>
+      <c r="R262" t="n">
+        <v>6705031</v>
+      </c>
+      <c r="S262" t="n">
+        <v>10</v>
+      </c>
+      <c r="T262" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U262" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V262" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W262" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y262" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AA262" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AD262" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE262" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG262" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT262" t="inlineStr"/>
+      <c r="AW262" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX262" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY262" t="inlineStr"/>
+    </row>
+    <row r="263">
+      <c r="A263" t="n">
+        <v>127683187</v>
+      </c>
+      <c r="B263" t="n">
+        <v>98448</v>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E263" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H263" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I263" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J263" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K263" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="P263" t="inlineStr">
+        <is>
+          <t>Pellkärret, Dlr</t>
+        </is>
+      </c>
+      <c r="Q263" t="n">
+        <v>564215</v>
+      </c>
+      <c r="R263" t="n">
+        <v>6705203</v>
+      </c>
+      <c r="S263" t="n">
+        <v>10</v>
+      </c>
+      <c r="T263" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U263" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V263" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W263" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y263" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AA263" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AD263" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE263" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG263" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT263" t="inlineStr"/>
+      <c r="AW263" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX263" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY263" t="inlineStr"/>
+    </row>
+    <row r="264">
+      <c r="A264" t="n">
+        <v>127683172</v>
+      </c>
+      <c r="B264" t="n">
+        <v>95304</v>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E264" t="n">
+        <v>2387</v>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>Källpraktmossa</t>
+        </is>
+      </c>
+      <c r="G264" t="inlineStr">
+        <is>
+          <t>Pseudobryum cinclidioides</t>
+        </is>
+      </c>
+      <c r="H264" t="inlineStr">
+        <is>
+          <t>(Huebener) T.J.Kop.</t>
+        </is>
+      </c>
+      <c r="I264" t="inlineStr"/>
+      <c r="P264" t="inlineStr">
+        <is>
+          <t>Pellkärret, Dlr</t>
+        </is>
+      </c>
+      <c r="Q264" t="n">
+        <v>563914</v>
+      </c>
+      <c r="R264" t="n">
+        <v>6704945</v>
+      </c>
+      <c r="S264" t="n">
+        <v>10</v>
+      </c>
+      <c r="T264" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U264" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V264" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W264" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y264" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AA264" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AC264" t="inlineStr">
+        <is>
+          <t>I källdråg utan planerad hänsyn</t>
+        </is>
+      </c>
+      <c r="AD264" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE264" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG264" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT264" t="inlineStr"/>
+      <c r="AW264" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX264" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY264" t="inlineStr"/>
+    </row>
+    <row r="265">
+      <c r="A265" t="n">
+        <v>127683130</v>
+      </c>
+      <c r="B265" t="n">
+        <v>91542</v>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E265" t="n">
+        <v>1106</v>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>Vågticka</t>
+        </is>
+      </c>
+      <c r="G265" t="inlineStr">
+        <is>
+          <t>Osteina undosa</t>
+        </is>
+      </c>
+      <c r="H265" t="inlineStr">
+        <is>
+          <t>(Peck) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I265" t="inlineStr"/>
+      <c r="P265" t="inlineStr">
+        <is>
+          <t>Pellkärret, Dlr</t>
+        </is>
+      </c>
+      <c r="Q265" t="n">
+        <v>564057</v>
+      </c>
+      <c r="R265" t="n">
+        <v>6705032</v>
+      </c>
+      <c r="S265" t="n">
+        <v>10</v>
+      </c>
+      <c r="T265" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U265" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V265" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W265" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y265" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AA265" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AD265" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE265" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG265" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT265" t="inlineStr"/>
+      <c r="AW265" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX265" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY265" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 58548-2022 artfynd.xlsx
+++ b/artfynd/A 58548-2022 artfynd.xlsx
@@ -25139,10 +25139,10 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>127683156</v>
+        <v>127683181</v>
       </c>
       <c r="B223" t="n">
-        <v>57658</v>
+        <v>91696</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -25150,39 +25150,34 @@
         </is>
       </c>
       <c r="E223" t="n">
-        <v>100049</v>
+        <v>2064</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kilporing</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Skeletocutis kuehneri</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>A.David</t>
         </is>
       </c>
       <c r="I223" t="inlineStr"/>
-      <c r="M223" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P223" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>564124</v>
+        <v>564128</v>
       </c>
       <c r="R223" t="n">
-        <v>6705171</v>
+        <v>6705055</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -25215,6 +25210,11 @@
       <c r="AA223" t="inlineStr">
         <is>
           <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AC223" t="inlineStr">
+        <is>
+          <t>Kommer att mikroskoperas</t>
         </is>
       </c>
       <c r="AD223" t="b">
@@ -25241,45 +25241,59 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>127683140</v>
+        <v>127683183</v>
       </c>
       <c r="B224" t="n">
-        <v>91330</v>
+        <v>98448</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E224" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I224" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I224" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J224" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P224" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>564253</v>
+        <v>564023</v>
       </c>
       <c r="R224" t="n">
-        <v>6705225</v>
+        <v>6705072</v>
       </c>
       <c r="S224" t="n">
         <v>10</v>
@@ -25312,6 +25326,11 @@
       <c r="AA224" t="inlineStr">
         <is>
           <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AC224" t="inlineStr">
+        <is>
+          <t>2 blomstjälkar</t>
         </is>
       </c>
       <c r="AD224" t="b">
@@ -25338,10 +25357,10 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>127683181</v>
+        <v>127683140</v>
       </c>
       <c r="B225" t="n">
-        <v>91696</v>
+        <v>91330</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -25349,21 +25368,21 @@
         </is>
       </c>
       <c r="E225" t="n">
-        <v>2064</v>
+        <v>1202</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Kilporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Skeletocutis kuehneri</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>A.David</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I225" t="inlineStr"/>
@@ -25373,10 +25392,10 @@
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>564128</v>
+        <v>564253</v>
       </c>
       <c r="R225" t="n">
-        <v>6705055</v>
+        <v>6705225</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -25409,11 +25428,6 @@
       <c r="AA225" t="inlineStr">
         <is>
           <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="AC225" t="inlineStr">
-        <is>
-          <t>Kommer att mikroskoperas</t>
         </is>
       </c>
       <c r="AD225" t="b">
@@ -25440,59 +25454,45 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>127683183</v>
+        <v>127683144</v>
       </c>
       <c r="B226" t="n">
-        <v>98448</v>
+        <v>91330</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E226" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I226" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J226" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K226" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I226" t="inlineStr"/>
       <c r="P226" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>564023</v>
+        <v>563970</v>
       </c>
       <c r="R226" t="n">
-        <v>6705072</v>
+        <v>6704986</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -25525,11 +25525,6 @@
       <c r="AA226" t="inlineStr">
         <is>
           <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="AC226" t="inlineStr">
-        <is>
-          <t>2 blomstjälkar</t>
         </is>
       </c>
       <c r="AD226" t="b">
@@ -25556,45 +25551,50 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>127683166</v>
+        <v>127683156</v>
       </c>
       <c r="B227" t="n">
-        <v>97325</v>
+        <v>57658</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E227" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I227" t="inlineStr"/>
+      <c r="M227" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P227" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>563939</v>
+        <v>564124</v>
       </c>
       <c r="R227" t="n">
-        <v>6704940</v>
+        <v>6705171</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -25653,42 +25653,38 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>127683193</v>
+        <v>127683154</v>
       </c>
       <c r="B228" t="n">
-        <v>92654</v>
+        <v>57658</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E228" t="n">
-        <v>5964</v>
+        <v>100049</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I228" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J228" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I228" t="inlineStr"/>
+      <c r="M228" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P228" t="inlineStr">
@@ -25697,10 +25693,10 @@
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>563883</v>
+        <v>564140</v>
       </c>
       <c r="R228" t="n">
-        <v>6704908</v>
+        <v>6705076</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -25759,45 +25755,54 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>127683144</v>
+        <v>127683193</v>
       </c>
       <c r="B229" t="n">
-        <v>91330</v>
+        <v>92654</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E229" t="n">
-        <v>1202</v>
+        <v>5964</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I229" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J229" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P229" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>563970</v>
+        <v>563883</v>
       </c>
       <c r="R229" t="n">
-        <v>6704986</v>
+        <v>6704908</v>
       </c>
       <c r="S229" t="n">
         <v>10</v>
@@ -25856,50 +25861,45 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>127683154</v>
+        <v>127683166</v>
       </c>
       <c r="B230" t="n">
-        <v>57658</v>
+        <v>97325</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E230" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I230" t="inlineStr"/>
-      <c r="M230" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P230" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>564140</v>
+        <v>563939</v>
       </c>
       <c r="R230" t="n">
-        <v>6705076</v>
+        <v>6704940</v>
       </c>
       <c r="S230" t="n">
         <v>10</v>
@@ -25958,50 +25958,45 @@
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>127683147</v>
+        <v>127683173</v>
       </c>
       <c r="B231" t="n">
-        <v>57821</v>
+        <v>95304</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E231" t="n">
-        <v>103021</v>
+        <v>2387</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I231" t="inlineStr"/>
-      <c r="M231" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P231" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>564237</v>
+        <v>563865</v>
       </c>
       <c r="R231" t="n">
-        <v>6705225</v>
+        <v>6704888</v>
       </c>
       <c r="S231" t="n">
         <v>10</v>
@@ -26034,6 +26029,11 @@
       <c r="AA231" t="inlineStr">
         <is>
           <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AC231" t="inlineStr">
+        <is>
+          <t>I källdråg utan planerad hänsyn</t>
         </is>
       </c>
       <c r="AD231" t="b">
@@ -26157,45 +26157,50 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>127683173</v>
+        <v>127683147</v>
       </c>
       <c r="B233" t="n">
-        <v>95304</v>
+        <v>57821</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E233" t="n">
-        <v>2387</v>
+        <v>103021</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I233" t="inlineStr"/>
+      <c r="M233" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P233" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>563865</v>
+        <v>564237</v>
       </c>
       <c r="R233" t="n">
-        <v>6704888</v>
+        <v>6705225</v>
       </c>
       <c r="S233" t="n">
         <v>10</v>
@@ -26228,11 +26233,6 @@
       <c r="AA233" t="inlineStr">
         <is>
           <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="AC233" t="inlineStr">
-        <is>
-          <t>I källdråg utan planerad hänsyn</t>
         </is>
       </c>
       <c r="AD233" t="b">
@@ -26555,47 +26555,42 @@
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>127683188</v>
+        <v>127683152</v>
       </c>
       <c r="B237" t="n">
-        <v>98448</v>
+        <v>92265</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E237" t="n">
-        <v>220787</v>
+        <v>4769</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I237" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J237" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K237" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P237" t="inlineStr">
@@ -26604,10 +26599,10 @@
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>563940</v>
+        <v>563895</v>
       </c>
       <c r="R237" t="n">
-        <v>6704945</v>
+        <v>6704903</v>
       </c>
       <c r="S237" t="n">
         <v>10</v>
@@ -26666,10 +26661,10 @@
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>127683152</v>
+        <v>127683163</v>
       </c>
       <c r="B238" t="n">
-        <v>92265</v>
+        <v>91102</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -26677,43 +26672,34 @@
         </is>
       </c>
       <c r="E238" t="n">
-        <v>4769</v>
+        <v>3215</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I238" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J238" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I238" t="inlineStr"/>
       <c r="P238" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q238" t="n">
-        <v>563895</v>
+        <v>564121</v>
       </c>
       <c r="R238" t="n">
-        <v>6704903</v>
+        <v>6705165</v>
       </c>
       <c r="S238" t="n">
         <v>10</v>
@@ -26746,6 +26732,11 @@
       <c r="AA238" t="inlineStr">
         <is>
           <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AC238" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD238" t="b">
@@ -26772,45 +26763,59 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>127683163</v>
+        <v>127683188</v>
       </c>
       <c r="B239" t="n">
-        <v>91102</v>
+        <v>98448</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E239" t="n">
-        <v>3215</v>
+        <v>220787</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I239" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I239" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J239" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K239" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P239" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>564121</v>
+        <v>563940</v>
       </c>
       <c r="R239" t="n">
-        <v>6705165</v>
+        <v>6704945</v>
       </c>
       <c r="S239" t="n">
         <v>10</v>
@@ -26843,11 +26848,6 @@
       <c r="AA239" t="inlineStr">
         <is>
           <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="AC239" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD239" t="b">
@@ -26980,10 +26980,10 @@
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>127683138</v>
+        <v>127683185</v>
       </c>
       <c r="B241" t="n">
-        <v>91688</v>
+        <v>98448</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -26991,34 +26991,48 @@
         </is>
       </c>
       <c r="E241" t="n">
-        <v>2062</v>
+        <v>220787</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I241" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I241" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J241" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K241" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P241" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q241" t="n">
-        <v>564145</v>
+        <v>564009</v>
       </c>
       <c r="R241" t="n">
-        <v>6705081</v>
+        <v>6705051</v>
       </c>
       <c r="S241" t="n">
         <v>10</v>
@@ -27077,10 +27091,10 @@
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>127683185</v>
+        <v>127683138</v>
       </c>
       <c r="B242" t="n">
-        <v>98448</v>
+        <v>91688</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -27088,48 +27102,34 @@
         </is>
       </c>
       <c r="E242" t="n">
-        <v>220787</v>
+        <v>2062</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I242" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J242" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K242" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I242" t="inlineStr"/>
       <c r="P242" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q242" t="n">
-        <v>564009</v>
+        <v>564145</v>
       </c>
       <c r="R242" t="n">
-        <v>6705051</v>
+        <v>6705081</v>
       </c>
       <c r="S242" t="n">
         <v>10</v>
@@ -27285,50 +27285,45 @@
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>127683149</v>
+        <v>127683162</v>
       </c>
       <c r="B244" t="n">
-        <v>57821</v>
+        <v>95692</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E244" t="n">
-        <v>103021</v>
+        <v>2813</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I244" t="inlineStr"/>
-      <c r="M244" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P244" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q244" t="n">
-        <v>564082</v>
+        <v>563934</v>
       </c>
       <c r="R244" t="n">
-        <v>6705145</v>
+        <v>6704860</v>
       </c>
       <c r="S244" t="n">
         <v>10</v>
@@ -27387,45 +27382,50 @@
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>127683162</v>
+        <v>127683149</v>
       </c>
       <c r="B245" t="n">
-        <v>95692</v>
+        <v>57821</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E245" t="n">
-        <v>2813</v>
+        <v>103021</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I245" t="inlineStr"/>
+      <c r="M245" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P245" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q245" t="n">
-        <v>563934</v>
+        <v>564082</v>
       </c>
       <c r="R245" t="n">
-        <v>6704860</v>
+        <v>6705145</v>
       </c>
       <c r="S245" t="n">
         <v>10</v>
@@ -28099,32 +28099,32 @@
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>127683199</v>
+        <v>127683139</v>
       </c>
       <c r="B252" t="n">
-        <v>95299</v>
+        <v>91688</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E252" t="n">
-        <v>2383</v>
+        <v>2062</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Bågpraktmossa</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>Plagiomnium medium</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>(Bruch &amp; Schimp.) T.J.Kop.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I252" t="inlineStr"/>
@@ -28134,10 +28134,10 @@
         </is>
       </c>
       <c r="Q252" t="n">
-        <v>564058</v>
+        <v>563999</v>
       </c>
       <c r="R252" t="n">
-        <v>6705124</v>
+        <v>6705007</v>
       </c>
       <c r="S252" t="n">
         <v>10</v>
@@ -28170,11 +28170,6 @@
       <c r="AA252" t="inlineStr">
         <is>
           <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="AC252" t="inlineStr">
-        <is>
-          <t>i översinlningsområde utanför hänsyn</t>
         </is>
       </c>
       <c r="AD252" t="b">
@@ -28201,32 +28196,32 @@
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>127683139</v>
+        <v>127683199</v>
       </c>
       <c r="B253" t="n">
-        <v>91688</v>
+        <v>95299</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E253" t="n">
-        <v>2062</v>
+        <v>2383</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Bågpraktmossa</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Plagiomnium medium</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Bruch &amp; Schimp.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I253" t="inlineStr"/>
@@ -28236,10 +28231,10 @@
         </is>
       </c>
       <c r="Q253" t="n">
-        <v>563999</v>
+        <v>564058</v>
       </c>
       <c r="R253" t="n">
-        <v>6705007</v>
+        <v>6705124</v>
       </c>
       <c r="S253" t="n">
         <v>10</v>
@@ -28272,6 +28267,11 @@
       <c r="AA253" t="inlineStr">
         <is>
           <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AC253" t="inlineStr">
+        <is>
+          <t>i översinlningsområde utanför hänsyn</t>
         </is>
       </c>
       <c r="AD253" t="b">
@@ -28492,10 +28492,10 @@
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>127683155</v>
+        <v>127683142</v>
       </c>
       <c r="B256" t="n">
-        <v>57658</v>
+        <v>91330</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -28503,39 +28503,34 @@
         </is>
       </c>
       <c r="E256" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I256" t="inlineStr"/>
-      <c r="M256" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P256" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q256" t="n">
-        <v>564144</v>
+        <v>564128</v>
       </c>
       <c r="R256" t="n">
-        <v>6705112</v>
+        <v>6705064</v>
       </c>
       <c r="S256" t="n">
         <v>10</v>
@@ -28594,45 +28589,50 @@
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>127683201</v>
+        <v>127683155</v>
       </c>
       <c r="B257" t="n">
-        <v>100630</v>
+        <v>57658</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E257" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I257" t="inlineStr"/>
+      <c r="M257" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P257" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q257" t="n">
-        <v>563881</v>
+        <v>564144</v>
       </c>
       <c r="R257" t="n">
-        <v>6704905</v>
+        <v>6705112</v>
       </c>
       <c r="S257" t="n">
         <v>10</v>
@@ -28691,32 +28691,32 @@
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>127683142</v>
+        <v>127683201</v>
       </c>
       <c r="B258" t="n">
-        <v>91330</v>
+        <v>100630</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E258" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I258" t="inlineStr"/>
@@ -28726,10 +28726,10 @@
         </is>
       </c>
       <c r="Q258" t="n">
-        <v>564128</v>
+        <v>563881</v>
       </c>
       <c r="R258" t="n">
-        <v>6705064</v>
+        <v>6704905</v>
       </c>
       <c r="S258" t="n">
         <v>10</v>
@@ -28788,50 +28788,45 @@
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>127683158</v>
+        <v>127683164</v>
       </c>
       <c r="B259" t="n">
-        <v>57658</v>
+        <v>91102</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E259" t="n">
-        <v>100049</v>
+        <v>3215</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I259" t="inlineStr"/>
-      <c r="M259" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P259" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q259" t="n">
-        <v>563970</v>
+        <v>564133</v>
       </c>
       <c r="R259" t="n">
-        <v>6704954</v>
+        <v>6705173</v>
       </c>
       <c r="S259" t="n">
         <v>10</v>
@@ -28890,40 +28885,35 @@
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>127683157</v>
+        <v>127683133</v>
       </c>
       <c r="B260" t="n">
-        <v>57658</v>
+        <v>91295</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E260" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I260" t="inlineStr"/>
-      <c r="M260" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P260" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
@@ -28992,45 +28982,50 @@
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>127683164</v>
+        <v>127683157</v>
       </c>
       <c r="B261" t="n">
-        <v>91102</v>
+        <v>57658</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E261" t="n">
-        <v>3215</v>
+        <v>100049</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I261" t="inlineStr"/>
+      <c r="M261" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P261" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q261" t="n">
-        <v>564133</v>
+        <v>564052</v>
       </c>
       <c r="R261" t="n">
-        <v>6705173</v>
+        <v>6705031</v>
       </c>
       <c r="S261" t="n">
         <v>10</v>
@@ -29089,45 +29084,50 @@
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>127683133</v>
+        <v>127683158</v>
       </c>
       <c r="B262" t="n">
-        <v>91295</v>
+        <v>57658</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E262" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I262" t="inlineStr"/>
+      <c r="M262" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P262" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q262" t="n">
-        <v>564052</v>
+        <v>563970</v>
       </c>
       <c r="R262" t="n">
-        <v>6705031</v>
+        <v>6704954</v>
       </c>
       <c r="S262" t="n">
         <v>10</v>
@@ -29186,59 +29186,45 @@
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>127683187</v>
+        <v>127683172</v>
       </c>
       <c r="B263" t="n">
-        <v>98448</v>
+        <v>95304</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E263" t="n">
-        <v>220787</v>
+        <v>2387</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I263" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J263" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K263" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Huebener) T.J.Kop.</t>
+        </is>
+      </c>
+      <c r="I263" t="inlineStr"/>
       <c r="P263" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q263" t="n">
-        <v>564215</v>
+        <v>563914</v>
       </c>
       <c r="R263" t="n">
-        <v>6705203</v>
+        <v>6704945</v>
       </c>
       <c r="S263" t="n">
         <v>10</v>
@@ -29271,6 +29257,11 @@
       <c r="AA263" t="inlineStr">
         <is>
           <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AC263" t="inlineStr">
+        <is>
+          <t>I källdråg utan planerad hänsyn</t>
         </is>
       </c>
       <c r="AD263" t="b">
@@ -29297,32 +29288,32 @@
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>127683172</v>
+        <v>127683130</v>
       </c>
       <c r="B264" t="n">
-        <v>95304</v>
+        <v>91542</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E264" t="n">
-        <v>2387</v>
+        <v>1106</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I264" t="inlineStr"/>
@@ -29332,10 +29323,10 @@
         </is>
       </c>
       <c r="Q264" t="n">
-        <v>563914</v>
+        <v>564057</v>
       </c>
       <c r="R264" t="n">
-        <v>6704945</v>
+        <v>6705032</v>
       </c>
       <c r="S264" t="n">
         <v>10</v>
@@ -29368,11 +29359,6 @@
       <c r="AA264" t="inlineStr">
         <is>
           <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="AC264" t="inlineStr">
-        <is>
-          <t>I källdråg utan planerad hänsyn</t>
         </is>
       </c>
       <c r="AD264" t="b">
@@ -29399,10 +29385,10 @@
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>127683130</v>
+        <v>127683187</v>
       </c>
       <c r="B265" t="n">
-        <v>91542</v>
+        <v>98448</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -29410,34 +29396,48 @@
         </is>
       </c>
       <c r="E265" t="n">
-        <v>1106</v>
+        <v>220787</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
-        </is>
-      </c>
-      <c r="I265" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I265" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J265" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K265" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P265" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q265" t="n">
-        <v>564057</v>
+        <v>564215</v>
       </c>
       <c r="R265" t="n">
-        <v>6705032</v>
+        <v>6705203</v>
       </c>
       <c r="S265" t="n">
         <v>10</v>

--- a/artfynd/A 58548-2022 artfynd.xlsx
+++ b/artfynd/A 58548-2022 artfynd.xlsx
@@ -28885,35 +28885,40 @@
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>127683133</v>
+        <v>127683157</v>
       </c>
       <c r="B260" t="n">
-        <v>91295</v>
+        <v>57658</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E260" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I260" t="inlineStr"/>
+      <c r="M260" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P260" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
@@ -28982,7 +28987,7 @@
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>127683157</v>
+        <v>127683158</v>
       </c>
       <c r="B261" t="n">
         <v>57658</v>
@@ -29022,10 +29027,10 @@
         </is>
       </c>
       <c r="Q261" t="n">
-        <v>564052</v>
+        <v>563970</v>
       </c>
       <c r="R261" t="n">
-        <v>6705031</v>
+        <v>6704954</v>
       </c>
       <c r="S261" t="n">
         <v>10</v>
@@ -29084,50 +29089,45 @@
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>127683158</v>
+        <v>127683133</v>
       </c>
       <c r="B262" t="n">
-        <v>57658</v>
+        <v>91295</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E262" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I262" t="inlineStr"/>
-      <c r="M262" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P262" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q262" t="n">
-        <v>563970</v>
+        <v>564052</v>
       </c>
       <c r="R262" t="n">
-        <v>6704954</v>
+        <v>6705031</v>
       </c>
       <c r="S262" t="n">
         <v>10</v>

--- a/artfynd/A 58548-2022 artfynd.xlsx
+++ b/artfynd/A 58548-2022 artfynd.xlsx
@@ -25139,10 +25139,10 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>127683181</v>
+        <v>127683144</v>
       </c>
       <c r="B223" t="n">
-        <v>91696</v>
+        <v>91332</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -25150,21 +25150,21 @@
         </is>
       </c>
       <c r="E223" t="n">
-        <v>2064</v>
+        <v>1202</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Kilporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Skeletocutis kuehneri</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>A.David</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I223" t="inlineStr"/>
@@ -25174,10 +25174,10 @@
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>564128</v>
+        <v>563970</v>
       </c>
       <c r="R223" t="n">
-        <v>6705055</v>
+        <v>6704986</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -25210,11 +25210,6 @@
       <c r="AA223" t="inlineStr">
         <is>
           <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="AC223" t="inlineStr">
-        <is>
-          <t>Kommer att mikroskoperas</t>
         </is>
       </c>
       <c r="AD223" t="b">
@@ -25241,59 +25236,45 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>127683183</v>
+        <v>127683140</v>
       </c>
       <c r="B224" t="n">
-        <v>98448</v>
+        <v>91332</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E224" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I224" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J224" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K224" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I224" t="inlineStr"/>
       <c r="P224" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>564023</v>
+        <v>564253</v>
       </c>
       <c r="R224" t="n">
-        <v>6705072</v>
+        <v>6705225</v>
       </c>
       <c r="S224" t="n">
         <v>10</v>
@@ -25326,11 +25307,6 @@
       <c r="AA224" t="inlineStr">
         <is>
           <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="AC224" t="inlineStr">
-        <is>
-          <t>2 blomstjälkar</t>
         </is>
       </c>
       <c r="AD224" t="b">
@@ -25357,45 +25333,54 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>127683140</v>
+        <v>127683193</v>
       </c>
       <c r="B225" t="n">
-        <v>91330</v>
+        <v>92656</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E225" t="n">
-        <v>1202</v>
+        <v>5964</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I225" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J225" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P225" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>564253</v>
+        <v>563883</v>
       </c>
       <c r="R225" t="n">
-        <v>6705225</v>
+        <v>6704908</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -25454,10 +25439,10 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>127683144</v>
+        <v>127683156</v>
       </c>
       <c r="B226" t="n">
-        <v>91330</v>
+        <v>57660</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -25465,34 +25450,39 @@
         </is>
       </c>
       <c r="E226" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I226" t="inlineStr"/>
+      <c r="M226" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P226" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>563970</v>
+        <v>564124</v>
       </c>
       <c r="R226" t="n">
-        <v>6704986</v>
+        <v>6705171</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -25551,10 +25541,10 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>127683156</v>
+        <v>127683154</v>
       </c>
       <c r="B227" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -25582,7 +25572,7 @@
       <c r="I227" t="inlineStr"/>
       <c r="M227" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P227" t="inlineStr">
@@ -25591,10 +25581,10 @@
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>564124</v>
+        <v>564140</v>
       </c>
       <c r="R227" t="n">
-        <v>6705171</v>
+        <v>6705076</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -25653,50 +25643,45 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>127683154</v>
+        <v>127683166</v>
       </c>
       <c r="B228" t="n">
-        <v>57658</v>
+        <v>97327</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E228" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I228" t="inlineStr"/>
-      <c r="M228" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P228" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>564140</v>
+        <v>563939</v>
       </c>
       <c r="R228" t="n">
-        <v>6705076</v>
+        <v>6704940</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -25755,54 +25740,45 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>127683193</v>
+        <v>127683181</v>
       </c>
       <c r="B229" t="n">
-        <v>92654</v>
+        <v>91698</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E229" t="n">
-        <v>5964</v>
+        <v>2064</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Kilporing</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Skeletocutis kuehneri</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I229" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J229" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>A.David</t>
+        </is>
+      </c>
+      <c r="I229" t="inlineStr"/>
       <c r="P229" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>563883</v>
+        <v>564128</v>
       </c>
       <c r="R229" t="n">
-        <v>6704908</v>
+        <v>6705055</v>
       </c>
       <c r="S229" t="n">
         <v>10</v>
@@ -25835,6 +25811,11 @@
       <c r="AA229" t="inlineStr">
         <is>
           <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AC229" t="inlineStr">
+        <is>
+          <t>Kommer att mikroskoperas</t>
         </is>
       </c>
       <c r="AD229" t="b">
@@ -25861,45 +25842,59 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>127683166</v>
+        <v>127683183</v>
       </c>
       <c r="B230" t="n">
-        <v>97325</v>
+        <v>98450</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E230" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I230" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J230" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P230" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>563939</v>
+        <v>564023</v>
       </c>
       <c r="R230" t="n">
-        <v>6704940</v>
+        <v>6705072</v>
       </c>
       <c r="S230" t="n">
         <v>10</v>
@@ -25932,6 +25927,11 @@
       <c r="AA230" t="inlineStr">
         <is>
           <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AC230" t="inlineStr">
+        <is>
+          <t>2 blomstjälkar</t>
         </is>
       </c>
       <c r="AD230" t="b">
@@ -25958,32 +25958,32 @@
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>127683173</v>
+        <v>127683203</v>
       </c>
       <c r="B231" t="n">
-        <v>95304</v>
+        <v>91733</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E231" t="n">
-        <v>2387</v>
+        <v>715</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Finporing</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Gloeoporus pannocinctus</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(Romell) J.Erikss.</t>
         </is>
       </c>
       <c r="I231" t="inlineStr"/>
@@ -25993,10 +25993,10 @@
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>563865</v>
+        <v>563955</v>
       </c>
       <c r="R231" t="n">
-        <v>6704888</v>
+        <v>6704996</v>
       </c>
       <c r="S231" t="n">
         <v>10</v>
@@ -26029,11 +26029,6 @@
       <c r="AA231" t="inlineStr">
         <is>
           <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="AC231" t="inlineStr">
-        <is>
-          <t>I källdråg utan planerad hänsyn</t>
         </is>
       </c>
       <c r="AD231" t="b">
@@ -26060,45 +26055,50 @@
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>127683203</v>
+        <v>127683147</v>
       </c>
       <c r="B232" t="n">
-        <v>91731</v>
+        <v>57823</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E232" t="n">
-        <v>715</v>
+        <v>103021</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Finporing</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Gloeoporus pannocinctus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>(Romell) J.Erikss.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I232" t="inlineStr"/>
+      <c r="M232" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P232" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>563955</v>
+        <v>564237</v>
       </c>
       <c r="R232" t="n">
-        <v>6704996</v>
+        <v>6705225</v>
       </c>
       <c r="S232" t="n">
         <v>10</v>
@@ -26157,50 +26157,45 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>127683147</v>
+        <v>127683173</v>
       </c>
       <c r="B233" t="n">
-        <v>57821</v>
+        <v>95306</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E233" t="n">
-        <v>103021</v>
+        <v>2387</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I233" t="inlineStr"/>
-      <c r="M233" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P233" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>564237</v>
+        <v>563865</v>
       </c>
       <c r="R233" t="n">
-        <v>6705225</v>
+        <v>6704888</v>
       </c>
       <c r="S233" t="n">
         <v>10</v>
@@ -26233,6 +26228,11 @@
       <c r="AA233" t="inlineStr">
         <is>
           <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AC233" t="inlineStr">
+        <is>
+          <t>I källdråg utan planerad hänsyn</t>
         </is>
       </c>
       <c r="AD233" t="b">
@@ -26262,7 +26262,7 @@
         <v>127683159</v>
       </c>
       <c r="B234" t="n">
-        <v>92232</v>
+        <v>92234</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -26356,45 +26356,50 @@
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>127683165</v>
+        <v>127683146</v>
       </c>
       <c r="B235" t="n">
-        <v>91952</v>
+        <v>4773</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E235" t="n">
-        <v>483</v>
+        <v>100299</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Rostskinn</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Crustoderma dryinum</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I235" t="inlineStr"/>
+      <c r="M235" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P235" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q235" t="n">
-        <v>564089</v>
+        <v>564057</v>
       </c>
       <c r="R235" t="n">
-        <v>6705072</v>
+        <v>6705124</v>
       </c>
       <c r="S235" t="n">
         <v>10</v>
@@ -26453,10 +26458,10 @@
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>127683146</v>
+        <v>127683152</v>
       </c>
       <c r="B236" t="n">
-        <v>4773</v>
+        <v>92267</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -26464,27 +26469,31 @@
         </is>
       </c>
       <c r="E236" t="n">
-        <v>100299</v>
+        <v>4769</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
-        </is>
-      </c>
-      <c r="I236" t="inlineStr"/>
-      <c r="M236" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I236" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J236" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P236" t="inlineStr">
@@ -26493,10 +26502,10 @@
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>564057</v>
+        <v>563895</v>
       </c>
       <c r="R236" t="n">
-        <v>6705124</v>
+        <v>6704903</v>
       </c>
       <c r="S236" t="n">
         <v>10</v>
@@ -26555,42 +26564,47 @@
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>127683152</v>
+        <v>127683188</v>
       </c>
       <c r="B237" t="n">
-        <v>92265</v>
+        <v>98450</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E237" t="n">
-        <v>4769</v>
+        <v>220787</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I237" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J237" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K237" t="inlineStr">
+        <is>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P237" t="inlineStr">
@@ -26599,10 +26613,10 @@
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>563895</v>
+        <v>563940</v>
       </c>
       <c r="R237" t="n">
-        <v>6704903</v>
+        <v>6704945</v>
       </c>
       <c r="S237" t="n">
         <v>10</v>
@@ -26664,7 +26678,7 @@
         <v>127683163</v>
       </c>
       <c r="B238" t="n">
-        <v>91102</v>
+        <v>91104</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -26763,47 +26777,42 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>127683188</v>
+        <v>127683196</v>
       </c>
       <c r="B239" t="n">
-        <v>98448</v>
+        <v>92656</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E239" t="n">
-        <v>220787</v>
+        <v>5964</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J239" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K239" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P239" t="inlineStr">
@@ -26812,10 +26821,10 @@
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>563940</v>
+        <v>564163</v>
       </c>
       <c r="R239" t="n">
-        <v>6704945</v>
+        <v>6705180</v>
       </c>
       <c r="S239" t="n">
         <v>10</v>
@@ -26874,54 +26883,45 @@
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>127683196</v>
+        <v>127683138</v>
       </c>
       <c r="B240" t="n">
-        <v>92654</v>
+        <v>91690</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E240" t="n">
-        <v>5964</v>
+        <v>2062</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I240" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J240" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I240" t="inlineStr"/>
       <c r="P240" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>564163</v>
+        <v>564145</v>
       </c>
       <c r="R240" t="n">
-        <v>6705180</v>
+        <v>6705081</v>
       </c>
       <c r="S240" t="n">
         <v>10</v>
@@ -26983,7 +26983,7 @@
         <v>127683185</v>
       </c>
       <c r="B241" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -27091,32 +27091,32 @@
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>127683138</v>
+        <v>127683182</v>
       </c>
       <c r="B242" t="n">
-        <v>91688</v>
+        <v>75082</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E242" t="n">
-        <v>2062</v>
+        <v>6426</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I242" t="inlineStr"/>
@@ -27126,10 +27126,10 @@
         </is>
       </c>
       <c r="Q242" t="n">
-        <v>564145</v>
+        <v>563929</v>
       </c>
       <c r="R242" t="n">
-        <v>6705081</v>
+        <v>6704888</v>
       </c>
       <c r="S242" t="n">
         <v>10</v>
@@ -27188,45 +27188,50 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>127683182</v>
+        <v>127683149</v>
       </c>
       <c r="B243" t="n">
-        <v>75080</v>
+        <v>57823</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E243" t="n">
-        <v>6426</v>
+        <v>103021</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I243" t="inlineStr"/>
+      <c r="M243" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P243" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>563929</v>
+        <v>564082</v>
       </c>
       <c r="R243" t="n">
-        <v>6704888</v>
+        <v>6705145</v>
       </c>
       <c r="S243" t="n">
         <v>10</v>
@@ -27288,7 +27293,7 @@
         <v>127683162</v>
       </c>
       <c r="B244" t="n">
-        <v>95692</v>
+        <v>95694</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -27382,38 +27387,42 @@
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>127683149</v>
+        <v>127683195</v>
       </c>
       <c r="B245" t="n">
-        <v>57821</v>
+        <v>92656</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E245" t="n">
-        <v>103021</v>
+        <v>5964</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I245" t="inlineStr"/>
-      <c r="M245" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I245" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J245" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P245" t="inlineStr">
@@ -27422,10 +27431,10 @@
         </is>
       </c>
       <c r="Q245" t="n">
-        <v>564082</v>
+        <v>563882</v>
       </c>
       <c r="R245" t="n">
-        <v>6705145</v>
+        <v>6704905</v>
       </c>
       <c r="S245" t="n">
         <v>10</v>
@@ -27484,10 +27493,10 @@
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>127683195</v>
+        <v>127683135</v>
       </c>
       <c r="B246" t="n">
-        <v>92654</v>
+        <v>91297</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -27495,43 +27504,34 @@
         </is>
       </c>
       <c r="E246" t="n">
-        <v>5964</v>
+        <v>5447</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I246" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J246" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I246" t="inlineStr"/>
       <c r="P246" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>563882</v>
+        <v>564226</v>
       </c>
       <c r="R246" t="n">
-        <v>6704905</v>
+        <v>6705244</v>
       </c>
       <c r="S246" t="n">
         <v>10</v>
@@ -27590,45 +27590,59 @@
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>127683135</v>
+        <v>127683184</v>
       </c>
       <c r="B247" t="n">
-        <v>91295</v>
+        <v>98450</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E247" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I247" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I247" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J247" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K247" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P247" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q247" t="n">
-        <v>564226</v>
+        <v>563880</v>
       </c>
       <c r="R247" t="n">
-        <v>6705244</v>
+        <v>6704891</v>
       </c>
       <c r="S247" t="n">
         <v>10</v>
@@ -27661,6 +27675,11 @@
       <c r="AA247" t="inlineStr">
         <is>
           <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AC247" t="inlineStr">
+        <is>
+          <t>3 blomstjälkar</t>
         </is>
       </c>
       <c r="AD247" t="b">
@@ -27687,10 +27706,10 @@
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>127683184</v>
+        <v>127683137</v>
       </c>
       <c r="B248" t="n">
-        <v>98448</v>
+        <v>91690</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -27698,48 +27717,34 @@
         </is>
       </c>
       <c r="E248" t="n">
-        <v>220787</v>
+        <v>2062</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I248" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J248" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K248" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I248" t="inlineStr"/>
       <c r="P248" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q248" t="n">
-        <v>563880</v>
+        <v>564130</v>
       </c>
       <c r="R248" t="n">
-        <v>6704891</v>
+        <v>6705091</v>
       </c>
       <c r="S248" t="n">
         <v>10</v>
@@ -27772,11 +27777,6 @@
       <c r="AA248" t="inlineStr">
         <is>
           <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="AC248" t="inlineStr">
-        <is>
-          <t>3 blomstjälkar</t>
         </is>
       </c>
       <c r="AD248" t="b">
@@ -27803,32 +27803,32 @@
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>127683137</v>
+        <v>127683141</v>
       </c>
       <c r="B249" t="n">
-        <v>91688</v>
+        <v>91332</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E249" t="n">
-        <v>2062</v>
+        <v>1202</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I249" t="inlineStr"/>
@@ -27903,7 +27903,7 @@
         <v>127683151</v>
       </c>
       <c r="B250" t="n">
-        <v>92265</v>
+        <v>92267</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -28002,32 +28002,32 @@
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>127683141</v>
+        <v>127683139</v>
       </c>
       <c r="B251" t="n">
-        <v>91330</v>
+        <v>91690</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E251" t="n">
-        <v>1202</v>
+        <v>2062</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I251" t="inlineStr"/>
@@ -28037,10 +28037,10 @@
         </is>
       </c>
       <c r="Q251" t="n">
-        <v>564130</v>
+        <v>563999</v>
       </c>
       <c r="R251" t="n">
-        <v>6705091</v>
+        <v>6705007</v>
       </c>
       <c r="S251" t="n">
         <v>10</v>
@@ -28099,32 +28099,32 @@
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>127683139</v>
+        <v>127683199</v>
       </c>
       <c r="B252" t="n">
-        <v>91688</v>
+        <v>95301</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E252" t="n">
-        <v>2062</v>
+        <v>2383</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Bågpraktmossa</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Plagiomnium medium</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Bruch &amp; Schimp.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I252" t="inlineStr"/>
@@ -28134,10 +28134,10 @@
         </is>
       </c>
       <c r="Q252" t="n">
-        <v>563999</v>
+        <v>564058</v>
       </c>
       <c r="R252" t="n">
-        <v>6705007</v>
+        <v>6705124</v>
       </c>
       <c r="S252" t="n">
         <v>10</v>
@@ -28170,6 +28170,11 @@
       <c r="AA252" t="inlineStr">
         <is>
           <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AC252" t="inlineStr">
+        <is>
+          <t>i översinlningsområde utanför hänsyn</t>
         </is>
       </c>
       <c r="AD252" t="b">
@@ -28196,10 +28201,10 @@
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>127683199</v>
+        <v>127683200</v>
       </c>
       <c r="B253" t="n">
-        <v>95299</v>
+        <v>100632</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -28207,21 +28212,21 @@
         </is>
       </c>
       <c r="E253" t="n">
-        <v>2383</v>
+        <v>222498</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Bågpraktmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Plagiomnium medium</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>(Bruch &amp; Schimp.) T.J.Kop.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I253" t="inlineStr"/>
@@ -28231,10 +28236,10 @@
         </is>
       </c>
       <c r="Q253" t="n">
-        <v>564058</v>
+        <v>563890</v>
       </c>
       <c r="R253" t="n">
-        <v>6705124</v>
+        <v>6704897</v>
       </c>
       <c r="S253" t="n">
         <v>10</v>
@@ -28267,11 +28272,6 @@
       <c r="AA253" t="inlineStr">
         <is>
           <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="AC253" t="inlineStr">
-        <is>
-          <t>i översinlningsområde utanför hänsyn</t>
         </is>
       </c>
       <c r="AD253" t="b">
@@ -28298,32 +28298,32 @@
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>127683200</v>
+        <v>127683145</v>
       </c>
       <c r="B254" t="n">
-        <v>100630</v>
+        <v>91332</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E254" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I254" t="inlineStr"/>
@@ -28333,10 +28333,10 @@
         </is>
       </c>
       <c r="Q254" t="n">
-        <v>563890</v>
+        <v>563995</v>
       </c>
       <c r="R254" t="n">
-        <v>6704897</v>
+        <v>6705021</v>
       </c>
       <c r="S254" t="n">
         <v>10</v>
@@ -28395,10 +28395,10 @@
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>127683145</v>
+        <v>127683155</v>
       </c>
       <c r="B255" t="n">
-        <v>91330</v>
+        <v>57660</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -28406,34 +28406,39 @@
         </is>
       </c>
       <c r="E255" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I255" t="inlineStr"/>
+      <c r="M255" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P255" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q255" t="n">
-        <v>563995</v>
+        <v>564144</v>
       </c>
       <c r="R255" t="n">
-        <v>6705021</v>
+        <v>6705112</v>
       </c>
       <c r="S255" t="n">
         <v>10</v>
@@ -28492,32 +28497,32 @@
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>127683142</v>
+        <v>127683201</v>
       </c>
       <c r="B256" t="n">
-        <v>91330</v>
+        <v>100632</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E256" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I256" t="inlineStr"/>
@@ -28527,10 +28532,10 @@
         </is>
       </c>
       <c r="Q256" t="n">
-        <v>564128</v>
+        <v>563881</v>
       </c>
       <c r="R256" t="n">
-        <v>6705064</v>
+        <v>6704905</v>
       </c>
       <c r="S256" t="n">
         <v>10</v>
@@ -28589,10 +28594,10 @@
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>127683155</v>
+        <v>127683142</v>
       </c>
       <c r="B257" t="n">
-        <v>57658</v>
+        <v>91332</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -28600,39 +28605,34 @@
         </is>
       </c>
       <c r="E257" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I257" t="inlineStr"/>
-      <c r="M257" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P257" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q257" t="n">
-        <v>564144</v>
+        <v>564128</v>
       </c>
       <c r="R257" t="n">
-        <v>6705112</v>
+        <v>6705064</v>
       </c>
       <c r="S257" t="n">
         <v>10</v>
@@ -28691,10 +28691,10 @@
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>127683201</v>
+        <v>127683164</v>
       </c>
       <c r="B258" t="n">
-        <v>100630</v>
+        <v>91104</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -28702,21 +28702,21 @@
         </is>
       </c>
       <c r="E258" t="n">
-        <v>222498</v>
+        <v>3215</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I258" t="inlineStr"/>
@@ -28726,10 +28726,10 @@
         </is>
       </c>
       <c r="Q258" t="n">
-        <v>563881</v>
+        <v>564133</v>
       </c>
       <c r="R258" t="n">
-        <v>6704905</v>
+        <v>6705173</v>
       </c>
       <c r="S258" t="n">
         <v>10</v>
@@ -28788,45 +28788,50 @@
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>127683164</v>
+        <v>127683157</v>
       </c>
       <c r="B259" t="n">
-        <v>91102</v>
+        <v>57660</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E259" t="n">
-        <v>3215</v>
+        <v>100049</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I259" t="inlineStr"/>
+      <c r="M259" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P259" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q259" t="n">
-        <v>564133</v>
+        <v>564052</v>
       </c>
       <c r="R259" t="n">
-        <v>6705173</v>
+        <v>6705031</v>
       </c>
       <c r="S259" t="n">
         <v>10</v>
@@ -28885,10 +28890,10 @@
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>127683157</v>
+        <v>127683158</v>
       </c>
       <c r="B260" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -28925,10 +28930,10 @@
         </is>
       </c>
       <c r="Q260" t="n">
-        <v>564052</v>
+        <v>563970</v>
       </c>
       <c r="R260" t="n">
-        <v>6705031</v>
+        <v>6704954</v>
       </c>
       <c r="S260" t="n">
         <v>10</v>
@@ -28987,50 +28992,45 @@
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>127683158</v>
+        <v>127683133</v>
       </c>
       <c r="B261" t="n">
-        <v>57658</v>
+        <v>91297</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E261" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I261" t="inlineStr"/>
-      <c r="M261" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P261" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q261" t="n">
-        <v>563970</v>
+        <v>564052</v>
       </c>
       <c r="R261" t="n">
-        <v>6704954</v>
+        <v>6705031</v>
       </c>
       <c r="S261" t="n">
         <v>10</v>
@@ -29089,32 +29089,32 @@
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>127683133</v>
+        <v>127683130</v>
       </c>
       <c r="B262" t="n">
-        <v>91295</v>
+        <v>91544</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E262" t="n">
-        <v>5447</v>
+        <v>1106</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I262" t="inlineStr"/>
@@ -29124,10 +29124,10 @@
         </is>
       </c>
       <c r="Q262" t="n">
-        <v>564052</v>
+        <v>564057</v>
       </c>
       <c r="R262" t="n">
-        <v>6705031</v>
+        <v>6705032</v>
       </c>
       <c r="S262" t="n">
         <v>10</v>
@@ -29189,7 +29189,7 @@
         <v>127683172</v>
       </c>
       <c r="B263" t="n">
-        <v>95304</v>
+        <v>95306</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -29288,10 +29288,10 @@
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>127683130</v>
+        <v>127683187</v>
       </c>
       <c r="B264" t="n">
-        <v>91542</v>
+        <v>98450</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -29299,34 +29299,48 @@
         </is>
       </c>
       <c r="E264" t="n">
-        <v>1106</v>
+        <v>220787</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
-        </is>
-      </c>
-      <c r="I264" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I264" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J264" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K264" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P264" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q264" t="n">
-        <v>564057</v>
+        <v>564215</v>
       </c>
       <c r="R264" t="n">
-        <v>6705032</v>
+        <v>6705203</v>
       </c>
       <c r="S264" t="n">
         <v>10</v>
@@ -29385,10 +29399,10 @@
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>127683187</v>
+        <v>127683165</v>
       </c>
       <c r="B265" t="n">
-        <v>98448</v>
+        <v>91954</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -29396,48 +29410,34 @@
         </is>
       </c>
       <c r="E265" t="n">
-        <v>220787</v>
+        <v>483</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rostskinn</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crustoderma dryinum</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I265" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J265" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K265" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
+        </is>
+      </c>
+      <c r="I265" t="inlineStr"/>
       <c r="P265" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q265" t="n">
-        <v>564215</v>
+        <v>564089</v>
       </c>
       <c r="R265" t="n">
-        <v>6705203</v>
+        <v>6705072</v>
       </c>
       <c r="S265" t="n">
         <v>10</v>

--- a/artfynd/A 58548-2022 artfynd.xlsx
+++ b/artfynd/A 58548-2022 artfynd.xlsx
@@ -25333,10 +25333,10 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>127683193</v>
+        <v>127683166</v>
       </c>
       <c r="B225" t="n">
-        <v>92656</v>
+        <v>97327</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -25344,43 +25344,34 @@
         </is>
       </c>
       <c r="E225" t="n">
-        <v>5964</v>
+        <v>221945</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I225" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J225" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I225" t="inlineStr"/>
       <c r="P225" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>563883</v>
+        <v>563939</v>
       </c>
       <c r="R225" t="n">
-        <v>6704908</v>
+        <v>6704940</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -25439,38 +25430,42 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>127683156</v>
+        <v>127683193</v>
       </c>
       <c r="B226" t="n">
-        <v>57660</v>
+        <v>92656</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E226" t="n">
-        <v>100049</v>
+        <v>5964</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I226" t="inlineStr"/>
-      <c r="M226" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J226" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P226" t="inlineStr">
@@ -25479,10 +25474,10 @@
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>564124</v>
+        <v>563883</v>
       </c>
       <c r="R226" t="n">
-        <v>6705171</v>
+        <v>6704908</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -25541,10 +25536,10 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>127683154</v>
+        <v>127683181</v>
       </c>
       <c r="B227" t="n">
-        <v>57660</v>
+        <v>91698</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -25552,39 +25547,34 @@
         </is>
       </c>
       <c r="E227" t="n">
-        <v>100049</v>
+        <v>2064</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kilporing</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Skeletocutis kuehneri</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>A.David</t>
         </is>
       </c>
       <c r="I227" t="inlineStr"/>
-      <c r="M227" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P227" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>564140</v>
+        <v>564128</v>
       </c>
       <c r="R227" t="n">
-        <v>6705076</v>
+        <v>6705055</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -25617,6 +25607,11 @@
       <c r="AA227" t="inlineStr">
         <is>
           <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AC227" t="inlineStr">
+        <is>
+          <t>Kommer att mikroskoperas</t>
         </is>
       </c>
       <c r="AD227" t="b">
@@ -25643,45 +25638,50 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>127683166</v>
+        <v>127683156</v>
       </c>
       <c r="B228" t="n">
-        <v>97327</v>
+        <v>57660</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E228" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I228" t="inlineStr"/>
+      <c r="M228" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P228" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>563939</v>
+        <v>564124</v>
       </c>
       <c r="R228" t="n">
-        <v>6704940</v>
+        <v>6705171</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -25740,10 +25740,10 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>127683181</v>
+        <v>127683154</v>
       </c>
       <c r="B229" t="n">
-        <v>91698</v>
+        <v>57660</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -25751,34 +25751,39 @@
         </is>
       </c>
       <c r="E229" t="n">
-        <v>2064</v>
+        <v>100049</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Kilporing</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Skeletocutis kuehneri</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>A.David</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I229" t="inlineStr"/>
+      <c r="M229" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P229" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>564128</v>
+        <v>564140</v>
       </c>
       <c r="R229" t="n">
-        <v>6705055</v>
+        <v>6705076</v>
       </c>
       <c r="S229" t="n">
         <v>10</v>
@@ -25811,11 +25816,6 @@
       <c r="AA229" t="inlineStr">
         <is>
           <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="AC229" t="inlineStr">
-        <is>
-          <t>Kommer att mikroskoperas</t>
         </is>
       </c>
       <c r="AD229" t="b">
@@ -26055,50 +26055,45 @@
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>127683147</v>
+        <v>127683173</v>
       </c>
       <c r="B232" t="n">
-        <v>57823</v>
+        <v>95306</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E232" t="n">
-        <v>103021</v>
+        <v>2387</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I232" t="inlineStr"/>
-      <c r="M232" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P232" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>564237</v>
+        <v>563865</v>
       </c>
       <c r="R232" t="n">
-        <v>6705225</v>
+        <v>6704888</v>
       </c>
       <c r="S232" t="n">
         <v>10</v>
@@ -26131,6 +26126,11 @@
       <c r="AA232" t="inlineStr">
         <is>
           <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AC232" t="inlineStr">
+        <is>
+          <t>I källdråg utan planerad hänsyn</t>
         </is>
       </c>
       <c r="AD232" t="b">
@@ -26157,45 +26157,50 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>127683173</v>
+        <v>127683147</v>
       </c>
       <c r="B233" t="n">
-        <v>95306</v>
+        <v>57823</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E233" t="n">
-        <v>2387</v>
+        <v>103021</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I233" t="inlineStr"/>
+      <c r="M233" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P233" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>563865</v>
+        <v>564237</v>
       </c>
       <c r="R233" t="n">
-        <v>6704888</v>
+        <v>6705225</v>
       </c>
       <c r="S233" t="n">
         <v>10</v>
@@ -26228,11 +26233,6 @@
       <c r="AA233" t="inlineStr">
         <is>
           <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="AC233" t="inlineStr">
-        <is>
-          <t>I källdråg utan planerad hänsyn</t>
         </is>
       </c>
       <c r="AD233" t="b">
@@ -26564,59 +26564,45 @@
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>127683188</v>
+        <v>127683163</v>
       </c>
       <c r="B237" t="n">
-        <v>98450</v>
+        <v>91104</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E237" t="n">
-        <v>220787</v>
+        <v>3215</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I237" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J237" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K237" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I237" t="inlineStr"/>
       <c r="P237" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>563940</v>
+        <v>564121</v>
       </c>
       <c r="R237" t="n">
-        <v>6704945</v>
+        <v>6705165</v>
       </c>
       <c r="S237" t="n">
         <v>10</v>
@@ -26649,6 +26635,11 @@
       <c r="AA237" t="inlineStr">
         <is>
           <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AC237" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD237" t="b">
@@ -26675,45 +26666,59 @@
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>127683163</v>
+        <v>127683188</v>
       </c>
       <c r="B238" t="n">
-        <v>91104</v>
+        <v>98450</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E238" t="n">
-        <v>3215</v>
+        <v>220787</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I238" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I238" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J238" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K238" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P238" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q238" t="n">
-        <v>564121</v>
+        <v>563940</v>
       </c>
       <c r="R238" t="n">
-        <v>6705165</v>
+        <v>6704945</v>
       </c>
       <c r="S238" t="n">
         <v>10</v>
@@ -26746,11 +26751,6 @@
       <c r="AA238" t="inlineStr">
         <is>
           <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="AC238" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD238" t="b">
@@ -27188,50 +27188,45 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>127683149</v>
+        <v>127683162</v>
       </c>
       <c r="B243" t="n">
-        <v>57823</v>
+        <v>95694</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E243" t="n">
-        <v>103021</v>
+        <v>2813</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I243" t="inlineStr"/>
-      <c r="M243" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P243" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>564082</v>
+        <v>563934</v>
       </c>
       <c r="R243" t="n">
-        <v>6705145</v>
+        <v>6704860</v>
       </c>
       <c r="S243" t="n">
         <v>10</v>
@@ -27290,45 +27285,50 @@
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>127683162</v>
+        <v>127683149</v>
       </c>
       <c r="B244" t="n">
-        <v>95694</v>
+        <v>57823</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E244" t="n">
-        <v>2813</v>
+        <v>103021</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I244" t="inlineStr"/>
+      <c r="M244" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P244" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q244" t="n">
-        <v>563934</v>
+        <v>564082</v>
       </c>
       <c r="R244" t="n">
-        <v>6704860</v>
+        <v>6705145</v>
       </c>
       <c r="S244" t="n">
         <v>10</v>
@@ -28395,10 +28395,10 @@
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>127683155</v>
+        <v>127683142</v>
       </c>
       <c r="B255" t="n">
-        <v>57660</v>
+        <v>91332</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -28406,39 +28406,34 @@
         </is>
       </c>
       <c r="E255" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I255" t="inlineStr"/>
-      <c r="M255" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P255" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q255" t="n">
-        <v>564144</v>
+        <v>564128</v>
       </c>
       <c r="R255" t="n">
-        <v>6705112</v>
+        <v>6705064</v>
       </c>
       <c r="S255" t="n">
         <v>10</v>
@@ -28497,45 +28492,50 @@
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>127683201</v>
+        <v>127683155</v>
       </c>
       <c r="B256" t="n">
-        <v>100632</v>
+        <v>57660</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E256" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I256" t="inlineStr"/>
+      <c r="M256" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P256" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q256" t="n">
-        <v>563881</v>
+        <v>564144</v>
       </c>
       <c r="R256" t="n">
-        <v>6704905</v>
+        <v>6705112</v>
       </c>
       <c r="S256" t="n">
         <v>10</v>
@@ -28594,32 +28594,32 @@
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>127683142</v>
+        <v>127683201</v>
       </c>
       <c r="B257" t="n">
-        <v>91332</v>
+        <v>100632</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E257" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I257" t="inlineStr"/>
@@ -28629,10 +28629,10 @@
         </is>
       </c>
       <c r="Q257" t="n">
-        <v>564128</v>
+        <v>563881</v>
       </c>
       <c r="R257" t="n">
-        <v>6705064</v>
+        <v>6704905</v>
       </c>
       <c r="S257" t="n">
         <v>10</v>
@@ -28788,40 +28788,35 @@
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>127683157</v>
+        <v>127683133</v>
       </c>
       <c r="B259" t="n">
-        <v>57660</v>
+        <v>91297</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E259" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I259" t="inlineStr"/>
-      <c r="M259" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P259" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
@@ -28890,7 +28885,7 @@
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>127683158</v>
+        <v>127683157</v>
       </c>
       <c r="B260" t="n">
         <v>57660</v>
@@ -28930,10 +28925,10 @@
         </is>
       </c>
       <c r="Q260" t="n">
-        <v>563970</v>
+        <v>564052</v>
       </c>
       <c r="R260" t="n">
-        <v>6704954</v>
+        <v>6705031</v>
       </c>
       <c r="S260" t="n">
         <v>10</v>
@@ -28992,45 +28987,50 @@
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>127683133</v>
+        <v>127683158</v>
       </c>
       <c r="B261" t="n">
-        <v>91297</v>
+        <v>57660</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E261" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I261" t="inlineStr"/>
+      <c r="M261" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P261" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q261" t="n">
-        <v>564052</v>
+        <v>563970</v>
       </c>
       <c r="R261" t="n">
-        <v>6705031</v>
+        <v>6704954</v>
       </c>
       <c r="S261" t="n">
         <v>10</v>

--- a/artfynd/A 58548-2022 artfynd.xlsx
+++ b/artfynd/A 58548-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY265"/>
+  <dimension ref="A1:AY281"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28002,32 +28002,32 @@
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>127683139</v>
+        <v>127683200</v>
       </c>
       <c r="B251" t="n">
-        <v>91690</v>
+        <v>100632</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E251" t="n">
-        <v>2062</v>
+        <v>222498</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I251" t="inlineStr"/>
@@ -28037,10 +28037,10 @@
         </is>
       </c>
       <c r="Q251" t="n">
-        <v>563999</v>
+        <v>563890</v>
       </c>
       <c r="R251" t="n">
-        <v>6705007</v>
+        <v>6704897</v>
       </c>
       <c r="S251" t="n">
         <v>10</v>
@@ -28099,32 +28099,32 @@
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>127683199</v>
+        <v>127683139</v>
       </c>
       <c r="B252" t="n">
-        <v>95301</v>
+        <v>91690</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E252" t="n">
-        <v>2383</v>
+        <v>2062</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Bågpraktmossa</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>Plagiomnium medium</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>(Bruch &amp; Schimp.) T.J.Kop.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I252" t="inlineStr"/>
@@ -28134,10 +28134,10 @@
         </is>
       </c>
       <c r="Q252" t="n">
-        <v>564058</v>
+        <v>563999</v>
       </c>
       <c r="R252" t="n">
-        <v>6705124</v>
+        <v>6705007</v>
       </c>
       <c r="S252" t="n">
         <v>10</v>
@@ -28170,11 +28170,6 @@
       <c r="AA252" t="inlineStr">
         <is>
           <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="AC252" t="inlineStr">
-        <is>
-          <t>i översinlningsområde utanför hänsyn</t>
         </is>
       </c>
       <c r="AD252" t="b">
@@ -28201,10 +28196,10 @@
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>127683200</v>
+        <v>127683199</v>
       </c>
       <c r="B253" t="n">
-        <v>100632</v>
+        <v>95301</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -28212,21 +28207,21 @@
         </is>
       </c>
       <c r="E253" t="n">
-        <v>222498</v>
+        <v>2383</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Bågpraktmossa</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Plagiomnium medium</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Bruch &amp; Schimp.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I253" t="inlineStr"/>
@@ -28236,10 +28231,10 @@
         </is>
       </c>
       <c r="Q253" t="n">
-        <v>563890</v>
+        <v>564058</v>
       </c>
       <c r="R253" t="n">
-        <v>6704897</v>
+        <v>6705124</v>
       </c>
       <c r="S253" t="n">
         <v>10</v>
@@ -28272,6 +28267,11 @@
       <c r="AA253" t="inlineStr">
         <is>
           <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AC253" t="inlineStr">
+        <is>
+          <t>i översinlningsområde utanför hänsyn</t>
         </is>
       </c>
       <c r="AD253" t="b">
@@ -29089,10 +29089,10 @@
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>127683130</v>
+        <v>127683187</v>
       </c>
       <c r="B262" t="n">
-        <v>91544</v>
+        <v>98450</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -29100,34 +29100,48 @@
         </is>
       </c>
       <c r="E262" t="n">
-        <v>1106</v>
+        <v>220787</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
-        </is>
-      </c>
-      <c r="I262" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I262" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J262" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K262" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P262" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q262" t="n">
-        <v>564057</v>
+        <v>564215</v>
       </c>
       <c r="R262" t="n">
-        <v>6705032</v>
+        <v>6705203</v>
       </c>
       <c r="S262" t="n">
         <v>10</v>
@@ -29186,32 +29200,32 @@
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>127683172</v>
+        <v>127683130</v>
       </c>
       <c r="B263" t="n">
-        <v>95306</v>
+        <v>91544</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E263" t="n">
-        <v>2387</v>
+        <v>1106</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I263" t="inlineStr"/>
@@ -29221,10 +29235,10 @@
         </is>
       </c>
       <c r="Q263" t="n">
-        <v>563914</v>
+        <v>564057</v>
       </c>
       <c r="R263" t="n">
-        <v>6704945</v>
+        <v>6705032</v>
       </c>
       <c r="S263" t="n">
         <v>10</v>
@@ -29257,11 +29271,6 @@
       <c r="AA263" t="inlineStr">
         <is>
           <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="AC263" t="inlineStr">
-        <is>
-          <t>I källdråg utan planerad hänsyn</t>
         </is>
       </c>
       <c r="AD263" t="b">
@@ -29288,59 +29297,45 @@
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>127683187</v>
+        <v>127683172</v>
       </c>
       <c r="B264" t="n">
-        <v>98450</v>
+        <v>95306</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E264" t="n">
-        <v>220787</v>
+        <v>2387</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I264" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J264" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K264" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Huebener) T.J.Kop.</t>
+        </is>
+      </c>
+      <c r="I264" t="inlineStr"/>
       <c r="P264" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q264" t="n">
-        <v>564215</v>
+        <v>563914</v>
       </c>
       <c r="R264" t="n">
-        <v>6705203</v>
+        <v>6704945</v>
       </c>
       <c r="S264" t="n">
         <v>10</v>
@@ -29373,6 +29368,11 @@
       <c r="AA264" t="inlineStr">
         <is>
           <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AC264" t="inlineStr">
+        <is>
+          <t>I källdråg utan planerad hänsyn</t>
         </is>
       </c>
       <c r="AD264" t="b">
@@ -29494,6 +29494,1702 @@
       </c>
       <c r="AY265" t="inlineStr"/>
     </row>
+    <row r="266">
+      <c r="A266" t="n">
+        <v>127785100</v>
+      </c>
+      <c r="B266" t="n">
+        <v>98450</v>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E266" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H266" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I266" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J266" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P266" t="inlineStr">
+        <is>
+          <t>Pellkärret, Dlr</t>
+        </is>
+      </c>
+      <c r="Q266" t="n">
+        <v>564391</v>
+      </c>
+      <c r="R266" t="n">
+        <v>6705389</v>
+      </c>
+      <c r="S266" t="n">
+        <v>10</v>
+      </c>
+      <c r="T266" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U266" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V266" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W266" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y266" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AA266" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AD266" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE266" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG266" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT266" t="inlineStr"/>
+      <c r="AW266" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX266" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY266" t="inlineStr"/>
+    </row>
+    <row r="267">
+      <c r="A267" t="n">
+        <v>127785097</v>
+      </c>
+      <c r="B267" t="n">
+        <v>98450</v>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E267" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H267" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I267" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J267" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P267" t="inlineStr">
+        <is>
+          <t>Pellkärret, Dlr</t>
+        </is>
+      </c>
+      <c r="Q267" t="n">
+        <v>564343</v>
+      </c>
+      <c r="R267" t="n">
+        <v>6705352</v>
+      </c>
+      <c r="S267" t="n">
+        <v>10</v>
+      </c>
+      <c r="T267" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U267" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V267" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W267" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y267" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AA267" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AD267" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE267" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG267" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT267" t="inlineStr"/>
+      <c r="AW267" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX267" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY267" t="inlineStr"/>
+    </row>
+    <row r="268">
+      <c r="A268" t="n">
+        <v>127785105</v>
+      </c>
+      <c r="B268" t="n">
+        <v>98450</v>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E268" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H268" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I268" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J268" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P268" t="inlineStr">
+        <is>
+          <t>Pellkärret, Dlr</t>
+        </is>
+      </c>
+      <c r="Q268" t="n">
+        <v>564387</v>
+      </c>
+      <c r="R268" t="n">
+        <v>6705389</v>
+      </c>
+      <c r="S268" t="n">
+        <v>10</v>
+      </c>
+      <c r="T268" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U268" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V268" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W268" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y268" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AA268" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AD268" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE268" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG268" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT268" t="inlineStr"/>
+      <c r="AW268" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX268" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY268" t="inlineStr"/>
+    </row>
+    <row r="269">
+      <c r="A269" t="n">
+        <v>127785087</v>
+      </c>
+      <c r="B269" t="n">
+        <v>91690</v>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E269" t="n">
+        <v>2062</v>
+      </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>Ulltickeporing</t>
+        </is>
+      </c>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>Skeletocutis brevispora</t>
+        </is>
+      </c>
+      <c r="H269" t="inlineStr">
+        <is>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I269" t="inlineStr"/>
+      <c r="P269" t="inlineStr">
+        <is>
+          <t>Pellkärret, Dlr</t>
+        </is>
+      </c>
+      <c r="Q269" t="n">
+        <v>564352</v>
+      </c>
+      <c r="R269" t="n">
+        <v>6705423</v>
+      </c>
+      <c r="S269" t="n">
+        <v>10</v>
+      </c>
+      <c r="T269" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U269" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V269" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W269" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y269" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AA269" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AD269" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE269" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG269" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT269" t="inlineStr"/>
+      <c r="AW269" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX269" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY269" t="inlineStr"/>
+    </row>
+    <row r="270">
+      <c r="A270" t="n">
+        <v>127785102</v>
+      </c>
+      <c r="B270" t="n">
+        <v>98450</v>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E270" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G270" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H270" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I270" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J270" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P270" t="inlineStr">
+        <is>
+          <t>Pellkärret, Dlr</t>
+        </is>
+      </c>
+      <c r="Q270" t="n">
+        <v>564383</v>
+      </c>
+      <c r="R270" t="n">
+        <v>6705410</v>
+      </c>
+      <c r="S270" t="n">
+        <v>10</v>
+      </c>
+      <c r="T270" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U270" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V270" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W270" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y270" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AA270" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AD270" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE270" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG270" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT270" t="inlineStr"/>
+      <c r="AW270" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX270" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY270" t="inlineStr"/>
+    </row>
+    <row r="271">
+      <c r="A271" t="n">
+        <v>127785088</v>
+      </c>
+      <c r="B271" t="n">
+        <v>91332</v>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E271" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H271" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I271" t="inlineStr"/>
+      <c r="P271" t="inlineStr">
+        <is>
+          <t>Pellkärret, Dlr</t>
+        </is>
+      </c>
+      <c r="Q271" t="n">
+        <v>564358</v>
+      </c>
+      <c r="R271" t="n">
+        <v>6705424</v>
+      </c>
+      <c r="S271" t="n">
+        <v>10</v>
+      </c>
+      <c r="T271" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U271" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V271" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W271" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y271" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AA271" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AD271" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE271" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG271" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT271" t="inlineStr"/>
+      <c r="AW271" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX271" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY271" t="inlineStr"/>
+    </row>
+    <row r="272">
+      <c r="A272" t="n">
+        <v>127785089</v>
+      </c>
+      <c r="B272" t="n">
+        <v>57823</v>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E272" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H272" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I272" t="inlineStr"/>
+      <c r="P272" t="inlineStr">
+        <is>
+          <t>Pellkärret, Dlr</t>
+        </is>
+      </c>
+      <c r="Q272" t="n">
+        <v>564303</v>
+      </c>
+      <c r="R272" t="n">
+        <v>6705322</v>
+      </c>
+      <c r="S272" t="n">
+        <v>10</v>
+      </c>
+      <c r="T272" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U272" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V272" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W272" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y272" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AA272" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AD272" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE272" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG272" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT272" t="inlineStr"/>
+      <c r="AW272" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX272" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY272" t="inlineStr"/>
+    </row>
+    <row r="273">
+      <c r="A273" t="n">
+        <v>127785096</v>
+      </c>
+      <c r="B273" t="n">
+        <v>98450</v>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E273" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H273" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I273" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J273" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K273" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="P273" t="inlineStr">
+        <is>
+          <t>Pellkärret, Dlr</t>
+        </is>
+      </c>
+      <c r="Q273" t="n">
+        <v>564308</v>
+      </c>
+      <c r="R273" t="n">
+        <v>6705320</v>
+      </c>
+      <c r="S273" t="n">
+        <v>10</v>
+      </c>
+      <c r="T273" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U273" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V273" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W273" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y273" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AA273" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AC273" t="inlineStr">
+        <is>
+          <t>2 blomstjälkar</t>
+        </is>
+      </c>
+      <c r="AD273" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE273" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG273" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT273" t="inlineStr"/>
+      <c r="AW273" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX273" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY273" t="inlineStr"/>
+    </row>
+    <row r="274">
+      <c r="A274" t="n">
+        <v>127785091</v>
+      </c>
+      <c r="B274" t="n">
+        <v>91628</v>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E274" t="n">
+        <v>658</v>
+      </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H274" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I274" t="inlineStr"/>
+      <c r="P274" t="inlineStr">
+        <is>
+          <t>Pellkärret, Dlr</t>
+        </is>
+      </c>
+      <c r="Q274" t="n">
+        <v>564349</v>
+      </c>
+      <c r="R274" t="n">
+        <v>6705423</v>
+      </c>
+      <c r="S274" t="n">
+        <v>10</v>
+      </c>
+      <c r="T274" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U274" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V274" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W274" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y274" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AA274" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AD274" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE274" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG274" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT274" t="inlineStr"/>
+      <c r="AW274" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX274" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY274" t="inlineStr"/>
+    </row>
+    <row r="275">
+      <c r="A275" t="n">
+        <v>127785103</v>
+      </c>
+      <c r="B275" t="n">
+        <v>98450</v>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E275" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H275" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I275" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J275" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K275" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="P275" t="inlineStr">
+        <is>
+          <t>Pellkärret, Dlr</t>
+        </is>
+      </c>
+      <c r="Q275" t="n">
+        <v>564314</v>
+      </c>
+      <c r="R275" t="n">
+        <v>6705330</v>
+      </c>
+      <c r="S275" t="n">
+        <v>10</v>
+      </c>
+      <c r="T275" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U275" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V275" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W275" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y275" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AA275" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AC275" t="inlineStr">
+        <is>
+          <t>3 blomstjälkar</t>
+        </is>
+      </c>
+      <c r="AD275" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE275" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG275" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT275" t="inlineStr"/>
+      <c r="AW275" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX275" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY275" t="inlineStr"/>
+    </row>
+    <row r="276">
+      <c r="A276" t="n">
+        <v>127785106</v>
+      </c>
+      <c r="B276" t="n">
+        <v>98450</v>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E276" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H276" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I276" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J276" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P276" t="inlineStr">
+        <is>
+          <t>Pellkärret, Dlr</t>
+        </is>
+      </c>
+      <c r="Q276" t="n">
+        <v>564345</v>
+      </c>
+      <c r="R276" t="n">
+        <v>6705441</v>
+      </c>
+      <c r="S276" t="n">
+        <v>10</v>
+      </c>
+      <c r="T276" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U276" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V276" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W276" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y276" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AA276" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AD276" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE276" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG276" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT276" t="inlineStr"/>
+      <c r="AW276" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX276" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY276" t="inlineStr"/>
+    </row>
+    <row r="277">
+      <c r="A277" t="n">
+        <v>127785092</v>
+      </c>
+      <c r="B277" t="n">
+        <v>98450</v>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E277" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H277" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I277" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J277" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P277" t="inlineStr">
+        <is>
+          <t>Pellkärret, Dlr</t>
+        </is>
+      </c>
+      <c r="Q277" t="n">
+        <v>564390</v>
+      </c>
+      <c r="R277" t="n">
+        <v>6705389</v>
+      </c>
+      <c r="S277" t="n">
+        <v>10</v>
+      </c>
+      <c r="T277" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U277" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V277" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W277" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y277" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AA277" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AD277" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE277" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG277" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT277" t="inlineStr"/>
+      <c r="AW277" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX277" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY277" t="inlineStr"/>
+    </row>
+    <row r="278">
+      <c r="A278" t="n">
+        <v>127785093</v>
+      </c>
+      <c r="B278" t="n">
+        <v>98450</v>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E278" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H278" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I278" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J278" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P278" t="inlineStr">
+        <is>
+          <t>Pellkärret, Dlr</t>
+        </is>
+      </c>
+      <c r="Q278" t="n">
+        <v>564348</v>
+      </c>
+      <c r="R278" t="n">
+        <v>6705441</v>
+      </c>
+      <c r="S278" t="n">
+        <v>10</v>
+      </c>
+      <c r="T278" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U278" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V278" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W278" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y278" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AA278" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AD278" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE278" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG278" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT278" t="inlineStr"/>
+      <c r="AW278" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX278" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY278" t="inlineStr"/>
+    </row>
+    <row r="279">
+      <c r="A279" t="n">
+        <v>127785099</v>
+      </c>
+      <c r="B279" t="n">
+        <v>98450</v>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E279" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H279" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I279" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J279" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K279" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="P279" t="inlineStr">
+        <is>
+          <t>Pellkärret, Dlr</t>
+        </is>
+      </c>
+      <c r="Q279" t="n">
+        <v>564367</v>
+      </c>
+      <c r="R279" t="n">
+        <v>6705367</v>
+      </c>
+      <c r="S279" t="n">
+        <v>10</v>
+      </c>
+      <c r="T279" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U279" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V279" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W279" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y279" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AA279" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AC279" t="inlineStr">
+        <is>
+          <t>2 blomstjälkar</t>
+        </is>
+      </c>
+      <c r="AD279" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE279" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG279" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT279" t="inlineStr"/>
+      <c r="AW279" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX279" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY279" t="inlineStr"/>
+    </row>
+    <row r="280">
+      <c r="A280" t="n">
+        <v>127785090</v>
+      </c>
+      <c r="B280" t="n">
+        <v>57660</v>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E280" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H280" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I280" t="inlineStr"/>
+      <c r="M280" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P280" t="inlineStr">
+        <is>
+          <t>Pellkärret, Dlr</t>
+        </is>
+      </c>
+      <c r="Q280" t="n">
+        <v>564322</v>
+      </c>
+      <c r="R280" t="n">
+        <v>6705433</v>
+      </c>
+      <c r="S280" t="n">
+        <v>10</v>
+      </c>
+      <c r="T280" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U280" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V280" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W280" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y280" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AA280" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AD280" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE280" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG280" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT280" t="inlineStr"/>
+      <c r="AW280" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX280" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY280" t="inlineStr"/>
+    </row>
+    <row r="281">
+      <c r="A281" t="n">
+        <v>127785095</v>
+      </c>
+      <c r="B281" t="n">
+        <v>98450</v>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E281" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H281" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I281" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J281" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K281" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="P281" t="inlineStr">
+        <is>
+          <t>Pellkärret, Dlr</t>
+        </is>
+      </c>
+      <c r="Q281" t="n">
+        <v>564309</v>
+      </c>
+      <c r="R281" t="n">
+        <v>6705424</v>
+      </c>
+      <c r="S281" t="n">
+        <v>10</v>
+      </c>
+      <c r="T281" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U281" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V281" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W281" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y281" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AA281" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AC281" t="inlineStr">
+        <is>
+          <t>3 blomstjälkar</t>
+        </is>
+      </c>
+      <c r="AD281" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE281" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG281" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT281" t="inlineStr"/>
+      <c r="AW281" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX281" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY281" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 58548-2022 artfynd.xlsx
+++ b/artfynd/A 58548-2022 artfynd.xlsx
@@ -25139,10 +25139,10 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>127683144</v>
+        <v>127683156</v>
       </c>
       <c r="B223" t="n">
-        <v>91332</v>
+        <v>57660</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -25150,34 +25150,39 @@
         </is>
       </c>
       <c r="E223" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I223" t="inlineStr"/>
+      <c r="M223" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P223" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>563970</v>
+        <v>564124</v>
       </c>
       <c r="R223" t="n">
-        <v>6704986</v>
+        <v>6705171</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -25236,10 +25241,10 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>127683140</v>
+        <v>127683154</v>
       </c>
       <c r="B224" t="n">
-        <v>91332</v>
+        <v>57660</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -25247,34 +25252,39 @@
         </is>
       </c>
       <c r="E224" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I224" t="inlineStr"/>
+      <c r="M224" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P224" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>564253</v>
+        <v>564140</v>
       </c>
       <c r="R224" t="n">
-        <v>6705225</v>
+        <v>6705076</v>
       </c>
       <c r="S224" t="n">
         <v>10</v>
@@ -25333,10 +25343,10 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>127683166</v>
+        <v>127683193</v>
       </c>
       <c r="B225" t="n">
-        <v>97327</v>
+        <v>92656</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -25344,34 +25354,43 @@
         </is>
       </c>
       <c r="E225" t="n">
-        <v>221945</v>
+        <v>5964</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I225" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J225" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P225" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>563939</v>
+        <v>563883</v>
       </c>
       <c r="R225" t="n">
-        <v>6704940</v>
+        <v>6704908</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -25430,54 +25449,45 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>127683193</v>
+        <v>127683181</v>
       </c>
       <c r="B226" t="n">
-        <v>92656</v>
+        <v>91698</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E226" t="n">
-        <v>5964</v>
+        <v>2064</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Kilporing</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Skeletocutis kuehneri</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I226" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J226" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>A.David</t>
+        </is>
+      </c>
+      <c r="I226" t="inlineStr"/>
       <c r="P226" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>563883</v>
+        <v>564128</v>
       </c>
       <c r="R226" t="n">
-        <v>6704908</v>
+        <v>6705055</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -25510,6 +25520,11 @@
       <c r="AA226" t="inlineStr">
         <is>
           <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AC226" t="inlineStr">
+        <is>
+          <t>Kommer att mikroskoperas</t>
         </is>
       </c>
       <c r="AD226" t="b">
@@ -25536,10 +25551,10 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>127683181</v>
+        <v>127683140</v>
       </c>
       <c r="B227" t="n">
-        <v>91698</v>
+        <v>91332</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -25547,21 +25562,21 @@
         </is>
       </c>
       <c r="E227" t="n">
-        <v>2064</v>
+        <v>1202</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Kilporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Skeletocutis kuehneri</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>A.David</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I227" t="inlineStr"/>
@@ -25571,10 +25586,10 @@
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>564128</v>
+        <v>564253</v>
       </c>
       <c r="R227" t="n">
-        <v>6705055</v>
+        <v>6705225</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -25607,11 +25622,6 @@
       <c r="AA227" t="inlineStr">
         <is>
           <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="AC227" t="inlineStr">
-        <is>
-          <t>Kommer att mikroskoperas</t>
         </is>
       </c>
       <c r="AD227" t="b">
@@ -25638,10 +25648,10 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>127683156</v>
+        <v>127683144</v>
       </c>
       <c r="B228" t="n">
-        <v>57660</v>
+        <v>91332</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -25649,39 +25659,34 @@
         </is>
       </c>
       <c r="E228" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I228" t="inlineStr"/>
-      <c r="M228" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P228" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>564124</v>
+        <v>563970</v>
       </c>
       <c r="R228" t="n">
-        <v>6705171</v>
+        <v>6704986</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -25740,38 +25745,47 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>127683154</v>
+        <v>127683183</v>
       </c>
       <c r="B229" t="n">
-        <v>57660</v>
+        <v>98450</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E229" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I229" t="inlineStr"/>
-      <c r="M229" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J229" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P229" t="inlineStr">
@@ -25780,10 +25794,10 @@
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>564140</v>
+        <v>564023</v>
       </c>
       <c r="R229" t="n">
-        <v>6705076</v>
+        <v>6705072</v>
       </c>
       <c r="S229" t="n">
         <v>10</v>
@@ -25816,6 +25830,11 @@
       <c r="AA229" t="inlineStr">
         <is>
           <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AC229" t="inlineStr">
+        <is>
+          <t>2 blomstjälkar</t>
         </is>
       </c>
       <c r="AD229" t="b">
@@ -25842,59 +25861,45 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>127683183</v>
+        <v>127683166</v>
       </c>
       <c r="B230" t="n">
-        <v>98450</v>
+        <v>97327</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E230" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I230" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J230" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K230" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I230" t="inlineStr"/>
       <c r="P230" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>564023</v>
+        <v>563939</v>
       </c>
       <c r="R230" t="n">
-        <v>6705072</v>
+        <v>6704940</v>
       </c>
       <c r="S230" t="n">
         <v>10</v>
@@ -25927,11 +25932,6 @@
       <c r="AA230" t="inlineStr">
         <is>
           <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="AC230" t="inlineStr">
-        <is>
-          <t>2 blomstjälkar</t>
         </is>
       </c>
       <c r="AD230" t="b">
@@ -25958,32 +25958,32 @@
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>127683203</v>
+        <v>127683173</v>
       </c>
       <c r="B231" t="n">
-        <v>91733</v>
+        <v>95306</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E231" t="n">
-        <v>715</v>
+        <v>2387</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Finporing</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Gloeoporus pannocinctus</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>(Romell) J.Erikss.</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I231" t="inlineStr"/>
@@ -25993,10 +25993,10 @@
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>563955</v>
+        <v>563865</v>
       </c>
       <c r="R231" t="n">
-        <v>6704996</v>
+        <v>6704888</v>
       </c>
       <c r="S231" t="n">
         <v>10</v>
@@ -26029,6 +26029,11 @@
       <c r="AA231" t="inlineStr">
         <is>
           <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AC231" t="inlineStr">
+        <is>
+          <t>I källdråg utan planerad hänsyn</t>
         </is>
       </c>
       <c r="AD231" t="b">
@@ -26055,32 +26060,32 @@
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>127683173</v>
+        <v>127683203</v>
       </c>
       <c r="B232" t="n">
-        <v>95306</v>
+        <v>91733</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E232" t="n">
-        <v>2387</v>
+        <v>715</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Finporing</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Gloeoporus pannocinctus</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(Romell) J.Erikss.</t>
         </is>
       </c>
       <c r="I232" t="inlineStr"/>
@@ -26090,10 +26095,10 @@
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>563865</v>
+        <v>563955</v>
       </c>
       <c r="R232" t="n">
-        <v>6704888</v>
+        <v>6704996</v>
       </c>
       <c r="S232" t="n">
         <v>10</v>
@@ -26126,11 +26131,6 @@
       <c r="AA232" t="inlineStr">
         <is>
           <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="AC232" t="inlineStr">
-        <is>
-          <t>I källdråg utan planerad hänsyn</t>
         </is>
       </c>
       <c r="AD232" t="b">
@@ -26458,10 +26458,10 @@
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>127683152</v>
+        <v>127683163</v>
       </c>
       <c r="B236" t="n">
-        <v>92267</v>
+        <v>91104</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -26469,43 +26469,34 @@
         </is>
       </c>
       <c r="E236" t="n">
-        <v>4769</v>
+        <v>3215</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I236" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J236" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I236" t="inlineStr"/>
       <c r="P236" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>563895</v>
+        <v>564121</v>
       </c>
       <c r="R236" t="n">
-        <v>6704903</v>
+        <v>6705165</v>
       </c>
       <c r="S236" t="n">
         <v>10</v>
@@ -26538,6 +26529,11 @@
       <c r="AA236" t="inlineStr">
         <is>
           <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AC236" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD236" t="b">
@@ -26564,10 +26560,10 @@
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>127683163</v>
+        <v>127683152</v>
       </c>
       <c r="B237" t="n">
-        <v>91104</v>
+        <v>92267</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -26575,34 +26571,43 @@
         </is>
       </c>
       <c r="E237" t="n">
-        <v>3215</v>
+        <v>4769</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I237" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I237" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J237" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P237" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>564121</v>
+        <v>563895</v>
       </c>
       <c r="R237" t="n">
-        <v>6705165</v>
+        <v>6704903</v>
       </c>
       <c r="S237" t="n">
         <v>10</v>
@@ -26635,11 +26640,6 @@
       <c r="AA237" t="inlineStr">
         <is>
           <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="AC237" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD237" t="b">
@@ -26777,54 +26777,45 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>127683196</v>
+        <v>127683138</v>
       </c>
       <c r="B239" t="n">
-        <v>92656</v>
+        <v>91690</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E239" t="n">
-        <v>5964</v>
+        <v>2062</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I239" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J239" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I239" t="inlineStr"/>
       <c r="P239" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>564163</v>
+        <v>564145</v>
       </c>
       <c r="R239" t="n">
-        <v>6705180</v>
+        <v>6705081</v>
       </c>
       <c r="S239" t="n">
         <v>10</v>
@@ -26883,45 +26874,54 @@
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>127683138</v>
+        <v>127683196</v>
       </c>
       <c r="B240" t="n">
-        <v>91690</v>
+        <v>92656</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E240" t="n">
-        <v>2062</v>
+        <v>5964</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I240" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I240" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J240" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P240" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>564145</v>
+        <v>564163</v>
       </c>
       <c r="R240" t="n">
-        <v>6705081</v>
+        <v>6705180</v>
       </c>
       <c r="S240" t="n">
         <v>10</v>
@@ -27188,45 +27188,50 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>127683162</v>
+        <v>127683149</v>
       </c>
       <c r="B243" t="n">
-        <v>95694</v>
+        <v>57823</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E243" t="n">
-        <v>2813</v>
+        <v>103021</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I243" t="inlineStr"/>
+      <c r="M243" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P243" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>563934</v>
+        <v>564082</v>
       </c>
       <c r="R243" t="n">
-        <v>6704860</v>
+        <v>6705145</v>
       </c>
       <c r="S243" t="n">
         <v>10</v>
@@ -27285,50 +27290,45 @@
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>127683149</v>
+        <v>127683162</v>
       </c>
       <c r="B244" t="n">
-        <v>57823</v>
+        <v>95694</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E244" t="n">
-        <v>103021</v>
+        <v>2813</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I244" t="inlineStr"/>
-      <c r="M244" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P244" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q244" t="n">
-        <v>564082</v>
+        <v>563934</v>
       </c>
       <c r="R244" t="n">
-        <v>6705145</v>
+        <v>6704860</v>
       </c>
       <c r="S244" t="n">
         <v>10</v>
@@ -28002,32 +28002,32 @@
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>127683200</v>
+        <v>127683139</v>
       </c>
       <c r="B251" t="n">
-        <v>100632</v>
+        <v>91690</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E251" t="n">
-        <v>222498</v>
+        <v>2062</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I251" t="inlineStr"/>
@@ -28037,10 +28037,10 @@
         </is>
       </c>
       <c r="Q251" t="n">
-        <v>563890</v>
+        <v>563999</v>
       </c>
       <c r="R251" t="n">
-        <v>6704897</v>
+        <v>6705007</v>
       </c>
       <c r="S251" t="n">
         <v>10</v>
@@ -28099,32 +28099,32 @@
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>127683139</v>
+        <v>127683199</v>
       </c>
       <c r="B252" t="n">
-        <v>91690</v>
+        <v>95301</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E252" t="n">
-        <v>2062</v>
+        <v>2383</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Bågpraktmossa</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Plagiomnium medium</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Bruch &amp; Schimp.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I252" t="inlineStr"/>
@@ -28134,10 +28134,10 @@
         </is>
       </c>
       <c r="Q252" t="n">
-        <v>563999</v>
+        <v>564058</v>
       </c>
       <c r="R252" t="n">
-        <v>6705007</v>
+        <v>6705124</v>
       </c>
       <c r="S252" t="n">
         <v>10</v>
@@ -28170,6 +28170,11 @@
       <c r="AA252" t="inlineStr">
         <is>
           <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AC252" t="inlineStr">
+        <is>
+          <t>i översinlningsområde utanför hänsyn</t>
         </is>
       </c>
       <c r="AD252" t="b">
@@ -28196,10 +28201,10 @@
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>127683199</v>
+        <v>127683200</v>
       </c>
       <c r="B253" t="n">
-        <v>95301</v>
+        <v>100632</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -28207,21 +28212,21 @@
         </is>
       </c>
       <c r="E253" t="n">
-        <v>2383</v>
+        <v>222498</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Bågpraktmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Plagiomnium medium</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>(Bruch &amp; Schimp.) T.J.Kop.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I253" t="inlineStr"/>
@@ -28231,10 +28236,10 @@
         </is>
       </c>
       <c r="Q253" t="n">
-        <v>564058</v>
+        <v>563890</v>
       </c>
       <c r="R253" t="n">
-        <v>6705124</v>
+        <v>6704897</v>
       </c>
       <c r="S253" t="n">
         <v>10</v>
@@ -28267,11 +28272,6 @@
       <c r="AA253" t="inlineStr">
         <is>
           <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="AC253" t="inlineStr">
-        <is>
-          <t>i översinlningsområde utanför hänsyn</t>
         </is>
       </c>
       <c r="AD253" t="b">
@@ -28395,10 +28395,10 @@
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>127683142</v>
+        <v>127683155</v>
       </c>
       <c r="B255" t="n">
-        <v>91332</v>
+        <v>57660</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -28406,34 +28406,39 @@
         </is>
       </c>
       <c r="E255" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I255" t="inlineStr"/>
+      <c r="M255" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P255" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q255" t="n">
-        <v>564128</v>
+        <v>564144</v>
       </c>
       <c r="R255" t="n">
-        <v>6705064</v>
+        <v>6705112</v>
       </c>
       <c r="S255" t="n">
         <v>10</v>
@@ -28492,10 +28497,10 @@
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>127683155</v>
+        <v>127683142</v>
       </c>
       <c r="B256" t="n">
-        <v>57660</v>
+        <v>91332</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -28503,39 +28508,34 @@
         </is>
       </c>
       <c r="E256" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I256" t="inlineStr"/>
-      <c r="M256" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P256" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q256" t="n">
-        <v>564144</v>
+        <v>564128</v>
       </c>
       <c r="R256" t="n">
-        <v>6705112</v>
+        <v>6705064</v>
       </c>
       <c r="S256" t="n">
         <v>10</v>
@@ -28691,45 +28691,50 @@
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>127683164</v>
+        <v>127683157</v>
       </c>
       <c r="B258" t="n">
-        <v>91104</v>
+        <v>57660</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E258" t="n">
-        <v>3215</v>
+        <v>100049</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I258" t="inlineStr"/>
+      <c r="M258" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P258" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q258" t="n">
-        <v>564133</v>
+        <v>564052</v>
       </c>
       <c r="R258" t="n">
-        <v>6705173</v>
+        <v>6705031</v>
       </c>
       <c r="S258" t="n">
         <v>10</v>
@@ -28788,45 +28793,50 @@
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>127683133</v>
+        <v>127683158</v>
       </c>
       <c r="B259" t="n">
-        <v>91297</v>
+        <v>57660</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E259" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I259" t="inlineStr"/>
+      <c r="M259" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P259" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q259" t="n">
-        <v>564052</v>
+        <v>563970</v>
       </c>
       <c r="R259" t="n">
-        <v>6705031</v>
+        <v>6704954</v>
       </c>
       <c r="S259" t="n">
         <v>10</v>
@@ -28885,50 +28895,45 @@
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>127683157</v>
+        <v>127683164</v>
       </c>
       <c r="B260" t="n">
-        <v>57660</v>
+        <v>91104</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E260" t="n">
-        <v>100049</v>
+        <v>3215</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I260" t="inlineStr"/>
-      <c r="M260" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P260" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q260" t="n">
-        <v>564052</v>
+        <v>564133</v>
       </c>
       <c r="R260" t="n">
-        <v>6705031</v>
+        <v>6705173</v>
       </c>
       <c r="S260" t="n">
         <v>10</v>
@@ -28987,50 +28992,45 @@
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>127683158</v>
+        <v>127683133</v>
       </c>
       <c r="B261" t="n">
-        <v>57660</v>
+        <v>91297</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E261" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I261" t="inlineStr"/>
-      <c r="M261" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P261" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q261" t="n">
-        <v>563970</v>
+        <v>564052</v>
       </c>
       <c r="R261" t="n">
-        <v>6704954</v>
+        <v>6705031</v>
       </c>
       <c r="S261" t="n">
         <v>10</v>
@@ -29089,59 +29089,45 @@
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>127683187</v>
+        <v>127683172</v>
       </c>
       <c r="B262" t="n">
-        <v>98450</v>
+        <v>95306</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E262" t="n">
-        <v>220787</v>
+        <v>2387</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I262" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J262" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K262" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Huebener) T.J.Kop.</t>
+        </is>
+      </c>
+      <c r="I262" t="inlineStr"/>
       <c r="P262" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q262" t="n">
-        <v>564215</v>
+        <v>563914</v>
       </c>
       <c r="R262" t="n">
-        <v>6705203</v>
+        <v>6704945</v>
       </c>
       <c r="S262" t="n">
         <v>10</v>
@@ -29174,6 +29160,11 @@
       <c r="AA262" t="inlineStr">
         <is>
           <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AC262" t="inlineStr">
+        <is>
+          <t>I källdråg utan planerad hänsyn</t>
         </is>
       </c>
       <c r="AD262" t="b">
@@ -29200,10 +29191,10 @@
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>127683130</v>
+        <v>127683187</v>
       </c>
       <c r="B263" t="n">
-        <v>91544</v>
+        <v>98450</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -29211,34 +29202,48 @@
         </is>
       </c>
       <c r="E263" t="n">
-        <v>1106</v>
+        <v>220787</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
-        </is>
-      </c>
-      <c r="I263" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I263" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J263" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K263" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P263" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q263" t="n">
-        <v>564057</v>
+        <v>564215</v>
       </c>
       <c r="R263" t="n">
-        <v>6705032</v>
+        <v>6705203</v>
       </c>
       <c r="S263" t="n">
         <v>10</v>
@@ -29297,32 +29302,32 @@
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>127683172</v>
+        <v>127683130</v>
       </c>
       <c r="B264" t="n">
-        <v>95306</v>
+        <v>91544</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E264" t="n">
-        <v>2387</v>
+        <v>1106</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I264" t="inlineStr"/>
@@ -29332,10 +29337,10 @@
         </is>
       </c>
       <c r="Q264" t="n">
-        <v>563914</v>
+        <v>564057</v>
       </c>
       <c r="R264" t="n">
-        <v>6704945</v>
+        <v>6705032</v>
       </c>
       <c r="S264" t="n">
         <v>10</v>
@@ -29368,11 +29373,6 @@
       <c r="AA264" t="inlineStr">
         <is>
           <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="AC264" t="inlineStr">
-        <is>
-          <t>I källdråg utan planerad hänsyn</t>
         </is>
       </c>
       <c r="AD264" t="b">
@@ -29496,7 +29496,7 @@
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>127785100</v>
+        <v>127785097</v>
       </c>
       <c r="B266" t="n">
         <v>98450</v>
@@ -29526,7 +29526,7 @@
       </c>
       <c r="I266" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J266" t="inlineStr">
@@ -29540,10 +29540,10 @@
         </is>
       </c>
       <c r="Q266" t="n">
-        <v>564391</v>
+        <v>564343</v>
       </c>
       <c r="R266" t="n">
-        <v>6705389</v>
+        <v>6705352</v>
       </c>
       <c r="S266" t="n">
         <v>10</v>
@@ -29602,7 +29602,7 @@
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>127785097</v>
+        <v>127785100</v>
       </c>
       <c r="B267" t="n">
         <v>98450</v>
@@ -29632,7 +29632,7 @@
       </c>
       <c r="I267" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J267" t="inlineStr">
@@ -29646,10 +29646,10 @@
         </is>
       </c>
       <c r="Q267" t="n">
-        <v>564343</v>
+        <v>564391</v>
       </c>
       <c r="R267" t="n">
-        <v>6705352</v>
+        <v>6705389</v>
       </c>
       <c r="S267" t="n">
         <v>10</v>
@@ -30114,10 +30114,10 @@
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>127785089</v>
+        <v>127785091</v>
       </c>
       <c r="B272" t="n">
-        <v>57823</v>
+        <v>91628</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -30125,21 +30125,21 @@
         </is>
       </c>
       <c r="E272" t="n">
-        <v>103021</v>
+        <v>658</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I272" t="inlineStr"/>
@@ -30149,10 +30149,10 @@
         </is>
       </c>
       <c r="Q272" t="n">
-        <v>564303</v>
+        <v>564349</v>
       </c>
       <c r="R272" t="n">
-        <v>6705322</v>
+        <v>6705423</v>
       </c>
       <c r="S272" t="n">
         <v>10</v>
@@ -30211,59 +30211,45 @@
     </row>
     <row r="273">
       <c r="A273" t="n">
-        <v>127785096</v>
+        <v>127785089</v>
       </c>
       <c r="B273" t="n">
-        <v>98450</v>
+        <v>57823</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E273" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I273" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J273" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K273" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I273" t="inlineStr"/>
       <c r="P273" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q273" t="n">
-        <v>564308</v>
+        <v>564303</v>
       </c>
       <c r="R273" t="n">
-        <v>6705320</v>
+        <v>6705322</v>
       </c>
       <c r="S273" t="n">
         <v>10</v>
@@ -30296,11 +30282,6 @@
       <c r="AA273" t="inlineStr">
         <is>
           <t>2025-08-24</t>
-        </is>
-      </c>
-      <c r="AC273" t="inlineStr">
-        <is>
-          <t>2 blomstjälkar</t>
         </is>
       </c>
       <c r="AD273" t="b">
@@ -30327,45 +30308,59 @@
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>127785091</v>
+        <v>127785096</v>
       </c>
       <c r="B274" t="n">
-        <v>91628</v>
+        <v>98450</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E274" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I274" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I274" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J274" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K274" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P274" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q274" t="n">
-        <v>564349</v>
+        <v>564308</v>
       </c>
       <c r="R274" t="n">
-        <v>6705423</v>
+        <v>6705320</v>
       </c>
       <c r="S274" t="n">
         <v>10</v>
@@ -30398,6 +30393,11 @@
       <c r="AA274" t="inlineStr">
         <is>
           <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AC274" t="inlineStr">
+        <is>
+          <t>2 blomstjälkar</t>
         </is>
       </c>
       <c r="AD274" t="b">
@@ -30858,47 +30858,38 @@
     </row>
     <row r="279">
       <c r="A279" t="n">
-        <v>127785099</v>
+        <v>127785090</v>
       </c>
       <c r="B279" t="n">
-        <v>98450</v>
+        <v>57660</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E279" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I279" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J279" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K279" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I279" t="inlineStr"/>
+      <c r="M279" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P279" t="inlineStr">
@@ -30907,10 +30898,10 @@
         </is>
       </c>
       <c r="Q279" t="n">
-        <v>564367</v>
+        <v>564322</v>
       </c>
       <c r="R279" t="n">
-        <v>6705367</v>
+        <v>6705433</v>
       </c>
       <c r="S279" t="n">
         <v>10</v>
@@ -30943,11 +30934,6 @@
       <c r="AA279" t="inlineStr">
         <is>
           <t>2025-08-24</t>
-        </is>
-      </c>
-      <c r="AC279" t="inlineStr">
-        <is>
-          <t>2 blomstjälkar</t>
         </is>
       </c>
       <c r="AD279" t="b">
@@ -30974,38 +30960,47 @@
     </row>
     <row r="280">
       <c r="A280" t="n">
-        <v>127785090</v>
+        <v>127785099</v>
       </c>
       <c r="B280" t="n">
-        <v>57660</v>
+        <v>98450</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E280" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I280" t="inlineStr"/>
-      <c r="M280" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I280" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J280" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K280" t="inlineStr">
+        <is>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P280" t="inlineStr">
@@ -31014,10 +31009,10 @@
         </is>
       </c>
       <c r="Q280" t="n">
-        <v>564322</v>
+        <v>564367</v>
       </c>
       <c r="R280" t="n">
-        <v>6705433</v>
+        <v>6705367</v>
       </c>
       <c r="S280" t="n">
         <v>10</v>
@@ -31050,6 +31045,11 @@
       <c r="AA280" t="inlineStr">
         <is>
           <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AC280" t="inlineStr">
+        <is>
+          <t>2 blomstjälkar</t>
         </is>
       </c>
       <c r="AD280" t="b">

--- a/artfynd/A 58548-2022 artfynd.xlsx
+++ b/artfynd/A 58548-2022 artfynd.xlsx
@@ -25139,10 +25139,10 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>127683156</v>
+        <v>127683181</v>
       </c>
       <c r="B223" t="n">
-        <v>57660</v>
+        <v>91704</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -25150,39 +25150,34 @@
         </is>
       </c>
       <c r="E223" t="n">
-        <v>100049</v>
+        <v>2064</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kilporing</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Skeletocutis kuehneri</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>A.David</t>
         </is>
       </c>
       <c r="I223" t="inlineStr"/>
-      <c r="M223" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P223" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>564124</v>
+        <v>564128</v>
       </c>
       <c r="R223" t="n">
-        <v>6705171</v>
+        <v>6705055</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -25215,6 +25210,11 @@
       <c r="AA223" t="inlineStr">
         <is>
           <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AC223" t="inlineStr">
+        <is>
+          <t>Kommer att mikroskoperas</t>
         </is>
       </c>
       <c r="AD223" t="b">
@@ -25241,38 +25241,42 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>127683154</v>
+        <v>127683193</v>
       </c>
       <c r="B224" t="n">
-        <v>57660</v>
+        <v>92662</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E224" t="n">
-        <v>100049</v>
+        <v>5964</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I224" t="inlineStr"/>
-      <c r="M224" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I224" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J224" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P224" t="inlineStr">
@@ -25281,10 +25285,10 @@
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>564140</v>
+        <v>563883</v>
       </c>
       <c r="R224" t="n">
-        <v>6705076</v>
+        <v>6704908</v>
       </c>
       <c r="S224" t="n">
         <v>10</v>
@@ -25343,42 +25347,38 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>127683193</v>
+        <v>127683156</v>
       </c>
       <c r="B225" t="n">
-        <v>92656</v>
+        <v>57660</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E225" t="n">
-        <v>5964</v>
+        <v>100049</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I225" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J225" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I225" t="inlineStr"/>
+      <c r="M225" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P225" t="inlineStr">
@@ -25387,10 +25387,10 @@
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>563883</v>
+        <v>564124</v>
       </c>
       <c r="R225" t="n">
-        <v>6704908</v>
+        <v>6705171</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -25449,10 +25449,10 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>127683181</v>
+        <v>127683154</v>
       </c>
       <c r="B226" t="n">
-        <v>91698</v>
+        <v>57660</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -25460,34 +25460,39 @@
         </is>
       </c>
       <c r="E226" t="n">
-        <v>2064</v>
+        <v>100049</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Kilporing</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Skeletocutis kuehneri</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>A.David</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I226" t="inlineStr"/>
+      <c r="M226" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P226" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>564128</v>
+        <v>564140</v>
       </c>
       <c r="R226" t="n">
-        <v>6705055</v>
+        <v>6705076</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -25520,11 +25525,6 @@
       <c r="AA226" t="inlineStr">
         <is>
           <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="AC226" t="inlineStr">
-        <is>
-          <t>Kommer att mikroskoperas</t>
         </is>
       </c>
       <c r="AD226" t="b">
@@ -25551,10 +25551,10 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>127683140</v>
+        <v>127683144</v>
       </c>
       <c r="B227" t="n">
-        <v>91332</v>
+        <v>91338</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>564253</v>
+        <v>563970</v>
       </c>
       <c r="R227" t="n">
-        <v>6705225</v>
+        <v>6704986</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -25648,10 +25648,10 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>127683144</v>
+        <v>127683140</v>
       </c>
       <c r="B228" t="n">
-        <v>91332</v>
+        <v>91338</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -25683,10 +25683,10 @@
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>563970</v>
+        <v>564253</v>
       </c>
       <c r="R228" t="n">
-        <v>6704986</v>
+        <v>6705225</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -25748,7 +25748,7 @@
         <v>127683183</v>
       </c>
       <c r="B229" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -25864,7 +25864,7 @@
         <v>127683166</v>
       </c>
       <c r="B230" t="n">
-        <v>97327</v>
+        <v>97333</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -25958,32 +25958,32 @@
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>127683173</v>
+        <v>127683203</v>
       </c>
       <c r="B231" t="n">
-        <v>95306</v>
+        <v>91739</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E231" t="n">
-        <v>2387</v>
+        <v>715</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Finporing</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Gloeoporus pannocinctus</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(Romell) J.Erikss.</t>
         </is>
       </c>
       <c r="I231" t="inlineStr"/>
@@ -25993,10 +25993,10 @@
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>563865</v>
+        <v>563955</v>
       </c>
       <c r="R231" t="n">
-        <v>6704888</v>
+        <v>6704996</v>
       </c>
       <c r="S231" t="n">
         <v>10</v>
@@ -26029,11 +26029,6 @@
       <c r="AA231" t="inlineStr">
         <is>
           <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="AC231" t="inlineStr">
-        <is>
-          <t>I källdråg utan planerad hänsyn</t>
         </is>
       </c>
       <c r="AD231" t="b">
@@ -26060,32 +26055,32 @@
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>127683203</v>
+        <v>127683173</v>
       </c>
       <c r="B232" t="n">
-        <v>91733</v>
+        <v>95312</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E232" t="n">
-        <v>715</v>
+        <v>2387</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Finporing</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Gloeoporus pannocinctus</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>(Romell) J.Erikss.</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I232" t="inlineStr"/>
@@ -26095,10 +26090,10 @@
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>563955</v>
+        <v>563865</v>
       </c>
       <c r="R232" t="n">
-        <v>6704996</v>
+        <v>6704888</v>
       </c>
       <c r="S232" t="n">
         <v>10</v>
@@ -26131,6 +26126,11 @@
       <c r="AA232" t="inlineStr">
         <is>
           <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AC232" t="inlineStr">
+        <is>
+          <t>I källdråg utan planerad hänsyn</t>
         </is>
       </c>
       <c r="AD232" t="b">
@@ -26262,7 +26262,7 @@
         <v>127683159</v>
       </c>
       <c r="B234" t="n">
-        <v>92234</v>
+        <v>92240</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -26458,10 +26458,10 @@
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>127683163</v>
+        <v>127683152</v>
       </c>
       <c r="B236" t="n">
-        <v>91104</v>
+        <v>92273</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -26469,34 +26469,43 @@
         </is>
       </c>
       <c r="E236" t="n">
-        <v>3215</v>
+        <v>4769</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I236" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I236" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J236" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P236" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>564121</v>
+        <v>563895</v>
       </c>
       <c r="R236" t="n">
-        <v>6705165</v>
+        <v>6704903</v>
       </c>
       <c r="S236" t="n">
         <v>10</v>
@@ -26529,11 +26538,6 @@
       <c r="AA236" t="inlineStr">
         <is>
           <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="AC236" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD236" t="b">
@@ -26560,10 +26564,10 @@
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>127683152</v>
+        <v>127683163</v>
       </c>
       <c r="B237" t="n">
-        <v>92267</v>
+        <v>91110</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -26571,43 +26575,34 @@
         </is>
       </c>
       <c r="E237" t="n">
-        <v>4769</v>
+        <v>3215</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I237" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J237" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I237" t="inlineStr"/>
       <c r="P237" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>563895</v>
+        <v>564121</v>
       </c>
       <c r="R237" t="n">
-        <v>6704903</v>
+        <v>6705165</v>
       </c>
       <c r="S237" t="n">
         <v>10</v>
@@ -26640,6 +26635,11 @@
       <c r="AA237" t="inlineStr">
         <is>
           <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AC237" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD237" t="b">
@@ -26669,7 +26669,7 @@
         <v>127683188</v>
       </c>
       <c r="B238" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -26777,45 +26777,54 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>127683138</v>
+        <v>127683196</v>
       </c>
       <c r="B239" t="n">
-        <v>91690</v>
+        <v>92662</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E239" t="n">
-        <v>2062</v>
+        <v>5964</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I239" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I239" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J239" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P239" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>564145</v>
+        <v>564163</v>
       </c>
       <c r="R239" t="n">
-        <v>6705081</v>
+        <v>6705180</v>
       </c>
       <c r="S239" t="n">
         <v>10</v>
@@ -26874,54 +26883,45 @@
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>127683196</v>
+        <v>127683138</v>
       </c>
       <c r="B240" t="n">
-        <v>92656</v>
+        <v>91696</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E240" t="n">
-        <v>5964</v>
+        <v>2062</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I240" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J240" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I240" t="inlineStr"/>
       <c r="P240" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>564163</v>
+        <v>564145</v>
       </c>
       <c r="R240" t="n">
-        <v>6705180</v>
+        <v>6705081</v>
       </c>
       <c r="S240" t="n">
         <v>10</v>
@@ -26983,7 +26983,7 @@
         <v>127683185</v>
       </c>
       <c r="B241" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -27293,7 +27293,7 @@
         <v>127683162</v>
       </c>
       <c r="B244" t="n">
-        <v>95694</v>
+        <v>95700</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -27390,7 +27390,7 @@
         <v>127683195</v>
       </c>
       <c r="B245" t="n">
-        <v>92656</v>
+        <v>92662</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -27496,7 +27496,7 @@
         <v>127683135</v>
       </c>
       <c r="B246" t="n">
-        <v>91297</v>
+        <v>91303</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -27593,7 +27593,7 @@
         <v>127683184</v>
       </c>
       <c r="B247" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -27709,7 +27709,7 @@
         <v>127683137</v>
       </c>
       <c r="B248" t="n">
-        <v>91690</v>
+        <v>91696</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -27806,7 +27806,7 @@
         <v>127683141</v>
       </c>
       <c r="B249" t="n">
-        <v>91332</v>
+        <v>91338</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -27903,7 +27903,7 @@
         <v>127683151</v>
       </c>
       <c r="B250" t="n">
-        <v>92267</v>
+        <v>92273</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -28002,32 +28002,32 @@
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>127683139</v>
+        <v>127683199</v>
       </c>
       <c r="B251" t="n">
-        <v>91690</v>
+        <v>95307</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E251" t="n">
-        <v>2062</v>
+        <v>2383</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Bågpraktmossa</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Plagiomnium medium</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Bruch &amp; Schimp.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I251" t="inlineStr"/>
@@ -28037,10 +28037,10 @@
         </is>
       </c>
       <c r="Q251" t="n">
-        <v>563999</v>
+        <v>564058</v>
       </c>
       <c r="R251" t="n">
-        <v>6705007</v>
+        <v>6705124</v>
       </c>
       <c r="S251" t="n">
         <v>10</v>
@@ -28073,6 +28073,11 @@
       <c r="AA251" t="inlineStr">
         <is>
           <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AC251" t="inlineStr">
+        <is>
+          <t>i översinlningsområde utanför hänsyn</t>
         </is>
       </c>
       <c r="AD251" t="b">
@@ -28099,10 +28104,10 @@
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>127683199</v>
+        <v>127683200</v>
       </c>
       <c r="B252" t="n">
-        <v>95301</v>
+        <v>100638</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -28110,21 +28115,21 @@
         </is>
       </c>
       <c r="E252" t="n">
-        <v>2383</v>
+        <v>222498</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Bågpraktmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>Plagiomnium medium</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>(Bruch &amp; Schimp.) T.J.Kop.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I252" t="inlineStr"/>
@@ -28134,10 +28139,10 @@
         </is>
       </c>
       <c r="Q252" t="n">
-        <v>564058</v>
+        <v>563890</v>
       </c>
       <c r="R252" t="n">
-        <v>6705124</v>
+        <v>6704897</v>
       </c>
       <c r="S252" t="n">
         <v>10</v>
@@ -28170,11 +28175,6 @@
       <c r="AA252" t="inlineStr">
         <is>
           <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="AC252" t="inlineStr">
-        <is>
-          <t>i översinlningsområde utanför hänsyn</t>
         </is>
       </c>
       <c r="AD252" t="b">
@@ -28201,32 +28201,32 @@
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>127683200</v>
+        <v>127683139</v>
       </c>
       <c r="B253" t="n">
-        <v>100632</v>
+        <v>91696</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E253" t="n">
-        <v>222498</v>
+        <v>2062</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I253" t="inlineStr"/>
@@ -28236,10 +28236,10 @@
         </is>
       </c>
       <c r="Q253" t="n">
-        <v>563890</v>
+        <v>563999</v>
       </c>
       <c r="R253" t="n">
-        <v>6704897</v>
+        <v>6705007</v>
       </c>
       <c r="S253" t="n">
         <v>10</v>
@@ -28301,7 +28301,7 @@
         <v>127683145</v>
       </c>
       <c r="B254" t="n">
-        <v>91332</v>
+        <v>91338</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -28395,10 +28395,10 @@
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>127683155</v>
+        <v>127683142</v>
       </c>
       <c r="B255" t="n">
-        <v>57660</v>
+        <v>91338</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -28406,39 +28406,34 @@
         </is>
       </c>
       <c r="E255" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I255" t="inlineStr"/>
-      <c r="M255" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P255" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q255" t="n">
-        <v>564144</v>
+        <v>564128</v>
       </c>
       <c r="R255" t="n">
-        <v>6705112</v>
+        <v>6705064</v>
       </c>
       <c r="S255" t="n">
         <v>10</v>
@@ -28497,10 +28492,10 @@
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>127683142</v>
+        <v>127683155</v>
       </c>
       <c r="B256" t="n">
-        <v>91332</v>
+        <v>57660</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -28508,34 +28503,39 @@
         </is>
       </c>
       <c r="E256" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I256" t="inlineStr"/>
+      <c r="M256" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P256" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q256" t="n">
-        <v>564128</v>
+        <v>564144</v>
       </c>
       <c r="R256" t="n">
-        <v>6705064</v>
+        <v>6705112</v>
       </c>
       <c r="S256" t="n">
         <v>10</v>
@@ -28597,7 +28597,7 @@
         <v>127683201</v>
       </c>
       <c r="B257" t="n">
-        <v>100632</v>
+        <v>100638</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -28691,50 +28691,45 @@
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>127683157</v>
+        <v>127683164</v>
       </c>
       <c r="B258" t="n">
-        <v>57660</v>
+        <v>91110</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E258" t="n">
-        <v>100049</v>
+        <v>3215</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I258" t="inlineStr"/>
-      <c r="M258" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P258" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q258" t="n">
-        <v>564052</v>
+        <v>564133</v>
       </c>
       <c r="R258" t="n">
-        <v>6705031</v>
+        <v>6705173</v>
       </c>
       <c r="S258" t="n">
         <v>10</v>
@@ -28793,50 +28788,45 @@
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>127683158</v>
+        <v>127683133</v>
       </c>
       <c r="B259" t="n">
-        <v>57660</v>
+        <v>91303</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E259" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I259" t="inlineStr"/>
-      <c r="M259" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P259" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q259" t="n">
-        <v>563970</v>
+        <v>564052</v>
       </c>
       <c r="R259" t="n">
-        <v>6704954</v>
+        <v>6705031</v>
       </c>
       <c r="S259" t="n">
         <v>10</v>
@@ -28895,45 +28885,50 @@
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>127683164</v>
+        <v>127683157</v>
       </c>
       <c r="B260" t="n">
-        <v>91104</v>
+        <v>57660</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E260" t="n">
-        <v>3215</v>
+        <v>100049</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I260" t="inlineStr"/>
+      <c r="M260" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P260" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q260" t="n">
-        <v>564133</v>
+        <v>564052</v>
       </c>
       <c r="R260" t="n">
-        <v>6705173</v>
+        <v>6705031</v>
       </c>
       <c r="S260" t="n">
         <v>10</v>
@@ -28992,45 +28987,50 @@
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>127683133</v>
+        <v>127683158</v>
       </c>
       <c r="B261" t="n">
-        <v>91297</v>
+        <v>57660</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E261" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I261" t="inlineStr"/>
+      <c r="M261" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P261" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q261" t="n">
-        <v>564052</v>
+        <v>563970</v>
       </c>
       <c r="R261" t="n">
-        <v>6705031</v>
+        <v>6704954</v>
       </c>
       <c r="S261" t="n">
         <v>10</v>
@@ -29089,32 +29089,32 @@
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>127683172</v>
+        <v>127683130</v>
       </c>
       <c r="B262" t="n">
-        <v>95306</v>
+        <v>91550</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E262" t="n">
-        <v>2387</v>
+        <v>1106</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I262" t="inlineStr"/>
@@ -29124,10 +29124,10 @@
         </is>
       </c>
       <c r="Q262" t="n">
-        <v>563914</v>
+        <v>564057</v>
       </c>
       <c r="R262" t="n">
-        <v>6704945</v>
+        <v>6705032</v>
       </c>
       <c r="S262" t="n">
         <v>10</v>
@@ -29160,11 +29160,6 @@
       <c r="AA262" t="inlineStr">
         <is>
           <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="AC262" t="inlineStr">
-        <is>
-          <t>I källdråg utan planerad hänsyn</t>
         </is>
       </c>
       <c r="AD262" t="b">
@@ -29191,59 +29186,45 @@
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>127683187</v>
+        <v>127683172</v>
       </c>
       <c r="B263" t="n">
-        <v>98450</v>
+        <v>95312</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E263" t="n">
-        <v>220787</v>
+        <v>2387</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I263" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J263" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K263" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Huebener) T.J.Kop.</t>
+        </is>
+      </c>
+      <c r="I263" t="inlineStr"/>
       <c r="P263" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q263" t="n">
-        <v>564215</v>
+        <v>563914</v>
       </c>
       <c r="R263" t="n">
-        <v>6705203</v>
+        <v>6704945</v>
       </c>
       <c r="S263" t="n">
         <v>10</v>
@@ -29276,6 +29257,11 @@
       <c r="AA263" t="inlineStr">
         <is>
           <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AC263" t="inlineStr">
+        <is>
+          <t>I källdråg utan planerad hänsyn</t>
         </is>
       </c>
       <c r="AD263" t="b">
@@ -29302,10 +29288,10 @@
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>127683130</v>
+        <v>127683187</v>
       </c>
       <c r="B264" t="n">
-        <v>91544</v>
+        <v>98456</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -29313,34 +29299,48 @@
         </is>
       </c>
       <c r="E264" t="n">
-        <v>1106</v>
+        <v>220787</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
-        </is>
-      </c>
-      <c r="I264" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I264" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J264" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K264" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P264" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q264" t="n">
-        <v>564057</v>
+        <v>564215</v>
       </c>
       <c r="R264" t="n">
-        <v>6705032</v>
+        <v>6705203</v>
       </c>
       <c r="S264" t="n">
         <v>10</v>
@@ -29402,7 +29402,7 @@
         <v>127683165</v>
       </c>
       <c r="B265" t="n">
-        <v>91954</v>
+        <v>91960</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -29499,7 +29499,7 @@
         <v>127785097</v>
       </c>
       <c r="B266" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -29605,7 +29605,7 @@
         <v>127785100</v>
       </c>
       <c r="B267" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -29711,7 +29711,7 @@
         <v>127785105</v>
       </c>
       <c r="B268" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -29817,7 +29817,7 @@
         <v>127785087</v>
       </c>
       <c r="B269" t="n">
-        <v>91690</v>
+        <v>91696</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -29914,7 +29914,7 @@
         <v>127785102</v>
       </c>
       <c r="B270" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -30020,7 +30020,7 @@
         <v>127785088</v>
       </c>
       <c r="B271" t="n">
-        <v>91332</v>
+        <v>91338</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -30114,10 +30114,10 @@
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>127785091</v>
+        <v>127785089</v>
       </c>
       <c r="B272" t="n">
-        <v>91628</v>
+        <v>57823</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -30125,21 +30125,21 @@
         </is>
       </c>
       <c r="E272" t="n">
-        <v>658</v>
+        <v>103021</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I272" t="inlineStr"/>
@@ -30149,10 +30149,10 @@
         </is>
       </c>
       <c r="Q272" t="n">
-        <v>564349</v>
+        <v>564303</v>
       </c>
       <c r="R272" t="n">
-        <v>6705423</v>
+        <v>6705322</v>
       </c>
       <c r="S272" t="n">
         <v>10</v>
@@ -30211,45 +30211,59 @@
     </row>
     <row r="273">
       <c r="A273" t="n">
-        <v>127785089</v>
+        <v>127785096</v>
       </c>
       <c r="B273" t="n">
-        <v>57823</v>
+        <v>98456</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E273" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I273" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I273" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J273" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K273" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P273" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q273" t="n">
-        <v>564303</v>
+        <v>564308</v>
       </c>
       <c r="R273" t="n">
-        <v>6705322</v>
+        <v>6705320</v>
       </c>
       <c r="S273" t="n">
         <v>10</v>
@@ -30282,6 +30296,11 @@
       <c r="AA273" t="inlineStr">
         <is>
           <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AC273" t="inlineStr">
+        <is>
+          <t>2 blomstjälkar</t>
         </is>
       </c>
       <c r="AD273" t="b">
@@ -30308,59 +30327,45 @@
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>127785096</v>
+        <v>127785091</v>
       </c>
       <c r="B274" t="n">
-        <v>98450</v>
+        <v>91634</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E274" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I274" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J274" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K274" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I274" t="inlineStr"/>
       <c r="P274" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q274" t="n">
-        <v>564308</v>
+        <v>564349</v>
       </c>
       <c r="R274" t="n">
-        <v>6705320</v>
+        <v>6705423</v>
       </c>
       <c r="S274" t="n">
         <v>10</v>
@@ -30393,11 +30398,6 @@
       <c r="AA274" t="inlineStr">
         <is>
           <t>2025-08-24</t>
-        </is>
-      </c>
-      <c r="AC274" t="inlineStr">
-        <is>
-          <t>2 blomstjälkar</t>
         </is>
       </c>
       <c r="AD274" t="b">
@@ -30427,7 +30427,7 @@
         <v>127785103</v>
       </c>
       <c r="B275" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -30543,7 +30543,7 @@
         <v>127785106</v>
       </c>
       <c r="B276" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -30646,10 +30646,10 @@
     </row>
     <row r="277">
       <c r="A277" t="n">
-        <v>127785092</v>
+        <v>127785093</v>
       </c>
       <c r="B277" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -30690,10 +30690,10 @@
         </is>
       </c>
       <c r="Q277" t="n">
-        <v>564390</v>
+        <v>564348</v>
       </c>
       <c r="R277" t="n">
-        <v>6705389</v>
+        <v>6705441</v>
       </c>
       <c r="S277" t="n">
         <v>10</v>
@@ -30752,10 +30752,10 @@
     </row>
     <row r="278">
       <c r="A278" t="n">
-        <v>127785093</v>
+        <v>127785092</v>
       </c>
       <c r="B278" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -30796,10 +30796,10 @@
         </is>
       </c>
       <c r="Q278" t="n">
-        <v>564348</v>
+        <v>564390</v>
       </c>
       <c r="R278" t="n">
-        <v>6705441</v>
+        <v>6705389</v>
       </c>
       <c r="S278" t="n">
         <v>10</v>
@@ -30960,10 +30960,10 @@
     </row>
     <row r="280">
       <c r="A280" t="n">
-        <v>127785099</v>
+        <v>127785095</v>
       </c>
       <c r="B280" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -30990,7 +30990,7 @@
       </c>
       <c r="I280" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J280" t="inlineStr">
@@ -31009,10 +31009,10 @@
         </is>
       </c>
       <c r="Q280" t="n">
-        <v>564367</v>
+        <v>564309</v>
       </c>
       <c r="R280" t="n">
-        <v>6705367</v>
+        <v>6705424</v>
       </c>
       <c r="S280" t="n">
         <v>10</v>
@@ -31049,7 +31049,7 @@
       </c>
       <c r="AC280" t="inlineStr">
         <is>
-          <t>2 blomstjälkar</t>
+          <t>3 blomstjälkar</t>
         </is>
       </c>
       <c r="AD280" t="b">
@@ -31076,10 +31076,10 @@
     </row>
     <row r="281">
       <c r="A281" t="n">
-        <v>127785095</v>
+        <v>127785099</v>
       </c>
       <c r="B281" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -31106,7 +31106,7 @@
       </c>
       <c r="I281" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J281" t="inlineStr">
@@ -31125,10 +31125,10 @@
         </is>
       </c>
       <c r="Q281" t="n">
-        <v>564309</v>
+        <v>564367</v>
       </c>
       <c r="R281" t="n">
-        <v>6705424</v>
+        <v>6705367</v>
       </c>
       <c r="S281" t="n">
         <v>10</v>
@@ -31165,7 +31165,7 @@
       </c>
       <c r="AC281" t="inlineStr">
         <is>
-          <t>3 blomstjälkar</t>
+          <t>2 blomstjälkar</t>
         </is>
       </c>
       <c r="AD281" t="b">

--- a/artfynd/A 58548-2022 artfynd.xlsx
+++ b/artfynd/A 58548-2022 artfynd.xlsx
@@ -25142,7 +25142,7 @@
         <v>127683181</v>
       </c>
       <c r="B223" t="n">
-        <v>91704</v>
+        <v>91707</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -25241,54 +25241,45 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>127683193</v>
+        <v>127683140</v>
       </c>
       <c r="B224" t="n">
-        <v>92662</v>
+        <v>91341</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E224" t="n">
-        <v>5964</v>
+        <v>1202</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I224" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J224" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I224" t="inlineStr"/>
       <c r="P224" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>563883</v>
+        <v>564253</v>
       </c>
       <c r="R224" t="n">
-        <v>6704908</v>
+        <v>6705225</v>
       </c>
       <c r="S224" t="n">
         <v>10</v>
@@ -25347,10 +25338,10 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>127683156</v>
+        <v>127683144</v>
       </c>
       <c r="B225" t="n">
-        <v>57660</v>
+        <v>91341</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -25358,39 +25349,34 @@
         </is>
       </c>
       <c r="E225" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I225" t="inlineStr"/>
-      <c r="M225" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P225" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>564124</v>
+        <v>563970</v>
       </c>
       <c r="R225" t="n">
-        <v>6705171</v>
+        <v>6704986</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -25449,10 +25435,10 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>127683154</v>
+        <v>127683156</v>
       </c>
       <c r="B226" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -25480,7 +25466,7 @@
       <c r="I226" t="inlineStr"/>
       <c r="M226" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P226" t="inlineStr">
@@ -25489,10 +25475,10 @@
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>564140</v>
+        <v>564124</v>
       </c>
       <c r="R226" t="n">
-        <v>6705076</v>
+        <v>6705171</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -25551,10 +25537,10 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>127683144</v>
+        <v>127683154</v>
       </c>
       <c r="B227" t="n">
-        <v>91338</v>
+        <v>57663</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -25562,34 +25548,39 @@
         </is>
       </c>
       <c r="E227" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I227" t="inlineStr"/>
+      <c r="M227" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P227" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>563970</v>
+        <v>564140</v>
       </c>
       <c r="R227" t="n">
-        <v>6704986</v>
+        <v>6705076</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -25648,45 +25639,54 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>127683140</v>
+        <v>127683193</v>
       </c>
       <c r="B228" t="n">
-        <v>91338</v>
+        <v>92665</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E228" t="n">
-        <v>1202</v>
+        <v>5964</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I228" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I228" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J228" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P228" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>564253</v>
+        <v>563883</v>
       </c>
       <c r="R228" t="n">
-        <v>6705225</v>
+        <v>6704908</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -25748,7 +25748,7 @@
         <v>127683183</v>
       </c>
       <c r="B229" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -25864,7 +25864,7 @@
         <v>127683166</v>
       </c>
       <c r="B230" t="n">
-        <v>97333</v>
+        <v>97336</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -25958,45 +25958,50 @@
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>127683203</v>
+        <v>127683147</v>
       </c>
       <c r="B231" t="n">
-        <v>91739</v>
+        <v>57826</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E231" t="n">
-        <v>715</v>
+        <v>103021</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Finporing</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Gloeoporus pannocinctus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>(Romell) J.Erikss.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I231" t="inlineStr"/>
+      <c r="M231" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P231" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>563955</v>
+        <v>564237</v>
       </c>
       <c r="R231" t="n">
-        <v>6704996</v>
+        <v>6705225</v>
       </c>
       <c r="S231" t="n">
         <v>10</v>
@@ -26058,7 +26063,7 @@
         <v>127683173</v>
       </c>
       <c r="B232" t="n">
-        <v>95312</v>
+        <v>95315</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -26157,50 +26162,45 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>127683147</v>
+        <v>127683203</v>
       </c>
       <c r="B233" t="n">
-        <v>57823</v>
+        <v>91742</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E233" t="n">
-        <v>103021</v>
+        <v>715</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Finporing</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Gloeoporus pannocinctus</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Romell) J.Erikss.</t>
         </is>
       </c>
       <c r="I233" t="inlineStr"/>
-      <c r="M233" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P233" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>564237</v>
+        <v>563955</v>
       </c>
       <c r="R233" t="n">
-        <v>6705225</v>
+        <v>6704996</v>
       </c>
       <c r="S233" t="n">
         <v>10</v>
@@ -26262,7 +26262,7 @@
         <v>127683159</v>
       </c>
       <c r="B234" t="n">
-        <v>92240</v>
+        <v>92243</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -26458,10 +26458,10 @@
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>127683152</v>
+        <v>127683163</v>
       </c>
       <c r="B236" t="n">
-        <v>92273</v>
+        <v>91113</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -26469,43 +26469,34 @@
         </is>
       </c>
       <c r="E236" t="n">
-        <v>4769</v>
+        <v>3215</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I236" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J236" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I236" t="inlineStr"/>
       <c r="P236" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>563895</v>
+        <v>564121</v>
       </c>
       <c r="R236" t="n">
-        <v>6704903</v>
+        <v>6705165</v>
       </c>
       <c r="S236" t="n">
         <v>10</v>
@@ -26538,6 +26529,11 @@
       <c r="AA236" t="inlineStr">
         <is>
           <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AC236" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD236" t="b">
@@ -26564,10 +26560,10 @@
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>127683163</v>
+        <v>127683152</v>
       </c>
       <c r="B237" t="n">
-        <v>91110</v>
+        <v>92276</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -26575,34 +26571,43 @@
         </is>
       </c>
       <c r="E237" t="n">
-        <v>3215</v>
+        <v>4769</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I237" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I237" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J237" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P237" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>564121</v>
+        <v>563895</v>
       </c>
       <c r="R237" t="n">
-        <v>6705165</v>
+        <v>6704903</v>
       </c>
       <c r="S237" t="n">
         <v>10</v>
@@ -26635,11 +26640,6 @@
       <c r="AA237" t="inlineStr">
         <is>
           <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="AC237" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD237" t="b">
@@ -26669,7 +26669,7 @@
         <v>127683188</v>
       </c>
       <c r="B238" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -26777,54 +26777,45 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>127683196</v>
+        <v>127683138</v>
       </c>
       <c r="B239" t="n">
-        <v>92662</v>
+        <v>91699</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E239" t="n">
-        <v>5964</v>
+        <v>2062</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I239" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J239" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I239" t="inlineStr"/>
       <c r="P239" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>564163</v>
+        <v>564145</v>
       </c>
       <c r="R239" t="n">
-        <v>6705180</v>
+        <v>6705081</v>
       </c>
       <c r="S239" t="n">
         <v>10</v>
@@ -26883,45 +26874,54 @@
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>127683138</v>
+        <v>127683196</v>
       </c>
       <c r="B240" t="n">
-        <v>91696</v>
+        <v>92665</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E240" t="n">
-        <v>2062</v>
+        <v>5964</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I240" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I240" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J240" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P240" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>564145</v>
+        <v>564163</v>
       </c>
       <c r="R240" t="n">
-        <v>6705081</v>
+        <v>6705180</v>
       </c>
       <c r="S240" t="n">
         <v>10</v>
@@ -26983,7 +26983,7 @@
         <v>127683185</v>
       </c>
       <c r="B241" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -27094,7 +27094,7 @@
         <v>127683182</v>
       </c>
       <c r="B242" t="n">
-        <v>75082</v>
+        <v>75085</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -27191,7 +27191,7 @@
         <v>127683149</v>
       </c>
       <c r="B243" t="n">
-        <v>57823</v>
+        <v>57826</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -27293,7 +27293,7 @@
         <v>127683162</v>
       </c>
       <c r="B244" t="n">
-        <v>95700</v>
+        <v>95703</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -27390,7 +27390,7 @@
         <v>127683195</v>
       </c>
       <c r="B245" t="n">
-        <v>92662</v>
+        <v>92665</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -27496,7 +27496,7 @@
         <v>127683135</v>
       </c>
       <c r="B246" t="n">
-        <v>91303</v>
+        <v>91306</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -27593,7 +27593,7 @@
         <v>127683184</v>
       </c>
       <c r="B247" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -27709,7 +27709,7 @@
         <v>127683137</v>
       </c>
       <c r="B248" t="n">
-        <v>91696</v>
+        <v>91699</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -27806,7 +27806,7 @@
         <v>127683141</v>
       </c>
       <c r="B249" t="n">
-        <v>91338</v>
+        <v>91341</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -27903,7 +27903,7 @@
         <v>127683151</v>
       </c>
       <c r="B250" t="n">
-        <v>92273</v>
+        <v>92276</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -28002,32 +28002,32 @@
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>127683199</v>
+        <v>127683139</v>
       </c>
       <c r="B251" t="n">
-        <v>95307</v>
+        <v>91699</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E251" t="n">
-        <v>2383</v>
+        <v>2062</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Bågpraktmossa</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>Plagiomnium medium</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>(Bruch &amp; Schimp.) T.J.Kop.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I251" t="inlineStr"/>
@@ -28037,10 +28037,10 @@
         </is>
       </c>
       <c r="Q251" t="n">
-        <v>564058</v>
+        <v>563999</v>
       </c>
       <c r="R251" t="n">
-        <v>6705124</v>
+        <v>6705007</v>
       </c>
       <c r="S251" t="n">
         <v>10</v>
@@ -28073,11 +28073,6 @@
       <c r="AA251" t="inlineStr">
         <is>
           <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="AC251" t="inlineStr">
-        <is>
-          <t>i översinlningsområde utanför hänsyn</t>
         </is>
       </c>
       <c r="AD251" t="b">
@@ -28104,10 +28099,10 @@
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>127683200</v>
+        <v>127683199</v>
       </c>
       <c r="B252" t="n">
-        <v>100638</v>
+        <v>95310</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -28115,21 +28110,21 @@
         </is>
       </c>
       <c r="E252" t="n">
-        <v>222498</v>
+        <v>2383</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Bågpraktmossa</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Plagiomnium medium</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Bruch &amp; Schimp.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I252" t="inlineStr"/>
@@ -28139,10 +28134,10 @@
         </is>
       </c>
       <c r="Q252" t="n">
-        <v>563890</v>
+        <v>564058</v>
       </c>
       <c r="R252" t="n">
-        <v>6704897</v>
+        <v>6705124</v>
       </c>
       <c r="S252" t="n">
         <v>10</v>
@@ -28175,6 +28170,11 @@
       <c r="AA252" t="inlineStr">
         <is>
           <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AC252" t="inlineStr">
+        <is>
+          <t>i översinlningsområde utanför hänsyn</t>
         </is>
       </c>
       <c r="AD252" t="b">
@@ -28201,32 +28201,32 @@
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>127683139</v>
+        <v>127683200</v>
       </c>
       <c r="B253" t="n">
-        <v>91696</v>
+        <v>100641</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E253" t="n">
-        <v>2062</v>
+        <v>222498</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I253" t="inlineStr"/>
@@ -28236,10 +28236,10 @@
         </is>
       </c>
       <c r="Q253" t="n">
-        <v>563999</v>
+        <v>563890</v>
       </c>
       <c r="R253" t="n">
-        <v>6705007</v>
+        <v>6704897</v>
       </c>
       <c r="S253" t="n">
         <v>10</v>
@@ -28301,7 +28301,7 @@
         <v>127683145</v>
       </c>
       <c r="B254" t="n">
-        <v>91338</v>
+        <v>91341</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -28395,10 +28395,10 @@
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>127683142</v>
+        <v>127683155</v>
       </c>
       <c r="B255" t="n">
-        <v>91338</v>
+        <v>57663</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -28406,34 +28406,39 @@
         </is>
       </c>
       <c r="E255" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I255" t="inlineStr"/>
+      <c r="M255" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P255" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q255" t="n">
-        <v>564128</v>
+        <v>564144</v>
       </c>
       <c r="R255" t="n">
-        <v>6705064</v>
+        <v>6705112</v>
       </c>
       <c r="S255" t="n">
         <v>10</v>
@@ -28492,10 +28497,10 @@
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>127683155</v>
+        <v>127683142</v>
       </c>
       <c r="B256" t="n">
-        <v>57660</v>
+        <v>91341</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -28503,39 +28508,34 @@
         </is>
       </c>
       <c r="E256" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I256" t="inlineStr"/>
-      <c r="M256" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P256" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q256" t="n">
-        <v>564144</v>
+        <v>564128</v>
       </c>
       <c r="R256" t="n">
-        <v>6705112</v>
+        <v>6705064</v>
       </c>
       <c r="S256" t="n">
         <v>10</v>
@@ -28597,7 +28597,7 @@
         <v>127683201</v>
       </c>
       <c r="B257" t="n">
-        <v>100638</v>
+        <v>100641</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -28691,45 +28691,50 @@
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>127683164</v>
+        <v>127683158</v>
       </c>
       <c r="B258" t="n">
-        <v>91110</v>
+        <v>57663</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E258" t="n">
-        <v>3215</v>
+        <v>100049</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I258" t="inlineStr"/>
+      <c r="M258" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P258" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q258" t="n">
-        <v>564133</v>
+        <v>563970</v>
       </c>
       <c r="R258" t="n">
-        <v>6705173</v>
+        <v>6704954</v>
       </c>
       <c r="S258" t="n">
         <v>10</v>
@@ -28788,10 +28793,10 @@
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>127683133</v>
+        <v>127683164</v>
       </c>
       <c r="B259" t="n">
-        <v>91303</v>
+        <v>91113</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -28799,21 +28804,21 @@
         </is>
       </c>
       <c r="E259" t="n">
-        <v>5447</v>
+        <v>3215</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I259" t="inlineStr"/>
@@ -28823,10 +28828,10 @@
         </is>
       </c>
       <c r="Q259" t="n">
-        <v>564052</v>
+        <v>564133</v>
       </c>
       <c r="R259" t="n">
-        <v>6705031</v>
+        <v>6705173</v>
       </c>
       <c r="S259" t="n">
         <v>10</v>
@@ -28885,40 +28890,35 @@
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>127683157</v>
+        <v>127683133</v>
       </c>
       <c r="B260" t="n">
-        <v>57660</v>
+        <v>91306</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E260" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I260" t="inlineStr"/>
-      <c r="M260" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P260" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
@@ -28987,10 +28987,10 @@
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>127683158</v>
+        <v>127683157</v>
       </c>
       <c r="B261" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -29027,10 +29027,10 @@
         </is>
       </c>
       <c r="Q261" t="n">
-        <v>563970</v>
+        <v>564052</v>
       </c>
       <c r="R261" t="n">
-        <v>6704954</v>
+        <v>6705031</v>
       </c>
       <c r="S261" t="n">
         <v>10</v>
@@ -29089,32 +29089,32 @@
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>127683130</v>
+        <v>127683172</v>
       </c>
       <c r="B262" t="n">
-        <v>91550</v>
+        <v>95315</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E262" t="n">
-        <v>1106</v>
+        <v>2387</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I262" t="inlineStr"/>
@@ -29124,10 +29124,10 @@
         </is>
       </c>
       <c r="Q262" t="n">
-        <v>564057</v>
+        <v>563914</v>
       </c>
       <c r="R262" t="n">
-        <v>6705032</v>
+        <v>6704945</v>
       </c>
       <c r="S262" t="n">
         <v>10</v>
@@ -29160,6 +29160,11 @@
       <c r="AA262" t="inlineStr">
         <is>
           <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AC262" t="inlineStr">
+        <is>
+          <t>I källdråg utan planerad hänsyn</t>
         </is>
       </c>
       <c r="AD262" t="b">
@@ -29186,32 +29191,32 @@
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>127683172</v>
+        <v>127683130</v>
       </c>
       <c r="B263" t="n">
-        <v>95312</v>
+        <v>91553</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E263" t="n">
-        <v>2387</v>
+        <v>1106</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I263" t="inlineStr"/>
@@ -29221,10 +29226,10 @@
         </is>
       </c>
       <c r="Q263" t="n">
-        <v>563914</v>
+        <v>564057</v>
       </c>
       <c r="R263" t="n">
-        <v>6704945</v>
+        <v>6705032</v>
       </c>
       <c r="S263" t="n">
         <v>10</v>
@@ -29257,11 +29262,6 @@
       <c r="AA263" t="inlineStr">
         <is>
           <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="AC263" t="inlineStr">
-        <is>
-          <t>I källdråg utan planerad hänsyn</t>
         </is>
       </c>
       <c r="AD263" t="b">
@@ -29291,7 +29291,7 @@
         <v>127683187</v>
       </c>
       <c r="B264" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -29402,7 +29402,7 @@
         <v>127683165</v>
       </c>
       <c r="B265" t="n">
-        <v>91960</v>
+        <v>91963</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -29499,7 +29499,7 @@
         <v>127785097</v>
       </c>
       <c r="B266" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -29605,7 +29605,7 @@
         <v>127785100</v>
       </c>
       <c r="B267" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -29711,7 +29711,7 @@
         <v>127785105</v>
       </c>
       <c r="B268" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -29817,7 +29817,7 @@
         <v>127785087</v>
       </c>
       <c r="B269" t="n">
-        <v>91696</v>
+        <v>91699</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -29914,7 +29914,7 @@
         <v>127785102</v>
       </c>
       <c r="B270" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -30020,7 +30020,7 @@
         <v>127785088</v>
       </c>
       <c r="B271" t="n">
-        <v>91338</v>
+        <v>91341</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -30114,10 +30114,10 @@
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>127785089</v>
+        <v>127785091</v>
       </c>
       <c r="B272" t="n">
-        <v>57823</v>
+        <v>91637</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -30125,21 +30125,21 @@
         </is>
       </c>
       <c r="E272" t="n">
-        <v>103021</v>
+        <v>658</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I272" t="inlineStr"/>
@@ -30149,10 +30149,10 @@
         </is>
       </c>
       <c r="Q272" t="n">
-        <v>564303</v>
+        <v>564349</v>
       </c>
       <c r="R272" t="n">
-        <v>6705322</v>
+        <v>6705423</v>
       </c>
       <c r="S272" t="n">
         <v>10</v>
@@ -30214,7 +30214,7 @@
         <v>127785096</v>
       </c>
       <c r="B273" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -30327,10 +30327,10 @@
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>127785091</v>
+        <v>127785089</v>
       </c>
       <c r="B274" t="n">
-        <v>91634</v>
+        <v>57826</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -30338,21 +30338,21 @@
         </is>
       </c>
       <c r="E274" t="n">
-        <v>658</v>
+        <v>103021</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I274" t="inlineStr"/>
@@ -30362,10 +30362,10 @@
         </is>
       </c>
       <c r="Q274" t="n">
-        <v>564349</v>
+        <v>564303</v>
       </c>
       <c r="R274" t="n">
-        <v>6705423</v>
+        <v>6705322</v>
       </c>
       <c r="S274" t="n">
         <v>10</v>
@@ -30427,7 +30427,7 @@
         <v>127785103</v>
       </c>
       <c r="B275" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -30543,7 +30543,7 @@
         <v>127785106</v>
       </c>
       <c r="B276" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -30646,10 +30646,10 @@
     </row>
     <row r="277">
       <c r="A277" t="n">
-        <v>127785093</v>
+        <v>127785092</v>
       </c>
       <c r="B277" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -30690,10 +30690,10 @@
         </is>
       </c>
       <c r="Q277" t="n">
-        <v>564348</v>
+        <v>564390</v>
       </c>
       <c r="R277" t="n">
-        <v>6705441</v>
+        <v>6705389</v>
       </c>
       <c r="S277" t="n">
         <v>10</v>
@@ -30752,10 +30752,10 @@
     </row>
     <row r="278">
       <c r="A278" t="n">
-        <v>127785092</v>
+        <v>127785093</v>
       </c>
       <c r="B278" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -30796,10 +30796,10 @@
         </is>
       </c>
       <c r="Q278" t="n">
-        <v>564390</v>
+        <v>564348</v>
       </c>
       <c r="R278" t="n">
-        <v>6705389</v>
+        <v>6705441</v>
       </c>
       <c r="S278" t="n">
         <v>10</v>
@@ -30861,7 +30861,7 @@
         <v>127785090</v>
       </c>
       <c r="B279" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -30963,7 +30963,7 @@
         <v>127785095</v>
       </c>
       <c r="B280" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -31079,7 +31079,7 @@
         <v>127785099</v>
       </c>
       <c r="B281" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>

--- a/artfynd/A 58548-2022 artfynd.xlsx
+++ b/artfynd/A 58548-2022 artfynd.xlsx
@@ -25142,7 +25142,7 @@
         <v>127683181</v>
       </c>
       <c r="B223" t="n">
-        <v>91707</v>
+        <v>91715</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -25241,10 +25241,10 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>127683140</v>
+        <v>127683144</v>
       </c>
       <c r="B224" t="n">
-        <v>91341</v>
+        <v>91349</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -25276,10 +25276,10 @@
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>564253</v>
+        <v>563970</v>
       </c>
       <c r="R224" t="n">
-        <v>6705225</v>
+        <v>6704986</v>
       </c>
       <c r="S224" t="n">
         <v>10</v>
@@ -25338,10 +25338,10 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>127683144</v>
+        <v>127683140</v>
       </c>
       <c r="B225" t="n">
-        <v>91341</v>
+        <v>91349</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -25373,10 +25373,10 @@
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>563970</v>
+        <v>564253</v>
       </c>
       <c r="R225" t="n">
-        <v>6704986</v>
+        <v>6705225</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -25435,10 +25435,10 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>127683156</v>
+        <v>127683154</v>
       </c>
       <c r="B226" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -25466,7 +25466,7 @@
       <c r="I226" t="inlineStr"/>
       <c r="M226" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P226" t="inlineStr">
@@ -25475,10 +25475,10 @@
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>564124</v>
+        <v>564140</v>
       </c>
       <c r="R226" t="n">
-        <v>6705171</v>
+        <v>6705076</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -25537,38 +25537,42 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>127683154</v>
+        <v>127683193</v>
       </c>
       <c r="B227" t="n">
-        <v>57663</v>
+        <v>92673</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E227" t="n">
-        <v>100049</v>
+        <v>5964</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I227" t="inlineStr"/>
-      <c r="M227" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J227" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P227" t="inlineStr">
@@ -25577,10 +25581,10 @@
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>564140</v>
+        <v>563883</v>
       </c>
       <c r="R227" t="n">
-        <v>6705076</v>
+        <v>6704908</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -25639,42 +25643,38 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>127683193</v>
+        <v>127683156</v>
       </c>
       <c r="B228" t="n">
-        <v>92665</v>
+        <v>57669</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E228" t="n">
-        <v>5964</v>
+        <v>100049</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I228" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J228" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I228" t="inlineStr"/>
+      <c r="M228" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P228" t="inlineStr">
@@ -25683,10 +25683,10 @@
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>563883</v>
+        <v>564124</v>
       </c>
       <c r="R228" t="n">
-        <v>6704908</v>
+        <v>6705171</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -25748,7 +25748,7 @@
         <v>127683183</v>
       </c>
       <c r="B229" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -25864,7 +25864,7 @@
         <v>127683166</v>
       </c>
       <c r="B230" t="n">
-        <v>97336</v>
+        <v>97344</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -25958,50 +25958,45 @@
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>127683147</v>
+        <v>127683173</v>
       </c>
       <c r="B231" t="n">
-        <v>57826</v>
+        <v>95323</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E231" t="n">
-        <v>103021</v>
+        <v>2387</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I231" t="inlineStr"/>
-      <c r="M231" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P231" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>564237</v>
+        <v>563865</v>
       </c>
       <c r="R231" t="n">
-        <v>6705225</v>
+        <v>6704888</v>
       </c>
       <c r="S231" t="n">
         <v>10</v>
@@ -26034,6 +26029,11 @@
       <c r="AA231" t="inlineStr">
         <is>
           <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AC231" t="inlineStr">
+        <is>
+          <t>I källdråg utan planerad hänsyn</t>
         </is>
       </c>
       <c r="AD231" t="b">
@@ -26060,32 +26060,32 @@
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>127683173</v>
+        <v>127683203</v>
       </c>
       <c r="B232" t="n">
-        <v>95315</v>
+        <v>91750</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E232" t="n">
-        <v>2387</v>
+        <v>715</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Finporing</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Gloeoporus pannocinctus</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(Romell) J.Erikss.</t>
         </is>
       </c>
       <c r="I232" t="inlineStr"/>
@@ -26095,10 +26095,10 @@
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>563865</v>
+        <v>563955</v>
       </c>
       <c r="R232" t="n">
-        <v>6704888</v>
+        <v>6704996</v>
       </c>
       <c r="S232" t="n">
         <v>10</v>
@@ -26131,11 +26131,6 @@
       <c r="AA232" t="inlineStr">
         <is>
           <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="AC232" t="inlineStr">
-        <is>
-          <t>I källdråg utan planerad hänsyn</t>
         </is>
       </c>
       <c r="AD232" t="b">
@@ -26162,45 +26157,50 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>127683203</v>
+        <v>127683147</v>
       </c>
       <c r="B233" t="n">
-        <v>91742</v>
+        <v>57832</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E233" t="n">
-        <v>715</v>
+        <v>103021</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Finporing</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Gloeoporus pannocinctus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>(Romell) J.Erikss.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I233" t="inlineStr"/>
+      <c r="M233" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P233" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>563955</v>
+        <v>564237</v>
       </c>
       <c r="R233" t="n">
-        <v>6704996</v>
+        <v>6705225</v>
       </c>
       <c r="S233" t="n">
         <v>10</v>
@@ -26262,7 +26262,7 @@
         <v>127683159</v>
       </c>
       <c r="B234" t="n">
-        <v>92243</v>
+        <v>92251</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -26461,7 +26461,7 @@
         <v>127683163</v>
       </c>
       <c r="B236" t="n">
-        <v>91113</v>
+        <v>91121</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -26563,7 +26563,7 @@
         <v>127683152</v>
       </c>
       <c r="B237" t="n">
-        <v>92276</v>
+        <v>92284</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -26669,7 +26669,7 @@
         <v>127683188</v>
       </c>
       <c r="B238" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -26777,45 +26777,54 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>127683138</v>
+        <v>127683196</v>
       </c>
       <c r="B239" t="n">
-        <v>91699</v>
+        <v>92673</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E239" t="n">
-        <v>2062</v>
+        <v>5964</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I239" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I239" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J239" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P239" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>564145</v>
+        <v>564163</v>
       </c>
       <c r="R239" t="n">
-        <v>6705081</v>
+        <v>6705180</v>
       </c>
       <c r="S239" t="n">
         <v>10</v>
@@ -26874,54 +26883,45 @@
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>127683196</v>
+        <v>127683138</v>
       </c>
       <c r="B240" t="n">
-        <v>92665</v>
+        <v>91707</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E240" t="n">
-        <v>5964</v>
+        <v>2062</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I240" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J240" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I240" t="inlineStr"/>
       <c r="P240" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>564163</v>
+        <v>564145</v>
       </c>
       <c r="R240" t="n">
-        <v>6705180</v>
+        <v>6705081</v>
       </c>
       <c r="S240" t="n">
         <v>10</v>
@@ -26983,7 +26983,7 @@
         <v>127683185</v>
       </c>
       <c r="B241" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -27094,7 +27094,7 @@
         <v>127683182</v>
       </c>
       <c r="B242" t="n">
-        <v>75085</v>
+        <v>75091</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -27188,50 +27188,45 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>127683149</v>
+        <v>127683162</v>
       </c>
       <c r="B243" t="n">
-        <v>57826</v>
+        <v>95711</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E243" t="n">
-        <v>103021</v>
+        <v>2813</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I243" t="inlineStr"/>
-      <c r="M243" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P243" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>564082</v>
+        <v>563934</v>
       </c>
       <c r="R243" t="n">
-        <v>6705145</v>
+        <v>6704860</v>
       </c>
       <c r="S243" t="n">
         <v>10</v>
@@ -27290,45 +27285,50 @@
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>127683162</v>
+        <v>127683149</v>
       </c>
       <c r="B244" t="n">
-        <v>95703</v>
+        <v>57832</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E244" t="n">
-        <v>2813</v>
+        <v>103021</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I244" t="inlineStr"/>
+      <c r="M244" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P244" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q244" t="n">
-        <v>563934</v>
+        <v>564082</v>
       </c>
       <c r="R244" t="n">
-        <v>6704860</v>
+        <v>6705145</v>
       </c>
       <c r="S244" t="n">
         <v>10</v>
@@ -27390,7 +27390,7 @@
         <v>127683195</v>
       </c>
       <c r="B245" t="n">
-        <v>92665</v>
+        <v>92673</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -27496,7 +27496,7 @@
         <v>127683135</v>
       </c>
       <c r="B246" t="n">
-        <v>91306</v>
+        <v>91314</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -27593,7 +27593,7 @@
         <v>127683184</v>
       </c>
       <c r="B247" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -27709,7 +27709,7 @@
         <v>127683137</v>
       </c>
       <c r="B248" t="n">
-        <v>91699</v>
+        <v>91707</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -27806,7 +27806,7 @@
         <v>127683141</v>
       </c>
       <c r="B249" t="n">
-        <v>91341</v>
+        <v>91349</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -27903,7 +27903,7 @@
         <v>127683151</v>
       </c>
       <c r="B250" t="n">
-        <v>92276</v>
+        <v>92284</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -28002,32 +28002,32 @@
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>127683139</v>
+        <v>127683200</v>
       </c>
       <c r="B251" t="n">
-        <v>91699</v>
+        <v>100649</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E251" t="n">
-        <v>2062</v>
+        <v>222498</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I251" t="inlineStr"/>
@@ -28037,10 +28037,10 @@
         </is>
       </c>
       <c r="Q251" t="n">
-        <v>563999</v>
+        <v>563890</v>
       </c>
       <c r="R251" t="n">
-        <v>6705007</v>
+        <v>6704897</v>
       </c>
       <c r="S251" t="n">
         <v>10</v>
@@ -28099,32 +28099,32 @@
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>127683199</v>
+        <v>127683139</v>
       </c>
       <c r="B252" t="n">
-        <v>95310</v>
+        <v>91707</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E252" t="n">
-        <v>2383</v>
+        <v>2062</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Bågpraktmossa</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>Plagiomnium medium</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>(Bruch &amp; Schimp.) T.J.Kop.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I252" t="inlineStr"/>
@@ -28134,10 +28134,10 @@
         </is>
       </c>
       <c r="Q252" t="n">
-        <v>564058</v>
+        <v>563999</v>
       </c>
       <c r="R252" t="n">
-        <v>6705124</v>
+        <v>6705007</v>
       </c>
       <c r="S252" t="n">
         <v>10</v>
@@ -28170,11 +28170,6 @@
       <c r="AA252" t="inlineStr">
         <is>
           <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="AC252" t="inlineStr">
-        <is>
-          <t>i översinlningsområde utanför hänsyn</t>
         </is>
       </c>
       <c r="AD252" t="b">
@@ -28201,10 +28196,10 @@
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>127683200</v>
+        <v>127683199</v>
       </c>
       <c r="B253" t="n">
-        <v>100641</v>
+        <v>95318</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -28212,21 +28207,21 @@
         </is>
       </c>
       <c r="E253" t="n">
-        <v>222498</v>
+        <v>2383</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Bågpraktmossa</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Plagiomnium medium</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Bruch &amp; Schimp.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I253" t="inlineStr"/>
@@ -28236,10 +28231,10 @@
         </is>
       </c>
       <c r="Q253" t="n">
-        <v>563890</v>
+        <v>564058</v>
       </c>
       <c r="R253" t="n">
-        <v>6704897</v>
+        <v>6705124</v>
       </c>
       <c r="S253" t="n">
         <v>10</v>
@@ -28272,6 +28267,11 @@
       <c r="AA253" t="inlineStr">
         <is>
           <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AC253" t="inlineStr">
+        <is>
+          <t>i översinlningsområde utanför hänsyn</t>
         </is>
       </c>
       <c r="AD253" t="b">
@@ -28301,7 +28301,7 @@
         <v>127683145</v>
       </c>
       <c r="B254" t="n">
-        <v>91341</v>
+        <v>91349</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -28395,10 +28395,10 @@
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>127683155</v>
+        <v>127683142</v>
       </c>
       <c r="B255" t="n">
-        <v>57663</v>
+        <v>91349</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -28406,39 +28406,34 @@
         </is>
       </c>
       <c r="E255" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I255" t="inlineStr"/>
-      <c r="M255" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P255" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q255" t="n">
-        <v>564144</v>
+        <v>564128</v>
       </c>
       <c r="R255" t="n">
-        <v>6705112</v>
+        <v>6705064</v>
       </c>
       <c r="S255" t="n">
         <v>10</v>
@@ -28497,10 +28492,10 @@
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>127683142</v>
+        <v>127683155</v>
       </c>
       <c r="B256" t="n">
-        <v>91341</v>
+        <v>57669</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -28508,34 +28503,39 @@
         </is>
       </c>
       <c r="E256" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I256" t="inlineStr"/>
+      <c r="M256" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P256" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q256" t="n">
-        <v>564128</v>
+        <v>564144</v>
       </c>
       <c r="R256" t="n">
-        <v>6705064</v>
+        <v>6705112</v>
       </c>
       <c r="S256" t="n">
         <v>10</v>
@@ -28597,7 +28597,7 @@
         <v>127683201</v>
       </c>
       <c r="B257" t="n">
-        <v>100641</v>
+        <v>100649</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -28691,50 +28691,45 @@
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>127683158</v>
+        <v>127683164</v>
       </c>
       <c r="B258" t="n">
-        <v>57663</v>
+        <v>91121</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E258" t="n">
-        <v>100049</v>
+        <v>3215</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I258" t="inlineStr"/>
-      <c r="M258" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P258" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q258" t="n">
-        <v>563970</v>
+        <v>564133</v>
       </c>
       <c r="R258" t="n">
-        <v>6704954</v>
+        <v>6705173</v>
       </c>
       <c r="S258" t="n">
         <v>10</v>
@@ -28793,45 +28788,50 @@
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>127683164</v>
+        <v>127683157</v>
       </c>
       <c r="B259" t="n">
-        <v>91113</v>
+        <v>57669</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E259" t="n">
-        <v>3215</v>
+        <v>100049</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I259" t="inlineStr"/>
+      <c r="M259" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P259" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q259" t="n">
-        <v>564133</v>
+        <v>564052</v>
       </c>
       <c r="R259" t="n">
-        <v>6705173</v>
+        <v>6705031</v>
       </c>
       <c r="S259" t="n">
         <v>10</v>
@@ -28890,45 +28890,50 @@
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>127683133</v>
+        <v>127683158</v>
       </c>
       <c r="B260" t="n">
-        <v>91306</v>
+        <v>57669</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E260" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I260" t="inlineStr"/>
+      <c r="M260" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P260" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q260" t="n">
-        <v>564052</v>
+        <v>563970</v>
       </c>
       <c r="R260" t="n">
-        <v>6705031</v>
+        <v>6704954</v>
       </c>
       <c r="S260" t="n">
         <v>10</v>
@@ -28987,40 +28992,35 @@
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>127683157</v>
+        <v>127683133</v>
       </c>
       <c r="B261" t="n">
-        <v>57663</v>
+        <v>91314</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E261" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I261" t="inlineStr"/>
-      <c r="M261" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P261" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
@@ -29092,7 +29092,7 @@
         <v>127683172</v>
       </c>
       <c r="B262" t="n">
-        <v>95315</v>
+        <v>95323</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -29194,7 +29194,7 @@
         <v>127683130</v>
       </c>
       <c r="B263" t="n">
-        <v>91553</v>
+        <v>91561</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -29291,7 +29291,7 @@
         <v>127683187</v>
       </c>
       <c r="B264" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -29402,7 +29402,7 @@
         <v>127683165</v>
       </c>
       <c r="B265" t="n">
-        <v>91963</v>
+        <v>91971</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -29499,7 +29499,7 @@
         <v>127785097</v>
       </c>
       <c r="B266" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -29605,7 +29605,7 @@
         <v>127785100</v>
       </c>
       <c r="B267" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -29711,7 +29711,7 @@
         <v>127785105</v>
       </c>
       <c r="B268" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -29817,7 +29817,7 @@
         <v>127785087</v>
       </c>
       <c r="B269" t="n">
-        <v>91699</v>
+        <v>91707</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -29914,7 +29914,7 @@
         <v>127785102</v>
       </c>
       <c r="B270" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -30020,7 +30020,7 @@
         <v>127785088</v>
       </c>
       <c r="B271" t="n">
-        <v>91341</v>
+        <v>91349</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -30117,7 +30117,7 @@
         <v>127785091</v>
       </c>
       <c r="B272" t="n">
-        <v>91637</v>
+        <v>91645</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -30211,59 +30211,45 @@
     </row>
     <row r="273">
       <c r="A273" t="n">
-        <v>127785096</v>
+        <v>127785089</v>
       </c>
       <c r="B273" t="n">
-        <v>98459</v>
+        <v>57832</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E273" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I273" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J273" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K273" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I273" t="inlineStr"/>
       <c r="P273" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q273" t="n">
-        <v>564308</v>
+        <v>564303</v>
       </c>
       <c r="R273" t="n">
-        <v>6705320</v>
+        <v>6705322</v>
       </c>
       <c r="S273" t="n">
         <v>10</v>
@@ -30296,11 +30282,6 @@
       <c r="AA273" t="inlineStr">
         <is>
           <t>2025-08-24</t>
-        </is>
-      </c>
-      <c r="AC273" t="inlineStr">
-        <is>
-          <t>2 blomstjälkar</t>
         </is>
       </c>
       <c r="AD273" t="b">
@@ -30327,45 +30308,59 @@
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>127785089</v>
+        <v>127785096</v>
       </c>
       <c r="B274" t="n">
-        <v>57826</v>
+        <v>98467</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E274" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I274" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I274" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J274" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K274" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P274" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q274" t="n">
-        <v>564303</v>
+        <v>564308</v>
       </c>
       <c r="R274" t="n">
-        <v>6705322</v>
+        <v>6705320</v>
       </c>
       <c r="S274" t="n">
         <v>10</v>
@@ -30398,6 +30393,11 @@
       <c r="AA274" t="inlineStr">
         <is>
           <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AC274" t="inlineStr">
+        <is>
+          <t>2 blomstjälkar</t>
         </is>
       </c>
       <c r="AD274" t="b">
@@ -30427,7 +30427,7 @@
         <v>127785103</v>
       </c>
       <c r="B275" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -30543,7 +30543,7 @@
         <v>127785106</v>
       </c>
       <c r="B276" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -30646,10 +30646,10 @@
     </row>
     <row r="277">
       <c r="A277" t="n">
-        <v>127785092</v>
+        <v>127785093</v>
       </c>
       <c r="B277" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -30690,10 +30690,10 @@
         </is>
       </c>
       <c r="Q277" t="n">
-        <v>564390</v>
+        <v>564348</v>
       </c>
       <c r="R277" t="n">
-        <v>6705389</v>
+        <v>6705441</v>
       </c>
       <c r="S277" t="n">
         <v>10</v>
@@ -30752,10 +30752,10 @@
     </row>
     <row r="278">
       <c r="A278" t="n">
-        <v>127785093</v>
+        <v>127785092</v>
       </c>
       <c r="B278" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -30796,10 +30796,10 @@
         </is>
       </c>
       <c r="Q278" t="n">
-        <v>564348</v>
+        <v>564390</v>
       </c>
       <c r="R278" t="n">
-        <v>6705441</v>
+        <v>6705389</v>
       </c>
       <c r="S278" t="n">
         <v>10</v>
@@ -30861,7 +30861,7 @@
         <v>127785090</v>
       </c>
       <c r="B279" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -30960,10 +30960,10 @@
     </row>
     <row r="280">
       <c r="A280" t="n">
-        <v>127785095</v>
+        <v>127785099</v>
       </c>
       <c r="B280" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -30990,7 +30990,7 @@
       </c>
       <c r="I280" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J280" t="inlineStr">
@@ -31009,10 +31009,10 @@
         </is>
       </c>
       <c r="Q280" t="n">
-        <v>564309</v>
+        <v>564367</v>
       </c>
       <c r="R280" t="n">
-        <v>6705424</v>
+        <v>6705367</v>
       </c>
       <c r="S280" t="n">
         <v>10</v>
@@ -31049,7 +31049,7 @@
       </c>
       <c r="AC280" t="inlineStr">
         <is>
-          <t>3 blomstjälkar</t>
+          <t>2 blomstjälkar</t>
         </is>
       </c>
       <c r="AD280" t="b">
@@ -31076,10 +31076,10 @@
     </row>
     <row r="281">
       <c r="A281" t="n">
-        <v>127785099</v>
+        <v>127785095</v>
       </c>
       <c r="B281" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -31106,7 +31106,7 @@
       </c>
       <c r="I281" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J281" t="inlineStr">
@@ -31125,10 +31125,10 @@
         </is>
       </c>
       <c r="Q281" t="n">
-        <v>564367</v>
+        <v>564309</v>
       </c>
       <c r="R281" t="n">
-        <v>6705367</v>
+        <v>6705424</v>
       </c>
       <c r="S281" t="n">
         <v>10</v>
@@ -31165,7 +31165,7 @@
       </c>
       <c r="AC281" t="inlineStr">
         <is>
-          <t>2 blomstjälkar</t>
+          <t>3 blomstjälkar</t>
         </is>
       </c>
       <c r="AD281" t="b">

--- a/artfynd/A 58548-2022 artfynd.xlsx
+++ b/artfynd/A 58548-2022 artfynd.xlsx
@@ -25139,45 +25139,54 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>127683181</v>
+        <v>127683193</v>
       </c>
       <c r="B223" t="n">
-        <v>91715</v>
+        <v>92674</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E223" t="n">
-        <v>2064</v>
+        <v>5964</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Kilporing</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Skeletocutis kuehneri</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>A.David</t>
-        </is>
-      </c>
-      <c r="I223" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J223" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P223" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>564128</v>
+        <v>563883</v>
       </c>
       <c r="R223" t="n">
-        <v>6705055</v>
+        <v>6704908</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -25210,11 +25219,6 @@
       <c r="AA223" t="inlineStr">
         <is>
           <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="AC223" t="inlineStr">
-        <is>
-          <t>Kommer att mikroskoperas</t>
         </is>
       </c>
       <c r="AD223" t="b">
@@ -25241,10 +25245,10 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>127683144</v>
+        <v>127683181</v>
       </c>
       <c r="B224" t="n">
-        <v>91349</v>
+        <v>91716</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -25252,21 +25256,21 @@
         </is>
       </c>
       <c r="E224" t="n">
-        <v>1202</v>
+        <v>2064</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kilporing</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Skeletocutis kuehneri</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>A.David</t>
         </is>
       </c>
       <c r="I224" t="inlineStr"/>
@@ -25276,10 +25280,10 @@
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>563970</v>
+        <v>564128</v>
       </c>
       <c r="R224" t="n">
-        <v>6704986</v>
+        <v>6705055</v>
       </c>
       <c r="S224" t="n">
         <v>10</v>
@@ -25312,6 +25316,11 @@
       <c r="AA224" t="inlineStr">
         <is>
           <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AC224" t="inlineStr">
+        <is>
+          <t>Kommer att mikroskoperas</t>
         </is>
       </c>
       <c r="AD224" t="b">
@@ -25341,7 +25350,7 @@
         <v>127683140</v>
       </c>
       <c r="B225" t="n">
-        <v>91349</v>
+        <v>91350</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -25435,10 +25444,10 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>127683154</v>
+        <v>127683144</v>
       </c>
       <c r="B226" t="n">
-        <v>57669</v>
+        <v>91350</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -25446,39 +25455,34 @@
         </is>
       </c>
       <c r="E226" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I226" t="inlineStr"/>
-      <c r="M226" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P226" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>564140</v>
+        <v>563970</v>
       </c>
       <c r="R226" t="n">
-        <v>6705076</v>
+        <v>6704986</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -25537,42 +25541,38 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>127683193</v>
+        <v>127683156</v>
       </c>
       <c r="B227" t="n">
-        <v>92673</v>
+        <v>57669</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E227" t="n">
-        <v>5964</v>
+        <v>100049</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I227" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J227" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I227" t="inlineStr"/>
+      <c r="M227" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P227" t="inlineStr">
@@ -25581,10 +25581,10 @@
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>563883</v>
+        <v>564124</v>
       </c>
       <c r="R227" t="n">
-        <v>6704908</v>
+        <v>6705171</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -25643,7 +25643,7 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>127683156</v>
+        <v>127683154</v>
       </c>
       <c r="B228" t="n">
         <v>57669</v>
@@ -25674,7 +25674,7 @@
       <c r="I228" t="inlineStr"/>
       <c r="M228" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P228" t="inlineStr">
@@ -25683,10 +25683,10 @@
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>564124</v>
+        <v>564140</v>
       </c>
       <c r="R228" t="n">
-        <v>6705171</v>
+        <v>6705076</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -25745,59 +25745,45 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>127683183</v>
+        <v>127683166</v>
       </c>
       <c r="B229" t="n">
-        <v>98467</v>
+        <v>97345</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E229" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I229" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J229" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K229" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I229" t="inlineStr"/>
       <c r="P229" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>564023</v>
+        <v>563939</v>
       </c>
       <c r="R229" t="n">
-        <v>6705072</v>
+        <v>6704940</v>
       </c>
       <c r="S229" t="n">
         <v>10</v>
@@ -25830,11 +25816,6 @@
       <c r="AA229" t="inlineStr">
         <is>
           <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="AC229" t="inlineStr">
-        <is>
-          <t>2 blomstjälkar</t>
         </is>
       </c>
       <c r="AD229" t="b">
@@ -25861,45 +25842,59 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>127683166</v>
+        <v>127683183</v>
       </c>
       <c r="B230" t="n">
-        <v>97344</v>
+        <v>98468</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E230" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I230" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J230" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P230" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>563939</v>
+        <v>564023</v>
       </c>
       <c r="R230" t="n">
-        <v>6704940</v>
+        <v>6705072</v>
       </c>
       <c r="S230" t="n">
         <v>10</v>
@@ -25932,6 +25927,11 @@
       <c r="AA230" t="inlineStr">
         <is>
           <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AC230" t="inlineStr">
+        <is>
+          <t>2 blomstjälkar</t>
         </is>
       </c>
       <c r="AD230" t="b">
@@ -25961,7 +25961,7 @@
         <v>127683173</v>
       </c>
       <c r="B231" t="n">
-        <v>95323</v>
+        <v>95324</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -26063,7 +26063,7 @@
         <v>127683203</v>
       </c>
       <c r="B232" t="n">
-        <v>91750</v>
+        <v>91751</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -26262,7 +26262,7 @@
         <v>127683159</v>
       </c>
       <c r="B234" t="n">
-        <v>92251</v>
+        <v>92252</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -26458,45 +26458,59 @@
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>127683163</v>
+        <v>127683188</v>
       </c>
       <c r="B236" t="n">
-        <v>91121</v>
+        <v>98468</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E236" t="n">
-        <v>3215</v>
+        <v>220787</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I236" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I236" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J236" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P236" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>564121</v>
+        <v>563940</v>
       </c>
       <c r="R236" t="n">
-        <v>6705165</v>
+        <v>6704945</v>
       </c>
       <c r="S236" t="n">
         <v>10</v>
@@ -26529,11 +26543,6 @@
       <c r="AA236" t="inlineStr">
         <is>
           <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="AC236" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD236" t="b">
@@ -26563,7 +26572,7 @@
         <v>127683152</v>
       </c>
       <c r="B237" t="n">
-        <v>92284</v>
+        <v>92285</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -26666,59 +26675,45 @@
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>127683188</v>
+        <v>127683163</v>
       </c>
       <c r="B238" t="n">
-        <v>98467</v>
+        <v>91122</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E238" t="n">
-        <v>220787</v>
+        <v>3215</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I238" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J238" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K238" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I238" t="inlineStr"/>
       <c r="P238" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q238" t="n">
-        <v>563940</v>
+        <v>564121</v>
       </c>
       <c r="R238" t="n">
-        <v>6704945</v>
+        <v>6705165</v>
       </c>
       <c r="S238" t="n">
         <v>10</v>
@@ -26751,6 +26746,11 @@
       <c r="AA238" t="inlineStr">
         <is>
           <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AC238" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD238" t="b">
@@ -26780,7 +26780,7 @@
         <v>127683196</v>
       </c>
       <c r="B239" t="n">
-        <v>92673</v>
+        <v>92674</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -26886,7 +26886,7 @@
         <v>127683138</v>
       </c>
       <c r="B240" t="n">
-        <v>91707</v>
+        <v>91708</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -26983,7 +26983,7 @@
         <v>127683185</v>
       </c>
       <c r="B241" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -27191,7 +27191,7 @@
         <v>127683162</v>
       </c>
       <c r="B243" t="n">
-        <v>95711</v>
+        <v>95712</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -27390,7 +27390,7 @@
         <v>127683195</v>
       </c>
       <c r="B245" t="n">
-        <v>92673</v>
+        <v>92674</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -27496,7 +27496,7 @@
         <v>127683135</v>
       </c>
       <c r="B246" t="n">
-        <v>91314</v>
+        <v>91315</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -27593,7 +27593,7 @@
         <v>127683184</v>
       </c>
       <c r="B247" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -27709,7 +27709,7 @@
         <v>127683137</v>
       </c>
       <c r="B248" t="n">
-        <v>91707</v>
+        <v>91708</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -27806,7 +27806,7 @@
         <v>127683141</v>
       </c>
       <c r="B249" t="n">
-        <v>91349</v>
+        <v>91350</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -27903,7 +27903,7 @@
         <v>127683151</v>
       </c>
       <c r="B250" t="n">
-        <v>92284</v>
+        <v>92285</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -28005,7 +28005,7 @@
         <v>127683200</v>
       </c>
       <c r="B251" t="n">
-        <v>100649</v>
+        <v>100650</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -28102,7 +28102,7 @@
         <v>127683139</v>
       </c>
       <c r="B252" t="n">
-        <v>91707</v>
+        <v>91708</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -28199,7 +28199,7 @@
         <v>127683199</v>
       </c>
       <c r="B253" t="n">
-        <v>95318</v>
+        <v>95319</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -28301,7 +28301,7 @@
         <v>127683145</v>
       </c>
       <c r="B254" t="n">
-        <v>91349</v>
+        <v>91350</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -28395,10 +28395,10 @@
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>127683142</v>
+        <v>127683155</v>
       </c>
       <c r="B255" t="n">
-        <v>91349</v>
+        <v>57669</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -28406,34 +28406,39 @@
         </is>
       </c>
       <c r="E255" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I255" t="inlineStr"/>
+      <c r="M255" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P255" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q255" t="n">
-        <v>564128</v>
+        <v>564144</v>
       </c>
       <c r="R255" t="n">
-        <v>6705064</v>
+        <v>6705112</v>
       </c>
       <c r="S255" t="n">
         <v>10</v>
@@ -28492,10 +28497,10 @@
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>127683155</v>
+        <v>127683142</v>
       </c>
       <c r="B256" t="n">
-        <v>57669</v>
+        <v>91350</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -28503,39 +28508,34 @@
         </is>
       </c>
       <c r="E256" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I256" t="inlineStr"/>
-      <c r="M256" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P256" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q256" t="n">
-        <v>564144</v>
+        <v>564128</v>
       </c>
       <c r="R256" t="n">
-        <v>6705112</v>
+        <v>6705064</v>
       </c>
       <c r="S256" t="n">
         <v>10</v>
@@ -28597,7 +28597,7 @@
         <v>127683201</v>
       </c>
       <c r="B257" t="n">
-        <v>100649</v>
+        <v>100650</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -28691,10 +28691,10 @@
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>127683164</v>
+        <v>127683133</v>
       </c>
       <c r="B258" t="n">
-        <v>91121</v>
+        <v>91315</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -28702,21 +28702,21 @@
         </is>
       </c>
       <c r="E258" t="n">
-        <v>3215</v>
+        <v>5447</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I258" t="inlineStr"/>
@@ -28726,10 +28726,10 @@
         </is>
       </c>
       <c r="Q258" t="n">
-        <v>564133</v>
+        <v>564052</v>
       </c>
       <c r="R258" t="n">
-        <v>6705173</v>
+        <v>6705031</v>
       </c>
       <c r="S258" t="n">
         <v>10</v>
@@ -28788,50 +28788,45 @@
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>127683157</v>
+        <v>127683164</v>
       </c>
       <c r="B259" t="n">
-        <v>57669</v>
+        <v>91122</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E259" t="n">
-        <v>100049</v>
+        <v>3215</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I259" t="inlineStr"/>
-      <c r="M259" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P259" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q259" t="n">
-        <v>564052</v>
+        <v>564133</v>
       </c>
       <c r="R259" t="n">
-        <v>6705031</v>
+        <v>6705173</v>
       </c>
       <c r="S259" t="n">
         <v>10</v>
@@ -28890,7 +28885,7 @@
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>127683158</v>
+        <v>127683157</v>
       </c>
       <c r="B260" t="n">
         <v>57669</v>
@@ -28930,10 +28925,10 @@
         </is>
       </c>
       <c r="Q260" t="n">
-        <v>563970</v>
+        <v>564052</v>
       </c>
       <c r="R260" t="n">
-        <v>6704954</v>
+        <v>6705031</v>
       </c>
       <c r="S260" t="n">
         <v>10</v>
@@ -28992,45 +28987,50 @@
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>127683133</v>
+        <v>127683158</v>
       </c>
       <c r="B261" t="n">
-        <v>91314</v>
+        <v>57669</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E261" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I261" t="inlineStr"/>
+      <c r="M261" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P261" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q261" t="n">
-        <v>564052</v>
+        <v>563970</v>
       </c>
       <c r="R261" t="n">
-        <v>6705031</v>
+        <v>6704954</v>
       </c>
       <c r="S261" t="n">
         <v>10</v>
@@ -29092,7 +29092,7 @@
         <v>127683172</v>
       </c>
       <c r="B262" t="n">
-        <v>95323</v>
+        <v>95324</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -29194,7 +29194,7 @@
         <v>127683130</v>
       </c>
       <c r="B263" t="n">
-        <v>91561</v>
+        <v>91562</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -29291,7 +29291,7 @@
         <v>127683187</v>
       </c>
       <c r="B264" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -29402,7 +29402,7 @@
         <v>127683165</v>
       </c>
       <c r="B265" t="n">
-        <v>91971</v>
+        <v>91972</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -29499,7 +29499,7 @@
         <v>127785097</v>
       </c>
       <c r="B266" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -29605,7 +29605,7 @@
         <v>127785100</v>
       </c>
       <c r="B267" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -29711,7 +29711,7 @@
         <v>127785105</v>
       </c>
       <c r="B268" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -29817,7 +29817,7 @@
         <v>127785087</v>
       </c>
       <c r="B269" t="n">
-        <v>91707</v>
+        <v>91708</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -29914,7 +29914,7 @@
         <v>127785102</v>
       </c>
       <c r="B270" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -30020,7 +30020,7 @@
         <v>127785088</v>
       </c>
       <c r="B271" t="n">
-        <v>91349</v>
+        <v>91350</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -30117,7 +30117,7 @@
         <v>127785091</v>
       </c>
       <c r="B272" t="n">
-        <v>91645</v>
+        <v>91646</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -30311,7 +30311,7 @@
         <v>127785096</v>
       </c>
       <c r="B274" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -30427,7 +30427,7 @@
         <v>127785103</v>
       </c>
       <c r="B275" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -30543,7 +30543,7 @@
         <v>127785106</v>
       </c>
       <c r="B276" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -30646,10 +30646,10 @@
     </row>
     <row r="277">
       <c r="A277" t="n">
-        <v>127785093</v>
+        <v>127785092</v>
       </c>
       <c r="B277" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -30690,10 +30690,10 @@
         </is>
       </c>
       <c r="Q277" t="n">
-        <v>564348</v>
+        <v>564390</v>
       </c>
       <c r="R277" t="n">
-        <v>6705441</v>
+        <v>6705389</v>
       </c>
       <c r="S277" t="n">
         <v>10</v>
@@ -30752,10 +30752,10 @@
     </row>
     <row r="278">
       <c r="A278" t="n">
-        <v>127785092</v>
+        <v>127785093</v>
       </c>
       <c r="B278" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -30796,10 +30796,10 @@
         </is>
       </c>
       <c r="Q278" t="n">
-        <v>564390</v>
+        <v>564348</v>
       </c>
       <c r="R278" t="n">
-        <v>6705389</v>
+        <v>6705441</v>
       </c>
       <c r="S278" t="n">
         <v>10</v>
@@ -30963,7 +30963,7 @@
         <v>127785099</v>
       </c>
       <c r="B280" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -31079,7 +31079,7 @@
         <v>127785095</v>
       </c>
       <c r="B281" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>

--- a/artfynd/A 58548-2022 artfynd.xlsx
+++ b/artfynd/A 58548-2022 artfynd.xlsx
@@ -25139,10 +25139,10 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>127683193</v>
+        <v>127683166</v>
       </c>
       <c r="B223" t="n">
-        <v>92674</v>
+        <v>97345</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -25150,43 +25150,34 @@
         </is>
       </c>
       <c r="E223" t="n">
-        <v>5964</v>
+        <v>221945</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I223" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J223" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I223" t="inlineStr"/>
       <c r="P223" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>563883</v>
+        <v>563939</v>
       </c>
       <c r="R223" t="n">
-        <v>6704908</v>
+        <v>6704940</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -25245,10 +25236,10 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>127683181</v>
+        <v>127683140</v>
       </c>
       <c r="B224" t="n">
-        <v>91716</v>
+        <v>91350</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -25256,21 +25247,21 @@
         </is>
       </c>
       <c r="E224" t="n">
-        <v>2064</v>
+        <v>1202</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Kilporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Skeletocutis kuehneri</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>A.David</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I224" t="inlineStr"/>
@@ -25280,10 +25271,10 @@
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>564128</v>
+        <v>564253</v>
       </c>
       <c r="R224" t="n">
-        <v>6705055</v>
+        <v>6705225</v>
       </c>
       <c r="S224" t="n">
         <v>10</v>
@@ -25316,11 +25307,6 @@
       <c r="AA224" t="inlineStr">
         <is>
           <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="AC224" t="inlineStr">
-        <is>
-          <t>Kommer att mikroskoperas</t>
         </is>
       </c>
       <c r="AD224" t="b">
@@ -25347,7 +25333,7 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>127683140</v>
+        <v>127683144</v>
       </c>
       <c r="B225" t="n">
         <v>91350</v>
@@ -25382,10 +25368,10 @@
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>564253</v>
+        <v>563970</v>
       </c>
       <c r="R225" t="n">
-        <v>6705225</v>
+        <v>6704986</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -25444,10 +25430,10 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>127683144</v>
+        <v>127683181</v>
       </c>
       <c r="B226" t="n">
-        <v>91350</v>
+        <v>91716</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -25455,21 +25441,21 @@
         </is>
       </c>
       <c r="E226" t="n">
-        <v>1202</v>
+        <v>2064</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kilporing</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Skeletocutis kuehneri</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>A.David</t>
         </is>
       </c>
       <c r="I226" t="inlineStr"/>
@@ -25479,10 +25465,10 @@
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>563970</v>
+        <v>564128</v>
       </c>
       <c r="R226" t="n">
-        <v>6704986</v>
+        <v>6705055</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -25515,6 +25501,11 @@
       <c r="AA226" t="inlineStr">
         <is>
           <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AC226" t="inlineStr">
+        <is>
+          <t>Kommer att mikroskoperas</t>
         </is>
       </c>
       <c r="AD226" t="b">
@@ -25541,38 +25532,42 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>127683156</v>
+        <v>127683193</v>
       </c>
       <c r="B227" t="n">
-        <v>57669</v>
+        <v>92674</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E227" t="n">
-        <v>100049</v>
+        <v>5964</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I227" t="inlineStr"/>
-      <c r="M227" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J227" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P227" t="inlineStr">
@@ -25581,10 +25576,10 @@
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>564124</v>
+        <v>563883</v>
       </c>
       <c r="R227" t="n">
-        <v>6705171</v>
+        <v>6704908</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -25643,7 +25638,7 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>127683154</v>
+        <v>127683156</v>
       </c>
       <c r="B228" t="n">
         <v>57669</v>
@@ -25674,7 +25669,7 @@
       <c r="I228" t="inlineStr"/>
       <c r="M228" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P228" t="inlineStr">
@@ -25683,10 +25678,10 @@
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>564140</v>
+        <v>564124</v>
       </c>
       <c r="R228" t="n">
-        <v>6705076</v>
+        <v>6705171</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -25745,45 +25740,50 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>127683166</v>
+        <v>127683154</v>
       </c>
       <c r="B229" t="n">
-        <v>97345</v>
+        <v>57669</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E229" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I229" t="inlineStr"/>
+      <c r="M229" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P229" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>563939</v>
+        <v>564140</v>
       </c>
       <c r="R229" t="n">
-        <v>6704940</v>
+        <v>6705076</v>
       </c>
       <c r="S229" t="n">
         <v>10</v>
@@ -25958,45 +25958,50 @@
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>127683173</v>
+        <v>127683147</v>
       </c>
       <c r="B231" t="n">
-        <v>95324</v>
+        <v>57832</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E231" t="n">
-        <v>2387</v>
+        <v>103021</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I231" t="inlineStr"/>
+      <c r="M231" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P231" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>563865</v>
+        <v>564237</v>
       </c>
       <c r="R231" t="n">
-        <v>6704888</v>
+        <v>6705225</v>
       </c>
       <c r="S231" t="n">
         <v>10</v>
@@ -26029,11 +26034,6 @@
       <c r="AA231" t="inlineStr">
         <is>
           <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="AC231" t="inlineStr">
-        <is>
-          <t>I källdråg utan planerad hänsyn</t>
         </is>
       </c>
       <c r="AD231" t="b">
@@ -26157,50 +26157,45 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>127683147</v>
+        <v>127683173</v>
       </c>
       <c r="B233" t="n">
-        <v>57832</v>
+        <v>95324</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E233" t="n">
-        <v>103021</v>
+        <v>2387</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I233" t="inlineStr"/>
-      <c r="M233" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P233" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>564237</v>
+        <v>563865</v>
       </c>
       <c r="R233" t="n">
-        <v>6705225</v>
+        <v>6704888</v>
       </c>
       <c r="S233" t="n">
         <v>10</v>
@@ -26233,6 +26228,11 @@
       <c r="AA233" t="inlineStr">
         <is>
           <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AC233" t="inlineStr">
+        <is>
+          <t>I källdråg utan planerad hänsyn</t>
         </is>
       </c>
       <c r="AD233" t="b">
@@ -26458,47 +26458,42 @@
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>127683188</v>
+        <v>127683152</v>
       </c>
       <c r="B236" t="n">
-        <v>98468</v>
+        <v>92285</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E236" t="n">
-        <v>220787</v>
+        <v>4769</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I236" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J236" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K236" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P236" t="inlineStr">
@@ -26507,10 +26502,10 @@
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>563940</v>
+        <v>563895</v>
       </c>
       <c r="R236" t="n">
-        <v>6704945</v>
+        <v>6704903</v>
       </c>
       <c r="S236" t="n">
         <v>10</v>
@@ -26569,10 +26564,10 @@
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>127683152</v>
+        <v>127683163</v>
       </c>
       <c r="B237" t="n">
-        <v>92285</v>
+        <v>91122</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -26580,43 +26575,34 @@
         </is>
       </c>
       <c r="E237" t="n">
-        <v>4769</v>
+        <v>3215</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I237" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J237" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I237" t="inlineStr"/>
       <c r="P237" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>563895</v>
+        <v>564121</v>
       </c>
       <c r="R237" t="n">
-        <v>6704903</v>
+        <v>6705165</v>
       </c>
       <c r="S237" t="n">
         <v>10</v>
@@ -26649,6 +26635,11 @@
       <c r="AA237" t="inlineStr">
         <is>
           <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AC237" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD237" t="b">
@@ -26675,45 +26666,59 @@
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>127683163</v>
+        <v>127683188</v>
       </c>
       <c r="B238" t="n">
-        <v>91122</v>
+        <v>98468</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E238" t="n">
-        <v>3215</v>
+        <v>220787</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I238" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I238" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J238" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K238" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P238" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q238" t="n">
-        <v>564121</v>
+        <v>563940</v>
       </c>
       <c r="R238" t="n">
-        <v>6705165</v>
+        <v>6704945</v>
       </c>
       <c r="S238" t="n">
         <v>10</v>
@@ -26746,11 +26751,6 @@
       <c r="AA238" t="inlineStr">
         <is>
           <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="AC238" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD238" t="b">
@@ -26777,54 +26777,45 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>127683196</v>
+        <v>127683138</v>
       </c>
       <c r="B239" t="n">
-        <v>92674</v>
+        <v>91708</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E239" t="n">
-        <v>5964</v>
+        <v>2062</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I239" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J239" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I239" t="inlineStr"/>
       <c r="P239" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>564163</v>
+        <v>564145</v>
       </c>
       <c r="R239" t="n">
-        <v>6705180</v>
+        <v>6705081</v>
       </c>
       <c r="S239" t="n">
         <v>10</v>
@@ -26883,45 +26874,54 @@
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>127683138</v>
+        <v>127683196</v>
       </c>
       <c r="B240" t="n">
-        <v>91708</v>
+        <v>92674</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E240" t="n">
-        <v>2062</v>
+        <v>5964</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I240" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I240" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J240" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P240" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>564145</v>
+        <v>564163</v>
       </c>
       <c r="R240" t="n">
-        <v>6705081</v>
+        <v>6705180</v>
       </c>
       <c r="S240" t="n">
         <v>10</v>
@@ -28002,32 +28002,32 @@
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>127683200</v>
+        <v>127683139</v>
       </c>
       <c r="B251" t="n">
-        <v>100650</v>
+        <v>91708</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E251" t="n">
-        <v>222498</v>
+        <v>2062</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I251" t="inlineStr"/>
@@ -28037,10 +28037,10 @@
         </is>
       </c>
       <c r="Q251" t="n">
-        <v>563890</v>
+        <v>563999</v>
       </c>
       <c r="R251" t="n">
-        <v>6704897</v>
+        <v>6705007</v>
       </c>
       <c r="S251" t="n">
         <v>10</v>
@@ -28099,32 +28099,32 @@
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>127683139</v>
+        <v>127683199</v>
       </c>
       <c r="B252" t="n">
-        <v>91708</v>
+        <v>95319</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E252" t="n">
-        <v>2062</v>
+        <v>2383</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Bågpraktmossa</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Plagiomnium medium</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Bruch &amp; Schimp.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I252" t="inlineStr"/>
@@ -28134,10 +28134,10 @@
         </is>
       </c>
       <c r="Q252" t="n">
-        <v>563999</v>
+        <v>564058</v>
       </c>
       <c r="R252" t="n">
-        <v>6705007</v>
+        <v>6705124</v>
       </c>
       <c r="S252" t="n">
         <v>10</v>
@@ -28170,6 +28170,11 @@
       <c r="AA252" t="inlineStr">
         <is>
           <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AC252" t="inlineStr">
+        <is>
+          <t>i översinlningsområde utanför hänsyn</t>
         </is>
       </c>
       <c r="AD252" t="b">
@@ -28196,10 +28201,10 @@
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>127683199</v>
+        <v>127683200</v>
       </c>
       <c r="B253" t="n">
-        <v>95319</v>
+        <v>100650</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -28207,21 +28212,21 @@
         </is>
       </c>
       <c r="E253" t="n">
-        <v>2383</v>
+        <v>222498</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Bågpraktmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Plagiomnium medium</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>(Bruch &amp; Schimp.) T.J.Kop.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I253" t="inlineStr"/>
@@ -28231,10 +28236,10 @@
         </is>
       </c>
       <c r="Q253" t="n">
-        <v>564058</v>
+        <v>563890</v>
       </c>
       <c r="R253" t="n">
-        <v>6705124</v>
+        <v>6704897</v>
       </c>
       <c r="S253" t="n">
         <v>10</v>
@@ -28267,11 +28272,6 @@
       <c r="AA253" t="inlineStr">
         <is>
           <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="AC253" t="inlineStr">
-        <is>
-          <t>i översinlningsområde utanför hänsyn</t>
         </is>
       </c>
       <c r="AD253" t="b">
@@ -28395,10 +28395,10 @@
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>127683155</v>
+        <v>127683142</v>
       </c>
       <c r="B255" t="n">
-        <v>57669</v>
+        <v>91350</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -28406,39 +28406,34 @@
         </is>
       </c>
       <c r="E255" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I255" t="inlineStr"/>
-      <c r="M255" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P255" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q255" t="n">
-        <v>564144</v>
+        <v>564128</v>
       </c>
       <c r="R255" t="n">
-        <v>6705112</v>
+        <v>6705064</v>
       </c>
       <c r="S255" t="n">
         <v>10</v>
@@ -28497,10 +28492,10 @@
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>127683142</v>
+        <v>127683155</v>
       </c>
       <c r="B256" t="n">
-        <v>91350</v>
+        <v>57669</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -28508,34 +28503,39 @@
         </is>
       </c>
       <c r="E256" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I256" t="inlineStr"/>
+      <c r="M256" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P256" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q256" t="n">
-        <v>564128</v>
+        <v>564144</v>
       </c>
       <c r="R256" t="n">
-        <v>6705064</v>
+        <v>6705112</v>
       </c>
       <c r="S256" t="n">
         <v>10</v>
@@ -28691,35 +28691,40 @@
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>127683133</v>
+        <v>127683157</v>
       </c>
       <c r="B258" t="n">
-        <v>91315</v>
+        <v>57669</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E258" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I258" t="inlineStr"/>
+      <c r="M258" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P258" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
@@ -28788,45 +28793,50 @@
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>127683164</v>
+        <v>127683158</v>
       </c>
       <c r="B259" t="n">
-        <v>91122</v>
+        <v>57669</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E259" t="n">
-        <v>3215</v>
+        <v>100049</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I259" t="inlineStr"/>
+      <c r="M259" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P259" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q259" t="n">
-        <v>564133</v>
+        <v>563970</v>
       </c>
       <c r="R259" t="n">
-        <v>6705173</v>
+        <v>6704954</v>
       </c>
       <c r="S259" t="n">
         <v>10</v>
@@ -28885,50 +28895,45 @@
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>127683157</v>
+        <v>127683164</v>
       </c>
       <c r="B260" t="n">
-        <v>57669</v>
+        <v>91122</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E260" t="n">
-        <v>100049</v>
+        <v>3215</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I260" t="inlineStr"/>
-      <c r="M260" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P260" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q260" t="n">
-        <v>564052</v>
+        <v>564133</v>
       </c>
       <c r="R260" t="n">
-        <v>6705031</v>
+        <v>6705173</v>
       </c>
       <c r="S260" t="n">
         <v>10</v>
@@ -28987,50 +28992,45 @@
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>127683158</v>
+        <v>127683133</v>
       </c>
       <c r="B261" t="n">
-        <v>57669</v>
+        <v>91315</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E261" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I261" t="inlineStr"/>
-      <c r="M261" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P261" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q261" t="n">
-        <v>563970</v>
+        <v>564052</v>
       </c>
       <c r="R261" t="n">
-        <v>6704954</v>
+        <v>6705031</v>
       </c>
       <c r="S261" t="n">
         <v>10</v>
@@ -29089,45 +29089,59 @@
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>127683172</v>
+        <v>127683187</v>
       </c>
       <c r="B262" t="n">
-        <v>95324</v>
+        <v>98468</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E262" t="n">
-        <v>2387</v>
+        <v>220787</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
-        </is>
-      </c>
-      <c r="I262" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I262" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J262" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K262" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P262" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q262" t="n">
-        <v>563914</v>
+        <v>564215</v>
       </c>
       <c r="R262" t="n">
-        <v>6704945</v>
+        <v>6705203</v>
       </c>
       <c r="S262" t="n">
         <v>10</v>
@@ -29160,11 +29174,6 @@
       <c r="AA262" t="inlineStr">
         <is>
           <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="AC262" t="inlineStr">
-        <is>
-          <t>I källdråg utan planerad hänsyn</t>
         </is>
       </c>
       <c r="AD262" t="b">
@@ -29288,59 +29297,45 @@
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>127683187</v>
+        <v>127683172</v>
       </c>
       <c r="B264" t="n">
-        <v>98468</v>
+        <v>95324</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E264" t="n">
-        <v>220787</v>
+        <v>2387</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I264" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J264" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K264" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Huebener) T.J.Kop.</t>
+        </is>
+      </c>
+      <c r="I264" t="inlineStr"/>
       <c r="P264" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q264" t="n">
-        <v>564215</v>
+        <v>563914</v>
       </c>
       <c r="R264" t="n">
-        <v>6705203</v>
+        <v>6704945</v>
       </c>
       <c r="S264" t="n">
         <v>10</v>
@@ -29373,6 +29368,11 @@
       <c r="AA264" t="inlineStr">
         <is>
           <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AC264" t="inlineStr">
+        <is>
+          <t>I källdråg utan planerad hänsyn</t>
         </is>
       </c>
       <c r="AD264" t="b">
@@ -30960,7 +30960,7 @@
     </row>
     <row r="280">
       <c r="A280" t="n">
-        <v>127785099</v>
+        <v>127785095</v>
       </c>
       <c r="B280" t="n">
         <v>98468</v>
@@ -30990,7 +30990,7 @@
       </c>
       <c r="I280" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J280" t="inlineStr">
@@ -31009,10 +31009,10 @@
         </is>
       </c>
       <c r="Q280" t="n">
-        <v>564367</v>
+        <v>564309</v>
       </c>
       <c r="R280" t="n">
-        <v>6705367</v>
+        <v>6705424</v>
       </c>
       <c r="S280" t="n">
         <v>10</v>
@@ -31049,7 +31049,7 @@
       </c>
       <c r="AC280" t="inlineStr">
         <is>
-          <t>2 blomstjälkar</t>
+          <t>3 blomstjälkar</t>
         </is>
       </c>
       <c r="AD280" t="b">
@@ -31076,7 +31076,7 @@
     </row>
     <row r="281">
       <c r="A281" t="n">
-        <v>127785095</v>
+        <v>127785099</v>
       </c>
       <c r="B281" t="n">
         <v>98468</v>
@@ -31106,7 +31106,7 @@
       </c>
       <c r="I281" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J281" t="inlineStr">
@@ -31125,10 +31125,10 @@
         </is>
       </c>
       <c r="Q281" t="n">
-        <v>564309</v>
+        <v>564367</v>
       </c>
       <c r="R281" t="n">
-        <v>6705424</v>
+        <v>6705367</v>
       </c>
       <c r="S281" t="n">
         <v>10</v>
@@ -31165,7 +31165,7 @@
       </c>
       <c r="AC281" t="inlineStr">
         <is>
-          <t>3 blomstjälkar</t>
+          <t>2 blomstjälkar</t>
         </is>
       </c>
       <c r="AD281" t="b">

--- a/artfynd/A 58548-2022 artfynd.xlsx
+++ b/artfynd/A 58548-2022 artfynd.xlsx
@@ -25139,32 +25139,32 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>127683166</v>
+        <v>127683181</v>
       </c>
       <c r="B223" t="n">
-        <v>97345</v>
+        <v>91717</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E223" t="n">
-        <v>221945</v>
+        <v>2064</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kilporing</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Skeletocutis kuehneri</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>A.David</t>
         </is>
       </c>
       <c r="I223" t="inlineStr"/>
@@ -25174,10 +25174,10 @@
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>563939</v>
+        <v>564128</v>
       </c>
       <c r="R223" t="n">
-        <v>6704940</v>
+        <v>6705055</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -25210,6 +25210,11 @@
       <c r="AA223" t="inlineStr">
         <is>
           <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AC223" t="inlineStr">
+        <is>
+          <t>Kommer att mikroskoperas</t>
         </is>
       </c>
       <c r="AD223" t="b">
@@ -25239,7 +25244,7 @@
         <v>127683140</v>
       </c>
       <c r="B224" t="n">
-        <v>91350</v>
+        <v>91351</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -25336,7 +25341,7 @@
         <v>127683144</v>
       </c>
       <c r="B225" t="n">
-        <v>91350</v>
+        <v>91351</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -25430,45 +25435,54 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>127683181</v>
+        <v>127683193</v>
       </c>
       <c r="B226" t="n">
-        <v>91716</v>
+        <v>92675</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E226" t="n">
-        <v>2064</v>
+        <v>5964</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Kilporing</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Skeletocutis kuehneri</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>A.David</t>
-        </is>
-      </c>
-      <c r="I226" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J226" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P226" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>564128</v>
+        <v>563883</v>
       </c>
       <c r="R226" t="n">
-        <v>6705055</v>
+        <v>6704908</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -25501,11 +25515,6 @@
       <c r="AA226" t="inlineStr">
         <is>
           <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="AC226" t="inlineStr">
-        <is>
-          <t>Kommer att mikroskoperas</t>
         </is>
       </c>
       <c r="AD226" t="b">
@@ -25532,42 +25541,38 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>127683193</v>
+        <v>127683156</v>
       </c>
       <c r="B227" t="n">
-        <v>92674</v>
+        <v>57669</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E227" t="n">
-        <v>5964</v>
+        <v>100049</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I227" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J227" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I227" t="inlineStr"/>
+      <c r="M227" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P227" t="inlineStr">
@@ -25576,10 +25581,10 @@
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>563883</v>
+        <v>564124</v>
       </c>
       <c r="R227" t="n">
-        <v>6704908</v>
+        <v>6705171</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -25638,7 +25643,7 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>127683156</v>
+        <v>127683154</v>
       </c>
       <c r="B228" t="n">
         <v>57669</v>
@@ -25669,7 +25674,7 @@
       <c r="I228" t="inlineStr"/>
       <c r="M228" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P228" t="inlineStr">
@@ -25678,10 +25683,10 @@
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>564124</v>
+        <v>564140</v>
       </c>
       <c r="R228" t="n">
-        <v>6705171</v>
+        <v>6705076</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -25740,38 +25745,47 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>127683154</v>
+        <v>127683183</v>
       </c>
       <c r="B229" t="n">
-        <v>57669</v>
+        <v>98469</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E229" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I229" t="inlineStr"/>
-      <c r="M229" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J229" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P229" t="inlineStr">
@@ -25780,10 +25794,10 @@
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>564140</v>
+        <v>564023</v>
       </c>
       <c r="R229" t="n">
-        <v>6705076</v>
+        <v>6705072</v>
       </c>
       <c r="S229" t="n">
         <v>10</v>
@@ -25816,6 +25830,11 @@
       <c r="AA229" t="inlineStr">
         <is>
           <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AC229" t="inlineStr">
+        <is>
+          <t>2 blomstjälkar</t>
         </is>
       </c>
       <c r="AD229" t="b">
@@ -25842,59 +25861,45 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>127683183</v>
+        <v>127683166</v>
       </c>
       <c r="B230" t="n">
-        <v>98468</v>
+        <v>97346</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E230" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I230" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J230" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K230" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I230" t="inlineStr"/>
       <c r="P230" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>564023</v>
+        <v>563939</v>
       </c>
       <c r="R230" t="n">
-        <v>6705072</v>
+        <v>6704940</v>
       </c>
       <c r="S230" t="n">
         <v>10</v>
@@ -25927,11 +25932,6 @@
       <c r="AA230" t="inlineStr">
         <is>
           <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="AC230" t="inlineStr">
-        <is>
-          <t>2 blomstjälkar</t>
         </is>
       </c>
       <c r="AD230" t="b">
@@ -25958,50 +25958,45 @@
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>127683147</v>
+        <v>127683173</v>
       </c>
       <c r="B231" t="n">
-        <v>57832</v>
+        <v>95325</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E231" t="n">
-        <v>103021</v>
+        <v>2387</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I231" t="inlineStr"/>
-      <c r="M231" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P231" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>564237</v>
+        <v>563865</v>
       </c>
       <c r="R231" t="n">
-        <v>6705225</v>
+        <v>6704888</v>
       </c>
       <c r="S231" t="n">
         <v>10</v>
@@ -26034,6 +26029,11 @@
       <c r="AA231" t="inlineStr">
         <is>
           <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AC231" t="inlineStr">
+        <is>
+          <t>I källdråg utan planerad hänsyn</t>
         </is>
       </c>
       <c r="AD231" t="b">
@@ -26063,7 +26063,7 @@
         <v>127683203</v>
       </c>
       <c r="B232" t="n">
-        <v>91751</v>
+        <v>91752</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -26157,45 +26157,50 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>127683173</v>
+        <v>127683147</v>
       </c>
       <c r="B233" t="n">
-        <v>95324</v>
+        <v>57832</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E233" t="n">
-        <v>2387</v>
+        <v>103021</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I233" t="inlineStr"/>
+      <c r="M233" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P233" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>563865</v>
+        <v>564237</v>
       </c>
       <c r="R233" t="n">
-        <v>6704888</v>
+        <v>6705225</v>
       </c>
       <c r="S233" t="n">
         <v>10</v>
@@ -26228,11 +26233,6 @@
       <c r="AA233" t="inlineStr">
         <is>
           <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="AC233" t="inlineStr">
-        <is>
-          <t>I källdråg utan planerad hänsyn</t>
         </is>
       </c>
       <c r="AD233" t="b">
@@ -26262,7 +26262,7 @@
         <v>127683159</v>
       </c>
       <c r="B234" t="n">
-        <v>92252</v>
+        <v>92253</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -26461,7 +26461,7 @@
         <v>127683152</v>
       </c>
       <c r="B236" t="n">
-        <v>92285</v>
+        <v>92286</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -26567,7 +26567,7 @@
         <v>127683163</v>
       </c>
       <c r="B237" t="n">
-        <v>91122</v>
+        <v>91123</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -26669,7 +26669,7 @@
         <v>127683188</v>
       </c>
       <c r="B238" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -26780,7 +26780,7 @@
         <v>127683138</v>
       </c>
       <c r="B239" t="n">
-        <v>91708</v>
+        <v>91709</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -26877,7 +26877,7 @@
         <v>127683196</v>
       </c>
       <c r="B240" t="n">
-        <v>92674</v>
+        <v>92675</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -26983,7 +26983,7 @@
         <v>127683185</v>
       </c>
       <c r="B241" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -27191,7 +27191,7 @@
         <v>127683162</v>
       </c>
       <c r="B243" t="n">
-        <v>95712</v>
+        <v>95713</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -27390,7 +27390,7 @@
         <v>127683195</v>
       </c>
       <c r="B245" t="n">
-        <v>92674</v>
+        <v>92675</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -27496,7 +27496,7 @@
         <v>127683135</v>
       </c>
       <c r="B246" t="n">
-        <v>91315</v>
+        <v>91316</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -27593,7 +27593,7 @@
         <v>127683184</v>
       </c>
       <c r="B247" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -27709,7 +27709,7 @@
         <v>127683137</v>
       </c>
       <c r="B248" t="n">
-        <v>91708</v>
+        <v>91709</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -27803,32 +27803,32 @@
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>127683141</v>
+        <v>127683151</v>
       </c>
       <c r="B249" t="n">
-        <v>91350</v>
+        <v>92286</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E249" t="n">
-        <v>1202</v>
+        <v>4769</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I249" t="inlineStr"/>
@@ -27838,10 +27838,10 @@
         </is>
       </c>
       <c r="Q249" t="n">
-        <v>564130</v>
+        <v>563873</v>
       </c>
       <c r="R249" t="n">
-        <v>6705091</v>
+        <v>6704890</v>
       </c>
       <c r="S249" t="n">
         <v>10</v>
@@ -27874,6 +27874,11 @@
       <c r="AA249" t="inlineStr">
         <is>
           <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AC249" t="inlineStr">
+        <is>
+          <t>Intill källdråg utan planerad hänsyn</t>
         </is>
       </c>
       <c r="AD249" t="b">
@@ -27900,32 +27905,32 @@
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>127683151</v>
+        <v>127683141</v>
       </c>
       <c r="B250" t="n">
-        <v>92285</v>
+        <v>91351</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E250" t="n">
-        <v>4769</v>
+        <v>1202</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I250" t="inlineStr"/>
@@ -27935,10 +27940,10 @@
         </is>
       </c>
       <c r="Q250" t="n">
-        <v>563873</v>
+        <v>564130</v>
       </c>
       <c r="R250" t="n">
-        <v>6704890</v>
+        <v>6705091</v>
       </c>
       <c r="S250" t="n">
         <v>10</v>
@@ -27971,11 +27976,6 @@
       <c r="AA250" t="inlineStr">
         <is>
           <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="AC250" t="inlineStr">
-        <is>
-          <t>Intill källdråg utan planerad hänsyn</t>
         </is>
       </c>
       <c r="AD250" t="b">
@@ -28005,7 +28005,7 @@
         <v>127683139</v>
       </c>
       <c r="B251" t="n">
-        <v>91708</v>
+        <v>91709</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -28099,10 +28099,10 @@
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>127683199</v>
+        <v>127683200</v>
       </c>
       <c r="B252" t="n">
-        <v>95319</v>
+        <v>100651</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -28110,21 +28110,21 @@
         </is>
       </c>
       <c r="E252" t="n">
-        <v>2383</v>
+        <v>222498</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Bågpraktmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>Plagiomnium medium</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>(Bruch &amp; Schimp.) T.J.Kop.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I252" t="inlineStr"/>
@@ -28134,10 +28134,10 @@
         </is>
       </c>
       <c r="Q252" t="n">
-        <v>564058</v>
+        <v>563890</v>
       </c>
       <c r="R252" t="n">
-        <v>6705124</v>
+        <v>6704897</v>
       </c>
       <c r="S252" t="n">
         <v>10</v>
@@ -28170,11 +28170,6 @@
       <c r="AA252" t="inlineStr">
         <is>
           <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="AC252" t="inlineStr">
-        <is>
-          <t>i översinlningsområde utanför hänsyn</t>
         </is>
       </c>
       <c r="AD252" t="b">
@@ -28201,10 +28196,10 @@
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>127683200</v>
+        <v>127683199</v>
       </c>
       <c r="B253" t="n">
-        <v>100650</v>
+        <v>95320</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -28212,21 +28207,21 @@
         </is>
       </c>
       <c r="E253" t="n">
-        <v>222498</v>
+        <v>2383</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Bågpraktmossa</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Plagiomnium medium</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Bruch &amp; Schimp.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I253" t="inlineStr"/>
@@ -28236,10 +28231,10 @@
         </is>
       </c>
       <c r="Q253" t="n">
-        <v>563890</v>
+        <v>564058</v>
       </c>
       <c r="R253" t="n">
-        <v>6704897</v>
+        <v>6705124</v>
       </c>
       <c r="S253" t="n">
         <v>10</v>
@@ -28272,6 +28267,11 @@
       <c r="AA253" t="inlineStr">
         <is>
           <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AC253" t="inlineStr">
+        <is>
+          <t>i översinlningsområde utanför hänsyn</t>
         </is>
       </c>
       <c r="AD253" t="b">
@@ -28301,7 +28301,7 @@
         <v>127683145</v>
       </c>
       <c r="B254" t="n">
-        <v>91350</v>
+        <v>91351</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -28398,7 +28398,7 @@
         <v>127683142</v>
       </c>
       <c r="B255" t="n">
-        <v>91350</v>
+        <v>91351</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -28597,7 +28597,7 @@
         <v>127683201</v>
       </c>
       <c r="B257" t="n">
-        <v>100650</v>
+        <v>100651</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -28691,50 +28691,45 @@
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>127683157</v>
+        <v>127683164</v>
       </c>
       <c r="B258" t="n">
-        <v>57669</v>
+        <v>91123</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E258" t="n">
-        <v>100049</v>
+        <v>3215</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I258" t="inlineStr"/>
-      <c r="M258" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P258" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q258" t="n">
-        <v>564052</v>
+        <v>564133</v>
       </c>
       <c r="R258" t="n">
-        <v>6705031</v>
+        <v>6705173</v>
       </c>
       <c r="S258" t="n">
         <v>10</v>
@@ -28793,50 +28788,45 @@
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>127683158</v>
+        <v>127683133</v>
       </c>
       <c r="B259" t="n">
-        <v>57669</v>
+        <v>91316</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E259" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I259" t="inlineStr"/>
-      <c r="M259" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P259" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q259" t="n">
-        <v>563970</v>
+        <v>564052</v>
       </c>
       <c r="R259" t="n">
-        <v>6704954</v>
+        <v>6705031</v>
       </c>
       <c r="S259" t="n">
         <v>10</v>
@@ -28895,45 +28885,50 @@
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>127683164</v>
+        <v>127683157</v>
       </c>
       <c r="B260" t="n">
-        <v>91122</v>
+        <v>57669</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E260" t="n">
-        <v>3215</v>
+        <v>100049</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I260" t="inlineStr"/>
+      <c r="M260" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P260" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q260" t="n">
-        <v>564133</v>
+        <v>564052</v>
       </c>
       <c r="R260" t="n">
-        <v>6705173</v>
+        <v>6705031</v>
       </c>
       <c r="S260" t="n">
         <v>10</v>
@@ -28992,45 +28987,50 @@
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>127683133</v>
+        <v>127683158</v>
       </c>
       <c r="B261" t="n">
-        <v>91315</v>
+        <v>57669</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E261" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I261" t="inlineStr"/>
+      <c r="M261" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P261" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q261" t="n">
-        <v>564052</v>
+        <v>563970</v>
       </c>
       <c r="R261" t="n">
-        <v>6705031</v>
+        <v>6704954</v>
       </c>
       <c r="S261" t="n">
         <v>10</v>
@@ -29089,59 +29089,45 @@
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>127683187</v>
+        <v>127683172</v>
       </c>
       <c r="B262" t="n">
-        <v>98468</v>
+        <v>95325</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E262" t="n">
-        <v>220787</v>
+        <v>2387</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I262" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J262" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K262" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Huebener) T.J.Kop.</t>
+        </is>
+      </c>
+      <c r="I262" t="inlineStr"/>
       <c r="P262" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q262" t="n">
-        <v>564215</v>
+        <v>563914</v>
       </c>
       <c r="R262" t="n">
-        <v>6705203</v>
+        <v>6704945</v>
       </c>
       <c r="S262" t="n">
         <v>10</v>
@@ -29174,6 +29160,11 @@
       <c r="AA262" t="inlineStr">
         <is>
           <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AC262" t="inlineStr">
+        <is>
+          <t>I källdråg utan planerad hänsyn</t>
         </is>
       </c>
       <c r="AD262" t="b">
@@ -29203,7 +29194,7 @@
         <v>127683130</v>
       </c>
       <c r="B263" t="n">
-        <v>91562</v>
+        <v>91563</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -29297,45 +29288,59 @@
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>127683172</v>
+        <v>127683187</v>
       </c>
       <c r="B264" t="n">
-        <v>95324</v>
+        <v>98469</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E264" t="n">
-        <v>2387</v>
+        <v>220787</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
-        </is>
-      </c>
-      <c r="I264" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I264" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J264" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K264" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P264" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q264" t="n">
-        <v>563914</v>
+        <v>564215</v>
       </c>
       <c r="R264" t="n">
-        <v>6704945</v>
+        <v>6705203</v>
       </c>
       <c r="S264" t="n">
         <v>10</v>
@@ -29368,11 +29373,6 @@
       <c r="AA264" t="inlineStr">
         <is>
           <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="AC264" t="inlineStr">
-        <is>
-          <t>I källdråg utan planerad hänsyn</t>
         </is>
       </c>
       <c r="AD264" t="b">
@@ -29402,7 +29402,7 @@
         <v>127683165</v>
       </c>
       <c r="B265" t="n">
-        <v>91972</v>
+        <v>91973</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -29499,7 +29499,7 @@
         <v>127785097</v>
       </c>
       <c r="B266" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -29605,7 +29605,7 @@
         <v>127785100</v>
       </c>
       <c r="B267" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -29711,7 +29711,7 @@
         <v>127785105</v>
       </c>
       <c r="B268" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -29817,7 +29817,7 @@
         <v>127785087</v>
       </c>
       <c r="B269" t="n">
-        <v>91708</v>
+        <v>91709</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -29914,7 +29914,7 @@
         <v>127785102</v>
       </c>
       <c r="B270" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -30020,7 +30020,7 @@
         <v>127785088</v>
       </c>
       <c r="B271" t="n">
-        <v>91350</v>
+        <v>91351</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -30117,7 +30117,7 @@
         <v>127785091</v>
       </c>
       <c r="B272" t="n">
-        <v>91646</v>
+        <v>91647</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -30311,7 +30311,7 @@
         <v>127785096</v>
       </c>
       <c r="B274" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -30427,7 +30427,7 @@
         <v>127785103</v>
       </c>
       <c r="B275" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -30543,7 +30543,7 @@
         <v>127785106</v>
       </c>
       <c r="B276" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -30646,10 +30646,10 @@
     </row>
     <row r="277">
       <c r="A277" t="n">
-        <v>127785092</v>
+        <v>127785093</v>
       </c>
       <c r="B277" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -30690,10 +30690,10 @@
         </is>
       </c>
       <c r="Q277" t="n">
-        <v>564390</v>
+        <v>564348</v>
       </c>
       <c r="R277" t="n">
-        <v>6705389</v>
+        <v>6705441</v>
       </c>
       <c r="S277" t="n">
         <v>10</v>
@@ -30752,10 +30752,10 @@
     </row>
     <row r="278">
       <c r="A278" t="n">
-        <v>127785093</v>
+        <v>127785092</v>
       </c>
       <c r="B278" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -30796,10 +30796,10 @@
         </is>
       </c>
       <c r="Q278" t="n">
-        <v>564348</v>
+        <v>564390</v>
       </c>
       <c r="R278" t="n">
-        <v>6705441</v>
+        <v>6705389</v>
       </c>
       <c r="S278" t="n">
         <v>10</v>
@@ -30963,7 +30963,7 @@
         <v>127785095</v>
       </c>
       <c r="B280" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -31079,7 +31079,7 @@
         <v>127785099</v>
       </c>
       <c r="B281" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>

--- a/artfynd/A 58548-2022 artfynd.xlsx
+++ b/artfynd/A 58548-2022 artfynd.xlsx
@@ -25139,45 +25139,54 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>127683181</v>
+        <v>127683193</v>
       </c>
       <c r="B223" t="n">
-        <v>91717</v>
+        <v>92676</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E223" t="n">
-        <v>2064</v>
+        <v>5964</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Kilporing</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Skeletocutis kuehneri</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>A.David</t>
-        </is>
-      </c>
-      <c r="I223" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J223" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P223" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>564128</v>
+        <v>563883</v>
       </c>
       <c r="R223" t="n">
-        <v>6705055</v>
+        <v>6704908</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -25210,11 +25219,6 @@
       <c r="AA223" t="inlineStr">
         <is>
           <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="AC223" t="inlineStr">
-        <is>
-          <t>Kommer att mikroskoperas</t>
         </is>
       </c>
       <c r="AD223" t="b">
@@ -25241,10 +25245,10 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>127683140</v>
+        <v>127683181</v>
       </c>
       <c r="B224" t="n">
-        <v>91351</v>
+        <v>91718</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -25252,21 +25256,21 @@
         </is>
       </c>
       <c r="E224" t="n">
-        <v>1202</v>
+        <v>2064</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kilporing</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Skeletocutis kuehneri</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>A.David</t>
         </is>
       </c>
       <c r="I224" t="inlineStr"/>
@@ -25276,10 +25280,10 @@
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>564253</v>
+        <v>564128</v>
       </c>
       <c r="R224" t="n">
-        <v>6705225</v>
+        <v>6705055</v>
       </c>
       <c r="S224" t="n">
         <v>10</v>
@@ -25312,6 +25316,11 @@
       <c r="AA224" t="inlineStr">
         <is>
           <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AC224" t="inlineStr">
+        <is>
+          <t>Kommer att mikroskoperas</t>
         </is>
       </c>
       <c r="AD224" t="b">
@@ -25338,45 +25347,59 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>127683144</v>
+        <v>127683183</v>
       </c>
       <c r="B225" t="n">
-        <v>91351</v>
+        <v>98470</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E225" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I225" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J225" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P225" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>563970</v>
+        <v>564023</v>
       </c>
       <c r="R225" t="n">
-        <v>6704986</v>
+        <v>6705072</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -25409,6 +25432,11 @@
       <c r="AA225" t="inlineStr">
         <is>
           <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AC225" t="inlineStr">
+        <is>
+          <t>2 blomstjälkar</t>
         </is>
       </c>
       <c r="AD225" t="b">
@@ -25435,54 +25463,45 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>127683193</v>
+        <v>127683140</v>
       </c>
       <c r="B226" t="n">
-        <v>92675</v>
+        <v>91352</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E226" t="n">
-        <v>5964</v>
+        <v>1202</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I226" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J226" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I226" t="inlineStr"/>
       <c r="P226" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>563883</v>
+        <v>564253</v>
       </c>
       <c r="R226" t="n">
-        <v>6704908</v>
+        <v>6705225</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -25541,10 +25560,10 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>127683156</v>
+        <v>127683144</v>
       </c>
       <c r="B227" t="n">
-        <v>57669</v>
+        <v>91352</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -25552,39 +25571,34 @@
         </is>
       </c>
       <c r="E227" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I227" t="inlineStr"/>
-      <c r="M227" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P227" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>564124</v>
+        <v>563970</v>
       </c>
       <c r="R227" t="n">
-        <v>6705171</v>
+        <v>6704986</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -25745,47 +25759,38 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>127683183</v>
+        <v>127683156</v>
       </c>
       <c r="B229" t="n">
-        <v>98469</v>
+        <v>57669</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E229" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I229" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J229" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K229" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I229" t="inlineStr"/>
+      <c r="M229" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P229" t="inlineStr">
@@ -25794,10 +25799,10 @@
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>564023</v>
+        <v>564124</v>
       </c>
       <c r="R229" t="n">
-        <v>6705072</v>
+        <v>6705171</v>
       </c>
       <c r="S229" t="n">
         <v>10</v>
@@ -25830,11 +25835,6 @@
       <c r="AA229" t="inlineStr">
         <is>
           <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="AC229" t="inlineStr">
-        <is>
-          <t>2 blomstjälkar</t>
         </is>
       </c>
       <c r="AD229" t="b">
@@ -25864,7 +25864,7 @@
         <v>127683166</v>
       </c>
       <c r="B230" t="n">
-        <v>97346</v>
+        <v>97347</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -25958,45 +25958,50 @@
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>127683173</v>
+        <v>127683147</v>
       </c>
       <c r="B231" t="n">
-        <v>95325</v>
+        <v>57832</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E231" t="n">
-        <v>2387</v>
+        <v>103021</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I231" t="inlineStr"/>
+      <c r="M231" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P231" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>563865</v>
+        <v>564237</v>
       </c>
       <c r="R231" t="n">
-        <v>6704888</v>
+        <v>6705225</v>
       </c>
       <c r="S231" t="n">
         <v>10</v>
@@ -26029,11 +26034,6 @@
       <c r="AA231" t="inlineStr">
         <is>
           <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="AC231" t="inlineStr">
-        <is>
-          <t>I källdråg utan planerad hänsyn</t>
         </is>
       </c>
       <c r="AD231" t="b">
@@ -26060,32 +26060,32 @@
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>127683203</v>
+        <v>127683173</v>
       </c>
       <c r="B232" t="n">
-        <v>91752</v>
+        <v>95326</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E232" t="n">
-        <v>715</v>
+        <v>2387</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Finporing</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Gloeoporus pannocinctus</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>(Romell) J.Erikss.</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I232" t="inlineStr"/>
@@ -26095,10 +26095,10 @@
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>563955</v>
+        <v>563865</v>
       </c>
       <c r="R232" t="n">
-        <v>6704996</v>
+        <v>6704888</v>
       </c>
       <c r="S232" t="n">
         <v>10</v>
@@ -26131,6 +26131,11 @@
       <c r="AA232" t="inlineStr">
         <is>
           <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AC232" t="inlineStr">
+        <is>
+          <t>I källdråg utan planerad hänsyn</t>
         </is>
       </c>
       <c r="AD232" t="b">
@@ -26157,50 +26162,45 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>127683147</v>
+        <v>127683203</v>
       </c>
       <c r="B233" t="n">
-        <v>57832</v>
+        <v>91753</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E233" t="n">
-        <v>103021</v>
+        <v>715</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Finporing</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Gloeoporus pannocinctus</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Romell) J.Erikss.</t>
         </is>
       </c>
       <c r="I233" t="inlineStr"/>
-      <c r="M233" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P233" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>564237</v>
+        <v>563955</v>
       </c>
       <c r="R233" t="n">
-        <v>6705225</v>
+        <v>6704996</v>
       </c>
       <c r="S233" t="n">
         <v>10</v>
@@ -26262,7 +26262,7 @@
         <v>127683159</v>
       </c>
       <c r="B234" t="n">
-        <v>92253</v>
+        <v>92254</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -26461,7 +26461,7 @@
         <v>127683152</v>
       </c>
       <c r="B236" t="n">
-        <v>92286</v>
+        <v>92287</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -26567,7 +26567,7 @@
         <v>127683163</v>
       </c>
       <c r="B237" t="n">
-        <v>91123</v>
+        <v>91124</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -26669,7 +26669,7 @@
         <v>127683188</v>
       </c>
       <c r="B238" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -26777,45 +26777,54 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>127683138</v>
+        <v>127683196</v>
       </c>
       <c r="B239" t="n">
-        <v>91709</v>
+        <v>92676</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E239" t="n">
-        <v>2062</v>
+        <v>5964</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I239" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I239" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J239" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P239" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>564145</v>
+        <v>564163</v>
       </c>
       <c r="R239" t="n">
-        <v>6705081</v>
+        <v>6705180</v>
       </c>
       <c r="S239" t="n">
         <v>10</v>
@@ -26874,54 +26883,45 @@
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>127683196</v>
+        <v>127683138</v>
       </c>
       <c r="B240" t="n">
-        <v>92675</v>
+        <v>91710</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E240" t="n">
-        <v>5964</v>
+        <v>2062</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I240" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J240" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I240" t="inlineStr"/>
       <c r="P240" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>564163</v>
+        <v>564145</v>
       </c>
       <c r="R240" t="n">
-        <v>6705180</v>
+        <v>6705081</v>
       </c>
       <c r="S240" t="n">
         <v>10</v>
@@ -26983,7 +26983,7 @@
         <v>127683185</v>
       </c>
       <c r="B241" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -27191,7 +27191,7 @@
         <v>127683162</v>
       </c>
       <c r="B243" t="n">
-        <v>95713</v>
+        <v>95714</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -27390,7 +27390,7 @@
         <v>127683195</v>
       </c>
       <c r="B245" t="n">
-        <v>92675</v>
+        <v>92676</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -27496,7 +27496,7 @@
         <v>127683135</v>
       </c>
       <c r="B246" t="n">
-        <v>91316</v>
+        <v>91317</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -27593,7 +27593,7 @@
         <v>127683184</v>
       </c>
       <c r="B247" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -27709,7 +27709,7 @@
         <v>127683137</v>
       </c>
       <c r="B248" t="n">
-        <v>91709</v>
+        <v>91710</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -27806,7 +27806,7 @@
         <v>127683151</v>
       </c>
       <c r="B249" t="n">
-        <v>92286</v>
+        <v>92287</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -27908,7 +27908,7 @@
         <v>127683141</v>
       </c>
       <c r="B250" t="n">
-        <v>91351</v>
+        <v>91352</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -28005,7 +28005,7 @@
         <v>127683139</v>
       </c>
       <c r="B251" t="n">
-        <v>91709</v>
+        <v>91710</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -28099,10 +28099,10 @@
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>127683200</v>
+        <v>127683199</v>
       </c>
       <c r="B252" t="n">
-        <v>100651</v>
+        <v>95321</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -28110,21 +28110,21 @@
         </is>
       </c>
       <c r="E252" t="n">
-        <v>222498</v>
+        <v>2383</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Bågpraktmossa</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Plagiomnium medium</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Bruch &amp; Schimp.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I252" t="inlineStr"/>
@@ -28134,10 +28134,10 @@
         </is>
       </c>
       <c r="Q252" t="n">
-        <v>563890</v>
+        <v>564058</v>
       </c>
       <c r="R252" t="n">
-        <v>6704897</v>
+        <v>6705124</v>
       </c>
       <c r="S252" t="n">
         <v>10</v>
@@ -28170,6 +28170,11 @@
       <c r="AA252" t="inlineStr">
         <is>
           <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AC252" t="inlineStr">
+        <is>
+          <t>i översinlningsområde utanför hänsyn</t>
         </is>
       </c>
       <c r="AD252" t="b">
@@ -28196,10 +28201,10 @@
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>127683199</v>
+        <v>127683200</v>
       </c>
       <c r="B253" t="n">
-        <v>95320</v>
+        <v>100652</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -28207,21 +28212,21 @@
         </is>
       </c>
       <c r="E253" t="n">
-        <v>2383</v>
+        <v>222498</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Bågpraktmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Plagiomnium medium</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>(Bruch &amp; Schimp.) T.J.Kop.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I253" t="inlineStr"/>
@@ -28231,10 +28236,10 @@
         </is>
       </c>
       <c r="Q253" t="n">
-        <v>564058</v>
+        <v>563890</v>
       </c>
       <c r="R253" t="n">
-        <v>6705124</v>
+        <v>6704897</v>
       </c>
       <c r="S253" t="n">
         <v>10</v>
@@ -28267,11 +28272,6 @@
       <c r="AA253" t="inlineStr">
         <is>
           <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="AC253" t="inlineStr">
-        <is>
-          <t>i översinlningsområde utanför hänsyn</t>
         </is>
       </c>
       <c r="AD253" t="b">
@@ -28301,7 +28301,7 @@
         <v>127683145</v>
       </c>
       <c r="B254" t="n">
-        <v>91351</v>
+        <v>91352</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -28395,10 +28395,10 @@
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>127683142</v>
+        <v>127683155</v>
       </c>
       <c r="B255" t="n">
-        <v>91351</v>
+        <v>57669</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -28406,34 +28406,39 @@
         </is>
       </c>
       <c r="E255" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I255" t="inlineStr"/>
+      <c r="M255" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P255" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q255" t="n">
-        <v>564128</v>
+        <v>564144</v>
       </c>
       <c r="R255" t="n">
-        <v>6705064</v>
+        <v>6705112</v>
       </c>
       <c r="S255" t="n">
         <v>10</v>
@@ -28492,10 +28497,10 @@
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>127683155</v>
+        <v>127683142</v>
       </c>
       <c r="B256" t="n">
-        <v>57669</v>
+        <v>91352</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -28503,39 +28508,34 @@
         </is>
       </c>
       <c r="E256" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I256" t="inlineStr"/>
-      <c r="M256" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P256" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q256" t="n">
-        <v>564144</v>
+        <v>564128</v>
       </c>
       <c r="R256" t="n">
-        <v>6705112</v>
+        <v>6705064</v>
       </c>
       <c r="S256" t="n">
         <v>10</v>
@@ -28597,7 +28597,7 @@
         <v>127683201</v>
       </c>
       <c r="B257" t="n">
-        <v>100651</v>
+        <v>100652</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -28691,45 +28691,50 @@
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>127683164</v>
+        <v>127683158</v>
       </c>
       <c r="B258" t="n">
-        <v>91123</v>
+        <v>57669</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E258" t="n">
-        <v>3215</v>
+        <v>100049</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I258" t="inlineStr"/>
+      <c r="M258" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P258" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q258" t="n">
-        <v>564133</v>
+        <v>563970</v>
       </c>
       <c r="R258" t="n">
-        <v>6705173</v>
+        <v>6704954</v>
       </c>
       <c r="S258" t="n">
         <v>10</v>
@@ -28788,35 +28793,40 @@
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>127683133</v>
+        <v>127683157</v>
       </c>
       <c r="B259" t="n">
-        <v>91316</v>
+        <v>57669</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E259" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I259" t="inlineStr"/>
+      <c r="M259" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P259" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
@@ -28885,50 +28895,45 @@
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>127683157</v>
+        <v>127683164</v>
       </c>
       <c r="B260" t="n">
-        <v>57669</v>
+        <v>91124</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E260" t="n">
-        <v>100049</v>
+        <v>3215</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I260" t="inlineStr"/>
-      <c r="M260" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P260" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q260" t="n">
-        <v>564052</v>
+        <v>564133</v>
       </c>
       <c r="R260" t="n">
-        <v>6705031</v>
+        <v>6705173</v>
       </c>
       <c r="S260" t="n">
         <v>10</v>
@@ -28987,50 +28992,45 @@
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>127683158</v>
+        <v>127683133</v>
       </c>
       <c r="B261" t="n">
-        <v>57669</v>
+        <v>91317</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E261" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I261" t="inlineStr"/>
-      <c r="M261" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P261" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q261" t="n">
-        <v>563970</v>
+        <v>564052</v>
       </c>
       <c r="R261" t="n">
-        <v>6704954</v>
+        <v>6705031</v>
       </c>
       <c r="S261" t="n">
         <v>10</v>
@@ -29092,7 +29092,7 @@
         <v>127683172</v>
       </c>
       <c r="B262" t="n">
-        <v>95325</v>
+        <v>95326</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -29194,7 +29194,7 @@
         <v>127683130</v>
       </c>
       <c r="B263" t="n">
-        <v>91563</v>
+        <v>91564</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -29291,7 +29291,7 @@
         <v>127683187</v>
       </c>
       <c r="B264" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -29402,7 +29402,7 @@
         <v>127683165</v>
       </c>
       <c r="B265" t="n">
-        <v>91973</v>
+        <v>91974</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -29499,7 +29499,7 @@
         <v>127785097</v>
       </c>
       <c r="B266" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -29605,7 +29605,7 @@
         <v>127785100</v>
       </c>
       <c r="B267" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -29711,7 +29711,7 @@
         <v>127785105</v>
       </c>
       <c r="B268" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -29817,7 +29817,7 @@
         <v>127785087</v>
       </c>
       <c r="B269" t="n">
-        <v>91709</v>
+        <v>91710</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -29914,7 +29914,7 @@
         <v>127785102</v>
       </c>
       <c r="B270" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -30020,7 +30020,7 @@
         <v>127785088</v>
       </c>
       <c r="B271" t="n">
-        <v>91351</v>
+        <v>91352</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -30114,10 +30114,10 @@
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>127785091</v>
+        <v>127785089</v>
       </c>
       <c r="B272" t="n">
-        <v>91647</v>
+        <v>57832</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -30125,21 +30125,21 @@
         </is>
       </c>
       <c r="E272" t="n">
-        <v>658</v>
+        <v>103021</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I272" t="inlineStr"/>
@@ -30149,10 +30149,10 @@
         </is>
       </c>
       <c r="Q272" t="n">
-        <v>564349</v>
+        <v>564303</v>
       </c>
       <c r="R272" t="n">
-        <v>6705423</v>
+        <v>6705322</v>
       </c>
       <c r="S272" t="n">
         <v>10</v>
@@ -30211,10 +30211,10 @@
     </row>
     <row r="273">
       <c r="A273" t="n">
-        <v>127785089</v>
+        <v>127785091</v>
       </c>
       <c r="B273" t="n">
-        <v>57832</v>
+        <v>91648</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -30222,21 +30222,21 @@
         </is>
       </c>
       <c r="E273" t="n">
-        <v>103021</v>
+        <v>658</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I273" t="inlineStr"/>
@@ -30246,10 +30246,10 @@
         </is>
       </c>
       <c r="Q273" t="n">
-        <v>564303</v>
+        <v>564349</v>
       </c>
       <c r="R273" t="n">
-        <v>6705322</v>
+        <v>6705423</v>
       </c>
       <c r="S273" t="n">
         <v>10</v>
@@ -30311,7 +30311,7 @@
         <v>127785096</v>
       </c>
       <c r="B274" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -30427,7 +30427,7 @@
         <v>127785103</v>
       </c>
       <c r="B275" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -30543,7 +30543,7 @@
         <v>127785106</v>
       </c>
       <c r="B276" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -30646,10 +30646,10 @@
     </row>
     <row r="277">
       <c r="A277" t="n">
-        <v>127785093</v>
+        <v>127785092</v>
       </c>
       <c r="B277" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -30690,10 +30690,10 @@
         </is>
       </c>
       <c r="Q277" t="n">
-        <v>564348</v>
+        <v>564390</v>
       </c>
       <c r="R277" t="n">
-        <v>6705441</v>
+        <v>6705389</v>
       </c>
       <c r="S277" t="n">
         <v>10</v>
@@ -30752,10 +30752,10 @@
     </row>
     <row r="278">
       <c r="A278" t="n">
-        <v>127785092</v>
+        <v>127785093</v>
       </c>
       <c r="B278" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -30796,10 +30796,10 @@
         </is>
       </c>
       <c r="Q278" t="n">
-        <v>564390</v>
+        <v>564348</v>
       </c>
       <c r="R278" t="n">
-        <v>6705389</v>
+        <v>6705441</v>
       </c>
       <c r="S278" t="n">
         <v>10</v>
@@ -30960,10 +30960,10 @@
     </row>
     <row r="280">
       <c r="A280" t="n">
-        <v>127785095</v>
+        <v>127785099</v>
       </c>
       <c r="B280" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -30990,7 +30990,7 @@
       </c>
       <c r="I280" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J280" t="inlineStr">
@@ -31009,10 +31009,10 @@
         </is>
       </c>
       <c r="Q280" t="n">
-        <v>564309</v>
+        <v>564367</v>
       </c>
       <c r="R280" t="n">
-        <v>6705424</v>
+        <v>6705367</v>
       </c>
       <c r="S280" t="n">
         <v>10</v>
@@ -31049,7 +31049,7 @@
       </c>
       <c r="AC280" t="inlineStr">
         <is>
-          <t>3 blomstjälkar</t>
+          <t>2 blomstjälkar</t>
         </is>
       </c>
       <c r="AD280" t="b">
@@ -31076,10 +31076,10 @@
     </row>
     <row r="281">
       <c r="A281" t="n">
-        <v>127785099</v>
+        <v>127785095</v>
       </c>
       <c r="B281" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -31106,7 +31106,7 @@
       </c>
       <c r="I281" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J281" t="inlineStr">
@@ -31125,10 +31125,10 @@
         </is>
       </c>
       <c r="Q281" t="n">
-        <v>564367</v>
+        <v>564309</v>
       </c>
       <c r="R281" t="n">
-        <v>6705367</v>
+        <v>6705424</v>
       </c>
       <c r="S281" t="n">
         <v>10</v>
@@ -31165,7 +31165,7 @@
       </c>
       <c r="AC281" t="inlineStr">
         <is>
-          <t>2 blomstjälkar</t>
+          <t>3 blomstjälkar</t>
         </is>
       </c>
       <c r="AD281" t="b">

--- a/artfynd/A 58548-2022 artfynd.xlsx
+++ b/artfynd/A 58548-2022 artfynd.xlsx
@@ -25139,54 +25139,45 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>127683193</v>
+        <v>127683140</v>
       </c>
       <c r="B223" t="n">
-        <v>92676</v>
+        <v>91352</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E223" t="n">
-        <v>5964</v>
+        <v>1202</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I223" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J223" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I223" t="inlineStr"/>
       <c r="P223" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>563883</v>
+        <v>564253</v>
       </c>
       <c r="R223" t="n">
-        <v>6704908</v>
+        <v>6705225</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -25245,10 +25236,10 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>127683181</v>
+        <v>127683144</v>
       </c>
       <c r="B224" t="n">
-        <v>91718</v>
+        <v>91352</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -25256,21 +25247,21 @@
         </is>
       </c>
       <c r="E224" t="n">
-        <v>2064</v>
+        <v>1202</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Kilporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Skeletocutis kuehneri</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>A.David</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I224" t="inlineStr"/>
@@ -25280,10 +25271,10 @@
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>564128</v>
+        <v>563970</v>
       </c>
       <c r="R224" t="n">
-        <v>6705055</v>
+        <v>6704986</v>
       </c>
       <c r="S224" t="n">
         <v>10</v>
@@ -25316,11 +25307,6 @@
       <c r="AA224" t="inlineStr">
         <is>
           <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="AC224" t="inlineStr">
-        <is>
-          <t>Kommer att mikroskoperas</t>
         </is>
       </c>
       <c r="AD224" t="b">
@@ -25347,59 +25333,45 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>127683183</v>
+        <v>127683181</v>
       </c>
       <c r="B225" t="n">
-        <v>98470</v>
+        <v>91718</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E225" t="n">
-        <v>220787</v>
+        <v>2064</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kilporing</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Skeletocutis kuehneri</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I225" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J225" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K225" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>A.David</t>
+        </is>
+      </c>
+      <c r="I225" t="inlineStr"/>
       <c r="P225" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>564023</v>
+        <v>564128</v>
       </c>
       <c r="R225" t="n">
-        <v>6705072</v>
+        <v>6705055</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -25436,7 +25408,7 @@
       </c>
       <c r="AC225" t="inlineStr">
         <is>
-          <t>2 blomstjälkar</t>
+          <t>Kommer att mikroskoperas</t>
         </is>
       </c>
       <c r="AD225" t="b">
@@ -25463,10 +25435,10 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>127683140</v>
+        <v>127683156</v>
       </c>
       <c r="B226" t="n">
-        <v>91352</v>
+        <v>57669</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -25474,34 +25446,39 @@
         </is>
       </c>
       <c r="E226" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I226" t="inlineStr"/>
+      <c r="M226" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P226" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>564253</v>
+        <v>564124</v>
       </c>
       <c r="R226" t="n">
-        <v>6705225</v>
+        <v>6705171</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -25560,10 +25537,10 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>127683144</v>
+        <v>127683154</v>
       </c>
       <c r="B227" t="n">
-        <v>91352</v>
+        <v>57669</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -25571,34 +25548,39 @@
         </is>
       </c>
       <c r="E227" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I227" t="inlineStr"/>
+      <c r="M227" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P227" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>563970</v>
+        <v>564140</v>
       </c>
       <c r="R227" t="n">
-        <v>6704986</v>
+        <v>6705076</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -25657,38 +25639,42 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>127683154</v>
+        <v>127683193</v>
       </c>
       <c r="B228" t="n">
-        <v>57669</v>
+        <v>92676</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E228" t="n">
-        <v>100049</v>
+        <v>5964</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I228" t="inlineStr"/>
-      <c r="M228" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I228" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J228" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P228" t="inlineStr">
@@ -25697,10 +25683,10 @@
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>564140</v>
+        <v>563883</v>
       </c>
       <c r="R228" t="n">
-        <v>6705076</v>
+        <v>6704908</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -25759,38 +25745,47 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>127683156</v>
+        <v>127683183</v>
       </c>
       <c r="B229" t="n">
-        <v>57669</v>
+        <v>98470</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E229" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I229" t="inlineStr"/>
-      <c r="M229" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J229" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P229" t="inlineStr">
@@ -25799,10 +25794,10 @@
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>564124</v>
+        <v>564023</v>
       </c>
       <c r="R229" t="n">
-        <v>6705171</v>
+        <v>6705072</v>
       </c>
       <c r="S229" t="n">
         <v>10</v>
@@ -25835,6 +25830,11 @@
       <c r="AA229" t="inlineStr">
         <is>
           <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AC229" t="inlineStr">
+        <is>
+          <t>2 blomstjälkar</t>
         </is>
       </c>
       <c r="AD229" t="b">
@@ -26060,32 +26060,32 @@
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>127683173</v>
+        <v>127683203</v>
       </c>
       <c r="B232" t="n">
-        <v>95326</v>
+        <v>91753</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E232" t="n">
-        <v>2387</v>
+        <v>715</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Finporing</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Gloeoporus pannocinctus</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(Romell) J.Erikss.</t>
         </is>
       </c>
       <c r="I232" t="inlineStr"/>
@@ -26095,10 +26095,10 @@
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>563865</v>
+        <v>563955</v>
       </c>
       <c r="R232" t="n">
-        <v>6704888</v>
+        <v>6704996</v>
       </c>
       <c r="S232" t="n">
         <v>10</v>
@@ -26131,11 +26131,6 @@
       <c r="AA232" t="inlineStr">
         <is>
           <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="AC232" t="inlineStr">
-        <is>
-          <t>I källdråg utan planerad hänsyn</t>
         </is>
       </c>
       <c r="AD232" t="b">
@@ -26162,32 +26157,32 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>127683203</v>
+        <v>127683173</v>
       </c>
       <c r="B233" t="n">
-        <v>91753</v>
+        <v>95326</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E233" t="n">
-        <v>715</v>
+        <v>2387</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Finporing</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Gloeoporus pannocinctus</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>(Romell) J.Erikss.</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I233" t="inlineStr"/>
@@ -26197,10 +26192,10 @@
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>563955</v>
+        <v>563865</v>
       </c>
       <c r="R233" t="n">
-        <v>6704996</v>
+        <v>6704888</v>
       </c>
       <c r="S233" t="n">
         <v>10</v>
@@ -26233,6 +26228,11 @@
       <c r="AA233" t="inlineStr">
         <is>
           <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AC233" t="inlineStr">
+        <is>
+          <t>I källdråg utan planerad hänsyn</t>
         </is>
       </c>
       <c r="AD233" t="b">
@@ -26458,42 +26458,47 @@
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>127683152</v>
+        <v>127683188</v>
       </c>
       <c r="B236" t="n">
-        <v>92287</v>
+        <v>98470</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E236" t="n">
-        <v>4769</v>
+        <v>220787</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I236" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J236" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P236" t="inlineStr">
@@ -26502,10 +26507,10 @@
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>563895</v>
+        <v>563940</v>
       </c>
       <c r="R236" t="n">
-        <v>6704903</v>
+        <v>6704945</v>
       </c>
       <c r="S236" t="n">
         <v>10</v>
@@ -26564,10 +26569,10 @@
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>127683163</v>
+        <v>127683152</v>
       </c>
       <c r="B237" t="n">
-        <v>91124</v>
+        <v>92287</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -26575,34 +26580,43 @@
         </is>
       </c>
       <c r="E237" t="n">
-        <v>3215</v>
+        <v>4769</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I237" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I237" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J237" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P237" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>564121</v>
+        <v>563895</v>
       </c>
       <c r="R237" t="n">
-        <v>6705165</v>
+        <v>6704903</v>
       </c>
       <c r="S237" t="n">
         <v>10</v>
@@ -26635,11 +26649,6 @@
       <c r="AA237" t="inlineStr">
         <is>
           <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="AC237" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD237" t="b">
@@ -26666,59 +26675,45 @@
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>127683188</v>
+        <v>127683163</v>
       </c>
       <c r="B238" t="n">
-        <v>98470</v>
+        <v>91124</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E238" t="n">
-        <v>220787</v>
+        <v>3215</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I238" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J238" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K238" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I238" t="inlineStr"/>
       <c r="P238" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q238" t="n">
-        <v>563940</v>
+        <v>564121</v>
       </c>
       <c r="R238" t="n">
-        <v>6704945</v>
+        <v>6705165</v>
       </c>
       <c r="S238" t="n">
         <v>10</v>
@@ -26751,6 +26746,11 @@
       <c r="AA238" t="inlineStr">
         <is>
           <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AC238" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD238" t="b">
@@ -26883,10 +26883,10 @@
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>127683138</v>
+        <v>127683185</v>
       </c>
       <c r="B240" t="n">
-        <v>91710</v>
+        <v>98470</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -26894,34 +26894,48 @@
         </is>
       </c>
       <c r="E240" t="n">
-        <v>2062</v>
+        <v>220787</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I240" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I240" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J240" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K240" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P240" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>564145</v>
+        <v>564009</v>
       </c>
       <c r="R240" t="n">
-        <v>6705081</v>
+        <v>6705051</v>
       </c>
       <c r="S240" t="n">
         <v>10</v>
@@ -26980,10 +26994,10 @@
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>127683185</v>
+        <v>127683138</v>
       </c>
       <c r="B241" t="n">
-        <v>98470</v>
+        <v>91710</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -26991,48 +27005,34 @@
         </is>
       </c>
       <c r="E241" t="n">
-        <v>220787</v>
+        <v>2062</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I241" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J241" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K241" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I241" t="inlineStr"/>
       <c r="P241" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q241" t="n">
-        <v>564009</v>
+        <v>564145</v>
       </c>
       <c r="R241" t="n">
-        <v>6705051</v>
+        <v>6705081</v>
       </c>
       <c r="S241" t="n">
         <v>10</v>
@@ -27803,32 +27803,32 @@
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>127683151</v>
+        <v>127683141</v>
       </c>
       <c r="B249" t="n">
-        <v>92287</v>
+        <v>91352</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E249" t="n">
-        <v>4769</v>
+        <v>1202</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I249" t="inlineStr"/>
@@ -27838,10 +27838,10 @@
         </is>
       </c>
       <c r="Q249" t="n">
-        <v>563873</v>
+        <v>564130</v>
       </c>
       <c r="R249" t="n">
-        <v>6704890</v>
+        <v>6705091</v>
       </c>
       <c r="S249" t="n">
         <v>10</v>
@@ -27874,11 +27874,6 @@
       <c r="AA249" t="inlineStr">
         <is>
           <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="AC249" t="inlineStr">
-        <is>
-          <t>Intill källdråg utan planerad hänsyn</t>
         </is>
       </c>
       <c r="AD249" t="b">
@@ -27905,32 +27900,32 @@
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>127683141</v>
+        <v>127683151</v>
       </c>
       <c r="B250" t="n">
-        <v>91352</v>
+        <v>92287</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E250" t="n">
-        <v>1202</v>
+        <v>4769</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I250" t="inlineStr"/>
@@ -27940,10 +27935,10 @@
         </is>
       </c>
       <c r="Q250" t="n">
-        <v>564130</v>
+        <v>563873</v>
       </c>
       <c r="R250" t="n">
-        <v>6705091</v>
+        <v>6704890</v>
       </c>
       <c r="S250" t="n">
         <v>10</v>
@@ -27976,6 +27971,11 @@
       <c r="AA250" t="inlineStr">
         <is>
           <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AC250" t="inlineStr">
+        <is>
+          <t>Intill källdråg utan planerad hänsyn</t>
         </is>
       </c>
       <c r="AD250" t="b">
@@ -28691,50 +28691,45 @@
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>127683158</v>
+        <v>127683164</v>
       </c>
       <c r="B258" t="n">
-        <v>57669</v>
+        <v>91124</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E258" t="n">
-        <v>100049</v>
+        <v>3215</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I258" t="inlineStr"/>
-      <c r="M258" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P258" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q258" t="n">
-        <v>563970</v>
+        <v>564133</v>
       </c>
       <c r="R258" t="n">
-        <v>6704954</v>
+        <v>6705173</v>
       </c>
       <c r="S258" t="n">
         <v>10</v>
@@ -28793,40 +28788,35 @@
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>127683157</v>
+        <v>127683133</v>
       </c>
       <c r="B259" t="n">
-        <v>57669</v>
+        <v>91317</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E259" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I259" t="inlineStr"/>
-      <c r="M259" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P259" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
@@ -28895,45 +28885,50 @@
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>127683164</v>
+        <v>127683157</v>
       </c>
       <c r="B260" t="n">
-        <v>91124</v>
+        <v>57669</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E260" t="n">
-        <v>3215</v>
+        <v>100049</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I260" t="inlineStr"/>
+      <c r="M260" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P260" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q260" t="n">
-        <v>564133</v>
+        <v>564052</v>
       </c>
       <c r="R260" t="n">
-        <v>6705173</v>
+        <v>6705031</v>
       </c>
       <c r="S260" t="n">
         <v>10</v>
@@ -28992,45 +28987,50 @@
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>127683133</v>
+        <v>127683158</v>
       </c>
       <c r="B261" t="n">
-        <v>91317</v>
+        <v>57669</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E261" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I261" t="inlineStr"/>
+      <c r="M261" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P261" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q261" t="n">
-        <v>564052</v>
+        <v>563970</v>
       </c>
       <c r="R261" t="n">
-        <v>6705031</v>
+        <v>6704954</v>
       </c>
       <c r="S261" t="n">
         <v>10</v>
@@ -29089,32 +29089,32 @@
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>127683172</v>
+        <v>127683130</v>
       </c>
       <c r="B262" t="n">
-        <v>95326</v>
+        <v>91564</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E262" t="n">
-        <v>2387</v>
+        <v>1106</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I262" t="inlineStr"/>
@@ -29124,10 +29124,10 @@
         </is>
       </c>
       <c r="Q262" t="n">
-        <v>563914</v>
+        <v>564057</v>
       </c>
       <c r="R262" t="n">
-        <v>6704945</v>
+        <v>6705032</v>
       </c>
       <c r="S262" t="n">
         <v>10</v>
@@ -29160,11 +29160,6 @@
       <c r="AA262" t="inlineStr">
         <is>
           <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="AC262" t="inlineStr">
-        <is>
-          <t>I källdråg utan planerad hänsyn</t>
         </is>
       </c>
       <c r="AD262" t="b">
@@ -29191,32 +29186,32 @@
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>127683130</v>
+        <v>127683172</v>
       </c>
       <c r="B263" t="n">
-        <v>91564</v>
+        <v>95326</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E263" t="n">
-        <v>1106</v>
+        <v>2387</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I263" t="inlineStr"/>
@@ -29226,10 +29221,10 @@
         </is>
       </c>
       <c r="Q263" t="n">
-        <v>564057</v>
+        <v>563914</v>
       </c>
       <c r="R263" t="n">
-        <v>6705032</v>
+        <v>6704945</v>
       </c>
       <c r="S263" t="n">
         <v>10</v>
@@ -29262,6 +29257,11 @@
       <c r="AA263" t="inlineStr">
         <is>
           <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AC263" t="inlineStr">
+        <is>
+          <t>I källdråg utan planerad hänsyn</t>
         </is>
       </c>
       <c r="AD263" t="b">

--- a/artfynd/A 58548-2022 artfynd.xlsx
+++ b/artfynd/A 58548-2022 artfynd.xlsx
@@ -26458,47 +26458,42 @@
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>127683188</v>
+        <v>127683152</v>
       </c>
       <c r="B236" t="n">
-        <v>98470</v>
+        <v>92287</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E236" t="n">
-        <v>220787</v>
+        <v>4769</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I236" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J236" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K236" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P236" t="inlineStr">
@@ -26507,10 +26502,10 @@
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>563940</v>
+        <v>563895</v>
       </c>
       <c r="R236" t="n">
-        <v>6704945</v>
+        <v>6704903</v>
       </c>
       <c r="S236" t="n">
         <v>10</v>
@@ -26569,10 +26564,10 @@
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>127683152</v>
+        <v>127683163</v>
       </c>
       <c r="B237" t="n">
-        <v>92287</v>
+        <v>91124</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -26580,43 +26575,34 @@
         </is>
       </c>
       <c r="E237" t="n">
-        <v>4769</v>
+        <v>3215</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I237" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J237" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I237" t="inlineStr"/>
       <c r="P237" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>563895</v>
+        <v>564121</v>
       </c>
       <c r="R237" t="n">
-        <v>6704903</v>
+        <v>6705165</v>
       </c>
       <c r="S237" t="n">
         <v>10</v>
@@ -26649,6 +26635,11 @@
       <c r="AA237" t="inlineStr">
         <is>
           <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AC237" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD237" t="b">
@@ -26675,45 +26666,59 @@
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>127683163</v>
+        <v>127683188</v>
       </c>
       <c r="B238" t="n">
-        <v>91124</v>
+        <v>98470</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E238" t="n">
-        <v>3215</v>
+        <v>220787</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I238" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I238" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J238" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K238" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P238" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q238" t="n">
-        <v>564121</v>
+        <v>563940</v>
       </c>
       <c r="R238" t="n">
-        <v>6705165</v>
+        <v>6704945</v>
       </c>
       <c r="S238" t="n">
         <v>10</v>
@@ -26746,11 +26751,6 @@
       <c r="AA238" t="inlineStr">
         <is>
           <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="AC238" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD238" t="b">
@@ -26777,54 +26777,45 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>127683196</v>
+        <v>127683138</v>
       </c>
       <c r="B239" t="n">
-        <v>92676</v>
+        <v>91710</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E239" t="n">
-        <v>5964</v>
+        <v>2062</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I239" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J239" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I239" t="inlineStr"/>
       <c r="P239" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>564163</v>
+        <v>564145</v>
       </c>
       <c r="R239" t="n">
-        <v>6705180</v>
+        <v>6705081</v>
       </c>
       <c r="S239" t="n">
         <v>10</v>
@@ -26883,47 +26874,42 @@
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>127683185</v>
+        <v>127683196</v>
       </c>
       <c r="B240" t="n">
-        <v>98470</v>
+        <v>92676</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E240" t="n">
-        <v>220787</v>
+        <v>5964</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I240" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J240" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K240" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P240" t="inlineStr">
@@ -26932,10 +26918,10 @@
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>564009</v>
+        <v>564163</v>
       </c>
       <c r="R240" t="n">
-        <v>6705051</v>
+        <v>6705180</v>
       </c>
       <c r="S240" t="n">
         <v>10</v>
@@ -26994,10 +26980,10 @@
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>127683138</v>
+        <v>127683185</v>
       </c>
       <c r="B241" t="n">
-        <v>91710</v>
+        <v>98470</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -27005,34 +26991,48 @@
         </is>
       </c>
       <c r="E241" t="n">
-        <v>2062</v>
+        <v>220787</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I241" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I241" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J241" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K241" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P241" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q241" t="n">
-        <v>564145</v>
+        <v>564009</v>
       </c>
       <c r="R241" t="n">
-        <v>6705081</v>
+        <v>6705051</v>
       </c>
       <c r="S241" t="n">
         <v>10</v>
@@ -27188,45 +27188,50 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>127683162</v>
+        <v>127683149</v>
       </c>
       <c r="B243" t="n">
-        <v>95714</v>
+        <v>57832</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E243" t="n">
-        <v>2813</v>
+        <v>103021</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I243" t="inlineStr"/>
+      <c r="M243" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P243" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>563934</v>
+        <v>564082</v>
       </c>
       <c r="R243" t="n">
-        <v>6704860</v>
+        <v>6705145</v>
       </c>
       <c r="S243" t="n">
         <v>10</v>
@@ -27285,50 +27290,45 @@
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>127683149</v>
+        <v>127683162</v>
       </c>
       <c r="B244" t="n">
-        <v>57832</v>
+        <v>95714</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E244" t="n">
-        <v>103021</v>
+        <v>2813</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I244" t="inlineStr"/>
-      <c r="M244" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P244" t="inlineStr">
         <is>
           <t>Pellkärret, Dlr</t>
         </is>
       </c>
       <c r="Q244" t="n">
-        <v>564082</v>
+        <v>563934</v>
       </c>
       <c r="R244" t="n">
-        <v>6705145</v>
+        <v>6704860</v>
       </c>
       <c r="S244" t="n">
         <v>10</v>
@@ -28002,32 +28002,32 @@
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>127683139</v>
+        <v>127683200</v>
       </c>
       <c r="B251" t="n">
-        <v>91710</v>
+        <v>100652</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E251" t="n">
-        <v>2062</v>
+        <v>222498</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I251" t="inlineStr"/>
@@ -28037,10 +28037,10 @@
         </is>
       </c>
       <c r="Q251" t="n">
-        <v>563999</v>
+        <v>563890</v>
       </c>
       <c r="R251" t="n">
-        <v>6705007</v>
+        <v>6704897</v>
       </c>
       <c r="S251" t="n">
         <v>10</v>
@@ -28099,32 +28099,32 @@
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>127683199</v>
+        <v>127683139</v>
       </c>
       <c r="B252" t="n">
-        <v>95321</v>
+        <v>91710</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E252" t="n">
-        <v>2383</v>
+        <v>2062</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Bågpraktmossa</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>Plagiomnium medium</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>(Bruch &amp; Schimp.) T.J.Kop.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I252" t="inlineStr"/>
@@ -28134,10 +28134,10 @@
         </is>
       </c>
       <c r="Q252" t="n">
-        <v>564058</v>
+        <v>563999</v>
       </c>
       <